--- a/data/Airline-World-Workbook.xlsx
+++ b/data/Airline-World-Workbook.xlsx
@@ -1,29 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapters" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HandSumRules" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Archetypes" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Routes" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RouteCatalogue" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aircraft" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Finance" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Airports" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calendar" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Market" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Events" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Challenges" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mechanics" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catering" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hunts" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Chapters" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="HandSumRules" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Settings" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Archetypes" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Routes" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="RouteCatalogue" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Aircraft" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Finance" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Airports" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Calendar" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Market" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Events" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Challenges" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Mechanics" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Catering" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Livery" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Hunts" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -133,7 +134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -197,6 +198,13 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -562,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -641,7 +649,7 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>SHEETS: Settings · Chapters · HandSumRules · Calendar (days 1–21) · Market (weeks 1–416) · Events · Routes · RouteCatalogue · Archetypes · Aircraft · Finance · Catering · Airports · Challenges · Hunts · Mechanics.</t>
+          <t>SHEETS: Settings · Chapters · HandSumRules · Calendar (days 1–21) · Market (weeks 1–416) · Events · Routes · RouteCatalogue · Archetypes · Aircraft · Finance · Catering · Airports · Challenges · Hunts · Mechanics. · Livery</t>
         </is>
       </c>
     </row>
@@ -677,6 +685,13 @@
       <c r="A16" s="10" t="inlineStr">
         <is>
           <t>v4.2 (6 Oct, late): STATUS FIX. Everything dated inside chapter 1 (to 28 Dec 2030) is now live: Market weeks 4–17 (the fuel climb, the spike, the oil find, the first winter seasons), the chapter-1 events (fuel_shock, fault, football_final, price_war, oil_find, first_snow, christmas, new_year), and the A220, A320 and 737 in the shop from day 50. The rule stays: Claude Code loads live rows only. Placeholder now means 'chapter 2 onwards, not yet designed'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>v4.3 draft (7 Oct, Claude Code, for Fable to adopt): Change Request 5. New sheet Livery (palette, stripes, tail symbols, logo shapes, plane-name suggestions); Aircraft columns artworkId and photoFile/Credit/Licence/Source; Settings blockedFlightCodes, soundDefault, revealSeconds. Everything the pupil chooses (airline name, flight code, logo, each plane's registration, name and livery) lives in the save state, not here.</t>
         </is>
       </c>
     </row>
@@ -22602,6 +22617,975 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>kind</t>
+        </is>
+      </c>
+      <c r="B1" s="24" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C1" s="24" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" s="24" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E1" s="24" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="F1" s="24" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="23" t="inlineStr">
+        <is>
+          <t>colour</t>
+        </is>
+      </c>
+      <c r="B2" s="23" t="inlineStr">
+        <is>
+          <t>white</t>
+        </is>
+      </c>
+      <c r="C2" s="23" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+      <c r="D2" s="23" t="inlineStr">
+        <is>
+          <t>#F4F6F8</t>
+        </is>
+      </c>
+      <c r="E2" s="23" t="inlineStr">
+        <is>
+          <t>Twelve-colour palette for every paintable layer and the logo (CR5).</t>
+        </is>
+      </c>
+      <c r="F2" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="23" t="inlineStr">
+        <is>
+          <t>colour</t>
+        </is>
+      </c>
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>navy</t>
+        </is>
+      </c>
+      <c r="C3" s="23" t="inlineStr">
+        <is>
+          <t>Navy</t>
+        </is>
+      </c>
+      <c r="D3" s="23" t="inlineStr">
+        <is>
+          <t>#1B2A4A</t>
+        </is>
+      </c>
+      <c r="E3" s="23" t="inlineStr"/>
+      <c r="F3" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="23" t="inlineStr">
+        <is>
+          <t>colour</t>
+        </is>
+      </c>
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="C4" s="23" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="D4" s="23" t="inlineStr">
+        <is>
+          <t>#D7263D</t>
+        </is>
+      </c>
+      <c r="E4" s="23" t="inlineStr"/>
+      <c r="F4" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="23" t="inlineStr">
+        <is>
+          <t>colour</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="D5" s="23" t="inlineStr">
+        <is>
+          <t>#F46036</t>
+        </is>
+      </c>
+      <c r="E5" s="23" t="inlineStr"/>
+      <c r="F5" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="23" t="inlineStr">
+        <is>
+          <t>colour</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>yellow</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>#F2C14E</t>
+        </is>
+      </c>
+      <c r="E6" s="23" t="inlineStr"/>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="23" t="inlineStr">
+        <is>
+          <t>colour</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="D7" s="23" t="inlineStr">
+        <is>
+          <t>#2E8B57</t>
+        </is>
+      </c>
+      <c r="E7" s="23" t="inlineStr"/>
+      <c r="F7" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>colour</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>teal</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>Teal</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>#1B998B</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="inlineStr"/>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="23" t="inlineStr">
+        <is>
+          <t>colour</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>sky</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>Sky</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>#3FA7D6</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="inlineStr"/>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t>colour</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>purple</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>Purple</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>#6A4C93</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="inlineStr"/>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="23" t="inlineStr">
+        <is>
+          <t>colour</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>pink</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>Pink</t>
+        </is>
+      </c>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t>#E56399</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="inlineStr"/>
+      <c r="F11" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>colour</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>silver</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>#A9B4C2</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="inlineStr"/>
+      <c r="F12" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="23" t="inlineStr">
+        <is>
+          <t>colour</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>black</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="D13" s="23" t="inlineStr">
+        <is>
+          <t>#1E1E24</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="inlineStr"/>
+      <c r="F13" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="23" t="inlineStr">
+        <is>
+          <t>stripe</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr"/>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>Stripe styles along the fuselage, in the second colour.</t>
+        </is>
+      </c>
+      <c r="F14" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="23" t="inlineStr">
+        <is>
+          <t>stripe</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>thin</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>Thin line</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="inlineStr"/>
+      <c r="E15" s="23" t="inlineStr"/>
+      <c r="F15" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="23" t="inlineStr">
+        <is>
+          <t>stripe</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>band</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>Bold band</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="inlineStr"/>
+      <c r="E16" s="23" t="inlineStr"/>
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="23" t="inlineStr">
+        <is>
+          <t>stripe</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>swoosh</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
+        <is>
+          <t>Swoosh</t>
+        </is>
+      </c>
+      <c r="D17" s="23" t="inlineStr"/>
+      <c r="E17" s="23" t="inlineStr"/>
+      <c r="F17" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="23" t="inlineStr">
+        <is>
+          <t>tail</t>
+        </is>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>stripe</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="inlineStr"/>
+      <c r="E18" s="23" t="inlineStr">
+        <is>
+          <t>Tail-fin symbols, in the second colour. "logo" draws the airline logo on the fin.</t>
+        </is>
+      </c>
+      <c r="F18" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="23" t="inlineStr">
+        <is>
+          <t>tail</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>star</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>Star</t>
+        </is>
+      </c>
+      <c r="D19" s="23" t="inlineStr"/>
+      <c r="E19" s="23" t="inlineStr"/>
+      <c r="F19" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="23" t="inlineStr">
+        <is>
+          <t>tail</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>chevron</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="D20" s="23" t="inlineStr"/>
+      <c r="E20" s="23" t="inlineStr"/>
+      <c r="F20" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="23" t="inlineStr">
+        <is>
+          <t>tail</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>wave</t>
+        </is>
+      </c>
+      <c r="C21" s="23" t="inlineStr">
+        <is>
+          <t>Wave</t>
+        </is>
+      </c>
+      <c r="D21" s="23" t="inlineStr"/>
+      <c r="E21" s="23" t="inlineStr"/>
+      <c r="F21" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="23" t="inlineStr">
+        <is>
+          <t>tail</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>circle</t>
+        </is>
+      </c>
+      <c r="C22" s="23" t="inlineStr">
+        <is>
+          <t>Circle</t>
+        </is>
+      </c>
+      <c r="D22" s="23" t="inlineStr"/>
+      <c r="E22" s="23" t="inlineStr"/>
+      <c r="F22" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="23" t="inlineStr">
+        <is>
+          <t>tail</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>arrow</t>
+        </is>
+      </c>
+      <c r="C23" s="23" t="inlineStr">
+        <is>
+          <t>Arrow</t>
+        </is>
+      </c>
+      <c r="D23" s="23" t="inlineStr"/>
+      <c r="E23" s="23" t="inlineStr"/>
+      <c r="F23" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="23" t="inlineStr">
+        <is>
+          <t>tail</t>
+        </is>
+      </c>
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>logo</t>
+        </is>
+      </c>
+      <c r="C24" s="23" t="inlineStr">
+        <is>
+          <t>Your logo</t>
+        </is>
+      </c>
+      <c r="D24" s="23" t="inlineStr"/>
+      <c r="E24" s="23" t="inlineStr"/>
+      <c r="F24" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="23" t="inlineStr">
+        <is>
+          <t>logoShape</t>
+        </is>
+      </c>
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>square</t>
+        </is>
+      </c>
+      <c r="C25" s="23" t="inlineStr">
+        <is>
+          <t>Square</t>
+        </is>
+      </c>
+      <c r="D25" s="23" t="inlineStr"/>
+      <c r="E25" s="23" t="inlineStr">
+        <is>
+          <t>Logo backgrounds: shape × symbol (the tail set) × two colours.</t>
+        </is>
+      </c>
+      <c r="F25" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="23" t="inlineStr">
+        <is>
+          <t>logoShape</t>
+        </is>
+      </c>
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>circle</t>
+        </is>
+      </c>
+      <c r="C26" s="23" t="inlineStr">
+        <is>
+          <t>Circle</t>
+        </is>
+      </c>
+      <c r="D26" s="23" t="inlineStr"/>
+      <c r="E26" s="23" t="inlineStr"/>
+      <c r="F26" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="23" t="inlineStr">
+        <is>
+          <t>logoShape</t>
+        </is>
+      </c>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>shield</t>
+        </is>
+      </c>
+      <c r="C27" s="23" t="inlineStr">
+        <is>
+          <t>Shield</t>
+        </is>
+      </c>
+      <c r="D27" s="23" t="inlineStr"/>
+      <c r="E27" s="23" t="inlineStr"/>
+      <c r="F27" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="23" t="inlineStr">
+        <is>
+          <t>logoShape</t>
+        </is>
+      </c>
+      <c r="B28" s="23" t="inlineStr">
+        <is>
+          <t>fin</t>
+        </is>
+      </c>
+      <c r="C28" s="23" t="inlineStr">
+        <is>
+          <t>Tail fin</t>
+        </is>
+      </c>
+      <c r="D28" s="23" t="inlineStr"/>
+      <c r="E28" s="23" t="inlineStr"/>
+      <c r="F28" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="23" t="inlineStr">
+        <is>
+          <t>planeName</t>
+        </is>
+      </c>
+      <c r="B29" s="23" t="inlineStr">
+        <is>
+          <t>spirit</t>
+        </is>
+      </c>
+      <c r="C29" s="23" t="inlineStr">
+        <is>
+          <t>Spirit of Wales</t>
+        </is>
+      </c>
+      <c r="D29" s="23" t="inlineStr"/>
+      <c r="E29" s="23" t="inlineStr">
+        <is>
+          <t>Tap-to-use suggestions on the Name it tab; four are offered at a time.</t>
+        </is>
+      </c>
+      <c r="F29" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="23" t="inlineStr">
+        <is>
+          <t>planeName</t>
+        </is>
+      </c>
+      <c r="B30" s="23" t="inlineStr">
+        <is>
+          <t>cloud</t>
+        </is>
+      </c>
+      <c r="C30" s="23" t="inlineStr">
+        <is>
+          <t>Cloud Runner</t>
+        </is>
+      </c>
+      <c r="D30" s="23" t="inlineStr"/>
+      <c r="E30" s="23" t="inlineStr"/>
+      <c r="F30" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="23" t="inlineStr">
+        <is>
+          <t>planeName</t>
+        </is>
+      </c>
+      <c r="B31" s="23" t="inlineStr">
+        <is>
+          <t>dragon</t>
+        </is>
+      </c>
+      <c r="C31" s="23" t="inlineStr">
+        <is>
+          <t>Red Dragon</t>
+        </is>
+      </c>
+      <c r="D31" s="23" t="inlineStr"/>
+      <c r="E31" s="23" t="inlineStr"/>
+      <c r="F31" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="23" t="inlineStr">
+        <is>
+          <t>planeName</t>
+        </is>
+      </c>
+      <c r="B32" s="23" t="inlineStr">
+        <is>
+          <t>hopper</t>
+        </is>
+      </c>
+      <c r="C32" s="23" t="inlineStr">
+        <is>
+          <t>Sky Hopper</t>
+        </is>
+      </c>
+      <c r="D32" s="23" t="inlineStr"/>
+      <c r="E32" s="23" t="inlineStr"/>
+      <c r="F32" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="23" t="inlineStr">
+        <is>
+          <t>planeName</t>
+        </is>
+      </c>
+      <c r="B33" s="23" t="inlineStr">
+        <is>
+          <t>star</t>
+        </is>
+      </c>
+      <c r="C33" s="23" t="inlineStr">
+        <is>
+          <t>Morning Star</t>
+        </is>
+      </c>
+      <c r="D33" s="23" t="inlineStr"/>
+      <c r="E33" s="23" t="inlineStr"/>
+      <c r="F33" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="23" t="inlineStr">
+        <is>
+          <t>planeName</t>
+        </is>
+      </c>
+      <c r="B34" s="23" t="inlineStr">
+        <is>
+          <t>severn</t>
+        </is>
+      </c>
+      <c r="C34" s="23" t="inlineStr">
+        <is>
+          <t>Severn Breeze</t>
+        </is>
+      </c>
+      <c r="D34" s="23" t="inlineStr"/>
+      <c r="E34" s="23" t="inlineStr"/>
+      <c r="F34" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="23" t="inlineStr">
+        <is>
+          <t>planeName</t>
+        </is>
+      </c>
+      <c r="B35" s="23" t="inlineStr">
+        <is>
+          <t>comet</t>
+        </is>
+      </c>
+      <c r="C35" s="23" t="inlineStr">
+        <is>
+          <t>Little Comet</t>
+        </is>
+      </c>
+      <c r="D35" s="23" t="inlineStr"/>
+      <c r="E35" s="23" t="inlineStr"/>
+      <c r="F35" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="23" t="inlineStr">
+        <is>
+          <t>planeName</t>
+        </is>
+      </c>
+      <c r="B36" s="23" t="inlineStr">
+        <is>
+          <t>wren</t>
+        </is>
+      </c>
+      <c r="C36" s="23" t="inlineStr">
+        <is>
+          <t>Jenny Wren</t>
+        </is>
+      </c>
+      <c r="D36" s="23" t="inlineStr"/>
+      <c r="E36" s="23" t="inlineStr"/>
+      <c r="F36" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Note: the game reads live rows only. Colours are hex; stripe, tail and logoShape ids match the artwork layers; planeName ids are only there so a row can be referred to.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -23689,7 +24673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -24721,6 +25705,70 @@
         </is>
       </c>
       <c r="D49" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="23" t="inlineStr">
+        <is>
+          <t>blockedFlightCodes</t>
+        </is>
+      </c>
+      <c r="B50" s="23" t="inlineStr">
+        <is>
+          <t>BA, EZ, FR, VS, LH, AF, KL, U2</t>
+        </is>
+      </c>
+      <c r="C50" s="23" t="inlineStr">
+        <is>
+          <t>CR5. Real airline codes the pupil cannot pick; refused calmly ("That code belongs to a real airline, try another").</t>
+        </is>
+      </c>
+      <c r="D50" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="23" t="inlineStr">
+        <is>
+          <t>soundDefault</t>
+        </is>
+      </c>
+      <c r="B51" s="23" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="C51" s="23" t="inlineStr">
+        <is>
+          <t>CR5. Sound (take-off, airport chimes, announcements) is off until the teacher turns it on; a mute control sits in the top bar.</t>
+        </is>
+      </c>
+      <c r="D51" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="23" t="inlineStr">
+        <is>
+          <t>revealSeconds</t>
+        </is>
+      </c>
+      <c r="B52" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="C52" s="23" t="inlineStr">
+        <is>
+          <t>CR5. The hangar reveal on launch day: doors close, open, the plane rolls in. Later planes get about half.</t>
+        </is>
+      </c>
+      <c r="D52" s="23" t="inlineStr">
         <is>
           <t>live</t>
         </is>
@@ -28131,7 +29179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -28147,7 +29195,11 @@
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="60" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="26" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="40" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -28216,7 +29268,32 @@
           <t>identity</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="N1" s="24" t="inlineStr">
+        <is>
+          <t>artworkId</t>
+        </is>
+      </c>
+      <c r="O1" s="24" t="inlineStr">
+        <is>
+          <t>photoFile</t>
+        </is>
+      </c>
+      <c r="P1" s="24" t="inlineStr">
+        <is>
+          <t>photoCredit</t>
+        </is>
+      </c>
+      <c r="Q1" s="24" t="inlineStr">
+        <is>
+          <t>photoLicence</t>
+        </is>
+      </c>
+      <c r="R1" s="24" t="inlineStr">
+        <is>
+          <t>photoSource</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
         <is>
           <t>status</t>
         </is>
@@ -28270,7 +29347,16 @@
           <t>Small, flexible, cheap. Fits any route. Slow on long legs.</t>
         </is>
       </c>
-      <c r="N2" s="12" t="inlineStr">
+      <c r="N2" s="23" t="inlineStr">
+        <is>
+          <t>dhc6</t>
+        </is>
+      </c>
+      <c r="O2" s="23" t="n"/>
+      <c r="P2" s="23" t="n"/>
+      <c r="Q2" s="23" t="n"/>
+      <c r="R2" s="23" t="n"/>
+      <c r="S2" s="12" t="inlineStr">
         <is>
           <t>live</t>
         </is>
@@ -28322,7 +29408,16 @@
           <t>More seats and faster: Dublin and Amsterdam fit it. Half-empty on Paris.</t>
         </is>
       </c>
-      <c r="N3" s="12" t="inlineStr">
+      <c r="N3" s="23" t="inlineStr">
+        <is>
+          <t>sf34</t>
+        </is>
+      </c>
+      <c r="O3" s="23" t="n"/>
+      <c r="P3" s="23" t="n"/>
+      <c r="Q3" s="23" t="n"/>
+      <c r="R3" s="23" t="n"/>
+      <c r="S3" s="12" t="inlineStr">
         <is>
           <t>live</t>
         </is>
@@ -28374,7 +29469,16 @@
           <t>Biggest short-haul. Cheapest per seat. Only pays on busy routes; just reaches Madrid (1,350 of 1,500 km).</t>
         </is>
       </c>
-      <c r="N4" s="12" t="inlineStr">
+      <c r="N4" s="23" t="inlineStr">
+        <is>
+          <t>at72</t>
+        </is>
+      </c>
+      <c r="O4" s="23" t="n"/>
+      <c r="P4" s="23" t="n"/>
+      <c r="Q4" s="23" t="n"/>
+      <c r="R4" s="23" t="n"/>
+      <c r="S4" s="12" t="inlineStr">
         <is>
           <t>live</t>
         </is>
@@ -28426,7 +29530,16 @@
           <t>First jet: speed and range. Opens every medium-haul route the ATR cannot reach. Tutorial price.</t>
         </is>
       </c>
-      <c r="N5" s="12" t="inlineStr">
+      <c r="N5" s="23" t="inlineStr">
+        <is>
+          <t>e190</t>
+        </is>
+      </c>
+      <c r="O5" s="23" t="n"/>
+      <c r="P5" s="23" t="n"/>
+      <c r="Q5" s="23" t="n"/>
+      <c r="R5" s="23" t="n"/>
+      <c r="S5" s="12" t="inlineStr">
         <is>
           <t>live</t>
         </is>
@@ -28478,7 +29591,16 @@
           <t>The first plane priced like a real jet. Leased or saved for.</t>
         </is>
       </c>
-      <c r="N6" s="12" t="inlineStr">
+      <c r="N6" s="23" t="inlineStr">
+        <is>
+          <t>narrowbody</t>
+        </is>
+      </c>
+      <c r="O6" s="23" t="n"/>
+      <c r="P6" s="23" t="n"/>
+      <c r="Q6" s="23" t="n"/>
+      <c r="R6" s="23" t="n"/>
+      <c r="S6" s="12" t="inlineStr">
         <is>
           <t>live</t>
         </is>
@@ -28530,7 +29652,16 @@
           <t>The one he named ('an Airbus'). Rome, Athens, Istanbul.</t>
         </is>
       </c>
-      <c r="N7" s="12" t="inlineStr">
+      <c r="N7" s="23" t="inlineStr">
+        <is>
+          <t>narrowbody</t>
+        </is>
+      </c>
+      <c r="O7" s="23" t="n"/>
+      <c r="P7" s="23" t="n"/>
+      <c r="Q7" s="23" t="n"/>
+      <c r="R7" s="23" t="n"/>
+      <c r="S7" s="12" t="inlineStr">
         <is>
           <t>live</t>
         </is>
@@ -28582,7 +29713,16 @@
           <t>Named by the pupil. Same numbers as the A320: the choice is taste, as in real life.</t>
         </is>
       </c>
-      <c r="N8" s="12" t="inlineStr">
+      <c r="N8" s="23" t="inlineStr">
+        <is>
+          <t>narrowbody</t>
+        </is>
+      </c>
+      <c r="O8" s="23" t="n"/>
+      <c r="P8" s="23" t="n"/>
+      <c r="Q8" s="23" t="n"/>
+      <c r="R8" s="23" t="n"/>
+      <c r="S8" s="12" t="inlineStr">
         <is>
           <t>live</t>
         </is>
@@ -28634,7 +29774,12 @@
           <t>Named by the pupil. Opens long haul, January 2031, by lease; bought outright from chapter 3.</t>
         </is>
       </c>
-      <c r="N9" s="15" t="inlineStr">
+      <c r="N9" s="25" t="n"/>
+      <c r="O9" s="25" t="n"/>
+      <c r="P9" s="25" t="n"/>
+      <c r="Q9" s="25" t="n"/>
+      <c r="R9" s="25" t="n"/>
+      <c r="S9" s="15" t="inlineStr">
         <is>
           <t>later</t>
         </is>
@@ -28686,7 +29831,12 @@
           <t>Range for Sydney. Chapter 3.</t>
         </is>
       </c>
-      <c r="N10" s="15" t="inlineStr">
+      <c r="N10" s="25" t="n"/>
+      <c r="O10" s="25" t="n"/>
+      <c r="P10" s="25" t="n"/>
+      <c r="Q10" s="25" t="n"/>
+      <c r="R10" s="25" t="n"/>
+      <c r="S10" s="15" t="inlineStr">
         <is>
           <t>later</t>
         </is>
@@ -28738,7 +29888,12 @@
           <t>Named by the pupil. The Jumbo: roomy, thirsty. Chapter 4.</t>
         </is>
       </c>
-      <c r="N11" s="15" t="inlineStr">
+      <c r="N11" s="25" t="n"/>
+      <c r="O11" s="25" t="n"/>
+      <c r="P11" s="25" t="n"/>
+      <c r="Q11" s="25" t="n"/>
+      <c r="R11" s="25" t="n"/>
+      <c r="S11" s="15" t="inlineStr">
         <is>
           <t>later</t>
         </is>
@@ -28790,7 +29945,12 @@
           <t>'The ultimate plane.' Chapter 4's new idea: financed, not bought. Only fills on the busiest route with a strong reputation.</t>
         </is>
       </c>
-      <c r="N12" s="15" t="inlineStr">
+      <c r="N12" s="25" t="n"/>
+      <c r="O12" s="25" t="n"/>
+      <c r="P12" s="25" t="n"/>
+      <c r="Q12" s="25" t="n"/>
+      <c r="R12" s="25" t="n"/>
+      <c r="S12" s="15" t="inlineStr">
         <is>
           <t>later</t>
         </is>
@@ -28842,7 +30002,12 @@
           <t>Removed 6 Oct (D41).</t>
         </is>
       </c>
-      <c r="N13" s="19" t="inlineStr">
+      <c r="N13" s="26" t="n"/>
+      <c r="O13" s="26" t="n"/>
+      <c r="P13" s="26" t="n"/>
+      <c r="Q13" s="26" t="n"/>
+      <c r="R13" s="26" t="n"/>
+      <c r="S13" s="19" t="inlineStr">
         <is>
           <t>removed</t>
         </is>
@@ -28895,7 +30060,16 @@
           <t>The smaller, cheaper first jet. Beats the E190 on smaller pools (Marrakech). Tutorial price.</t>
         </is>
       </c>
-      <c r="N15" s="13" t="inlineStr">
+      <c r="N15" s="23" t="inlineStr">
+        <is>
+          <t>e175</t>
+        </is>
+      </c>
+      <c r="O15" s="23" t="n"/>
+      <c r="P15" s="23" t="n"/>
+      <c r="Q15" s="23" t="n"/>
+      <c r="R15" s="23" t="n"/>
+      <c r="S15" s="13" t="inlineStr">
         <is>
           <t>live</t>
         </is>
@@ -28947,7 +30121,12 @@
           <t>Long and narrow with big engines: reaches New York with fewer seats than a widebody. The cheap way into long haul. Chapter 2, by lease.</t>
         </is>
       </c>
-      <c r="N16" s="14" t="inlineStr">
+      <c r="N16" s="27" t="n"/>
+      <c r="O16" s="27" t="n"/>
+      <c r="P16" s="27" t="n"/>
+      <c r="Q16" s="27" t="n"/>
+      <c r="R16" s="27" t="n"/>
+      <c r="S16" s="14" t="inlineStr">
         <is>
           <t>placeholder</t>
         </is>
@@ -28999,7 +30178,12 @@
           <t>Four engines make it thirsty for its size; a bargain when fuel is cheap, a trap when it is dear. Chapter 3.</t>
         </is>
       </c>
-      <c r="N17" s="18" t="inlineStr">
+      <c r="N17" s="25" t="n"/>
+      <c r="O17" s="25" t="n"/>
+      <c r="P17" s="25" t="n"/>
+      <c r="Q17" s="25" t="n"/>
+      <c r="R17" s="25" t="n"/>
+      <c r="S17" s="18" t="inlineStr">
         <is>
           <t>later</t>
         </is>
@@ -29051,7 +30235,12 @@
           <t>The biggest twin: the long-haul workhorse. Chapter 3.</t>
         </is>
       </c>
-      <c r="N18" s="18" t="inlineStr">
+      <c r="N18" s="25" t="n"/>
+      <c r="O18" s="25" t="n"/>
+      <c r="P18" s="25" t="n"/>
+      <c r="Q18" s="25" t="n"/>
+      <c r="R18" s="25" t="n"/>
+      <c r="S18" s="18" t="inlineStr">
         <is>
           <t>later</t>
         </is>
@@ -29062,6 +30251,13 @@
       <c r="A20" s="17" t="inlineStr">
         <is>
           <t>Prices from the A220 up are tuned to the cash curve (F5, replacing D16's three-tenths rule): on the Steady path each plane is a few lessons of saving away when it is meant to arrive. Tutorial planes (Twin Otter to E190, E175) keep launch-deal prices. Real prices are on the plane card for interest only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>v4.3 draft (CR5): artworkId names the painted side-view drawing (narrowbody is a stand-in until the A220, A320 and 737 are drawn); photo* record the showroom photo: file name under src/opening/assets/photos, author, licence, source URL. Openly licensed only, plain or maker colours.</t>
         </is>
       </c>
     </row>
@@ -29891,7 +31087,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
       <c r="A18" s="17" t="inlineStr">
         <is>

--- a/data/Airline-World-Workbook.xlsx
+++ b/data/Airline-World-Workbook.xlsx
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -692,6 +692,13 @@
       <c r="A17" t="inlineStr">
         <is>
           <t>v4.3 draft (7 Oct, Claude Code, for Fable to adopt): Change Request 5. New sheet Livery (palette, stripes, tail symbols, logo shapes, plane-name suggestions); Aircraft columns artworkId and photoFile/Credit/Licence/Source; Settings blockedFlightCodes, soundDefault, revealSeconds. Everything the pupil chooses (airline name, flight code, logo, each plane's registration, name and livery) lives in the save state, not here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>v4.3 draft (8 Oct, Claude Code, for Fable to adopt): Week-1 review. Settings crewFromDate (crew duty waits for the airline-type choice; the Calendar day-5 "crew duty" mechanic is ignored before it, so the row can stay until it is moved).</t>
         </is>
       </c>
     </row>
@@ -24673,7 +24680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -25769,6 +25776,28 @@
         </is>
       </c>
       <c r="D52" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="23" t="inlineStr">
+        <is>
+          <t>crewFromDate</t>
+        </is>
+      </c>
+      <c r="B53" s="23" t="inlineStr">
+        <is>
+          <t>2031-01-06</t>
+        </is>
+      </c>
+      <c r="C53" s="23" t="inlineStr">
+        <is>
+          <t>Week-1 review (8 Oct). Crew duty (the 12-hour day and the second crew) is switched off before this date: no briefing, no cost, no crews line. Set to the day the airline type is chosen (chapter 2). The Calendar day-5 mechanic "crew duty" is ignored before it.</t>
+        </is>
+      </c>
+      <c r="D53" s="23" t="inlineStr">
         <is>
           <t>live</t>
         </is>
@@ -30013,7 +30042,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
         <is>
@@ -30246,7 +30274,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="A20" s="17" t="inlineStr">
         <is>

--- a/data/Airline-World-Workbook.xlsx
+++ b/data/Airline-World-Workbook.xlsx
@@ -1,30 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Chapters" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="HandSumRules" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Settings" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Archetypes" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Routes" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="RouteCatalogue" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Aircraft" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Finance" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Airports" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Calendar" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Market" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Events" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Challenges" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Mechanics" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Catering" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Livery" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Hunts" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapters" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HandSumRules" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Archetypes" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Routes" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RouteCatalogue" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aircraft" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Finance" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Airports" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calendar" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Market" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Events" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Challenges" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mechanics" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catering" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Livery" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hunts" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -29384,7 +29384,11 @@
       <c r="O2" s="23" t="n"/>
       <c r="P2" s="23" t="n"/>
       <c r="Q2" s="23" t="n"/>
-      <c r="R2" s="23" t="n"/>
+      <c r="R2" s="23" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:First_Flight_Twin_Otter_Series_400_C-FDHT.jpg</t>
+        </is>
+      </c>
       <c r="S2" s="12" t="inlineStr">
         <is>
           <t>live</t>
@@ -29445,7 +29449,11 @@
       <c r="O3" s="23" t="n"/>
       <c r="P3" s="23" t="n"/>
       <c r="Q3" s="23" t="n"/>
-      <c r="R3" s="23" t="n"/>
+      <c r="R3" s="23" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Saab-Fairchild_340_in_flight.jpg</t>
+        </is>
+      </c>
       <c r="S3" s="12" t="inlineStr">
         <is>
           <t>live</t>
@@ -29506,7 +29514,11 @@
       <c r="O4" s="23" t="n"/>
       <c r="P4" s="23" t="n"/>
       <c r="Q4" s="23" t="n"/>
-      <c r="R4" s="23" t="n"/>
+      <c r="R4" s="23" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:ATR_72-600_ATR_house_colors_F-WWEY_-_MSN_98_%289742100696%29.jpg</t>
+        </is>
+      </c>
       <c r="S4" s="12" t="inlineStr">
         <is>
           <t>live</t>
@@ -29567,7 +29579,11 @@
       <c r="O5" s="23" t="n"/>
       <c r="P5" s="23" t="n"/>
       <c r="Q5" s="23" t="n"/>
-      <c r="R5" s="23" t="n"/>
+      <c r="R5" s="23" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Embraer_190-100_PP-XMB_%286921229367%29.jpg</t>
+        </is>
+      </c>
       <c r="S5" s="12" t="inlineStr">
         <is>
           <t>live</t>
@@ -29628,7 +29644,11 @@
       <c r="O6" s="23" t="n"/>
       <c r="P6" s="23" t="n"/>
       <c r="Q6" s="23" t="n"/>
-      <c r="R6" s="23" t="n"/>
+      <c r="R6" s="23" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Bombardier%2C_BD-500_CSeries_CS300%2C_C-FFDK_%2818777967098%29.jpg</t>
+        </is>
+      </c>
       <c r="S6" s="12" t="inlineStr">
         <is>
           <t>live</t>
@@ -29689,7 +29709,11 @@
       <c r="O7" s="23" t="n"/>
       <c r="P7" s="23" t="n"/>
       <c r="Q7" s="23" t="n"/>
-      <c r="R7" s="23" t="n"/>
+      <c r="R7" s="23" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:AIB_A320neo_F-WNEW_27may15_LFBO-1.jpg</t>
+        </is>
+      </c>
       <c r="S7" s="12" t="inlineStr">
         <is>
           <t>live</t>
@@ -29750,7 +29774,11 @@
       <c r="O8" s="23" t="n"/>
       <c r="P8" s="23" t="n"/>
       <c r="Q8" s="23" t="n"/>
-      <c r="R8" s="23" t="n"/>
+      <c r="R8" s="23" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Boeing%2C_N8701Q%2C_Boeing_737-8_MAX_%282%29.jpg</t>
+        </is>
+      </c>
       <c r="S8" s="12" t="inlineStr">
         <is>
           <t>live</t>
@@ -29807,7 +29835,11 @@
       <c r="O9" s="25" t="n"/>
       <c r="P9" s="25" t="n"/>
       <c r="Q9" s="25" t="n"/>
-      <c r="R9" s="25" t="n"/>
+      <c r="R9" s="25" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:N787BA_01.jpg</t>
+        </is>
+      </c>
       <c r="S9" s="15" t="inlineStr">
         <is>
           <t>later</t>
@@ -29864,7 +29896,11 @@
       <c r="O10" s="25" t="n"/>
       <c r="P10" s="25" t="n"/>
       <c r="Q10" s="25" t="n"/>
-      <c r="R10" s="25" t="n"/>
+      <c r="R10" s="25" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:AIB_A350_F-WXWB_24oct14_LFBO-2.jpg</t>
+        </is>
+      </c>
       <c r="S10" s="15" t="inlineStr">
         <is>
           <t>later</t>
@@ -29921,7 +29957,11 @@
       <c r="O11" s="25" t="n"/>
       <c r="P11" s="25" t="n"/>
       <c r="Q11" s="25" t="n"/>
-      <c r="R11" s="25" t="n"/>
+      <c r="R11" s="25" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Boeing_747-8_first_flight_Everett%2C_WA.jpg</t>
+        </is>
+      </c>
       <c r="S11" s="15" t="inlineStr">
         <is>
           <t>later</t>
@@ -29978,7 +30018,11 @@
       <c r="O12" s="25" t="n"/>
       <c r="P12" s="25" t="n"/>
       <c r="Q12" s="25" t="n"/>
-      <c r="R12" s="25" t="n"/>
+      <c r="R12" s="25" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Airbus_Industrie%2C_F-WWOW%2C_Airbus_A380-841_%2835679929105%29.jpg</t>
+        </is>
+      </c>
       <c r="S12" s="15" t="inlineStr">
         <is>
           <t>later</t>
@@ -30042,6 +30086,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
         <is>
@@ -30096,7 +30141,11 @@
       <c r="O15" s="23" t="n"/>
       <c r="P15" s="23" t="n"/>
       <c r="Q15" s="23" t="n"/>
-      <c r="R15" s="23" t="n"/>
+      <c r="R15" s="23" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Republic_Airways_N401YX_E75L.jpg</t>
+        </is>
+      </c>
       <c r="S15" s="13" t="inlineStr">
         <is>
           <t>live</t>
@@ -30153,7 +30202,11 @@
       <c r="O16" s="27" t="n"/>
       <c r="P16" s="27" t="n"/>
       <c r="Q16" s="27" t="n"/>
-      <c r="R16" s="27" t="n"/>
+      <c r="R16" s="27" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:N767AN_Boeing_757F_All_White_Colours_%288736741972%29.jpg</t>
+        </is>
+      </c>
       <c r="S16" s="14" t="inlineStr">
         <is>
           <t>placeholder</t>
@@ -30210,7 +30263,11 @@
       <c r="O17" s="25" t="n"/>
       <c r="P17" s="25" t="n"/>
       <c r="Q17" s="25" t="n"/>
-      <c r="R17" s="25" t="n"/>
+      <c r="R17" s="25" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:F-WWCA_A340-642_%28proto%29_Airbus_TLS_09SEP10_%284979496505%29.jpg</t>
+        </is>
+      </c>
       <c r="S17" s="18" t="inlineStr">
         <is>
           <t>later</t>
@@ -30267,13 +30324,18 @@
       <c r="O18" s="25" t="n"/>
       <c r="P18" s="25" t="n"/>
       <c r="Q18" s="25" t="n"/>
-      <c r="R18" s="25" t="n"/>
+      <c r="R18" s="25" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Boeing_777X_at_Dubai_Airshow_2021_3.jpg</t>
+        </is>
+      </c>
       <c r="S18" s="18" t="inlineStr">
         <is>
           <t>later</t>
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="17" t="inlineStr">
         <is>

--- a/data/Airline-World-Workbook.xlsx
+++ b/data/Airline-World-Workbook.xlsx
@@ -29381,9 +29381,21 @@
           <t>dhc6</t>
         </is>
       </c>
-      <c r="O2" s="23" t="n"/>
-      <c r="P2" s="23" t="n"/>
-      <c r="Q2" s="23" t="n"/>
+      <c r="O2" s="23" t="inlineStr">
+        <is>
+          <t>dhc6.jpg</t>
+        </is>
+      </c>
+      <c r="P2" s="23" t="inlineStr">
+        <is>
+          <t>Paneuropean</t>
+        </is>
+      </c>
+      <c r="Q2" s="23" t="inlineStr">
+        <is>
+          <t>CC BY-SA 3.0</t>
+        </is>
+      </c>
       <c r="R2" s="23" t="inlineStr">
         <is>
           <t>https://commons.wikimedia.org/wiki/File:First_Flight_Twin_Otter_Series_400_C-FDHT.jpg</t>
@@ -29446,9 +29458,21 @@
           <t>sf34</t>
         </is>
       </c>
-      <c r="O3" s="23" t="n"/>
-      <c r="P3" s="23" t="n"/>
-      <c r="Q3" s="23" t="n"/>
+      <c r="O3" s="23" t="inlineStr">
+        <is>
+          <t>saab340.jpg</t>
+        </is>
+      </c>
+      <c r="P3" s="23" t="inlineStr">
+        <is>
+          <t>SDASM Archives</t>
+        </is>
+      </c>
+      <c r="Q3" s="23" t="inlineStr">
+        <is>
+          <t>Public domain</t>
+        </is>
+      </c>
       <c r="R3" s="23" t="inlineStr">
         <is>
           <t>https://commons.wikimedia.org/wiki/File:Saab-Fairchild_340_in_flight.jpg</t>
@@ -29511,9 +29535,21 @@
           <t>at72</t>
         </is>
       </c>
-      <c r="O4" s="23" t="n"/>
-      <c r="P4" s="23" t="n"/>
-      <c r="Q4" s="23" t="n"/>
+      <c r="O4" s="23" t="inlineStr">
+        <is>
+          <t>atr72.jpg</t>
+        </is>
+      </c>
+      <c r="P4" s="23" t="inlineStr">
+        <is>
+          <t>Laurent ERRERA</t>
+        </is>
+      </c>
+      <c r="Q4" s="23" t="inlineStr">
+        <is>
+          <t>CC BY-SA 2.0</t>
+        </is>
+      </c>
       <c r="R4" s="23" t="inlineStr">
         <is>
           <t>https://commons.wikimedia.org/wiki/File:ATR_72-600_ATR_house_colors_F-WWEY_-_MSN_98_%289742100696%29.jpg</t>
@@ -29576,9 +29612,21 @@
           <t>e190</t>
         </is>
       </c>
-      <c r="O5" s="23" t="n"/>
-      <c r="P5" s="23" t="n"/>
-      <c r="Q5" s="23" t="n"/>
+      <c r="O5" s="23" t="inlineStr">
+        <is>
+          <t>e190.jpg</t>
+        </is>
+      </c>
+      <c r="P5" s="23" t="inlineStr">
+        <is>
+          <t>Bob Adams</t>
+        </is>
+      </c>
+      <c r="Q5" s="23" t="inlineStr">
+        <is>
+          <t>CC BY-SA 2.0</t>
+        </is>
+      </c>
       <c r="R5" s="23" t="inlineStr">
         <is>
           <t>https://commons.wikimedia.org/wiki/File:Embraer_190-100_PP-XMB_%286921229367%29.jpg</t>
@@ -29641,9 +29689,21 @@
           <t>narrowbody</t>
         </is>
       </c>
-      <c r="O6" s="23" t="n"/>
-      <c r="P6" s="23" t="n"/>
-      <c r="Q6" s="23" t="n"/>
+      <c r="O6" s="23" t="inlineStr">
+        <is>
+          <t>a220.jpg</t>
+        </is>
+      </c>
+      <c r="P6" s="23" t="inlineStr">
+        <is>
+          <t>Eric Salard</t>
+        </is>
+      </c>
+      <c r="Q6" s="23" t="inlineStr">
+        <is>
+          <t>CC BY-SA 2.0</t>
+        </is>
+      </c>
       <c r="R6" s="23" t="inlineStr">
         <is>
           <t>https://commons.wikimedia.org/wiki/File:Bombardier%2C_BD-500_CSeries_CS300%2C_C-FFDK_%2818777967098%29.jpg</t>
@@ -29706,9 +29766,21 @@
           <t>narrowbody</t>
         </is>
       </c>
-      <c r="O7" s="23" t="n"/>
-      <c r="P7" s="23" t="n"/>
-      <c r="Q7" s="23" t="n"/>
+      <c r="O7" s="23" t="inlineStr">
+        <is>
+          <t>a320.jpg</t>
+        </is>
+      </c>
+      <c r="P7" s="23" t="inlineStr">
+        <is>
+          <t>Gyrostat</t>
+        </is>
+      </c>
+      <c r="Q7" s="23" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0</t>
+        </is>
+      </c>
       <c r="R7" s="23" t="inlineStr">
         <is>
           <t>https://commons.wikimedia.org/wiki/File:AIB_A320neo_F-WNEW_27may15_LFBO-1.jpg</t>
@@ -29771,9 +29843,21 @@
           <t>narrowbody</t>
         </is>
       </c>
-      <c r="O8" s="23" t="n"/>
-      <c r="P8" s="23" t="n"/>
-      <c r="Q8" s="23" t="n"/>
+      <c r="O8" s="23" t="inlineStr">
+        <is>
+          <t>b737.jpg</t>
+        </is>
+      </c>
+      <c r="P8" s="23" t="inlineStr">
+        <is>
+          <t>John Crowley</t>
+        </is>
+      </c>
+      <c r="Q8" s="23" t="inlineStr">
+        <is>
+          <t>CC BY-SA 2.0</t>
+        </is>
+      </c>
       <c r="R8" s="23" t="inlineStr">
         <is>
           <t>https://commons.wikimedia.org/wiki/File:Boeing%2C_N8701Q%2C_Boeing_737-8_MAX_%282%29.jpg</t>
@@ -29832,9 +29916,21 @@
         </is>
       </c>
       <c r="N9" s="25" t="n"/>
-      <c r="O9" s="25" t="n"/>
-      <c r="P9" s="25" t="n"/>
-      <c r="Q9" s="25" t="n"/>
+      <c r="O9" s="25" t="inlineStr">
+        <is>
+          <t>b787.jpg</t>
+        </is>
+      </c>
+      <c r="P9" s="25" t="inlineStr">
+        <is>
+          <t>Maksim Sidorov</t>
+        </is>
+      </c>
+      <c r="Q9" s="25" t="inlineStr">
+        <is>
+          <t>CC BY 3.0</t>
+        </is>
+      </c>
       <c r="R9" s="25" t="inlineStr">
         <is>
           <t>https://commons.wikimedia.org/wiki/File:N787BA_01.jpg</t>
@@ -29893,9 +29989,21 @@
         </is>
       </c>
       <c r="N10" s="25" t="n"/>
-      <c r="O10" s="25" t="n"/>
-      <c r="P10" s="25" t="n"/>
-      <c r="Q10" s="25" t="n"/>
+      <c r="O10" s="25" t="inlineStr">
+        <is>
+          <t>a350.jpg</t>
+        </is>
+      </c>
+      <c r="P10" s="25" t="inlineStr">
+        <is>
+          <t>Gyrostat</t>
+        </is>
+      </c>
+      <c r="Q10" s="25" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0</t>
+        </is>
+      </c>
       <c r="R10" s="25" t="inlineStr">
         <is>
           <t>https://commons.wikimedia.org/wiki/File:AIB_A350_F-WXWB_24oct14_LFBO-2.jpg</t>
@@ -29954,9 +30062,21 @@
         </is>
       </c>
       <c r="N11" s="25" t="n"/>
-      <c r="O11" s="25" t="n"/>
-      <c r="P11" s="25" t="n"/>
-      <c r="Q11" s="25" t="n"/>
+      <c r="O11" s="25" t="inlineStr">
+        <is>
+          <t>b747.jpg</t>
+        </is>
+      </c>
+      <c r="P11" s="25" t="inlineStr">
+        <is>
+          <t>Boeing Dreamscape</t>
+        </is>
+      </c>
+      <c r="Q11" s="25" t="inlineStr">
+        <is>
+          <t>CC BY 2.0</t>
+        </is>
+      </c>
       <c r="R11" s="25" t="inlineStr">
         <is>
           <t>https://commons.wikimedia.org/wiki/File:Boeing_747-8_first_flight_Everett%2C_WA.jpg</t>
@@ -30015,9 +30135,21 @@
         </is>
       </c>
       <c r="N12" s="25" t="n"/>
-      <c r="O12" s="25" t="n"/>
-      <c r="P12" s="25" t="n"/>
-      <c r="Q12" s="25" t="n"/>
+      <c r="O12" s="25" t="inlineStr">
+        <is>
+          <t>a380.jpg</t>
+        </is>
+      </c>
+      <c r="P12" s="25" t="inlineStr">
+        <is>
+          <t>Anna Zvereva</t>
+        </is>
+      </c>
+      <c r="Q12" s="25" t="inlineStr">
+        <is>
+          <t>CC BY-SA 2.0</t>
+        </is>
+      </c>
       <c r="R12" s="25" t="inlineStr">
         <is>
           <t>https://commons.wikimedia.org/wiki/File:Airbus_Industrie%2C_F-WWOW%2C_Airbus_A380-841_%2835679929105%29.jpg</t>
@@ -30138,9 +30270,21 @@
           <t>e175</t>
         </is>
       </c>
-      <c r="O15" s="23" t="n"/>
-      <c r="P15" s="23" t="n"/>
-      <c r="Q15" s="23" t="n"/>
+      <c r="O15" s="23" t="inlineStr">
+        <is>
+          <t>e175.jpg</t>
+        </is>
+      </c>
+      <c r="P15" s="23" t="inlineStr">
+        <is>
+          <t>AVA Navigate</t>
+        </is>
+      </c>
+      <c r="Q15" s="23" t="inlineStr">
+        <is>
+          <t>CC BY 4.0</t>
+        </is>
+      </c>
       <c r="R15" s="23" t="inlineStr">
         <is>
           <t>https://commons.wikimedia.org/wiki/File:Republic_Airways_N401YX_E75L.jpg</t>
@@ -30199,9 +30343,21 @@
         </is>
       </c>
       <c r="N16" s="27" t="n"/>
-      <c r="O16" s="27" t="n"/>
-      <c r="P16" s="27" t="n"/>
-      <c r="Q16" s="27" t="n"/>
+      <c r="O16" s="27" t="inlineStr">
+        <is>
+          <t>b757.jpg</t>
+        </is>
+      </c>
+      <c r="P16" s="27" t="inlineStr">
+        <is>
+          <t>Aeroprints.com</t>
+        </is>
+      </c>
+      <c r="Q16" s="27" t="inlineStr">
+        <is>
+          <t>CC BY-SA 3.0</t>
+        </is>
+      </c>
       <c r="R16" s="27" t="inlineStr">
         <is>
           <t>https://commons.wikimedia.org/wiki/File:N767AN_Boeing_757F_All_White_Colours_%288736741972%29.jpg</t>
@@ -30260,9 +30416,21 @@
         </is>
       </c>
       <c r="N17" s="25" t="n"/>
-      <c r="O17" s="25" t="n"/>
-      <c r="P17" s="25" t="n"/>
-      <c r="Q17" s="25" t="n"/>
+      <c r="O17" s="25" t="inlineStr">
+        <is>
+          <t>a340.jpg</t>
+        </is>
+      </c>
+      <c r="P17" s="25" t="inlineStr">
+        <is>
+          <t>Ken Fielding</t>
+        </is>
+      </c>
+      <c r="Q17" s="25" t="inlineStr">
+        <is>
+          <t>CC BY-SA 3.0</t>
+        </is>
+      </c>
       <c r="R17" s="25" t="inlineStr">
         <is>
           <t>https://commons.wikimedia.org/wiki/File:F-WWCA_A340-642_%28proto%29_Airbus_TLS_09SEP10_%284979496505%29.jpg</t>
@@ -30321,9 +30489,21 @@
         </is>
       </c>
       <c r="N18" s="25" t="n"/>
-      <c r="O18" s="25" t="n"/>
-      <c r="P18" s="25" t="n"/>
-      <c r="Q18" s="25" t="n"/>
+      <c r="O18" s="25" t="inlineStr">
+        <is>
+          <t>b777.jpg</t>
+        </is>
+      </c>
+      <c r="P18" s="25" t="inlineStr">
+        <is>
+          <t>Mztourist</t>
+        </is>
+      </c>
+      <c r="Q18" s="25" t="inlineStr">
+        <is>
+          <t>CC BY-SA 4.0</t>
+        </is>
+      </c>
       <c r="R18" s="25" t="inlineStr">
         <is>
           <t>https://commons.wikimedia.org/wiki/File:Boeing_777X_at_Dubai_Airshow_2021_3.jpg</t>

--- a/data/Airline-World-Workbook.xlsx
+++ b/data/Airline-World-Workbook.xlsx
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A18"/>
+  <dimension ref="A1:A19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -689,16 +689,23 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>v4.3 draft (7 Oct, Claude Code, for Fable to adopt): Change Request 5. New sheet Livery (palette, stripes, tail symbols, logo shapes, plane-name suggestions); Aircraft columns artworkId and photoFile/Credit/Licence/Source; Settings blockedFlightCodes, soundDefault, revealSeconds. Everything the pupil chooses (airline name, flight code, logo, each plane's registration, name and livery) lives in the save state, not here.</t>
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>v4.3 (8 Oct): D50 Red Kite rule (Settings rivalSwitch*, Events rivalFare/durationDays/advertiseCost; Dublin table extended to £50) and D51 crew mechanic off until 2031-01-06 (Settings crewMechanicFromDate). Week 1 re-run without crew cost: Balance Report v4.3 addendum.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>v4.3 draft (8 Oct, Claude Code, for Fable to adopt): Week-1 review. Settings crewFromDate (crew duty waits for the airline-type choice; the Calendar day-5 "crew duty" mechanic is ignored before it, so the row can stay until it is moved).</t>
+          <t>v4.3 + CR5 rows re-added by Claude Code (8 Oct): Fable's v4.3 did not carry the CR5 draft, so the Livery sheet, the Aircraft columns artworkId/photoFile/photoCredit/photoLicence/photoSource, and Settings blockedFlightCodes, soundDefault, revealSeconds are added again, plus practiceQuestionsPerDay (design note). The game reads crewMechanicFromDate (D51); the earlier draft key crewFromDate is dropped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>v4.3 draft (7 Oct, Claude Code, for Fable to adopt): Change Request 5. New sheet Livery (palette, stripes, tail symbols, logo shapes, plane-name suggestions); Aircraft columns artworkId and photoFile/Credit/Licence/Source; Settings blockedFlightCodes, soundDefault, revealSeconds. Everything the pupil chooses (airline name, flight code, logo, each plane's registration, name and livery) lives in the save state, not here.</t>
         </is>
       </c>
     </row>
@@ -19694,7 +19701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N39"/>
+  <dimension ref="A1:S39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -19783,6 +19790,31 @@
           <t>costShare (of a day's profit, from day 22)</t>
         </is>
       </c>
+      <c r="O1" s="20" t="inlineStr">
+        <is>
+          <t>rivalFare</t>
+        </is>
+      </c>
+      <c r="P1" s="20" t="inlineStr">
+        <is>
+          <t>rivalFareCut</t>
+        </is>
+      </c>
+      <c r="Q1" s="20" t="inlineStr">
+        <is>
+          <t>durationDays</t>
+        </is>
+      </c>
+      <c r="R1" s="20" t="inlineStr">
+        <is>
+          <t>advertiseCost</t>
+        </is>
+      </c>
+      <c r="S1" s="20" t="inlineStr">
+        <is>
+          <t>affectsRoutes</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="12" t="inlineStr">
@@ -19802,7 +19834,7 @@
       </c>
       <c r="D2" s="12" t="inlineStr">
         <is>
-          <t>Red Kite Air sells Dublin tickets for £50. Some of your passengers have switched to them.</t>
+          <t>Red Kite Air is selling Dublin at £50 from today until Sunday. For every £10 you charge above them, 1 in 10 of your passengers will fly with Red Kite instead. The card shows the numbers for each choice.</t>
         </is>
       </c>
       <c r="E2" s="12" t="n">
@@ -19823,7 +19855,7 @@
       <c r="J2" s="12" t="inlineStr"/>
       <c r="K2" s="12" t="inlineStr">
         <is>
-          <t>setPrice dub=50</t>
+          <t>switch share = min(0.6, 0.1 × (yourFare − 50) ÷ 10); options: match (your fare → £50), hold, advertise (£300, switch share halved, −½★ as before); the pupil may also move the plane to Paris</t>
         </is>
       </c>
       <c r="L2" s="12" t="inlineStr">
@@ -19839,6 +19871,20 @@
       <c r="N2" s="13" t="inlineStr">
         <is>
           <t>advertise 300 (fixed)</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>4</v>
+      </c>
+      <c r="R2" t="n">
+        <v>300</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>dub</t>
         </is>
       </c>
     </row>
@@ -19854,7 +19900,11 @@
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr"/>
-      <c r="D3" s="12" t="inlineStr"/>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>Red Kite Air is selling Dublin at £50 from today until Sunday. For every £10 you charge above them, 1 in 10 of your passengers will fly with Red Kite instead. The card shows the numbers for each choice.</t>
+        </is>
+      </c>
       <c r="E3" s="12" t="n">
         <v>2</v>
       </c>
@@ -19871,7 +19921,11 @@
       <c r="H3" s="12" t="inlineStr"/>
       <c r="I3" s="12" t="inlineStr"/>
       <c r="J3" s="12" t="inlineStr"/>
-      <c r="K3" s="12" t="inlineStr"/>
+      <c r="K3" s="12" t="inlineStr">
+        <is>
+          <t>switch share = min(0.6, 0.1 × (yourFare − 50) ÷ 10); options: match (your fare → £50), hold, advertise (£300, switch share halved, −½★ as before); the pupil may also move the plane to Paris</t>
+        </is>
+      </c>
       <c r="L3" s="12" t="inlineStr">
         <is>
           <t>You held your price. Red Kite keeps stealing a few passengers.</t>
@@ -19883,6 +19937,20 @@
         </is>
       </c>
       <c r="N3" s="13" t="n"/>
+      <c r="O3" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>4</v>
+      </c>
+      <c r="R3" t="n">
+        <v>300</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>dub</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
@@ -19896,7 +19964,11 @@
         </is>
       </c>
       <c r="C4" s="12" t="inlineStr"/>
-      <c r="D4" s="12" t="inlineStr"/>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>Red Kite Air is selling Dublin at £50 from today until Sunday. For every £10 you charge above them, 1 in 10 of your passengers will fly with Red Kite instead. The card shows the numbers for each choice.</t>
+        </is>
+      </c>
       <c r="E4" s="12" t="n">
         <v>3</v>
       </c>
@@ -19917,7 +19989,11 @@
         <v>0.5</v>
       </c>
       <c r="J4" s="12" t="inlineStr"/>
-      <c r="K4" s="12" t="inlineStr"/>
+      <c r="K4" s="12" t="inlineStr">
+        <is>
+          <t>switch share = min(0.6, 0.1 × (yourFare − 50) ÷ 10); options: match (your fare → £50), hold, advertise (£300, switch share halved, −½★ as before); the pupil may also move the plane to Paris</t>
+        </is>
+      </c>
       <c r="L4" s="12" t="inlineStr">
         <is>
           <t>Your posters worked: +½ star. It cost £300.</t>
@@ -19929,6 +20005,20 @@
         </is>
       </c>
       <c r="N4" s="13" t="n"/>
+      <c r="O4" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>4</v>
+      </c>
+      <c r="R4" t="n">
+        <v>300</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>dub</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
@@ -20395,7 +20485,7 @@
       <c r="J14" s="12" t="inlineStr"/>
       <c r="K14" s="12" t="inlineStr">
         <is>
-          <t>rival fares on all routes for the week</t>
+          <t>Red Kite's fare on every route = your fare × 0.8 for seven days; same switch rule (1 in 10 per £10 dearer, cap 6 in 10); advertising £1,000 halves it. Costs scale from day 22 (D21): advertise = 0.3 of a day's profit instead of £1,000 once costShare applies</t>
         </is>
       </c>
       <c r="L14" s="12" t="inlineStr"/>
@@ -20405,6 +20495,20 @@
         </is>
       </c>
       <c r="N14" s="13" t="n"/>
+      <c r="P14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>7</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
@@ -24680,7 +24784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -24852,40 +24956,40 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>secondCrewCost</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B9" s="11" t="n">
         <v>250</v>
       </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Charged when a plane's duty day exceeds maxDutyHours</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>live</t>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>Applies only from crewMechanicFromDate (D51). Will vary by airline type.</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>placeholder</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>maxDutyHours</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Duty = 30 min before first departure to 30 min after last arrival</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>Applies only from crewMechanicFromDate (D51).</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>live</t>
         </is>
@@ -25718,86 +25822,166 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="23" t="inlineStr">
+      <c r="A50" s="13" t="inlineStr">
+        <is>
+          <t>crewMechanicFromDate</t>
+        </is>
+      </c>
+      <c r="B50" s="13" t="inlineStr">
+        <is>
+          <t>2031-01-06</t>
+        </is>
+      </c>
+      <c r="C50" s="13" t="inlineStr">
+        <is>
+          <t>D51: before this date there is no duty limit and no second-crew cost; a plane may fly any timetable that fits airportOpen–airportClose. From this date maxDutyHours and secondCrewCost apply, with the cost depending on airline type (values when chapter 2 is designed).</t>
+        </is>
+      </c>
+      <c r="D50" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="13" t="inlineStr">
+        <is>
+          <t>rivalSwitchPerTenPounds</t>
+        </is>
+      </c>
+      <c r="B51" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C51" s="13" t="inlineStr">
+        <is>
+          <t>D50: for every £10 the pupil's fare is above Red Kite's on that route, 1 in 10 of his passengers switches to Red Kite.</t>
+        </is>
+      </c>
+      <c r="D51" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="13" t="inlineStr">
+        <is>
+          <t>rivalSwitchCap</t>
+        </is>
+      </c>
+      <c r="B52" s="13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C52" s="13" t="inlineStr">
+        <is>
+          <t>Never more than 6 in 10 switch.</t>
+        </is>
+      </c>
+      <c r="D52" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="13" t="inlineStr">
+        <is>
+          <t>rivalAdvertiseFactor</t>
+        </is>
+      </c>
+      <c r="B53" s="13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C53" s="13" t="inlineStr">
+        <is>
+          <t>Advertising halves the number who switch, for the event's duration.</t>
+        </is>
+      </c>
+      <c r="D53" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="23" t="inlineStr">
         <is>
           <t>blockedFlightCodes</t>
         </is>
       </c>
-      <c r="B50" s="23" t="inlineStr">
+      <c r="B54" s="23" t="inlineStr">
         <is>
           <t>BA, EZ, FR, VS, LH, AF, KL, U2</t>
         </is>
       </c>
-      <c r="C50" s="23" t="inlineStr">
+      <c r="C54" s="23" t="inlineStr">
         <is>
           <t>CR5. Real airline codes the pupil cannot pick; refused calmly ("That code belongs to a real airline, try another").</t>
         </is>
       </c>
-      <c r="D50" s="23" t="inlineStr">
+      <c r="D54" s="23" t="inlineStr">
         <is>
           <t>live</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="23" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="23" t="inlineStr">
         <is>
           <t>soundDefault</t>
         </is>
       </c>
-      <c r="B51" s="23" t="inlineStr">
+      <c r="B55" s="23" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="C51" s="23" t="inlineStr">
+      <c r="C55" s="23" t="inlineStr">
         <is>
           <t>CR5. Sound (take-off, airport chimes, announcements) is off until the teacher turns it on; a mute control sits in the top bar.</t>
         </is>
       </c>
-      <c r="D51" s="23" t="inlineStr">
+      <c r="D55" s="23" t="inlineStr">
         <is>
           <t>live</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="23" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="23" t="inlineStr">
         <is>
           <t>revealSeconds</t>
         </is>
       </c>
-      <c r="B52" s="23" t="n">
+      <c r="B56" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="C52" s="23" t="inlineStr">
+      <c r="C56" s="23" t="inlineStr">
         <is>
           <t>CR5. The hangar reveal on launch day: doors close, open, the plane rolls in. Later planes get about half.</t>
         </is>
       </c>
-      <c r="D52" s="23" t="inlineStr">
+      <c r="D56" s="23" t="inlineStr">
         <is>
           <t>live</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="23" t="inlineStr">
-        <is>
-          <t>crewFromDate</t>
-        </is>
-      </c>
-      <c r="B53" s="23" t="inlineStr">
-        <is>
-          <t>2031-01-06</t>
-        </is>
-      </c>
-      <c r="C53" s="23" t="inlineStr">
-        <is>
-          <t>Week-1 review (8 Oct). Crew duty (the 12-hour day and the second crew) is switched off before this date: no briefing, no cost, no crews line. Set to the day the airline type is chosen (chapter 2). The Calendar day-5 mechanic "crew duty" is ignored before it.</t>
-        </is>
-      </c>
-      <c r="D53" s="23" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="23" t="inlineStr">
+        <is>
+          <t>practiceQuestionsPerDay</t>
+        </is>
+      </c>
+      <c r="B57" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="23" t="inlineStr">
+        <is>
+          <t>Design note 8 Oct. Optional practice questions after the day's sums on the workings page, with the pupil's own numbers: 0, 1 or 3 (the teacher panel can change it).</t>
+        </is>
+      </c>
+      <c r="D57" s="23" t="inlineStr">
         <is>
           <t>live</t>
         </is>
@@ -26505,7 +26689,7 @@
       </c>
       <c r="N2" s="12" t="inlineStr">
         <is>
-          <t>70:80|80:72|90:62|100:44|110:30|120:18</t>
+          <t>50:96|60:88|70:80|80:72|90:62|100:44|110:30|120:18</t>
         </is>
       </c>
       <c r="O2" s="12" t="n">
@@ -30042,6 +30226,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
         <is>
@@ -30274,6 +30459,7 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="17" t="inlineStr">
         <is>

--- a/data/Airline-World-Workbook.xlsx
+++ b/data/Airline-World-Workbook.xlsx
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A19"/>
+  <dimension ref="A1:A20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -696,14 +696,21 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>v4.3 + CR5 rows re-added by Claude Code (8 Oct): Fable's v4.3 did not carry the CR5 draft, so the Livery sheet, the Aircraft columns artworkId/photoFile/photoCredit/photoLicence/photoSource, and Settings blockedFlightCodes, soundDefault, revealSeconds are added again, plus practiceQuestionsPerDay (design note). The game reads crewMechanicFromDate (D51); the earlier draft key crewFromDate is dropped.</t>
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>v4.4 (12 Oct): D52–D55. Chapter 1 is played a WEEK at a time (Calendar weekPhase: plan / run / review; days 1–28 rewritten); both routes from Launch Day; week 2 = second plane; four routes week 3; Madrid week 4; Marrakech and weekly skips from day 29; later routes and the A220/A320/737 shift a week. Tutorial plane prices 2½× (second plane rented or financed first); aircraft day costs raised (bad plans lose money); missed-profit line in every weekly review; use-it-or-lose-it from week 3 (Settings neglect*). Chapter-1 events aligned to Mondays. Balance Report v4.4 addendum.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
+        <is>
+          <t>v4.3 + CR5 rows re-added by Claude Code (8 Oct): Fable's v4.3 did not carry the CR5 draft, so the Livery sheet, the Aircraft columns artworkId/photoFile/photoCredit/photoLicence/photoSource, and Settings blockedFlightCodes, soundDefault, revealSeconds are added again, plus practiceQuestionsPerDay (design note). The game reads crewMechanicFromDate (D51); the earlier draft key crewFromDate is dropped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>v4.3 draft (7 Oct, Claude Code, for Fable to adopt): Change Request 5. New sheet Livery (palette, stripes, tail symbols, logo shapes, plane-name suggestions); Aircraft columns artworkId and photoFile/Credit/Licence/Source; Settings blockedFlightCodes, soundDefault, revealSeconds. Everything the pupil chooses (airline name, flight code, logo, each plane's registration, name and livery) lives in the save state, not here.</t>
         </is>
@@ -1028,7 +1035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:R29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1136,951 +1143,927 @@
           <t>status</t>
         </is>
       </c>
+      <c r="R1" s="20" t="inlineStr">
+        <is>
+          <t>weekPhase</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="12" t="inlineStr">
+      <c r="A2" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>2030-09-02</t>
         </is>
       </c>
-      <c r="C2" s="12" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>Mon</t>
         </is>
       </c>
-      <c r="D2" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" s="12" t="inlineStr">
-        <is>
-          <t>setup</t>
-        </is>
-      </c>
-      <c r="F2" s="12" t="n">
+      <c r="D2" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="13" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="F2" s="13" t="n">
         <v>1.2</v>
       </c>
-      <c r="G2" s="12" t="inlineStr">
-        <is>
-          <t>Launch day</t>
-        </is>
-      </c>
-      <c r="H2" s="12" t="inlineStr">
-        <is>
-          <t>New airline launches from London.</t>
-        </is>
-      </c>
-      <c r="I2" s="12" t="inlineStr">
-        <is>
-          <t>Fuel steady at £1.20 a litre.</t>
-        </is>
-      </c>
-      <c r="J2" s="12" t="inlineStr"/>
-      <c r="K2" s="12" t="inlineStr">
-        <is>
-          <t>routes: first market (pupil chooses dub or par); planes: dhc6 (launch deal); mechanics: fare, services, timetable</t>
-        </is>
-      </c>
-      <c r="L2" s="12" t="inlineStr"/>
-      <c r="M2" s="12" t="inlineStr"/>
-      <c r="N2" s="12" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
+        <is>
+          <t>Launch Day: build your standing plan</t>
+        </is>
+      </c>
+      <c r="H2" s="13" t="inlineStr">
+        <is>
+          <t>Your airline is cleared for take-off. Build the week's plan: timetable, fare, snacks, fuel.</t>
+        </is>
+      </c>
+      <c r="I2" s="13" t="inlineStr">
+        <is>
+          <t>Fuel is free today and tomorrow.</t>
+        </is>
+      </c>
+      <c r="J2" s="13" t="inlineStr"/>
+      <c r="K2" s="13" t="inlineStr">
+        <is>
+          <t>routes: dub, par; planes: dhc6 (launch deal); mechanics: timetable with demand curve, fare, snacks, fuel, modelling tool, workings page</t>
+        </is>
+      </c>
+      <c r="L2" s="13" t="inlineStr"/>
+      <c r="M2" s="13" t="n"/>
+      <c r="N2" s="13" t="inlineStr">
+        <is>
+          <t>pricing,timetable,cabin,fuel</t>
+        </is>
+      </c>
+      <c r="O2" s="13" t="inlineStr">
+        <is>
+          <t>ticketRevenue,profit,snackRevenue,fuelCost</t>
+        </is>
+      </c>
+      <c r="P2" s="13" t="n"/>
+      <c r="Q2" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="R2" s="13" t="inlineStr">
+        <is>
+          <t>plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>2030-09-03</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="F3" s="13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>Day two runs to plan.</t>
+        </is>
+      </c>
+      <c r="I3" s="13" t="inlineStr">
+        <is>
+          <t>Fuel is free today.</t>
+        </is>
+      </c>
+      <c r="J3" s="13" t="inlineStr"/>
+      <c r="K3" s="13" t="inlineStr"/>
+      <c r="L3" s="13" t="inlineStr"/>
+      <c r="M3" s="13" t="n"/>
+      <c r="N3" s="13" t="inlineStr"/>
+      <c r="O3" s="13" t="inlineStr"/>
+      <c r="P3" s="13" t="n"/>
+      <c r="Q3" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="R3" s="13" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>2030-09-04</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>Wednesday: fuel is yours to buy</t>
+        </is>
+      </c>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t>The launch deal is over: from today you buy your own fuel.</t>
+        </is>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>Fuel £1.30 a litre.</t>
+        </is>
+      </c>
+      <c r="J4" s="13" t="inlineStr"/>
+      <c r="K4" s="13" t="inlineStr"/>
+      <c r="L4" s="13" t="inlineStr"/>
+      <c r="M4" s="13" t="n"/>
+      <c r="N4" s="13" t="inlineStr"/>
+      <c r="O4" s="13" t="inlineStr"/>
+      <c r="P4" s="13" t="n"/>
+      <c r="Q4" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="R4" s="13" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>2030-09-05</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="F5" s="13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G5" s="13" t="inlineStr">
+        <is>
+          <t>Thursday: Red Kite</t>
+        </is>
+      </c>
+      <c r="H5" s="13" t="inlineStr">
+        <is>
+          <t>Red Kite Air is selling Dublin at £50 until Sunday.</t>
+        </is>
+      </c>
+      <c r="I5" s="13" t="inlineStr"/>
+      <c r="J5" s="13" t="inlineStr">
+        <is>
+          <t>undercut_dub</t>
+        </is>
+      </c>
+      <c r="K5" s="13" t="inlineStr"/>
+      <c r="L5" s="13" t="inlineStr"/>
+      <c r="M5" s="13" t="n"/>
+      <c r="N5" s="13" t="inlineStr">
         <is>
           <t>pricing</t>
         </is>
       </c>
-      <c r="O2" s="12" t="inlineStr">
-        <is>
-          <t>revenue</t>
-        </is>
-      </c>
-      <c r="P2" s="12" t="inlineStr"/>
-      <c r="Q2" s="12" t="inlineStr">
+      <c r="O5" s="13" t="inlineStr">
+        <is>
+          <t>rivalSwitch</t>
+        </is>
+      </c>
+      <c r="P5" s="13" t="n"/>
+      <c r="Q5" s="13" t="inlineStr">
         <is>
           <t>live</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="12" t="n">
+      <c r="R5" s="13" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>2030-09-06</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G6" s="13" t="inlineStr">
+        <is>
+          <t>Friday: storm</t>
+        </is>
+      </c>
+      <c r="H6" s="13" t="inlineStr">
+        <is>
+          <t>A storm is forecast for this afternoon.</t>
+        </is>
+      </c>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>Fuel £1.40 a litre.</t>
+        </is>
+      </c>
+      <c r="J6" s="13" t="inlineStr">
+        <is>
+          <t>storm</t>
+        </is>
+      </c>
+      <c r="K6" s="13" t="inlineStr"/>
+      <c r="L6" s="13" t="inlineStr"/>
+      <c r="M6" s="13" t="n"/>
+      <c r="N6" s="13" t="inlineStr"/>
+      <c r="O6" s="13" t="inlineStr"/>
+      <c r="P6" s="13" t="n"/>
+      <c r="Q6" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="R6" s="13" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>2030-09-07</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>weekend</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G7" s="13" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="H7" s="13" t="inlineStr">
+        <is>
+          <t>Quiet at the airport: business travellers stay home, families fly.</t>
+        </is>
+      </c>
+      <c r="I7" s="13" t="inlineStr"/>
+      <c r="J7" s="13" t="inlineStr"/>
+      <c r="K7" s="13" t="inlineStr"/>
+      <c r="L7" s="13" t="inlineStr">
+        <is>
+          <t>weekend multipliers (Settings)</t>
+        </is>
+      </c>
+      <c r="M7" s="13" t="n"/>
+      <c r="N7" s="13" t="inlineStr"/>
+      <c r="O7" s="13" t="inlineStr"/>
+      <c r="P7" s="13" t="n"/>
+      <c r="Q7" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="R7" s="13" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>2030-09-08</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>weekend</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G8" s="13" t="inlineStr">
+        <is>
+          <t>Sunday: the week's accounts</t>
+        </is>
+      </c>
+      <c r="H8" s="13" t="inlineStr">
+        <is>
+          <t>Seven days flown. Add up the week; compare it with the plan.</t>
+        </is>
+      </c>
+      <c r="I8" s="13" t="inlineStr"/>
+      <c r="J8" s="13" t="inlineStr"/>
+      <c r="K8" s="13" t="inlineStr">
+        <is>
+          <t>mechanics: weekly review, seven-row table, projected − actual, missed-profit line</t>
+        </is>
+      </c>
+      <c r="L8" s="13" t="inlineStr">
+        <is>
+          <t>weekend multipliers (Settings)</t>
+        </is>
+      </c>
+      <c r="M8" s="13" t="n"/>
+      <c r="N8" s="13" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="O8" s="13" t="inlineStr">
+        <is>
+          <t>weekTotal,projectedVsActual</t>
+        </is>
+      </c>
+      <c r="P8" s="13" t="n"/>
+      <c r="Q8" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="R8" s="13" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>2030-09-09</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>2030-09-03</t>
-        </is>
-      </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>Week 2: a second plane</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="inlineStr">
+        <is>
+          <t>One plane cannot serve both routes fully. The shop has a Saab 340 and an ATR 72. Rent, finance, or save to buy?</t>
+        </is>
+      </c>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>Fuel £1.50 a litre.</t>
+        </is>
+      </c>
+      <c r="J9" s="13" t="inlineStr"/>
+      <c r="K9" s="13" t="inlineStr">
+        <is>
+          <t>planes: dhc6 (second), saab340, atr72; mechanics: rent-or-buy sum, launch-deal finance, buy greyed until affordable, two timetables, assignment</t>
+        </is>
+      </c>
+      <c r="L9" s="13" t="inlineStr"/>
+      <c r="M9" s="13" t="n"/>
+      <c r="N9" s="13" t="inlineStr">
+        <is>
+          <t>fleet,assignment,timetable</t>
+        </is>
+      </c>
+      <c r="O9" s="13" t="inlineStr">
+        <is>
+          <t>rentOrBuy</t>
+        </is>
+      </c>
+      <c r="P9" s="13" t="n"/>
+      <c r="Q9" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="R9" s="13" t="inlineStr">
+        <is>
+          <t>plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>2030-09-10</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
         <is>
           <t>Tue</t>
         </is>
       </c>
-      <c r="D3" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="12" t="inlineStr">
+      <c r="D10" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
         <is>
           <t>day</t>
         </is>
       </c>
-      <c r="F3" s="12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="G3" s="12" t="inlineStr">
-        <is>
-          <t>A catering offer</t>
-        </is>
-      </c>
-      <c r="H3" s="12" t="inlineStr">
-        <is>
-          <t>A catering supplier offers snacks on board.</t>
-        </is>
-      </c>
-      <c r="I3" s="12" t="inlineStr">
-        <is>
-          <t>Fuel steady at £1.20 a litre.</t>
-        </is>
-      </c>
-      <c r="J3" s="12" t="inlineStr"/>
-      <c r="K3" s="12" t="inlineStr">
-        <is>
-          <t>mechanics: snacks (on-board sales)</t>
-        </is>
-      </c>
-      <c r="L3" s="12" t="inlineStr"/>
-      <c r="M3" s="12" t="inlineStr"/>
-      <c r="N3" s="12" t="inlineStr">
-        <is>
-          <t>pricing,cabin</t>
-        </is>
-      </c>
-      <c r="O3" s="12" t="inlineStr">
-        <is>
-          <t>snackRevenue</t>
-        </is>
-      </c>
-      <c r="P3" s="12" t="inlineStr"/>
-      <c r="Q3" s="12" t="inlineStr">
+      <c r="F10" s="13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="H10" s="13" t="inlineStr">
+        <is>
+          <t>Two planes on the board.</t>
+        </is>
+      </c>
+      <c r="I10" s="13" t="inlineStr"/>
+      <c r="J10" s="13" t="inlineStr"/>
+      <c r="K10" s="13" t="inlineStr"/>
+      <c r="L10" s="13" t="inlineStr"/>
+      <c r="M10" s="13" t="n"/>
+      <c r="N10" s="13" t="inlineStr"/>
+      <c r="O10" s="13" t="inlineStr"/>
+      <c r="P10" s="13" t="n"/>
+      <c r="Q10" s="13" t="inlineStr">
         <is>
           <t>live</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="12" t="n">
+      <c r="R10" s="13" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>2030-09-11</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G11" s="13" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="H11" s="13" t="inlineStr"/>
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>Fuel £1.60 a litre.</t>
+        </is>
+      </c>
+      <c r="J11" s="13" t="inlineStr"/>
+      <c r="K11" s="13" t="inlineStr"/>
+      <c r="L11" s="13" t="inlineStr"/>
+      <c r="M11" s="13" t="n"/>
+      <c r="N11" s="13" t="inlineStr"/>
+      <c r="O11" s="13" t="inlineStr"/>
+      <c r="P11" s="13" t="n"/>
+      <c r="Q11" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="R11" s="13" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>2030-09-12</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G12" s="13" t="inlineStr">
+        <is>
+          <t>Thursday: crew sickness</t>
+        </is>
+      </c>
+      <c r="H12" s="13" t="inlineStr">
+        <is>
+          <t>The captain has flu.</t>
+        </is>
+      </c>
+      <c r="I12" s="13" t="inlineStr"/>
+      <c r="J12" s="13" t="inlineStr">
+        <is>
+          <t>crew</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="inlineStr"/>
+      <c r="L12" s="13" t="inlineStr"/>
+      <c r="M12" s="13" t="n"/>
+      <c r="N12" s="13" t="inlineStr"/>
+      <c r="O12" s="13" t="inlineStr"/>
+      <c r="P12" s="13" t="n"/>
+      <c r="Q12" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="R12" s="13" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>2030-09-13</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G13" s="13" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="H13" s="13" t="inlineStr"/>
+      <c r="I13" s="13" t="inlineStr">
+        <is>
+          <t>Fuel £1.70 a litre.</t>
+        </is>
+      </c>
+      <c r="J13" s="13" t="inlineStr"/>
+      <c r="K13" s="13" t="inlineStr"/>
+      <c r="L13" s="13" t="inlineStr"/>
+      <c r="M13" s="13" t="n"/>
+      <c r="N13" s="13" t="inlineStr"/>
+      <c r="O13" s="13" t="inlineStr"/>
+      <c r="P13" s="13" t="n"/>
+      <c r="Q13" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="R13" s="13" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>2030-09-14</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>weekend</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G14" s="13" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="H14" s="13" t="inlineStr"/>
+      <c r="I14" s="13" t="inlineStr"/>
+      <c r="J14" s="13" t="inlineStr"/>
+      <c r="K14" s="13" t="inlineStr"/>
+      <c r="L14" s="13" t="inlineStr">
+        <is>
+          <t>weekend multipliers (Settings)</t>
+        </is>
+      </c>
+      <c r="M14" s="13" t="n"/>
+      <c r="N14" s="13" t="inlineStr"/>
+      <c r="O14" s="13" t="inlineStr"/>
+      <c r="P14" s="13" t="n"/>
+      <c r="Q14" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="R14" s="13" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>2030-09-15</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>weekend</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>Sunday: week 2 accounts</t>
+        </is>
+      </c>
+      <c r="H15" s="13" t="inlineStr"/>
+      <c r="I15" s="13" t="inlineStr"/>
+      <c r="J15" s="13" t="inlineStr"/>
+      <c r="K15" s="13" t="inlineStr"/>
+      <c r="L15" s="13" t="inlineStr">
+        <is>
+          <t>weekend multipliers (Settings)</t>
+        </is>
+      </c>
+      <c r="M15" s="13" t="n"/>
+      <c r="N15" s="13" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="O15" s="13" t="inlineStr">
+        <is>
+          <t>weekTotal,projectedVsActual</t>
+        </is>
+      </c>
+      <c r="P15" s="13" t="n"/>
+      <c r="Q15" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="R15" s="13" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>2030-09-16</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>2030-09-04</t>
-        </is>
-      </c>
-      <c r="C4" s="12" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="D4" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
         <is>
           <t>day</t>
         </is>
       </c>
-      <c r="F4" s="12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="G4" s="12" t="inlineStr">
-        <is>
-          <t>Fuel on the move</t>
-        </is>
-      </c>
-      <c r="H4" s="12" t="inlineStr">
-        <is>
-          <t>Fuel rises to £1.30 a litre.</t>
-        </is>
-      </c>
-      <c r="I4" s="12" t="inlineStr">
-        <is>
-          <t>Oil experts say fuel will keep rising this year.</t>
-        </is>
-      </c>
-      <c r="J4" s="12" t="inlineStr"/>
-      <c r="K4" s="12" t="inlineStr">
-        <is>
-          <t>mechanics:fuel,tank</t>
-        </is>
-      </c>
-      <c r="L4" s="12" t="inlineStr"/>
-      <c r="M4" s="12" t="inlineStr"/>
-      <c r="N4" s="12" t="inlineStr">
-        <is>
-          <t>fuel,pricing</t>
-        </is>
-      </c>
-      <c r="O4" s="12" t="inlineStr">
-        <is>
-          <t>fuel</t>
-        </is>
-      </c>
-      <c r="P4" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="12" t="inlineStr">
+      <c r="F16" s="13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G16" s="13" t="inlineStr">
+        <is>
+          <t>Week 3: four new routes</t>
+        </is>
+      </c>
+      <c r="H16" s="13" t="inlineStr">
+        <is>
+          <t>Amsterdam, Frankfurt, Geneva and Barcelona open. Fares step by £5.</t>
+        </is>
+      </c>
+      <c r="I16" s="13" t="inlineStr">
+        <is>
+          <t>Fuel £1.70 a litre. Red Kite flies from Luton.</t>
+        </is>
+      </c>
+      <c r="J16" s="13" t="inlineStr"/>
+      <c r="K16" s="13" t="inlineStr">
+        <is>
+          <t>routes: ams, fra, gva, bcn; mechanics: £5 fares, season badge on route cards, use-it-or-lose-it from this week</t>
+        </is>
+      </c>
+      <c r="L16" s="13" t="inlineStr"/>
+      <c r="M16" s="13" t="n"/>
+      <c r="N16" s="13" t="inlineStr">
+        <is>
+          <t>pricing,assignment,timetable</t>
+        </is>
+      </c>
+      <c r="O16" s="13" t="inlineStr">
+        <is>
+          <t>ticketRevenueLong,flightTime</t>
+        </is>
+      </c>
+      <c r="P16" s="13" t="n"/>
+      <c r="Q16" s="13" t="inlineStr">
         <is>
           <t>live</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="12" t="inlineStr">
-        <is>
-          <t>2030-09-05</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="12" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-      <c r="F5" s="12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="G5" s="12" t="inlineStr">
-        <is>
-          <t>Red Kite arrives</t>
-        </is>
-      </c>
-      <c r="H5" s="12" t="inlineStr">
-        <is>
-          <t>Red Kite Air cuts Dublin fares to £50!</t>
-        </is>
-      </c>
-      <c r="I5" s="12" t="inlineStr">
-        <is>
-          <t>Fuel £1.30 a litre.</t>
-        </is>
-      </c>
-      <c r="J5" s="12" t="inlineStr">
-        <is>
-          <t>undercut_dub</t>
-        </is>
-      </c>
-      <c r="K5" s="12" t="inlineStr">
-        <is>
-          <t>routes: the other of dub/par; mechanics: rival fares, time-of-day demand, second route</t>
-        </is>
-      </c>
-      <c r="L5" s="12" t="inlineStr"/>
-      <c r="M5" s="12" t="inlineStr">
-        <is>
-          <t>dub:50</t>
-        </is>
-      </c>
-      <c r="N5" s="12" t="inlineStr">
-        <is>
-          <t>pricing</t>
-        </is>
-      </c>
-      <c r="O5" s="12" t="inlineStr">
-        <is>
-          <t>revenue</t>
-        </is>
-      </c>
-      <c r="P5" s="12" t="inlineStr"/>
-      <c r="Q5" s="12" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>2030-09-06</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-      <c r="F6" s="12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="G6" s="12" t="inlineStr">
-        <is>
-          <t>The storm</t>
-        </is>
-      </c>
-      <c r="H6" s="12" t="inlineStr">
-        <is>
-          <t>Storm warning: strong winds over the Irish Sea.</t>
-        </is>
-      </c>
-      <c r="I6" s="12" t="inlineStr">
-        <is>
-          <t>Fuel £1.40 a litre and rising.</t>
-        </is>
-      </c>
-      <c r="J6" s="12" t="inlineStr">
-        <is>
-          <t>storm</t>
-        </is>
-      </c>
-      <c r="K6" s="12" t="inlineStr">
-        <is>
-          <t>mechanics:crew duty</t>
-        </is>
-      </c>
-      <c r="L6" s="12" t="inlineStr"/>
-      <c r="M6" s="12" t="inlineStr">
-        <is>
-          <t>dub:50</t>
-        </is>
-      </c>
-      <c r="N6" s="12" t="inlineStr">
-        <is>
-          <t>checkFlight,pricing</t>
-        </is>
-      </c>
-      <c r="O6" s="12" t="inlineStr">
-        <is>
-          <t>flight</t>
-        </is>
-      </c>
-      <c r="P6" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q6" s="12" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>2030-09-07</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>Sat</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="12" t="inlineStr">
-        <is>
-          <t>weekend</t>
-        </is>
-      </c>
-      <c r="F7" s="12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="G7" s="12" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="H7" s="12" t="inlineStr">
-        <is>
-          <t>Quiet weekend at the airport. Business travellers stay home; families fly.</t>
-        </is>
-      </c>
-      <c r="I7" s="12" t="inlineStr"/>
-      <c r="J7" s="12" t="inlineStr"/>
-      <c r="K7" s="12" t="inlineStr"/>
-      <c r="L7" s="12" t="inlineStr">
-        <is>
-          <t>weekend multipliers (Settings)</t>
-        </is>
-      </c>
-      <c r="M7" s="12" t="inlineStr">
-        <is>
-          <t>dub:50</t>
-        </is>
-      </c>
-      <c r="N7" s="12" t="inlineStr"/>
-      <c r="O7" s="12" t="inlineStr"/>
-      <c r="P7" s="12" t="inlineStr"/>
-      <c r="Q7" s="12" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>2030-09-08</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>Sun</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>weekend</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="G8" s="12" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="H8" s="12" t="inlineStr"/>
-      <c r="I8" s="12" t="inlineStr"/>
-      <c r="J8" s="12" t="inlineStr"/>
-      <c r="K8" s="12" t="inlineStr"/>
-      <c r="L8" s="12" t="inlineStr">
-        <is>
-          <t>weekend multipliers (Settings)</t>
-        </is>
-      </c>
-      <c r="M8" s="12" t="inlineStr">
-        <is>
-          <t>dub:50</t>
-        </is>
-      </c>
-      <c r="N8" s="12" t="inlineStr"/>
-      <c r="O8" s="12" t="inlineStr"/>
-      <c r="P8" s="12" t="inlineStr"/>
-      <c r="Q8" s="12" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>2030-09-09</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E9" s="12" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-      <c r="F9" s="12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G9" s="12" t="inlineStr">
-        <is>
-          <t>Week 2: a bigger airline</t>
-        </is>
-      </c>
-      <c r="H9" s="12" t="inlineStr">
-        <is>
-          <t>Four new destinations open. Time to choose a second aircraft.</t>
-        </is>
-      </c>
-      <c r="I9" s="12" t="inlineStr">
-        <is>
-          <t>Fuel £1.50 a litre. Red Kite, flying from Luton, says its costs are lower than yours.</t>
-        </is>
-      </c>
-      <c r="J9" s="12" t="inlineStr"/>
-      <c r="K9" s="12" t="inlineStr">
-        <is>
-          <t>routes:ams,fra,gva,bcn; planes:saab340,atr72,dhc6; mechanics:assignment,finance,season badge</t>
-        </is>
-      </c>
-      <c r="L9" s="12" t="inlineStr"/>
-      <c r="M9" s="12" t="inlineStr"/>
-      <c r="N9" s="12" t="inlineStr">
-        <is>
-          <t>fleet,assignment,pricing</t>
-        </is>
-      </c>
-      <c r="O9" s="12" t="inlineStr">
-        <is>
-          <t>revenue</t>
-        </is>
-      </c>
-      <c r="P9" s="12" t="inlineStr"/>
-      <c r="Q9" s="12" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>2030-09-10</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E10" s="12" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-      <c r="F10" s="12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G10" s="12" t="inlineStr">
-        <is>
-          <t>Two planes, two plans</t>
-        </is>
-      </c>
-      <c r="H10" s="12" t="inlineStr">
-        <is>
-          <t>Your second aircraft flies today.</t>
-        </is>
-      </c>
-      <c r="I10" s="12" t="inlineStr">
-        <is>
-          <t>Barcelona still warm; Geneva quiet until the snow.</t>
-        </is>
-      </c>
-      <c r="J10" s="12" t="inlineStr"/>
-      <c r="K10" s="12" t="inlineStr">
-        <is>
-          <t>mechanics:two timetables</t>
-        </is>
-      </c>
-      <c r="L10" s="12" t="inlineStr"/>
-      <c r="M10" s="12" t="inlineStr"/>
-      <c r="N10" s="12" t="inlineStr">
-        <is>
-          <t>assignment,pricing</t>
-        </is>
-      </c>
-      <c r="O10" s="12" t="inlineStr">
-        <is>
-          <t>revenue</t>
-        </is>
-      </c>
-      <c r="P10" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q10" s="12" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>2030-09-11</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E11" s="12" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-      <c r="F11" s="12" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="G11" s="12" t="inlineStr">
-        <is>
-          <t>Who flies where?</t>
-        </is>
-      </c>
-      <c r="H11" s="12" t="inlineStr">
-        <is>
-          <t>Amsterdam is heaving. Paris is not.</t>
-        </is>
-      </c>
-      <c r="I11" s="12" t="inlineStr">
-        <is>
-          <t>Fuel £1.60 a litre.</t>
-        </is>
-      </c>
-      <c r="J11" s="12" t="inlineStr"/>
-      <c r="K11" s="12" t="inlineStr"/>
-      <c r="L11" s="12" t="inlineStr"/>
-      <c r="M11" s="12" t="inlineStr"/>
-      <c r="N11" s="12" t="inlineStr">
-        <is>
-          <t>assignment,fuel</t>
-        </is>
-      </c>
-      <c r="O11" s="12" t="inlineStr">
-        <is>
-          <t>fuel</t>
-        </is>
-      </c>
-      <c r="P11" s="12" t="inlineStr"/>
-      <c r="Q11" s="12" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>2030-09-12</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E12" s="12" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-      <c r="F12" s="12" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="G12" s="12" t="inlineStr">
-        <is>
-          <t>Crew sickness</t>
-        </is>
-      </c>
-      <c r="H12" s="12" t="inlineStr">
-        <is>
-          <t>Flu going round the airport this week.</t>
-        </is>
-      </c>
-      <c r="I12" s="12" t="inlineStr">
-        <is>
-          <t>Fuel £1.60 a litre.</t>
-        </is>
-      </c>
-      <c r="J12" s="12" t="inlineStr">
-        <is>
-          <t>crew</t>
-        </is>
-      </c>
-      <c r="K12" s="12" t="inlineStr"/>
-      <c r="L12" s="12" t="inlineStr"/>
-      <c r="M12" s="12" t="inlineStr"/>
-      <c r="N12" s="12" t="inlineStr">
-        <is>
-          <t>pricing</t>
-        </is>
-      </c>
-      <c r="O12" s="12" t="inlineStr">
-        <is>
-          <t>revenue</t>
-        </is>
-      </c>
-      <c r="P12" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q12" s="12" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>2030-09-13</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E13" s="12" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-      <c r="F13" s="12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="G13" s="12" t="inlineStr">
-        <is>
-          <t>Season forecast</t>
-        </is>
-      </c>
-      <c r="H13" s="12" t="inlineStr">
-        <is>
-          <t>Weather office: a cold, snowy winter is on the way.</t>
-        </is>
-      </c>
-      <c r="I13" s="12" t="inlineStr">
-        <is>
-          <t>Fuel £1.70 a litre.</t>
-        </is>
-      </c>
-      <c r="J13" s="12" t="inlineStr"/>
-      <c r="K13" s="12" t="inlineStr">
-        <is>
-          <t>mechanics:season forecast card</t>
-        </is>
-      </c>
-      <c r="L13" s="12" t="inlineStr">
-        <is>
-          <t>gva:+10</t>
-        </is>
-      </c>
-      <c r="M13" s="12" t="inlineStr"/>
-      <c r="N13" s="12" t="inlineStr">
-        <is>
-          <t>pricing,cabin</t>
-        </is>
-      </c>
-      <c r="O13" s="12" t="inlineStr">
-        <is>
-          <t>cabin</t>
-        </is>
-      </c>
-      <c r="P13" s="12" t="inlineStr"/>
-      <c r="Q13" s="12" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>2030-09-14</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>Sat</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E14" s="12" t="inlineStr">
-        <is>
-          <t>weekend</t>
-        </is>
-      </c>
-      <c r="F14" s="12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="G14" s="12" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="H14" s="12" t="inlineStr"/>
-      <c r="I14" s="12" t="inlineStr"/>
-      <c r="J14" s="12" t="inlineStr"/>
-      <c r="K14" s="12" t="inlineStr"/>
-      <c r="L14" s="12" t="inlineStr">
-        <is>
-          <t>weekend multipliers (Settings)</t>
-        </is>
-      </c>
-      <c r="M14" s="12" t="inlineStr"/>
-      <c r="N14" s="12" t="inlineStr"/>
-      <c r="O14" s="12" t="inlineStr"/>
-      <c r="P14" s="12" t="inlineStr"/>
-      <c r="Q14" s="12" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>2030-09-15</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>Sun</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" s="12" t="inlineStr">
-        <is>
-          <t>weekend</t>
-        </is>
-      </c>
-      <c r="F15" s="12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="G15" s="12" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="H15" s="12" t="inlineStr"/>
-      <c r="I15" s="12" t="inlineStr"/>
-      <c r="J15" s="12" t="inlineStr"/>
-      <c r="K15" s="12" t="inlineStr"/>
-      <c r="L15" s="12" t="inlineStr">
-        <is>
-          <t>weekend multipliers (Settings)</t>
-        </is>
-      </c>
-      <c r="M15" s="12" t="inlineStr"/>
-      <c r="N15" s="12" t="inlineStr"/>
-      <c r="O15" s="12" t="inlineStr"/>
-      <c r="P15" s="12" t="inlineStr"/>
-      <c r="Q15" s="12" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="12" t="inlineStr">
-        <is>
-          <t>2030-09-16</t>
-        </is>
-      </c>
-      <c r="C16" s="12" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="E16" s="12" t="inlineStr">
-        <is>
-          <t>day</t>
-        </is>
-      </c>
-      <c r="F16" s="12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="G16" s="12" t="inlineStr">
-        <is>
-          <t>Week 3: medium haul</t>
-        </is>
-      </c>
-      <c r="H16" s="12" t="inlineStr">
-        <is>
-          <t>Madrid opens. A jet appears in the shop.</t>
-        </is>
-      </c>
-      <c r="I16" s="12" t="inlineStr">
-        <is>
-          <t>Fuel £1.70 a litre.</t>
-        </is>
-      </c>
-      <c r="J16" s="12" t="inlineStr"/>
-      <c r="K16" s="12" t="inlineStr">
-        <is>
-          <t>routes: mad; planes: e190; mechanics: range check, services per day on a long leg (ATR or E190)</t>
-        </is>
-      </c>
-      <c r="L16" s="12" t="inlineStr"/>
-      <c r="M16" s="12" t="inlineStr"/>
-      <c r="N16" s="12" t="inlineStr">
-        <is>
-          <t>fleet,assignment,pricing</t>
-        </is>
-      </c>
-      <c r="O16" s="12" t="inlineStr">
-        <is>
-          <t>range,flightTime</t>
-        </is>
-      </c>
-      <c r="P16" s="12" t="inlineStr"/>
-      <c r="Q16" s="12" t="inlineStr">
-        <is>
-          <t>live</t>
+      <c r="R16" s="13" t="inlineStr">
+        <is>
+          <t>plan</t>
         </is>
       </c>
     </row>
@@ -2111,33 +2094,26 @@
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
-          <t>Two planes, three routes</t>
-        </is>
-      </c>
-      <c r="H17" s="13" t="inlineStr">
-        <is>
-          <t>Where does the jet earn most?</t>
-        </is>
-      </c>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="H17" s="13" t="inlineStr"/>
       <c r="I17" s="13" t="inlineStr"/>
-      <c r="J17" s="13" t="n"/>
-      <c r="K17" s="13" t="n"/>
+      <c r="J17" s="13" t="inlineStr"/>
+      <c r="K17" s="13" t="inlineStr"/>
       <c r="L17" s="13" t="inlineStr"/>
       <c r="M17" s="13" t="n"/>
-      <c r="N17" s="13" t="inlineStr">
-        <is>
-          <t>assignment,pricing</t>
-        </is>
-      </c>
-      <c r="O17" s="13" t="inlineStr">
-        <is>
-          <t>revenue</t>
-        </is>
-      </c>
+      <c r="N17" s="13" t="inlineStr"/>
+      <c r="O17" s="13" t="inlineStr"/>
       <c r="P17" s="13" t="n"/>
       <c r="Q17" s="13" t="inlineStr">
         <is>
           <t>live</t>
+        </is>
+      </c>
+      <c r="R17" s="13" t="inlineStr">
+        <is>
+          <t>run</t>
         </is>
       </c>
     </row>
@@ -2168,37 +2144,26 @@
       </c>
       <c r="G18" s="13" t="inlineStr">
         <is>
-          <t>Fuel for a jet</t>
-        </is>
-      </c>
-      <c r="H18" s="13" t="inlineStr">
-        <is>
-          <t>A jet burns in one trip what a Twin Otter burns in a week.</t>
-        </is>
-      </c>
-      <c r="I18" s="13" t="inlineStr">
-        <is>
-          <t>Fuel £1.70 a litre.</t>
-        </is>
-      </c>
-      <c r="J18" s="13" t="n"/>
-      <c r="K18" s="13" t="n"/>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="H18" s="13" t="inlineStr"/>
+      <c r="I18" s="13" t="inlineStr"/>
+      <c r="J18" s="13" t="inlineStr"/>
+      <c r="K18" s="13" t="inlineStr"/>
       <c r="L18" s="13" t="inlineStr"/>
       <c r="M18" s="13" t="n"/>
-      <c r="N18" s="13" t="inlineStr">
-        <is>
-          <t>fuel</t>
-        </is>
-      </c>
-      <c r="O18" s="13" t="inlineStr">
-        <is>
-          <t>fuel</t>
-        </is>
-      </c>
+      <c r="N18" s="13" t="inlineStr"/>
+      <c r="O18" s="13" t="inlineStr"/>
       <c r="P18" s="13" t="n"/>
       <c r="Q18" s="13" t="inlineStr">
         <is>
           <t>live</t>
+        </is>
+      </c>
+      <c r="R18" s="13" t="inlineStr">
+        <is>
+          <t>run</t>
         </is>
       </c>
     </row>
@@ -2229,33 +2194,26 @@
       </c>
       <c r="G19" s="13" t="inlineStr">
         <is>
-          <t>Red Kite copies you</t>
-        </is>
-      </c>
-      <c r="H19" s="13" t="inlineStr">
-        <is>
-          <t>Red Kite announces Madrid flights from Luton.</t>
-        </is>
-      </c>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="H19" s="13" t="inlineStr"/>
       <c r="I19" s="13" t="inlineStr"/>
-      <c r="J19" s="13" t="n"/>
-      <c r="K19" s="13" t="n"/>
+      <c r="J19" s="13" t="inlineStr"/>
+      <c r="K19" s="13" t="inlineStr"/>
       <c r="L19" s="13" t="inlineStr"/>
       <c r="M19" s="13" t="n"/>
-      <c r="N19" s="13" t="inlineStr">
-        <is>
-          <t>pricing</t>
-        </is>
-      </c>
-      <c r="O19" s="13" t="inlineStr">
-        <is>
-          <t>revenue</t>
-        </is>
-      </c>
+      <c r="N19" s="13" t="inlineStr"/>
+      <c r="O19" s="13" t="inlineStr"/>
       <c r="P19" s="13" t="n"/>
       <c r="Q19" s="13" t="inlineStr">
         <is>
           <t>live</t>
+        </is>
+      </c>
+      <c r="R19" s="13" t="inlineStr">
+        <is>
+          <t>run</t>
         </is>
       </c>
     </row>
@@ -2286,33 +2244,34 @@
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
-          <t>Full planes</t>
+          <t>Friday: the season forecast</t>
         </is>
       </c>
       <c r="H20" s="13" t="inlineStr">
         <is>
-          <t>Operations: the Madrid flight was full. Was the fare right?</t>
+          <t>The weather office forecasts a cold, snowy winter.</t>
         </is>
       </c>
       <c r="I20" s="13" t="inlineStr"/>
-      <c r="J20" s="13" t="n"/>
-      <c r="K20" s="13" t="n"/>
+      <c r="J20" s="13" t="inlineStr"/>
+      <c r="K20" s="13" t="inlineStr">
+        <is>
+          <t>mechanics: season forecast card</t>
+        </is>
+      </c>
       <c r="L20" s="13" t="inlineStr"/>
       <c r="M20" s="13" t="n"/>
-      <c r="N20" s="13" t="inlineStr">
-        <is>
-          <t>pricing</t>
-        </is>
-      </c>
-      <c r="O20" s="13" t="inlineStr">
-        <is>
-          <t>emptySeats</t>
-        </is>
-      </c>
+      <c r="N20" s="13" t="inlineStr"/>
+      <c r="O20" s="13" t="inlineStr"/>
       <c r="P20" s="13" t="n"/>
       <c r="Q20" s="13" t="inlineStr">
         <is>
           <t>live</t>
+        </is>
+      </c>
+      <c r="R20" s="13" t="inlineStr">
+        <is>
+          <t>run</t>
         </is>
       </c>
     </row>
@@ -2348,8 +2307,8 @@
       </c>
       <c r="H21" s="13" t="inlineStr"/>
       <c r="I21" s="13" t="inlineStr"/>
-      <c r="J21" s="13" t="n"/>
-      <c r="K21" s="13" t="n"/>
+      <c r="J21" s="13" t="inlineStr"/>
+      <c r="K21" s="13" t="inlineStr"/>
       <c r="L21" s="13" t="inlineStr">
         <is>
           <t>weekend multipliers (Settings)</t>
@@ -2364,6 +2323,11 @@
           <t>live</t>
         </is>
       </c>
+      <c r="R21" s="13" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="13" t="n">
@@ -2392,25 +2356,448 @@
       </c>
       <c r="G22" s="13" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Sunday: week 3 accounts</t>
         </is>
       </c>
       <c r="H22" s="13" t="inlineStr"/>
       <c r="I22" s="13" t="inlineStr"/>
-      <c r="J22" s="13" t="n"/>
-      <c r="K22" s="13" t="n"/>
+      <c r="J22" s="13" t="inlineStr"/>
+      <c r="K22" s="13" t="inlineStr"/>
       <c r="L22" s="13" t="inlineStr">
         <is>
           <t>weekend multipliers (Settings)</t>
         </is>
       </c>
       <c r="M22" s="13" t="n"/>
-      <c r="N22" s="13" t="inlineStr"/>
-      <c r="O22" s="13" t="inlineStr"/>
+      <c r="N22" s="13" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="O22" s="13" t="inlineStr">
+        <is>
+          <t>weekTotal,projectedVsActual</t>
+        </is>
+      </c>
       <c r="P22" s="13" t="n"/>
       <c r="Q22" s="13" t="inlineStr">
         <is>
           <t>live</t>
+        </is>
+      </c>
+      <c r="R22" s="13" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>2030-09-23</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G23" s="13" t="inlineStr">
+        <is>
+          <t>Week 4: medium haul</t>
+        </is>
+      </c>
+      <c r="H23" s="13" t="inlineStr">
+        <is>
+          <t>Madrid opens. Two jets are in the shop: the E175 and the E190. Does your plane have the range?</t>
+        </is>
+      </c>
+      <c r="I23" s="13" t="inlineStr">
+        <is>
+          <t>Fuel £1.80 a litre.</t>
+        </is>
+      </c>
+      <c r="J23" s="13" t="inlineStr"/>
+      <c r="K23" s="13" t="inlineStr">
+        <is>
+          <t>routes: mad; planes: e175, e190; mechanics: range check, services per day on a long leg, load factor as a percentage</t>
+        </is>
+      </c>
+      <c r="L23" s="13" t="inlineStr"/>
+      <c r="M23" s="13" t="n"/>
+      <c r="N23" s="13" t="inlineStr">
+        <is>
+          <t>fleet,assignment,pricing</t>
+        </is>
+      </c>
+      <c r="O23" s="13" t="inlineStr">
+        <is>
+          <t>range,flightTime,loadFactor</t>
+        </is>
+      </c>
+      <c r="P23" s="13" t="n"/>
+      <c r="Q23" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="R23" s="13" t="inlineStr">
+        <is>
+          <t>plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>2030-09-24</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="F24" s="13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G24" s="13" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="H24" s="13" t="inlineStr"/>
+      <c r="I24" s="13" t="inlineStr"/>
+      <c r="J24" s="13" t="inlineStr"/>
+      <c r="K24" s="13" t="inlineStr"/>
+      <c r="L24" s="13" t="inlineStr"/>
+      <c r="M24" s="13" t="n"/>
+      <c r="N24" s="13" t="inlineStr"/>
+      <c r="O24" s="13" t="inlineStr"/>
+      <c r="P24" s="13" t="n"/>
+      <c r="Q24" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="R24" s="13" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>2030-09-25</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G25" s="13" t="inlineStr">
+        <is>
+          <t>Wednesday: fuel for a jet</t>
+        </is>
+      </c>
+      <c r="H25" s="13" t="inlineStr">
+        <is>
+          <t>A jet burns in one trip what a Twin Otter burns in a week.</t>
+        </is>
+      </c>
+      <c r="I25" s="13" t="inlineStr"/>
+      <c r="J25" s="13" t="inlineStr"/>
+      <c r="K25" s="13" t="inlineStr"/>
+      <c r="L25" s="13" t="inlineStr"/>
+      <c r="M25" s="13" t="n"/>
+      <c r="N25" s="13" t="inlineStr">
+        <is>
+          <t>fuel</t>
+        </is>
+      </c>
+      <c r="O25" s="13" t="inlineStr">
+        <is>
+          <t>fuelCost</t>
+        </is>
+      </c>
+      <c r="P25" s="13" t="n"/>
+      <c r="Q25" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="R25" s="13" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>2030-09-26</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="F26" s="13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G26" s="13" t="inlineStr">
+        <is>
+          <t>Thursday: Red Kite copies you</t>
+        </is>
+      </c>
+      <c r="H26" s="13" t="inlineStr">
+        <is>
+          <t>Red Kite announces Madrid flights from Luton.</t>
+        </is>
+      </c>
+      <c r="I26" s="13" t="inlineStr"/>
+      <c r="J26" s="13" t="inlineStr"/>
+      <c r="K26" s="13" t="inlineStr"/>
+      <c r="L26" s="13" t="inlineStr"/>
+      <c r="M26" s="13" t="n"/>
+      <c r="N26" s="13" t="inlineStr"/>
+      <c r="O26" s="13" t="inlineStr"/>
+      <c r="P26" s="13" t="n"/>
+      <c r="Q26" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="R26" s="13" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>2030-09-27</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G27" s="13" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="H27" s="13" t="inlineStr"/>
+      <c r="I27" s="13" t="inlineStr"/>
+      <c r="J27" s="13" t="inlineStr"/>
+      <c r="K27" s="13" t="inlineStr"/>
+      <c r="L27" s="13" t="inlineStr"/>
+      <c r="M27" s="13" t="n"/>
+      <c r="N27" s="13" t="inlineStr"/>
+      <c r="O27" s="13" t="inlineStr"/>
+      <c r="P27" s="13" t="n"/>
+      <c r="Q27" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="R27" s="13" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>2030-09-28</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>weekend</t>
+        </is>
+      </c>
+      <c r="F28" s="13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G28" s="13" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="H28" s="13" t="inlineStr"/>
+      <c r="I28" s="13" t="inlineStr"/>
+      <c r="J28" s="13" t="inlineStr"/>
+      <c r="K28" s="13" t="inlineStr"/>
+      <c r="L28" s="13" t="inlineStr">
+        <is>
+          <t>weekend multipliers (Settings)</t>
+        </is>
+      </c>
+      <c r="M28" s="13" t="n"/>
+      <c r="N28" s="13" t="inlineStr"/>
+      <c r="O28" s="13" t="inlineStr"/>
+      <c r="P28" s="13" t="n"/>
+      <c r="Q28" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="R28" s="13" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>2030-09-29</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="D29" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>weekend</t>
+        </is>
+      </c>
+      <c r="F29" s="13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G29" s="13" t="inlineStr">
+        <is>
+          <t>Sunday: week 4 accounts; chapter 1 moves to weekly play</t>
+        </is>
+      </c>
+      <c r="H29" s="13" t="inlineStr">
+        <is>
+          <t>From next week the game runs a week at a time.</t>
+        </is>
+      </c>
+      <c r="I29" s="13" t="inlineStr"/>
+      <c r="J29" s="13" t="inlineStr"/>
+      <c r="K29" s="13" t="inlineStr">
+        <is>
+          <t>mechanics: weekly skips begin day 29</t>
+        </is>
+      </c>
+      <c r="L29" s="13" t="inlineStr">
+        <is>
+          <t>weekend multipliers (Settings)</t>
+        </is>
+      </c>
+      <c r="M29" s="13" t="n"/>
+      <c r="N29" s="13" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="O29" s="13" t="inlineStr">
+        <is>
+          <t>weekTotal,projectedVsActual</t>
+        </is>
+      </c>
+      <c r="P29" s="13" t="n"/>
+      <c r="Q29" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="R29" s="13" t="inlineStr">
+        <is>
+          <t>review</t>
         </is>
       </c>
     </row>
@@ -20340,7 +20727,7 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>2030-10-15</t>
+          <t>2030-10-14</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
@@ -20424,7 +20811,7 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>2030-11-03</t>
+          <t>2030-11-02</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
@@ -20464,7 +20851,7 @@
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>2030-11-12</t>
+          <t>2030-11-11</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
@@ -20518,7 +20905,7 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>2030-12-03</t>
+          <t>2030-12-02</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -20558,7 +20945,7 @@
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>2030-12-17</t>
+          <t>2030-12-16</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
@@ -21961,7 +22348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -21998,12 +22385,12 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>Fare, services, plane-loads, timetable</t>
+          <t>Launch Day: standing plan on one page; all opening sums in one sitting (tickets ×3, profit, snacks ×2, fuel); both routes; modelling tool; workings page</t>
         </is>
       </c>
       <c r="C2" s="13" t="inlineStr">
         <is>
-          <t>Launch Day</t>
+          <t>D52, D54</t>
         </is>
       </c>
       <c r="D2" s="13" t="inlineStr">
@@ -22018,10 +22405,14 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Snacks (by hand once, then model)</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr"/>
+          <t>The week runs day by day on the operations board; results equal the projection; pauses for events (day 4 Red Kite with numbers, day 5 storm)</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>D52, D50</t>
+        </is>
+      </c>
       <c r="D3" s="13" t="inlineStr">
         <is>
           <t>live</t>
@@ -22030,14 +22421,18 @@
     </row>
     <row r="4">
       <c r="A4" s="13" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>Fuel: litres, price, tank</t>
-        </is>
-      </c>
-      <c r="C4" s="13" t="inlineStr"/>
+          <t>Weekly review every Sunday: seven-row table, total by hand, projected − actual, missed-profit line</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>D55</t>
+        </is>
+      </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
           <t>live</t>
@@ -22046,14 +22441,18 @@
     </row>
     <row r="5">
       <c r="A5" s="13" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Rival fares; time-of-day demand; second route</t>
-        </is>
-      </c>
-      <c r="C5" s="13" t="inlineStr"/>
+          <t>Week 2: second plane; rent-or-buy sum; launch-deal finance; Buy greyed until affordable; two timetables; assignment</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>D53, D55</t>
+        </is>
+      </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
           <t>live</t>
@@ -22062,14 +22461,18 @@
     </row>
     <row r="6">
       <c r="A6" s="13" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Crew duty and second crew</t>
-        </is>
-      </c>
-      <c r="C6" s="13" t="inlineStr"/>
+          <t>Week 3: four routes; £5 fares; season badge; use-it-or-lose-it begins</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>D28, D55</t>
+        </is>
+      </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
           <t>live</t>
@@ -22078,11 +22481,11 @@
     </row>
     <row r="7">
       <c r="A7" s="13" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>Weekend demand</t>
+          <t>Season forecast card</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr"/>
@@ -22094,16 +22497,16 @@
     </row>
     <row r="8">
       <c r="A8" s="13" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>Second plane: buy or rent (tutorial tier); the rent-or-buy sum; assignment; season badge; £5 fares</t>
+          <t>Week 4: medium haul; range check; services per day; E175 and E190; load factor as a percentage</t>
         </is>
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>Week 2</t>
+          <t>D19, D23</t>
         </is>
       </c>
       <c r="D8" s="13" t="inlineStr">
@@ -22114,14 +22517,18 @@
     </row>
     <row r="9">
       <c r="A9" s="13" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>Two timetables; one plane on two routes</t>
-        </is>
-      </c>
-      <c r="C9" s="13" t="inlineStr"/>
+          <t>Week-at-a-time skips; Marrakech; event costs as a share of a day</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>D21</t>
+        </is>
+      </c>
       <c r="D9" s="13" t="inlineStr">
         <is>
           <t>live</t>
@@ -22129,12 +22536,14 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="n">
-        <v>12</v>
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>2030-12-02</t>
+        </is>
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>Season forecast card</t>
+          <t>Month-at-a-time play; monthly reports from here on</t>
         </is>
       </c>
       <c r="C10" s="13" t="inlineStr"/>
@@ -22145,19 +22554,17 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="n">
-        <v>15</v>
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>2030-12-29</t>
+        </is>
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>Medium haul: range check, services per day; E175 and E190 in the shop</t>
-        </is>
-      </c>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>Week 3</t>
-        </is>
-      </c>
+          <t>Chapter 1 review: chapter accounts by hand; the long-haul decision</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr"/>
       <c r="D11" s="13" t="inlineStr">
         <is>
           <t>live</t>
@@ -22165,85 +22572,71 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="n">
-        <v>22</v>
-      </c>
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>Week-at-a-time play; load factor %; event costs as a share of profit; weekly review</t>
-        </is>
-      </c>
-      <c r="C12" s="13" t="inlineStr">
-        <is>
-          <t>Week 4</t>
-        </is>
-      </c>
-      <c r="D12" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>2031-01-06</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>CHAPTER 2: long haul, overnight rotations, time zones; leasing; reputation revealed; airline type; Value extras; crew cost by type; Captain's challenges; hunts</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr"/>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>placeholder</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>2030-12-02</t>
-        </is>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>Month-at-a-time play; monthly reports from here on</t>
-        </is>
-      </c>
-      <c r="C13" s="13" t="inlineStr">
-        <is>
-          <t>Chapter 1 run</t>
-        </is>
-      </c>
-      <c r="D13" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>2031-08-31</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>Chapter 2 review</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr"/>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>placeholder</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t>2030-12-28</t>
-        </is>
-      </c>
-      <c r="B14" s="13" t="inlineStr">
-        <is>
-          <t>Chapter 1 review: chapter accounts by hand; the long-haul decision</t>
-        </is>
-      </c>
-      <c r="C14" s="13" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="D14" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>2031-09-02</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>CHAPTER 3: buy outright; overdraft safety net</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr"/>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>placeholder</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>2031-01-06</t>
+          <t>2032-08-31</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>CHAPTER 2 set-up: long haul, overnight rotations, time zones; leasing (standing); reputation revealed; airline type; Value extras; Captain's challenges begin</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="inlineStr">
-        <is>
-          <t>Chapter 2</t>
-        </is>
-      </c>
+          <t>Chapter 3 review</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr"/>
       <c r="D15" s="14" t="inlineStr">
         <is>
           <t>placeholder</t>
@@ -22251,87 +22644,71 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t>2031-08-31</t>
-        </is>
-      </c>
-      <c r="B16" s="14" t="inlineStr">
-        <is>
-          <t>Chapter 2 review: year-1 accounts, first hunt, next investment</t>
-        </is>
-      </c>
-      <c r="C16" s="14" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="D16" s="14" t="inlineStr">
-        <is>
-          <t>placeholder</t>
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>2032-09-07</t>
+        </is>
+      </c>
+      <c r="B16" s="18" t="inlineStr">
+        <is>
+          <t>CHAPTER 4: A380 on finance; reputation that matters</t>
+        </is>
+      </c>
+      <c r="C16" s="18" t="inlineStr"/>
+      <c r="D16" s="18" t="inlineStr">
+        <is>
+          <t>later</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="inlineStr">
-        <is>
-          <t>2031-09-02</t>
-        </is>
-      </c>
-      <c r="B17" s="14" t="inlineStr">
-        <is>
-          <t>CHAPTER 3 set-up: buy outright (price − cash, ÷ profit a week); overdraft safety net</t>
-        </is>
-      </c>
-      <c r="C17" s="14" t="inlineStr">
-        <is>
-          <t>Chapter 3</t>
-        </is>
-      </c>
-      <c r="D17" s="14" t="inlineStr">
-        <is>
-          <t>placeholder</t>
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t>2033-08-31</t>
+        </is>
+      </c>
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t>Chapter 4 review</t>
+        </is>
+      </c>
+      <c r="C17" s="18" t="inlineStr"/>
+      <c r="D17" s="18" t="inlineStr">
+        <is>
+          <t>later</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="14" t="inlineStr">
-        <is>
-          <t>2032-08-31</t>
-        </is>
-      </c>
-      <c r="B18" s="14" t="inlineStr">
-        <is>
-          <t>Chapter 3 review</t>
-        </is>
-      </c>
-      <c r="C18" s="14" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="D18" s="14" t="inlineStr">
-        <is>
-          <t>placeholder</t>
+      <c r="A18" s="18" t="inlineStr">
+        <is>
+          <t>2033-09-06</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>CHAPTER 5: rival enters the best route; marketing; quarterly comparison task</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="inlineStr"/>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>later</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="18" t="inlineStr">
         <is>
-          <t>2032-09-07</t>
+          <t>2034-08-31</t>
         </is>
       </c>
       <c r="B19" s="18" t="inlineStr">
         <is>
-          <t>CHAPTER 4 set-up: the A380; reputation that moves demand; finance (deposit, weekly repayments)</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>Chapter 4</t>
-        </is>
-      </c>
+          <t>Chapter 5 review</t>
+        </is>
+      </c>
+      <c r="C19" s="18" t="inlineStr"/>
       <c r="D19" s="18" t="inlineStr">
         <is>
           <t>later</t>
@@ -22341,19 +22718,15 @@
     <row r="20">
       <c r="A20" s="18" t="inlineStr">
         <is>
-          <t>2033-08-31</t>
+          <t>2034-09-05</t>
         </is>
       </c>
       <c r="B20" s="18" t="inlineStr">
         <is>
-          <t>Chapter 4 review</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
+          <t>CHAPTER 6: no new mechanic; the five-year review</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="inlineStr"/>
       <c r="D20" s="18" t="inlineStr">
         <is>
           <t>later</t>
@@ -22361,128 +22734,22 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="inlineStr">
-        <is>
-          <t>2033-09-06</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>CHAPTER 5 set-up: rival enters the best route; marketing; quarterly comparison task</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>Chapter 5</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="18" t="inlineStr">
-        <is>
-          <t>2034-08-31</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>Chapter 5 review</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>Review</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="18" t="inlineStr">
-        <is>
-          <t>2034-09-05</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>CHAPTER 6: no new mechanic; the five-year review builds through the year</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>Chapter 6</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="18" t="inlineStr">
-        <is>
-          <t>2035-08-31</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
-        <is>
-          <t>Five-year review: graphs and averages</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="inlineStr">
-        <is>
-          <t>End</t>
-        </is>
-      </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="13" t="inlineStr">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>rule</t>
         </is>
       </c>
-      <c r="B25" s="13" t="inlineStr">
-        <is>
-          <t>Reports follow the time step (D40); hand sums follow HandSumRules (D34); cash rules D26 with no overdraft charge (F7)</t>
-        </is>
-      </c>
-      <c r="C25" s="13" t="inlineStr"/>
-      <c r="D25" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="13" t="inlineStr">
-        <is>
-          <t>rule</t>
-        </is>
-      </c>
-      <c r="B26" s="13" t="inlineStr">
-        <is>
-          <t>No second hub, no sell-back, no fleet renewal, no investor; Heathrow only; Luton via the April 2031 event</t>
-        </is>
-      </c>
-      <c r="C26" s="13" t="inlineStr">
-        <is>
-          <t>D25 D31 D32 D44 D46</t>
-        </is>
-      </c>
-      <c r="D26" s="13" t="inlineStr">
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>No crew mechanic before 2031-01-06; no second hub, sell-back, fleet renewal, investor; Heathrow only; cash reserve block before Sep 2031; HandSumRules govern hand sums</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>D51 D31 D25 D46 D44 D32 D26 D34</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
         <is>
           <t>live</t>
         </is>
@@ -24149,11 +24416,11 @@
         </is>
       </c>
       <c r="E2" s="13" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="F2" s="13" t="inlineStr">
         <is>
-          <t>day → week (from day 22) → month (from Dec)</t>
+          <t>week (plan → run → review) to day 28; week-skips from day 29; months from 2030-12-02</t>
         </is>
       </c>
       <c r="G2" s="13" t="inlineStr">
@@ -24163,12 +24430,12 @@
       </c>
       <c r="H2" s="13" t="inlineStr">
         <is>
-          <t>Running an airline: fare, services, timetable, fuel, time of day, two routes, a second plane, medium haul</t>
+          <t>Running an airline a week at a time: the standing plan on one page (timetable with demand curve, fare, snacks, fuel), the week on the operations board, the weekly review</t>
         </is>
       </c>
       <c r="I2" s="13" t="inlineStr">
         <is>
-          <t>timetable; snacks; fuel; rival fares; crew duty; weekends; second plane (buy or lease, tutorial tier); seasons; medium haul; £5 fares; load factor % (day 22); scaled event costs (day 22)</t>
+          <t>Launch Day: timetable, fare, snacks, fuel, both routes, modelling tool, workings page; week 2: second plane, rent-or-buy, launch-deal finance; week 3: four routes, £5 fares, seasons, use-it-or-lose-it; week 4: medium haul, range, E175/E190, load factor %; from week 5: weekly skips, Marrakech, the autumn pairs, scaled event costs</t>
         </is>
       </c>
       <c r="J2" s="13" t="n">
@@ -24784,7 +25051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D57"/>
+  <dimension ref="A1:D66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -25294,11 +25561,11 @@
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C25" s="13" t="inlineStr">
         <is>
-          <t>From day 22 (week 4) an event's cost is costShare × yesterday's profit, rounded to £10 and printed on the card (D21). Days 1–21 use the fixed cash column.</t>
+          <t>D21: fixed pounds through week 4 (the four fully written events); costShare from week 5 (day 29).</t>
         </is>
       </c>
       <c r="D25" s="13" t="inlineStr">
@@ -25318,7 +25585,7 @@
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>Load factor shown as a percentage from the first weekly review; before that '15 of 19' and empty seats only (D23).</t>
+          <t>D23: from the week-4 review.</t>
         </is>
       </c>
       <c r="D26" s="13" t="inlineStr">
@@ -25620,7 +25887,7 @@
       </c>
       <c r="C40" s="13" t="inlineStr">
         <is>
-          <t>HandSumRules rule 2: fuel is asked by hand when the price has moved 50p or more since it was last asked.</t>
+          <t>HandSumRules rule 2. Launch Day's fuel sum is done at Wednesday's price (£1.30); the next by hand is the week of 14 October (£3.00).</t>
         </is>
       </c>
       <c r="D40" s="13" t="inlineStr">
@@ -25904,84 +26171,260 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="23" t="inlineStr">
+      <c r="A54" s="13" t="inlineStr">
+        <is>
+          <t>openingPlayMode</t>
+        </is>
+      </c>
+      <c r="B54" s="13" t="inlineStr">
+        <is>
+          <t>week</t>
+        </is>
+      </c>
+      <c r="C54" s="13" t="inlineStr">
+        <is>
+          <t>D52: in chapter 1 the pupil builds a standing plan on one page, the week runs day by day on the operations board pausing only for events, and ends with a seven-row table, the total by hand and projected against actual. Day-by-day play remains a teacher option (teacherDayByDay).</t>
+        </is>
+      </c>
+      <c r="D54" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="13" t="inlineStr">
+        <is>
+          <t>teacherDayByDay</t>
+        </is>
+      </c>
+      <c r="B55" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="C55" s="13" t="inlineStr">
+        <is>
+          <t>Teacher panel: TRUE runs chapter 1 a day at a time instead of a week at a time.</t>
+        </is>
+      </c>
+      <c r="D55" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="13" t="inlineStr">
+        <is>
+          <t>weeklyReviewFromDay</t>
+        </is>
+      </c>
+      <c r="B56" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="C56" s="13" t="inlineStr">
+        <is>
+          <t>Every week ends with a review: seven-row table, total by hand, projected − actual, missed-profit line.</t>
+        </is>
+      </c>
+      <c r="D56" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="13" t="inlineStr">
+        <is>
+          <t>missedProfitLine</t>
+        </is>
+      </c>
+      <c r="B57" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="C57" s="13" t="inlineStr">
+        <is>
+          <t>D55: the weekly review shows 'your plan £X · best plan available with your planes £Y · missed £Z', from the engine's plan sweep. No cash is taken.</t>
+        </is>
+      </c>
+      <c r="D57" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="13" t="inlineStr">
+        <is>
+          <t>neglectFromDay</t>
+        </is>
+      </c>
+      <c r="B58" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="C58" s="13" t="inlineStr">
+        <is>
+          <t>D55 use-it-or-lose-it: from week 3, a route with no service for a week, or flown under neglectLoadFactor all week, loses neglectLossShare of its passengers to Red Kite the next week; it recovers neglectRecoverShare a week once flown properly. The review names the route.</t>
+        </is>
+      </c>
+      <c r="D58" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="13" t="inlineStr">
+        <is>
+          <t>neglectLoadFactor</t>
+        </is>
+      </c>
+      <c r="B59" s="13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C59" s="13" t="inlineStr"/>
+      <c r="D59" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="13" t="inlineStr">
+        <is>
+          <t>neglectLossShare</t>
+        </is>
+      </c>
+      <c r="B60" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C60" s="13" t="inlineStr">
+        <is>
+          <t>A tenth: the sum stays in tenths.</t>
+        </is>
+      </c>
+      <c r="D60" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="13" t="inlineStr">
+        <is>
+          <t>neglectRecoverShare</t>
+        </is>
+      </c>
+      <c r="B61" s="13" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C61" s="13" t="inlineStr"/>
+      <c r="D61" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="13" t="inlineStr">
+        <is>
+          <t>launchDaySums</t>
+        </is>
+      </c>
+      <c r="B62" s="13" t="inlineStr">
+        <is>
+          <t>tickets ×3 fares; profit; snacks ×2 prices; fuel after a guided example</t>
+        </is>
+      </c>
+      <c r="C62" s="13" t="inlineStr">
+        <is>
+          <t>D54: all on Launch Day, in one sitting, on the workings page, in this order.</t>
+        </is>
+      </c>
+      <c r="D62" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="13" t="inlineStr">
+        <is>
+          <t>practiceQuestionsPerDay</t>
+        </is>
+      </c>
+      <c r="B63" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C63" s="13" t="inlineStr">
+        <is>
+          <t>Teacher panel: 0 | 1 | 3. Practice questions use the pupil's own numbers and appear after the plan sums, marked optional (Design Note 8 Oct).</t>
+        </is>
+      </c>
+      <c r="D63" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="23" t="inlineStr">
         <is>
           <t>blockedFlightCodes</t>
         </is>
       </c>
-      <c r="B54" s="23" t="inlineStr">
+      <c r="B64" s="23" t="inlineStr">
         <is>
           <t>BA, EZ, FR, VS, LH, AF, KL, U2</t>
         </is>
       </c>
-      <c r="C54" s="23" t="inlineStr">
+      <c r="C64" s="23" t="inlineStr">
         <is>
           <t>CR5. Real airline codes the pupil cannot pick; refused calmly ("That code belongs to a real airline, try another").</t>
         </is>
       </c>
-      <c r="D54" s="23" t="inlineStr">
+      <c r="D64" s="23" t="inlineStr">
         <is>
           <t>live</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="23" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="23" t="inlineStr">
         <is>
           <t>soundDefault</t>
         </is>
       </c>
-      <c r="B55" s="23" t="inlineStr">
+      <c r="B65" s="23" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="C55" s="23" t="inlineStr">
+      <c r="C65" s="23" t="inlineStr">
         <is>
           <t>CR5. Sound (take-off, airport chimes, announcements) is off until the teacher turns it on; a mute control sits in the top bar.</t>
         </is>
       </c>
-      <c r="D55" s="23" t="inlineStr">
+      <c r="D65" s="23" t="inlineStr">
         <is>
           <t>live</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="23" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="23" t="inlineStr">
         <is>
           <t>revealSeconds</t>
         </is>
       </c>
-      <c r="B56" s="23" t="n">
+      <c r="B66" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="C56" s="23" t="inlineStr">
+      <c r="C66" s="23" t="inlineStr">
         <is>
           <t>CR5. The hangar reveal on launch day: doors close, open, the plane rolls in. Later planes get about half.</t>
         </is>
       </c>
-      <c r="D56" s="23" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="23" t="inlineStr">
-        <is>
-          <t>practiceQuestionsPerDay</t>
-        </is>
-      </c>
-      <c r="B57" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C57" s="23" t="inlineStr">
-        <is>
-          <t>Design note 8 Oct. Optional practice questions after the day's sums on the workings page, with the pupil's own numbers: 0, 1 or 3 (the teacher panel can change it).</t>
-        </is>
-      </c>
-      <c r="D57" s="23" t="inlineStr">
+      <c r="D66" s="23" t="inlineStr">
         <is>
           <t>live</t>
         </is>
@@ -26844,7 +27287,7 @@
         <v>0.2</v>
       </c>
       <c r="P4" s="12" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="Q4" s="12" t="inlineStr">
         <is>
@@ -26918,7 +27361,7 @@
         <v>0.15</v>
       </c>
       <c r="P5" s="12" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="Q5" s="12" t="inlineStr">
         <is>
@@ -26992,7 +27435,7 @@
         <v>0.15</v>
       </c>
       <c r="P6" s="12" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="Q6" s="12" t="inlineStr">
         <is>
@@ -27066,7 +27509,7 @@
         <v>0.25</v>
       </c>
       <c r="P7" s="12" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="Q7" s="12" t="inlineStr">
         <is>
@@ -27140,7 +27583,7 @@
         <v>0.2</v>
       </c>
       <c r="P8" s="12" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="Q8" s="12" t="inlineStr">
         <is>
@@ -27214,7 +27657,7 @@
         <v>0.2</v>
       </c>
       <c r="P9" s="12" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="Q9" s="12" t="inlineStr">
         <is>
@@ -27436,7 +27879,7 @@
         <v>0.2</v>
       </c>
       <c r="P12" s="13" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="Q12" s="13" t="inlineStr">
         <is>
@@ -27510,7 +27953,7 @@
         <v>0.2</v>
       </c>
       <c r="P13" s="13" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="Q13" s="13" t="inlineStr">
         <is>
@@ -27584,7 +28027,7 @@
         <v>0.2</v>
       </c>
       <c r="P14" s="13" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="Q14" s="13" t="inlineStr">
         <is>
@@ -27658,7 +28101,7 @@
         <v>0.25</v>
       </c>
       <c r="P15" s="13" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="Q15" s="13" t="inlineStr">
         <is>
@@ -27732,7 +28175,7 @@
         <v>0.25</v>
       </c>
       <c r="P16" s="13" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="Q16" s="13" t="inlineStr">
         <is>
@@ -27806,7 +28249,7 @@
         <v>0.25</v>
       </c>
       <c r="P17" s="13" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="Q17" s="13" t="inlineStr">
         <is>
@@ -27880,7 +28323,7 @@
         <v>0.2</v>
       </c>
       <c r="P18" s="13" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="Q18" s="13" t="inlineStr">
         <is>
@@ -27954,7 +28397,7 @@
         <v>0.2</v>
       </c>
       <c r="P19" s="13" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="Q19" s="13" t="inlineStr">
         <is>
@@ -28028,7 +28471,7 @@
         <v>0.15</v>
       </c>
       <c r="P20" s="13" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="Q20" s="13" t="inlineStr">
         <is>
@@ -28102,7 +28545,7 @@
         <v>0.2</v>
       </c>
       <c r="P21" s="13" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="Q21" s="13" t="inlineStr">
         <is>
@@ -28248,7 +28691,7 @@
         </is>
       </c>
       <c r="J2" s="15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K2" s="15" t="inlineStr">
         <is>
@@ -28304,7 +28747,7 @@
         </is>
       </c>
       <c r="J3" s="15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K3" s="15" t="inlineStr">
         <is>
@@ -28360,7 +28803,7 @@
         </is>
       </c>
       <c r="J4" s="15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K4" s="15" t="inlineStr">
         <is>
@@ -28416,7 +28859,7 @@
         </is>
       </c>
       <c r="J5" s="15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K5" s="15" t="inlineStr">
         <is>
@@ -28472,7 +28915,7 @@
         </is>
       </c>
       <c r="J6" s="15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K6" s="15" t="inlineStr">
         <is>
@@ -28528,7 +28971,7 @@
         </is>
       </c>
       <c r="J7" s="15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K7" s="15" t="inlineStr">
         <is>
@@ -28584,7 +29027,7 @@
         </is>
       </c>
       <c r="J8" s="15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K8" s="15" t="inlineStr">
         <is>
@@ -28640,7 +29083,7 @@
         </is>
       </c>
       <c r="J9" s="15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K9" s="15" t="inlineStr">
         <is>
@@ -28696,7 +29139,7 @@
         </is>
       </c>
       <c r="J10" s="15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K10" s="15" t="inlineStr">
         <is>
@@ -28752,7 +29195,7 @@
         </is>
       </c>
       <c r="J11" s="15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K11" s="15" t="inlineStr">
         <is>
@@ -28808,7 +29251,7 @@
         </is>
       </c>
       <c r="J12" s="15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K12" s="15" t="inlineStr">
         <is>
@@ -28864,7 +29307,7 @@
         </is>
       </c>
       <c r="J13" s="15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K13" s="15" t="inlineStr">
         <is>
@@ -29544,10 +29987,10 @@
         <v>150</v>
       </c>
       <c r="I2" s="12" t="n">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="J2" s="12" t="n">
-        <v>5000</v>
+        <v>12000</v>
       </c>
       <c r="K2" s="12" t="n">
         <v>2500</v>
@@ -29607,10 +30050,10 @@
         <v>200</v>
       </c>
       <c r="I3" s="12" t="n">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="J3" s="12" t="n">
-        <v>9000</v>
+        <v>22000</v>
       </c>
       <c r="K3" s="12" t="inlineStr"/>
       <c r="L3" s="12" t="n">
@@ -29668,10 +30111,10 @@
         <v>350</v>
       </c>
       <c r="I4" s="12" t="n">
-        <v>1200</v>
+        <v>1800</v>
       </c>
       <c r="J4" s="12" t="n">
-        <v>15000</v>
+        <v>36000</v>
       </c>
       <c r="K4" s="12" t="inlineStr"/>
       <c r="L4" s="12" t="n">
@@ -29729,14 +30172,14 @@
         <v>900</v>
       </c>
       <c r="I5" s="12" t="n">
-        <v>2500</v>
+        <v>3500</v>
       </c>
       <c r="J5" s="12" t="n">
-        <v>30000</v>
+        <v>70000</v>
       </c>
       <c r="K5" s="12" t="inlineStr"/>
       <c r="L5" s="12" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="M5" s="12" t="inlineStr">
         <is>
@@ -29797,7 +30240,7 @@
       </c>
       <c r="K6" s="12" t="inlineStr"/>
       <c r="L6" s="12" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="M6" s="12" t="inlineStr">
         <is>
@@ -29858,7 +30301,7 @@
       </c>
       <c r="K7" s="12" t="inlineStr"/>
       <c r="L7" s="12" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="M7" s="12" t="inlineStr">
         <is>
@@ -29919,7 +30362,7 @@
       </c>
       <c r="K8" s="12" t="inlineStr"/>
       <c r="L8" s="12" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="M8" s="12" t="inlineStr">
         <is>
@@ -30259,14 +30702,14 @@
         <v>700</v>
       </c>
       <c r="I15" s="13" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="J15" s="13" t="n">
-        <v>20000</v>
+        <v>50000</v>
       </c>
       <c r="K15" s="13" t="n"/>
       <c r="L15" s="13" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="M15" s="13" t="inlineStr">
         <is>
@@ -30485,7 +30928,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -30571,24 +31014,22 @@
         </is>
       </c>
       <c r="B2" s="13" t="n">
-        <v>5000</v>
+        <v>12000</v>
       </c>
       <c r="C2" s="13" t="n">
         <v>250</v>
       </c>
       <c r="D2" s="13" t="n">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="E2" s="13" t="n">
         <v>300</v>
       </c>
       <c r="F2" s="13" t="n">
-        <v>12</v>
-      </c>
-      <c r="G2" s="13" t="inlineStr">
-        <is>
-          <t>launch deal</t>
-        </is>
+        <v>30</v>
+      </c>
+      <c r="G2" s="13" t="n">
+        <v>13000</v>
       </c>
       <c r="H2" s="13" t="inlineStr">
         <is>
@@ -30597,7 +31038,7 @@
       </c>
       <c r="I2" s="13" t="inlineStr">
         <is>
-          <t>day 1</t>
+          <t>day 8</t>
         </is>
       </c>
       <c r="J2" s="13" t="inlineStr">
@@ -30607,7 +31048,7 @@
       </c>
       <c r="K2" s="13" t="inlineStr">
         <is>
-          <t>Second Twin Otter: rent £250 a day or buy £5,000 → 20 days. Launch-deal finance kept: £2,000 down, £300 a day for 12 days (days, not weeks).</t>
+          <t>Second Twin Otter: rent £250 a day; 12,000 ÷ 250 = 48 days. Launch-deal finance £4,000 down, £300 a day for 30 days (£13,000).</t>
         </is>
       </c>
       <c r="L2" s="13" t="inlineStr">
@@ -30623,24 +31064,22 @@
         </is>
       </c>
       <c r="B3" s="13" t="n">
-        <v>9000</v>
+        <v>22000</v>
       </c>
       <c r="C3" s="13" t="n">
         <v>400</v>
       </c>
       <c r="D3" s="13" t="n">
-        <v>3000</v>
+        <v>7000</v>
       </c>
       <c r="E3" s="13" t="n">
         <v>500</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>14</v>
-      </c>
-      <c r="G3" s="13" t="inlineStr">
-        <is>
-          <t>launch deal</t>
-        </is>
+        <v>32</v>
+      </c>
+      <c r="G3" s="13" t="n">
+        <v>23000</v>
       </c>
       <c r="H3" s="13" t="inlineStr">
         <is>
@@ -30659,7 +31098,7 @@
       </c>
       <c r="K3" s="13" t="inlineStr">
         <is>
-          <t>The week-2 lesson: 9,000 ÷ 400 = 22½ days. Launch-deal finance £3,000 down, £500 a day for 14 days.</t>
+          <t>The week-2 sum: 22,000 ÷ 400 = 55 days. Launch-deal finance £7,000 down, £500 a day for 32 days (£23,000). Buy greyed out until cash ≥ price + reserve.</t>
         </is>
       </c>
       <c r="L3" s="13" t="inlineStr">
@@ -30675,24 +31114,22 @@
         </is>
       </c>
       <c r="B4" s="13" t="n">
-        <v>15000</v>
+        <v>36000</v>
       </c>
       <c r="C4" s="13" t="n">
         <v>650</v>
       </c>
       <c r="D4" s="13" t="n">
-        <v>5000</v>
+        <v>11000</v>
       </c>
       <c r="E4" s="13" t="n">
         <v>800</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>14</v>
-      </c>
-      <c r="G4" s="13" t="inlineStr">
-        <is>
-          <t>launch deal</t>
-        </is>
+        <v>35</v>
+      </c>
+      <c r="G4" s="13" t="n">
+        <v>39000</v>
       </c>
       <c r="H4" s="13" t="inlineStr">
         <is>
@@ -30711,7 +31148,7 @@
       </c>
       <c r="K4" s="13" t="inlineStr">
         <is>
-          <t>Launch-deal finance £5,000 down, £800 a day for 14 days.</t>
+          <t>36,000 ÷ 650 ≈ 55 days. Finance £11,000 down, £800 a day for 35 days (£39,000).</t>
         </is>
       </c>
       <c r="L4" s="13" t="inlineStr">
@@ -30727,33 +31164,31 @@
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>20000</v>
+        <v>50000</v>
       </c>
       <c r="C5" s="13" t="n">
         <v>900</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>7000</v>
+        <v>15000</v>
       </c>
       <c r="E5" s="13" t="n">
         <v>1000</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>14</v>
-      </c>
-      <c r="G5" s="13" t="inlineStr">
-        <is>
-          <t>launch deal</t>
-        </is>
+        <v>38</v>
+      </c>
+      <c r="G5" s="13" t="n">
+        <v>53000</v>
       </c>
       <c r="H5" s="13" t="inlineStr">
         <is>
-          <t>day 15</t>
+          <t>day 22</t>
         </is>
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
-          <t>day 15</t>
+          <t>day 22</t>
         </is>
       </c>
       <c r="J5" s="13" t="inlineStr">
@@ -30763,7 +31198,7 @@
       </c>
       <c r="K5" s="13" t="inlineStr">
         <is>
-          <t>Tutorial jet. 20,000 ÷ 900 ≈ 22 days.</t>
+          <t>50,000 ÷ 900 ≈ 56 days. Finance £15,000 down, £1,000 a day for 38 days (£53,000).</t>
         </is>
       </c>
       <c r="L5" s="13" t="inlineStr">
@@ -30779,33 +31214,31 @@
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>30000</v>
+        <v>70000</v>
       </c>
       <c r="C6" s="13" t="n">
         <v>1200</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>10000</v>
+        <v>21000</v>
       </c>
       <c r="E6" s="13" t="n">
         <v>1500</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>16</v>
-      </c>
-      <c r="G6" s="13" t="inlineStr">
-        <is>
-          <t>launch deal</t>
-        </is>
+        <v>36</v>
+      </c>
+      <c r="G6" s="13" t="n">
+        <v>75000</v>
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>day 15</t>
+          <t>day 22</t>
         </is>
       </c>
       <c r="I6" s="13" t="inlineStr">
         <is>
-          <t>day 15</t>
+          <t>day 22</t>
         </is>
       </c>
       <c r="J6" s="13" t="inlineStr">
@@ -30815,7 +31248,7 @@
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
-          <t>Tutorial jet. 30,000 ÷ 1,200 = 25 days.</t>
+          <t>70,000 ÷ 1,200 ≈ 58 days. Finance £21,000 down, £1,500 a day for 36 days (£75,000).</t>
         </is>
       </c>
       <c r="L6" s="13" t="inlineStr">
@@ -31304,6 +31737,13 @@
       <c r="A18" s="17" t="inlineStr">
         <is>
           <t>Note on the launch-deal rows: tutorial finance is in daily payments (as in the game today), because the opening is played by the day; from the A220 the payments are weekly, because chapter 4 is played by the month. 'When does renting cost more than buying?' = price ÷ leaseDaily: about 20–25 days for tutorial planes (launch deals), 1,000 days for every jet from the A220 up (F4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>Tutorial prices are 2½× v4.3 (D55): the second plane is rented or financed in week 2 and bought outright around week 4–5. The first Twin Otter is still the £2,500 launch deal. Rent-or-buy ≈ 55 days for every tutorial plane; 1,000 days for jets from the A220 up.</t>
         </is>
       </c>
     </row>

--- a/data/Airline-World-Workbook.xlsx
+++ b/data/Airline-World-Workbook.xlsx
@@ -10,21 +10,23 @@
     <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Chapters" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="HandSumRules" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Settings" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Archetypes" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Routes" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="RouteCatalogue" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Aircraft" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Finance" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Airports" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Calendar" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Market" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Events" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Challenges" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Mechanics" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Catering" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Livery" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Hunts" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="WorkingMethods" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Settings" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="RouteNews" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Archetypes" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Routes" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="RouteCatalogue" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Aircraft" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Finance" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Airports" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Calendar" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Market" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Events" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Challenges" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Mechanics" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Catering" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Hunts" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Livery" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -134,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -202,9 +204,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -649,7 +648,7 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>SHEETS: Settings · Chapters · HandSumRules · Calendar (days 1–21) · Market (weeks 1–416) · Events · Routes · RouteCatalogue · Archetypes · Aircraft · Finance · Catering · Airports · Challenges · Hunts · Mechanics. · Livery</t>
+          <t>SHEETS: Settings · Chapters · HandSumRules · Calendar (days 1–21) · Market (weeks 1–416) · Events · Routes · RouteCatalogue · Archetypes · Aircraft · Finance · Catering · Airports · Challenges · Hunts · Mechanics.</t>
         </is>
       </c>
     </row>
@@ -703,16 +702,16 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>v4.3 + CR5 rows re-added by Claude Code (8 Oct): Fable's v4.3 did not carry the CR5 draft, so the Livery sheet, the Aircraft columns artworkId/photoFile/photoCredit/photoLicence/photoSource, and Settings blockedFlightCodes, soundDefault, revealSeconds are added again, plus practiceQuestionsPerDay (design note). The game reads crewMechanicFromDate (D51); the earlier draft key crewFromDate is dropped.</t>
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>v4.5 (12 Oct): D56 RouteNews sheet (13 items, weeks 5–17); D57 fuel desk data — Market forecastLow/forecastHigh/fuelHeadline for weeks 2–17, Settings fuelLotSize 1000, tankCapacity 20000, fuelUseOrder oldest first, emergencyFuelPremium £0.10, fuelHandSum per trip on the load sheet; D58 planningSpreadsheetFromDay 8. Design note: 'The desks' (12 Oct).</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>v4.3 draft (7 Oct, Claude Code, for Fable to adopt): Change Request 5. New sheet Livery (palette, stripes, tail symbols, logo shapes, plane-name suggestions); Aircraft columns artworkId and photoFile/Credit/Licence/Source; Settings blockedFlightCodes, soundDefault, revealSeconds. Everything the pupil chooses (airline name, flight code, logo, each plane's registration, name and livery) lives in the save state, not here.</t>
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>v4.6 (12 Oct): D60. Week 1 fuel bought automatically (no desk); Fuel procurement desk from day 8 with an 8,000 L tank growing to 20,000 L on day 29; Market weeks 2–17 fuel in odd pennies (£1.47, £1.68 …) with forecast ranges recomputed, forecastConfidence and a second conflicting signal in weeks 9, 12, 16; new WorkingMethods sheet (methods offered per relationship, by level). Design Note: The desks, v2.</t>
         </is>
       </c>
     </row>
@@ -722,6 +721,1846 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:S20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>tier</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>seats</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>speedKmh</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>rangeKm</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>fuelPer100Km</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>hourlyCost</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>dayCost</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>listPrice</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>launchDealPrice</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>shopFromDay</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="N1" s="24" t="inlineStr">
+        <is>
+          <t>artworkId</t>
+        </is>
+      </c>
+      <c r="O1" s="24" t="inlineStr">
+        <is>
+          <t>photoFile</t>
+        </is>
+      </c>
+      <c r="P1" s="24" t="inlineStr">
+        <is>
+          <t>photoCredit</t>
+        </is>
+      </c>
+      <c r="Q1" s="24" t="inlineStr">
+        <is>
+          <t>photoLicence</t>
+        </is>
+      </c>
+      <c r="R1" s="24" t="inlineStr">
+        <is>
+          <t>photoSource</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>dhc6</t>
+        </is>
+      </c>
+      <c r="B2" s="12" t="inlineStr">
+        <is>
+          <t>DHC-6 Twin Otter</t>
+        </is>
+      </c>
+      <c r="C2" s="12" t="inlineStr">
+        <is>
+          <t>starter</t>
+        </is>
+      </c>
+      <c r="D2" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="E2" s="12" t="n">
+        <v>300</v>
+      </c>
+      <c r="F2" s="12" t="n">
+        <v>1400</v>
+      </c>
+      <c r="G2" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="H2" s="12" t="n">
+        <v>150</v>
+      </c>
+      <c r="I2" s="12" t="n">
+        <v>900</v>
+      </c>
+      <c r="J2" s="12" t="n">
+        <v>12000</v>
+      </c>
+      <c r="K2" s="12" t="n">
+        <v>2500</v>
+      </c>
+      <c r="L2" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" s="12" t="inlineStr">
+        <is>
+          <t>Small, flexible, cheap. Fits any route. Slow on long legs.</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>dhc6</t>
+        </is>
+      </c>
+      <c r="S2" s="12" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>saab340</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>Saab 340</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>regional</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="E3" s="12" t="n">
+        <v>450</v>
+      </c>
+      <c r="F3" s="12" t="n">
+        <v>1700</v>
+      </c>
+      <c r="G3" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="H3" s="12" t="n">
+        <v>200</v>
+      </c>
+      <c r="I3" s="12" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J3" s="12" t="n">
+        <v>22000</v>
+      </c>
+      <c r="K3" s="12" t="inlineStr"/>
+      <c r="L3" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="M3" s="12" t="inlineStr">
+        <is>
+          <t>More seats and faster: Dublin and Amsterdam fit it. Half-empty on Paris.</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>sf34</t>
+        </is>
+      </c>
+      <c r="S3" s="12" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>atr72</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>ATR 72</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>regional</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="n">
+        <v>70</v>
+      </c>
+      <c r="E4" s="12" t="n">
+        <v>450</v>
+      </c>
+      <c r="F4" s="12" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G4" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="H4" s="12" t="n">
+        <v>350</v>
+      </c>
+      <c r="I4" s="12" t="n">
+        <v>1800</v>
+      </c>
+      <c r="J4" s="12" t="n">
+        <v>36000</v>
+      </c>
+      <c r="K4" s="12" t="inlineStr"/>
+      <c r="L4" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="M4" s="12" t="inlineStr">
+        <is>
+          <t>Biggest short-haul. Cheapest per seat. Only pays on busy routes; just reaches Madrid (1,350 of 1,500 km).</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>at72</t>
+        </is>
+      </c>
+      <c r="S4" s="12" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>e190</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>Embraer E190</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>regional jet</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="E5" s="12" t="n">
+        <v>900</v>
+      </c>
+      <c r="F5" s="12" t="n">
+        <v>4500</v>
+      </c>
+      <c r="G5" s="12" t="n">
+        <v>70</v>
+      </c>
+      <c r="H5" s="12" t="n">
+        <v>900</v>
+      </c>
+      <c r="I5" s="12" t="n">
+        <v>3500</v>
+      </c>
+      <c r="J5" s="12" t="n">
+        <v>70000</v>
+      </c>
+      <c r="K5" s="12" t="inlineStr"/>
+      <c r="L5" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="M5" s="12" t="inlineStr">
+        <is>
+          <t>First jet: speed and range. Opens every medium-haul route the ATR cannot reach. Tutorial price.</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>e190</t>
+        </is>
+      </c>
+      <c r="S5" s="12" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>a220</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Airbus A220</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>small mainline</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="n">
+        <v>130</v>
+      </c>
+      <c r="E6" s="12" t="n">
+        <v>900</v>
+      </c>
+      <c r="F6" s="12" t="n">
+        <v>6300</v>
+      </c>
+      <c r="G6" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="H6" s="12" t="n">
+        <v>1100</v>
+      </c>
+      <c r="I6" s="12" t="n">
+        <v>3000</v>
+      </c>
+      <c r="J6" s="12" t="n">
+        <v>300000</v>
+      </c>
+      <c r="K6" s="12" t="inlineStr"/>
+      <c r="L6" s="12" t="n">
+        <v>57</v>
+      </c>
+      <c r="M6" s="12" t="inlineStr">
+        <is>
+          <t>The first plane priced like a real jet. Leased or saved for.</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>narrowbody</t>
+        </is>
+      </c>
+      <c r="S6" s="12" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>a320</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>Airbus A320</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>workhorse</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="n">
+        <v>150</v>
+      </c>
+      <c r="E7" s="12" t="n">
+        <v>900</v>
+      </c>
+      <c r="F7" s="12" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G7" s="12" t="n">
+        <v>90</v>
+      </c>
+      <c r="H7" s="12" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I7" s="12" t="n">
+        <v>3500</v>
+      </c>
+      <c r="J7" s="12" t="n">
+        <v>400000</v>
+      </c>
+      <c r="K7" s="12" t="inlineStr"/>
+      <c r="L7" s="12" t="n">
+        <v>57</v>
+      </c>
+      <c r="M7" s="12" t="inlineStr">
+        <is>
+          <t>The one he named ('an Airbus'). Rome, Athens, Istanbul.</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>narrowbody</t>
+        </is>
+      </c>
+      <c r="S7" s="12" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>b737</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Boeing 737</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>workhorse</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="n">
+        <v>150</v>
+      </c>
+      <c r="E8" s="12" t="n">
+        <v>900</v>
+      </c>
+      <c r="F8" s="12" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G8" s="12" t="n">
+        <v>90</v>
+      </c>
+      <c r="H8" s="12" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I8" s="12" t="n">
+        <v>3500</v>
+      </c>
+      <c r="J8" s="12" t="n">
+        <v>400000</v>
+      </c>
+      <c r="K8" s="12" t="inlineStr"/>
+      <c r="L8" s="12" t="n">
+        <v>57</v>
+      </c>
+      <c r="M8" s="12" t="inlineStr">
+        <is>
+          <t>Named by the pupil. Same numbers as the A320: the choice is taste, as in real life.</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>narrowbody</t>
+        </is>
+      </c>
+      <c r="S8" s="12" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>b787</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>Boeing 787 Dreamliner</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>long-haul</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="n">
+        <v>250</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>900</v>
+      </c>
+      <c r="F9" s="15" t="n">
+        <v>14000</v>
+      </c>
+      <c r="G9" s="15" t="n">
+        <v>200</v>
+      </c>
+      <c r="H9" s="15" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I9" s="15" t="n">
+        <v>8000</v>
+      </c>
+      <c r="J9" s="15" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="K9" s="15" t="inlineStr"/>
+      <c r="L9" s="15" t="n">
+        <v>127</v>
+      </c>
+      <c r="M9" s="15" t="inlineStr">
+        <is>
+          <t>Named by the pupil. Opens long haul, January 2031, by lease; bought outright from chapter 3.</t>
+        </is>
+      </c>
+      <c r="S9" s="15" t="inlineStr">
+        <is>
+          <t>later</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>a350</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>Airbus A350</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>long-haul</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="n">
+        <v>300</v>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>900</v>
+      </c>
+      <c r="F10" s="15" t="n">
+        <v>18000</v>
+      </c>
+      <c r="G10" s="15" t="n">
+        <v>220</v>
+      </c>
+      <c r="H10" s="15" t="n">
+        <v>3400</v>
+      </c>
+      <c r="I10" s="15" t="n">
+        <v>9000</v>
+      </c>
+      <c r="J10" s="15" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="K10" s="15" t="inlineStr"/>
+      <c r="L10" s="15" t="n">
+        <v>366</v>
+      </c>
+      <c r="M10" s="15" t="inlineStr">
+        <is>
+          <t>Range for Sydney. Chapter 3.</t>
+        </is>
+      </c>
+      <c r="S10" s="15" t="inlineStr">
+        <is>
+          <t>later</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>b747</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>Boeing 747</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>icon</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="n">
+        <v>400</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>900</v>
+      </c>
+      <c r="F11" s="15" t="n">
+        <v>13000</v>
+      </c>
+      <c r="G11" s="15" t="n">
+        <v>300</v>
+      </c>
+      <c r="H11" s="15" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I11" s="15" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J11" s="15" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="K11" s="15" t="inlineStr"/>
+      <c r="L11" s="15" t="n">
+        <v>736</v>
+      </c>
+      <c r="M11" s="15" t="inlineStr">
+        <is>
+          <t>Named by the pupil. The Jumbo: roomy, thirsty. Chapter 4.</t>
+        </is>
+      </c>
+      <c r="S11" s="15" t="inlineStr">
+        <is>
+          <t>later</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>a380</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>Airbus A380</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>icon</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="n">
+        <v>500</v>
+      </c>
+      <c r="E12" s="15" t="n">
+        <v>900</v>
+      </c>
+      <c r="F12" s="15" t="n">
+        <v>15000</v>
+      </c>
+      <c r="G12" s="15" t="n">
+        <v>360</v>
+      </c>
+      <c r="H12" s="15" t="n">
+        <v>5500</v>
+      </c>
+      <c r="I12" s="15" t="n">
+        <v>15000</v>
+      </c>
+      <c r="J12" s="15" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="K12" s="15" t="inlineStr"/>
+      <c r="L12" s="15" t="n">
+        <v>736</v>
+      </c>
+      <c r="M12" s="15" t="inlineStr">
+        <is>
+          <t>'The ultimate plane.' Chapter 4's new idea: financed, not bought. Only fills on the busiest route with a strong reputation.</t>
+        </is>
+      </c>
+      <c r="S12" s="15" t="inlineStr">
+        <is>
+          <t>later</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>concorde</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>Concorde</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="inlineStr">
+        <is>
+          <t>wildcard</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="n">
+        <v>100</v>
+      </c>
+      <c r="E13" s="19" t="n">
+        <v>2100</v>
+      </c>
+      <c r="F13" s="19" t="n">
+        <v>7000</v>
+      </c>
+      <c r="G13" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="H13" s="19" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I13" s="19" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J13" s="19" t="n">
+        <v>60000000</v>
+      </c>
+      <c r="K13" s="19" t="inlineStr"/>
+      <c r="L13" s="19" t="n">
+        <v>834</v>
+      </c>
+      <c r="M13" s="19" t="inlineStr">
+        <is>
+          <t>Removed 6 Oct (D41).</t>
+        </is>
+      </c>
+      <c r="S13" s="19" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>e175</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>Embraer E175</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>regional jet</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="n">
+        <v>80</v>
+      </c>
+      <c r="E15" s="13" t="n">
+        <v>900</v>
+      </c>
+      <c r="F15" s="13" t="n">
+        <v>3700</v>
+      </c>
+      <c r="G15" s="13" t="n">
+        <v>55</v>
+      </c>
+      <c r="H15" s="13" t="n">
+        <v>700</v>
+      </c>
+      <c r="I15" s="13" t="n">
+        <v>3000</v>
+      </c>
+      <c r="J15" s="13" t="n">
+        <v>50000</v>
+      </c>
+      <c r="K15" s="13" t="n"/>
+      <c r="L15" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="M15" s="13" t="inlineStr">
+        <is>
+          <t>The smaller, cheaper first jet. Beats the E190 on smaller pools (Marrakech). Tutorial price.</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>e175</t>
+        </is>
+      </c>
+      <c r="S15" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>b757</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>Boeing 757</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>narrowbody long-range</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="n">
+        <v>200</v>
+      </c>
+      <c r="E16" s="14" t="n">
+        <v>900</v>
+      </c>
+      <c r="F16" s="14" t="n">
+        <v>7200</v>
+      </c>
+      <c r="G16" s="14" t="n">
+        <v>110</v>
+      </c>
+      <c r="H16" s="14" t="n">
+        <v>1600</v>
+      </c>
+      <c r="I16" s="14" t="n">
+        <v>4200</v>
+      </c>
+      <c r="J16" s="14" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="K16" s="14" t="n"/>
+      <c r="L16" s="14" t="n">
+        <v>127</v>
+      </c>
+      <c r="M16" s="14" t="inlineStr">
+        <is>
+          <t>Long and narrow with big engines: reaches New York with fewer seats than a widebody. The cheap way into long haul. Chapter 2, by lease.</t>
+        </is>
+      </c>
+      <c r="S16" s="14" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t>a340</t>
+        </is>
+      </c>
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t>Airbus A340</t>
+        </is>
+      </c>
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>four-engined long-haul</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="n">
+        <v>280</v>
+      </c>
+      <c r="E17" s="18" t="n">
+        <v>900</v>
+      </c>
+      <c r="F17" s="18" t="n">
+        <v>13500</v>
+      </c>
+      <c r="G17" s="18" t="n">
+        <v>260</v>
+      </c>
+      <c r="H17" s="18" t="n">
+        <v>3600</v>
+      </c>
+      <c r="I17" s="18" t="n">
+        <v>8500</v>
+      </c>
+      <c r="J17" s="18" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="K17" s="18" t="n"/>
+      <c r="L17" s="18" t="n">
+        <v>366</v>
+      </c>
+      <c r="M17" s="18" t="inlineStr">
+        <is>
+          <t>Four engines make it thirsty for its size; a bargain when fuel is cheap, a trap when it is dear. Chapter 3.</t>
+        </is>
+      </c>
+      <c r="S17" s="18" t="inlineStr">
+        <is>
+          <t>later</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="18" t="inlineStr">
+        <is>
+          <t>b777</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>Boeing 777</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="inlineStr">
+        <is>
+          <t>long-haul</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="n">
+        <v>350</v>
+      </c>
+      <c r="E18" s="18" t="n">
+        <v>900</v>
+      </c>
+      <c r="F18" s="18" t="n">
+        <v>14000</v>
+      </c>
+      <c r="G18" s="18" t="n">
+        <v>250</v>
+      </c>
+      <c r="H18" s="18" t="n">
+        <v>4000</v>
+      </c>
+      <c r="I18" s="18" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J18" s="18" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="K18" s="18" t="n"/>
+      <c r="L18" s="18" t="n">
+        <v>366</v>
+      </c>
+      <c r="M18" s="18" t="inlineStr">
+        <is>
+          <t>The biggest twin: the long-haul workhorse. Chapter 3.</t>
+        </is>
+      </c>
+      <c r="S18" s="18" t="inlineStr">
+        <is>
+          <t>later</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>Prices from the A220 up are tuned to the cash curve (F5, replacing D16's three-tenths rule): on the Steady path each plane is a few lessons of saving away when it is meant to arrive. Tutorial planes (Twin Otter to E190, E175) keep launch-deal prices. Real prices are on the plane card for interest only.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="21" t="inlineStr">
+        <is>
+          <t>aircraftId</t>
+        </is>
+      </c>
+      <c r="B1" s="21" t="inlineStr">
+        <is>
+          <t>cashPrice</t>
+        </is>
+      </c>
+      <c r="C1" s="21" t="inlineStr">
+        <is>
+          <t>leaseDaily</t>
+        </is>
+      </c>
+      <c r="D1" s="21" t="inlineStr">
+        <is>
+          <t>financeDeposit</t>
+        </is>
+      </c>
+      <c r="E1" s="21" t="inlineStr">
+        <is>
+          <t>financeWeeklyPayment</t>
+        </is>
+      </c>
+      <c r="F1" s="21" t="inlineStr">
+        <is>
+          <t>financeWeeks</t>
+        </is>
+      </c>
+      <c r="G1" s="21" t="inlineStr">
+        <is>
+          <t>financeTotalPaid</t>
+        </is>
+      </c>
+      <c r="H1" s="21" t="inlineStr">
+        <is>
+          <t>leaseFrom</t>
+        </is>
+      </c>
+      <c r="I1" s="21" t="inlineStr">
+        <is>
+          <t>buyFrom</t>
+        </is>
+      </c>
+      <c r="J1" s="21" t="inlineStr">
+        <is>
+          <t>financeFrom</t>
+        </is>
+      </c>
+      <c r="K1" s="21" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="L1" s="21" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>dhc6</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="n">
+        <v>12000</v>
+      </c>
+      <c r="C2" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="D2" s="13" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E2" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="F2" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="G2" s="13" t="n">
+        <v>13000</v>
+      </c>
+      <c r="H2" s="13" t="inlineStr">
+        <is>
+          <t>day 8</t>
+        </is>
+      </c>
+      <c r="I2" s="13" t="inlineStr">
+        <is>
+          <t>day 8</t>
+        </is>
+      </c>
+      <c r="J2" s="13" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K2" s="13" t="inlineStr">
+        <is>
+          <t>Second Twin Otter: rent £250 a day; 12,000 ÷ 250 = 48 days. Launch-deal finance £4,000 down, £300 a day for 30 days (£13,000).</t>
+        </is>
+      </c>
+      <c r="L2" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>saab340</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="n">
+        <v>22000</v>
+      </c>
+      <c r="C3" s="13" t="n">
+        <v>400</v>
+      </c>
+      <c r="D3" s="13" t="n">
+        <v>7000</v>
+      </c>
+      <c r="E3" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="F3" s="13" t="n">
+        <v>32</v>
+      </c>
+      <c r="G3" s="13" t="n">
+        <v>23000</v>
+      </c>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>day 8</t>
+        </is>
+      </c>
+      <c r="I3" s="13" t="inlineStr">
+        <is>
+          <t>day 8</t>
+        </is>
+      </c>
+      <c r="J3" s="13" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K3" s="13" t="inlineStr">
+        <is>
+          <t>The week-2 sum: 22,000 ÷ 400 = 55 days. Launch-deal finance £7,000 down, £500 a day for 32 days (£23,000). Buy greyed out until cash ≥ price + reserve.</t>
+        </is>
+      </c>
+      <c r="L3" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>atr72</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="n">
+        <v>36000</v>
+      </c>
+      <c r="C4" s="13" t="n">
+        <v>650</v>
+      </c>
+      <c r="D4" s="13" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E4" s="13" t="n">
+        <v>800</v>
+      </c>
+      <c r="F4" s="13" t="n">
+        <v>35</v>
+      </c>
+      <c r="G4" s="13" t="n">
+        <v>39000</v>
+      </c>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t>day 8</t>
+        </is>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>day 8</t>
+        </is>
+      </c>
+      <c r="J4" s="13" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K4" s="13" t="inlineStr">
+        <is>
+          <t>36,000 ÷ 650 ≈ 55 days. Finance £11,000 down, £800 a day for 35 days (£39,000).</t>
+        </is>
+      </c>
+      <c r="L4" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>e175</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="n">
+        <v>50000</v>
+      </c>
+      <c r="C5" s="13" t="n">
+        <v>900</v>
+      </c>
+      <c r="D5" s="13" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E5" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F5" s="13" t="n">
+        <v>38</v>
+      </c>
+      <c r="G5" s="13" t="n">
+        <v>53000</v>
+      </c>
+      <c r="H5" s="13" t="inlineStr">
+        <is>
+          <t>day 22</t>
+        </is>
+      </c>
+      <c r="I5" s="13" t="inlineStr">
+        <is>
+          <t>day 22</t>
+        </is>
+      </c>
+      <c r="J5" s="13" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K5" s="13" t="inlineStr">
+        <is>
+          <t>50,000 ÷ 900 ≈ 56 days. Finance £15,000 down, £1,000 a day for 38 days (£53,000).</t>
+        </is>
+      </c>
+      <c r="L5" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>e190</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="n">
+        <v>70000</v>
+      </c>
+      <c r="C6" s="13" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D6" s="13" t="n">
+        <v>21000</v>
+      </c>
+      <c r="E6" s="13" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F6" s="13" t="n">
+        <v>36</v>
+      </c>
+      <c r="G6" s="13" t="n">
+        <v>75000</v>
+      </c>
+      <c r="H6" s="13" t="inlineStr">
+        <is>
+          <t>day 22</t>
+        </is>
+      </c>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>day 22</t>
+        </is>
+      </c>
+      <c r="J6" s="13" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K6" s="13" t="inlineStr">
+        <is>
+          <t>70,000 ÷ 1,200 ≈ 58 days. Finance £21,000 down, £1,500 a day for 36 days (£75,000).</t>
+        </is>
+      </c>
+      <c r="L6" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>a220</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="n">
+        <v>300000</v>
+      </c>
+      <c r="C7" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="D7" s="13" t="n">
+        <v>90000</v>
+      </c>
+      <c r="E7" s="13" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F7" s="13" t="n">
+        <v>52</v>
+      </c>
+      <c r="G7" s="13" t="n">
+        <v>298000</v>
+      </c>
+      <c r="H7" s="13" t="inlineStr">
+        <is>
+          <t>2031-01-06</t>
+        </is>
+      </c>
+      <c r="I7" s="13" t="inlineStr">
+        <is>
+          <t>2031-09-02</t>
+        </is>
+      </c>
+      <c r="J7" s="13" t="inlineStr">
+        <is>
+          <t>2032-09-07</t>
+        </is>
+      </c>
+      <c r="K7" s="13" t="inlineStr">
+        <is>
+          <t>Rent = price ÷ 1,000. Finance = 30% deposit, balance over 52 weeks, rounded to £1,000.</t>
+        </is>
+      </c>
+      <c r="L7" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>a320</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="n">
+        <v>400000</v>
+      </c>
+      <c r="C8" s="13" t="n">
+        <v>400</v>
+      </c>
+      <c r="D8" s="13" t="n">
+        <v>120000</v>
+      </c>
+      <c r="E8" s="13" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F8" s="13" t="n">
+        <v>52</v>
+      </c>
+      <c r="G8" s="13" t="n">
+        <v>380000</v>
+      </c>
+      <c r="H8" s="13" t="inlineStr">
+        <is>
+          <t>2031-01-06</t>
+        </is>
+      </c>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>2031-09-02</t>
+        </is>
+      </c>
+      <c r="J8" s="13" t="inlineStr">
+        <is>
+          <t>2032-09-07</t>
+        </is>
+      </c>
+      <c r="K8" s="13" t="inlineStr"/>
+      <c r="L8" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>b737</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="n">
+        <v>400000</v>
+      </c>
+      <c r="C9" s="13" t="n">
+        <v>400</v>
+      </c>
+      <c r="D9" s="13" t="n">
+        <v>120000</v>
+      </c>
+      <c r="E9" s="13" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F9" s="13" t="n">
+        <v>52</v>
+      </c>
+      <c r="G9" s="13" t="n">
+        <v>380000</v>
+      </c>
+      <c r="H9" s="13" t="inlineStr">
+        <is>
+          <t>2031-01-06</t>
+        </is>
+      </c>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>2031-09-02</t>
+        </is>
+      </c>
+      <c r="J9" s="13" t="inlineStr">
+        <is>
+          <t>2032-09-07</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="inlineStr"/>
+      <c r="L9" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>b757</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="C10" s="14" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D10" s="14" t="n">
+        <v>450000</v>
+      </c>
+      <c r="E10" s="14" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F10" s="14" t="n">
+        <v>52</v>
+      </c>
+      <c r="G10" s="14" t="n">
+        <v>1490000</v>
+      </c>
+      <c r="H10" s="14" t="inlineStr">
+        <is>
+          <t>2031-01-06</t>
+        </is>
+      </c>
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>2031-09-02</t>
+        </is>
+      </c>
+      <c r="J10" s="14" t="inlineStr">
+        <is>
+          <t>2032-09-07</t>
+        </is>
+      </c>
+      <c r="K10" s="14" t="inlineStr">
+        <is>
+          <t>The cheap way into long haul by lease in chapter 2.</t>
+        </is>
+      </c>
+      <c r="L10" s="14" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="18" t="inlineStr">
+        <is>
+          <t>b787</t>
+        </is>
+      </c>
+      <c r="B11" s="18" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="C11" s="18" t="n">
+        <v>6000</v>
+      </c>
+      <c r="D11" s="18" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="E11" s="18" t="n">
+        <v>81000</v>
+      </c>
+      <c r="F11" s="18" t="n">
+        <v>52</v>
+      </c>
+      <c r="G11" s="18" t="n">
+        <v>6012000</v>
+      </c>
+      <c r="H11" s="18" t="inlineStr">
+        <is>
+          <t>2031-01-06</t>
+        </is>
+      </c>
+      <c r="I11" s="18" t="inlineStr">
+        <is>
+          <t>2031-09-02</t>
+        </is>
+      </c>
+      <c r="J11" s="18" t="inlineStr">
+        <is>
+          <t>2032-09-07</t>
+        </is>
+      </c>
+      <c r="K11" s="18" t="inlineStr">
+        <is>
+          <t>Leased Jan 2031; first big plane bought outright Sep 2031 on the Steady path. 6,000,000 ÷ 6,000 = 1,000 days.</t>
+        </is>
+      </c>
+      <c r="L11" s="18" t="inlineStr">
+        <is>
+          <t>later</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>a340</t>
+        </is>
+      </c>
+      <c r="B12" s="18" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="C12" s="18" t="n">
+        <v>8000</v>
+      </c>
+      <c r="D12" s="18" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="E12" s="18" t="n">
+        <v>108000</v>
+      </c>
+      <c r="F12" s="18" t="n">
+        <v>52</v>
+      </c>
+      <c r="G12" s="18" t="n">
+        <v>8016000</v>
+      </c>
+      <c r="H12" s="18" t="inlineStr">
+        <is>
+          <t>2031-09-02</t>
+        </is>
+      </c>
+      <c r="I12" s="18" t="inlineStr">
+        <is>
+          <t>2031-09-02</t>
+        </is>
+      </c>
+      <c r="J12" s="18" t="inlineStr">
+        <is>
+          <t>2032-09-07</t>
+        </is>
+      </c>
+      <c r="K12" s="18" t="inlineStr"/>
+      <c r="L12" s="18" t="inlineStr">
+        <is>
+          <t>later</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>b777</t>
+        </is>
+      </c>
+      <c r="B13" s="18" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="C13" s="18" t="n">
+        <v>12000</v>
+      </c>
+      <c r="D13" s="18" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="E13" s="18" t="n">
+        <v>162000</v>
+      </c>
+      <c r="F13" s="18" t="n">
+        <v>52</v>
+      </c>
+      <c r="G13" s="18" t="n">
+        <v>12024000</v>
+      </c>
+      <c r="H13" s="18" t="inlineStr">
+        <is>
+          <t>2031-09-02</t>
+        </is>
+      </c>
+      <c r="I13" s="18" t="inlineStr">
+        <is>
+          <t>2031-09-02</t>
+        </is>
+      </c>
+      <c r="J13" s="18" t="inlineStr">
+        <is>
+          <t>2032-09-07</t>
+        </is>
+      </c>
+      <c r="K13" s="18" t="inlineStr"/>
+      <c r="L13" s="18" t="inlineStr">
+        <is>
+          <t>later</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>a350</t>
+        </is>
+      </c>
+      <c r="B14" s="18" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="C14" s="18" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D14" s="18" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="E14" s="18" t="n">
+        <v>202000</v>
+      </c>
+      <c r="F14" s="18" t="n">
+        <v>52</v>
+      </c>
+      <c r="G14" s="18" t="n">
+        <v>15004000</v>
+      </c>
+      <c r="H14" s="18" t="inlineStr">
+        <is>
+          <t>2031-09-02</t>
+        </is>
+      </c>
+      <c r="I14" s="18" t="inlineStr">
+        <is>
+          <t>2031-09-02</t>
+        </is>
+      </c>
+      <c r="J14" s="18" t="inlineStr">
+        <is>
+          <t>2032-09-07</t>
+        </is>
+      </c>
+      <c r="K14" s="18" t="inlineStr"/>
+      <c r="L14" s="18" t="inlineStr">
+        <is>
+          <t>later</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>b747</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="C15" s="18" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D15" s="18" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="E15" s="18" t="n">
+        <v>269000</v>
+      </c>
+      <c r="F15" s="18" t="n">
+        <v>52</v>
+      </c>
+      <c r="G15" s="18" t="n">
+        <v>19988000</v>
+      </c>
+      <c r="H15" s="18" t="inlineStr">
+        <is>
+          <t>2032-09-07</t>
+        </is>
+      </c>
+      <c r="I15" s="18" t="inlineStr">
+        <is>
+          <t>2032-09-07</t>
+        </is>
+      </c>
+      <c r="J15" s="18" t="inlineStr">
+        <is>
+          <t>2032-09-07</t>
+        </is>
+      </c>
+      <c r="K15" s="18" t="inlineStr"/>
+      <c r="L15" s="18" t="inlineStr">
+        <is>
+          <t>later</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>a380</t>
+        </is>
+      </c>
+      <c r="B16" s="18" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="C16" s="18" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D16" s="18" t="n">
+        <v>9000000</v>
+      </c>
+      <c r="E16" s="18" t="n">
+        <v>404000</v>
+      </c>
+      <c r="F16" s="18" t="n">
+        <v>52</v>
+      </c>
+      <c r="G16" s="18" t="n">
+        <v>30008000</v>
+      </c>
+      <c r="H16" s="18" t="inlineStr">
+        <is>
+          <t>2032-09-07</t>
+        </is>
+      </c>
+      <c r="I16" s="18" t="inlineStr">
+        <is>
+          <t>2032-09-07</t>
+        </is>
+      </c>
+      <c r="J16" s="18" t="inlineStr">
+        <is>
+          <t>2032-09-07</t>
+        </is>
+      </c>
+      <c r="K16" s="18" t="inlineStr">
+        <is>
+          <t>Chapter 4's worked example: 30,000,000 − 9,000,000 = 21,000,000; ÷ 52 ≈ £404,000 a week; total paid £30.0m.</t>
+        </is>
+      </c>
+      <c r="L16" s="18" t="inlineStr">
+        <is>
+          <t>later</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>Note on the launch-deal rows: tutorial finance is in daily payments (as in the game today), because the opening is played by the day; from the A220 the payments are weekly, because chapter 4 is played by the month. 'When does renting cost more than buying?' = price ÷ leaseDaily: about 20–25 days for tutorial planes (launch deals), 1,000 days for every jet from the A220 up (F4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>Tutorial prices are 2½× v4.3 (D55): the second plane is rented or financed in week 2 and bought outright around week 4–5. The first Twin Otter is still the £2,500 launch deal. Rent-or-buy ≈ 55 days for every tutorial plane; 1,000 days for jets from the A220 up.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1029,7 +2868,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1614,7 +3453,7 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="G9" s="13" t="inlineStr">
         <is>
@@ -1628,13 +3467,13 @@
       </c>
       <c r="I9" s="13" t="inlineStr">
         <is>
-          <t>Fuel £1.50 a litre.</t>
+          <t>Fuel £1.47 a litre.</t>
         </is>
       </c>
       <c r="J9" s="13" t="inlineStr"/>
       <c r="K9" s="13" t="inlineStr">
         <is>
-          <t>planes: dhc6 (second), saab340, atr72; mechanics: rent-or-buy sum, launch-deal finance, buy greyed until affordable, two timetables, assignment</t>
+          <t>planes: dhc6 (second), saab340, atr72; mechanics: rent-or-buy sum, launch-deal finance, buy greyed until affordable, two timetables, assignment; FUEL DESK opens (market, tank 8,000 L, buy in 1,000 L blocks, scenario table)</t>
         </is>
       </c>
       <c r="L9" s="13" t="inlineStr"/>
@@ -1684,7 +3523,7 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="G10" s="13" t="inlineStr">
         <is>
@@ -1738,7 +3577,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="G11" s="13" t="inlineStr">
         <is>
@@ -1748,7 +3587,7 @@
       <c r="H11" s="13" t="inlineStr"/>
       <c r="I11" s="13" t="inlineStr">
         <is>
-          <t>Fuel £1.60 a litre.</t>
+          <t>Fuel £1.47 a litre.</t>
         </is>
       </c>
       <c r="J11" s="13" t="inlineStr"/>
@@ -1792,7 +3631,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="G12" s="13" t="inlineStr">
         <is>
@@ -1850,7 +3689,7 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>1.7</v>
+        <v>1.47</v>
       </c>
       <c r="G13" s="13" t="inlineStr">
         <is>
@@ -1860,7 +3699,7 @@
       <c r="H13" s="13" t="inlineStr"/>
       <c r="I13" s="13" t="inlineStr">
         <is>
-          <t>Fuel £1.70 a litre.</t>
+          <t>Fuel £1.47 a litre.</t>
         </is>
       </c>
       <c r="J13" s="13" t="inlineStr"/>
@@ -1904,7 +3743,7 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>1.7</v>
+        <v>1.47</v>
       </c>
       <c r="G14" s="13" t="inlineStr">
         <is>
@@ -1958,7 +3797,7 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>1.7</v>
+        <v>1.47</v>
       </c>
       <c r="G15" s="13" t="inlineStr">
         <is>
@@ -2020,7 +3859,7 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
@@ -2034,7 +3873,7 @@
       </c>
       <c r="I16" s="13" t="inlineStr">
         <is>
-          <t>Fuel £1.70 a litre. Red Kite flies from Luton.</t>
+          <t>Fuel £1.68 a litre.</t>
         </is>
       </c>
       <c r="J16" s="13" t="inlineStr"/>
@@ -2090,7 +3929,7 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
@@ -2140,7 +3979,7 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="G18" s="13" t="inlineStr">
         <is>
@@ -2190,7 +4029,7 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="G19" s="13" t="inlineStr">
         <is>
@@ -2240,7 +4079,7 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
@@ -2298,7 +4137,7 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="G21" s="13" t="inlineStr">
         <is>
@@ -2352,7 +4191,7 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="G22" s="13" t="inlineStr">
         <is>
@@ -2414,7 +4253,7 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="G23" s="13" t="inlineStr">
         <is>
@@ -2428,7 +4267,7 @@
       </c>
       <c r="I23" s="13" t="inlineStr">
         <is>
-          <t>Fuel £1.80 a litre.</t>
+          <t>Fuel £1.79 a litre.</t>
         </is>
       </c>
       <c r="J23" s="13" t="inlineStr"/>
@@ -2484,7 +4323,7 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="G24" s="13" t="inlineStr">
         <is>
@@ -2534,7 +4373,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="G25" s="13" t="inlineStr">
         <is>
@@ -2596,7 +4435,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="G26" s="13" t="inlineStr">
         <is>
@@ -2650,7 +4489,7 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="G27" s="13" t="inlineStr">
         <is>
@@ -2700,7 +4539,7 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="G28" s="13" t="inlineStr">
         <is>
@@ -2754,7 +4593,7 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="G29" s="13" t="inlineStr">
         <is>
@@ -2806,13 +4645,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K417"/>
+  <dimension ref="A1:P417"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2826,6 +4665,11 @@
     <col width="34" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="40" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2884,6 +4728,31 @@
           <t>status</t>
         </is>
       </c>
+      <c r="L1" s="20" t="inlineStr">
+        <is>
+          <t>forecastLow (next week)</t>
+        </is>
+      </c>
+      <c r="M1" s="20" t="inlineStr">
+        <is>
+          <t>forecastHigh (next week)</t>
+        </is>
+      </c>
+      <c r="N1" s="20" t="inlineStr">
+        <is>
+          <t>fuelHeadline</t>
+        </is>
+      </c>
+      <c r="O1" s="20" t="inlineStr">
+        <is>
+          <t>forecastConfidence</t>
+        </is>
+      </c>
+      <c r="P1" s="20" t="inlineStr">
+        <is>
+          <t>fuelHeadline2 (second signal)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="12" t="n">
@@ -2927,6 +4796,22 @@
       <c r="K2" s="12" t="inlineStr">
         <is>
           <t>live</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Prices are climbing gently as autumn begins.</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>high</t>
         </is>
       </c>
     </row>
@@ -2945,7 +4830,7 @@
         </is>
       </c>
       <c r="D3" s="12" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="E3" s="12" t="n">
         <v>1</v>
@@ -2972,6 +4857,22 @@
       <c r="K3" s="12" t="inlineStr">
         <is>
           <t>live</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Prices are climbing steadily as winter approaches.</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>high</t>
         </is>
       </c>
     </row>
@@ -2990,7 +4891,7 @@
         </is>
       </c>
       <c r="D4" s="12" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>1</v>
@@ -3017,6 +4918,22 @@
       <c r="K4" s="12" t="inlineStr">
         <is>
           <t>live</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Analysts expect another small rise next week.</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>high</t>
         </is>
       </c>
     </row>
@@ -3035,7 +4952,7 @@
         </is>
       </c>
       <c r="D5" s="12" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>1</v>
@@ -3058,6 +4975,22 @@
       <c r="K5" s="12" t="inlineStr">
         <is>
           <t>live</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Steady rises continue.</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>high</t>
         </is>
       </c>
     </row>
@@ -3076,7 +5009,7 @@
         </is>
       </c>
       <c r="D6" s="12" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>1</v>
@@ -3099,6 +5032,22 @@
       <c r="K6" s="12" t="inlineStr">
         <is>
           <t>live</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Little change expected.</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>medium</t>
         </is>
       </c>
     </row>
@@ -3117,7 +5066,7 @@
         </is>
       </c>
       <c r="D7" s="12" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>1</v>
@@ -3140,6 +5089,22 @@
       <c r="K7" s="12" t="inlineStr">
         <is>
           <t>live</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Pipeline fire in the North Sea: prices expected to jump sharply next week.</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>medium</t>
         </is>
       </c>
     </row>
@@ -3158,7 +5123,7 @@
         </is>
       </c>
       <c r="D8" s="12" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>1</v>
@@ -3185,6 +5150,22 @@
       <c r="K8" s="12" t="inlineStr">
         <is>
           <t>live</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>The pipeline is repaired: prices expected to fall back next week.</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>medium</t>
         </is>
       </c>
     </row>
@@ -3203,7 +5184,7 @@
         </is>
       </c>
       <c r="D9" s="12" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>1</v>
@@ -3230,6 +5211,22 @@
       <c r="K9" s="12" t="inlineStr">
         <is>
           <t>live</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Prices settling.</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>high</t>
         </is>
       </c>
     </row>
@@ -3248,7 +5245,7 @@
         </is>
       </c>
       <c r="D10" s="12" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>1</v>
@@ -3271,6 +5268,27 @@
       <c r="K10" s="12" t="inlineStr">
         <is>
           <t>live</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Energy market: refinery maintenance finishes on Friday, so supply should increase and prices may ease.</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Weather: a major Atlantic storm is building and shipping may be disrupted — that would push prices up.</t>
         </is>
       </c>
     </row>
@@ -3289,7 +5307,7 @@
         </is>
       </c>
       <c r="D11" s="12" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="E11" s="12" t="n">
         <v>1</v>
@@ -3312,6 +5330,22 @@
       <c r="K11" s="12" t="inlineStr">
         <is>
           <t>live</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Little change expected.</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>medium</t>
         </is>
       </c>
     </row>
@@ -3330,7 +5364,7 @@
         </is>
       </c>
       <c r="D12" s="12" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>1</v>
@@ -3357,6 +5391,22 @@
       <c r="K12" s="12" t="inlineStr">
         <is>
           <t>live</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>A small rise expected as cold weather arrives.</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>medium</t>
         </is>
       </c>
     </row>
@@ -3375,7 +5425,7 @@
         </is>
       </c>
       <c r="D13" s="12" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="E13" s="12" t="n">
         <v>1</v>
@@ -3402,6 +5452,27 @@
       <c r="K13" s="12" t="inlineStr">
         <is>
           <t>live</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Prices expected to ease slightly.</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Weather: a mild spell is forecast across Europe, which usually lowers demand for fuel.</t>
         </is>
       </c>
     </row>
@@ -3420,7 +5491,7 @@
         </is>
       </c>
       <c r="D14" s="12" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="E14" s="12" t="n">
         <v>1</v>
@@ -3443,6 +5514,22 @@
       <c r="K14" s="12" t="inlineStr">
         <is>
           <t>live</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Huge new oil field found in the Atlantic: prices expected to fall sharply next week.</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>medium</t>
         </is>
       </c>
     </row>
@@ -3461,7 +5548,7 @@
         </is>
       </c>
       <c r="D15" s="12" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="E15" s="12" t="n">
         <v>1</v>
@@ -3488,6 +5575,22 @@
       <c r="K15" s="12" t="inlineStr">
         <is>
           <t>live</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Prices recovering from the oil-field low.</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>high</t>
         </is>
       </c>
     </row>
@@ -3506,7 +5609,7 @@
         </is>
       </c>
       <c r="D16" s="12" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="E16" s="12" t="n">
         <v>1</v>
@@ -3533,6 +5636,22 @@
       <c r="K16" s="12" t="inlineStr">
         <is>
           <t>live</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Recovery continues.</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>high</t>
         </is>
       </c>
     </row>
@@ -3551,7 +5670,7 @@
         </is>
       </c>
       <c r="D17" s="12" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="E17" s="12" t="n">
         <v>0.7</v>
@@ -3574,6 +5693,27 @@
       <c r="K17" s="12" t="inlineStr">
         <is>
           <t>live</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Recovery continues into Christmas.</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Weather: very cold weather in North America could lift prices worldwide.</t>
         </is>
       </c>
     </row>
@@ -3592,7 +5732,7 @@
         </is>
       </c>
       <c r="D18" s="12" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="E18" s="12" t="n">
         <v>0.7</v>
@@ -3619,6 +5759,22 @@
       <c r="K18" s="12" t="inlineStr">
         <is>
           <t>live</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Prices expected to keep rising in January.</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>medium</t>
         </is>
       </c>
     </row>
@@ -20082,7 +22238,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -21926,7 +24082,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -22342,7 +24498,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -22760,7 +24916,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -22989,976 +25145,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F38"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="24" t="inlineStr">
-        <is>
-          <t>kind</t>
-        </is>
-      </c>
-      <c r="B1" s="24" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="C1" s="24" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="D1" s="24" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="E1" s="24" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="F1" s="24" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="23" t="inlineStr">
-        <is>
-          <t>colour</t>
-        </is>
-      </c>
-      <c r="B2" s="23" t="inlineStr">
-        <is>
-          <t>white</t>
-        </is>
-      </c>
-      <c r="C2" s="23" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
-      <c r="D2" s="23" t="inlineStr">
-        <is>
-          <t>#F4F6F8</t>
-        </is>
-      </c>
-      <c r="E2" s="23" t="inlineStr">
-        <is>
-          <t>Twelve-colour palette for every paintable layer and the logo (CR5).</t>
-        </is>
-      </c>
-      <c r="F2" s="23" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="23" t="inlineStr">
-        <is>
-          <t>colour</t>
-        </is>
-      </c>
-      <c r="B3" s="23" t="inlineStr">
-        <is>
-          <t>navy</t>
-        </is>
-      </c>
-      <c r="C3" s="23" t="inlineStr">
-        <is>
-          <t>Navy</t>
-        </is>
-      </c>
-      <c r="D3" s="23" t="inlineStr">
-        <is>
-          <t>#1B2A4A</t>
-        </is>
-      </c>
-      <c r="E3" s="23" t="inlineStr"/>
-      <c r="F3" s="23" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="23" t="inlineStr">
-        <is>
-          <t>colour</t>
-        </is>
-      </c>
-      <c r="B4" s="23" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="C4" s="23" t="inlineStr">
-        <is>
-          <t>Red</t>
-        </is>
-      </c>
-      <c r="D4" s="23" t="inlineStr">
-        <is>
-          <t>#D7263D</t>
-        </is>
-      </c>
-      <c r="E4" s="23" t="inlineStr"/>
-      <c r="F4" s="23" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="23" t="inlineStr">
-        <is>
-          <t>colour</t>
-        </is>
-      </c>
-      <c r="B5" s="23" t="inlineStr">
-        <is>
-          <t>orange</t>
-        </is>
-      </c>
-      <c r="C5" s="23" t="inlineStr">
-        <is>
-          <t>Orange</t>
-        </is>
-      </c>
-      <c r="D5" s="23" t="inlineStr">
-        <is>
-          <t>#F46036</t>
-        </is>
-      </c>
-      <c r="E5" s="23" t="inlineStr"/>
-      <c r="F5" s="23" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="23" t="inlineStr">
-        <is>
-          <t>colour</t>
-        </is>
-      </c>
-      <c r="B6" s="23" t="inlineStr">
-        <is>
-          <t>yellow</t>
-        </is>
-      </c>
-      <c r="C6" s="23" t="inlineStr">
-        <is>
-          <t>Yellow</t>
-        </is>
-      </c>
-      <c r="D6" s="23" t="inlineStr">
-        <is>
-          <t>#F2C14E</t>
-        </is>
-      </c>
-      <c r="E6" s="23" t="inlineStr"/>
-      <c r="F6" s="23" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="23" t="inlineStr">
-        <is>
-          <t>colour</t>
-        </is>
-      </c>
-      <c r="B7" s="23" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="C7" s="23" t="inlineStr">
-        <is>
-          <t>Green</t>
-        </is>
-      </c>
-      <c r="D7" s="23" t="inlineStr">
-        <is>
-          <t>#2E8B57</t>
-        </is>
-      </c>
-      <c r="E7" s="23" t="inlineStr"/>
-      <c r="F7" s="23" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="23" t="inlineStr">
-        <is>
-          <t>colour</t>
-        </is>
-      </c>
-      <c r="B8" s="23" t="inlineStr">
-        <is>
-          <t>teal</t>
-        </is>
-      </c>
-      <c r="C8" s="23" t="inlineStr">
-        <is>
-          <t>Teal</t>
-        </is>
-      </c>
-      <c r="D8" s="23" t="inlineStr">
-        <is>
-          <t>#1B998B</t>
-        </is>
-      </c>
-      <c r="E8" s="23" t="inlineStr"/>
-      <c r="F8" s="23" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="23" t="inlineStr">
-        <is>
-          <t>colour</t>
-        </is>
-      </c>
-      <c r="B9" s="23" t="inlineStr">
-        <is>
-          <t>sky</t>
-        </is>
-      </c>
-      <c r="C9" s="23" t="inlineStr">
-        <is>
-          <t>Sky</t>
-        </is>
-      </c>
-      <c r="D9" s="23" t="inlineStr">
-        <is>
-          <t>#3FA7D6</t>
-        </is>
-      </c>
-      <c r="E9" s="23" t="inlineStr"/>
-      <c r="F9" s="23" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="23" t="inlineStr">
-        <is>
-          <t>colour</t>
-        </is>
-      </c>
-      <c r="B10" s="23" t="inlineStr">
-        <is>
-          <t>purple</t>
-        </is>
-      </c>
-      <c r="C10" s="23" t="inlineStr">
-        <is>
-          <t>Purple</t>
-        </is>
-      </c>
-      <c r="D10" s="23" t="inlineStr">
-        <is>
-          <t>#6A4C93</t>
-        </is>
-      </c>
-      <c r="E10" s="23" t="inlineStr"/>
-      <c r="F10" s="23" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="23" t="inlineStr">
-        <is>
-          <t>colour</t>
-        </is>
-      </c>
-      <c r="B11" s="23" t="inlineStr">
-        <is>
-          <t>pink</t>
-        </is>
-      </c>
-      <c r="C11" s="23" t="inlineStr">
-        <is>
-          <t>Pink</t>
-        </is>
-      </c>
-      <c r="D11" s="23" t="inlineStr">
-        <is>
-          <t>#E56399</t>
-        </is>
-      </c>
-      <c r="E11" s="23" t="inlineStr"/>
-      <c r="F11" s="23" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="23" t="inlineStr">
-        <is>
-          <t>colour</t>
-        </is>
-      </c>
-      <c r="B12" s="23" t="inlineStr">
-        <is>
-          <t>silver</t>
-        </is>
-      </c>
-      <c r="C12" s="23" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="D12" s="23" t="inlineStr">
-        <is>
-          <t>#A9B4C2</t>
-        </is>
-      </c>
-      <c r="E12" s="23" t="inlineStr"/>
-      <c r="F12" s="23" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="23" t="inlineStr">
-        <is>
-          <t>colour</t>
-        </is>
-      </c>
-      <c r="B13" s="23" t="inlineStr">
-        <is>
-          <t>black</t>
-        </is>
-      </c>
-      <c r="C13" s="23" t="inlineStr">
-        <is>
-          <t>Black</t>
-        </is>
-      </c>
-      <c r="D13" s="23" t="inlineStr">
-        <is>
-          <t>#1E1E24</t>
-        </is>
-      </c>
-      <c r="E13" s="23" t="inlineStr"/>
-      <c r="F13" s="23" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="23" t="inlineStr">
-        <is>
-          <t>stripe</t>
-        </is>
-      </c>
-      <c r="B14" s="23" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C14" s="23" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D14" s="23" t="inlineStr"/>
-      <c r="E14" s="23" t="inlineStr">
-        <is>
-          <t>Stripe styles along the fuselage, in the second colour.</t>
-        </is>
-      </c>
-      <c r="F14" s="23" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="23" t="inlineStr">
-        <is>
-          <t>stripe</t>
-        </is>
-      </c>
-      <c r="B15" s="23" t="inlineStr">
-        <is>
-          <t>thin</t>
-        </is>
-      </c>
-      <c r="C15" s="23" t="inlineStr">
-        <is>
-          <t>Thin line</t>
-        </is>
-      </c>
-      <c r="D15" s="23" t="inlineStr"/>
-      <c r="E15" s="23" t="inlineStr"/>
-      <c r="F15" s="23" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="23" t="inlineStr">
-        <is>
-          <t>stripe</t>
-        </is>
-      </c>
-      <c r="B16" s="23" t="inlineStr">
-        <is>
-          <t>band</t>
-        </is>
-      </c>
-      <c r="C16" s="23" t="inlineStr">
-        <is>
-          <t>Bold band</t>
-        </is>
-      </c>
-      <c r="D16" s="23" t="inlineStr"/>
-      <c r="E16" s="23" t="inlineStr"/>
-      <c r="F16" s="23" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="23" t="inlineStr">
-        <is>
-          <t>stripe</t>
-        </is>
-      </c>
-      <c r="B17" s="23" t="inlineStr">
-        <is>
-          <t>swoosh</t>
-        </is>
-      </c>
-      <c r="C17" s="23" t="inlineStr">
-        <is>
-          <t>Swoosh</t>
-        </is>
-      </c>
-      <c r="D17" s="23" t="inlineStr"/>
-      <c r="E17" s="23" t="inlineStr"/>
-      <c r="F17" s="23" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="23" t="inlineStr">
-        <is>
-          <t>tail</t>
-        </is>
-      </c>
-      <c r="B18" s="23" t="inlineStr">
-        <is>
-          <t>stripe</t>
-        </is>
-      </c>
-      <c r="C18" s="23" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="D18" s="23" t="inlineStr"/>
-      <c r="E18" s="23" t="inlineStr">
-        <is>
-          <t>Tail-fin symbols, in the second colour. "logo" draws the airline logo on the fin.</t>
-        </is>
-      </c>
-      <c r="F18" s="23" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="23" t="inlineStr">
-        <is>
-          <t>tail</t>
-        </is>
-      </c>
-      <c r="B19" s="23" t="inlineStr">
-        <is>
-          <t>star</t>
-        </is>
-      </c>
-      <c r="C19" s="23" t="inlineStr">
-        <is>
-          <t>Star</t>
-        </is>
-      </c>
-      <c r="D19" s="23" t="inlineStr"/>
-      <c r="E19" s="23" t="inlineStr"/>
-      <c r="F19" s="23" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="23" t="inlineStr">
-        <is>
-          <t>tail</t>
-        </is>
-      </c>
-      <c r="B20" s="23" t="inlineStr">
-        <is>
-          <t>chevron</t>
-        </is>
-      </c>
-      <c r="C20" s="23" t="inlineStr">
-        <is>
-          <t>Chevron</t>
-        </is>
-      </c>
-      <c r="D20" s="23" t="inlineStr"/>
-      <c r="E20" s="23" t="inlineStr"/>
-      <c r="F20" s="23" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="23" t="inlineStr">
-        <is>
-          <t>tail</t>
-        </is>
-      </c>
-      <c r="B21" s="23" t="inlineStr">
-        <is>
-          <t>wave</t>
-        </is>
-      </c>
-      <c r="C21" s="23" t="inlineStr">
-        <is>
-          <t>Wave</t>
-        </is>
-      </c>
-      <c r="D21" s="23" t="inlineStr"/>
-      <c r="E21" s="23" t="inlineStr"/>
-      <c r="F21" s="23" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="23" t="inlineStr">
-        <is>
-          <t>tail</t>
-        </is>
-      </c>
-      <c r="B22" s="23" t="inlineStr">
-        <is>
-          <t>circle</t>
-        </is>
-      </c>
-      <c r="C22" s="23" t="inlineStr">
-        <is>
-          <t>Circle</t>
-        </is>
-      </c>
-      <c r="D22" s="23" t="inlineStr"/>
-      <c r="E22" s="23" t="inlineStr"/>
-      <c r="F22" s="23" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="23" t="inlineStr">
-        <is>
-          <t>tail</t>
-        </is>
-      </c>
-      <c r="B23" s="23" t="inlineStr">
-        <is>
-          <t>arrow</t>
-        </is>
-      </c>
-      <c r="C23" s="23" t="inlineStr">
-        <is>
-          <t>Arrow</t>
-        </is>
-      </c>
-      <c r="D23" s="23" t="inlineStr"/>
-      <c r="E23" s="23" t="inlineStr"/>
-      <c r="F23" s="23" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="23" t="inlineStr">
-        <is>
-          <t>tail</t>
-        </is>
-      </c>
-      <c r="B24" s="23" t="inlineStr">
-        <is>
-          <t>logo</t>
-        </is>
-      </c>
-      <c r="C24" s="23" t="inlineStr">
-        <is>
-          <t>Your logo</t>
-        </is>
-      </c>
-      <c r="D24" s="23" t="inlineStr"/>
-      <c r="E24" s="23" t="inlineStr"/>
-      <c r="F24" s="23" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="23" t="inlineStr">
-        <is>
-          <t>logoShape</t>
-        </is>
-      </c>
-      <c r="B25" s="23" t="inlineStr">
-        <is>
-          <t>square</t>
-        </is>
-      </c>
-      <c r="C25" s="23" t="inlineStr">
-        <is>
-          <t>Square</t>
-        </is>
-      </c>
-      <c r="D25" s="23" t="inlineStr"/>
-      <c r="E25" s="23" t="inlineStr">
-        <is>
-          <t>Logo backgrounds: shape × symbol (the tail set) × two colours.</t>
-        </is>
-      </c>
-      <c r="F25" s="23" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="23" t="inlineStr">
-        <is>
-          <t>logoShape</t>
-        </is>
-      </c>
-      <c r="B26" s="23" t="inlineStr">
-        <is>
-          <t>circle</t>
-        </is>
-      </c>
-      <c r="C26" s="23" t="inlineStr">
-        <is>
-          <t>Circle</t>
-        </is>
-      </c>
-      <c r="D26" s="23" t="inlineStr"/>
-      <c r="E26" s="23" t="inlineStr"/>
-      <c r="F26" s="23" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="23" t="inlineStr">
-        <is>
-          <t>logoShape</t>
-        </is>
-      </c>
-      <c r="B27" s="23" t="inlineStr">
-        <is>
-          <t>shield</t>
-        </is>
-      </c>
-      <c r="C27" s="23" t="inlineStr">
-        <is>
-          <t>Shield</t>
-        </is>
-      </c>
-      <c r="D27" s="23" t="inlineStr"/>
-      <c r="E27" s="23" t="inlineStr"/>
-      <c r="F27" s="23" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="23" t="inlineStr">
-        <is>
-          <t>logoShape</t>
-        </is>
-      </c>
-      <c r="B28" s="23" t="inlineStr">
-        <is>
-          <t>fin</t>
-        </is>
-      </c>
-      <c r="C28" s="23" t="inlineStr">
-        <is>
-          <t>Tail fin</t>
-        </is>
-      </c>
-      <c r="D28" s="23" t="inlineStr"/>
-      <c r="E28" s="23" t="inlineStr"/>
-      <c r="F28" s="23" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="23" t="inlineStr">
-        <is>
-          <t>planeName</t>
-        </is>
-      </c>
-      <c r="B29" s="23" t="inlineStr">
-        <is>
-          <t>spirit</t>
-        </is>
-      </c>
-      <c r="C29" s="23" t="inlineStr">
-        <is>
-          <t>Spirit of Wales</t>
-        </is>
-      </c>
-      <c r="D29" s="23" t="inlineStr"/>
-      <c r="E29" s="23" t="inlineStr">
-        <is>
-          <t>Tap-to-use suggestions on the Name it tab; four are offered at a time.</t>
-        </is>
-      </c>
-      <c r="F29" s="23" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="23" t="inlineStr">
-        <is>
-          <t>planeName</t>
-        </is>
-      </c>
-      <c r="B30" s="23" t="inlineStr">
-        <is>
-          <t>cloud</t>
-        </is>
-      </c>
-      <c r="C30" s="23" t="inlineStr">
-        <is>
-          <t>Cloud Runner</t>
-        </is>
-      </c>
-      <c r="D30" s="23" t="inlineStr"/>
-      <c r="E30" s="23" t="inlineStr"/>
-      <c r="F30" s="23" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="23" t="inlineStr">
-        <is>
-          <t>planeName</t>
-        </is>
-      </c>
-      <c r="B31" s="23" t="inlineStr">
-        <is>
-          <t>dragon</t>
-        </is>
-      </c>
-      <c r="C31" s="23" t="inlineStr">
-        <is>
-          <t>Red Dragon</t>
-        </is>
-      </c>
-      <c r="D31" s="23" t="inlineStr"/>
-      <c r="E31" s="23" t="inlineStr"/>
-      <c r="F31" s="23" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="23" t="inlineStr">
-        <is>
-          <t>planeName</t>
-        </is>
-      </c>
-      <c r="B32" s="23" t="inlineStr">
-        <is>
-          <t>hopper</t>
-        </is>
-      </c>
-      <c r="C32" s="23" t="inlineStr">
-        <is>
-          <t>Sky Hopper</t>
-        </is>
-      </c>
-      <c r="D32" s="23" t="inlineStr"/>
-      <c r="E32" s="23" t="inlineStr"/>
-      <c r="F32" s="23" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="23" t="inlineStr">
-        <is>
-          <t>planeName</t>
-        </is>
-      </c>
-      <c r="B33" s="23" t="inlineStr">
-        <is>
-          <t>star</t>
-        </is>
-      </c>
-      <c r="C33" s="23" t="inlineStr">
-        <is>
-          <t>Morning Star</t>
-        </is>
-      </c>
-      <c r="D33" s="23" t="inlineStr"/>
-      <c r="E33" s="23" t="inlineStr"/>
-      <c r="F33" s="23" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="23" t="inlineStr">
-        <is>
-          <t>planeName</t>
-        </is>
-      </c>
-      <c r="B34" s="23" t="inlineStr">
-        <is>
-          <t>severn</t>
-        </is>
-      </c>
-      <c r="C34" s="23" t="inlineStr">
-        <is>
-          <t>Severn Breeze</t>
-        </is>
-      </c>
-      <c r="D34" s="23" t="inlineStr"/>
-      <c r="E34" s="23" t="inlineStr"/>
-      <c r="F34" s="23" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="23" t="inlineStr">
-        <is>
-          <t>planeName</t>
-        </is>
-      </c>
-      <c r="B35" s="23" t="inlineStr">
-        <is>
-          <t>comet</t>
-        </is>
-      </c>
-      <c r="C35" s="23" t="inlineStr">
-        <is>
-          <t>Little Comet</t>
-        </is>
-      </c>
-      <c r="D35" s="23" t="inlineStr"/>
-      <c r="E35" s="23" t="inlineStr"/>
-      <c r="F35" s="23" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="23" t="inlineStr">
-        <is>
-          <t>planeName</t>
-        </is>
-      </c>
-      <c r="B36" s="23" t="inlineStr">
-        <is>
-          <t>wren</t>
-        </is>
-      </c>
-      <c r="C36" s="23" t="inlineStr">
-        <is>
-          <t>Jenny Wren</t>
-        </is>
-      </c>
-      <c r="D36" s="23" t="inlineStr"/>
-      <c r="E36" s="23" t="inlineStr"/>
-      <c r="F36" s="23" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Note: the game reads live rows only. Colours are hex; stripe, tail and logoShape ids match the artwork layers; planeName ids are only there so a row can be referred to.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -24744,6 +25931,976 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="24" t="inlineStr">
+        <is>
+          <t>kind</t>
+        </is>
+      </c>
+      <c r="B1" s="24" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C1" s="24" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" s="24" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="E1" s="24" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="F1" s="24" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="23" t="inlineStr">
+        <is>
+          <t>colour</t>
+        </is>
+      </c>
+      <c r="B2" s="23" t="inlineStr">
+        <is>
+          <t>white</t>
+        </is>
+      </c>
+      <c r="C2" s="23" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+      <c r="D2" s="23" t="inlineStr">
+        <is>
+          <t>#F4F6F8</t>
+        </is>
+      </c>
+      <c r="E2" s="23" t="inlineStr">
+        <is>
+          <t>Twelve-colour palette for every paintable layer and the logo (CR5).</t>
+        </is>
+      </c>
+      <c r="F2" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="23" t="inlineStr">
+        <is>
+          <t>colour</t>
+        </is>
+      </c>
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>navy</t>
+        </is>
+      </c>
+      <c r="C3" s="23" t="inlineStr">
+        <is>
+          <t>Navy</t>
+        </is>
+      </c>
+      <c r="D3" s="23" t="inlineStr">
+        <is>
+          <t>#1B2A4A</t>
+        </is>
+      </c>
+      <c r="E3" s="23" t="n"/>
+      <c r="F3" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="23" t="inlineStr">
+        <is>
+          <t>colour</t>
+        </is>
+      </c>
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="C4" s="23" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="D4" s="23" t="inlineStr">
+        <is>
+          <t>#D7263D</t>
+        </is>
+      </c>
+      <c r="E4" s="23" t="n"/>
+      <c r="F4" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="23" t="inlineStr">
+        <is>
+          <t>colour</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="D5" s="23" t="inlineStr">
+        <is>
+          <t>#F46036</t>
+        </is>
+      </c>
+      <c r="E5" s="23" t="n"/>
+      <c r="F5" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="23" t="inlineStr">
+        <is>
+          <t>colour</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>yellow</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>#F2C14E</t>
+        </is>
+      </c>
+      <c r="E6" s="23" t="n"/>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="23" t="inlineStr">
+        <is>
+          <t>colour</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="D7" s="23" t="inlineStr">
+        <is>
+          <t>#2E8B57</t>
+        </is>
+      </c>
+      <c r="E7" s="23" t="n"/>
+      <c r="F7" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>colour</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>teal</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>Teal</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>#1B998B</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="n"/>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="23" t="inlineStr">
+        <is>
+          <t>colour</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>sky</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>Sky</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>#3FA7D6</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="n"/>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t>colour</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>purple</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>Purple</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>#6A4C93</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="n"/>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="23" t="inlineStr">
+        <is>
+          <t>colour</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>pink</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>Pink</t>
+        </is>
+      </c>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t>#E56399</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="n"/>
+      <c r="F11" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>colour</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>silver</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>#A9B4C2</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="n"/>
+      <c r="F12" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="23" t="inlineStr">
+        <is>
+          <t>colour</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>black</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="D13" s="23" t="inlineStr">
+        <is>
+          <t>#1E1E24</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="n"/>
+      <c r="F13" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="23" t="inlineStr">
+        <is>
+          <t>stripe</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="n"/>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>Stripe styles along the fuselage, in the second colour.</t>
+        </is>
+      </c>
+      <c r="F14" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="23" t="inlineStr">
+        <is>
+          <t>stripe</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>thin</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>Thin line</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="n"/>
+      <c r="E15" s="23" t="n"/>
+      <c r="F15" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="23" t="inlineStr">
+        <is>
+          <t>stripe</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>band</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>Bold band</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="n"/>
+      <c r="E16" s="23" t="n"/>
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="23" t="inlineStr">
+        <is>
+          <t>stripe</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>swoosh</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
+        <is>
+          <t>Swoosh</t>
+        </is>
+      </c>
+      <c r="D17" s="23" t="n"/>
+      <c r="E17" s="23" t="n"/>
+      <c r="F17" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="23" t="inlineStr">
+        <is>
+          <t>tail</t>
+        </is>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>stripe</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="n"/>
+      <c r="E18" s="23" t="inlineStr">
+        <is>
+          <t>Tail-fin symbols, in the second colour. "logo" draws the airline logo on the fin.</t>
+        </is>
+      </c>
+      <c r="F18" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="23" t="inlineStr">
+        <is>
+          <t>tail</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>star</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>Star</t>
+        </is>
+      </c>
+      <c r="D19" s="23" t="n"/>
+      <c r="E19" s="23" t="n"/>
+      <c r="F19" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="23" t="inlineStr">
+        <is>
+          <t>tail</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>chevron</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>Chevron</t>
+        </is>
+      </c>
+      <c r="D20" s="23" t="n"/>
+      <c r="E20" s="23" t="n"/>
+      <c r="F20" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="23" t="inlineStr">
+        <is>
+          <t>tail</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>wave</t>
+        </is>
+      </c>
+      <c r="C21" s="23" t="inlineStr">
+        <is>
+          <t>Wave</t>
+        </is>
+      </c>
+      <c r="D21" s="23" t="n"/>
+      <c r="E21" s="23" t="n"/>
+      <c r="F21" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="23" t="inlineStr">
+        <is>
+          <t>tail</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>circle</t>
+        </is>
+      </c>
+      <c r="C22" s="23" t="inlineStr">
+        <is>
+          <t>Circle</t>
+        </is>
+      </c>
+      <c r="D22" s="23" t="n"/>
+      <c r="E22" s="23" t="n"/>
+      <c r="F22" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="23" t="inlineStr">
+        <is>
+          <t>tail</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>arrow</t>
+        </is>
+      </c>
+      <c r="C23" s="23" t="inlineStr">
+        <is>
+          <t>Arrow</t>
+        </is>
+      </c>
+      <c r="D23" s="23" t="n"/>
+      <c r="E23" s="23" t="n"/>
+      <c r="F23" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="23" t="inlineStr">
+        <is>
+          <t>tail</t>
+        </is>
+      </c>
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>logo</t>
+        </is>
+      </c>
+      <c r="C24" s="23" t="inlineStr">
+        <is>
+          <t>Your logo</t>
+        </is>
+      </c>
+      <c r="D24" s="23" t="n"/>
+      <c r="E24" s="23" t="n"/>
+      <c r="F24" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="23" t="inlineStr">
+        <is>
+          <t>logoShape</t>
+        </is>
+      </c>
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>square</t>
+        </is>
+      </c>
+      <c r="C25" s="23" t="inlineStr">
+        <is>
+          <t>Square</t>
+        </is>
+      </c>
+      <c r="D25" s="23" t="n"/>
+      <c r="E25" s="23" t="inlineStr">
+        <is>
+          <t>Logo backgrounds: shape × symbol (the tail set) × two colours.</t>
+        </is>
+      </c>
+      <c r="F25" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="23" t="inlineStr">
+        <is>
+          <t>logoShape</t>
+        </is>
+      </c>
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>circle</t>
+        </is>
+      </c>
+      <c r="C26" s="23" t="inlineStr">
+        <is>
+          <t>Circle</t>
+        </is>
+      </c>
+      <c r="D26" s="23" t="n"/>
+      <c r="E26" s="23" t="n"/>
+      <c r="F26" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="23" t="inlineStr">
+        <is>
+          <t>logoShape</t>
+        </is>
+      </c>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>shield</t>
+        </is>
+      </c>
+      <c r="C27" s="23" t="inlineStr">
+        <is>
+          <t>Shield</t>
+        </is>
+      </c>
+      <c r="D27" s="23" t="n"/>
+      <c r="E27" s="23" t="n"/>
+      <c r="F27" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="23" t="inlineStr">
+        <is>
+          <t>logoShape</t>
+        </is>
+      </c>
+      <c r="B28" s="23" t="inlineStr">
+        <is>
+          <t>fin</t>
+        </is>
+      </c>
+      <c r="C28" s="23" t="inlineStr">
+        <is>
+          <t>Tail fin</t>
+        </is>
+      </c>
+      <c r="D28" s="23" t="n"/>
+      <c r="E28" s="23" t="n"/>
+      <c r="F28" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="23" t="inlineStr">
+        <is>
+          <t>planeName</t>
+        </is>
+      </c>
+      <c r="B29" s="23" t="inlineStr">
+        <is>
+          <t>spirit</t>
+        </is>
+      </c>
+      <c r="C29" s="23" t="inlineStr">
+        <is>
+          <t>Spirit of Wales</t>
+        </is>
+      </c>
+      <c r="D29" s="23" t="n"/>
+      <c r="E29" s="23" t="inlineStr">
+        <is>
+          <t>Tap-to-use suggestions on the Name it tab; four are offered at a time.</t>
+        </is>
+      </c>
+      <c r="F29" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="23" t="inlineStr">
+        <is>
+          <t>planeName</t>
+        </is>
+      </c>
+      <c r="B30" s="23" t="inlineStr">
+        <is>
+          <t>cloud</t>
+        </is>
+      </c>
+      <c r="C30" s="23" t="inlineStr">
+        <is>
+          <t>Cloud Runner</t>
+        </is>
+      </c>
+      <c r="D30" s="23" t="n"/>
+      <c r="E30" s="23" t="n"/>
+      <c r="F30" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="23" t="inlineStr">
+        <is>
+          <t>planeName</t>
+        </is>
+      </c>
+      <c r="B31" s="23" t="inlineStr">
+        <is>
+          <t>dragon</t>
+        </is>
+      </c>
+      <c r="C31" s="23" t="inlineStr">
+        <is>
+          <t>Red Dragon</t>
+        </is>
+      </c>
+      <c r="D31" s="23" t="n"/>
+      <c r="E31" s="23" t="n"/>
+      <c r="F31" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="23" t="inlineStr">
+        <is>
+          <t>planeName</t>
+        </is>
+      </c>
+      <c r="B32" s="23" t="inlineStr">
+        <is>
+          <t>hopper</t>
+        </is>
+      </c>
+      <c r="C32" s="23" t="inlineStr">
+        <is>
+          <t>Sky Hopper</t>
+        </is>
+      </c>
+      <c r="D32" s="23" t="n"/>
+      <c r="E32" s="23" t="n"/>
+      <c r="F32" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="23" t="inlineStr">
+        <is>
+          <t>planeName</t>
+        </is>
+      </c>
+      <c r="B33" s="23" t="inlineStr">
+        <is>
+          <t>star</t>
+        </is>
+      </c>
+      <c r="C33" s="23" t="inlineStr">
+        <is>
+          <t>Morning Star</t>
+        </is>
+      </c>
+      <c r="D33" s="23" t="n"/>
+      <c r="E33" s="23" t="n"/>
+      <c r="F33" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="23" t="inlineStr">
+        <is>
+          <t>planeName</t>
+        </is>
+      </c>
+      <c r="B34" s="23" t="inlineStr">
+        <is>
+          <t>severn</t>
+        </is>
+      </c>
+      <c r="C34" s="23" t="inlineStr">
+        <is>
+          <t>Severn Breeze</t>
+        </is>
+      </c>
+      <c r="D34" s="23" t="n"/>
+      <c r="E34" s="23" t="n"/>
+      <c r="F34" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="23" t="inlineStr">
+        <is>
+          <t>planeName</t>
+        </is>
+      </c>
+      <c r="B35" s="23" t="inlineStr">
+        <is>
+          <t>comet</t>
+        </is>
+      </c>
+      <c r="C35" s="23" t="inlineStr">
+        <is>
+          <t>Little Comet</t>
+        </is>
+      </c>
+      <c r="D35" s="23" t="n"/>
+      <c r="E35" s="23" t="n"/>
+      <c r="F35" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="23" t="inlineStr">
+        <is>
+          <t>planeName</t>
+        </is>
+      </c>
+      <c r="B36" s="23" t="inlineStr">
+        <is>
+          <t>wren</t>
+        </is>
+      </c>
+      <c r="C36" s="23" t="inlineStr">
+        <is>
+          <t>Jenny Wren</t>
+        </is>
+      </c>
+      <c r="D36" s="23" t="n"/>
+      <c r="E36" s="23" t="n"/>
+      <c r="F36" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Note: the game reads live rows only. Colours are hex; stripe, tail and logoShape ids match the artwork layers; planeName ids are only there so a row can be referred to.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -25051,7 +27208,392 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D66"/>
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="20" t="inlineStr">
+        <is>
+          <t>relationship</t>
+        </is>
+      </c>
+      <c r="B1" s="20" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="C1" s="20" t="inlineStr">
+        <is>
+          <t>whereItLives</t>
+        </is>
+      </c>
+      <c r="D1" s="20" t="inlineStr">
+        <is>
+          <t>methodsOffered</t>
+        </is>
+      </c>
+      <c r="E1" s="20" t="inlineStr">
+        <is>
+          <t>example</t>
+        </is>
+      </c>
+      <c r="F1" s="20" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>passengers × fare</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="inlineStr">
+        <is>
+          <t>Planning board → sign-off</t>
+        </is>
+      </c>
+      <c r="D2" s="13" t="inlineStr">
+        <is>
+          <t>formal multiplication | partition tens and ones</t>
+        </is>
+      </c>
+      <c r="E2" s="13" t="inlineStr">
+        <is>
+          <t>38 × £90; 34 × £95</t>
+        </is>
+      </c>
+      <c r="F2" s="13" t="inlineStr">
+        <is>
+          <t>Short × then × 10 for £10 fares; long × for £5 fares and fares over £100</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>litres × price per litre</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>Aircraft performance card</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>partition the price (£1 + 40p + 7p) | scale from 100 L | make it pence | count the decimal places | formal multiplication</t>
+        </is>
+      </c>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>120 L × £1.47</t>
+        </is>
+      </c>
+      <c r="F3" s="13" t="inlineStr">
+        <is>
+          <t>Scale from 100 L: 100 L costs £147, so 20 L costs £29.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>revenue − costs</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>Sign-off; weekly accounts</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>vertical money subtraction | revenue and cost blocks (drag cost off revenue)</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>£3,420 − £1,830</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>day profit × 7</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Weekly accounts</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>seven-day strip, then efficient multiplication</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>£1,700 × 7</t>
+        </is>
+      </c>
+      <c r="F5" s="13" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>difference between plans</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>Analytics console</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>side-by-side bars | subtraction</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>£1,386 − £1,142</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>Shown in the 'What changed?' panel</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>fuel purchase</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>strategic</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>Fuel procurement desk</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>cost of 1,000 L × number of blocks</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>1,000 L at £1.47 = £1,470; 3,000 L = 3 × £1,470</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>buy now or wait</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>strategic</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>Fuel procurement desk → Model the options</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>scenario table (price rows × buy nothing / buy now / difference)</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>3,000 L: at £1.60 next week, buying now saves 3,000 × 13p = £390</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>'Saved compared with buying later', never profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>price ÷ rent</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Shop sign-off</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>short division | make the sum smaller</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>22,000 ÷ 400 = 55 days</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>load factor</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Weekly accounts (from week 4)</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>filled aircraft graphic → fraction → percentage</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>15 of 19 → 15⁄19 → 79%</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>tenths of passengers</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Event card; weekend</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>bar split into tenths</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>4 tenths of 62</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>average of a period</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>Monthly and quarterly reports (later)</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>period cards combined and shared</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr"/>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>Chapter 2 onwards</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>D60: the workbench (Work it out) offers the methods listed for the relationship being signed off; the pupil chooses. Levels: operational (what does this one thing cost? — taught and calculated), model (what happens if I change this? — the console calculates), strategic (what should I do when the future is uncertain? — maths supports judgement).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -26367,64 +28909,394 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="23" t="inlineStr">
+      <c r="A64" s="13" t="inlineStr">
+        <is>
+          <t>fuelLotSize</t>
+        </is>
+      </c>
+      <c r="B64" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C64" s="13" t="inlineStr">
+        <is>
+          <t>D57: fuel is bought in whole thousands of litres on the fuel desk (replaces the 500-litre lot).</t>
+        </is>
+      </c>
+      <c r="D64" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="13" t="inlineStr">
+        <is>
+          <t>tankCapacity</t>
+        </is>
+      </c>
+      <c r="B65" s="13" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C65" s="13" t="inlineStr">
+        <is>
+          <t>D60: litres of storage from week 2.</t>
+        </is>
+      </c>
+      <c r="D65" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="13" t="inlineStr">
+        <is>
+          <t>fuelUseOrder</t>
+        </is>
+      </c>
+      <c r="B66" s="13" t="inlineStr">
+        <is>
+          <t>oldest first</t>
+        </is>
+      </c>
+      <c r="C66" s="13" t="inlineStr">
+        <is>
+          <t>D57: each trip draws fuel from the oldest layer in the tank and is costed at that layer's price. If a trip spans two layers, the litres are split between them.</t>
+        </is>
+      </c>
+      <c r="D66" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="13" t="inlineStr">
+        <is>
+          <t>fuelBuyWhen</t>
+        </is>
+      </c>
+      <c r="B67" s="13" t="inlineStr">
+        <is>
+          <t>Monday plan</t>
+        </is>
+      </c>
+      <c r="C67" s="13" t="inlineStr">
+        <is>
+          <t>Fuel is bought on the fuel desk at the week's Market price during the Monday plan. If the tank runs dry mid-week, the game buys the shortfall automatically at that day's Calendar price plus emergencyFuelPremium, and the review says so.</t>
+        </is>
+      </c>
+      <c r="D67" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="13" t="inlineStr">
+        <is>
+          <t>emergencyFuelPremium</t>
+        </is>
+      </c>
+      <c r="B68" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C68" s="13" t="inlineStr">
+        <is>
+          <t>Pence per litre added to emergency fuel (£0.10).</t>
+        </is>
+      </c>
+      <c r="D68" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="13" t="inlineStr">
+        <is>
+          <t>fuelForecastFromWeek</t>
+        </is>
+      </c>
+      <c r="B69" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C69" s="13" t="inlineStr">
+        <is>
+          <t>From week 2 the fuel desk shows next week's forecast range and headline (Market forecastLow, forecastHigh, fuelHeadline).</t>
+        </is>
+      </c>
+      <c r="D69" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="13" t="inlineStr">
+        <is>
+          <t>fuelHandSum</t>
+        </is>
+      </c>
+      <c r="B70" s="13" t="inlineStr">
+        <is>
+          <t>per service on the aircraft performance card</t>
+        </is>
+      </c>
+      <c r="C70" s="13" t="inlineStr">
+        <is>
+          <t>D60: litres × price per litre is asked on the performance card the first time a plane flies a route, and again when the price it is valued at has moved 50p or more. Purchases on the desk are 1,000 L blocks: cost of 1,000 L × number of blocks.</t>
+        </is>
+      </c>
+      <c r="D70" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="13" t="inlineStr">
+        <is>
+          <t>planningSpreadsheetFromDay</t>
+        </is>
+      </c>
+      <c r="B71" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="C71" s="13" t="inlineStr">
+        <is>
+          <t>D58: the planning spreadsheet opens in week 2 as the modelling tool and the Build stage (the pupil writes formulas by clicking cells).</t>
+        </is>
+      </c>
+      <c r="D71" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="13" t="inlineStr">
+        <is>
+          <t>worldReport</t>
+        </is>
+      </c>
+      <c r="B72" s="13" t="inlineStr">
+        <is>
+          <t>Monday plan page</t>
+        </is>
+      </c>
+      <c r="C72" s="13" t="inlineStr">
+        <is>
+          <t>D56: fuel line graph, this week's and next week's fuel forecast, Red Kite's fares, one route's demand graph, this week's headlines and next week's announced news.</t>
+        </is>
+      </c>
+      <c r="D72" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="13" t="inlineStr">
+        <is>
+          <t>fuelWeek1</t>
+        </is>
+      </c>
+      <c r="B73" s="13" t="inlineStr">
+        <is>
+          <t>buy what the plan burns</t>
+        </is>
+      </c>
+      <c r="C73" s="13" t="inlineStr">
+        <is>
+          <t>D60: in week 1 there is no fuel desk. Each day the game buys exactly the litres the day's plan burns at that day's Calendar price (free on days 1–2). The only fuel maths is the per-service cost on the aircraft performance card.</t>
+        </is>
+      </c>
+      <c r="D73" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="13" t="inlineStr">
+        <is>
+          <t>fuelDeskFromDay</t>
+        </is>
+      </c>
+      <c r="B74" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="C74" s="13" t="inlineStr">
+        <is>
+          <t>D60: the Fuel procurement desk opens in week 2.</t>
+        </is>
+      </c>
+      <c r="D74" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="13" t="inlineStr">
+        <is>
+          <t>tankUpgradeDay</t>
+        </is>
+      </c>
+      <c r="B75" s="13" t="n">
+        <v>29</v>
+      </c>
+      <c r="C75" s="13" t="inlineStr">
+        <is>
+          <t>D60: storage grows to tankCapacityUpgraded on this day, announced as a storage upgrade.</t>
+        </is>
+      </c>
+      <c r="D75" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="13" t="inlineStr">
+        <is>
+          <t>tankCapacityUpgraded</t>
+        </is>
+      </c>
+      <c r="B76" s="13" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C76" s="13" t="inlineStr"/>
+      <c r="D76" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="13" t="inlineStr">
+        <is>
+          <t>fuelAdvantageWording</t>
+        </is>
+      </c>
+      <c r="B77" s="13" t="inlineStr">
+        <is>
+          <t>saved compared with buying later</t>
+        </is>
+      </c>
+      <c r="C77" s="13" t="inlineStr">
+        <is>
+          <t>D60: buying ahead is reported as 'Fuel purchasing advantage: +£X (saved compared with buying next week)' or '−£X', never as profit.</t>
+        </is>
+      </c>
+      <c r="D77" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="13" t="inlineStr">
+        <is>
+          <t>fuelCoverage</t>
+        </is>
+      </c>
+      <c r="B78" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="C78" s="13" t="inlineStr">
+        <is>
+          <t>D60: the desk shows this week's requirement (litres the standing plan burns), litres in storage, % covered, and litres still exposed to the market price.</t>
+        </is>
+      </c>
+      <c r="D78" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="13" t="inlineStr">
+        <is>
+          <t>forecastConfidenceLevels</t>
+        </is>
+      </c>
+      <c r="B79" s="13" t="inlineStr">
+        <is>
+          <t>high | medium | low</t>
+        </is>
+      </c>
+      <c r="C79" s="13" t="inlineStr">
+        <is>
+          <t>D60: Market forecastConfidence; low-confidence weeks have a wider range and may carry a second, conflicting signal (fuelHeadline2). The actual price always lies inside the range (no randomness).</t>
+        </is>
+      </c>
+      <c r="D79" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="23" t="inlineStr">
         <is>
           <t>blockedFlightCodes</t>
         </is>
       </c>
-      <c r="B64" s="23" t="inlineStr">
+      <c r="B80" s="23" t="inlineStr">
         <is>
           <t>BA, EZ, FR, VS, LH, AF, KL, U2</t>
         </is>
       </c>
-      <c r="C64" s="23" t="inlineStr">
+      <c r="C80" s="23" t="inlineStr">
         <is>
           <t>CR5. Real airline codes the pupil cannot pick; refused calmly ("That code belongs to a real airline, try another").</t>
         </is>
       </c>
-      <c r="D64" s="23" t="inlineStr">
+      <c r="D80" s="23" t="inlineStr">
         <is>
           <t>live</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="23" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="23" t="inlineStr">
         <is>
           <t>soundDefault</t>
         </is>
       </c>
-      <c r="B65" s="23" t="inlineStr">
+      <c r="B81" s="23" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="C65" s="23" t="inlineStr">
+      <c r="C81" s="23" t="inlineStr">
         <is>
           <t>CR5. Sound (take-off, airport chimes, announcements) is off until the teacher turns it on; a mute control sits in the top bar.</t>
         </is>
       </c>
-      <c r="D65" s="23" t="inlineStr">
+      <c r="D81" s="23" t="inlineStr">
         <is>
           <t>live</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="23" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="23" t="inlineStr">
         <is>
           <t>revealSeconds</t>
         </is>
       </c>
-      <c r="B66" s="23" t="n">
+      <c r="B82" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="C66" s="23" t="inlineStr">
+      <c r="C82" s="23" t="inlineStr">
         <is>
           <t>CR5. The hangar reveal on launch day: doors close, open, the plane rolls in. Later planes get about half.</t>
         </is>
       </c>
-      <c r="D66" s="23" t="inlineStr">
+      <c r="D82" s="23" t="inlineStr">
         <is>
           <t>live</t>
         </is>
@@ -26435,7 +29307,858 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="20" t="inlineStr">
+        <is>
+          <t>newsId</t>
+        </is>
+      </c>
+      <c r="B1" s="20" t="inlineStr">
+        <is>
+          <t>announceDate</t>
+        </is>
+      </c>
+      <c r="C1" s="20" t="inlineStr">
+        <is>
+          <t>startDate</t>
+        </is>
+      </c>
+      <c r="D1" s="20" t="inlineStr">
+        <is>
+          <t>endDate</t>
+        </is>
+      </c>
+      <c r="E1" s="20" t="inlineStr">
+        <is>
+          <t>kind</t>
+        </is>
+      </c>
+      <c r="F1" s="20" t="inlineStr">
+        <is>
+          <t>routes</t>
+        </is>
+      </c>
+      <c r="G1" s="20" t="inlineStr">
+        <is>
+          <t>demandMultiplier</t>
+        </is>
+      </c>
+      <c r="H1" s="20" t="inlineStr">
+        <is>
+          <t>segment</t>
+        </is>
+      </c>
+      <c r="I1" s="20" t="inlineStr">
+        <is>
+          <t>announced</t>
+        </is>
+      </c>
+      <c r="J1" s="20" t="inlineStr">
+        <is>
+          <t>headline</t>
+        </is>
+      </c>
+      <c r="K1" s="20" t="inlineStr">
+        <is>
+          <t>goodResponse</t>
+        </is>
+      </c>
+      <c r="L1" s="20" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>dub_rugby</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>2030-09-23</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="inlineStr">
+        <is>
+          <t>2030-10-05</t>
+        </is>
+      </c>
+      <c r="D2" s="13" t="inlineStr">
+        <is>
+          <t>2030-10-06</t>
+        </is>
+      </c>
+      <c r="E2" s="13" t="inlineStr">
+        <is>
+          <t>sport</t>
+        </is>
+      </c>
+      <c r="F2" s="13" t="inlineStr">
+        <is>
+          <t>dub</t>
+        </is>
+      </c>
+      <c r="G2" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" s="13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I2" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J2" s="13" t="inlineStr">
+        <is>
+          <t>Ireland play the All Blacks in Dublin on Saturday 5 October: every flight to Dublin that weekend is wanted.</t>
+        </is>
+      </c>
+      <c r="K2" s="13" t="inlineStr">
+        <is>
+          <t>Raise the Dublin fare for the weekend, and put the bigger plane on Dublin.</t>
+        </is>
+      </c>
+      <c r="L2" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>par_atc_strike</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>2030-10-01</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>2030-10-08</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>2030-10-10</t>
+        </is>
+      </c>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>political</t>
+        </is>
+      </c>
+      <c r="F3" s="13" t="inlineStr">
+        <is>
+          <t>par</t>
+        </is>
+      </c>
+      <c r="G3" s="13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I3" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J3" s="13" t="inlineStr">
+        <is>
+          <t>French air-traffic controllers will strike from Tuesday 8 to Thursday 10 October. Few people will try to fly to Paris.</t>
+        </is>
+      </c>
+      <c r="K3" s="13" t="inlineStr">
+        <is>
+          <t>Move the Paris plane to another route for three days (Dublin alone earns about £630 a day; the mixed day loses about £500).</t>
+        </is>
+      </c>
+      <c r="L3" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>mad_tech_week</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>2030-10-07</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>2030-10-14</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>2030-10-18</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>economic</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>mad</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t>business</t>
+        </is>
+      </c>
+      <c r="I4" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4" s="13" t="inlineStr">
+        <is>
+          <t>A big technology conference fills Madrid's hotels from 14 to 18 October.</t>
+        </is>
+      </c>
+      <c r="K4" s="13" t="inlineStr">
+        <is>
+          <t>Keep Madrid flying and hold the fare — a cushion in fuel-spike week.</t>
+        </is>
+      </c>
+      <c r="L4" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>bcn_hotel_bug</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>2030-10-22</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>2030-10-22</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>2030-10-25</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>bcn</t>
+        </is>
+      </c>
+      <c r="G5" s="13" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H5" s="13" t="inlineStr">
+        <is>
+          <t>leisure</t>
+        </is>
+      </c>
+      <c r="I5" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" s="13" t="inlineStr">
+        <is>
+          <t>A stomach bug closes two big Barcelona hotels; holidaymakers are cancelling.</t>
+        </is>
+      </c>
+      <c r="K5" s="13" t="inlineStr">
+        <is>
+          <t>None possible in advance: explains the dip in the review.</t>
+        </is>
+      </c>
+      <c r="L5" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>mxp_trade_fair</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>2030-10-21</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>2030-10-28</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>2030-11-01</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>economic</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>mxp</t>
+        </is>
+      </c>
+      <c r="G6" s="13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H6" s="13" t="inlineStr">
+        <is>
+          <t>business</t>
+        </is>
+      </c>
+      <c r="I6" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6" s="13" t="inlineStr">
+        <is>
+          <t>Milan's furniture trade fair runs from 28 October to 1 November.</t>
+        </is>
+      </c>
+      <c r="K6" s="13" t="inlineStr">
+        <is>
+          <t>Add a Milan service or move the Saab there for the week.</t>
+        </is>
+      </c>
+      <c r="L6" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>de_slowdown</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>2030-10-28</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>2030-11-04</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>2030-11-29</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>economic</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>fra,ber</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H7" s="13" t="inlineStr">
+        <is>
+          <t>business</t>
+        </is>
+      </c>
+      <c r="I7" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" s="13" t="inlineStr">
+        <is>
+          <t>Germany's economy is slowing: businesses are cutting travel through November.</t>
+        </is>
+      </c>
+      <c r="K7" s="13" t="inlineStr">
+        <is>
+          <t>Fly Frankfurt and Berlin less often, or move a plane to a growing route.</t>
+        </is>
+      </c>
+      <c r="L7" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>rak_film_festival</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>2030-11-04</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>2030-11-11</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>2030-11-17</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>culture</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>rak</t>
+        </is>
+      </c>
+      <c r="G8" s="13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H8" s="13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I8" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" s="13" t="inlineStr">
+        <is>
+          <t>The Marrakech film festival runs from 11 to 17 November.</t>
+        </is>
+      </c>
+      <c r="K8" s="13" t="inlineStr">
+        <is>
+          <t>Raise the Marrakech fare: the E175 fills anyway.</t>
+        </is>
+      </c>
+      <c r="L8" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>ie_ferry_strike</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>2030-11-18</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>2030-11-18</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>2030-11-24</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>political</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>dub</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H9" s="13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I9" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" s="13" t="inlineStr">
+        <is>
+          <t>Irish ferry workers walk out without warning: people who would have sailed are flying.</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="inlineStr">
+        <is>
+          <t>None in advance; a pupil with spare seats on Dublin gains.</t>
+        </is>
+      </c>
+      <c r="L9" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>ist_visa_easier</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>2030-11-18</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>2030-11-25</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>2031-01-05</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>political</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>ist</t>
+        </is>
+      </c>
+      <c r="G10" s="13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H10" s="13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I10" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10" s="13" t="inlineStr">
+        <is>
+          <t>Turkey simplifies visas for British visitors from 25 November.</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="inlineStr">
+        <is>
+          <t>Istanbul is worth a bigger plane or a second service.</t>
+        </is>
+      </c>
+      <c r="L10" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>xmas_markets</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>2030-11-25</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>2030-12-02</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>2030-12-22</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>culture</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>bru,ber</t>
+        </is>
+      </c>
+      <c r="G11" s="13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H11" s="13" t="inlineStr">
+        <is>
+          <t>leisure</t>
+        </is>
+      </c>
+      <c r="I11" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J11" s="13" t="inlineStr">
+        <is>
+          <t>Christmas markets open in Brussels and Berlin from 2 December.</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="inlineStr">
+        <is>
+          <t>Berlin's slowdown is offset: keep it flying, consider a fare rise on Brussels.</t>
+        </is>
+      </c>
+      <c r="L11" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>iceland_tremors</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>2030-12-09</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>2030-12-09</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>2030-12-15</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>nature</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>rek</t>
+        </is>
+      </c>
+      <c r="G12" s="13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H12" s="13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I12" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" s="13" t="inlineStr">
+        <is>
+          <t>Earthquakes near Reykjavik: some visitors are staying away this week.</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="inlineStr">
+        <is>
+          <t>None in advance; explains the dip.</t>
+        </is>
+      </c>
+      <c r="L12" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>cai_museum</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>2030-12-09</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>2030-12-16</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>2031-01-12</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>culture</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>cai</t>
+        </is>
+      </c>
+      <c r="G13" s="13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H13" s="13" t="inlineStr">
+        <is>
+          <t>leisure</t>
+        </is>
+      </c>
+      <c r="I13" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J13" s="13" t="inlineStr">
+        <is>
+          <t>Cairo's new museum opens its doors on 16 December.</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="inlineStr">
+        <is>
+          <t>Cairo can take a bigger plane in winter; raise the fare.</t>
+        </is>
+      </c>
+      <c r="L13" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>be_rail_strike</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>2030-12-16</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>2030-12-23</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>2030-12-27</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>political</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <t>bru</t>
+        </is>
+      </c>
+      <c r="G14" s="13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H14" s="13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I14" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J14" s="13" t="inlineStr">
+        <is>
+          <t>Belgian rail workers strike over Christmas week: travellers to Brussels switch to flying.</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="inlineStr">
+        <is>
+          <t>Add a Brussels service for Christmas week.</t>
+        </is>
+      </c>
+      <c r="L14" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>D56. Engine rule: on each day between startDate and endDate, demand on each listed route (for the named segment: business, leisure or all) is multiplied by demandMultiplier, on top of seasons, weekends, growth and the neglect rule. Announced items appear on the World report from announceDate (the week before); surprises appear on their startDate and are named in the review as the reason for the gap between projected and actual. Ten announced, three surprises; eight good, five bad. Chapter 2's news is written with chapter 2.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -26957,7 +30680,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -28563,7 +32286,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -29827,1927 +33550,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:S21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="60" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
-    <col width="26" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="40" customWidth="1" min="18" max="18"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>tier</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>seats</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>speedKmh</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>rangeKm</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>fuelPer100Km</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>hourlyCost</t>
-        </is>
-      </c>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>dayCost</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="inlineStr">
-        <is>
-          <t>listPrice</t>
-        </is>
-      </c>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>launchDealPrice</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="inlineStr">
-        <is>
-          <t>shopFromDay</t>
-        </is>
-      </c>
-      <c r="M1" s="3" t="inlineStr">
-        <is>
-          <t>identity</t>
-        </is>
-      </c>
-      <c r="N1" s="24" t="inlineStr">
-        <is>
-          <t>artworkId</t>
-        </is>
-      </c>
-      <c r="O1" s="24" t="inlineStr">
-        <is>
-          <t>photoFile</t>
-        </is>
-      </c>
-      <c r="P1" s="24" t="inlineStr">
-        <is>
-          <t>photoCredit</t>
-        </is>
-      </c>
-      <c r="Q1" s="24" t="inlineStr">
-        <is>
-          <t>photoLicence</t>
-        </is>
-      </c>
-      <c r="R1" s="24" t="inlineStr">
-        <is>
-          <t>photoSource</t>
-        </is>
-      </c>
-      <c r="S1" s="3" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="12" t="inlineStr">
-        <is>
-          <t>dhc6</t>
-        </is>
-      </c>
-      <c r="B2" s="12" t="inlineStr">
-        <is>
-          <t>DHC-6 Twin Otter</t>
-        </is>
-      </c>
-      <c r="C2" s="12" t="inlineStr">
-        <is>
-          <t>starter</t>
-        </is>
-      </c>
-      <c r="D2" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="E2" s="12" t="n">
-        <v>300</v>
-      </c>
-      <c r="F2" s="12" t="n">
-        <v>1400</v>
-      </c>
-      <c r="G2" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="H2" s="12" t="n">
-        <v>150</v>
-      </c>
-      <c r="I2" s="12" t="n">
-        <v>900</v>
-      </c>
-      <c r="J2" s="12" t="n">
-        <v>12000</v>
-      </c>
-      <c r="K2" s="12" t="n">
-        <v>2500</v>
-      </c>
-      <c r="L2" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M2" s="12" t="inlineStr">
-        <is>
-          <t>Small, flexible, cheap. Fits any route. Slow on long legs.</t>
-        </is>
-      </c>
-      <c r="N2" s="23" t="inlineStr">
-        <is>
-          <t>dhc6</t>
-        </is>
-      </c>
-      <c r="O2" s="23" t="n"/>
-      <c r="P2" s="23" t="n"/>
-      <c r="Q2" s="23" t="n"/>
-      <c r="R2" s="23" t="n"/>
-      <c r="S2" s="12" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="12" t="inlineStr">
-        <is>
-          <t>saab340</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>Saab 340</t>
-        </is>
-      </c>
-      <c r="C3" s="12" t="inlineStr">
-        <is>
-          <t>regional</t>
-        </is>
-      </c>
-      <c r="D3" s="12" t="n">
-        <v>34</v>
-      </c>
-      <c r="E3" s="12" t="n">
-        <v>450</v>
-      </c>
-      <c r="F3" s="12" t="n">
-        <v>1700</v>
-      </c>
-      <c r="G3" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="H3" s="12" t="n">
-        <v>200</v>
-      </c>
-      <c r="I3" s="12" t="n">
-        <v>1200</v>
-      </c>
-      <c r="J3" s="12" t="n">
-        <v>22000</v>
-      </c>
-      <c r="K3" s="12" t="inlineStr"/>
-      <c r="L3" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="M3" s="12" t="inlineStr">
-        <is>
-          <t>More seats and faster: Dublin and Amsterdam fit it. Half-empty on Paris.</t>
-        </is>
-      </c>
-      <c r="N3" s="23" t="inlineStr">
-        <is>
-          <t>sf34</t>
-        </is>
-      </c>
-      <c r="O3" s="23" t="n"/>
-      <c r="P3" s="23" t="n"/>
-      <c r="Q3" s="23" t="n"/>
-      <c r="R3" s="23" t="n"/>
-      <c r="S3" s="12" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>atr72</t>
-        </is>
-      </c>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>ATR 72</t>
-        </is>
-      </c>
-      <c r="C4" s="12" t="inlineStr">
-        <is>
-          <t>regional</t>
-        </is>
-      </c>
-      <c r="D4" s="12" t="n">
-        <v>70</v>
-      </c>
-      <c r="E4" s="12" t="n">
-        <v>450</v>
-      </c>
-      <c r="F4" s="12" t="n">
-        <v>1500</v>
-      </c>
-      <c r="G4" s="12" t="n">
-        <v>40</v>
-      </c>
-      <c r="H4" s="12" t="n">
-        <v>350</v>
-      </c>
-      <c r="I4" s="12" t="n">
-        <v>1800</v>
-      </c>
-      <c r="J4" s="12" t="n">
-        <v>36000</v>
-      </c>
-      <c r="K4" s="12" t="inlineStr"/>
-      <c r="L4" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="M4" s="12" t="inlineStr">
-        <is>
-          <t>Biggest short-haul. Cheapest per seat. Only pays on busy routes; just reaches Madrid (1,350 of 1,500 km).</t>
-        </is>
-      </c>
-      <c r="N4" s="23" t="inlineStr">
-        <is>
-          <t>at72</t>
-        </is>
-      </c>
-      <c r="O4" s="23" t="n"/>
-      <c r="P4" s="23" t="n"/>
-      <c r="Q4" s="23" t="n"/>
-      <c r="R4" s="23" t="n"/>
-      <c r="S4" s="12" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>e190</t>
-        </is>
-      </c>
-      <c r="B5" s="12" t="inlineStr">
-        <is>
-          <t>Embraer E190</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>regional jet</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="n">
-        <v>100</v>
-      </c>
-      <c r="E5" s="12" t="n">
-        <v>900</v>
-      </c>
-      <c r="F5" s="12" t="n">
-        <v>4500</v>
-      </c>
-      <c r="G5" s="12" t="n">
-        <v>70</v>
-      </c>
-      <c r="H5" s="12" t="n">
-        <v>900</v>
-      </c>
-      <c r="I5" s="12" t="n">
-        <v>3500</v>
-      </c>
-      <c r="J5" s="12" t="n">
-        <v>70000</v>
-      </c>
-      <c r="K5" s="12" t="inlineStr"/>
-      <c r="L5" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="M5" s="12" t="inlineStr">
-        <is>
-          <t>First jet: speed and range. Opens every medium-haul route the ATR cannot reach. Tutorial price.</t>
-        </is>
-      </c>
-      <c r="N5" s="23" t="inlineStr">
-        <is>
-          <t>e190</t>
-        </is>
-      </c>
-      <c r="O5" s="23" t="n"/>
-      <c r="P5" s="23" t="n"/>
-      <c r="Q5" s="23" t="n"/>
-      <c r="R5" s="23" t="n"/>
-      <c r="S5" s="12" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>a220</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>Airbus A220</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>small mainline</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="n">
-        <v>130</v>
-      </c>
-      <c r="E6" s="12" t="n">
-        <v>900</v>
-      </c>
-      <c r="F6" s="12" t="n">
-        <v>6300</v>
-      </c>
-      <c r="G6" s="12" t="n">
-        <v>80</v>
-      </c>
-      <c r="H6" s="12" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I6" s="12" t="n">
-        <v>3000</v>
-      </c>
-      <c r="J6" s="12" t="n">
-        <v>300000</v>
-      </c>
-      <c r="K6" s="12" t="inlineStr"/>
-      <c r="L6" s="12" t="n">
-        <v>57</v>
-      </c>
-      <c r="M6" s="12" t="inlineStr">
-        <is>
-          <t>The first plane priced like a real jet. Leased or saved for.</t>
-        </is>
-      </c>
-      <c r="N6" s="23" t="inlineStr">
-        <is>
-          <t>narrowbody</t>
-        </is>
-      </c>
-      <c r="O6" s="23" t="n"/>
-      <c r="P6" s="23" t="n"/>
-      <c r="Q6" s="23" t="n"/>
-      <c r="R6" s="23" t="n"/>
-      <c r="S6" s="12" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>a320</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>Airbus A320</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>workhorse</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="n">
-        <v>150</v>
-      </c>
-      <c r="E7" s="12" t="n">
-        <v>900</v>
-      </c>
-      <c r="F7" s="12" t="n">
-        <v>6000</v>
-      </c>
-      <c r="G7" s="12" t="n">
-        <v>90</v>
-      </c>
-      <c r="H7" s="12" t="n">
-        <v>1300</v>
-      </c>
-      <c r="I7" s="12" t="n">
-        <v>3500</v>
-      </c>
-      <c r="J7" s="12" t="n">
-        <v>400000</v>
-      </c>
-      <c r="K7" s="12" t="inlineStr"/>
-      <c r="L7" s="12" t="n">
-        <v>57</v>
-      </c>
-      <c r="M7" s="12" t="inlineStr">
-        <is>
-          <t>The one he named ('an Airbus'). Rome, Athens, Istanbul.</t>
-        </is>
-      </c>
-      <c r="N7" s="23" t="inlineStr">
-        <is>
-          <t>narrowbody</t>
-        </is>
-      </c>
-      <c r="O7" s="23" t="n"/>
-      <c r="P7" s="23" t="n"/>
-      <c r="Q7" s="23" t="n"/>
-      <c r="R7" s="23" t="n"/>
-      <c r="S7" s="12" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>b737</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>Boeing 737</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>workhorse</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="n">
-        <v>150</v>
-      </c>
-      <c r="E8" s="12" t="n">
-        <v>900</v>
-      </c>
-      <c r="F8" s="12" t="n">
-        <v>6000</v>
-      </c>
-      <c r="G8" s="12" t="n">
-        <v>90</v>
-      </c>
-      <c r="H8" s="12" t="n">
-        <v>1300</v>
-      </c>
-      <c r="I8" s="12" t="n">
-        <v>3500</v>
-      </c>
-      <c r="J8" s="12" t="n">
-        <v>400000</v>
-      </c>
-      <c r="K8" s="12" t="inlineStr"/>
-      <c r="L8" s="12" t="n">
-        <v>57</v>
-      </c>
-      <c r="M8" s="12" t="inlineStr">
-        <is>
-          <t>Named by the pupil. Same numbers as the A320: the choice is taste, as in real life.</t>
-        </is>
-      </c>
-      <c r="N8" s="23" t="inlineStr">
-        <is>
-          <t>narrowbody</t>
-        </is>
-      </c>
-      <c r="O8" s="23" t="n"/>
-      <c r="P8" s="23" t="n"/>
-      <c r="Q8" s="23" t="n"/>
-      <c r="R8" s="23" t="n"/>
-      <c r="S8" s="12" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="15" t="inlineStr">
-        <is>
-          <t>b787</t>
-        </is>
-      </c>
-      <c r="B9" s="15" t="inlineStr">
-        <is>
-          <t>Boeing 787 Dreamliner</t>
-        </is>
-      </c>
-      <c r="C9" s="15" t="inlineStr">
-        <is>
-          <t>long-haul</t>
-        </is>
-      </c>
-      <c r="D9" s="15" t="n">
-        <v>250</v>
-      </c>
-      <c r="E9" s="15" t="n">
-        <v>900</v>
-      </c>
-      <c r="F9" s="15" t="n">
-        <v>14000</v>
-      </c>
-      <c r="G9" s="15" t="n">
-        <v>200</v>
-      </c>
-      <c r="H9" s="15" t="n">
-        <v>3000</v>
-      </c>
-      <c r="I9" s="15" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J9" s="15" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="K9" s="15" t="inlineStr"/>
-      <c r="L9" s="15" t="n">
-        <v>127</v>
-      </c>
-      <c r="M9" s="15" t="inlineStr">
-        <is>
-          <t>Named by the pupil. Opens long haul, January 2031, by lease; bought outright from chapter 3.</t>
-        </is>
-      </c>
-      <c r="N9" s="25" t="n"/>
-      <c r="O9" s="25" t="n"/>
-      <c r="P9" s="25" t="n"/>
-      <c r="Q9" s="25" t="n"/>
-      <c r="R9" s="25" t="n"/>
-      <c r="S9" s="15" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>a350</t>
-        </is>
-      </c>
-      <c r="B10" s="15" t="inlineStr">
-        <is>
-          <t>Airbus A350</t>
-        </is>
-      </c>
-      <c r="C10" s="15" t="inlineStr">
-        <is>
-          <t>long-haul</t>
-        </is>
-      </c>
-      <c r="D10" s="15" t="n">
-        <v>300</v>
-      </c>
-      <c r="E10" s="15" t="n">
-        <v>900</v>
-      </c>
-      <c r="F10" s="15" t="n">
-        <v>18000</v>
-      </c>
-      <c r="G10" s="15" t="n">
-        <v>220</v>
-      </c>
-      <c r="H10" s="15" t="n">
-        <v>3400</v>
-      </c>
-      <c r="I10" s="15" t="n">
-        <v>9000</v>
-      </c>
-      <c r="J10" s="15" t="n">
-        <v>15000000</v>
-      </c>
-      <c r="K10" s="15" t="inlineStr"/>
-      <c r="L10" s="15" t="n">
-        <v>366</v>
-      </c>
-      <c r="M10" s="15" t="inlineStr">
-        <is>
-          <t>Range for Sydney. Chapter 3.</t>
-        </is>
-      </c>
-      <c r="N10" s="25" t="n"/>
-      <c r="O10" s="25" t="n"/>
-      <c r="P10" s="25" t="n"/>
-      <c r="Q10" s="25" t="n"/>
-      <c r="R10" s="25" t="n"/>
-      <c r="S10" s="15" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>b747</t>
-        </is>
-      </c>
-      <c r="B11" s="15" t="inlineStr">
-        <is>
-          <t>Boeing 747</t>
-        </is>
-      </c>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>icon</t>
-        </is>
-      </c>
-      <c r="D11" s="15" t="n">
-        <v>400</v>
-      </c>
-      <c r="E11" s="15" t="n">
-        <v>900</v>
-      </c>
-      <c r="F11" s="15" t="n">
-        <v>13000</v>
-      </c>
-      <c r="G11" s="15" t="n">
-        <v>300</v>
-      </c>
-      <c r="H11" s="15" t="n">
-        <v>4500</v>
-      </c>
-      <c r="I11" s="15" t="n">
-        <v>12000</v>
-      </c>
-      <c r="J11" s="15" t="n">
-        <v>20000000</v>
-      </c>
-      <c r="K11" s="15" t="inlineStr"/>
-      <c r="L11" s="15" t="n">
-        <v>736</v>
-      </c>
-      <c r="M11" s="15" t="inlineStr">
-        <is>
-          <t>Named by the pupil. The Jumbo: roomy, thirsty. Chapter 4.</t>
-        </is>
-      </c>
-      <c r="N11" s="25" t="n"/>
-      <c r="O11" s="25" t="n"/>
-      <c r="P11" s="25" t="n"/>
-      <c r="Q11" s="25" t="n"/>
-      <c r="R11" s="25" t="n"/>
-      <c r="S11" s="15" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>a380</t>
-        </is>
-      </c>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>Airbus A380</t>
-        </is>
-      </c>
-      <c r="C12" s="15" t="inlineStr">
-        <is>
-          <t>icon</t>
-        </is>
-      </c>
-      <c r="D12" s="15" t="n">
-        <v>500</v>
-      </c>
-      <c r="E12" s="15" t="n">
-        <v>900</v>
-      </c>
-      <c r="F12" s="15" t="n">
-        <v>15000</v>
-      </c>
-      <c r="G12" s="15" t="n">
-        <v>360</v>
-      </c>
-      <c r="H12" s="15" t="n">
-        <v>5500</v>
-      </c>
-      <c r="I12" s="15" t="n">
-        <v>15000</v>
-      </c>
-      <c r="J12" s="15" t="n">
-        <v>30000000</v>
-      </c>
-      <c r="K12" s="15" t="inlineStr"/>
-      <c r="L12" s="15" t="n">
-        <v>736</v>
-      </c>
-      <c r="M12" s="15" t="inlineStr">
-        <is>
-          <t>'The ultimate plane.' Chapter 4's new idea: financed, not bought. Only fills on the busiest route with a strong reputation.</t>
-        </is>
-      </c>
-      <c r="N12" s="25" t="n"/>
-      <c r="O12" s="25" t="n"/>
-      <c r="P12" s="25" t="n"/>
-      <c r="Q12" s="25" t="n"/>
-      <c r="R12" s="25" t="n"/>
-      <c r="S12" s="15" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>concorde</t>
-        </is>
-      </c>
-      <c r="B13" s="19" t="inlineStr">
-        <is>
-          <t>Concorde</t>
-        </is>
-      </c>
-      <c r="C13" s="19" t="inlineStr">
-        <is>
-          <t>wildcard</t>
-        </is>
-      </c>
-      <c r="D13" s="19" t="n">
-        <v>100</v>
-      </c>
-      <c r="E13" s="19" t="n">
-        <v>2100</v>
-      </c>
-      <c r="F13" s="19" t="n">
-        <v>7000</v>
-      </c>
-      <c r="G13" s="19" t="n">
-        <v>500</v>
-      </c>
-      <c r="H13" s="19" t="n">
-        <v>6000</v>
-      </c>
-      <c r="I13" s="19" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J13" s="19" t="n">
-        <v>60000000</v>
-      </c>
-      <c r="K13" s="19" t="inlineStr"/>
-      <c r="L13" s="19" t="n">
-        <v>834</v>
-      </c>
-      <c r="M13" s="19" t="inlineStr">
-        <is>
-          <t>Removed 6 Oct (D41).</t>
-        </is>
-      </c>
-      <c r="N13" s="26" t="n"/>
-      <c r="O13" s="26" t="n"/>
-      <c r="P13" s="26" t="n"/>
-      <c r="Q13" s="26" t="n"/>
-      <c r="R13" s="26" t="n"/>
-      <c r="S13" s="19" t="inlineStr">
-        <is>
-          <t>removed</t>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" s="13" t="inlineStr">
-        <is>
-          <t>e175</t>
-        </is>
-      </c>
-      <c r="B15" s="13" t="inlineStr">
-        <is>
-          <t>Embraer E175</t>
-        </is>
-      </c>
-      <c r="C15" s="13" t="inlineStr">
-        <is>
-          <t>regional jet</t>
-        </is>
-      </c>
-      <c r="D15" s="13" t="n">
-        <v>80</v>
-      </c>
-      <c r="E15" s="13" t="n">
-        <v>900</v>
-      </c>
-      <c r="F15" s="13" t="n">
-        <v>3700</v>
-      </c>
-      <c r="G15" s="13" t="n">
-        <v>55</v>
-      </c>
-      <c r="H15" s="13" t="n">
-        <v>700</v>
-      </c>
-      <c r="I15" s="13" t="n">
-        <v>3000</v>
-      </c>
-      <c r="J15" s="13" t="n">
-        <v>50000</v>
-      </c>
-      <c r="K15" s="13" t="n"/>
-      <c r="L15" s="13" t="n">
-        <v>22</v>
-      </c>
-      <c r="M15" s="13" t="inlineStr">
-        <is>
-          <t>The smaller, cheaper first jet. Beats the E190 on smaller pools (Marrakech). Tutorial price.</t>
-        </is>
-      </c>
-      <c r="N15" s="23" t="inlineStr">
-        <is>
-          <t>e175</t>
-        </is>
-      </c>
-      <c r="O15" s="23" t="n"/>
-      <c r="P15" s="23" t="n"/>
-      <c r="Q15" s="23" t="n"/>
-      <c r="R15" s="23" t="n"/>
-      <c r="S15" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t>b757</t>
-        </is>
-      </c>
-      <c r="B16" s="14" t="inlineStr">
-        <is>
-          <t>Boeing 757</t>
-        </is>
-      </c>
-      <c r="C16" s="14" t="inlineStr">
-        <is>
-          <t>narrowbody long-range</t>
-        </is>
-      </c>
-      <c r="D16" s="14" t="n">
-        <v>200</v>
-      </c>
-      <c r="E16" s="14" t="n">
-        <v>900</v>
-      </c>
-      <c r="F16" s="14" t="n">
-        <v>7200</v>
-      </c>
-      <c r="G16" s="14" t="n">
-        <v>110</v>
-      </c>
-      <c r="H16" s="14" t="n">
-        <v>1600</v>
-      </c>
-      <c r="I16" s="14" t="n">
-        <v>4200</v>
-      </c>
-      <c r="J16" s="14" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="K16" s="14" t="n"/>
-      <c r="L16" s="14" t="n">
-        <v>127</v>
-      </c>
-      <c r="M16" s="14" t="inlineStr">
-        <is>
-          <t>Long and narrow with big engines: reaches New York with fewer seats than a widebody. The cheap way into long haul. Chapter 2, by lease.</t>
-        </is>
-      </c>
-      <c r="N16" s="27" t="n"/>
-      <c r="O16" s="27" t="n"/>
-      <c r="P16" s="27" t="n"/>
-      <c r="Q16" s="27" t="n"/>
-      <c r="R16" s="27" t="n"/>
-      <c r="S16" s="14" t="inlineStr">
-        <is>
-          <t>placeholder</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="18" t="inlineStr">
-        <is>
-          <t>a340</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>Airbus A340</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>four-engined long-haul</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="n">
-        <v>280</v>
-      </c>
-      <c r="E17" s="18" t="n">
-        <v>900</v>
-      </c>
-      <c r="F17" s="18" t="n">
-        <v>13500</v>
-      </c>
-      <c r="G17" s="18" t="n">
-        <v>260</v>
-      </c>
-      <c r="H17" s="18" t="n">
-        <v>3600</v>
-      </c>
-      <c r="I17" s="18" t="n">
-        <v>8500</v>
-      </c>
-      <c r="J17" s="18" t="n">
-        <v>8000000</v>
-      </c>
-      <c r="K17" s="18" t="n"/>
-      <c r="L17" s="18" t="n">
-        <v>366</v>
-      </c>
-      <c r="M17" s="18" t="inlineStr">
-        <is>
-          <t>Four engines make it thirsty for its size; a bargain when fuel is cheap, a trap when it is dear. Chapter 3.</t>
-        </is>
-      </c>
-      <c r="N17" s="25" t="n"/>
-      <c r="O17" s="25" t="n"/>
-      <c r="P17" s="25" t="n"/>
-      <c r="Q17" s="25" t="n"/>
-      <c r="R17" s="25" t="n"/>
-      <c r="S17" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="18" t="inlineStr">
-        <is>
-          <t>b777</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>Boeing 777</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>long-haul</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="n">
-        <v>350</v>
-      </c>
-      <c r="E18" s="18" t="n">
-        <v>900</v>
-      </c>
-      <c r="F18" s="18" t="n">
-        <v>14000</v>
-      </c>
-      <c r="G18" s="18" t="n">
-        <v>250</v>
-      </c>
-      <c r="H18" s="18" t="n">
-        <v>4000</v>
-      </c>
-      <c r="I18" s="18" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J18" s="18" t="n">
-        <v>12000000</v>
-      </c>
-      <c r="K18" s="18" t="n"/>
-      <c r="L18" s="18" t="n">
-        <v>366</v>
-      </c>
-      <c r="M18" s="18" t="inlineStr">
-        <is>
-          <t>The biggest twin: the long-haul workhorse. Chapter 3.</t>
-        </is>
-      </c>
-      <c r="N18" s="25" t="n"/>
-      <c r="O18" s="25" t="n"/>
-      <c r="P18" s="25" t="n"/>
-      <c r="Q18" s="25" t="n"/>
-      <c r="R18" s="25" t="n"/>
-      <c r="S18" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="17" t="inlineStr">
-        <is>
-          <t>Prices from the A220 up are tuned to the cash curve (F5, replacing D16's three-tenths rule): on the Steady path each plane is a few lessons of saving away when it is meant to arrive. Tutorial planes (Twin Otter to E190, E175) keep launch-deal prices. Real prices are on the plane card for interest only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>v4.3 draft (CR5): artworkId names the painted side-view drawing (narrowbody is a stand-in until the A220, A320 and 737 are drawn); photo* record the showroom photo: file name under src/opening/assets/photos, author, licence, source URL. Openly licensed only, plain or maker colours.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="60" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="21" t="inlineStr">
-        <is>
-          <t>aircraftId</t>
-        </is>
-      </c>
-      <c r="B1" s="21" t="inlineStr">
-        <is>
-          <t>cashPrice</t>
-        </is>
-      </c>
-      <c r="C1" s="21" t="inlineStr">
-        <is>
-          <t>leaseDaily</t>
-        </is>
-      </c>
-      <c r="D1" s="21" t="inlineStr">
-        <is>
-          <t>financeDeposit</t>
-        </is>
-      </c>
-      <c r="E1" s="21" t="inlineStr">
-        <is>
-          <t>financeWeeklyPayment</t>
-        </is>
-      </c>
-      <c r="F1" s="21" t="inlineStr">
-        <is>
-          <t>financeWeeks</t>
-        </is>
-      </c>
-      <c r="G1" s="21" t="inlineStr">
-        <is>
-          <t>financeTotalPaid</t>
-        </is>
-      </c>
-      <c r="H1" s="21" t="inlineStr">
-        <is>
-          <t>leaseFrom</t>
-        </is>
-      </c>
-      <c r="I1" s="21" t="inlineStr">
-        <is>
-          <t>buyFrom</t>
-        </is>
-      </c>
-      <c r="J1" s="21" t="inlineStr">
-        <is>
-          <t>financeFrom</t>
-        </is>
-      </c>
-      <c r="K1" s="21" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="L1" s="21" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="13" t="inlineStr">
-        <is>
-          <t>dhc6</t>
-        </is>
-      </c>
-      <c r="B2" s="13" t="n">
-        <v>12000</v>
-      </c>
-      <c r="C2" s="13" t="n">
-        <v>250</v>
-      </c>
-      <c r="D2" s="13" t="n">
-        <v>4000</v>
-      </c>
-      <c r="E2" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="F2" s="13" t="n">
-        <v>30</v>
-      </c>
-      <c r="G2" s="13" t="n">
-        <v>13000</v>
-      </c>
-      <c r="H2" s="13" t="inlineStr">
-        <is>
-          <t>day 8</t>
-        </is>
-      </c>
-      <c r="I2" s="13" t="inlineStr">
-        <is>
-          <t>day 8</t>
-        </is>
-      </c>
-      <c r="J2" s="13" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="K2" s="13" t="inlineStr">
-        <is>
-          <t>Second Twin Otter: rent £250 a day; 12,000 ÷ 250 = 48 days. Launch-deal finance £4,000 down, £300 a day for 30 days (£13,000).</t>
-        </is>
-      </c>
-      <c r="L2" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="13" t="inlineStr">
-        <is>
-          <t>saab340</t>
-        </is>
-      </c>
-      <c r="B3" s="13" t="n">
-        <v>22000</v>
-      </c>
-      <c r="C3" s="13" t="n">
-        <v>400</v>
-      </c>
-      <c r="D3" s="13" t="n">
-        <v>7000</v>
-      </c>
-      <c r="E3" s="13" t="n">
-        <v>500</v>
-      </c>
-      <c r="F3" s="13" t="n">
-        <v>32</v>
-      </c>
-      <c r="G3" s="13" t="n">
-        <v>23000</v>
-      </c>
-      <c r="H3" s="13" t="inlineStr">
-        <is>
-          <t>day 8</t>
-        </is>
-      </c>
-      <c r="I3" s="13" t="inlineStr">
-        <is>
-          <t>day 8</t>
-        </is>
-      </c>
-      <c r="J3" s="13" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="K3" s="13" t="inlineStr">
-        <is>
-          <t>The week-2 sum: 22,000 ÷ 400 = 55 days. Launch-deal finance £7,000 down, £500 a day for 32 days (£23,000). Buy greyed out until cash ≥ price + reserve.</t>
-        </is>
-      </c>
-      <c r="L3" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>atr72</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="n">
-        <v>36000</v>
-      </c>
-      <c r="C4" s="13" t="n">
-        <v>650</v>
-      </c>
-      <c r="D4" s="13" t="n">
-        <v>11000</v>
-      </c>
-      <c r="E4" s="13" t="n">
-        <v>800</v>
-      </c>
-      <c r="F4" s="13" t="n">
-        <v>35</v>
-      </c>
-      <c r="G4" s="13" t="n">
-        <v>39000</v>
-      </c>
-      <c r="H4" s="13" t="inlineStr">
-        <is>
-          <t>day 8</t>
-        </is>
-      </c>
-      <c r="I4" s="13" t="inlineStr">
-        <is>
-          <t>day 8</t>
-        </is>
-      </c>
-      <c r="J4" s="13" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="K4" s="13" t="inlineStr">
-        <is>
-          <t>36,000 ÷ 650 ≈ 55 days. Finance £11,000 down, £800 a day for 35 days (£39,000).</t>
-        </is>
-      </c>
-      <c r="L4" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>e175</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="n">
-        <v>50000</v>
-      </c>
-      <c r="C5" s="13" t="n">
-        <v>900</v>
-      </c>
-      <c r="D5" s="13" t="n">
-        <v>15000</v>
-      </c>
-      <c r="E5" s="13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F5" s="13" t="n">
-        <v>38</v>
-      </c>
-      <c r="G5" s="13" t="n">
-        <v>53000</v>
-      </c>
-      <c r="H5" s="13" t="inlineStr">
-        <is>
-          <t>day 22</t>
-        </is>
-      </c>
-      <c r="I5" s="13" t="inlineStr">
-        <is>
-          <t>day 22</t>
-        </is>
-      </c>
-      <c r="J5" s="13" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="K5" s="13" t="inlineStr">
-        <is>
-          <t>50,000 ÷ 900 ≈ 56 days. Finance £15,000 down, £1,000 a day for 38 days (£53,000).</t>
-        </is>
-      </c>
-      <c r="L5" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>e190</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="n">
-        <v>70000</v>
-      </c>
-      <c r="C6" s="13" t="n">
-        <v>1200</v>
-      </c>
-      <c r="D6" s="13" t="n">
-        <v>21000</v>
-      </c>
-      <c r="E6" s="13" t="n">
-        <v>1500</v>
-      </c>
-      <c r="F6" s="13" t="n">
-        <v>36</v>
-      </c>
-      <c r="G6" s="13" t="n">
-        <v>75000</v>
-      </c>
-      <c r="H6" s="13" t="inlineStr">
-        <is>
-          <t>day 22</t>
-        </is>
-      </c>
-      <c r="I6" s="13" t="inlineStr">
-        <is>
-          <t>day 22</t>
-        </is>
-      </c>
-      <c r="J6" s="13" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="K6" s="13" t="inlineStr">
-        <is>
-          <t>70,000 ÷ 1,200 ≈ 58 days. Finance £21,000 down, £1,500 a day for 36 days (£75,000).</t>
-        </is>
-      </c>
-      <c r="L6" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>a220</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="n">
-        <v>300000</v>
-      </c>
-      <c r="C7" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="D7" s="13" t="n">
-        <v>90000</v>
-      </c>
-      <c r="E7" s="13" t="n">
-        <v>4000</v>
-      </c>
-      <c r="F7" s="13" t="n">
-        <v>52</v>
-      </c>
-      <c r="G7" s="13" t="n">
-        <v>298000</v>
-      </c>
-      <c r="H7" s="13" t="inlineStr">
-        <is>
-          <t>2031-01-06</t>
-        </is>
-      </c>
-      <c r="I7" s="13" t="inlineStr">
-        <is>
-          <t>2031-09-02</t>
-        </is>
-      </c>
-      <c r="J7" s="13" t="inlineStr">
-        <is>
-          <t>2032-09-07</t>
-        </is>
-      </c>
-      <c r="K7" s="13" t="inlineStr">
-        <is>
-          <t>Rent = price ÷ 1,000. Finance = 30% deposit, balance over 52 weeks, rounded to £1,000.</t>
-        </is>
-      </c>
-      <c r="L7" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>a320</t>
-        </is>
-      </c>
-      <c r="B8" s="13" t="n">
-        <v>400000</v>
-      </c>
-      <c r="C8" s="13" t="n">
-        <v>400</v>
-      </c>
-      <c r="D8" s="13" t="n">
-        <v>120000</v>
-      </c>
-      <c r="E8" s="13" t="n">
-        <v>5000</v>
-      </c>
-      <c r="F8" s="13" t="n">
-        <v>52</v>
-      </c>
-      <c r="G8" s="13" t="n">
-        <v>380000</v>
-      </c>
-      <c r="H8" s="13" t="inlineStr">
-        <is>
-          <t>2031-01-06</t>
-        </is>
-      </c>
-      <c r="I8" s="13" t="inlineStr">
-        <is>
-          <t>2031-09-02</t>
-        </is>
-      </c>
-      <c r="J8" s="13" t="inlineStr">
-        <is>
-          <t>2032-09-07</t>
-        </is>
-      </c>
-      <c r="K8" s="13" t="inlineStr"/>
-      <c r="L8" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>b737</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="n">
-        <v>400000</v>
-      </c>
-      <c r="C9" s="13" t="n">
-        <v>400</v>
-      </c>
-      <c r="D9" s="13" t="n">
-        <v>120000</v>
-      </c>
-      <c r="E9" s="13" t="n">
-        <v>5000</v>
-      </c>
-      <c r="F9" s="13" t="n">
-        <v>52</v>
-      </c>
-      <c r="G9" s="13" t="n">
-        <v>380000</v>
-      </c>
-      <c r="H9" s="13" t="inlineStr">
-        <is>
-          <t>2031-01-06</t>
-        </is>
-      </c>
-      <c r="I9" s="13" t="inlineStr">
-        <is>
-          <t>2031-09-02</t>
-        </is>
-      </c>
-      <c r="J9" s="13" t="inlineStr">
-        <is>
-          <t>2032-09-07</t>
-        </is>
-      </c>
-      <c r="K9" s="13" t="inlineStr"/>
-      <c r="L9" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="14" t="inlineStr">
-        <is>
-          <t>b757</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="C10" s="14" t="n">
-        <v>1500</v>
-      </c>
-      <c r="D10" s="14" t="n">
-        <v>450000</v>
-      </c>
-      <c r="E10" s="14" t="n">
-        <v>20000</v>
-      </c>
-      <c r="F10" s="14" t="n">
-        <v>52</v>
-      </c>
-      <c r="G10" s="14" t="n">
-        <v>1490000</v>
-      </c>
-      <c r="H10" s="14" t="inlineStr">
-        <is>
-          <t>2031-01-06</t>
-        </is>
-      </c>
-      <c r="I10" s="14" t="inlineStr">
-        <is>
-          <t>2031-09-02</t>
-        </is>
-      </c>
-      <c r="J10" s="14" t="inlineStr">
-        <is>
-          <t>2032-09-07</t>
-        </is>
-      </c>
-      <c r="K10" s="14" t="inlineStr">
-        <is>
-          <t>The cheap way into long haul by lease in chapter 2.</t>
-        </is>
-      </c>
-      <c r="L10" s="14" t="inlineStr">
-        <is>
-          <t>placeholder</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="18" t="inlineStr">
-        <is>
-          <t>b787</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="C11" s="18" t="n">
-        <v>6000</v>
-      </c>
-      <c r="D11" s="18" t="n">
-        <v>1800000</v>
-      </c>
-      <c r="E11" s="18" t="n">
-        <v>81000</v>
-      </c>
-      <c r="F11" s="18" t="n">
-        <v>52</v>
-      </c>
-      <c r="G11" s="18" t="n">
-        <v>6012000</v>
-      </c>
-      <c r="H11" s="18" t="inlineStr">
-        <is>
-          <t>2031-01-06</t>
-        </is>
-      </c>
-      <c r="I11" s="18" t="inlineStr">
-        <is>
-          <t>2031-09-02</t>
-        </is>
-      </c>
-      <c r="J11" s="18" t="inlineStr">
-        <is>
-          <t>2032-09-07</t>
-        </is>
-      </c>
-      <c r="K11" s="18" t="inlineStr">
-        <is>
-          <t>Leased Jan 2031; first big plane bought outright Sep 2031 on the Steady path. 6,000,000 ÷ 6,000 = 1,000 days.</t>
-        </is>
-      </c>
-      <c r="L11" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="18" t="inlineStr">
-        <is>
-          <t>a340</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="n">
-        <v>8000000</v>
-      </c>
-      <c r="C12" s="18" t="n">
-        <v>8000</v>
-      </c>
-      <c r="D12" s="18" t="n">
-        <v>2400000</v>
-      </c>
-      <c r="E12" s="18" t="n">
-        <v>108000</v>
-      </c>
-      <c r="F12" s="18" t="n">
-        <v>52</v>
-      </c>
-      <c r="G12" s="18" t="n">
-        <v>8016000</v>
-      </c>
-      <c r="H12" s="18" t="inlineStr">
-        <is>
-          <t>2031-09-02</t>
-        </is>
-      </c>
-      <c r="I12" s="18" t="inlineStr">
-        <is>
-          <t>2031-09-02</t>
-        </is>
-      </c>
-      <c r="J12" s="18" t="inlineStr">
-        <is>
-          <t>2032-09-07</t>
-        </is>
-      </c>
-      <c r="K12" s="18" t="inlineStr"/>
-      <c r="L12" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="18" t="inlineStr">
-        <is>
-          <t>b777</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="n">
-        <v>12000000</v>
-      </c>
-      <c r="C13" s="18" t="n">
-        <v>12000</v>
-      </c>
-      <c r="D13" s="18" t="n">
-        <v>3600000</v>
-      </c>
-      <c r="E13" s="18" t="n">
-        <v>162000</v>
-      </c>
-      <c r="F13" s="18" t="n">
-        <v>52</v>
-      </c>
-      <c r="G13" s="18" t="n">
-        <v>12024000</v>
-      </c>
-      <c r="H13" s="18" t="inlineStr">
-        <is>
-          <t>2031-09-02</t>
-        </is>
-      </c>
-      <c r="I13" s="18" t="inlineStr">
-        <is>
-          <t>2031-09-02</t>
-        </is>
-      </c>
-      <c r="J13" s="18" t="inlineStr">
-        <is>
-          <t>2032-09-07</t>
-        </is>
-      </c>
-      <c r="K13" s="18" t="inlineStr"/>
-      <c r="L13" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="18" t="inlineStr">
-        <is>
-          <t>a350</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="n">
-        <v>15000000</v>
-      </c>
-      <c r="C14" s="18" t="n">
-        <v>15000</v>
-      </c>
-      <c r="D14" s="18" t="n">
-        <v>4500000</v>
-      </c>
-      <c r="E14" s="18" t="n">
-        <v>202000</v>
-      </c>
-      <c r="F14" s="18" t="n">
-        <v>52</v>
-      </c>
-      <c r="G14" s="18" t="n">
-        <v>15004000</v>
-      </c>
-      <c r="H14" s="18" t="inlineStr">
-        <is>
-          <t>2031-09-02</t>
-        </is>
-      </c>
-      <c r="I14" s="18" t="inlineStr">
-        <is>
-          <t>2031-09-02</t>
-        </is>
-      </c>
-      <c r="J14" s="18" t="inlineStr">
-        <is>
-          <t>2032-09-07</t>
-        </is>
-      </c>
-      <c r="K14" s="18" t="inlineStr"/>
-      <c r="L14" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="18" t="inlineStr">
-        <is>
-          <t>b747</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="n">
-        <v>20000000</v>
-      </c>
-      <c r="C15" s="18" t="n">
-        <v>20000</v>
-      </c>
-      <c r="D15" s="18" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="E15" s="18" t="n">
-        <v>269000</v>
-      </c>
-      <c r="F15" s="18" t="n">
-        <v>52</v>
-      </c>
-      <c r="G15" s="18" t="n">
-        <v>19988000</v>
-      </c>
-      <c r="H15" s="18" t="inlineStr">
-        <is>
-          <t>2032-09-07</t>
-        </is>
-      </c>
-      <c r="I15" s="18" t="inlineStr">
-        <is>
-          <t>2032-09-07</t>
-        </is>
-      </c>
-      <c r="J15" s="18" t="inlineStr">
-        <is>
-          <t>2032-09-07</t>
-        </is>
-      </c>
-      <c r="K15" s="18" t="inlineStr"/>
-      <c r="L15" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="18" t="inlineStr">
-        <is>
-          <t>a380</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="n">
-        <v>30000000</v>
-      </c>
-      <c r="C16" s="18" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D16" s="18" t="n">
-        <v>9000000</v>
-      </c>
-      <c r="E16" s="18" t="n">
-        <v>404000</v>
-      </c>
-      <c r="F16" s="18" t="n">
-        <v>52</v>
-      </c>
-      <c r="G16" s="18" t="n">
-        <v>30008000</v>
-      </c>
-      <c r="H16" s="18" t="inlineStr">
-        <is>
-          <t>2032-09-07</t>
-        </is>
-      </c>
-      <c r="I16" s="18" t="inlineStr">
-        <is>
-          <t>2032-09-07</t>
-        </is>
-      </c>
-      <c r="J16" s="18" t="inlineStr">
-        <is>
-          <t>2032-09-07</t>
-        </is>
-      </c>
-      <c r="K16" s="18" t="inlineStr">
-        <is>
-          <t>Chapter 4's worked example: 30,000,000 − 9,000,000 = 21,000,000; ÷ 52 ≈ £404,000 a week; total paid £30.0m.</t>
-        </is>
-      </c>
-      <c r="L16" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="17" t="inlineStr">
-        <is>
-          <t>Note on the launch-deal rows: tutorial finance is in daily payments (as in the game today), because the opening is played by the day; from the A220 the payments are weekly, because chapter 4 is played by the month. 'When does renting cost more than buying?' = price ÷ leaseDaily: about 20–25 days for tutorial planes (launch deals), 1,000 days for every jet from the A220 up (F4).</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="17" t="inlineStr">
-        <is>
-          <t>Tutorial prices are 2½× v4.3 (D55): the second plane is rented or financed in week 2 and bought outright around week 4–5. The first Twin Otter is still the £2,500 launch deal. Rent-or-buy ≈ 55 days for every tutorial plane; 1,000 days for jets from the A220 up.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/data/Airline-World-Workbook.xlsx
+++ b/data/Airline-World-Workbook.xlsx
@@ -569,7 +569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:A21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -712,6 +712,13 @@
       <c r="A20" s="17" t="inlineStr">
         <is>
           <t>v4.6 (12 Oct): D60. Week 1 fuel bought automatically (no desk); Fuel procurement desk from day 8 with an 8,000 L tank growing to 20,000 L on day 29; Market weeks 2–17 fuel in odd pennies (£1.47, £1.68 …) with forecast ranges recomputed, forecastConfidence and a second conflicting signal in weeks 9, 12, 16; new WorkingMethods sheet (methods offered per relationship, by level). Design Note: The desks, v2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>v4.7 (12 Oct): D61 review totals and means are Build steps (show what to add, show the divisor); D62 second-aircraft comparison (Settings secondAircraftCompare, whereCouldItFly). Brief: Second aircraft and reviews.</t>
         </is>
       </c>
     </row>
@@ -27016,12 +27023,12 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>Totals at every review</t>
+          <t>Totals and means at every review: show what to do</t>
         </is>
       </c>
       <c r="C4" s="13" t="inlineStr">
         <is>
-          <t>At each chapter review the model shows the lines and the pupil adds them to total revenue, total costs and profit, and finds projected − actual.</t>
+          <t>D61: at each weekly and chapter review the pupil does not add the figures up. He shows what to add (selects the right figures and the operation, e.g. the seven daily profits joined with +), shows the order of a difference (actual − projected), and for a mean shows the divisor (total ÷ 7 for a day, ÷ number of weeks for a week). The game then calculates. This is the Build stage applied to totals and averages.</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr">
@@ -27346,7 +27353,7 @@
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>day profit × 7</t>
+          <t>week's total and the mean</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
@@ -27361,15 +27368,19 @@
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>seven-day strip, then efficient multiplication</t>
+          <t>show what to add (select the seven figures, +) | show the divisor (total ÷ 7)</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>£1,700 × 7</t>
-        </is>
-      </c>
-      <c r="F5" s="13" t="inlineStr"/>
+          <t>£1,709 + £1,709 + … ; total ÷ 7</t>
+        </is>
+      </c>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>D61: Build, not Calculate</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
@@ -27565,13 +27576,13 @@
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>period cards combined and shared</t>
+          <t>show the divisor (total ÷ number of periods)</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr"/>
       <c r="F12" s="13" t="inlineStr">
         <is>
-          <t>Chapter 2 onwards</t>
+          <t>Monthly reports from December; quarterly task later</t>
         </is>
       </c>
     </row>
@@ -27593,7 +27604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D82"/>
+  <dimension ref="A1:D86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -29239,64 +29250,150 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="23" t="inlineStr">
+      <c r="A80" s="13" t="inlineStr">
+        <is>
+          <t>reviewTotalsMode</t>
+        </is>
+      </c>
+      <c r="B80" s="13" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="C80" s="13" t="inlineStr">
+        <is>
+          <t>D61: totals, differences and means at reviews are Build steps (pupil selects figures, operation, order or divisor; the game calculates). Teacher can set Calculate per pupil.</t>
+        </is>
+      </c>
+      <c r="D80" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="13" t="inlineStr">
+        <is>
+          <t>meanFromDay</t>
+        </is>
+      </c>
+      <c r="B81" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="C81" s="13" t="inlineStr">
+        <is>
+          <t>D61: from the first weekly review, the review asks for the average profit a day (total ÷ number of days flown). Monthly reports from December ask for the average week (month total ÷ number of weeks).</t>
+        </is>
+      </c>
+      <c r="D81" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="13" t="inlineStr">
+        <is>
+          <t>secondAircraftCompare</t>
+        </is>
+      </c>
+      <c r="B82" s="13" t="inlineStr">
+        <is>
+          <t>choose plane, then how to pay</t>
+        </is>
+      </c>
+      <c r="C82" s="13" t="inlineStr">
+        <is>
+          <t>D62: the week-2 decision is two screens: compare the three aircraft side by side, then compare rent / finance / buy for the chosen one.</t>
+        </is>
+      </c>
+      <c r="D82" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="13" t="inlineStr">
+        <is>
+          <t>whereCouldItFly</t>
+        </is>
+      </c>
+      <c r="B83" s="13" t="inlineStr">
+        <is>
+          <t>today, week 3, week 4</t>
+        </is>
+      </c>
+      <c r="C83" s="13" t="inlineStr">
+        <is>
+          <t>D62: the comparison's what-if preview shows each plane's extra profit a day on today's routes, on the routes opening in week 3 (Amsterdam, Barcelona) and in week 4 (Madrid), plus a Dublin-demand tab.</t>
+        </is>
+      </c>
+      <c r="D83" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="23" t="inlineStr">
         <is>
           <t>blockedFlightCodes</t>
         </is>
       </c>
-      <c r="B80" s="23" t="inlineStr">
+      <c r="B84" s="23" t="inlineStr">
         <is>
           <t>BA, EZ, FR, VS, LH, AF, KL, U2</t>
         </is>
       </c>
-      <c r="C80" s="23" t="inlineStr">
+      <c r="C84" s="23" t="inlineStr">
         <is>
           <t>CR5. Real airline codes the pupil cannot pick; refused calmly ("That code belongs to a real airline, try another").</t>
         </is>
       </c>
-      <c r="D80" s="23" t="inlineStr">
+      <c r="D84" s="23" t="inlineStr">
         <is>
           <t>live</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="23" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="23" t="inlineStr">
         <is>
           <t>soundDefault</t>
         </is>
       </c>
-      <c r="B81" s="23" t="inlineStr">
+      <c r="B85" s="23" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="C81" s="23" t="inlineStr">
+      <c r="C85" s="23" t="inlineStr">
         <is>
           <t>CR5. Sound (take-off, airport chimes, announcements) is off until the teacher turns it on; a mute control sits in the top bar.</t>
         </is>
       </c>
-      <c r="D81" s="23" t="inlineStr">
+      <c r="D85" s="23" t="inlineStr">
         <is>
           <t>live</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="23" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="23" t="inlineStr">
         <is>
           <t>revealSeconds</t>
         </is>
       </c>
-      <c r="B82" s="23" t="n">
+      <c r="B86" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="C82" s="23" t="inlineStr">
+      <c r="C86" s="23" t="inlineStr">
         <is>
           <t>CR5. The hangar reveal on launch day: doors close, open, the plane rolls in. Later planes get about half.</t>
         </is>
       </c>
-      <c r="D82" s="23" t="inlineStr">
+      <c r="D86" s="23" t="inlineStr">
         <is>
           <t>live</t>
         </is>

--- a/data/Airline-World-Workbook.xlsx
+++ b/data/Airline-World-Workbook.xlsx
@@ -1,32 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Chapters" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="HandSumRules" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="WorkingMethods" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Settings" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="RouteNews" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Archetypes" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Routes" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="RouteCatalogue" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Aircraft" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Finance" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Airports" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Calendar" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Market" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Events" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Challenges" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Mechanics" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Catering" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Hunts" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Livery" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapters" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HandSumRules" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WorkingMethods" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RouteNews" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Archetypes" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Routes" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RouteCatalogue" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aircraft" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Finance" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Airports" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calendar" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Market" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Events" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Challenges" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mechanics" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catering" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hunts" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Livery" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -569,7 +569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:A22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -719,6 +719,13 @@
       <c r="A21" s="17" t="inlineStr">
         <is>
           <t>v4.7 (12 Oct): D61 review totals and means are Build steps (show what to add, show the divisor); D62 second-aircraft comparison (Settings secondAircraftCompare, whereCouldItFly). Brief: Second aircraft and reviews.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>v4.9 (13 Oct): base is Claude Code's installed v4.7 (with the CR5 Livery sheet, Aircraft artworkId/photo columns and blockedFlightCodes/soundDefault/revealSeconds), so no merge script is needed from here. Adds D63 cap of three Calculate sign-offs a week from week 2 with repetition decay (HandSumRules 9–10, Settings signOffCapPerWeek, signOffDecayAfter) and D64 the floor: a monthly audit, becoming a board review with three sign-offs and a required change when the plan has not changed all month (HandSumRules 11, Settings auditFloor, boardNudge*). Brief: Cap, decay and floor.</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1517,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
         <is>
@@ -1724,7 +1730,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="A20" s="17" t="inlineStr">
         <is>
@@ -26895,7 +26900,6 @@
         </is>
       </c>
     </row>
-    <row r="37"/>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
@@ -26914,7 +26918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -27197,8 +27201,99 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>A cap of three a week from week 2</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>At most signOffCapPerWeek Calculate sign-offs in a week; the most instructive first; the rest Build or Model; overflow carried to the next relevant week. Launch Day and review Build steps are outside the cap.</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>weekly, from day 8</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>week 3: 34 × £95, 675 ÷ 450 and the Saab's Amsterdam fuel; Frankfurt, Geneva and Barcelona tickets as Build</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Sums get lighter with repetition</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Calculate the first two times a relationship appears; Build for a new instance from the third time; Model when nothing is new.</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>relationship.count</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>tickets on a new route in week 4 is a Build (pick passengers, ×, fare), not a long multiplication</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>The floor: a monthly audit, and the board when nothing has changed</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>The world's penalties run all the time (missed profit, neglect, day costs, fuel, news). At each month end Finance sends one audit on the pupil's weakest line. If the plan has not changed all month, the audit becomes a board review: three sign-offs and a required change of plan before the next month runs.</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>month end; plan unchanged for 4 weeks</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>end of October: 'Finance: check the Geneva line before the accounts close'; a coasting pupil in November: 'The board wants to see a plan that tests a different fare or route'</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>Rough count: chapter 1 about 25 hand sums, chapter 2 about 8, chapter 3 about 6, chapter 4 about 6, chapter 5 about 5, chapter 6 about 4 — roughly 55 over the game, half of them × or ÷, excluding challenges and hunts. The teacher's Calculate / Build / Model setting overrides any rule (D34).</t>
         </is>
@@ -27604,7 +27699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D86"/>
+  <dimension ref="A1:D92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -29394,6 +29489,124 @@
         </is>
       </c>
       <c r="D86" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="13" t="inlineStr">
+        <is>
+          <t>signOffCapPerWeek</t>
+        </is>
+      </c>
+      <c r="B87" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C87" s="13" t="inlineStr">
+        <is>
+          <t>D63: from week 2, at most this many Calculate sign-offs in a week (teacher dial 1–3). Launch Day's sums and the review's Build steps are outside the cap. When more qualify, the game asks the most instructive first: a relationship never met, then a known relationship with a changed input (a fuel price jump), then the one with the most money in it; the rest are filled by the model with ƒ. A sum that misses the cap is carried to the next week it is relevant.</t>
+        </is>
+      </c>
+      <c r="D87" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="13" t="inlineStr">
+        <is>
+          <t>signOffDecayAfter</t>
+        </is>
+      </c>
+      <c r="B88" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C88" s="13" t="inlineStr">
+        <is>
+          <t>D63: a relationship is Calculate the first two times it appears; a new instance from the third time (tickets on a new route, fuel for a new plane) is Build; once nothing is new it is Model. The teacher can hold any relationship at Calculate.</t>
+        </is>
+      </c>
+      <c r="D88" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="13" t="inlineStr">
+        <is>
+          <t>auditFloor</t>
+        </is>
+      </c>
+      <c r="B89" s="13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C89" s="13" t="inlineStr">
+        <is>
+          <t>D64: at each month end Finance sends an audit — re-check one existing figure from the pupil's own airline, chosen as the route with the most missed profit. Falls on the last day of each month; from December it comes with the monthly report.</t>
+        </is>
+      </c>
+      <c r="D89" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="13" t="inlineStr">
+        <is>
+          <t>boardNudgeIdleWeeks</t>
+        </is>
+      </c>
+      <c r="B90" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C90" s="13" t="inlineStr">
+        <is>
+          <t>D64: if the standing plan has not changed for a month, the month-end audit becomes a board review: three sign-offs (re-check two lines and the month's average day) and the board asks for a plan that tests a different fare or route before the next month runs.</t>
+        </is>
+      </c>
+      <c r="D90" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="13" t="inlineStr">
+        <is>
+          <t>boardNudgeMissedShare</t>
+        </is>
+      </c>
+      <c r="B91" s="13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C91" s="13" t="inlineStr">
+        <is>
+          <t>Missed profit as a share of the best plan available, over the month.</t>
+        </is>
+      </c>
+      <c r="D91" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="13" t="inlineStr">
+        <is>
+          <t>boardReviewSignOffs</t>
+        </is>
+      </c>
+      <c r="B92" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C92" s="13" t="inlineStr"/>
+      <c r="D92" s="13" t="inlineStr">
         <is>
           <t>live</t>
         </is>

--- a/data/Airline-World-Workbook.xlsx
+++ b/data/Airline-World-Workbook.xlsx
@@ -12,21 +12,22 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HandSumRules" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WorkingMethods" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RouteNews" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Archetypes" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Routes" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RouteCatalogue" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aircraft" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Finance" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Airports" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calendar" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Market" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Events" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Challenges" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mechanics" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catering" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hunts" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Livery" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PlanTips" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RouteNews" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Archetypes" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Routes" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RouteCatalogue" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aircraft" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Finance" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Airports" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calendar" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Market" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Events" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Challenges" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mechanics" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catering" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hunts" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Livery" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -569,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A22"/>
+  <dimension ref="A1:A23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -729,12 +730,1285 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="17" t="inlineStr">
+        <is>
+          <t>v4.10 (13 Oct): D66 Operating Plan Studio data — seat-fill thresholds (Settings seatFillGood/Medium), per-route demand strip (demandStripMode), the four-step bar (planStudioSteps), and the PlanTips sheet (ten data-driven live tips). Data appendix: Operating Plan Studio.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="52" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>distanceKm</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>archetype</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>haul</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>baseFare (£60 + 8p/km)</t>
+        </is>
+      </c>
+      <c r="I1" s="16" t="inlineStr">
+        <is>
+          <t>leg hours TO 300 / Saab-ATR 450 / jet 900 km/h</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>plannedOpenWeek</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>bru</t>
+        </is>
+      </c>
+      <c r="B2" s="15" t="inlineStr">
+        <is>
+          <t>Brussels</t>
+        </is>
+      </c>
+      <c r="C2" s="15" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="D2" s="15" t="inlineStr">
+        <is>
+          <t>BRU</t>
+        </is>
+      </c>
+      <c r="E2" s="15" t="n">
+        <v>225</v>
+      </c>
+      <c r="F2" s="15" t="inlineStr">
+        <is>
+          <t>business_shuttle</t>
+        </is>
+      </c>
+      <c r="G2" s="15" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="H2" s="15" t="n">
+        <v>80</v>
+      </c>
+      <c r="I2" s="15" t="inlineStr">
+        <is>
+          <t>0.75 / 0.50 / 0.25</t>
+        </is>
+      </c>
+      <c r="J2" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="K2" s="15" t="inlineStr">
+        <is>
+          <t>Very short hop; business; fits a Twin Otter or Saab</t>
+        </is>
+      </c>
+      <c r="L2" s="15" t="inlineStr">
+        <is>
+          <t>moved to Routes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>edi</t>
+        </is>
+      </c>
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>Edinburgh</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>EDI</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="n">
+        <v>450</v>
+      </c>
+      <c r="F3" s="15" t="inlineStr">
+        <is>
+          <t>city_break_mixed</t>
+        </is>
+      </c>
+      <c r="G3" s="15" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="H3" s="15" t="n">
+        <v>100</v>
+      </c>
+      <c r="I3" s="15" t="inlineStr">
+        <is>
+          <t>1.50 / 1.00 / 0.50</t>
+        </is>
+      </c>
+      <c r="J3" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="K3" s="15" t="inlineStr">
+        <is>
+          <t>Domestic; mixed; 450 km keeps quarter-hours on every plane</t>
+        </is>
+      </c>
+      <c r="L3" s="15" t="inlineStr">
+        <is>
+          <t>moved to Routes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>ber</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>BER</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="n">
+        <v>900</v>
+      </c>
+      <c r="F4" s="15" t="inlineStr">
+        <is>
+          <t>city_break_mixed</t>
+        </is>
+      </c>
+      <c r="G4" s="15" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="H4" s="15" t="n">
+        <v>130</v>
+      </c>
+      <c r="I4" s="15" t="inlineStr">
+        <is>
+          <t>3.00 / 2.00 / 1.00</t>
+        </is>
+      </c>
+      <c r="J4" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="K4" s="15" t="inlineStr">
+        <is>
+          <t>City break; steady</t>
+        </is>
+      </c>
+      <c r="L4" s="15" t="inlineStr">
+        <is>
+          <t>moved to Routes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>mxp</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>MXP</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>900</v>
+      </c>
+      <c r="F5" s="15" t="inlineStr">
+        <is>
+          <t>business_shuttle</t>
+        </is>
+      </c>
+      <c r="G5" s="15" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="H5" s="15" t="n">
+        <v>130</v>
+      </c>
+      <c r="I5" s="15" t="inlineStr">
+        <is>
+          <t>3.00 / 2.00 / 1.00</t>
+        </is>
+      </c>
+      <c r="J5" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="K5" s="15" t="inlineStr">
+        <is>
+          <t>Business and fashion; evening peak</t>
+        </is>
+      </c>
+      <c r="L5" s="15" t="inlineStr">
+        <is>
+          <t>moved to Routes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>mad</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>MAD</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="n">
+        <v>1350</v>
+      </c>
+      <c r="F6" s="15" t="inlineStr">
+        <is>
+          <t>leisure_short</t>
+        </is>
+      </c>
+      <c r="G6" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H6" s="15" t="n">
+        <v>170</v>
+      </c>
+      <c r="I6" s="15" t="inlineStr">
+        <is>
+          <t>4.50 / 3.00 / 1.50</t>
+        </is>
+      </c>
+      <c r="J6" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="K6" s="15" t="inlineStr">
+        <is>
+          <t>First medium-haul route (ATR or jet); summer busy</t>
+        </is>
+      </c>
+      <c r="L6" s="15" t="inlineStr">
+        <is>
+          <t>moved to Routes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>fco</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>Rome</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>FCO</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>1575</v>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>leisure_short</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H7" s="15" t="n">
+        <v>190</v>
+      </c>
+      <c r="I7" s="15" t="inlineStr">
+        <is>
+          <t>5.25 / 3.50 / 1.75</t>
+        </is>
+      </c>
+      <c r="J7" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="K7" s="15" t="inlineStr">
+        <is>
+          <t>Leisure; spring and autumn peaks</t>
+        </is>
+      </c>
+      <c r="L7" s="15" t="inlineStr">
+        <is>
+          <t>moved to Routes</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>lis</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>LIS</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="n">
+        <v>1575</v>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>leisure_short</t>
+        </is>
+      </c>
+      <c r="G8" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H8" s="15" t="n">
+        <v>190</v>
+      </c>
+      <c r="I8" s="15" t="inlineStr">
+        <is>
+          <t>5.25 / 3.50 / 1.75</t>
+        </is>
+      </c>
+      <c r="J8" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="K8" s="15" t="inlineStr">
+        <is>
+          <t>Leisure; mild all year</t>
+        </is>
+      </c>
+      <c r="L8" s="15" t="inlineStr">
+        <is>
+          <t>moved to Routes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>rek</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>Reykjavik</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>KEF</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>1800</v>
+      </c>
+      <c r="F9" s="15" t="inlineStr">
+        <is>
+          <t>sun_holiday</t>
+        </is>
+      </c>
+      <c r="G9" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H9" s="15" t="n">
+        <v>200</v>
+      </c>
+      <c r="I9" s="15" t="inlineStr">
+        <is>
+          <t>6.00 / 4.00 / 2.00</t>
+        </is>
+      </c>
+      <c r="J9" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="K9" s="15" t="inlineStr">
+        <is>
+          <t>Winter northern lights; summer midnight sun; small pool</t>
+        </is>
+      </c>
+      <c r="L9" s="15" t="inlineStr">
+        <is>
+          <t>moved to Routes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>rak</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>Marrakech</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>Morocco</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>RAK</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>2250</v>
+      </c>
+      <c r="F10" s="15" t="inlineStr">
+        <is>
+          <t>sun_holiday</t>
+        </is>
+      </c>
+      <c r="G10" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H10" s="15" t="n">
+        <v>240</v>
+      </c>
+      <c r="I10" s="15" t="inlineStr">
+        <is>
+          <t>7.50 / 5.00 / 2.50</t>
+        </is>
+      </c>
+      <c r="J10" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="K10" s="15" t="inlineStr">
+        <is>
+          <t>Winter sun; strong Dec-Mar</t>
+        </is>
+      </c>
+      <c r="L10" s="15" t="inlineStr">
+        <is>
+          <t>moved to Routes</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>ath</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>Athens</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>ATH</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>2475</v>
+      </c>
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>leisure_short</t>
+        </is>
+      </c>
+      <c r="G11" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H11" s="15" t="n">
+        <v>260</v>
+      </c>
+      <c r="I11" s="15" t="inlineStr">
+        <is>
+          <t>8.25 / 5.50 / 2.75</t>
+        </is>
+      </c>
+      <c r="J11" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="K11" s="15" t="inlineStr">
+        <is>
+          <t>Summer sun; big pool</t>
+        </is>
+      </c>
+      <c r="L11" s="15" t="inlineStr">
+        <is>
+          <t>moved to Routes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>ist</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>Istanbul</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>IST</t>
+        </is>
+      </c>
+      <c r="E12" s="15" t="n">
+        <v>2475</v>
+      </c>
+      <c r="F12" s="15" t="inlineStr">
+        <is>
+          <t>long_haul_mixed</t>
+        </is>
+      </c>
+      <c r="G12" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H12" s="15" t="n">
+        <v>260</v>
+      </c>
+      <c r="I12" s="15" t="inlineStr">
+        <is>
+          <t>8.25 / 5.50 / 2.75</t>
+        </is>
+      </c>
+      <c r="J12" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="K12" s="15" t="inlineStr">
+        <is>
+          <t>Gateway; mixed</t>
+        </is>
+      </c>
+      <c r="L12" s="15" t="inlineStr">
+        <is>
+          <t>moved to Routes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>cai</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>Cairo</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>CAI</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="n">
+        <v>3600</v>
+      </c>
+      <c r="F13" s="15" t="inlineStr">
+        <is>
+          <t>sun_holiday</t>
+        </is>
+      </c>
+      <c r="G13" s="15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="H13" s="15" t="n">
+        <v>350</v>
+      </c>
+      <c r="I13" s="15" t="inlineStr">
+        <is>
+          <t>12.00 / 8.00 / 4.00</t>
+        </is>
+      </c>
+      <c r="J13" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="K13" s="15" t="inlineStr">
+        <is>
+          <t>Winter sun; pyramids; jet only</t>
+        </is>
+      </c>
+      <c r="L13" s="15" t="inlineStr">
+        <is>
+          <t>moved to Routes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>los</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>Lagos</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>LOS</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="n">
+        <v>4950</v>
+      </c>
+      <c r="F14" s="11" t="inlineStr">
+        <is>
+          <t>long_haul_mixed</t>
+        </is>
+      </c>
+      <c r="G14" s="11" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="H14" s="11" t="n">
+        <v>460</v>
+      </c>
+      <c r="I14" s="11" t="inlineStr">
+        <is>
+          <t>16.50 / 11.00 / 5.50</t>
+        </is>
+      </c>
+      <c r="J14" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="K14" s="11" t="inlineStr">
+        <is>
+          <t>Business travellers; steady</t>
+        </is>
+      </c>
+      <c r="L14" s="11" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>nyc</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>JFK</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>5625</v>
+      </c>
+      <c r="F15" s="15" t="inlineStr">
+        <is>
+          <t>long_haul_mixed</t>
+        </is>
+      </c>
+      <c r="G15" s="15" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="H15" s="15" t="n">
+        <v>510</v>
+      </c>
+      <c r="I15" s="15" t="inlineStr">
+        <is>
+          <t>18.75 / 12.50 / 6.25</t>
+        </is>
+      </c>
+      <c r="J15" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="K15" s="15" t="inlineStr">
+        <is>
+          <t>The big one; overnight return</t>
+        </is>
+      </c>
+      <c r="L15" s="15" t="inlineStr">
+        <is>
+          <t>moved to Routes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>yyz</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>Toronto</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>YYZ</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="n">
+        <v>5625</v>
+      </c>
+      <c r="F16" s="11" t="inlineStr">
+        <is>
+          <t>long_haul_mixed</t>
+        </is>
+      </c>
+      <c r="G16" s="11" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="H16" s="11" t="n">
+        <v>510</v>
+      </c>
+      <c r="I16" s="11" t="inlineStr">
+        <is>
+          <t>18.75 / 12.50 / 6.25</t>
+        </is>
+      </c>
+      <c r="J16" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="K16" s="11" t="inlineStr">
+        <is>
+          <t>Winter demand (families)</t>
+        </is>
+      </c>
+      <c r="L16" s="11" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>dxb</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>DXB</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="n">
+        <v>5400</v>
+      </c>
+      <c r="F17" s="15" t="inlineStr">
+        <is>
+          <t>long_haul_mixed</t>
+        </is>
+      </c>
+      <c r="G17" s="15" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="H17" s="15" t="n">
+        <v>490</v>
+      </c>
+      <c r="I17" s="15" t="inlineStr">
+        <is>
+          <t>18.00 / 12.00 / 6.00</t>
+        </is>
+      </c>
+      <c r="J17" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="K17" s="15" t="inlineStr">
+        <is>
+          <t>High fares; winter busy</t>
+        </is>
+      </c>
+      <c r="L17" s="15" t="inlineStr">
+        <is>
+          <t>moved to Routes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>del</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>DEL</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="n">
+        <v>6750</v>
+      </c>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>long_haul_mixed</t>
+        </is>
+      </c>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="H18" s="11" t="n">
+        <v>600</v>
+      </c>
+      <c r="I18" s="11" t="inlineStr">
+        <is>
+          <t>22.50 / 15.00 / 7.50</t>
+        </is>
+      </c>
+      <c r="J18" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="K18" s="11" t="inlineStr">
+        <is>
+          <t>Very busy; overnight</t>
+        </is>
+      </c>
+      <c r="L18" s="11" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>cpt</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>Cape Town</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>CPT</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="n">
+        <v>9675</v>
+      </c>
+      <c r="F19" s="11" t="inlineStr">
+        <is>
+          <t>sun_holiday</t>
+        </is>
+      </c>
+      <c r="G19" s="11" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="H19" s="11" t="n">
+        <v>830</v>
+      </c>
+      <c r="I19" s="11" t="inlineStr">
+        <is>
+          <t>32.25 / 21.50 / 10.75</t>
+        </is>
+      </c>
+      <c r="J19" s="11" t="n">
+        <v>54</v>
+      </c>
+      <c r="K19" s="11" t="inlineStr">
+        <is>
+          <t>UK winter = their summer; strong Dec-Feb</t>
+        </is>
+      </c>
+      <c r="L19" s="11" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>tyo</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>Tokyo</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>HND</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="n">
+        <v>9450</v>
+      </c>
+      <c r="F20" s="11" t="inlineStr">
+        <is>
+          <t>long_haul_mixed</t>
+        </is>
+      </c>
+      <c r="G20" s="11" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="H20" s="11" t="n">
+        <v>820</v>
+      </c>
+      <c r="I20" s="11" t="inlineStr">
+        <is>
+          <t>31.50 / 21.00 / 10.50</t>
+        </is>
+      </c>
+      <c r="J20" s="11" t="n">
+        <v>54</v>
+      </c>
+      <c r="K20" s="11" t="inlineStr">
+        <is>
+          <t>Huge demand; cherry blossom spike (event)</t>
+        </is>
+      </c>
+      <c r="L20" s="11" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>sin</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>SIN</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="n">
+        <v>10800</v>
+      </c>
+      <c r="F21" s="11" t="inlineStr">
+        <is>
+          <t>long_haul_mixed</t>
+        </is>
+      </c>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="H21" s="11" t="n">
+        <v>920</v>
+      </c>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>36.00 / 24.00 / 12.00</t>
+        </is>
+      </c>
+      <c r="J21" s="11" t="n">
+        <v>62</v>
+      </c>
+      <c r="K21" s="11" t="inlineStr">
+        <is>
+          <t>Gateway to Asia</t>
+        </is>
+      </c>
+      <c r="L21" s="11" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>syd</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>SYD</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="n">
+        <v>17100</v>
+      </c>
+      <c r="F22" s="11" t="inlineStr">
+        <is>
+          <t>long_haul_mixed</t>
+        </is>
+      </c>
+      <c r="G22" s="11" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="H22" s="11" t="n">
+        <v>1430</v>
+      </c>
+      <c r="I22" s="11" t="inlineStr">
+        <is>
+          <t>57.00 / 38.00 / 19.00</t>
+        </is>
+      </c>
+      <c r="J22" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="K22" s="11" t="inlineStr">
+        <is>
+          <t>Longest flight; A350 only; the final flex</t>
+        </is>
+      </c>
+      <c r="L22" s="11" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1742,7 +3016,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2572,7 +3846,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2880,7 +4154,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4657,7 +5931,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -22250,7 +23524,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -24094,7 +25368,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -24510,7 +25784,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -24928,7 +26202,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -25149,359 +26423,6 @@
       <c r="A7" s="17" t="inlineStr">
         <is>
           <t>Today's game values, moved into the workbook (F3). Extras for the Value airline (bag fee, seat fee, take-up) to be added here when chapter 2 is designed (D37).</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
-    <col width="36" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="21" t="inlineStr">
-        <is>
-          <t>huntId</t>
-        </is>
-      </c>
-      <c r="B1" s="21" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="C1" s="21" t="inlineStr">
-        <is>
-          <t>chapter</t>
-        </is>
-      </c>
-      <c r="D1" s="21" t="inlineStr">
-        <is>
-          <t>host</t>
-        </is>
-      </c>
-      <c r="E1" s="21" t="inlineStr">
-        <is>
-          <t>whatIsWrong</t>
-        </is>
-      </c>
-      <c r="F1" s="21" t="inlineStr">
-        <is>
-          <t>pupilChecks</t>
-        </is>
-      </c>
-      <c r="G1" s="21" t="inlineStr">
-        <is>
-          <t>consequenceIfMissed</t>
-        </is>
-      </c>
-      <c r="H1" s="21" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="14" t="inlineStr">
-        <is>
-          <t>h1</t>
-        </is>
-      </c>
-      <c r="B2" s="14" t="inlineStr">
-        <is>
-          <t>2031-08-31</t>
-        </is>
-      </c>
-      <c r="C2" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="D2" s="14" t="inlineStr">
-        <is>
-          <t>Year-1 accounts</t>
-        </is>
-      </c>
-      <c r="E2" s="14" t="inlineStr">
-        <is>
-          <t>One route's revenue total is £1,000 too high (a × with a slipped digit)</t>
-        </is>
-      </c>
-      <c r="F2" s="14" t="inlineStr">
-        <is>
-          <t>Re-multiply the route's passengers × fare and compare</t>
-        </is>
-      </c>
-      <c r="G2" s="14" t="inlineStr">
-        <is>
-          <t>The cash forecast for chapter 3 starts £1,000 out</t>
-        </is>
-      </c>
-      <c r="H2" s="14" t="inlineStr">
-        <is>
-          <t>placeholder</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="14" t="inlineStr">
-        <is>
-          <t>h2</t>
-        </is>
-      </c>
-      <c r="B3" s="14" t="inlineStr">
-        <is>
-          <t>2031-04-21</t>
-        </is>
-      </c>
-      <c r="C3" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>Fuel invoice</t>
-        </is>
-      </c>
-      <c r="E3" s="14" t="inlineStr">
-        <is>
-          <t>Litres × price does not match the total</t>
-        </is>
-      </c>
-      <c r="F3" s="14" t="inlineStr">
-        <is>
-          <t>Multiply litres by price</t>
-        </is>
-      </c>
-      <c r="G3" s="14" t="inlineStr">
-        <is>
-          <t>Overpaid; corrected next month if found later</t>
-        </is>
-      </c>
-      <c r="H3" s="14" t="inlineStr">
-        <is>
-          <t>placeholder</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="14" t="inlineStr">
-        <is>
-          <t>h3</t>
-        </is>
-      </c>
-      <c r="B4" s="14" t="inlineStr">
-        <is>
-          <t>2032-08-31</t>
-        </is>
-      </c>
-      <c r="C4" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="D4" s="14" t="inlineStr">
-        <is>
-          <t>Year-2 accounts</t>
-        </is>
-      </c>
-      <c r="E4" s="14" t="inlineStr">
-        <is>
-          <t>Total costs omit one month's lease</t>
-        </is>
-      </c>
-      <c r="F4" s="14" t="inlineStr">
-        <is>
-          <t>Add the monthly lines</t>
-        </is>
-      </c>
-      <c r="G4" s="14" t="inlineStr">
-        <is>
-          <t>Profit looks £180,000 too good</t>
-        </is>
-      </c>
-      <c r="H4" s="14" t="inlineStr">
-        <is>
-          <t>placeholder</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="14" t="inlineStr">
-        <is>
-          <t>h4</t>
-        </is>
-      </c>
-      <c r="B5" s="14" t="inlineStr">
-        <is>
-          <t>2032-02-10</t>
-        </is>
-      </c>
-      <c r="C5" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="D5" s="14" t="inlineStr">
-        <is>
-          <t>Departure board</t>
-        </is>
-      </c>
-      <c r="E5" s="14" t="inlineStr">
-        <is>
-          <t>A Tokyo arrival shown in the wrong zone (+9 h applied twice)</t>
-        </is>
-      </c>
-      <c r="F5" s="14" t="inlineStr">
-        <is>
-          <t>Add the flight time and the zone once</t>
-        </is>
-      </c>
-      <c r="G5" s="14" t="inlineStr">
-        <is>
-          <t>Passengers miss connections: −½ star</t>
-        </is>
-      </c>
-      <c r="H5" s="14" t="inlineStr">
-        <is>
-          <t>placeholder</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="14" t="inlineStr">
-        <is>
-          <t>h5</t>
-        </is>
-      </c>
-      <c r="B6" s="14" t="inlineStr">
-        <is>
-          <t>2033-08-31</t>
-        </is>
-      </c>
-      <c r="C6" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="D6" s="14" t="inlineStr">
-        <is>
-          <t>Finance statement</t>
-        </is>
-      </c>
-      <c r="E6" s="14" t="inlineStr">
-        <is>
-          <t>Weekly repayment × weeks does not reach the balance</t>
-        </is>
-      </c>
-      <c r="F6" s="14" t="inlineStr">
-        <is>
-          <t>(price − deposit) ÷ 52; compare</t>
-        </is>
-      </c>
-      <c r="G6" s="14" t="inlineStr">
-        <is>
-          <t>Repayments run a month longer</t>
-        </is>
-      </c>
-      <c r="H6" s="14" t="inlineStr">
-        <is>
-          <t>placeholder</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="14" t="inlineStr">
-        <is>
-          <t>h6</t>
-        </is>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>2034-08-31</t>
-        </is>
-      </c>
-      <c r="C7" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>Quarterly comparison</t>
-        </is>
-      </c>
-      <c r="E7" s="14" t="inlineStr">
-        <is>
-          <t>One quarter's average uses two months instead of three</t>
-        </is>
-      </c>
-      <c r="F7" s="14" t="inlineStr">
-        <is>
-          <t>Average of three months</t>
-        </is>
-      </c>
-      <c r="G7" s="14" t="inlineStr">
-        <is>
-          <t>Trend misread</t>
-        </is>
-      </c>
-      <c r="H7" s="14" t="inlineStr">
-        <is>
-          <t>placeholder</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="14" t="inlineStr">
-        <is>
-          <t>h7</t>
-        </is>
-      </c>
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t>2035-08-31</t>
-        </is>
-      </c>
-      <c r="C8" s="14" t="n">
-        <v>6</v>
-      </c>
-      <c r="D8" s="14" t="inlineStr">
-        <is>
-          <t>Five-year review</t>
-        </is>
-      </c>
-      <c r="E8" s="14" t="inlineStr">
-        <is>
-          <t>A graph's scale mislabelled (£k shown as £m)</t>
-        </is>
-      </c>
-      <c r="F8" s="14" t="inlineStr">
-        <is>
-          <t>Read the axis against the table</t>
-        </is>
-      </c>
-      <c r="G8" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H8" s="14" t="inlineStr">
-        <is>
-          <t>placeholder</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="17" t="inlineStr">
-        <is>
-          <t>D39: one hunt in every review from chapter 2, plus occasional hunts in the run (h2, h4). Hosts and errors are first drafts; each is written properly when its chapter is designed. Claude Code: a hunt is a document with one planted error; the pupil finds it (or not) and the consequence applies.</t>
         </is>
       </c>
     </row>
@@ -25949,6 +26870,359 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="21" t="inlineStr">
+        <is>
+          <t>huntId</t>
+        </is>
+      </c>
+      <c r="B1" s="21" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C1" s="21" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="D1" s="21" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="E1" s="21" t="inlineStr">
+        <is>
+          <t>whatIsWrong</t>
+        </is>
+      </c>
+      <c r="F1" s="21" t="inlineStr">
+        <is>
+          <t>pupilChecks</t>
+        </is>
+      </c>
+      <c r="G1" s="21" t="inlineStr">
+        <is>
+          <t>consequenceIfMissed</t>
+        </is>
+      </c>
+      <c r="H1" s="21" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>2031-08-31</t>
+        </is>
+      </c>
+      <c r="C2" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" s="14" t="inlineStr">
+        <is>
+          <t>Year-1 accounts</t>
+        </is>
+      </c>
+      <c r="E2" s="14" t="inlineStr">
+        <is>
+          <t>One route's revenue total is £1,000 too high (a × with a slipped digit)</t>
+        </is>
+      </c>
+      <c r="F2" s="14" t="inlineStr">
+        <is>
+          <t>Re-multiply the route's passengers × fare and compare</t>
+        </is>
+      </c>
+      <c r="G2" s="14" t="inlineStr">
+        <is>
+          <t>The cash forecast for chapter 3 starts £1,000 out</t>
+        </is>
+      </c>
+      <c r="H2" s="14" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>2031-04-21</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>Fuel invoice</t>
+        </is>
+      </c>
+      <c r="E3" s="14" t="inlineStr">
+        <is>
+          <t>Litres × price does not match the total</t>
+        </is>
+      </c>
+      <c r="F3" s="14" t="inlineStr">
+        <is>
+          <t>Multiply litres by price</t>
+        </is>
+      </c>
+      <c r="G3" s="14" t="inlineStr">
+        <is>
+          <t>Overpaid; corrected next month if found later</t>
+        </is>
+      </c>
+      <c r="H3" s="14" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>h3</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>2032-08-31</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>Year-2 accounts</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>Total costs omit one month's lease</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>Add the monthly lines</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>Profit looks £180,000 too good</t>
+        </is>
+      </c>
+      <c r="H4" s="14" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>h4</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>2032-02-10</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>Departure board</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>A Tokyo arrival shown in the wrong zone (+9 h applied twice)</t>
+        </is>
+      </c>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t>Add the flight time and the zone once</t>
+        </is>
+      </c>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>Passengers miss connections: −½ star</t>
+        </is>
+      </c>
+      <c r="H5" s="14" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>h5</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>2033-08-31</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>Finance statement</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>Weekly repayment × weeks does not reach the balance</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>(price − deposit) ÷ 52; compare</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>Repayments run a month longer</t>
+        </is>
+      </c>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>h6</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>2034-08-31</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>Quarterly comparison</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>One quarter's average uses two months instead of three</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>Average of three months</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>Trend misread</t>
+        </is>
+      </c>
+      <c r="H7" s="14" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>h7</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>2035-08-31</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>Five-year review</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>A graph's scale mislabelled (£k shown as £m)</t>
+        </is>
+      </c>
+      <c r="F8" s="14" t="inlineStr">
+        <is>
+          <t>Read the axis against the table</t>
+        </is>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H8" s="14" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>D39: one hunt in every review from chapter 2, plus occasional hunts in the run (h2, h4). Hosts and errors are first drafts; each is written properly when its chapter is designed. Claude Code: a hunt is a document with one planted error; the pupil finds it (or not) and the consequence applies.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -27291,7 +28565,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="17" t="inlineStr">
         <is>
@@ -27699,7 +28972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D92"/>
+  <dimension ref="A1:D96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -29612,12 +30885,453 @@
         </is>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" s="13" t="inlineStr">
+        <is>
+          <t>seatFillGood</t>
+        </is>
+      </c>
+      <c r="B93" s="13" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C93" s="13" t="inlineStr">
+        <is>
+          <t>D66: a service block is green at 80% of seats filled or more, amber from 50% to 79%, red under 50% (the neglect rule's line). Blocks show filled seats / seats on that plane.</t>
+        </is>
+      </c>
+      <c r="D93" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="13" t="inlineStr">
+        <is>
+          <t>seatFillMedium</t>
+        </is>
+      </c>
+      <c r="B94" s="13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C94" s="13" t="inlineStr"/>
+      <c r="D94" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="13" t="inlineStr">
+        <is>
+          <t>demandStripMode</t>
+        </is>
+      </c>
+      <c r="B95" s="13" t="inlineStr">
+        <is>
+          <t>selected route, else all routes</t>
+        </is>
+      </c>
+      <c r="C95" s="13" t="inlineStr">
+        <is>
+          <t>D66: the demand-through-the-day strip shows the selected or hovered route's own five bands (Archetypes shares); with nothing selected, the sum across open routes.</t>
+        </is>
+      </c>
+      <c r="D95" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="13" t="inlineStr">
+        <is>
+          <t>planStudioSteps</t>
+        </is>
+      </c>
+      <c r="B96" s="13" t="inlineStr">
+        <is>
+          <t>Choose routes | Set fares | Place services | Review seat fill</t>
+        </is>
+      </c>
+      <c r="C96" s="13" t="inlineStr">
+        <is>
+          <t>D66: the four-step bar on the Operating Plan Studio. Step 4's three figures (seats likely filled, empty seats, turned away) are the same three the Sunday review reports as actuals.</t>
+        </is>
+      </c>
+      <c r="D96" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="20" t="inlineStr">
+        <is>
+          <t>tipId</t>
+        </is>
+      </c>
+      <c r="B1" s="20" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="C1" s="20" t="inlineStr">
+        <is>
+          <t>threshold</t>
+        </is>
+      </c>
+      <c r="D1" s="20" t="inlineStr">
+        <is>
+          <t>message (route, band, numbers filled by the engine)</t>
+        </is>
+      </c>
+      <c r="E1" s="20" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="F1" s="20" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>peak_unserved</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>A day band holding ≥ threshold of a route's time-locked demand has no service on that route</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="D2" s="13" t="inlineStr">
+        <is>
+          <t>This timetable leaves the {band} {route} peak unserved — about {n} people want to fly then.</t>
+        </is>
+      </c>
+      <c r="E2" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>service_weak</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>A service is projected under seatFillMedium full</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>{band} {route} is weak: {empty} empty seats of {seats}. Try a later time or a lower fare.</t>
+        </is>
+      </c>
+      <c r="E3" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>turned_away</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Demand at the chosen fare exceeds seats offered on the route by more than one plane-load</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>1 plane</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>{route}: about {n} people a day won't get a seat. Add a service or raise the fare.</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>fare_too_high</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>At the chosen fare, demand falls below the seats offered on the route</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>At £{fare}, {route} no longer fills {services} services — {empty} seats would be empty.</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>fare_too_low</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>A lower fare was chosen but demand already exceeded seats at the higher fare</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>You cut the {route} fare to £{fare}, but the planes were already full: that is £{lost} a day less for the same passengers.</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>idle_plane</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>A plane has more than 4 hours of unused time inside airport hours</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>4 h</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>{plane} is idle for {hours} this afternoon. Another service would fit.</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>long_leg_warning</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>A service's flying time on this plane is over 3 hours each way</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>3 h</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>{route} is {hours} each way in a {plane} — slow planes lose a whole day's work to one trip.</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>range_fail</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>A route is dropped onto a plane without the range</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>{plane} can't reach {route} ({distance} km against {range} km range).</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>all_good</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>No other tip fires and projected fill ≥ seatFillGood on every service</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>Most seats are filling well. Try a different fare or time and see what changes.</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>general_tradeoff</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Default when the plan is empty or nothing else applies</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>Higher fares earn more per seat but fewer people fly. Timing matters: demand changes through the day.</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>D66: the Live seat fill panel shows at most two tips, lowest priority number first. Conditions are evaluated on the projected plan every time it changes; the same conditions feed the Sunday review's explanation of missed profit.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -30468,7 +32182,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -30990,7 +32704,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -32594,1270 +34308,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="52" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>country</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>code</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>distanceKm</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>archetype</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>haul</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>baseFare (£60 + 8p/km)</t>
-        </is>
-      </c>
-      <c r="I1" s="16" t="inlineStr">
-        <is>
-          <t>leg hours TO 300 / Saab-ATR 450 / jet 900 km/h</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="inlineStr">
-        <is>
-          <t>plannedOpenWeek</t>
-        </is>
-      </c>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="15" t="inlineStr">
-        <is>
-          <t>bru</t>
-        </is>
-      </c>
-      <c r="B2" s="15" t="inlineStr">
-        <is>
-          <t>Brussels</t>
-        </is>
-      </c>
-      <c r="C2" s="15" t="inlineStr">
-        <is>
-          <t>Belgium</t>
-        </is>
-      </c>
-      <c r="D2" s="15" t="inlineStr">
-        <is>
-          <t>BRU</t>
-        </is>
-      </c>
-      <c r="E2" s="15" t="n">
-        <v>225</v>
-      </c>
-      <c r="F2" s="15" t="inlineStr">
-        <is>
-          <t>business_shuttle</t>
-        </is>
-      </c>
-      <c r="G2" s="15" t="inlineStr">
-        <is>
-          <t>short</t>
-        </is>
-      </c>
-      <c r="H2" s="15" t="n">
-        <v>80</v>
-      </c>
-      <c r="I2" s="15" t="inlineStr">
-        <is>
-          <t>0.75 / 0.50 / 0.25</t>
-        </is>
-      </c>
-      <c r="J2" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="K2" s="15" t="inlineStr">
-        <is>
-          <t>Very short hop; business; fits a Twin Otter or Saab</t>
-        </is>
-      </c>
-      <c r="L2" s="15" t="inlineStr">
-        <is>
-          <t>moved to Routes</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="15" t="inlineStr">
-        <is>
-          <t>edi</t>
-        </is>
-      </c>
-      <c r="B3" s="15" t="inlineStr">
-        <is>
-          <t>Edinburgh</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>UK</t>
-        </is>
-      </c>
-      <c r="D3" s="15" t="inlineStr">
-        <is>
-          <t>EDI</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="n">
-        <v>450</v>
-      </c>
-      <c r="F3" s="15" t="inlineStr">
-        <is>
-          <t>city_break_mixed</t>
-        </is>
-      </c>
-      <c r="G3" s="15" t="inlineStr">
-        <is>
-          <t>short</t>
-        </is>
-      </c>
-      <c r="H3" s="15" t="n">
-        <v>100</v>
-      </c>
-      <c r="I3" s="15" t="inlineStr">
-        <is>
-          <t>1.50 / 1.00 / 0.50</t>
-        </is>
-      </c>
-      <c r="J3" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="K3" s="15" t="inlineStr">
-        <is>
-          <t>Domestic; mixed; 450 km keeps quarter-hours on every plane</t>
-        </is>
-      </c>
-      <c r="L3" s="15" t="inlineStr">
-        <is>
-          <t>moved to Routes</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="15" t="inlineStr">
-        <is>
-          <t>ber</t>
-        </is>
-      </c>
-      <c r="B4" s="15" t="inlineStr">
-        <is>
-          <t>Berlin</t>
-        </is>
-      </c>
-      <c r="C4" s="15" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="D4" s="15" t="inlineStr">
-        <is>
-          <t>BER</t>
-        </is>
-      </c>
-      <c r="E4" s="15" t="n">
-        <v>900</v>
-      </c>
-      <c r="F4" s="15" t="inlineStr">
-        <is>
-          <t>city_break_mixed</t>
-        </is>
-      </c>
-      <c r="G4" s="15" t="inlineStr">
-        <is>
-          <t>short</t>
-        </is>
-      </c>
-      <c r="H4" s="15" t="n">
-        <v>130</v>
-      </c>
-      <c r="I4" s="15" t="inlineStr">
-        <is>
-          <t>3.00 / 2.00 / 1.00</t>
-        </is>
-      </c>
-      <c r="J4" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="K4" s="15" t="inlineStr">
-        <is>
-          <t>City break; steady</t>
-        </is>
-      </c>
-      <c r="L4" s="15" t="inlineStr">
-        <is>
-          <t>moved to Routes</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="15" t="inlineStr">
-        <is>
-          <t>mxp</t>
-        </is>
-      </c>
-      <c r="B5" s="15" t="inlineStr">
-        <is>
-          <t>Milan</t>
-        </is>
-      </c>
-      <c r="C5" s="15" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="D5" s="15" t="inlineStr">
-        <is>
-          <t>MXP</t>
-        </is>
-      </c>
-      <c r="E5" s="15" t="n">
-        <v>900</v>
-      </c>
-      <c r="F5" s="15" t="inlineStr">
-        <is>
-          <t>business_shuttle</t>
-        </is>
-      </c>
-      <c r="G5" s="15" t="inlineStr">
-        <is>
-          <t>short</t>
-        </is>
-      </c>
-      <c r="H5" s="15" t="n">
-        <v>130</v>
-      </c>
-      <c r="I5" s="15" t="inlineStr">
-        <is>
-          <t>3.00 / 2.00 / 1.00</t>
-        </is>
-      </c>
-      <c r="J5" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="K5" s="15" t="inlineStr">
-        <is>
-          <t>Business and fashion; evening peak</t>
-        </is>
-      </c>
-      <c r="L5" s="15" t="inlineStr">
-        <is>
-          <t>moved to Routes</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="15" t="inlineStr">
-        <is>
-          <t>mad</t>
-        </is>
-      </c>
-      <c r="B6" s="15" t="inlineStr">
-        <is>
-          <t>Madrid</t>
-        </is>
-      </c>
-      <c r="C6" s="15" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="D6" s="15" t="inlineStr">
-        <is>
-          <t>MAD</t>
-        </is>
-      </c>
-      <c r="E6" s="15" t="n">
-        <v>1350</v>
-      </c>
-      <c r="F6" s="15" t="inlineStr">
-        <is>
-          <t>leisure_short</t>
-        </is>
-      </c>
-      <c r="G6" s="15" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="H6" s="15" t="n">
-        <v>170</v>
-      </c>
-      <c r="I6" s="15" t="inlineStr">
-        <is>
-          <t>4.50 / 3.00 / 1.50</t>
-        </is>
-      </c>
-      <c r="J6" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="K6" s="15" t="inlineStr">
-        <is>
-          <t>First medium-haul route (ATR or jet); summer busy</t>
-        </is>
-      </c>
-      <c r="L6" s="15" t="inlineStr">
-        <is>
-          <t>moved to Routes</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>fco</t>
-        </is>
-      </c>
-      <c r="B7" s="15" t="inlineStr">
-        <is>
-          <t>Rome</t>
-        </is>
-      </c>
-      <c r="C7" s="15" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="D7" s="15" t="inlineStr">
-        <is>
-          <t>FCO</t>
-        </is>
-      </c>
-      <c r="E7" s="15" t="n">
-        <v>1575</v>
-      </c>
-      <c r="F7" s="15" t="inlineStr">
-        <is>
-          <t>leisure_short</t>
-        </is>
-      </c>
-      <c r="G7" s="15" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="H7" s="15" t="n">
-        <v>190</v>
-      </c>
-      <c r="I7" s="15" t="inlineStr">
-        <is>
-          <t>5.25 / 3.50 / 1.75</t>
-        </is>
-      </c>
-      <c r="J7" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="K7" s="15" t="inlineStr">
-        <is>
-          <t>Leisure; spring and autumn peaks</t>
-        </is>
-      </c>
-      <c r="L7" s="15" t="inlineStr">
-        <is>
-          <t>moved to Routes</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="15" t="inlineStr">
-        <is>
-          <t>lis</t>
-        </is>
-      </c>
-      <c r="B8" s="15" t="inlineStr">
-        <is>
-          <t>Lisbon</t>
-        </is>
-      </c>
-      <c r="C8" s="15" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="D8" s="15" t="inlineStr">
-        <is>
-          <t>LIS</t>
-        </is>
-      </c>
-      <c r="E8" s="15" t="n">
-        <v>1575</v>
-      </c>
-      <c r="F8" s="15" t="inlineStr">
-        <is>
-          <t>leisure_short</t>
-        </is>
-      </c>
-      <c r="G8" s="15" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="H8" s="15" t="n">
-        <v>190</v>
-      </c>
-      <c r="I8" s="15" t="inlineStr">
-        <is>
-          <t>5.25 / 3.50 / 1.75</t>
-        </is>
-      </c>
-      <c r="J8" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="K8" s="15" t="inlineStr">
-        <is>
-          <t>Leisure; mild all year</t>
-        </is>
-      </c>
-      <c r="L8" s="15" t="inlineStr">
-        <is>
-          <t>moved to Routes</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="15" t="inlineStr">
-        <is>
-          <t>rek</t>
-        </is>
-      </c>
-      <c r="B9" s="15" t="inlineStr">
-        <is>
-          <t>Reykjavik</t>
-        </is>
-      </c>
-      <c r="C9" s="15" t="inlineStr">
-        <is>
-          <t>Iceland</t>
-        </is>
-      </c>
-      <c r="D9" s="15" t="inlineStr">
-        <is>
-          <t>KEF</t>
-        </is>
-      </c>
-      <c r="E9" s="15" t="n">
-        <v>1800</v>
-      </c>
-      <c r="F9" s="15" t="inlineStr">
-        <is>
-          <t>sun_holiday</t>
-        </is>
-      </c>
-      <c r="G9" s="15" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="H9" s="15" t="n">
-        <v>200</v>
-      </c>
-      <c r="I9" s="15" t="inlineStr">
-        <is>
-          <t>6.00 / 4.00 / 2.00</t>
-        </is>
-      </c>
-      <c r="J9" s="15" t="n">
-        <v>11</v>
-      </c>
-      <c r="K9" s="15" t="inlineStr">
-        <is>
-          <t>Winter northern lights; summer midnight sun; small pool</t>
-        </is>
-      </c>
-      <c r="L9" s="15" t="inlineStr">
-        <is>
-          <t>moved to Routes</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>rak</t>
-        </is>
-      </c>
-      <c r="B10" s="15" t="inlineStr">
-        <is>
-          <t>Marrakech</t>
-        </is>
-      </c>
-      <c r="C10" s="15" t="inlineStr">
-        <is>
-          <t>Morocco</t>
-        </is>
-      </c>
-      <c r="D10" s="15" t="inlineStr">
-        <is>
-          <t>RAK</t>
-        </is>
-      </c>
-      <c r="E10" s="15" t="n">
-        <v>2250</v>
-      </c>
-      <c r="F10" s="15" t="inlineStr">
-        <is>
-          <t>sun_holiday</t>
-        </is>
-      </c>
-      <c r="G10" s="15" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="H10" s="15" t="n">
-        <v>240</v>
-      </c>
-      <c r="I10" s="15" t="inlineStr">
-        <is>
-          <t>7.50 / 5.00 / 2.50</t>
-        </is>
-      </c>
-      <c r="J10" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="K10" s="15" t="inlineStr">
-        <is>
-          <t>Winter sun; strong Dec-Mar</t>
-        </is>
-      </c>
-      <c r="L10" s="15" t="inlineStr">
-        <is>
-          <t>moved to Routes</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>ath</t>
-        </is>
-      </c>
-      <c r="B11" s="15" t="inlineStr">
-        <is>
-          <t>Athens</t>
-        </is>
-      </c>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>Greece</t>
-        </is>
-      </c>
-      <c r="D11" s="15" t="inlineStr">
-        <is>
-          <t>ATH</t>
-        </is>
-      </c>
-      <c r="E11" s="15" t="n">
-        <v>2475</v>
-      </c>
-      <c r="F11" s="15" t="inlineStr">
-        <is>
-          <t>leisure_short</t>
-        </is>
-      </c>
-      <c r="G11" s="15" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="H11" s="15" t="n">
-        <v>260</v>
-      </c>
-      <c r="I11" s="15" t="inlineStr">
-        <is>
-          <t>8.25 / 5.50 / 2.75</t>
-        </is>
-      </c>
-      <c r="J11" s="15" t="n">
-        <v>9</v>
-      </c>
-      <c r="K11" s="15" t="inlineStr">
-        <is>
-          <t>Summer sun; big pool</t>
-        </is>
-      </c>
-      <c r="L11" s="15" t="inlineStr">
-        <is>
-          <t>moved to Routes</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>ist</t>
-        </is>
-      </c>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>Istanbul</t>
-        </is>
-      </c>
-      <c r="C12" s="15" t="inlineStr">
-        <is>
-          <t>Turkey</t>
-        </is>
-      </c>
-      <c r="D12" s="15" t="inlineStr">
-        <is>
-          <t>IST</t>
-        </is>
-      </c>
-      <c r="E12" s="15" t="n">
-        <v>2475</v>
-      </c>
-      <c r="F12" s="15" t="inlineStr">
-        <is>
-          <t>long_haul_mixed</t>
-        </is>
-      </c>
-      <c r="G12" s="15" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="H12" s="15" t="n">
-        <v>260</v>
-      </c>
-      <c r="I12" s="15" t="inlineStr">
-        <is>
-          <t>8.25 / 5.50 / 2.75</t>
-        </is>
-      </c>
-      <c r="J12" s="15" t="n">
-        <v>9</v>
-      </c>
-      <c r="K12" s="15" t="inlineStr">
-        <is>
-          <t>Gateway; mixed</t>
-        </is>
-      </c>
-      <c r="L12" s="15" t="inlineStr">
-        <is>
-          <t>moved to Routes</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="15" t="inlineStr">
-        <is>
-          <t>cai</t>
-        </is>
-      </c>
-      <c r="B13" s="15" t="inlineStr">
-        <is>
-          <t>Cairo</t>
-        </is>
-      </c>
-      <c r="C13" s="15" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-      <c r="D13" s="15" t="inlineStr">
-        <is>
-          <t>CAI</t>
-        </is>
-      </c>
-      <c r="E13" s="15" t="n">
-        <v>3600</v>
-      </c>
-      <c r="F13" s="15" t="inlineStr">
-        <is>
-          <t>sun_holiday</t>
-        </is>
-      </c>
-      <c r="G13" s="15" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="H13" s="15" t="n">
-        <v>350</v>
-      </c>
-      <c r="I13" s="15" t="inlineStr">
-        <is>
-          <t>12.00 / 8.00 / 4.00</t>
-        </is>
-      </c>
-      <c r="J13" s="15" t="n">
-        <v>13</v>
-      </c>
-      <c r="K13" s="15" t="inlineStr">
-        <is>
-          <t>Winter sun; pyramids; jet only</t>
-        </is>
-      </c>
-      <c r="L13" s="15" t="inlineStr">
-        <is>
-          <t>moved to Routes</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>los</t>
-        </is>
-      </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>Lagos</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>Nigeria</t>
-        </is>
-      </c>
-      <c r="D14" s="11" t="inlineStr">
-        <is>
-          <t>LOS</t>
-        </is>
-      </c>
-      <c r="E14" s="11" t="n">
-        <v>4950</v>
-      </c>
-      <c r="F14" s="11" t="inlineStr">
-        <is>
-          <t>long_haul_mixed</t>
-        </is>
-      </c>
-      <c r="G14" s="11" t="inlineStr">
-        <is>
-          <t>long</t>
-        </is>
-      </c>
-      <c r="H14" s="11" t="n">
-        <v>460</v>
-      </c>
-      <c r="I14" s="11" t="inlineStr">
-        <is>
-          <t>16.50 / 11.00 / 5.50</t>
-        </is>
-      </c>
-      <c r="J14" s="11" t="n">
-        <v>32</v>
-      </c>
-      <c r="K14" s="11" t="inlineStr">
-        <is>
-          <t>Business travellers; steady</t>
-        </is>
-      </c>
-      <c r="L14" s="11" t="inlineStr">
-        <is>
-          <t>placeholder</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>nyc</t>
-        </is>
-      </c>
-      <c r="B15" s="15" t="inlineStr">
-        <is>
-          <t>New York</t>
-        </is>
-      </c>
-      <c r="C15" s="15" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D15" s="15" t="inlineStr">
-        <is>
-          <t>JFK</t>
-        </is>
-      </c>
-      <c r="E15" s="15" t="n">
-        <v>5625</v>
-      </c>
-      <c r="F15" s="15" t="inlineStr">
-        <is>
-          <t>long_haul_mixed</t>
-        </is>
-      </c>
-      <c r="G15" s="15" t="inlineStr">
-        <is>
-          <t>long</t>
-        </is>
-      </c>
-      <c r="H15" s="15" t="n">
-        <v>510</v>
-      </c>
-      <c r="I15" s="15" t="inlineStr">
-        <is>
-          <t>18.75 / 12.50 / 6.25</t>
-        </is>
-      </c>
-      <c r="J15" s="15" t="n">
-        <v>19</v>
-      </c>
-      <c r="K15" s="15" t="inlineStr">
-        <is>
-          <t>The big one; overnight return</t>
-        </is>
-      </c>
-      <c r="L15" s="15" t="inlineStr">
-        <is>
-          <t>moved to Routes</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="11" t="inlineStr">
-        <is>
-          <t>yyz</t>
-        </is>
-      </c>
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>Toronto</t>
-        </is>
-      </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="D16" s="11" t="inlineStr">
-        <is>
-          <t>YYZ</t>
-        </is>
-      </c>
-      <c r="E16" s="11" t="n">
-        <v>5625</v>
-      </c>
-      <c r="F16" s="11" t="inlineStr">
-        <is>
-          <t>long_haul_mixed</t>
-        </is>
-      </c>
-      <c r="G16" s="11" t="inlineStr">
-        <is>
-          <t>long</t>
-        </is>
-      </c>
-      <c r="H16" s="11" t="n">
-        <v>510</v>
-      </c>
-      <c r="I16" s="11" t="inlineStr">
-        <is>
-          <t>18.75 / 12.50 / 6.25</t>
-        </is>
-      </c>
-      <c r="J16" s="11" t="n">
-        <v>27</v>
-      </c>
-      <c r="K16" s="11" t="inlineStr">
-        <is>
-          <t>Winter demand (families)</t>
-        </is>
-      </c>
-      <c r="L16" s="11" t="inlineStr">
-        <is>
-          <t>placeholder</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="15" t="inlineStr">
-        <is>
-          <t>dxb</t>
-        </is>
-      </c>
-      <c r="B17" s="15" t="inlineStr">
-        <is>
-          <t>Dubai</t>
-        </is>
-      </c>
-      <c r="C17" s="15" t="inlineStr">
-        <is>
-          <t>UAE</t>
-        </is>
-      </c>
-      <c r="D17" s="15" t="inlineStr">
-        <is>
-          <t>DXB</t>
-        </is>
-      </c>
-      <c r="E17" s="15" t="n">
-        <v>5400</v>
-      </c>
-      <c r="F17" s="15" t="inlineStr">
-        <is>
-          <t>long_haul_mixed</t>
-        </is>
-      </c>
-      <c r="G17" s="15" t="inlineStr">
-        <is>
-          <t>long</t>
-        </is>
-      </c>
-      <c r="H17" s="15" t="n">
-        <v>490</v>
-      </c>
-      <c r="I17" s="15" t="inlineStr">
-        <is>
-          <t>18.00 / 12.00 / 6.00</t>
-        </is>
-      </c>
-      <c r="J17" s="15" t="n">
-        <v>19</v>
-      </c>
-      <c r="K17" s="15" t="inlineStr">
-        <is>
-          <t>High fares; winter busy</t>
-        </is>
-      </c>
-      <c r="L17" s="15" t="inlineStr">
-        <is>
-          <t>moved to Routes</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="11" t="inlineStr">
-        <is>
-          <t>del</t>
-        </is>
-      </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>Delhi</t>
-        </is>
-      </c>
-      <c r="C18" s="11" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
-      <c r="D18" s="11" t="inlineStr">
-        <is>
-          <t>DEL</t>
-        </is>
-      </c>
-      <c r="E18" s="11" t="n">
-        <v>6750</v>
-      </c>
-      <c r="F18" s="11" t="inlineStr">
-        <is>
-          <t>long_haul_mixed</t>
-        </is>
-      </c>
-      <c r="G18" s="11" t="inlineStr">
-        <is>
-          <t>long</t>
-        </is>
-      </c>
-      <c r="H18" s="11" t="n">
-        <v>600</v>
-      </c>
-      <c r="I18" s="11" t="inlineStr">
-        <is>
-          <t>22.50 / 15.00 / 7.50</t>
-        </is>
-      </c>
-      <c r="J18" s="11" t="n">
-        <v>40</v>
-      </c>
-      <c r="K18" s="11" t="inlineStr">
-        <is>
-          <t>Very busy; overnight</t>
-        </is>
-      </c>
-      <c r="L18" s="11" t="inlineStr">
-        <is>
-          <t>placeholder</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>cpt</t>
-        </is>
-      </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>Cape Town</t>
-        </is>
-      </c>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
-          <t>South Africa</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t>CPT</t>
-        </is>
-      </c>
-      <c r="E19" s="11" t="n">
-        <v>9675</v>
-      </c>
-      <c r="F19" s="11" t="inlineStr">
-        <is>
-          <t>sun_holiday</t>
-        </is>
-      </c>
-      <c r="G19" s="11" t="inlineStr">
-        <is>
-          <t>long</t>
-        </is>
-      </c>
-      <c r="H19" s="11" t="n">
-        <v>830</v>
-      </c>
-      <c r="I19" s="11" t="inlineStr">
-        <is>
-          <t>32.25 / 21.50 / 10.75</t>
-        </is>
-      </c>
-      <c r="J19" s="11" t="n">
-        <v>54</v>
-      </c>
-      <c r="K19" s="11" t="inlineStr">
-        <is>
-          <t>UK winter = their summer; strong Dec-Feb</t>
-        </is>
-      </c>
-      <c r="L19" s="11" t="inlineStr">
-        <is>
-          <t>placeholder</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t>tyo</t>
-        </is>
-      </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t>Tokyo</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="D20" s="11" t="inlineStr">
-        <is>
-          <t>HND</t>
-        </is>
-      </c>
-      <c r="E20" s="11" t="n">
-        <v>9450</v>
-      </c>
-      <c r="F20" s="11" t="inlineStr">
-        <is>
-          <t>long_haul_mixed</t>
-        </is>
-      </c>
-      <c r="G20" s="11" t="inlineStr">
-        <is>
-          <t>long</t>
-        </is>
-      </c>
-      <c r="H20" s="11" t="n">
-        <v>820</v>
-      </c>
-      <c r="I20" s="11" t="inlineStr">
-        <is>
-          <t>31.50 / 21.00 / 10.50</t>
-        </is>
-      </c>
-      <c r="J20" s="11" t="n">
-        <v>54</v>
-      </c>
-      <c r="K20" s="11" t="inlineStr">
-        <is>
-          <t>Huge demand; cherry blossom spike (event)</t>
-        </is>
-      </c>
-      <c r="L20" s="11" t="inlineStr">
-        <is>
-          <t>placeholder</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>sin</t>
-        </is>
-      </c>
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t>Singapore</t>
-        </is>
-      </c>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>Singapore</t>
-        </is>
-      </c>
-      <c r="D21" s="11" t="inlineStr">
-        <is>
-          <t>SIN</t>
-        </is>
-      </c>
-      <c r="E21" s="11" t="n">
-        <v>10800</v>
-      </c>
-      <c r="F21" s="11" t="inlineStr">
-        <is>
-          <t>long_haul_mixed</t>
-        </is>
-      </c>
-      <c r="G21" s="11" t="inlineStr">
-        <is>
-          <t>long</t>
-        </is>
-      </c>
-      <c r="H21" s="11" t="n">
-        <v>920</v>
-      </c>
-      <c r="I21" s="11" t="inlineStr">
-        <is>
-          <t>36.00 / 24.00 / 12.00</t>
-        </is>
-      </c>
-      <c r="J21" s="11" t="n">
-        <v>62</v>
-      </c>
-      <c r="K21" s="11" t="inlineStr">
-        <is>
-          <t>Gateway to Asia</t>
-        </is>
-      </c>
-      <c r="L21" s="11" t="inlineStr">
-        <is>
-          <t>placeholder</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="11" t="inlineStr">
-        <is>
-          <t>syd</t>
-        </is>
-      </c>
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t>Sydney</t>
-        </is>
-      </c>
-      <c r="C22" s="11" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="D22" s="11" t="inlineStr">
-        <is>
-          <t>SYD</t>
-        </is>
-      </c>
-      <c r="E22" s="11" t="n">
-        <v>17100</v>
-      </c>
-      <c r="F22" s="11" t="inlineStr">
-        <is>
-          <t>long_haul_mixed</t>
-        </is>
-      </c>
-      <c r="G22" s="11" t="inlineStr">
-        <is>
-          <t>long</t>
-        </is>
-      </c>
-      <c r="H22" s="11" t="n">
-        <v>1430</v>
-      </c>
-      <c r="I22" s="11" t="inlineStr">
-        <is>
-          <t>57.00 / 38.00 / 19.00</t>
-        </is>
-      </c>
-      <c r="J22" s="11" t="n">
-        <v>80</v>
-      </c>
-      <c r="K22" s="11" t="inlineStr">
-        <is>
-          <t>Longest flight; A350 only; the final flex</t>
-        </is>
-      </c>
-      <c r="L22" s="11" t="inlineStr">
-        <is>
-          <t>placeholder</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/data/Airline-World-Workbook.xlsx
+++ b/data/Airline-World-Workbook.xlsx
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A23"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -734,6 +734,13 @@
       <c r="A23" s="17" t="inlineStr">
         <is>
           <t>v4.10 (13 Oct): D66 Operating Plan Studio data — seat-fill thresholds (Settings seatFillGood/Medium), per-route demand strip (demandStripMode), the four-step bar (planStudioSteps), and the PlanTips sheet (ten data-driven live tips). Data appendix: Operating Plan Studio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="17" t="inlineStr">
+        <is>
+          <t>v4.11 (13 Oct): D67 flight Days setting (All week / Mon–Fri / Sat–Sun) from week 2, weekday and weekend seat fill shown separately, patterns may be a day plus extras; haul-band settings; PlanTips gains fare_lower_fills and weekend_only_news.</t>
         </is>
       </c>
     </row>
@@ -28972,7 +28979,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D96"/>
+  <dimension ref="A1:D102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -30960,6 +30967,124 @@
         </is>
       </c>
       <c r="D96" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="13" t="inlineStr">
+        <is>
+          <t>flightDays</t>
+        </is>
+      </c>
+      <c r="B97" s="13" t="inlineStr">
+        <is>
+          <t>All week | Mon–Fri | Sat–Sun</t>
+        </is>
+      </c>
+      <c r="C97" s="13" t="inlineStr">
+        <is>
+          <t>D67: every flight in a standing plan has a Days setting, default All week, set in the flight editor. Weekend-only services exist for news such as the Dublin rugby; weekday-only services suit business routes that are quiet on Saturdays.</t>
+        </is>
+      </c>
+      <c r="D97" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="13" t="inlineStr">
+        <is>
+          <t>flightDaysFromDay</t>
+        </is>
+      </c>
+      <c r="B98" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="C98" s="13" t="inlineStr">
+        <is>
+          <t>The Days setting appears from week 2 (Launch Day keeps one timetable for the week).</t>
+        </is>
+      </c>
+      <c r="D98" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="13" t="inlineStr">
+        <is>
+          <t>summaryWeekdayWeekend</t>
+        </is>
+      </c>
+      <c r="B99" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="C99" s="13" t="inlineStr">
+        <is>
+          <t>D67: the summary bar and the Sunday review show seat fill for weekdays and the weekend separately when any flight is not All week.</t>
+        </is>
+      </c>
+      <c r="D99" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="13" t="inlineStr">
+        <is>
+          <t>patternPlusExtras</t>
+        </is>
+      </c>
+      <c r="B100" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="C100" s="13" t="inlineStr">
+        <is>
+          <t>D67: a regular operating pattern is a whole day, and an aircraft may fly a pattern plus extra flights (for example Pattern A all week plus a Saturday Dublin service).</t>
+        </is>
+      </c>
+      <c r="D100" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="13" t="inlineStr">
+        <is>
+          <t>shortHaulMaxKm</t>
+        </is>
+      </c>
+      <c r="B101" s="13" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C101" s="13" t="inlineStr">
+        <is>
+          <t>Haul bands for the network filters (from Claude Code's revised Studio): short haul up to 1,500 km, medium to 4,000 km, long beyond.</t>
+        </is>
+      </c>
+      <c r="D101" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="13" t="inlineStr">
+        <is>
+          <t>mediumHaulMaxKm</t>
+        </is>
+      </c>
+      <c r="B102" s="13" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C102" s="13" t="inlineStr"/>
+      <c r="D102" s="13" t="inlineStr">
         <is>
           <t>live</t>
         </is>
@@ -30976,7 +31101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -31319,8 +31444,69 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>fare_lower_fills</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>Seats are empty on a route and more people want to fly at the next fare down</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>{route} could fill all {seats} seats at £{lower}, but would earn £{diff} less per passenger.</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>weekend_only_news</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>Announced news lifts a route's demand on the weekend only and the plan has no Sat–Sun service on it</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>{route} is busy this weekend only: add a Sat–Sun service rather than one all week.</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>D66: the Live seat fill panel shows at most two tips, lowest priority number first. Conditions are evaluated on the projected plan every time it changes; the same conditions feed the Sunday review's explanation of missed profit.</t>
         </is>

--- a/data/Airline-World-Workbook.xlsx
+++ b/data/Airline-World-Workbook.xlsx
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -741,6 +741,13 @@
       <c r="A24" s="17" t="inlineStr">
         <is>
           <t>v4.11 (13 Oct): D67 flight Days setting (All week / Mon–Fri / Sat–Sun) from week 2, weekday and weekend seat fill shown separately, patterns may be a day plus extras; haul-band settings; PlanTips gains fare_lower_fills and weekend_only_news.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>v5.0 (13 Oct): CHAPTER 2 LIVE. New York and Dubai (unlockDay 127), Toronto (183), Lagos (218), Delhi (274, the first overnight rotation); a long_haul archetype (one flight a day, one in ten time-locked, growth 5% a week to ×1.5); the 757 and 787 live to lease, the 787 re-costed to be cheaper per seat than the 757 (130 L/100 km, £2,000/h, £6,000/day); A320/737 range 5,500 km and A220 5,000 so the Atlantic needs a long-haul plane; same-day long haul to 6,000 km with a £500 second crew; reputation ×5% a half-star from January with the autumn's stars banked; light airline types (Premium two higher fares and faster stars, Value one lower fare and the £20 bag fee at four in ten); demand tables extended a step below and two above every live route's options; fuel forecasts weeks 18–52; 19 route-news items January–August; the spring and summer events written with options; Challenges 1–2 and Hunts h1–h2 live; chapter-2 Calendar days 127–133. Balance Report v5.0.</t>
         </is>
       </c>
     </row>
@@ -1507,58 +1514,58 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>los</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>Lagos</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C14" s="15" t="inlineStr">
         <is>
           <t>Nigeria</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="D14" s="15" t="inlineStr">
         <is>
           <t>LOS</t>
         </is>
       </c>
-      <c r="E14" s="11" t="n">
+      <c r="E14" s="15" t="n">
         <v>4950</v>
       </c>
-      <c r="F14" s="11" t="inlineStr">
+      <c r="F14" s="15" t="inlineStr">
         <is>
           <t>long_haul_mixed</t>
         </is>
       </c>
-      <c r="G14" s="11" t="inlineStr">
+      <c r="G14" s="15" t="inlineStr">
         <is>
           <t>long</t>
         </is>
       </c>
-      <c r="H14" s="11" t="n">
+      <c r="H14" s="15" t="n">
         <v>460</v>
       </c>
-      <c r="I14" s="11" t="inlineStr">
+      <c r="I14" s="15" t="inlineStr">
         <is>
           <t>16.50 / 11.00 / 5.50</t>
         </is>
       </c>
-      <c r="J14" s="11" t="n">
+      <c r="J14" s="15" t="n">
         <v>32</v>
       </c>
-      <c r="K14" s="11" t="inlineStr">
+      <c r="K14" s="15" t="inlineStr">
         <is>
           <t>Business travellers; steady</t>
         </is>
       </c>
-      <c r="L14" s="11" t="inlineStr">
-        <is>
-          <t>placeholder</t>
+      <c r="L14" s="15" t="inlineStr">
+        <is>
+          <t>moved to Routes</t>
         </is>
       </c>
     </row>
@@ -1619,58 +1626,58 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>yyz</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr">
         <is>
           <t>Toronto</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C16" s="15" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="15" t="inlineStr">
         <is>
           <t>YYZ</t>
         </is>
       </c>
-      <c r="E16" s="11" t="n">
+      <c r="E16" s="15" t="n">
         <v>5625</v>
       </c>
-      <c r="F16" s="11" t="inlineStr">
+      <c r="F16" s="15" t="inlineStr">
         <is>
           <t>long_haul_mixed</t>
         </is>
       </c>
-      <c r="G16" s="11" t="inlineStr">
+      <c r="G16" s="15" t="inlineStr">
         <is>
           <t>long</t>
         </is>
       </c>
-      <c r="H16" s="11" t="n">
+      <c r="H16" s="15" t="n">
         <v>510</v>
       </c>
-      <c r="I16" s="11" t="inlineStr">
+      <c r="I16" s="15" t="inlineStr">
         <is>
           <t>18.75 / 12.50 / 6.25</t>
         </is>
       </c>
-      <c r="J16" s="11" t="n">
+      <c r="J16" s="15" t="n">
         <v>27</v>
       </c>
-      <c r="K16" s="11" t="inlineStr">
+      <c r="K16" s="15" t="inlineStr">
         <is>
           <t>Winter demand (families)</t>
         </is>
       </c>
-      <c r="L16" s="11" t="inlineStr">
-        <is>
-          <t>placeholder</t>
+      <c r="L16" s="15" t="inlineStr">
+        <is>
+          <t>moved to Routes</t>
         </is>
       </c>
     </row>
@@ -1731,58 +1738,58 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>del</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="15" t="inlineStr">
         <is>
           <t>Delhi</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C18" s="15" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="D18" s="15" t="inlineStr">
         <is>
           <t>DEL</t>
         </is>
       </c>
-      <c r="E18" s="11" t="n">
+      <c r="E18" s="15" t="n">
         <v>6750</v>
       </c>
-      <c r="F18" s="11" t="inlineStr">
+      <c r="F18" s="15" t="inlineStr">
         <is>
           <t>long_haul_mixed</t>
         </is>
       </c>
-      <c r="G18" s="11" t="inlineStr">
+      <c r="G18" s="15" t="inlineStr">
         <is>
           <t>long</t>
         </is>
       </c>
-      <c r="H18" s="11" t="n">
+      <c r="H18" s="15" t="n">
         <v>600</v>
       </c>
-      <c r="I18" s="11" t="inlineStr">
+      <c r="I18" s="15" t="inlineStr">
         <is>
           <t>22.50 / 15.00 / 7.50</t>
         </is>
       </c>
-      <c r="J18" s="11" t="n">
+      <c r="J18" s="15" t="n">
         <v>40</v>
       </c>
-      <c r="K18" s="11" t="inlineStr">
+      <c r="K18" s="15" t="inlineStr">
         <is>
           <t>Very busy; overnight</t>
         </is>
       </c>
-      <c r="L18" s="11" t="inlineStr">
-        <is>
-          <t>placeholder</t>
+      <c r="L18" s="15" t="inlineStr">
+        <is>
+          <t>moved to Routes</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2397,7 @@
         <v>900</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>6300</v>
+        <v>5000</v>
       </c>
       <c r="G6" s="12" t="n">
         <v>80</v>
@@ -2447,7 +2454,7 @@
         <v>900</v>
       </c>
       <c r="F7" s="12" t="n">
-        <v>6000</v>
+        <v>5500</v>
       </c>
       <c r="G7" s="12" t="n">
         <v>90</v>
@@ -2467,7 +2474,7 @@
       </c>
       <c r="M7" s="12" t="inlineStr">
         <is>
-          <t>The one he named ('an Airbus'). Rome, Athens, Istanbul.</t>
+          <t>The one he named ('an Airbus'). Rome, Athens, Istanbul, Cairo — but not the Atlantic: 5,500 km range.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -2504,7 +2511,7 @@
         <v>900</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>6000</v>
+        <v>5500</v>
       </c>
       <c r="G8" s="12" t="n">
         <v>90</v>
@@ -2539,54 +2546,59 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>b787</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>Boeing 787 Dreamliner</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>long-haul</t>
         </is>
       </c>
-      <c r="D9" s="15" t="n">
+      <c r="D9" s="12" t="n">
         <v>250</v>
       </c>
-      <c r="E9" s="15" t="n">
+      <c r="E9" s="12" t="n">
         <v>900</v>
       </c>
-      <c r="F9" s="15" t="n">
+      <c r="F9" s="12" t="n">
         <v>14000</v>
       </c>
-      <c r="G9" s="15" t="n">
-        <v>200</v>
-      </c>
-      <c r="H9" s="15" t="n">
-        <v>3000</v>
-      </c>
-      <c r="I9" s="15" t="n">
-        <v>8000</v>
-      </c>
-      <c r="J9" s="15" t="n">
+      <c r="G9" s="12" t="n">
+        <v>130</v>
+      </c>
+      <c r="H9" s="12" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I9" s="12" t="n">
+        <v>6000</v>
+      </c>
+      <c r="J9" s="12" t="n">
         <v>6000000</v>
       </c>
-      <c r="K9" s="15" t="inlineStr"/>
-      <c r="L9" s="15" t="n">
+      <c r="K9" s="12" t="inlineStr"/>
+      <c r="L9" s="12" t="n">
         <v>127</v>
       </c>
-      <c r="M9" s="15" t="inlineStr">
-        <is>
-          <t>Named by the pupil. Opens long haul, January 2031, by lease; bought outright from chapter 3.</t>
-        </is>
-      </c>
-      <c r="S9" s="15" t="inlineStr">
-        <is>
-          <t>later</t>
+      <c r="M9" s="12" t="inlineStr">
+        <is>
+          <t>Named by the pupil. 250 seats, cheaper per seat than the 757 but four times the rent: the plane to grow into. Beats the 757 once a route has grown or the stars are up.</t>
+        </is>
+      </c>
+      <c r="N9" s="13" t="n"/>
+      <c r="O9" s="13" t="n"/>
+      <c r="P9" s="13" t="n"/>
+      <c r="Q9" s="13" t="n"/>
+      <c r="R9" s="13" t="n"/>
+      <c r="S9" s="12" t="inlineStr">
+        <is>
+          <t>live</t>
         </is>
       </c>
     </row>
@@ -2856,54 +2868,59 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>b757</t>
         </is>
       </c>
-      <c r="B16" s="14" t="inlineStr">
+      <c r="B16" s="13" t="inlineStr">
         <is>
           <t>Boeing 757</t>
         </is>
       </c>
-      <c r="C16" s="14" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
         <is>
           <t>narrowbody long-range</t>
         </is>
       </c>
-      <c r="D16" s="14" t="n">
+      <c r="D16" s="13" t="n">
         <v>200</v>
       </c>
-      <c r="E16" s="14" t="n">
+      <c r="E16" s="13" t="n">
         <v>900</v>
       </c>
-      <c r="F16" s="14" t="n">
+      <c r="F16" s="13" t="n">
         <v>7200</v>
       </c>
-      <c r="G16" s="14" t="n">
+      <c r="G16" s="13" t="n">
         <v>110</v>
       </c>
-      <c r="H16" s="14" t="n">
+      <c r="H16" s="13" t="n">
         <v>1600</v>
       </c>
-      <c r="I16" s="14" t="n">
+      <c r="I16" s="13" t="n">
         <v>4200</v>
       </c>
-      <c r="J16" s="14" t="n">
+      <c r="J16" s="13" t="n">
         <v>1500000</v>
       </c>
-      <c r="K16" s="14" t="n"/>
-      <c r="L16" s="14" t="n">
+      <c r="K16" s="13" t="n"/>
+      <c r="L16" s="13" t="n">
         <v>127</v>
       </c>
-      <c r="M16" s="14" t="inlineStr">
-        <is>
-          <t>Long and narrow with big engines: reaches New York with fewer seats than a widebody. The cheap way into long haul. Chapter 2, by lease.</t>
-        </is>
-      </c>
-      <c r="S16" s="14" t="inlineStr">
-        <is>
-          <t>placeholder</t>
+      <c r="M16" s="13" t="inlineStr">
+        <is>
+          <t>Long and narrow with big engines: 200 seats, reaches New York. The plane that fills on day one of long haul. Rent £1,500.</t>
+        </is>
+      </c>
+      <c r="N16" s="13" t="n"/>
+      <c r="O16" s="13" t="n"/>
+      <c r="P16" s="13" t="n"/>
+      <c r="Q16" s="13" t="n"/>
+      <c r="R16" s="13" t="n"/>
+      <c r="S16" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
         </is>
       </c>
     </row>
@@ -3501,102 +3518,102 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>b757</t>
         </is>
       </c>
-      <c r="B10" s="14" t="n">
+      <c r="B10" s="13" t="n">
         <v>1500000</v>
       </c>
-      <c r="C10" s="14" t="n">
+      <c r="C10" s="13" t="n">
         <v>1500</v>
       </c>
-      <c r="D10" s="14" t="n">
+      <c r="D10" s="13" t="n">
         <v>450000</v>
       </c>
-      <c r="E10" s="14" t="n">
+      <c r="E10" s="13" t="n">
         <v>20000</v>
       </c>
-      <c r="F10" s="14" t="n">
+      <c r="F10" s="13" t="n">
         <v>52</v>
       </c>
-      <c r="G10" s="14" t="n">
+      <c r="G10" s="13" t="n">
         <v>1490000</v>
       </c>
-      <c r="H10" s="14" t="inlineStr">
+      <c r="H10" s="13" t="inlineStr">
         <is>
           <t>2031-01-06</t>
         </is>
       </c>
-      <c r="I10" s="14" t="inlineStr">
+      <c r="I10" s="13" t="inlineStr">
         <is>
           <t>2031-09-02</t>
         </is>
       </c>
-      <c r="J10" s="14" t="inlineStr">
+      <c r="J10" s="13" t="inlineStr">
         <is>
           <t>2032-09-07</t>
         </is>
       </c>
-      <c r="K10" s="14" t="inlineStr">
-        <is>
-          <t>The cheap way into long haul by lease in chapter 2.</t>
-        </is>
-      </c>
-      <c r="L10" s="14" t="inlineStr">
-        <is>
-          <t>placeholder</t>
+      <c r="K10" s="13" t="inlineStr">
+        <is>
+          <t>Leased in January 2031 at £1,500 a day (price ÷ 1,000). Buy from chapter 3.</t>
+        </is>
+      </c>
+      <c r="L10" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>b787</t>
         </is>
       </c>
-      <c r="B11" s="18" t="n">
+      <c r="B11" s="13" t="n">
         <v>6000000</v>
       </c>
-      <c r="C11" s="18" t="n">
+      <c r="C11" s="13" t="n">
         <v>6000</v>
       </c>
-      <c r="D11" s="18" t="n">
+      <c r="D11" s="13" t="n">
         <v>1800000</v>
       </c>
-      <c r="E11" s="18" t="n">
+      <c r="E11" s="13" t="n">
         <v>81000</v>
       </c>
-      <c r="F11" s="18" t="n">
+      <c r="F11" s="13" t="n">
         <v>52</v>
       </c>
-      <c r="G11" s="18" t="n">
+      <c r="G11" s="13" t="n">
         <v>6012000</v>
       </c>
-      <c r="H11" s="18" t="inlineStr">
+      <c r="H11" s="13" t="inlineStr">
         <is>
           <t>2031-01-06</t>
         </is>
       </c>
-      <c r="I11" s="18" t="inlineStr">
+      <c r="I11" s="13" t="inlineStr">
         <is>
           <t>2031-09-02</t>
         </is>
       </c>
-      <c r="J11" s="18" t="inlineStr">
+      <c r="J11" s="13" t="inlineStr">
         <is>
           <t>2032-09-07</t>
         </is>
       </c>
-      <c r="K11" s="18" t="inlineStr">
-        <is>
-          <t>Leased Jan 2031; first big plane bought outright Sep 2031 on the Steady path. 6,000,000 ÷ 6,000 = 1,000 days.</t>
-        </is>
-      </c>
-      <c r="L11" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
+      <c r="K11" s="13" t="inlineStr">
+        <is>
+          <t>Leased in January 2031 at £6,000 a day. Buy from chapter 3. 6,000,000 ÷ 6,000 = 1,000 days.</t>
+        </is>
+      </c>
+      <c r="L11" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R29"/>
+  <dimension ref="A1:R36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5928,6 +5945,408 @@
         </is>
       </c>
       <c r="R29" s="13" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="n">
+        <v>127</v>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>2031-01-06</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="F30" s="13" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="G30" s="13" t="inlineStr">
+        <is>
+          <t>Chapter 2: going long</t>
+        </is>
+      </c>
+      <c r="H30" s="13" t="inlineStr">
+        <is>
+          <t>New York and Dubai open. The 757 and the 787 are in the shop to lease. Your star rating is now public.</t>
+        </is>
+      </c>
+      <c r="I30" s="13" t="inlineStr">
+        <is>
+          <t>Fuel £2.17 a litre.</t>
+        </is>
+      </c>
+      <c r="J30" s="13" t="inlineStr">
+        <is>
+          <t>long_haul_open</t>
+        </is>
+      </c>
+      <c r="K30" s="13" t="inlineStr">
+        <is>
+          <t>routes: nyc, dxb; planes: b757, b787 (lease); mechanics: long haul same-day, local time, reputation, airline type, bag fee (Value), long-haul crew £500</t>
+        </is>
+      </c>
+      <c r="L30" s="13" t="n"/>
+      <c r="M30" s="13" t="n"/>
+      <c r="N30" s="13" t="inlineStr">
+        <is>
+          <t>fleet,assignment,pricing</t>
+        </is>
+      </c>
+      <c r="O30" s="13" t="inlineStr">
+        <is>
+          <t>longHaulTickets,bagFee</t>
+        </is>
+      </c>
+      <c r="P30" s="13" t="n"/>
+      <c r="Q30" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="R30" s="13" t="inlineStr">
+        <is>
+          <t>plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="13" t="n">
+        <v>128</v>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>2031-01-07</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D31" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="F31" s="13" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="G31" s="13" t="inlineStr">
+        <is>
+          <t>Tuesday: the first transatlantic flight</t>
+        </is>
+      </c>
+      <c r="H31" s="13" t="inlineStr">
+        <is>
+          <t>Out at 06:30, in New York at 07:45 their time.</t>
+        </is>
+      </c>
+      <c r="I31" s="13" t="inlineStr"/>
+      <c r="J31" s="13" t="inlineStr"/>
+      <c r="K31" s="13" t="inlineStr"/>
+      <c r="L31" s="13" t="n"/>
+      <c r="M31" s="13" t="n"/>
+      <c r="N31" s="13" t="inlineStr"/>
+      <c r="O31" s="13" t="inlineStr"/>
+      <c r="P31" s="13" t="n"/>
+      <c r="Q31" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="R31" s="13" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="n">
+        <v>129</v>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>2031-01-08</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="D32" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="F32" s="13" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="G32" s="13" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="H32" s="13" t="inlineStr"/>
+      <c r="I32" s="13" t="inlineStr"/>
+      <c r="J32" s="13" t="inlineStr"/>
+      <c r="K32" s="13" t="inlineStr"/>
+      <c r="L32" s="13" t="n"/>
+      <c r="M32" s="13" t="n"/>
+      <c r="N32" s="13" t="inlineStr">
+        <is>
+          <t>fuel</t>
+        </is>
+      </c>
+      <c r="O32" s="13" t="inlineStr">
+        <is>
+          <t>fuelCost</t>
+        </is>
+      </c>
+      <c r="P32" s="13" t="n"/>
+      <c r="Q32" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="R32" s="13" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="13" t="n">
+        <v>130</v>
+      </c>
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>2031-01-09</t>
+        </is>
+      </c>
+      <c r="C33" s="13" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="D33" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="E33" s="13" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="F33" s="13" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="G33" s="13" t="inlineStr">
+        <is>
+          <t>Thursday: what sort of airline?</t>
+        </is>
+      </c>
+      <c r="H33" s="13" t="inlineStr">
+        <is>
+          <t>Passengers want to know what sort of airline you are.</t>
+        </is>
+      </c>
+      <c r="I33" s="13" t="inlineStr"/>
+      <c r="J33" s="13" t="inlineStr"/>
+      <c r="K33" s="13" t="inlineStr">
+        <is>
+          <t>mechanics: airline type confirmed</t>
+        </is>
+      </c>
+      <c r="L33" s="13" t="n"/>
+      <c r="M33" s="13" t="n"/>
+      <c r="N33" s="13" t="inlineStr"/>
+      <c r="O33" s="13" t="inlineStr"/>
+      <c r="P33" s="13" t="n"/>
+      <c r="Q33" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="R33" s="13" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="n">
+        <v>131</v>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>2031-01-10</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="D34" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="E34" s="13" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="F34" s="13" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="G34" s="13" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="H34" s="13" t="inlineStr"/>
+      <c r="I34" s="13" t="inlineStr"/>
+      <c r="J34" s="13" t="inlineStr"/>
+      <c r="K34" s="13" t="inlineStr"/>
+      <c r="L34" s="13" t="n"/>
+      <c r="M34" s="13" t="n"/>
+      <c r="N34" s="13" t="inlineStr"/>
+      <c r="O34" s="13" t="inlineStr"/>
+      <c r="P34" s="13" t="n"/>
+      <c r="Q34" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="R34" s="13" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="13" t="n">
+        <v>132</v>
+      </c>
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>2031-01-11</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="D35" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="E35" s="13" t="inlineStr">
+        <is>
+          <t>weekend</t>
+        </is>
+      </c>
+      <c r="F35" s="13" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="G35" s="13" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="H35" s="13" t="inlineStr"/>
+      <c r="I35" s="13" t="inlineStr"/>
+      <c r="J35" s="13" t="inlineStr"/>
+      <c r="K35" s="13" t="inlineStr"/>
+      <c r="L35" s="13" t="n"/>
+      <c r="M35" s="13" t="n"/>
+      <c r="N35" s="13" t="inlineStr"/>
+      <c r="O35" s="13" t="inlineStr"/>
+      <c r="P35" s="13" t="n"/>
+      <c r="Q35" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="R35" s="13" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="n">
+        <v>133</v>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>2031-01-12</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="D36" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="E36" s="13" t="inlineStr">
+        <is>
+          <t>weekend</t>
+        </is>
+      </c>
+      <c r="F36" s="13" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="G36" s="13" t="inlineStr">
+        <is>
+          <t>Sunday: the first long-haul week</t>
+        </is>
+      </c>
+      <c r="H36" s="13" t="inlineStr"/>
+      <c r="I36" s="13" t="inlineStr"/>
+      <c r="J36" s="13" t="inlineStr"/>
+      <c r="K36" s="13" t="inlineStr"/>
+      <c r="L36" s="13" t="n"/>
+      <c r="M36" s="13" t="n"/>
+      <c r="N36" s="13" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="O36" s="13" t="inlineStr">
+        <is>
+          <t>weekTotal,projectedVsActual,mean</t>
+        </is>
+      </c>
+      <c r="P36" s="13" t="n"/>
+      <c r="Q36" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="R36" s="13" t="inlineStr">
         <is>
           <t>review</t>
         </is>
@@ -7072,1463 +7491,1962 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="n">
+      <c r="A19" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>2030-12-30</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C19" s="12" t="inlineStr">
         <is>
           <t>winter</t>
         </is>
       </c>
-      <c r="D19" s="11" t="n">
+      <c r="D19" s="12" t="n">
         <v>1.9</v>
       </c>
-      <c r="E19" s="11" t="n">
+      <c r="E19" s="12" t="n">
         <v>0.7</v>
       </c>
-      <c r="F19" s="11" t="n">
+      <c r="F19" s="12" t="n">
         <v>1.3</v>
       </c>
-      <c r="G19" s="11" t="n">
+      <c r="G19" s="12" t="n">
         <v>0.6</v>
       </c>
-      <c r="H19" s="11" t="n">
+      <c r="H19" s="12" t="n">
         <v>1.4</v>
       </c>
-      <c r="I19" s="11" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="J19" s="11" t="inlineStr">
+      <c r="I19" s="12" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="J19" s="12" t="inlineStr">
         <is>
           <t>Christmas week: airports packed with families.</t>
         </is>
       </c>
-      <c r="K19" s="11" t="inlineStr">
-        <is>
-          <t>placeholder</t>
-        </is>
-      </c>
+      <c r="K19" s="12" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L19" s="13" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="M19" s="13" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="N19" s="13" t="inlineStr">
+        <is>
+          <t>Winter demand keeps prices firm.</t>
+        </is>
+      </c>
+      <c r="O19" s="13" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P19" s="13" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="n">
+      <c r="A20" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>2031-01-06</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr">
+      <c r="C20" s="12" t="inlineStr">
         <is>
           <t>winter</t>
         </is>
       </c>
-      <c r="D20" s="11" t="n">
+      <c r="D20" s="12" t="n">
         <v>2.16</v>
       </c>
-      <c r="E20" s="11" t="n">
+      <c r="E20" s="12" t="n">
         <v>0.7</v>
       </c>
-      <c r="F20" s="11" t="n">
+      <c r="F20" s="12" t="n">
         <v>1.3</v>
       </c>
-      <c r="G20" s="11" t="n">
+      <c r="G20" s="12" t="n">
         <v>0.6</v>
       </c>
-      <c r="H20" s="11" t="n">
+      <c r="H20" s="12" t="n">
         <v>1.4</v>
       </c>
-      <c r="I20" s="11" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="J20" s="11" t="inlineStr">
+      <c r="I20" s="12" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="J20" s="12" t="inlineStr">
         <is>
           <t>Long haul opens: New York and Dubai. Your reputation is now public. What sort of airline are you?</t>
         </is>
       </c>
-      <c r="K20" s="11" t="inlineStr">
-        <is>
-          <t>placeholder</t>
-        </is>
-      </c>
+      <c r="K20" s="12" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L20" s="13" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="M20" s="13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="N20" s="13" t="inlineStr">
+        <is>
+          <t>Long haul opens: a 757 to New York burns in one trip what the whole airline burned in a week last September.</t>
+        </is>
+      </c>
+      <c r="O20" s="13" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P20" s="13" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="n">
+      <c r="A21" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B21" s="12" t="inlineStr">
         <is>
           <t>2031-01-13</t>
         </is>
       </c>
-      <c r="C21" s="15" t="inlineStr">
+      <c r="C21" s="12" t="inlineStr">
         <is>
           <t>winter</t>
         </is>
       </c>
-      <c r="D21" s="15" t="n">
+      <c r="D21" s="12" t="n">
         <v>2.17</v>
       </c>
-      <c r="E21" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" s="15" t="n">
+      <c r="E21" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="12" t="n">
         <v>0.6</v>
       </c>
-      <c r="H21" s="15" t="n">
+      <c r="H21" s="12" t="n">
         <v>1.4</v>
       </c>
-      <c r="I21" s="15" t="inlineStr">
+      <c r="I21" s="12" t="inlineStr">
         <is>
           <t>Icy runways: de-icing needed</t>
         </is>
       </c>
-      <c r="J21" s="15" t="inlineStr"/>
-      <c r="K21" s="15" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="J21" s="12" t="inlineStr"/>
+      <c r="K21" s="12" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L21" s="13" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="M21" s="13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="N21" s="13" t="n"/>
+      <c r="O21" s="13" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P21" s="13" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="n">
+      <c r="A22" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>2031-01-20</t>
         </is>
       </c>
-      <c r="C22" s="15" t="inlineStr">
+      <c r="C22" s="12" t="inlineStr">
         <is>
           <t>winter</t>
         </is>
       </c>
-      <c r="D22" s="15" t="n">
+      <c r="D22" s="12" t="n">
         <v>2.17</v>
       </c>
-      <c r="E22" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" s="15" t="n">
+      <c r="E22" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="12" t="n">
         <v>0.6</v>
       </c>
-      <c r="H22" s="15" t="n">
+      <c r="H22" s="12" t="n">
         <v>1.4</v>
       </c>
-      <c r="I22" s="15" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="J22" s="15" t="inlineStr"/>
-      <c r="K22" s="15" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="I22" s="12" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="J22" s="12" t="inlineStr"/>
+      <c r="K22" s="12" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L22" s="13" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="M22" s="13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="N22" s="13" t="n"/>
+      <c r="O22" s="13" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P22" s="13" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="n">
+      <c r="A23" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="15" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>2031-01-27</t>
         </is>
       </c>
-      <c r="C23" s="15" t="inlineStr">
+      <c r="C23" s="12" t="inlineStr">
         <is>
           <t>winter</t>
         </is>
       </c>
-      <c r="D23" s="15" t="n">
+      <c r="D23" s="12" t="n">
         <v>2.17</v>
       </c>
-      <c r="E23" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" s="15" t="n">
+      <c r="E23" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="12" t="n">
         <v>0.6</v>
       </c>
-      <c r="H23" s="15" t="n">
+      <c r="H23" s="12" t="n">
         <v>1.4</v>
       </c>
-      <c r="I23" s="15" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="J23" s="15" t="inlineStr"/>
-      <c r="K23" s="15" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="I23" s="12" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="J23" s="12" t="inlineStr"/>
+      <c r="K23" s="12" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L23" s="13" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="M23" s="13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="N23" s="13" t="inlineStr">
+        <is>
+          <t>Mild winter so far: prices easing slightly.</t>
+        </is>
+      </c>
+      <c r="O23" s="13" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P23" s="13" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="n">
+      <c r="A24" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="15" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>2031-02-03</t>
         </is>
       </c>
-      <c r="C24" s="15" t="inlineStr">
+      <c r="C24" s="12" t="inlineStr">
         <is>
           <t>winter</t>
         </is>
       </c>
-      <c r="D24" s="15" t="n">
+      <c r="D24" s="12" t="n">
         <v>2.17</v>
       </c>
-      <c r="E24" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" s="15" t="n">
+      <c r="E24" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="12" t="n">
         <v>0.6</v>
       </c>
-      <c r="H24" s="15" t="n">
+      <c r="H24" s="12" t="n">
         <v>1.4</v>
       </c>
-      <c r="I24" s="15" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="J24" s="15" t="inlineStr"/>
-      <c r="K24" s="15" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="I24" s="12" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="J24" s="12" t="inlineStr"/>
+      <c r="K24" s="12" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L24" s="13" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="M24" s="13" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="N24" s="13" t="n"/>
+      <c r="O24" s="13" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P24" s="13" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="n">
+      <c r="A25" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="15" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>2031-02-10</t>
         </is>
       </c>
-      <c r="C25" s="15" t="inlineStr">
+      <c r="C25" s="12" t="inlineStr">
         <is>
           <t>winter</t>
         </is>
       </c>
-      <c r="D25" s="15" t="n">
+      <c r="D25" s="12" t="n">
         <v>2.16</v>
       </c>
-      <c r="E25" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" s="15" t="n">
+      <c r="E25" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="12" t="n">
         <v>0.6</v>
       </c>
-      <c r="H25" s="15" t="n">
+      <c r="H25" s="12" t="n">
         <v>1.4</v>
       </c>
-      <c r="I25" s="15" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="J25" s="15" t="inlineStr"/>
-      <c r="K25" s="15" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="I25" s="12" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="J25" s="12" t="inlineStr"/>
+      <c r="K25" s="12" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L25" s="13" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="M25" s="13" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="N25" s="13" t="n"/>
+      <c r="O25" s="13" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P25" s="13" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="n">
+      <c r="A26" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="15" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t>2031-02-17</t>
         </is>
       </c>
-      <c r="C26" s="15" t="inlineStr">
+      <c r="C26" s="12" t="inlineStr">
         <is>
           <t>winter</t>
         </is>
       </c>
-      <c r="D26" s="15" t="n">
+      <c r="D26" s="12" t="n">
         <v>2.15</v>
       </c>
-      <c r="E26" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" s="15" t="n">
+      <c r="E26" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="12" t="n">
         <v>0.6</v>
       </c>
-      <c r="H26" s="15" t="n">
+      <c r="H26" s="12" t="n">
         <v>1.4</v>
       </c>
-      <c r="I26" s="15" t="inlineStr">
+      <c r="I26" s="12" t="inlineStr">
         <is>
           <t>Heavy snow at Geneva</t>
         </is>
       </c>
-      <c r="J26" s="15" t="inlineStr">
+      <c r="J26" s="12" t="inlineStr">
         <is>
           <t>February half-term: ski season at its peak.</t>
         </is>
       </c>
-      <c r="K26" s="15" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="K26" s="12" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L26" s="13" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="M26" s="13" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="N26" s="13" t="n"/>
+      <c r="O26" s="13" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P26" s="13" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="15" t="n">
+      <c r="A27" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="15" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>2031-02-24</t>
         </is>
       </c>
-      <c r="C27" s="15" t="inlineStr">
+      <c r="C27" s="12" t="inlineStr">
         <is>
           <t>winter</t>
         </is>
       </c>
-      <c r="D27" s="15" t="n">
+      <c r="D27" s="12" t="n">
         <v>2.14</v>
       </c>
-      <c r="E27" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F27" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" s="15" t="n">
+      <c r="E27" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="12" t="n">
         <v>0.6</v>
       </c>
-      <c r="H27" s="15" t="n">
+      <c r="H27" s="12" t="n">
         <v>1.4</v>
       </c>
-      <c r="I27" s="15" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="J27" s="15" t="inlineStr"/>
-      <c r="K27" s="15" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="I27" s="12" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="J27" s="12" t="inlineStr"/>
+      <c r="K27" s="12" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L27" s="13" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="M27" s="13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="N27" s="13" t="inlineStr">
+        <is>
+          <t>Spring: refineries switch to summer fuel, prices drift down.</t>
+        </is>
+      </c>
+      <c r="O27" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P27" s="13" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="n">
+      <c r="A28" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>2031-03-03</t>
         </is>
       </c>
-      <c r="C28" s="15" t="inlineStr">
+      <c r="C28" s="12" t="inlineStr">
         <is>
           <t>spring</t>
         </is>
       </c>
-      <c r="D28" s="15" t="n">
+      <c r="D28" s="12" t="n">
         <v>2.12</v>
       </c>
-      <c r="E28" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" s="15" t="n">
+      <c r="E28" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="12" t="n">
         <v>0.9</v>
       </c>
-      <c r="H28" s="15" t="n">
+      <c r="H28" s="12" t="n">
         <v>1.2</v>
       </c>
-      <c r="I28" s="15" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="J28" s="15" t="inlineStr"/>
-      <c r="K28" s="15" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="I28" s="12" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="J28" s="12" t="inlineStr"/>
+      <c r="K28" s="12" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L28" s="13" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="M28" s="13" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="N28" s="13" t="n"/>
+      <c r="O28" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P28" s="13" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="n">
+      <c r="A29" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="B29" s="12" t="inlineStr">
         <is>
           <t>2031-03-10</t>
         </is>
       </c>
-      <c r="C29" s="15" t="inlineStr">
+      <c r="C29" s="12" t="inlineStr">
         <is>
           <t>spring</t>
         </is>
       </c>
-      <c r="D29" s="15" t="n">
+      <c r="D29" s="12" t="n">
         <v>2.11</v>
       </c>
-      <c r="E29" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F29" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" s="15" t="n">
+      <c r="E29" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="12" t="n">
         <v>0.9</v>
       </c>
-      <c r="H29" s="15" t="n">
+      <c r="H29" s="12" t="n">
         <v>1.2</v>
       </c>
-      <c r="I29" s="15" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="J29" s="15" t="inlineStr"/>
-      <c r="K29" s="15" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="I29" s="12" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="J29" s="12" t="inlineStr"/>
+      <c r="K29" s="12" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L29" s="13" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="M29" s="13" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="N29" s="13" t="n"/>
+      <c r="O29" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P29" s="13" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="15" t="n">
+      <c r="A30" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="15" t="inlineStr">
+      <c r="B30" s="12" t="inlineStr">
         <is>
           <t>2031-03-17</t>
         </is>
       </c>
-      <c r="C30" s="15" t="inlineStr">
+      <c r="C30" s="12" t="inlineStr">
         <is>
           <t>spring</t>
         </is>
       </c>
-      <c r="D30" s="15" t="n">
+      <c r="D30" s="12" t="n">
         <v>2.09</v>
       </c>
-      <c r="E30" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F30" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" s="15" t="n">
+      <c r="E30" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="12" t="n">
         <v>0.9</v>
       </c>
-      <c r="H30" s="15" t="n">
+      <c r="H30" s="12" t="n">
         <v>1.2</v>
       </c>
-      <c r="I30" s="15" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="J30" s="15" t="inlineStr"/>
-      <c r="K30" s="15" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="I30" s="12" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="J30" s="12" t="inlineStr"/>
+      <c r="K30" s="12" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L30" s="13" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="M30" s="13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="N30" s="13" t="n"/>
+      <c r="O30" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P30" s="13" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="15" t="n">
+      <c r="A31" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="15" t="inlineStr">
+      <c r="B31" s="12" t="inlineStr">
         <is>
           <t>2031-03-24</t>
         </is>
       </c>
-      <c r="C31" s="15" t="inlineStr">
+      <c r="C31" s="12" t="inlineStr">
         <is>
           <t>spring</t>
         </is>
       </c>
-      <c r="D31" s="15" t="n">
+      <c r="D31" s="12" t="n">
         <v>2.07</v>
       </c>
-      <c r="E31" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F31" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G31" s="15" t="n">
+      <c r="E31" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="12" t="n">
         <v>0.9</v>
       </c>
-      <c r="H31" s="15" t="n">
+      <c r="H31" s="12" t="n">
         <v>1.2</v>
       </c>
-      <c r="I31" s="15" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="J31" s="15" t="inlineStr"/>
-      <c r="K31" s="15" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="I31" s="12" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="J31" s="12" t="inlineStr"/>
+      <c r="K31" s="12" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L31" s="13" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="M31" s="13" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="N31" s="13" t="inlineStr">
+        <is>
+          <t>Steady.</t>
+        </is>
+      </c>
+      <c r="O31" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P31" s="13" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="15" t="n">
+      <c r="A32" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="15" t="inlineStr">
+      <c r="B32" s="12" t="inlineStr">
         <is>
           <t>2031-03-31</t>
         </is>
       </c>
-      <c r="C32" s="15" t="inlineStr">
+      <c r="C32" s="12" t="inlineStr">
         <is>
           <t>spring</t>
         </is>
       </c>
-      <c r="D32" s="15" t="n">
+      <c r="D32" s="12" t="n">
         <v>2.06</v>
       </c>
-      <c r="E32" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" s="15" t="n">
+      <c r="E32" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="12" t="n">
         <v>0.9</v>
       </c>
-      <c r="H32" s="15" t="n">
+      <c r="H32" s="12" t="n">
         <v>1.2</v>
       </c>
-      <c r="I32" s="15" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="J32" s="15" t="inlineStr"/>
-      <c r="K32" s="15" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="I32" s="12" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="J32" s="12" t="inlineStr"/>
+      <c r="K32" s="12" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L32" s="13" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="M32" s="13" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="N32" s="13" t="n"/>
+      <c r="O32" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P32" s="13" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="15" t="n">
+      <c r="A33" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="15" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>2031-04-07</t>
         </is>
       </c>
-      <c r="C33" s="15" t="inlineStr">
+      <c r="C33" s="12" t="inlineStr">
         <is>
           <t>spring</t>
         </is>
       </c>
-      <c r="D33" s="15" t="n">
+      <c r="D33" s="12" t="n">
         <v>2.04</v>
       </c>
-      <c r="E33" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F33" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G33" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H33" s="15" t="n">
+      <c r="E33" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="12" t="n">
         <v>0.9</v>
       </c>
-      <c r="I33" s="15" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="J33" s="15" t="inlineStr"/>
-      <c r="K33" s="15" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="I33" s="12" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="J33" s="12" t="inlineStr"/>
+      <c r="K33" s="12" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L33" s="13" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="M33" s="13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N33" s="13" t="n"/>
+      <c r="O33" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P33" s="13" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="n">
+      <c r="A34" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="15" t="inlineStr">
+      <c r="B34" s="12" t="inlineStr">
         <is>
           <t>2031-04-14</t>
         </is>
       </c>
-      <c r="C34" s="15" t="inlineStr">
+      <c r="C34" s="12" t="inlineStr">
         <is>
           <t>spring</t>
         </is>
       </c>
-      <c r="D34" s="15" t="n">
+      <c r="D34" s="12" t="n">
         <v>2.02</v>
       </c>
-      <c r="E34" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F34" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H34" s="15" t="n">
+      <c r="E34" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="12" t="n">
         <v>0.9</v>
       </c>
-      <c r="I34" s="15" t="inlineStr">
+      <c r="I34" s="12" t="inlineStr">
         <is>
           <t>Volcanic ash cloud over Europe</t>
         </is>
       </c>
-      <c r="J34" s="15" t="inlineStr"/>
-      <c r="K34" s="15" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="J34" s="12" t="inlineStr"/>
+      <c r="K34" s="12" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L34" s="13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="M34" s="13" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="N34" s="13" t="n"/>
+      <c r="O34" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P34" s="13" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="n">
+      <c r="A35" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="15" t="inlineStr">
+      <c r="B35" s="12" t="inlineStr">
         <is>
           <t>2031-04-21</t>
         </is>
       </c>
-      <c r="C35" s="15" t="inlineStr">
+      <c r="C35" s="12" t="inlineStr">
         <is>
           <t>spring</t>
         </is>
       </c>
-      <c r="D35" s="15" t="n">
+      <c r="D35" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="E35" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F35" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H35" s="15" t="n">
+      <c r="E35" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="12" t="n">
         <v>0.9</v>
       </c>
-      <c r="I35" s="15" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="J35" s="15" t="inlineStr">
+      <c r="I35" s="12" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="J35" s="12" t="inlineStr">
         <is>
           <t>Easter holidays: leisure routes busy.</t>
         </is>
       </c>
-      <c r="K35" s="15" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="K35" s="12" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L35" s="13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="M35" s="13" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="N35" s="13" t="inlineStr">
+        <is>
+          <t>Quiet market.</t>
+        </is>
+      </c>
+      <c r="O35" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P35" s="13" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="15" t="n">
+      <c r="A36" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="15" t="inlineStr">
+      <c r="B36" s="12" t="inlineStr">
         <is>
           <t>2031-04-28</t>
         </is>
       </c>
-      <c r="C36" s="15" t="inlineStr">
+      <c r="C36" s="12" t="inlineStr">
         <is>
           <t>spring</t>
         </is>
       </c>
-      <c r="D36" s="15" t="n">
+      <c r="D36" s="12" t="n">
         <v>1.99</v>
       </c>
-      <c r="E36" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F36" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H36" s="15" t="n">
+      <c r="E36" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" s="12" t="n">
         <v>0.9</v>
       </c>
-      <c r="I36" s="15" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="J36" s="15" t="inlineStr"/>
-      <c r="K36" s="15" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="I36" s="12" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="J36" s="12" t="inlineStr"/>
+      <c r="K36" s="12" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L36" s="13" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="M36" s="13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="N36" s="13" t="n"/>
+      <c r="O36" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P36" s="13" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="15" t="n">
+      <c r="A37" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="15" t="inlineStr">
+      <c r="B37" s="12" t="inlineStr">
         <is>
           <t>2031-05-05</t>
         </is>
       </c>
-      <c r="C37" s="15" t="inlineStr">
+      <c r="C37" s="12" t="inlineStr">
         <is>
           <t>spring</t>
         </is>
       </c>
-      <c r="D37" s="15" t="n">
+      <c r="D37" s="12" t="n">
         <v>1.97</v>
       </c>
-      <c r="E37" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F37" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H37" s="15" t="n">
+      <c r="E37" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="I37" s="15" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="J37" s="15" t="inlineStr"/>
-      <c r="K37" s="15" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="I37" s="12" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="J37" s="12" t="inlineStr"/>
+      <c r="K37" s="12" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L37" s="13" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="M37" s="13" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="N37" s="13" t="n"/>
+      <c r="O37" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P37" s="13" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="15" t="n">
+      <c r="A38" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="15" t="inlineStr">
+      <c r="B38" s="12" t="inlineStr">
         <is>
           <t>2031-05-12</t>
         </is>
       </c>
-      <c r="C38" s="15" t="inlineStr">
+      <c r="C38" s="12" t="inlineStr">
         <is>
           <t>spring</t>
         </is>
       </c>
-      <c r="D38" s="15" t="n">
+      <c r="D38" s="12" t="n">
         <v>1.96</v>
       </c>
-      <c r="E38" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F38" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38" s="15" t="n">
+      <c r="E38" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="I38" s="15" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="J38" s="15" t="inlineStr"/>
-      <c r="K38" s="15" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="I38" s="12" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="J38" s="12" t="inlineStr"/>
+      <c r="K38" s="12" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L38" s="13" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="M38" s="13" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="N38" s="13" t="n"/>
+      <c r="O38" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P38" s="13" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="15" t="n">
+      <c r="A39" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="15" t="inlineStr">
+      <c r="B39" s="12" t="inlineStr">
         <is>
           <t>2031-05-19</t>
         </is>
       </c>
-      <c r="C39" s="15" t="inlineStr">
+      <c r="C39" s="12" t="inlineStr">
         <is>
           <t>spring</t>
         </is>
       </c>
-      <c r="D39" s="15" t="n">
+      <c r="D39" s="12" t="n">
         <v>1.95</v>
       </c>
-      <c r="E39" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F39" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H39" s="15" t="n">
+      <c r="E39" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="I39" s="15" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="J39" s="15" t="inlineStr"/>
-      <c r="K39" s="15" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="I39" s="12" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="J39" s="12" t="inlineStr"/>
+      <c r="K39" s="12" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L39" s="13" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="M39" s="13" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="N39" s="13" t="inlineStr">
+        <is>
+          <t>Summer travel season approaching: airlines buying ahead.</t>
+        </is>
+      </c>
+      <c r="O39" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P39" s="13" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="15" t="n">
+      <c r="A40" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="15" t="inlineStr">
+      <c r="B40" s="12" t="inlineStr">
         <is>
           <t>2031-05-26</t>
         </is>
       </c>
-      <c r="C40" s="15" t="inlineStr">
+      <c r="C40" s="12" t="inlineStr">
         <is>
           <t>spring</t>
         </is>
       </c>
-      <c r="D40" s="15" t="n">
+      <c r="D40" s="12" t="n">
         <v>1.95</v>
       </c>
-      <c r="E40" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F40" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H40" s="15" t="n">
+      <c r="E40" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="I40" s="15" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="J40" s="15" t="inlineStr"/>
-      <c r="K40" s="15" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="I40" s="12" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="J40" s="12" t="inlineStr"/>
+      <c r="K40" s="12" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L40" s="13" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="M40" s="13" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="N40" s="13" t="n"/>
+      <c r="O40" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P40" s="13" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="15" t="n">
+      <c r="A41" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="15" t="inlineStr">
+      <c r="B41" s="12" t="inlineStr">
         <is>
           <t>2031-06-02</t>
         </is>
       </c>
-      <c r="C41" s="15" t="inlineStr">
+      <c r="C41" s="12" t="inlineStr">
         <is>
           <t>summer</t>
         </is>
       </c>
-      <c r="D41" s="15" t="n">
+      <c r="D41" s="12" t="n">
         <v>1.94</v>
       </c>
-      <c r="E41" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F41" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G41" s="15" t="n">
+      <c r="E41" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="12" t="n">
         <v>1.3</v>
       </c>
-      <c r="H41" s="15" t="n">
+      <c r="H41" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="I41" s="15" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="J41" s="15" t="inlineStr">
+      <c r="I41" s="12" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="J41" s="12" t="inlineStr">
         <is>
           <t>Football final weekend.</t>
         </is>
       </c>
-      <c r="K41" s="15" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="K41" s="12" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L41" s="13" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="M41" s="13" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="N41" s="13" t="n"/>
+      <c r="O41" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P41" s="13" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="15" t="n">
+      <c r="A42" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="15" t="inlineStr">
+      <c r="B42" s="12" t="inlineStr">
         <is>
           <t>2031-06-09</t>
         </is>
       </c>
-      <c r="C42" s="15" t="inlineStr">
+      <c r="C42" s="12" t="inlineStr">
         <is>
           <t>summer</t>
         </is>
       </c>
-      <c r="D42" s="15" t="n">
+      <c r="D42" s="12" t="n">
         <v>1.94</v>
       </c>
-      <c r="E42" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F42" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G42" s="15" t="n">
+      <c r="E42" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="12" t="n">
         <v>1.3</v>
       </c>
-      <c r="H42" s="15" t="n">
+      <c r="H42" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="I42" s="15" t="inlineStr">
+      <c r="I42" s="12" t="inlineStr">
         <is>
           <t>Summer thunderstorms</t>
         </is>
       </c>
-      <c r="J42" s="15" t="inlineStr"/>
-      <c r="K42" s="15" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="J42" s="12" t="inlineStr"/>
+      <c r="K42" s="12" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L42" s="13" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="M42" s="13" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="N42" s="13" t="n"/>
+      <c r="O42" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P42" s="13" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="15" t="n">
+      <c r="A43" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="15" t="inlineStr">
+      <c r="B43" s="12" t="inlineStr">
         <is>
           <t>2031-06-16</t>
         </is>
       </c>
-      <c r="C43" s="15" t="inlineStr">
+      <c r="C43" s="12" t="inlineStr">
         <is>
           <t>summer</t>
         </is>
       </c>
-      <c r="D43" s="15" t="n">
+      <c r="D43" s="12" t="n">
         <v>1.95</v>
       </c>
-      <c r="E43" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" s="15" t="n">
+      <c r="E43" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="12" t="n">
         <v>1.3</v>
       </c>
-      <c r="H43" s="15" t="n">
+      <c r="H43" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="I43" s="15" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="J43" s="15" t="inlineStr"/>
-      <c r="K43" s="15" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="I43" s="12" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="J43" s="12" t="inlineStr"/>
+      <c r="K43" s="12" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L43" s="13" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="M43" s="13" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="N43" s="13" t="inlineStr">
+        <is>
+          <t>Prices creeping up through the summer.</t>
+        </is>
+      </c>
+      <c r="O43" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P43" s="13" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="15" t="n">
+      <c r="A44" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="15" t="inlineStr">
+      <c r="B44" s="12" t="inlineStr">
         <is>
           <t>2031-06-23</t>
         </is>
       </c>
-      <c r="C44" s="15" t="inlineStr">
+      <c r="C44" s="12" t="inlineStr">
         <is>
           <t>summer</t>
         </is>
       </c>
-      <c r="D44" s="15" t="n">
+      <c r="D44" s="12" t="n">
         <v>1.95</v>
       </c>
-      <c r="E44" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F44" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G44" s="15" t="n">
+      <c r="E44" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="12" t="n">
         <v>1.3</v>
       </c>
-      <c r="H44" s="15" t="n">
+      <c r="H44" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="I44" s="15" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="J44" s="15" t="inlineStr"/>
-      <c r="K44" s="15" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="I44" s="12" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="J44" s="12" t="inlineStr"/>
+      <c r="K44" s="12" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L44" s="13" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="M44" s="13" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="N44" s="13" t="n"/>
+      <c r="O44" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P44" s="13" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="15" t="n">
+      <c r="A45" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="15" t="inlineStr">
+      <c r="B45" s="12" t="inlineStr">
         <is>
           <t>2031-06-30</t>
         </is>
       </c>
-      <c r="C45" s="15" t="inlineStr">
+      <c r="C45" s="12" t="inlineStr">
         <is>
           <t>summer</t>
         </is>
       </c>
-      <c r="D45" s="15" t="n">
+      <c r="D45" s="12" t="n">
         <v>1.96</v>
       </c>
-      <c r="E45" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F45" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G45" s="15" t="n">
+      <c r="E45" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="12" t="n">
         <v>1.3</v>
       </c>
-      <c r="H45" s="15" t="n">
+      <c r="H45" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="I45" s="15" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="J45" s="15" t="inlineStr"/>
-      <c r="K45" s="15" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="I45" s="12" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="J45" s="12" t="inlineStr"/>
+      <c r="K45" s="12" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L45" s="13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M45" s="13" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="N45" s="13" t="n"/>
+      <c r="O45" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P45" s="13" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="15" t="n">
+      <c r="A46" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="15" t="inlineStr">
+      <c r="B46" s="12" t="inlineStr">
         <is>
           <t>2031-07-07</t>
         </is>
       </c>
-      <c r="C46" s="15" t="inlineStr">
+      <c r="C46" s="12" t="inlineStr">
         <is>
           <t>summer</t>
         </is>
       </c>
-      <c r="D46" s="15" t="n">
+      <c r="D46" s="12" t="n">
         <v>1.98</v>
       </c>
-      <c r="E46" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F46" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G46" s="15" t="n">
+      <c r="E46" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="12" t="n">
         <v>1.3</v>
       </c>
-      <c r="H46" s="15" t="n">
+      <c r="H46" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="I46" s="15" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="J46" s="15" t="inlineStr"/>
-      <c r="K46" s="15" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="I46" s="12" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="J46" s="12" t="inlineStr"/>
+      <c r="K46" s="12" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L46" s="13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="M46" s="13" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="N46" s="13" t="n"/>
+      <c r="O46" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P46" s="13" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="15" t="n">
+      <c r="A47" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="15" t="inlineStr">
+      <c r="B47" s="12" t="inlineStr">
         <is>
           <t>2031-07-14</t>
         </is>
       </c>
-      <c r="C47" s="15" t="inlineStr">
+      <c r="C47" s="12" t="inlineStr">
         <is>
           <t>summer</t>
         </is>
       </c>
-      <c r="D47" s="15" t="n">
+      <c r="D47" s="12" t="n">
         <v>1.99</v>
       </c>
-      <c r="E47" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F47" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G47" s="15" t="n">
+      <c r="E47" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" s="12" t="n">
         <v>1.3</v>
       </c>
-      <c r="H47" s="15" t="n">
+      <c r="H47" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="I47" s="15" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="J47" s="15" t="inlineStr"/>
-      <c r="K47" s="15" t="inlineStr">
-        <is>
-          <t>later</t>
+      <c r="I47" s="12" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="J47" s="12" t="inlineStr"/>
+      <c r="K47" s="12" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L47" s="13" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="M47" s="13" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="N47" s="13" t="inlineStr">
+        <is>
+          <t>Hurricane season in the Gulf of Mexico: refineries may shut.</t>
+        </is>
+      </c>
+      <c r="O47" s="13" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="P47" s="13" t="inlineStr">
+        <is>
+          <t>Weather: a quiet hurricane season would leave prices unchanged.</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="15" t="n">
+      <c r="A48" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="15" t="inlineStr">
+      <c r="B48" s="12" t="inlineStr">
         <is>
           <t>2031-07-21</t>
         </is>
       </c>
-      <c r="C48" s="15" t="inlineStr">
+      <c r="C48" s="12" t="inlineStr">
         <is>
           <t>summer</t>
         </is>
       </c>
-      <c r="D48" s="15" t="n">
+      <c r="D48" s="12" t="n">
         <v>2.01</v>
       </c>
-      <c r="E48" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F48" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G48" s="15" t="n">
+      <c r="E48" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="12" t="n">
         <v>1.3</v>
       </c>
-      <c r="H48" s="15" t="n">
+      <c r="H48" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="I48" s="15" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="J48" s="15" t="inlineStr">
+      <c r="I48" s="12" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="J48" s="12" t="inlineStr">
         <is>
           <t>Summer holidays begin: Barcelona packed.</t>
         </is>
       </c>
-      <c r="K48" s="15" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="K48" s="12" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L48" s="13" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="M48" s="13" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="N48" s="13" t="n"/>
+      <c r="O48" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P48" s="13" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="15" t="n">
+      <c r="A49" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="15" t="inlineStr">
+      <c r="B49" s="12" t="inlineStr">
         <is>
           <t>2031-07-28</t>
         </is>
       </c>
-      <c r="C49" s="15" t="inlineStr">
+      <c r="C49" s="12" t="inlineStr">
         <is>
           <t>summer</t>
         </is>
       </c>
-      <c r="D49" s="15" t="n">
+      <c r="D49" s="12" t="n">
         <v>2.04</v>
       </c>
-      <c r="E49" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F49" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G49" s="15" t="n">
+      <c r="E49" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="12" t="n">
         <v>1.3</v>
       </c>
-      <c r="H49" s="15" t="n">
+      <c r="H49" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="I49" s="15" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="J49" s="15" t="inlineStr"/>
-      <c r="K49" s="15" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="I49" s="12" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="J49" s="12" t="inlineStr"/>
+      <c r="K49" s="12" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L49" s="13" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="M49" s="13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="N49" s="13" t="n"/>
+      <c r="O49" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P49" s="13" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="15" t="n">
+      <c r="A50" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="15" t="inlineStr">
+      <c r="B50" s="12" t="inlineStr">
         <is>
           <t>2031-08-04</t>
         </is>
       </c>
-      <c r="C50" s="15" t="inlineStr">
+      <c r="C50" s="12" t="inlineStr">
         <is>
           <t>summer</t>
         </is>
       </c>
-      <c r="D50" s="15" t="n">
+      <c r="D50" s="12" t="n">
         <v>2.07</v>
       </c>
-      <c r="E50" s="15" t="n">
+      <c r="E50" s="12" t="n">
         <v>0.85</v>
       </c>
-      <c r="F50" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G50" s="15" t="n">
+      <c r="F50" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="12" t="n">
         <v>1.3</v>
       </c>
-      <c r="H50" s="15" t="n">
+      <c r="H50" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="I50" s="15" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="J50" s="15" t="inlineStr"/>
-      <c r="K50" s="15" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="I50" s="12" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="J50" s="12" t="inlineStr"/>
+      <c r="K50" s="12" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L50" s="13" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="M50" s="13" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="N50" s="13" t="n"/>
+      <c r="O50" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P50" s="13" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="15" t="n">
+      <c r="A51" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="15" t="inlineStr">
+      <c r="B51" s="12" t="inlineStr">
         <is>
           <t>2031-08-11</t>
         </is>
       </c>
-      <c r="C51" s="15" t="inlineStr">
+      <c r="C51" s="12" t="inlineStr">
         <is>
           <t>summer</t>
         </is>
       </c>
-      <c r="D51" s="15" t="n">
+      <c r="D51" s="12" t="n">
         <v>2.1</v>
       </c>
-      <c r="E51" s="15" t="n">
+      <c r="E51" s="12" t="n">
         <v>0.85</v>
       </c>
-      <c r="F51" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G51" s="15" t="n">
+      <c r="F51" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="12" t="n">
         <v>1.3</v>
       </c>
-      <c r="H51" s="15" t="n">
+      <c r="H51" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="I51" s="15" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="J51" s="15" t="inlineStr"/>
-      <c r="K51" s="15" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="I51" s="12" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="J51" s="12" t="inlineStr"/>
+      <c r="K51" s="12" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L51" s="13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="M51" s="13" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="N51" s="13" t="inlineStr">
+        <is>
+          <t>Prices rising into the autumn.</t>
+        </is>
+      </c>
+      <c r="O51" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P51" s="13" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="15" t="n">
+      <c r="A52" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="B52" s="15" t="inlineStr">
+      <c r="B52" s="12" t="inlineStr">
         <is>
           <t>2031-08-18</t>
         </is>
       </c>
-      <c r="C52" s="15" t="inlineStr">
+      <c r="C52" s="12" t="inlineStr">
         <is>
           <t>summer</t>
         </is>
       </c>
-      <c r="D52" s="15" t="n">
+      <c r="D52" s="12" t="n">
         <v>2.13</v>
       </c>
-      <c r="E52" s="15" t="n">
+      <c r="E52" s="12" t="n">
         <v>0.85</v>
       </c>
-      <c r="F52" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G52" s="15" t="n">
+      <c r="F52" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="12" t="n">
         <v>1.3</v>
       </c>
-      <c r="H52" s="15" t="n">
+      <c r="H52" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="I52" s="15" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="J52" s="15" t="inlineStr"/>
-      <c r="K52" s="15" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="I52" s="12" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="J52" s="12" t="inlineStr"/>
+      <c r="K52" s="12" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L52" s="13" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="M52" s="13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="N52" s="13" t="n"/>
+      <c r="O52" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P52" s="13" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="15" t="n">
+      <c r="A53" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="B53" s="15" t="inlineStr">
+      <c r="B53" s="12" t="inlineStr">
         <is>
           <t>2031-08-25</t>
         </is>
       </c>
-      <c r="C53" s="15" t="inlineStr">
+      <c r="C53" s="12" t="inlineStr">
         <is>
           <t>summer</t>
         </is>
       </c>
-      <c r="D53" s="15" t="n">
+      <c r="D53" s="12" t="n">
         <v>2.17</v>
       </c>
-      <c r="E53" s="15" t="n">
+      <c r="E53" s="12" t="n">
         <v>0.85</v>
       </c>
-      <c r="F53" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G53" s="15" t="n">
+      <c r="F53" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="12" t="n">
         <v>1.3</v>
       </c>
-      <c r="H53" s="15" t="n">
+      <c r="H53" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="I53" s="15" t="inlineStr">
+      <c r="I53" s="12" t="inlineStr">
         <is>
           <t>Autumn gales</t>
         </is>
       </c>
-      <c r="J53" s="15" t="inlineStr"/>
-      <c r="K53" s="15" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="J53" s="12" t="inlineStr"/>
+      <c r="K53" s="12" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L53" s="13" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="M53" s="13" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="N53" s="13" t="n"/>
+      <c r="O53" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P53" s="13" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="15" t="n">
@@ -24507,304 +25425,339 @@
       <c r="N18" s="14" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>blogger</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>2031-01-15</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C19" s="12" t="inlineStr">
         <is>
           <t>The travel blogger</t>
         </is>
       </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="D19" s="12" t="inlineStr">
         <is>
           <t>A famous blogger books a seat.</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr"/>
-      <c r="F19" s="11" t="inlineStr"/>
-      <c r="G19" s="11" t="inlineStr"/>
-      <c r="H19" s="11" t="inlineStr"/>
-      <c r="I19" s="11" t="inlineStr"/>
-      <c r="J19" s="11" t="inlineStr"/>
-      <c r="K19" s="11" t="inlineStr">
-        <is>
-          <t>options: VIP £400 +1★ / upgrade £150 +½★ / treat as everyone</t>
-        </is>
-      </c>
-      <c r="L19" s="11" t="inlineStr"/>
-      <c r="M19" s="11" t="inlineStr">
-        <is>
-          <t>placeholder</t>
-        </is>
-      </c>
-      <c r="N19" s="14" t="inlineStr">
+      <c r="E19" s="12" t="inlineStr"/>
+      <c r="F19" s="12" t="inlineStr"/>
+      <c r="G19" s="12" t="inlineStr"/>
+      <c r="H19" s="12" t="inlineStr"/>
+      <c r="I19" s="12" t="inlineStr"/>
+      <c r="J19" s="12" t="inlineStr"/>
+      <c r="K19" s="12" t="inlineStr">
+        <is>
+          <t>A famous travel blogger is on your Dublin flight. VIP treatment (a quarter of a day's profit, +1★) · upgrade and a bottle of water (a tenth, +½★) · treat as anyone (−½★ if the flight is late).</t>
+        </is>
+      </c>
+      <c r="L19" s="12" t="inlineStr"/>
+      <c r="M19" s="12" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="N19" s="13" t="inlineStr">
         <is>
           <t>VIP 0.25 / upgrade 0.1</t>
         </is>
       </c>
+      <c r="O19" s="13" t="n"/>
+      <c r="P19" s="13" t="n"/>
+      <c r="Q19" s="13" t="n"/>
+      <c r="R19" s="13" t="n"/>
+      <c r="S19" s="13" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>fog</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>2031-01-22</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr">
+      <c r="C20" s="12" t="inlineStr">
         <is>
           <t>Fog at London</t>
         </is>
       </c>
-      <c r="D20" s="11" t="inlineStr">
+      <c r="D20" s="12" t="inlineStr">
         <is>
           <t>Runway closed to normal take-offs.</t>
         </is>
       </c>
-      <c r="E20" s="11" t="inlineStr"/>
-      <c r="F20" s="11" t="inlineStr"/>
-      <c r="G20" s="11" t="inlineStr"/>
-      <c r="H20" s="11" t="inlineStr"/>
-      <c r="I20" s="11" t="inlineStr"/>
-      <c r="J20" s="11" t="inlineStr"/>
-      <c r="K20" s="11" t="inlineStr">
-        <is>
-          <t>options: instrument crew £350 / wait DELAYED / cancel refund</t>
-        </is>
-      </c>
-      <c r="L20" s="11" t="inlineStr"/>
-      <c r="M20" s="11" t="inlineStr">
-        <is>
-          <t>placeholder</t>
-        </is>
-      </c>
-      <c r="N20" s="14" t="inlineStr">
+      <c r="E20" s="12" t="inlineStr"/>
+      <c r="F20" s="12" t="inlineStr"/>
+      <c r="G20" s="12" t="inlineStr"/>
+      <c r="H20" s="12" t="inlineStr"/>
+      <c r="I20" s="12" t="inlineStr"/>
+      <c r="J20" s="12" t="inlineStr"/>
+      <c r="K20" s="12" t="inlineStr">
+        <is>
+          <t>Fog at Heathrow: only instrument-rated crews can land. Hire one for the week (a fifth of a day's profit; everything flies) · wait for it to clear (lose the morning's flights) · cancel the day (−½★).</t>
+        </is>
+      </c>
+      <c r="L20" s="12" t="inlineStr"/>
+      <c r="M20" s="12" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="N20" s="13" t="inlineStr">
         <is>
           <t>instrument crew 0.2</t>
         </is>
       </c>
+      <c r="O20" s="13" t="n"/>
+      <c r="P20" s="13" t="n"/>
+      <c r="Q20" s="13" t="n"/>
+      <c r="R20" s="13" t="n"/>
+      <c r="S20" s="13" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="inlineStr">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>half_term</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B21" s="12" t="inlineStr">
         <is>
           <t>2031-02-18</t>
         </is>
       </c>
-      <c r="C21" s="11" t="inlineStr">
+      <c r="C21" s="12" t="inlineStr">
         <is>
           <t>February half-term</t>
         </is>
       </c>
-      <c r="D21" s="11" t="inlineStr">
+      <c r="D21" s="12" t="inlineStr">
         <is>
           <t>Ski season at its peak.</t>
         </is>
       </c>
-      <c r="E21" s="11" t="inlineStr"/>
-      <c r="F21" s="11" t="inlineStr"/>
-      <c r="G21" s="11" t="inlineStr"/>
-      <c r="H21" s="11" t="inlineStr"/>
-      <c r="I21" s="11" t="inlineStr"/>
-      <c r="J21" s="11" t="inlineStr"/>
-      <c r="K21" s="11" t="inlineStr">
-        <is>
-          <t>gva +30 for the week</t>
-        </is>
-      </c>
-      <c r="L21" s="11" t="inlineStr"/>
-      <c r="M21" s="11" t="inlineStr">
-        <is>
-          <t>placeholder</t>
-        </is>
-      </c>
-      <c r="N21" s="14" t="n"/>
+      <c r="E21" s="12" t="inlineStr"/>
+      <c r="F21" s="12" t="inlineStr"/>
+      <c r="G21" s="12" t="inlineStr"/>
+      <c r="H21" s="12" t="inlineStr"/>
+      <c r="I21" s="12" t="inlineStr"/>
+      <c r="J21" s="12" t="inlineStr"/>
+      <c r="K21" s="12" t="inlineStr">
+        <is>
+          <t>Half-term: skiers everywhere. Geneva +30 for the week; no choice, a headline.</t>
+        </is>
+      </c>
+      <c r="L21" s="12" t="inlineStr"/>
+      <c r="M21" s="12" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="N21" s="13" t="n"/>
+      <c r="O21" s="13" t="n"/>
+      <c r="P21" s="13" t="n"/>
+      <c r="Q21" s="13" t="n"/>
+      <c r="R21" s="13" t="n"/>
+      <c r="S21" s="13" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>ash_cloud</t>
         </is>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>2031-04-15</t>
         </is>
       </c>
-      <c r="C22" s="11" t="inlineStr">
+      <c r="C22" s="12" t="inlineStr">
         <is>
           <t>Ash cloud</t>
         </is>
       </c>
-      <c r="D22" s="11" t="inlineStr">
+      <c r="D22" s="12" t="inlineStr">
         <is>
           <t>Volcanic ash drifts over Europe.</t>
         </is>
       </c>
-      <c r="E22" s="11" t="inlineStr"/>
-      <c r="F22" s="11" t="inlineStr"/>
-      <c r="G22" s="11" t="inlineStr"/>
-      <c r="H22" s="11" t="inlineStr"/>
-      <c r="I22" s="11" t="inlineStr"/>
-      <c r="J22" s="11" t="inlineStr"/>
-      <c r="K22" s="11" t="inlineStr">
-        <is>
-          <t>options: cancel +½★ refund / long way round £600 DELAYED / fly −1★</t>
-        </is>
-      </c>
-      <c r="L22" s="11" t="inlineStr"/>
-      <c r="M22" s="11" t="inlineStr">
-        <is>
-          <t>placeholder</t>
-        </is>
-      </c>
-      <c r="N22" s="14" t="inlineStr">
+      <c r="E22" s="12" t="inlineStr"/>
+      <c r="F22" s="12" t="inlineStr"/>
+      <c r="G22" s="12" t="inlineStr"/>
+      <c r="H22" s="12" t="inlineStr"/>
+      <c r="I22" s="12" t="inlineStr"/>
+      <c r="J22" s="12" t="inlineStr"/>
+      <c r="K22" s="12" t="inlineStr">
+        <is>
+          <t>An Icelandic volcano: ash grounds Europe for five days. Cancel everything (+½★ for honesty; no revenue, no fuel burned) · fly the long way round (0.4 of a day's profit a day; flights delayed, −½★) · fly anyway (−1★, and a fine).</t>
+        </is>
+      </c>
+      <c r="L22" s="12" t="inlineStr"/>
+      <c r="M22" s="12" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="N22" s="13" t="inlineStr">
         <is>
           <t>long way round 0.4</t>
         </is>
       </c>
+      <c r="O22" s="13" t="n"/>
+      <c r="P22" s="13" t="n"/>
+      <c r="Q22" s="13" t="n"/>
+      <c r="R22" s="13" t="n"/>
+      <c r="S22" s="13" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t>fees_rise</t>
         </is>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>2031-04-02</t>
         </is>
       </c>
-      <c r="C23" s="11" t="inlineStr">
+      <c r="C23" s="12" t="inlineStr">
         <is>
           <t>Landing fees rise</t>
         </is>
       </c>
-      <c r="D23" s="11" t="inlineStr">
+      <c r="D23" s="12" t="inlineStr">
         <is>
           <t>Heathrow raises landing fees.</t>
         </is>
       </c>
-      <c r="E23" s="11" t="inlineStr"/>
-      <c r="F23" s="11" t="inlineStr"/>
-      <c r="G23" s="11" t="inlineStr"/>
-      <c r="H23" s="11" t="inlineStr"/>
-      <c r="I23" s="11" t="inlineStr"/>
-      <c r="J23" s="11" t="inlineStr"/>
-      <c r="K23" s="11" t="inlineStr">
-        <is>
-          <t>options: pay (0.3 of a day) / night slots −½★ / two-season deal (0.2 of a day) / MOVE TO LUTON: home airport becomes LTN for good — cheaper landings, fewer passengers (D32)</t>
-        </is>
-      </c>
-      <c r="L23" s="11" t="inlineStr"/>
-      <c r="M23" s="11" t="inlineStr">
-        <is>
-          <t>placeholder</t>
-        </is>
-      </c>
-      <c r="N23" s="14" t="inlineStr">
+      <c r="E23" s="12" t="inlineStr"/>
+      <c r="F23" s="12" t="inlineStr"/>
+      <c r="G23" s="12" t="inlineStr"/>
+      <c r="H23" s="12" t="inlineStr"/>
+      <c r="I23" s="12" t="inlineStr"/>
+      <c r="J23" s="12" t="inlineStr"/>
+      <c r="K23" s="12" t="inlineStr">
+        <is>
+          <t>Heathrow raises landing fees by £50 a landing. Pay (0.3 of a day's profit a week, permanent) · move to night slots (−½★; fees unchanged) · take a two-season deal (0.2 of a day a week, fees frozen) · MOVE TO LUTON for good (landing £40, −5% passengers, 40-min turnarounds; D32).</t>
+        </is>
+      </c>
+      <c r="L23" s="12" t="inlineStr"/>
+      <c r="M23" s="12" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="N23" s="13" t="inlineStr">
         <is>
           <t>pay 0.3 / deal 0.2 / move to Luton 0</t>
         </is>
       </c>
+      <c r="O23" s="13" t="n"/>
+      <c r="P23" s="13" t="n"/>
+      <c r="Q23" s="13" t="n"/>
+      <c r="R23" s="13" t="n"/>
+      <c r="S23" s="13" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="A24" s="12" t="inlineStr">
         <is>
           <t>easter</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>2031-04-19</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
+      <c r="C24" s="12" t="inlineStr">
         <is>
           <t>Easter holidays</t>
         </is>
       </c>
-      <c r="D24" s="11" t="inlineStr">
+      <c r="D24" s="12" t="inlineStr">
         <is>
           <t>Leisure routes busy.</t>
         </is>
       </c>
-      <c r="E24" s="11" t="inlineStr"/>
-      <c r="F24" s="11" t="inlineStr"/>
-      <c r="G24" s="11" t="inlineStr"/>
-      <c r="H24" s="11" t="inlineStr"/>
-      <c r="I24" s="11" t="inlineStr"/>
-      <c r="J24" s="11" t="inlineStr"/>
-      <c r="K24" s="11" t="inlineStr">
-        <is>
-          <t>leisureMult 1.2 for two weeks</t>
-        </is>
-      </c>
-      <c r="L24" s="11" t="inlineStr"/>
-      <c r="M24" s="11" t="inlineStr">
-        <is>
-          <t>placeholder</t>
-        </is>
-      </c>
-      <c r="N24" s="14" t="n"/>
+      <c r="E24" s="12" t="inlineStr"/>
+      <c r="F24" s="12" t="inlineStr"/>
+      <c r="G24" s="12" t="inlineStr"/>
+      <c r="H24" s="12" t="inlineStr"/>
+      <c r="I24" s="12" t="inlineStr"/>
+      <c r="J24" s="12" t="inlineStr"/>
+      <c r="K24" s="12" t="inlineStr">
+        <is>
+          <t>Easter: leisure routes +20% for two weeks. Headline only.</t>
+        </is>
+      </c>
+      <c r="L24" s="12" t="inlineStr"/>
+      <c r="M24" s="12" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="N24" s="13" t="n"/>
+      <c r="O24" s="13" t="n"/>
+      <c r="P24" s="13" t="n"/>
+      <c r="Q24" s="13" t="n"/>
+      <c r="R24" s="13" t="n"/>
+      <c r="S24" s="13" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>mystery_shopper</t>
         </is>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>2031-05-13</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr">
+      <c r="C25" s="12" t="inlineStr">
         <is>
           <t>Mystery shopper report</t>
         </is>
       </c>
-      <c r="D25" s="11" t="inlineStr">
+      <c r="D25" s="12" t="inlineStr">
         <is>
           <t>Red Kite's shoppers publish a report.</t>
         </is>
       </c>
-      <c r="E25" s="11" t="inlineStr"/>
-      <c r="F25" s="11" t="inlineStr"/>
-      <c r="G25" s="11" t="inlineStr"/>
-      <c r="H25" s="11" t="inlineStr"/>
-      <c r="I25" s="11" t="inlineStr"/>
-      <c r="J25" s="11" t="inlineStr"/>
-      <c r="K25" s="11" t="inlineStr">
-        <is>
-          <t>options: fix all £600 +1★ / cheap fixes £200 +½★ / ignore −½★</t>
-        </is>
-      </c>
-      <c r="L25" s="11" t="inlineStr"/>
-      <c r="M25" s="11" t="inlineStr">
-        <is>
-          <t>placeholder</t>
-        </is>
-      </c>
-      <c r="N25" s="14" t="inlineStr">
+      <c r="E25" s="12" t="inlineStr"/>
+      <c r="F25" s="12" t="inlineStr"/>
+      <c r="G25" s="12" t="inlineStr"/>
+      <c r="H25" s="12" t="inlineStr"/>
+      <c r="I25" s="12" t="inlineStr"/>
+      <c r="J25" s="12" t="inlineStr"/>
+      <c r="K25" s="12" t="inlineStr">
+        <is>
+          <t>Red Kite's mystery shoppers publish a report on your airline. Fix everything they found (0.4 of a day's profit, +1★) · the cheap fixes (0.15 of a day, +½★) · ignore it (−½★).</t>
+        </is>
+      </c>
+      <c r="L25" s="12" t="inlineStr"/>
+      <c r="M25" s="12" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="N25" s="13" t="inlineStr">
         <is>
           <t>fix all 0.4 / cheap 0.15</t>
         </is>
       </c>
+      <c r="O25" s="13" t="n"/>
+      <c r="P25" s="13" t="n"/>
+      <c r="Q25" s="13" t="n"/>
+      <c r="R25" s="13" t="n"/>
+      <c r="S25" s="13" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
@@ -25051,44 +26004,49 @@
       <c r="N31" s="14" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="inlineStr">
+      <c r="A32" s="13" t="inlineStr">
         <is>
           <t>long_haul_open</t>
         </is>
       </c>
-      <c r="B32" s="18" t="inlineStr">
+      <c r="B32" s="13" t="inlineStr">
         <is>
           <t>2031-01-06</t>
         </is>
       </c>
-      <c r="C32" s="18" t="inlineStr">
+      <c r="C32" s="13" t="inlineStr">
         <is>
           <t>Long haul opens</t>
         </is>
       </c>
-      <c r="D32" s="18" t="inlineStr">
+      <c r="D32" s="13" t="inlineStr">
         <is>
           <t>New York and Dubai. The Dreamliner and the 757 are in the shop, to lease. Your star rating is now public, and passengers ask what sort of airline you are.</t>
         </is>
       </c>
-      <c r="E32" s="18" t="n"/>
-      <c r="F32" s="18" t="n"/>
-      <c r="G32" s="18" t="n"/>
-      <c r="H32" s="18" t="n"/>
-      <c r="I32" s="18" t="n"/>
-      <c r="J32" s="18" t="n"/>
-      <c r="K32" s="18" t="inlineStr">
-        <is>
-          <t>reputation revealed at banked level; airline type choice; local time shown (D24, D30)</t>
-        </is>
-      </c>
-      <c r="L32" s="18" t="n"/>
-      <c r="M32" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
-      <c r="N32" s="18" t="n"/>
+      <c r="E32" s="13" t="n"/>
+      <c r="F32" s="13" t="n"/>
+      <c r="G32" s="13" t="n"/>
+      <c r="H32" s="13" t="n"/>
+      <c r="I32" s="13" t="n"/>
+      <c r="J32" s="13" t="n"/>
+      <c r="K32" s="13" t="inlineStr">
+        <is>
+          <t>New York and Dubai. The 757 and the 787 are in the shop, to lease. Your star rating is now public, and you choose what sort of airline you are: Premium, Full Service or Value.</t>
+        </is>
+      </c>
+      <c r="L32" s="13" t="n"/>
+      <c r="M32" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="N32" s="13" t="n"/>
+      <c r="O32" s="13" t="n"/>
+      <c r="P32" s="13" t="n"/>
+      <c r="Q32" s="13" t="n"/>
+      <c r="R32" s="13" t="n"/>
+      <c r="S32" s="13" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="18" t="inlineStr">
@@ -26021,38 +26979,38 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>2031-01-06</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>CHAPTER 2: long haul, overnight rotations, time zones; leasing; reputation revealed; airline type; Value extras; crew cost by type; Captain's challenges; hunts</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr"/>
-      <c r="D12" s="14" t="inlineStr">
-        <is>
-          <t>placeholder</t>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>CHAPTER 2 set-up (days 127–131, one at a time): long haul same-day to 6,000 km (New York, Dubai); the 757 and 787 to lease; arrival in local time; reputation revealed at the banked level and ×5% a half-star; the airline type chosen (light profiles); Value's bag fee; £500 second crew per long-haul service; Captain's challenge 1. Then weeks, then months from February.</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr"/>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>2031-08-31</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>Chapter 2 review</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="inlineStr"/>
-      <c r="D13" s="14" t="inlineStr">
-        <is>
-          <t>placeholder</t>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>Chapter 2 review: year-1 accounts (show what to add, the mean), hunt h1, the full airline-type profiles arrive, next investment (buying opens in chapter 3)</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr"/>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
         </is>
       </c>
     </row>
@@ -26580,58 +27538,58 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="n">
+      <c r="A3" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Going long</t>
         </is>
       </c>
-      <c r="C3" s="14" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>2031-01-06</t>
         </is>
       </c>
-      <c r="D3" s="14" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>2031-08-31</t>
         </is>
       </c>
-      <c r="E3" s="14" t="n">
+      <c r="E3" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="F3" s="14" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>week → month</t>
         </is>
       </c>
-      <c r="G3" s="14" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>2031-08-31</t>
         </is>
       </c>
-      <c r="H3" s="14" t="inlineStr">
+      <c r="H3" s="13" t="inlineStr">
         <is>
           <t>Long haul: overnight rotations, time zones; the 787 by lease; reputation revealed; airline type chosen</t>
         </is>
       </c>
-      <c r="I3" s="14" t="inlineStr">
+      <c r="I3" s="13" t="inlineStr">
         <is>
           <t>leasing (standing); reputation as demand multiplier; airline type; extras (Value only); Captain's challenge one a term; hunts</t>
         </is>
       </c>
-      <c r="J3" s="14" t="n">
+      <c r="J3" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="K3" s="14" t="inlineStr">
+      <c r="K3" s="13" t="inlineStr">
         <is>
           <t>big numbers (£k, £m) and estimating; revenue ÷ 2 for overnight rotations; time across zones; rent against earnings</t>
         </is>
       </c>
-      <c r="L3" s="14" t="inlineStr">
-        <is>
-          <t>placeholder</t>
+      <c r="L3" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
         </is>
       </c>
     </row>
@@ -26933,82 +27891,82 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>h1</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>2031-08-31</t>
         </is>
       </c>
-      <c r="C2" s="14" t="n">
+      <c r="C2" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="D2" s="14" t="inlineStr">
+      <c r="D2" s="13" t="inlineStr">
         <is>
           <t>Year-1 accounts</t>
         </is>
       </c>
-      <c r="E2" s="14" t="inlineStr">
-        <is>
-          <t>One route's revenue total is £1,000 too high (a × with a slipped digit)</t>
-        </is>
-      </c>
-      <c r="F2" s="14" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
+        <is>
+          <t>Year-1 accounts, August 2031: the New York line shows 200 passengers × £510 = £104,000 (should be £102,000: a × with a slipped digit). The pupil re-multiplies and finds £2,000 too much.</t>
+        </is>
+      </c>
+      <c r="F2" s="13" t="inlineStr">
         <is>
           <t>Re-multiply the route's passengers × fare and compare</t>
         </is>
       </c>
-      <c r="G2" s="14" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
         <is>
           <t>The cash forecast for chapter 3 starts £1,000 out</t>
         </is>
       </c>
-      <c r="H2" s="14" t="inlineStr">
-        <is>
-          <t>placeholder</t>
+      <c r="H2" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>h2</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>2031-04-21</t>
         </is>
       </c>
-      <c r="C3" s="14" t="n">
+      <c r="C3" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="D3" s="14" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>Fuel invoice</t>
         </is>
       </c>
-      <c r="E3" s="14" t="inlineStr">
-        <is>
-          <t>Litres × price does not match the total</t>
-        </is>
-      </c>
-      <c r="F3" s="14" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>Fuel invoice, April 2031: 14,000 L at £2.04 shown as £29,560; litres × price is £28,560. The pupil re-multiplies and finds £1,000 too much.</t>
+        </is>
+      </c>
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>Multiply litres by price</t>
         </is>
       </c>
-      <c r="G3" s="14" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>Overpaid; corrected next month if found later</t>
         </is>
       </c>
-      <c r="H3" s="14" t="inlineStr">
-        <is>
-          <t>placeholder</t>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
         </is>
       </c>
     </row>
@@ -27212,6 +28170,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="17" t="inlineStr">
         <is>
@@ -28979,7 +29938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D102"/>
+  <dimension ref="A1:D119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -31085,6 +32044,346 @@
       </c>
       <c r="C102" s="13" t="inlineStr"/>
       <c r="D102" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="13" t="inlineStr">
+        <is>
+          <t>longHaulFromKm</t>
+        </is>
+      </c>
+      <c r="B103" s="13" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C103" s="13" t="inlineStr">
+        <is>
+          <t>D68: a route over this distance is long haul: turnaround away longHaulTurnaroundMin, a flat second-crew charge longHaulCrewCost per service, arrival shown in local time.</t>
+        </is>
+      </c>
+      <c r="D103" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="13" t="inlineStr">
+        <is>
+          <t>longHaulTurnaroundMin</t>
+        </is>
+      </c>
+      <c r="B104" s="13" t="n">
+        <v>120</v>
+      </c>
+      <c r="C104" s="13" t="inlineStr"/>
+      <c r="D104" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="13" t="inlineStr">
+        <is>
+          <t>longHaulCrewCost</t>
+        </is>
+      </c>
+      <c r="B105" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="C105" s="13" t="inlineStr">
+        <is>
+          <t>D73: flat second crew per long-haul service from 2031-01-06.</t>
+        </is>
+      </c>
+      <c r="D105" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="13" t="inlineStr">
+        <is>
+          <t>longHaulSameDayMaxKm</t>
+        </is>
+      </c>
+      <c r="B106" s="13" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C106" s="13" t="inlineStr">
+        <is>
+          <t>D68: up to this distance a long-haul service goes out and back in one day (06:30 to about 21:30). Beyond it the route is an overnight rotation (Routes.rotation = overnight): out on day 1, back on day 2; the plane earns every second day and the day cost is paid both days. First overnight route: Delhi (June 2031).</t>
+        </is>
+      </c>
+      <c r="D106" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="13" t="inlineStr">
+        <is>
+          <t>reputationPerHalfStar</t>
+        </is>
+      </c>
+      <c r="B107" s="13" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C107" s="13" t="inlineStr">
+        <is>
+          <t>D69: from 2031-01-06, demand on every route × (1 + 0.05 × half-stars above or below 3). Five stars +20%, one star −20%.</t>
+        </is>
+      </c>
+      <c r="D107" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="13" t="inlineStr">
+        <is>
+          <t>reputationBankedFromAutumn</t>
+        </is>
+      </c>
+      <c r="B108" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="C108" s="13" t="inlineStr">
+        <is>
+          <t>D30: the autumn's star changes are applied silently and revealed on 2031-01-06.</t>
+        </is>
+      </c>
+      <c r="D108" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="13" t="inlineStr">
+        <is>
+          <t>airlineTypeMode</t>
+        </is>
+      </c>
+      <c r="B109" s="13" t="inlineStr">
+        <is>
+          <t>light</t>
+        </is>
+      </c>
+      <c r="C109" s="13" t="inlineStr">
+        <is>
+          <t>D70: from 2031-01-06 the pupil chooses Premium / Full Service / Value. Light profiles until the August review: Premium = two higher fare options on every route and stars gained 1.5× faster; Value = one lower fare option on every route and the bag fee (extrasBag*); Full Service = unchanged. Full profiles (crew cost by type, demand effects, free snacks) at the 2031-08-31 review (placeholder).</t>
+        </is>
+      </c>
+      <c r="D109" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="13" t="inlineStr">
+        <is>
+          <t>premiumExtraFareSteps</t>
+        </is>
+      </c>
+      <c r="B110" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C110" s="13" t="inlineStr">
+        <is>
+          <t>Premium: the Routes demand table's two steps above today's top fare option become available.</t>
+        </is>
+      </c>
+      <c r="D110" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="13" t="inlineStr">
+        <is>
+          <t>valueLowerFareSteps</t>
+        </is>
+      </c>
+      <c r="B111" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C111" s="13" t="inlineStr">
+        <is>
+          <t>Value: one step below today's lowest fare option becomes available (demand table extended downwards).</t>
+        </is>
+      </c>
+      <c r="D111" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="13" t="inlineStr">
+        <is>
+          <t>premiumStarRate</t>
+        </is>
+      </c>
+      <c r="B112" s="13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C112" s="13" t="inlineStr">
+        <is>
+          <t>Premium gains and loses stars 1.5× as fast; Value 0.75×; Full Service 1×.</t>
+        </is>
+      </c>
+      <c r="D112" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="13" t="inlineStr">
+        <is>
+          <t>valueStarRate</t>
+        </is>
+      </c>
+      <c r="B113" s="13" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C113" s="13" t="inlineStr"/>
+      <c r="D113" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="13" t="inlineStr">
+        <is>
+          <t>extrasBagFee</t>
+        </is>
+      </c>
+      <c r="B114" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="C114" s="13" t="inlineStr">
+        <is>
+          <t>D71: Value airline only, from 2031-01-06. Bag fee £20.</t>
+        </is>
+      </c>
+      <c r="D114" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="13" t="inlineStr">
+        <is>
+          <t>extrasBagTakeUp</t>
+        </is>
+      </c>
+      <c r="B115" s="13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C115" s="13" t="inlineStr">
+        <is>
+          <t>Four in ten passengers pay it. Revenue = passengers × 0.4 × £20, a modelling line after the first time (one hand sum on the first long-haul week).</t>
+        </is>
+      </c>
+      <c r="D115" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="13" t="inlineStr">
+        <is>
+          <t>timeZonesFromDate</t>
+        </is>
+      </c>
+      <c r="B116" s="13" t="inlineStr">
+        <is>
+          <t>2031-01-06</t>
+        </is>
+      </c>
+      <c r="C116" s="13" t="inlineStr">
+        <is>
+          <t>D24: arrival cards show local time from long haul: London time ± the route's utc offset.</t>
+        </is>
+      </c>
+      <c r="D116" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="13" t="inlineStr">
+        <is>
+          <t>chapter2SetUpDays</t>
+        </is>
+      </c>
+      <c r="B117" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C117" s="13" t="inlineStr">
+        <is>
+          <t>Chapter 2 opens with five days played one at a time (Calendar days 127–131), then weeks, then months from February.</t>
+        </is>
+      </c>
+      <c r="D117" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="13" t="inlineStr">
+        <is>
+          <t>captainsChallengeFirst</t>
+        </is>
+      </c>
+      <c r="B118" s="13" t="inlineStr">
+        <is>
+          <t>2031-01-06</t>
+        </is>
+      </c>
+      <c r="C118" s="13" t="inlineStr">
+        <is>
+          <t>D36: one a term, optional, with a reward. Challenges 1 and 2 live.</t>
+        </is>
+      </c>
+      <c r="D118" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="13" t="inlineStr">
+        <is>
+          <t>hunt1</t>
+        </is>
+      </c>
+      <c r="B119" s="13" t="inlineStr">
+        <is>
+          <t>2031-04-21</t>
+        </is>
+      </c>
+      <c r="C119" s="13" t="inlineStr">
+        <is>
+          <t>D39: first hunts live — h2 (fuel invoice) in the spring run, h1 (year-1 accounts) at the August review.</t>
+        </is>
+      </c>
+      <c r="D119" s="13" t="inlineStr">
         <is>
           <t>live</t>
         </is>
@@ -31504,7 +32803,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="17" t="inlineStr">
         <is>
@@ -31523,7 +32821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -32363,6 +33661,1108 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>nyc_launch_buzz</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>2031-01-06</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>2031-01-06</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>2031-01-19</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>rival</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="inlineStr">
+        <is>
+          <t>nyc</t>
+        </is>
+      </c>
+      <c r="G17" s="13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H17" s="13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I17" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" s="13" t="inlineStr">
+        <is>
+          <t>New York! Newspapers cover the first transatlantic flight by a British start-up; bookings surge for a fortnight.</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="inlineStr">
+        <is>
+          <t>Keep the fare at £510 and enjoy a full 757 — don't cut it.</t>
+        </is>
+      </c>
+      <c r="L17" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>dxb_shopping_festival</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>2031-01-06</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>2031-01-13</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>2031-02-02</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>culture</t>
+        </is>
+      </c>
+      <c r="F18" s="13" t="inlineStr">
+        <is>
+          <t>dxb</t>
+        </is>
+      </c>
+      <c r="G18" s="13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H18" s="13" t="inlineStr">
+        <is>
+          <t>leisure</t>
+        </is>
+      </c>
+      <c r="I18" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J18" s="13" t="inlineStr">
+        <is>
+          <t>Dubai's shopping festival runs through late January.</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="inlineStr">
+        <is>
+          <t>A 757 fills; a 787 nearly does. Raise the fare a step.</t>
+        </is>
+      </c>
+      <c r="L18" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>fra_bookfair_cancel</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>2031-01-13</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>2031-01-20</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>2031-01-24</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>economic</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
+        <is>
+          <t>fra</t>
+        </is>
+      </c>
+      <c r="G19" s="13" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H19" s="13" t="inlineStr">
+        <is>
+          <t>business</t>
+        </is>
+      </c>
+      <c r="I19" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J19" s="13" t="inlineStr">
+        <is>
+          <t>Frankfurt's winter trade fair is cancelled.</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="inlineStr">
+        <is>
+          <t>Move the Saab off Frankfurt for the week.</t>
+        </is>
+      </c>
+      <c r="L19" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>ski_snow_bonanza</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>2031-01-20</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>2031-01-27</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>2031-02-23</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>nature</t>
+        </is>
+      </c>
+      <c r="F20" s="13" t="inlineStr">
+        <is>
+          <t>gva</t>
+        </is>
+      </c>
+      <c r="G20" s="13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H20" s="13" t="inlineStr">
+        <is>
+          <t>leisure</t>
+        </is>
+      </c>
+      <c r="I20" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J20" s="13" t="inlineStr">
+        <is>
+          <t>Record snow in the Alps: the ski season is the best in years.</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="inlineStr">
+        <is>
+          <t>Geneva at ×1.4 season and ×1.3 news: put the biggest plane you have on it.</t>
+        </is>
+      </c>
+      <c r="L20" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>us_storm</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>2031-02-03</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>2031-02-03</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>2031-02-05</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>nature</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="inlineStr">
+        <is>
+          <t>nyc,yyz</t>
+        </is>
+      </c>
+      <c r="G21" s="13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H21" s="13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I21" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21" s="13" t="inlineStr">
+        <is>
+          <t>A blizzard closes New York and Toronto airports for three days.</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="inlineStr">
+        <is>
+          <t>None in advance; the review explains the empty days.</t>
+        </is>
+      </c>
+      <c r="L21" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>dub_six_nations</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>2031-02-10</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>2031-02-15</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>2031-02-16</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>sport</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="inlineStr">
+        <is>
+          <t>dub</t>
+        </is>
+      </c>
+      <c r="G22" s="13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H22" s="13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I22" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J22" s="13" t="inlineStr">
+        <is>
+          <t>Ireland play England in Dublin on Saturday 15 February.</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="inlineStr">
+        <is>
+          <t>A Sat–Sun Dublin service at a higher fare.</t>
+        </is>
+      </c>
+      <c r="L22" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>half_term_sun</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>2031-02-10</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>2031-02-17</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>2031-02-23</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>culture</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="inlineStr">
+        <is>
+          <t>rak,cai,dxb</t>
+        </is>
+      </c>
+      <c r="G23" s="13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H23" s="13" t="inlineStr">
+        <is>
+          <t>leisure</t>
+        </is>
+      </c>
+      <c r="I23" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J23" s="13" t="inlineStr">
+        <is>
+          <t>February half-term: families head for the sun.</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="inlineStr">
+        <is>
+          <t>Raise fares on Marrakech, Cairo and Dubai for the week.</t>
+        </is>
+      </c>
+      <c r="L23" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>par_fashion_week</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>2031-02-24</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>2031-03-03</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t>2031-03-09</t>
+        </is>
+      </c>
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>culture</t>
+        </is>
+      </c>
+      <c r="F24" s="13" t="inlineStr">
+        <is>
+          <t>par</t>
+        </is>
+      </c>
+      <c r="G24" s="13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H24" s="13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I24" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J24" s="13" t="inlineStr">
+        <is>
+          <t>Paris fashion week.</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="inlineStr">
+        <is>
+          <t>Add a Paris service or raise the fare.</t>
+        </is>
+      </c>
+      <c r="L24" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>lagos_fuel_strike</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>2031-03-10</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>2031-03-10</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>2031-03-16</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>political</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="inlineStr">
+        <is>
+          <t>los</t>
+        </is>
+      </c>
+      <c r="G25" s="13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H25" s="13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I25" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J25" s="13" t="inlineStr">
+        <is>
+          <t>A fuel-tanker strike at Lagos airport delays flights all week.</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="inlineStr">
+        <is>
+          <t>None in advance.</t>
+        </is>
+      </c>
+      <c r="L25" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>yyz_launch</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>2031-03-03</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>2031-03-03</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>2031-03-16</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>rival</t>
+        </is>
+      </c>
+      <c r="F26" s="13" t="inlineStr">
+        <is>
+          <t>yyz</t>
+        </is>
+      </c>
+      <c r="G26" s="13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H26" s="13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I26" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J26" s="13" t="inlineStr">
+        <is>
+          <t>Toronto opens with a launch-week buzz.</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="inlineStr">
+        <is>
+          <t>Open it with the 757.</t>
+        </is>
+      </c>
+      <c r="L26" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>mxp_design_week</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>2031-04-07</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>2031-04-14</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="inlineStr">
+        <is>
+          <t>2031-04-20</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>culture</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="inlineStr">
+        <is>
+          <t>mxp</t>
+        </is>
+      </c>
+      <c r="G27" s="13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H27" s="13" t="inlineStr">
+        <is>
+          <t>business</t>
+        </is>
+      </c>
+      <c r="I27" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J27" s="13" t="inlineStr">
+        <is>
+          <t>Milan design week.</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="inlineStr">
+        <is>
+          <t>Add a Milan service.</t>
+        </is>
+      </c>
+      <c r="L27" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>ash_cloud_warning</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>2031-04-07</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>2031-04-14</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="inlineStr">
+        <is>
+          <t>2031-04-18</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>nature</t>
+        </is>
+      </c>
+      <c r="F28" s="13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="G28" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I28" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J28" s="13" t="inlineStr">
+        <is>
+          <t>The ash cloud grounds European flights for five days (see Events).</t>
+        </is>
+      </c>
+      <c r="K28" s="13" t="inlineStr">
+        <is>
+          <t>Nothing flies; the fuel you don't burn stays in the tank.</t>
+        </is>
+      </c>
+      <c r="L28" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>easter_leisure</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>2031-04-14</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>2031-04-18</t>
+        </is>
+      </c>
+      <c r="D29" s="13" t="inlineStr">
+        <is>
+          <t>2031-05-04</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>culture</t>
+        </is>
+      </c>
+      <c r="F29" s="13" t="inlineStr">
+        <is>
+          <t>bcn,mad,lis,fco,ath,rak</t>
+        </is>
+      </c>
+      <c r="G29" s="13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H29" s="13" t="inlineStr">
+        <is>
+          <t>leisure</t>
+        </is>
+      </c>
+      <c r="I29" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J29" s="13" t="inlineStr">
+        <is>
+          <t>Easter holidays: leisure routes +20% for two weeks (Events).</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="inlineStr">
+        <is>
+          <t>Fares up a step on the sun routes.</t>
+        </is>
+      </c>
+      <c r="L29" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>del_pre_launch</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>2031-05-26</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>2031-06-02</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>2031-06-15</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>rival</t>
+        </is>
+      </c>
+      <c r="F30" s="13" t="inlineStr">
+        <is>
+          <t>del</t>
+        </is>
+      </c>
+      <c r="G30" s="13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H30" s="13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I30" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J30" s="13" t="inlineStr">
+        <is>
+          <t>Delhi opens: the first flight too far for a day.</t>
+        </is>
+      </c>
+      <c r="K30" s="13" t="inlineStr">
+        <is>
+          <t>Lease a 787 or a second 757 for the overnight rotation.</t>
+        </is>
+      </c>
+      <c r="L30" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="13" t="inlineStr">
+        <is>
+          <t>ist_summer_dip</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>2031-06-02</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="inlineStr">
+        <is>
+          <t>2031-06-09</t>
+        </is>
+      </c>
+      <c r="D31" s="13" t="inlineStr">
+        <is>
+          <t>2031-07-06</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>economic</t>
+        </is>
+      </c>
+      <c r="F31" s="13" t="inlineStr">
+        <is>
+          <t>ist</t>
+        </is>
+      </c>
+      <c r="G31" s="13" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H31" s="13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I31" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J31" s="13" t="inlineStr">
+        <is>
+          <t>A weak lira keeps Turkish business travellers at home this month.</t>
+        </is>
+      </c>
+      <c r="K31" s="13" t="inlineStr">
+        <is>
+          <t>Fewer Istanbul services.</t>
+        </is>
+      </c>
+      <c r="L31" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t>heatwave_spain</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>2031-07-07</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>2031-07-14</t>
+        </is>
+      </c>
+      <c r="D32" s="13" t="inlineStr">
+        <is>
+          <t>2031-07-27</t>
+        </is>
+      </c>
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>nature</t>
+        </is>
+      </c>
+      <c r="F32" s="13" t="inlineStr">
+        <is>
+          <t>bcn,mad</t>
+        </is>
+      </c>
+      <c r="G32" s="13" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H32" s="13" t="inlineStr">
+        <is>
+          <t>leisure</t>
+        </is>
+      </c>
+      <c r="I32" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J32" s="13" t="inlineStr">
+        <is>
+          <t>A heatwave in Spain: holidaymakers switch to cooler cities.</t>
+        </is>
+      </c>
+      <c r="K32" s="13" t="inlineStr">
+        <is>
+          <t>Move capacity from Barcelona to Lisbon or Edinburgh.</t>
+        </is>
+      </c>
+      <c r="L32" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t>edinburgh_festival</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>2031-07-28</t>
+        </is>
+      </c>
+      <c r="C33" s="13" t="inlineStr">
+        <is>
+          <t>2031-08-04</t>
+        </is>
+      </c>
+      <c r="D33" s="13" t="inlineStr">
+        <is>
+          <t>2031-08-24</t>
+        </is>
+      </c>
+      <c r="E33" s="13" t="inlineStr">
+        <is>
+          <t>culture</t>
+        </is>
+      </c>
+      <c r="F33" s="13" t="inlineStr">
+        <is>
+          <t>edi</t>
+        </is>
+      </c>
+      <c r="G33" s="13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H33" s="13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I33" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J33" s="13" t="inlineStr">
+        <is>
+          <t>The Edinburgh festivals: three weeks of full planes.</t>
+        </is>
+      </c>
+      <c r="K33" s="13" t="inlineStr">
+        <is>
+          <t>Edinburgh takes a Saab or an ATR for August.</t>
+        </is>
+      </c>
+      <c r="L33" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>red_kite_nyc</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>2031-07-21</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>2031-08-04</t>
+        </is>
+      </c>
+      <c r="D34" s="13" t="inlineStr">
+        <is>
+          <t>2031-08-31</t>
+        </is>
+      </c>
+      <c r="E34" s="13" t="inlineStr">
+        <is>
+          <t>rival</t>
+        </is>
+      </c>
+      <c r="F34" s="13" t="inlineStr">
+        <is>
+          <t>nyc</t>
+        </is>
+      </c>
+      <c r="G34" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H34" s="13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I34" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J34" s="13" t="inlineStr">
+        <is>
+          <t>Red Kite announces New York flights from Luton from 4 August.</t>
+        </is>
+      </c>
+      <c r="K34" s="13" t="inlineStr">
+        <is>
+          <t>Hold the fare and your stars; Red Kite's switching rule applies on New York.</t>
+        </is>
+      </c>
+      <c r="L34" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="13" t="inlineStr">
+        <is>
+          <t>atlantic_hurricane</t>
+        </is>
+      </c>
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>2031-08-18</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="inlineStr">
+        <is>
+          <t>2031-08-18</t>
+        </is>
+      </c>
+      <c r="D35" s="13" t="inlineStr">
+        <is>
+          <t>2031-08-20</t>
+        </is>
+      </c>
+      <c r="E35" s="13" t="inlineStr">
+        <is>
+          <t>nature</t>
+        </is>
+      </c>
+      <c r="F35" s="13" t="inlineStr">
+        <is>
+          <t>nyc,yyz</t>
+        </is>
+      </c>
+      <c r="G35" s="13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H35" s="13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I35" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J35" s="13" t="inlineStr">
+        <is>
+          <t>A hurricane shuts the US east coast for three days.</t>
+        </is>
+      </c>
+      <c r="K35" s="13" t="inlineStr">
+        <is>
+          <t>None in advance.</t>
+        </is>
+      </c>
+      <c r="L35" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -32374,7 +34774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R7"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -32885,6 +35285,72 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>long_haul</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>Long haul (one flight a day)</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D8" s="13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E8" s="13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F8" s="13" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G8" s="13" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H8" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="J8" s="13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K8" s="13" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L8" s="13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M8" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" s="13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O8" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" s="13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q8" s="13" t="inlineStr">
+        <is>
+          <t>Big crowds, big fares, one flight a day. Only one in ten minds what time it goes, so a single service catches almost everyone who wants to fly. Demand grows 5% a week to one and a half times.</t>
+        </is>
+      </c>
+      <c r="R8" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -32896,7 +35362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R21"/>
+  <dimension ref="A1:T24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -32917,6 +35383,8 @@
     <col width="9" customWidth="1" min="16" max="16"/>
     <col width="52" customWidth="1" min="17" max="17"/>
     <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="28" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -33010,6 +35478,16 @@
           <t>status</t>
         </is>
       </c>
+      <c r="S1" s="20" t="inlineStr">
+        <is>
+          <t>rotation</t>
+        </is>
+      </c>
+      <c r="T1" s="20" t="inlineStr">
+        <is>
+          <t>seasonOverride</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="12" t="inlineStr">
@@ -33065,7 +35543,7 @@
       </c>
       <c r="N2" s="12" t="inlineStr">
         <is>
-          <t>50:96|60:88|70:80|80:72|90:62|100:44|110:30|120:18</t>
+          <t>50:96|60:88|70:80|80:72|90:62|100:44|110:30|120:18|130:14</t>
         </is>
       </c>
       <c r="O2" s="12" t="n">
@@ -33139,7 +35617,7 @@
       </c>
       <c r="N3" s="12" t="inlineStr">
         <is>
-          <t>70:60|80:55|90:50|100:44|110:30|120:20</t>
+          <t>60:67|70:60|80:55|90:50|100:44|110:30|120:20|130:15</t>
         </is>
       </c>
       <c r="O3" s="12" t="n">
@@ -33213,7 +35691,7 @@
       </c>
       <c r="N4" s="12" t="inlineStr">
         <is>
-          <t>70:92|75:88|80:84|85:80|90:76|95:66|100:56|105:47|110:38|115:30|120:22</t>
+          <t>65:103|70:92|75:88|80:84|85:80|90:76|95:66|100:56|105:47|110:38|115:30|120:22</t>
         </is>
       </c>
       <c r="O4" s="12" t="n">
@@ -33287,7 +35765,7 @@
       </c>
       <c r="N5" s="12" t="inlineStr">
         <is>
-          <t>100:60|105:58|110:55|115:52|120:50|125:47|130:44|135:39|140:34|145:28|150:22</t>
+          <t>95:67|100:60|105:58|110:55|115:52|120:50|125:47|130:44|135:39|140:34|145:28|150:22</t>
         </is>
       </c>
       <c r="O5" s="12" t="n">
@@ -33361,7 +35839,7 @@
       </c>
       <c r="N6" s="12" t="inlineStr">
         <is>
-          <t>110:50|115:48|120:46|125:43|130:40|135:37|140:34|145:29|150:24|155:19|160:14</t>
+          <t>105:56|110:50|115:48|120:46|125:43|130:40|135:37|140:34|145:29|150:24|155:19|160:14</t>
         </is>
       </c>
       <c r="O6" s="12" t="n">
@@ -33435,7 +35913,7 @@
       </c>
       <c r="N7" s="12" t="inlineStr">
         <is>
-          <t>120:70|125:66|130:62|135:58|140:54|145:49|150:44|155:37|160:30|165:23|170:16</t>
+          <t>115:78|120:70|125:66|130:62|135:58|140:54|145:49|150:44|155:37|160:30|165:23|170:16</t>
         </is>
       </c>
       <c r="O7" s="12" t="n">
@@ -33509,7 +35987,7 @@
       </c>
       <c r="N8" s="12" t="inlineStr">
         <is>
-          <t>150:140|160:120|170:100|180:80|190:60|200:40</t>
+          <t>140:157|150:140|160:120|170:100|180:80|190:60|200:40|210:30</t>
         </is>
       </c>
       <c r="O8" s="12" t="n">
@@ -33583,7 +36061,7 @@
       </c>
       <c r="N9" s="12" t="inlineStr">
         <is>
-          <t>220:110|230:100|240:90|250:75|260:60|270:45</t>
+          <t>210:123|220:110|230:100|240:90|250:75|260:60|270:45|280:34</t>
         </is>
       </c>
       <c r="O9" s="12" t="n">
@@ -33604,150 +36082,166 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>nyc</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="D10" s="15" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>JFK</t>
         </is>
       </c>
-      <c r="E10" s="15" t="n">
+      <c r="E10" s="12" t="n">
         <v>40.64</v>
       </c>
-      <c r="F10" s="15" t="n">
+      <c r="F10" s="12" t="n">
         <v>-73.78</v>
       </c>
-      <c r="G10" s="15" t="n">
+      <c r="G10" s="12" t="n">
         <v>-5</v>
       </c>
-      <c r="H10" s="15" t="inlineStr">
-        <is>
-          <t>long_haul_mixed</t>
-        </is>
-      </c>
-      <c r="I10" s="15" t="n">
+      <c r="H10" s="12" t="inlineStr">
+        <is>
+          <t>long_haul</t>
+        </is>
+      </c>
+      <c r="I10" s="12" t="n">
         <v>5625</v>
       </c>
-      <c r="J10" s="15" t="n">
-        <v>90</v>
-      </c>
-      <c r="K10" s="15" t="n">
+      <c r="J10" s="12" t="n">
+        <v>120</v>
+      </c>
+      <c r="K10" s="12" t="n">
         <v>400</v>
       </c>
-      <c r="L10" s="15" t="n">
+      <c r="L10" s="12" t="n">
         <v>510</v>
       </c>
-      <c r="M10" s="15" t="inlineStr">
-        <is>
-          <t>150|200|250|300</t>
-        </is>
-      </c>
-      <c r="N10" s="15" t="inlineStr">
-        <is>
-          <t>placeholder</t>
-        </is>
-      </c>
-      <c r="O10" s="15" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="P10" s="15" t="n">
+      <c r="M10" s="12" t="inlineStr">
+        <is>
+          <t>470|490|510|530|550</t>
+        </is>
+      </c>
+      <c r="N10" s="12" t="inlineStr">
+        <is>
+          <t>450:320|470:290|490:255|510:220|530:185|550:150|570:120|590:95</t>
+        </is>
+      </c>
+      <c r="O10" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P10" s="12" t="n">
         <v>127</v>
       </c>
-      <c r="Q10" s="15" t="inlineStr">
-        <is>
-          <t>The big one. Overnight return; five hours behind London. Opens January 2031 (D17).</t>
-        </is>
-      </c>
-      <c r="R10" s="15" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="Q10" s="12" t="inlineStr">
+        <is>
+          <t>The big one. Six and a quarter hours each way; out at 06:30, back by 21:30. Five hours behind London: leave at 06:30 and land at 07:45 New York time. The 757 fills it on day one; the 787 needs the route to grow.</t>
+        </is>
+      </c>
+      <c r="R10" s="12" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="S10" s="13" t="inlineStr">
+        <is>
+          <t>same-day</t>
+        </is>
+      </c>
+      <c r="T10" s="13" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>dxb</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>Dubai</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>UAE</t>
         </is>
       </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t>DXB</t>
         </is>
       </c>
-      <c r="E11" s="15" t="n">
+      <c r="E11" s="12" t="n">
         <v>25.25</v>
       </c>
-      <c r="F11" s="15" t="n">
+      <c r="F11" s="12" t="n">
         <v>55.36</v>
       </c>
-      <c r="G11" s="15" t="n">
+      <c r="G11" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="H11" s="15" t="inlineStr">
-        <is>
-          <t>long_haul_mixed</t>
-        </is>
-      </c>
-      <c r="I11" s="15" t="n">
+      <c r="H11" s="12" t="inlineStr">
+        <is>
+          <t>long_haul</t>
+        </is>
+      </c>
+      <c r="I11" s="12" t="n">
         <v>5400</v>
       </c>
-      <c r="J11" s="15" t="n">
-        <v>90</v>
-      </c>
-      <c r="K11" s="15" t="n">
-        <v>400</v>
-      </c>
-      <c r="L11" s="15" t="n">
+      <c r="J11" s="12" t="n">
+        <v>120</v>
+      </c>
+      <c r="K11" s="12" t="n">
+        <v>350</v>
+      </c>
+      <c r="L11" s="12" t="n">
         <v>490</v>
       </c>
-      <c r="M11" s="15" t="inlineStr">
-        <is>
-          <t>200|250|300|350</t>
-        </is>
-      </c>
-      <c r="N11" s="15" t="inlineStr">
-        <is>
-          <t>placeholder</t>
-        </is>
-      </c>
-      <c r="O11" s="15" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="P11" s="15" t="n">
+      <c r="M11" s="12" t="inlineStr">
+        <is>
+          <t>450|470|490|510|530</t>
+        </is>
+      </c>
+      <c r="N11" s="12" t="inlineStr">
+        <is>
+          <t>430:310|450:280|470:245|490:210|510:175|530:140|550:110|570:85</t>
+        </is>
+      </c>
+      <c r="O11" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P11" s="12" t="n">
         <v>127</v>
       </c>
-      <c r="Q11" s="15" t="inlineStr">
-        <is>
-          <t>High fares, winter busy; four hours ahead. Opens January 2031 (D17).</t>
-        </is>
-      </c>
-      <c r="R11" s="15" t="inlineStr">
-        <is>
-          <t>later</t>
+      <c r="Q11" s="12" t="inlineStr">
+        <is>
+          <t>Winter sun and shopping; four hours ahead. Busy December to February, quiet in the summer heat.</t>
+        </is>
+      </c>
+      <c r="R11" s="12" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="S11" s="13" t="inlineStr">
+        <is>
+          <t>same-day</t>
+        </is>
+      </c>
+      <c r="T11" s="13" t="inlineStr">
+        <is>
+          <t>winter:1.2,summer:0.8</t>
         </is>
       </c>
     </row>
@@ -33805,7 +36299,7 @@
       </c>
       <c r="N12" s="13" t="inlineStr">
         <is>
-          <t>70:84|80:70|90:52|100:30|110:16</t>
+          <t>60:94|70:84|80:70|90:52|100:30|110:16|120:12|130:9</t>
         </is>
       </c>
       <c r="O12" s="13" t="n">
@@ -33879,7 +36373,7 @@
       </c>
       <c r="N13" s="13" t="inlineStr">
         <is>
-          <t>110:76|120:68|130:60|140:50|150:40|160:28</t>
+          <t>100:85|110:76|120:68|130:60|140:50|150:40|160:28|170:21</t>
         </is>
       </c>
       <c r="O13" s="13" t="n">
@@ -33953,7 +36447,7 @@
       </c>
       <c r="N14" s="13" t="inlineStr">
         <is>
-          <t>110:110|120:100|130:90|140:72|150:52|160:34</t>
+          <t>100:123|110:110|120:100|130:90|140:72|150:52|160:34|170:26</t>
         </is>
       </c>
       <c r="O14" s="13" t="n">
@@ -34027,7 +36521,7 @@
       </c>
       <c r="N15" s="13" t="inlineStr">
         <is>
-          <t>170:130|180:115|190:100|200:85|210:70|220:55</t>
+          <t>160:146|170:130|180:115|190:100|200:85|210:70|220:55|230:41</t>
         </is>
       </c>
       <c r="O15" s="13" t="n">
@@ -34101,7 +36595,7 @@
       </c>
       <c r="N16" s="13" t="inlineStr">
         <is>
-          <t>170:100|180:90|190:80|200:65|210:50|220:35</t>
+          <t>160:112|170:100|180:90|190:80|200:65|210:50|220:35|230:26</t>
         </is>
       </c>
       <c r="O16" s="13" t="n">
@@ -34175,7 +36669,7 @@
       </c>
       <c r="N17" s="13" t="inlineStr">
         <is>
-          <t>240:180|250:165|260:150|270:130|280:105|290:80</t>
+          <t>230:202|240:180|250:165|260:150|270:130|280:105|290:80|300:60</t>
         </is>
       </c>
       <c r="O17" s="13" t="n">
@@ -34249,7 +36743,7 @@
       </c>
       <c r="N18" s="13" t="inlineStr">
         <is>
-          <t>240:140|250:132|260:125|270:115|280:105|290:95</t>
+          <t>230:157|240:140|250:132|260:125|270:115|280:105|290:95|300:71</t>
         </is>
       </c>
       <c r="O18" s="13" t="n">
@@ -34323,7 +36817,7 @@
       </c>
       <c r="N19" s="13" t="inlineStr">
         <is>
-          <t>90:66|100:58|110:48|120:34|130:22</t>
+          <t>80:74|90:66|100:58|110:48|120:34|130:22|140:16|150:12</t>
         </is>
       </c>
       <c r="O19" s="13" t="n">
@@ -34397,7 +36891,7 @@
       </c>
       <c r="N20" s="13" t="inlineStr">
         <is>
-          <t>200:70|210:64|220:58|230:50|240:42|250:34</t>
+          <t>190:78|200:70|210:64|220:58|230:50|240:42|250:34|260:26</t>
         </is>
       </c>
       <c r="O20" s="13" t="n">
@@ -34471,7 +36965,7 @@
       </c>
       <c r="N21" s="13" t="inlineStr">
         <is>
-          <t>330:110|340:100|350:90|360:78|370:64|380:50</t>
+          <t>320:123|330:110|340:100|350:90|360:78|370:64|380:50|390:38</t>
         </is>
       </c>
       <c r="O21" s="13" t="n">
@@ -34488,6 +36982,250 @@
       <c r="R21" s="13" t="inlineStr">
         <is>
           <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>yyz</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>Toronto</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>YYZ</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="n">
+        <v>43.68</v>
+      </c>
+      <c r="F22" s="13" t="n">
+        <v>-79.63</v>
+      </c>
+      <c r="G22" s="13" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H22" s="13" t="inlineStr">
+        <is>
+          <t>long_haul</t>
+        </is>
+      </c>
+      <c r="I22" s="13" t="n">
+        <v>5700</v>
+      </c>
+      <c r="J22" s="13" t="n">
+        <v>120</v>
+      </c>
+      <c r="K22" s="13" t="n">
+        <v>380</v>
+      </c>
+      <c r="L22" s="13" t="n">
+        <v>520</v>
+      </c>
+      <c r="M22" s="13" t="inlineStr">
+        <is>
+          <t>480|500|520|540|560</t>
+        </is>
+      </c>
+      <c r="N22" s="13" t="inlineStr">
+        <is>
+          <t>460:255|480:230|500:205|520:180|540:155|560:130|580:105|600:85</t>
+        </is>
+      </c>
+      <c r="O22" s="13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P22" s="13" t="n">
+        <v>183</v>
+      </c>
+      <c r="Q22" s="13" t="inlineStr">
+        <is>
+          <t>A smaller New York. Opens March 2031. The 757's route until it grows.</t>
+        </is>
+      </c>
+      <c r="R22" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="S22" s="13" t="inlineStr">
+        <is>
+          <t>same-day</t>
+        </is>
+      </c>
+      <c r="T22" s="13" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>los</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>Lagos</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>LOS</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="F23" s="13" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="G23" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="13" t="inlineStr">
+        <is>
+          <t>long_haul</t>
+        </is>
+      </c>
+      <c r="I23" s="13" t="n">
+        <v>5000</v>
+      </c>
+      <c r="J23" s="13" t="n">
+        <v>120</v>
+      </c>
+      <c r="K23" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="L23" s="13" t="n">
+        <v>460</v>
+      </c>
+      <c r="M23" s="13" t="inlineStr">
+        <is>
+          <t>440|460|480|500|520</t>
+        </is>
+      </c>
+      <c r="N23" s="13" t="inlineStr">
+        <is>
+          <t>420:230|440:200|460:170|480:145|500:120|520:95|540:75|560:60</t>
+        </is>
+      </c>
+      <c r="O23" s="13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P23" s="13" t="n">
+        <v>218</v>
+      </c>
+      <c r="Q23" s="13" t="inlineStr">
+        <is>
+          <t>Business and family travel, one hour ahead. Opens April 2031. A 757 route; a 787 half-empties.</t>
+        </is>
+      </c>
+      <c r="R23" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="S23" s="13" t="inlineStr">
+        <is>
+          <t>same-day</t>
+        </is>
+      </c>
+      <c r="T23" s="13" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>del</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t>DEL</t>
+        </is>
+      </c>
+      <c r="E24" s="13" t="n">
+        <v>28.56</v>
+      </c>
+      <c r="F24" s="13" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="G24" s="13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H24" s="13" t="inlineStr">
+        <is>
+          <t>long_haul</t>
+        </is>
+      </c>
+      <c r="I24" s="13" t="n">
+        <v>6700</v>
+      </c>
+      <c r="J24" s="13" t="n">
+        <v>120</v>
+      </c>
+      <c r="K24" s="13" t="n">
+        <v>350</v>
+      </c>
+      <c r="L24" s="13" t="n">
+        <v>600</v>
+      </c>
+      <c r="M24" s="13" t="inlineStr">
+        <is>
+          <t>560|580|600|620|640</t>
+        </is>
+      </c>
+      <c r="N24" s="13" t="inlineStr">
+        <is>
+          <t>540:290|560:260|580:235|600:210|620:185|640:160|660:130|680:105</t>
+        </is>
+      </c>
+      <c r="O24" s="13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P24" s="13" t="n">
+        <v>274</v>
+      </c>
+      <c r="Q24" s="13" t="inlineStr">
+        <is>
+          <t>Too far for a day: the first overnight rotation (out day 1, back day 2, so the plane earns every second day). Five and a half hours ahead — the only half-hour time zone in the game. Opens June 2031.</t>
+        </is>
+      </c>
+      <c r="R24" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="S24" s="13" t="inlineStr">
+        <is>
+          <t>overnight</t>
+        </is>
+      </c>
+      <c r="T24" s="13" t="inlineStr">
+        <is>
+          <t>winter:1.1,summer:0.9</t>
         </is>
       </c>
     </row>

--- a/data/Airline-World-Workbook.xlsx
+++ b/data/Airline-World-Workbook.xlsx
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -748,6 +748,13 @@
       <c r="A25" s="10" t="inlineStr">
         <is>
           <t>v5.0 (13 Oct): CHAPTER 2 LIVE. New York and Dubai (unlockDay 127), Toronto (183), Lagos (218), Delhi (274, the first overnight rotation); a long_haul archetype (one flight a day, one in ten time-locked, growth 5% a week to ×1.5); the 757 and 787 live to lease, the 787 re-costed to be cheaper per seat than the 757 (130 L/100 km, £2,000/h, £6,000/day); A320/737 range 5,500 km and A220 5,000 so the Atlantic needs a long-haul plane; same-day long haul to 6,000 km with a £500 second crew; reputation ×5% a half-star from January with the autumn's stars banked; light airline types (Premium two higher fares and faster stars, Value one lower fare and the £20 bag fee at four in ten); demand tables extended a step below and two above every live route's options; fuel forecasts weeks 18–52; 19 route-news items January–August; the spring and summer events written with options; Challenges 1–2 and Hunts h1–h2 live; chapter-2 Calendar days 127–133. Balance Report v5.0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="17" t="inlineStr">
+        <is>
+          <t>v5.1 (13 Oct): D75 pupil record — WorkingMethods gains bettwsStatements (WPS 3 + PFA codes per kind of sum) and six more rows (time, flight time, local time, reading reports, multipliers, the aircraft comparison) so every printed entry can carry its statements. Brief: Pupil record and printout.</t>
         </is>
       </c>
     </row>
@@ -28170,7 +28177,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="17" t="inlineStr">
         <is>
@@ -29549,7 +29555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -29558,6 +29564,7 @@
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="44" customWidth="1" min="5" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -29591,6 +29598,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="G1" s="20" t="inlineStr">
+        <is>
+          <t>bettwsStatements (WPS 3 + PFA)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="13" t="inlineStr">
@@ -29623,6 +29635,11 @@
           <t>Short × then × 10 for £10 fares; long × for £5 fares and fares over £100</t>
         </is>
       </c>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>NCP-3-06 · NCP-3-04 · ALG-3-08 (partition) · MON-3-02</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
@@ -29655,6 +29672,11 @@
           <t>Scale from 100 L: 100 L costs £147, so 20 L costs £29.40</t>
         </is>
       </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>NCP-3-06 · NCP-3-05 (decimals) · ALG-3-08 (partition the price) · FDP-3-06 (estimate first, check it looks right)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
@@ -29683,6 +29705,11 @@
         </is>
       </c>
       <c r="F4" s="13" t="inlineStr"/>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>NCP-3-05 · MON-3-02 · MON-3-01 · PFA-MM-02</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
@@ -29715,6 +29742,11 @@
           <t>D61: Build, not Calculate</t>
         </is>
       </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>NCP-3-05 · STAT-3-19 (totals and differences from data) · STAT-3-23 (the mean) · MON-3-01 · PFA-MM-02</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
@@ -29747,6 +29779,11 @@
           <t>Shown in the 'What changed?' panel</t>
         </is>
       </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>NCP-3-05 · STAT-3-19 · STAT-3-18 (reading the comparison) · MON-3-02</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
@@ -29775,6 +29812,11 @@
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr"/>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>NCP-3-06 · NCP-3-02 (large numbers) · MON-3-01 · PFA-MM-02</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
@@ -29807,6 +29849,11 @@
           <t>'Saved compared with buying later', never profit</t>
         </is>
       </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>STAT-3-18 (reading a table) · STAT-3-25 (what the data cannot tell us) · MON-3-03 · PFA-MM-07 · FDP-3-06</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
@@ -29835,6 +29882,11 @@
         </is>
       </c>
       <c r="F9" s="13" t="inlineStr"/>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>NCP-3-06 (division, remainders) · MON-3-03 (best value, price per unit) · PFA-MM-07</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
@@ -29863,6 +29915,11 @@
         </is>
       </c>
       <c r="F10" s="13" t="inlineStr"/>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>FDP-3-02 · FDP-3-03 (fraction as division) · FDP-3-01 (everyday set) · FDP-3-04</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
@@ -29891,6 +29948,11 @@
         </is>
       </c>
       <c r="F11" s="13" t="inlineStr"/>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>FDP-3-02 · FDP-3-01 (one tenth = 10%) · FDP-3-03</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
@@ -29919,11 +29981,246 @@
           <t>Monthly reports from December; quarterly task later</t>
         </is>
       </c>
-    </row>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>STAT-3-23 (the mean) · STAT-3-19 · STAT-3-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>time: service length, departures, duty day</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>Planning board; performance card</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>adding mixed hours and minutes; counting on</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>1 h + 45 min + 1 h + 35 min = 3 h 20; 06:30 to 21:15</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="G14" s="13" t="inlineStr">
+        <is>
+          <t>TTT-3-01 · TTT-3-04 · CN-3-01 (reading a timetable) · DUR-3-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>flight time: distance ÷ speed</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>Performance card; route card</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>short division; reasoning from multiplication facts</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>1,350 ÷ 450 = 3 h</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>NCP-3-06 · NCP-3-04 · DUR-3-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>local time: departure + flight + time zone</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>Arrival card (long haul)</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>number line across the day</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>06:30 + 6 h 15 − 5 h = 07:45 New York time</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="G16" s="13" t="inlineStr">
+        <is>
+          <t>TTT-3-01 · TTT-3-02 · NCP-3-03 (through zero / negative offsets)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>reading the World report and the review</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>Monday plan page; Sunday review</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>reading graphs and tables; comparing projected with actual</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>fuel line, demand bars, seat-fill bars</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>STAT-3-18 · STAT-3-19 · STAT-3-24 · STAT-3-25 · PROB-3-03 (expected against what happened)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>reputation and news multipliers</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>Review; route cards</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>percentage of an amount</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>4½ stars: 3 × 5% = 15% more; Paris ×0.4 in strike week</t>
+        </is>
+      </c>
+      <c r="F18" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="G18" s="13" t="inlineStr">
+        <is>
+          <t>FDP-3-02 · PFA-MM-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>second-aircraft comparison</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>strategic</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>Aircraft comparison (week 2)</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>reading a comparison table; seat-dot grids; cash bar; payback by division</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>22,000 − 13,000; 22,000 ÷ 590</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="G19" s="13" t="inlineStr">
+        <is>
+          <t>STAT-3-18 · STAT-3-35 · MON-3-03 · MON-3-01 · NCP-3-06 · PFA-MM-04 (wants, needs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>D60: the workbench (Work it out) offers the methods listed for the relationship being signed off; the pupil chooses. Levels: operational (what does this one thing cost? — taught and calculated), model (what happens if I change this? — the console calculates), strategic (what should I do when the future is uncertain? — maths supports judgement).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>Statement codes are from Bettws-Master-Dataset-v1_21 (WPS 3 main curriculum and PFA Managing Money). Drafted by Fable 13 Oct for Bertie to check; the pupil record prints these codes against each entry.</t>
         </is>
       </c>
     </row>

--- a/data/Airline-World-Workbook.xlsx
+++ b/data/Airline-World-Workbook.xlsx
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A26"/>
+  <dimension ref="A1:A27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -755,6 +755,13 @@
       <c r="A26" s="17" t="inlineStr">
         <is>
           <t>v5.1 (13 Oct): D75 pupil record — WorkingMethods gains bettwsStatements (WPS 3 + PFA codes per kind of sum) and six more rows (time, flight time, local time, reading reports, multipliers, the aircraft comparison) so every printed entry can carry its statements. Brief: Pupil record and printout.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="17" t="inlineStr">
+        <is>
+          <t>v5.2 (13 Oct): D76 chapter 1 is buy only — no rent or launch-deal finance on the tutorial planes; the week-2 decision is buy a smaller plane now or wait for a bigger one, with the time-to-afford sum (price − cash) ÷ profit a day; second Twin Otter £10,000. Leasing first appears in January with the 757/787; finance in chapter 4.</t>
         </is>
       </c>
     </row>
@@ -2186,7 +2193,7 @@
         <v>900</v>
       </c>
       <c r="J2" s="12" t="n">
-        <v>12000</v>
+        <v>10000</v>
       </c>
       <c r="K2" s="12" t="n">
         <v>2500</v>
@@ -2196,7 +2203,7 @@
       </c>
       <c r="M2" s="12" t="inlineStr">
         <is>
-          <t>Small, flexible, cheap. Fits any route. Slow on long legs.</t>
+          <t>Small, flexible, cheap, frequent. First plane £2,500 on the launch deal; a second one £10,000.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -3139,7 +3146,7 @@
         </is>
       </c>
       <c r="B2" s="13" t="n">
-        <v>12000</v>
+        <v>10000</v>
       </c>
       <c r="C2" s="13" t="n">
         <v>250</v>
@@ -3158,14 +3165,14 @@
       </c>
       <c r="H2" s="13" t="inlineStr">
         <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I2" s="13" t="inlineStr">
+        <is>
           <t>day 8</t>
         </is>
       </c>
-      <c r="I2" s="13" t="inlineStr">
-        <is>
-          <t>day 8</t>
-        </is>
-      </c>
       <c r="J2" s="13" t="inlineStr">
         <is>
           <t>n/a</t>
@@ -3173,7 +3180,7 @@
       </c>
       <c r="K2" s="13" t="inlineStr">
         <is>
-          <t>Second Twin Otter: rent £250 a day; 12,000 ÷ 250 = 48 days. Launch-deal finance £4,000 down, £300 a day for 30 days (£13,000).</t>
+          <t>Chapter 1 is buy only (D76). Week-2 sum: (price − cash) ÷ profit a day = days to wait.</t>
         </is>
       </c>
       <c r="L2" s="13" t="inlineStr">
@@ -3208,14 +3215,14 @@
       </c>
       <c r="H3" s="13" t="inlineStr">
         <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I3" s="13" t="inlineStr">
+        <is>
           <t>day 8</t>
         </is>
       </c>
-      <c r="I3" s="13" t="inlineStr">
-        <is>
-          <t>day 8</t>
-        </is>
-      </c>
       <c r="J3" s="13" t="inlineStr">
         <is>
           <t>n/a</t>
@@ -3223,7 +3230,7 @@
       </c>
       <c r="K3" s="13" t="inlineStr">
         <is>
-          <t>The week-2 sum: 22,000 ÷ 400 = 55 days. Launch-deal finance £7,000 down, £500 a day for 32 days (£23,000). Buy greyed out until cash ≥ price + reserve.</t>
+          <t>Chapter 1 is buy only (D76). Week-2 sum: (price − cash) ÷ profit a day = days to wait.</t>
         </is>
       </c>
       <c r="L3" s="13" t="inlineStr">
@@ -3258,14 +3265,14 @@
       </c>
       <c r="H4" s="13" t="inlineStr">
         <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
           <t>day 8</t>
         </is>
       </c>
-      <c r="I4" s="13" t="inlineStr">
-        <is>
-          <t>day 8</t>
-        </is>
-      </c>
       <c r="J4" s="13" t="inlineStr">
         <is>
           <t>n/a</t>
@@ -3273,7 +3280,7 @@
       </c>
       <c r="K4" s="13" t="inlineStr">
         <is>
-          <t>36,000 ÷ 650 ≈ 55 days. Finance £11,000 down, £800 a day for 35 days (£39,000).</t>
+          <t>Chapter 1 is buy only (D76). Week-2 sum: (price − cash) ÷ profit a day = days to wait.</t>
         </is>
       </c>
       <c r="L4" s="13" t="inlineStr">
@@ -3308,14 +3315,14 @@
       </c>
       <c r="H5" s="13" t="inlineStr">
         <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I5" s="13" t="inlineStr">
+        <is>
           <t>day 22</t>
         </is>
       </c>
-      <c r="I5" s="13" t="inlineStr">
-        <is>
-          <t>day 22</t>
-        </is>
-      </c>
       <c r="J5" s="13" t="inlineStr">
         <is>
           <t>n/a</t>
@@ -3323,7 +3330,7 @@
       </c>
       <c r="K5" s="13" t="inlineStr">
         <is>
-          <t>50,000 ÷ 900 ≈ 56 days. Finance £15,000 down, £1,000 a day for 38 days (£53,000).</t>
+          <t>Chapter 1 is buy only (D76). Week-2 sum: (price − cash) ÷ profit a day = days to wait.</t>
         </is>
       </c>
       <c r="L5" s="13" t="inlineStr">
@@ -3358,14 +3365,14 @@
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
           <t>day 22</t>
         </is>
       </c>
-      <c r="I6" s="13" t="inlineStr">
-        <is>
-          <t>day 22</t>
-        </is>
-      </c>
       <c r="J6" s="13" t="inlineStr">
         <is>
           <t>n/a</t>
@@ -3373,7 +3380,7 @@
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
-          <t>70,000 ÷ 1,200 ≈ 58 days. Finance £21,000 down, £1,500 a day for 36 days (£75,000).</t>
+          <t>Chapter 1 is buy only (D76). Week-2 sum: (price − cash) ÷ profit a day = days to wait.</t>
         </is>
       </c>
       <c r="L6" s="13" t="inlineStr">
@@ -4774,12 +4781,12 @@
       </c>
       <c r="G9" s="13" t="inlineStr">
         <is>
-          <t>Week 2: a second plane</t>
+          <t>Week 2: buy now, or wait?</t>
         </is>
       </c>
       <c r="H9" s="13" t="inlineStr">
         <is>
-          <t>One plane cannot serve both routes fully. The shop has a Saab 340 and an ATR 72. Rent, finance, or save to buy?</t>
+          <t>One plane cannot serve both routes fully. A second Twin Otter you can afford today; a Saab or an ATR means waiting. How long?</t>
         </is>
       </c>
       <c r="I9" s="13" t="inlineStr">
@@ -4790,7 +4797,7 @@
       <c r="J9" s="13" t="inlineStr"/>
       <c r="K9" s="13" t="inlineStr">
         <is>
-          <t>planes: dhc6 (second), saab340, atr72; mechanics: rent-or-buy sum, launch-deal finance, buy greyed until affordable, two timetables, assignment; FUEL DESK opens (market, tank 8,000 L, buy in 1,000 L blocks, scenario table)</t>
+          <t>planes: dhc6 (second, £10,000), saab340, atr72 (buy only); mechanics: time to afford sum, Buy greyed until affordable, two timetables, assignment</t>
         </is>
       </c>
       <c r="L9" s="13" t="inlineStr"/>
@@ -4802,7 +4809,7 @@
       </c>
       <c r="O9" s="13" t="inlineStr">
         <is>
-          <t>rentOrBuy</t>
+          <t>timeToAfford</t>
         </is>
       </c>
       <c r="P9" s="13" t="n"/>
@@ -26859,7 +26866,7 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Week 2: second plane; rent-or-buy sum; launch-deal finance; Buy greyed until affordable; two timetables; assignment</t>
+          <t>Week 2: second plane, buy only; buy now or wait (time to afford); Buy greyed until affordable; two timetables; assignment</t>
         </is>
       </c>
       <c r="C5" s="13" t="inlineStr">
@@ -27527,7 +27534,7 @@
       </c>
       <c r="I2" s="13" t="inlineStr">
         <is>
-          <t>Launch Day: timetable, fare, snacks, fuel, both routes, modelling tool, workings page; week 2: second plane, rent-or-buy, launch-deal finance; week 3: four routes, £5 fares, seasons, use-it-or-lose-it; week 4: medium haul, range, E175/E190, load factor %; from week 5: weekly skips, Marrakech, the autumn pairs, scaled event costs</t>
+          <t>Launch Day: timetable, fare, snacks, fuel, both routes, modelling tool, workings page; week 2: second plane bought outright or wait for a bigger one; time-to-afford sum; week 3: four routes, £5 fares, seasons, use-it-or-lose-it; week 4: medium haul, range, E175/E190, load factor %; from week 5: weekly skips, Marrakech, the autumn pairs, scaled event costs</t>
         </is>
       </c>
       <c r="J2" s="13" t="n">
@@ -29318,7 +29325,7 @@
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>34 × £95; 70 × £170; 1,350 ÷ 450; 9,000 ÷ 400; 6,000,000 ÷ 6,000</t>
+          <t>34 × £95; 70 × £170; 1,350 ÷ 450; (22,000 − 13,000) ÷ 1,700 (week 2); 6,000,000 ÷ 6,000 (January)</t>
         </is>
       </c>
       <c r="F5" s="13" t="inlineStr">
@@ -29468,7 +29475,7 @@
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>week 3: 34 × £95, 675 ÷ 450 and the Saab's Amsterdam fuel; Frankfurt, Geneva and Barcelona tickets as Build</t>
+          <t>week 2: time to afford, the Twin Otter's revenue, two planes' day; week 3: 34 × £95, 675 ÷ 450 and the Saab's Amsterdam fuel</t>
         </is>
       </c>
       <c r="F10" s="13" t="inlineStr">
@@ -29537,6 +29544,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="17" t="inlineStr">
         <is>
@@ -29858,7 +29866,7 @@
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>price ÷ rent</t>
+          <t>time to afford, then rent-or-buy</t>
         </is>
       </c>
       <c r="B9" s="13" t="inlineStr">
@@ -29868,20 +29876,24 @@
       </c>
       <c r="C9" s="13" t="inlineStr">
         <is>
-          <t>Shop sign-off</t>
+          <t>Aircraft comparison (week 2); shop from January</t>
         </is>
       </c>
       <c r="D9" s="13" t="inlineStr">
         <is>
-          <t>short division | make the sum smaller</t>
+          <t>time to afford: (price − cash) ÷ profit a day | from January: price ÷ rent a day</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>22,000 ÷ 400 = 55 days</t>
-        </is>
-      </c>
-      <c r="F9" s="13" t="inlineStr"/>
+          <t>(22,000 − 13,000) ÷ 1,700 ≈ 5 days; 6,000,000 ÷ 6,000 = 1,000 days</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>D76: no rent-or-buy in chapter 1</t>
+        </is>
+      </c>
       <c r="G9" s="10" t="inlineStr">
         <is>
           <t>NCP-3-06 (division, remainders) · MON-3-03 (best value, price per unit) · PFA-MM-07</t>
@@ -30235,7 +30247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D119"/>
+  <dimension ref="A1:D121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -31007,7 +31019,7 @@
       </c>
       <c r="C37" s="13" t="inlineStr">
         <is>
-          <t>Planes above the tutorial tier can be leased from chapter 2 (D42). Tutorial planes can be leased from week 2 (the rent-or-buy lesson).</t>
+          <t>D42/D76: leasing first appears with the 757 and 787 in January 2031 (price ÷ 1,000 a day). The rent-or-buy sum (price ÷ rent) is first met there.</t>
         </is>
       </c>
       <c r="D37" s="13" t="inlineStr">
@@ -31051,7 +31063,7 @@
       </c>
       <c r="C39" s="13" t="inlineStr">
         <is>
-          <t>Finance (deposit and weekly repayments) available from chapter 4, introduced with the A380 (D43).</t>
+          <t>D43: finance (deposit and weekly payments) with the A380, chapter 4.</t>
         </is>
       </c>
       <c r="D39" s="13" t="inlineStr">
@@ -31930,12 +31942,12 @@
       </c>
       <c r="B82" s="13" t="inlineStr">
         <is>
-          <t>choose plane, then how to pay</t>
+          <t>choose plane, or wait</t>
         </is>
       </c>
       <c r="C82" s="13" t="inlineStr">
         <is>
-          <t>D62: the week-2 decision is two screens: compare the three aircraft side by side, then compare rent / finance / buy for the chosen one.</t>
+          <t>D62/D76: the week-2 comparison's second screen is 'Buy now or wait?': for each plane, cash now, price, still to save, days to wait at the current rate, and what waiting costs (the smaller plane's extra profit × days). Buy is greyed with the shortfall when unaffordable.</t>
         </is>
       </c>
       <c r="D82" s="13" t="inlineStr">
@@ -32681,6 +32693,48 @@
         </is>
       </c>
       <c r="D119" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="13" t="inlineStr">
+        <is>
+          <t>chapter1BuyOnly</t>
+        </is>
+      </c>
+      <c r="B120" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="C120" s="13" t="inlineStr">
+        <is>
+          <t>D76: in chapter 1 planes are bought outright only. No rent, no launch-deal finance. The week-2 decision is buy a smaller plane now or wait for a bigger one; the week-2 hand sum is time to afford: (price − cash) ÷ profit a day.</t>
+        </is>
+      </c>
+      <c r="D120" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="13" t="inlineStr">
+        <is>
+          <t>timeToAffordSum</t>
+        </is>
+      </c>
+      <c r="B121" s="13" t="inlineStr">
+        <is>
+          <t>(price − cash) ÷ profit a day = days to wait</t>
+        </is>
+      </c>
+      <c r="C121" s="13" t="inlineStr">
+        <is>
+          <t>D76: Calculate the first time (week 2), Build after.</t>
+        </is>
+      </c>
+      <c r="D121" s="13" t="inlineStr">
         <is>
           <t>live</t>
         </is>

--- a/data/Airline-World-Workbook.xlsx
+++ b/data/Airline-World-Workbook.xlsx
@@ -16,19 +16,20 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RouteNews" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Archetypes" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EventOptions" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Routes" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RouteCatalogue" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aircraft" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Finance" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Airports" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calendar" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Market" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Events" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Challenges" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mechanics" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catering" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hunts" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Livery" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Campaign" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Routes" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RouteCatalogue" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aircraft" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Finance" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Airports" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calendar" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Market" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Events" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Challenges" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mechanics" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catering" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hunts" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Livery" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -571,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A29"/>
+  <dimension ref="A1:A31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -777,6 +778,20 @@
       <c r="A29" s="17" t="inlineStr">
         <is>
           <t>v5.4 (14 Oct): D81 rules Claude Code asked for — overdraft replaces the reserve from 1 Sep 2031 and what happens at the limit; buying a rented plane (list price, rent stops); handing a lease back at a month end; new EventOptions sheet (one row per option for every event with choices, chapters 1–3); challenge rewards as a share of a day's profit or stars (Challenges.rewardShare), challenge 5's 52 weeks; h3 specified (the 787's June rent, £180,000); the missed-h1 effect; secondCrewCost live; five WorkingMethods rows for chapter 3's sums with Bettws codes; chapter 3 opens Monday 1 September 2031 (confirmed).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>v5.5 (14 Oct): CHAPTER 4 LIVE. Finance is monthly for every big plane (deposit, then 40 round monthly payments; A380 £20m + £1m × 40; 747 £16m + £600,000 × 40) from 6 Sep 2032 (D83); the 747 is a real alternative to the A380 (D84); Hong Kong and Los Angeles open 6 Sep 2032 with A380-sized pools (D85); the A380 and 747 live with per-seat costs; Market weeks 105–156 live with forecasts; 17 route-news items; year-3 events (storm3, fuel_shock3, ash_cloud3) and the A380 offer with option rows; Challenges 5–6 and Hunt h5 live; a Campaign sheet for the A380 launch project (D82) with placeholder funnel and reach values; chapter-4 Calendar days 736–742; WorkingMethods rows for finance, does-it-fill and the campaign funnel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="17" t="inlineStr">
+        <is>
+          <t>v5.6 (15 Oct): D86 working on paper — the workbench is an answer box, methods are reference cards; the two-tries rule; fuel is one sum a week (the Monday order, blocks × price per 1,000 L, by hand only on a 50p move) with the bill broken down by route and plane automatically; Launch Day keeps five sums (snacks as Build); cap of three a week confirmed. HandSumRules 2, 4 and 12. Every sum is numbered (Settings sumNumbering) so paper working matches the record.</t>
         </is>
       </c>
     </row>
@@ -791,7 +806,269 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V28"/>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="20" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="B1" s="20" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="C1" s="20" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="D1" s="20" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>project</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>The A380 launch</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="inlineStr">
+        <is>
+          <t>One standalone creative project (D82). The game pauses while the pupil works on it over several sessions; the result applies from the launch date he chooses.</t>
+        </is>
+      </c>
+      <c r="D2" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>brief</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>Fill the A380's first month on Hong Kong (or Los Angeles). Tell people what flying on it is like, and give them a reason to book now.</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>Shown as a letter from the board.</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>choices</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>route (hkg | lax); audience (business | families | holidaymakers); channel (stations | online | sponsorship); budget (share of a month's profit: 0.05 | 0.1 | 0.2); launch date; length (2 | 4 | 8 weeks)</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>The structured part the engine reads.</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>portfolio</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>livery and cabin concept; a poster or a 30–90 second advert (script and storyboard); an offer; optionally a snack or activity idea</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Hand-drawn work counts; photographed or scanned in.</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>aiSignals</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>audience_fit, message_clarity, offer_visibility, brand_consistency, distinctiveness, trust, experience_fit — each 0–4; plus strongest_feature and missed_opportunity</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>The AI (or the teacher from a rubric) returns these. The pupil sees three in plain words: speaks to the people you chose? offer clear? honest?</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>focusGroup</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>20 people from the chosen audience: count who would book, with short comments</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>Count = round(20 × average of audience_fit, message_clarity, offer_visibility, trust ÷ 4). The pupil's appeal figure, as a fraction and a percentage.</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>reach</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>stations: business 0.6, families 0.2, holidaymakers 0.3 · online: 0.3, 0.4, 0.6 · sponsorship: 0.2, 0.6, 0.4 — share of the route's pool reached per 0.1 of a month's profit spent, capped at 0.9</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>Placeholder values; deterministic.</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>funnel</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>reached → remember (0.8) → understand the offer (offer_visibility ÷ 4) → consider us (brand_consistency ÷ 4 × stars factor) → can use the fare and times (engine) → get a seat (capacity)</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>Shown as six bars; the last two are the engine's usual demand and capacity. Decays 20% a week after the campaign ends.</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>honesty</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>a claim the AI flags as untrue (cheapest, fastest, biggest) → trust 0 and −½★</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Shown by the focus group calling it out.</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>teacherOverride</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>The teacher sees the AI's signals first and can change them or score from the rubric with no AI.</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:V30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3037,12 +3314,184 @@
         <v>4</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>hkg</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="D29" s="13" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="n">
+        <v>22.31</v>
+      </c>
+      <c r="F29" s="13" t="n">
+        <v>113.92</v>
+      </c>
+      <c r="G29" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="H29" s="13" t="inlineStr">
+        <is>
+          <t>long_haul</t>
+        </is>
+      </c>
+      <c r="I29" s="13" t="n">
+        <v>9600</v>
+      </c>
+      <c r="J29" s="13" t="n">
+        <v>120</v>
+      </c>
+      <c r="K29" s="13" t="n">
+        <v>450</v>
+      </c>
+      <c r="L29" s="13" t="n">
+        <v>830</v>
+      </c>
+      <c r="M29" s="13" t="inlineStr">
+        <is>
+          <t>790|810|830|850|870</t>
+        </is>
+      </c>
+      <c r="N29" s="13" t="inlineStr">
+        <is>
+          <t>770:600|790:560|810:520|830:480|850:440|870:400|890:360|910:320</t>
+        </is>
+      </c>
+      <c r="O29" s="13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P29" s="13" t="n">
+        <v>736</v>
+      </c>
+      <c r="Q29" s="13" t="inlineStr">
+        <is>
+          <t>The A380's route. 480 want to fly at £830: a 747 fills, an A380 is 58 short — unless the stars are up or the fare comes down. Eight hours ahead.</t>
+        </is>
+      </c>
+      <c r="R29" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="S29" s="13" t="inlineStr">
+        <is>
+          <t>overnight</t>
+        </is>
+      </c>
+      <c r="T29" s="13" t="inlineStr"/>
+      <c r="U29" s="13" t="inlineStr"/>
+      <c r="V29" s="13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>lax</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>LAX</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="n">
+        <v>33.94</v>
+      </c>
+      <c r="F30" s="13" t="n">
+        <v>-118.41</v>
+      </c>
+      <c r="G30" s="13" t="n">
+        <v>-8</v>
+      </c>
+      <c r="H30" s="13" t="inlineStr">
+        <is>
+          <t>long_haul</t>
+        </is>
+      </c>
+      <c r="I30" s="13" t="n">
+        <v>8750</v>
+      </c>
+      <c r="J30" s="13" t="n">
+        <v>120</v>
+      </c>
+      <c r="K30" s="13" t="n">
+        <v>420</v>
+      </c>
+      <c r="L30" s="13" t="n">
+        <v>760</v>
+      </c>
+      <c r="M30" s="13" t="inlineStr">
+        <is>
+          <t>720|740|760|780|800</t>
+        </is>
+      </c>
+      <c r="N30" s="13" t="inlineStr">
+        <is>
+          <t>700:580|720:540|740:500|760:460|780:420|800:380|820:340|840:300</t>
+        </is>
+      </c>
+      <c r="O30" s="13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P30" s="13" t="n">
+        <v>736</v>
+      </c>
+      <c r="Q30" s="13" t="inlineStr">
+        <is>
+          <t>Eight hours behind: leave at 06:30, land at 08:15 the same morning, Los Angeles time. Big in summer. The second A380-sized pool.</t>
+        </is>
+      </c>
+      <c r="R30" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="S30" s="13" t="inlineStr">
+        <is>
+          <t>overnight</t>
+        </is>
+      </c>
+      <c r="T30" s="13" t="inlineStr">
+        <is>
+          <t>summer:1.15,winter:0.9</t>
+        </is>
+      </c>
+      <c r="U30" s="13" t="inlineStr"/>
+      <c r="V30" s="13" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4308,7 +4757,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4946,116 +5395,116 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>b747</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>Boeing 747</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>icon</t>
         </is>
       </c>
-      <c r="D11" s="15" t="n">
+      <c r="D11" s="12" t="n">
         <v>400</v>
       </c>
-      <c r="E11" s="15" t="n">
+      <c r="E11" s="12" t="n">
         <v>900</v>
       </c>
-      <c r="F11" s="15" t="n">
+      <c r="F11" s="12" t="n">
         <v>13000</v>
       </c>
-      <c r="G11" s="15" t="n">
-        <v>240</v>
-      </c>
-      <c r="H11" s="15" t="n">
-        <v>3600</v>
-      </c>
-      <c r="I11" s="15" t="n">
-        <v>10000</v>
-      </c>
-      <c r="J11" s="15" t="n">
+      <c r="G11" s="12" t="n">
+        <v>230</v>
+      </c>
+      <c r="H11" s="12" t="n">
+        <v>3400</v>
+      </c>
+      <c r="I11" s="12" t="n">
+        <v>9200</v>
+      </c>
+      <c r="J11" s="12" t="n">
         <v>40000000</v>
       </c>
-      <c r="K11" s="15" t="inlineStr"/>
-      <c r="L11" s="15" t="n">
+      <c r="K11" s="12" t="inlineStr"/>
+      <c r="L11" s="12" t="n">
         <v>736</v>
       </c>
-      <c r="M11" s="15" t="inlineStr">
-        <is>
-          <t>Named by the pupil. 400 seats, roomy, thirsty. Chapter 4.</t>
-        </is>
-      </c>
-      <c r="N11" s="18" t="n"/>
-      <c r="O11" s="18" t="n"/>
-      <c r="P11" s="18" t="n"/>
-      <c r="Q11" s="18" t="n"/>
-      <c r="R11" s="18" t="n"/>
-      <c r="S11" s="15" t="inlineStr">
-        <is>
-          <t>later</t>
+      <c r="M11" s="12" t="inlineStr">
+        <is>
+          <t>Named by the pupil. 400 seats, the famous hump, thirstier per seat than the A380 but £20m cheaper: the real alternative. Full at three stars on Hong Kong.</t>
+        </is>
+      </c>
+      <c r="N11" s="13" t="n"/>
+      <c r="O11" s="13" t="n"/>
+      <c r="P11" s="13" t="n"/>
+      <c r="Q11" s="13" t="n"/>
+      <c r="R11" s="13" t="n"/>
+      <c r="S11" s="12" t="inlineStr">
+        <is>
+          <t>live</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>a380</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>Airbus A380</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
         <is>
           <t>icon</t>
         </is>
       </c>
-      <c r="D12" s="15" t="n">
+      <c r="D12" s="12" t="n">
         <v>500</v>
       </c>
-      <c r="E12" s="15" t="n">
+      <c r="E12" s="12" t="n">
         <v>900</v>
       </c>
-      <c r="F12" s="15" t="n">
+      <c r="F12" s="12" t="n">
         <v>15000</v>
       </c>
-      <c r="G12" s="15" t="n">
+      <c r="G12" s="12" t="n">
         <v>250</v>
       </c>
-      <c r="H12" s="15" t="n">
+      <c r="H12" s="12" t="n">
         <v>4000</v>
       </c>
-      <c r="I12" s="15" t="n">
+      <c r="I12" s="12" t="n">
         <v>12000</v>
       </c>
-      <c r="J12" s="15" t="n">
+      <c r="J12" s="12" t="n">
         <v>60000000</v>
       </c>
-      <c r="K12" s="15" t="inlineStr"/>
-      <c r="L12" s="15" t="n">
+      <c r="K12" s="12" t="inlineStr"/>
+      <c r="L12" s="12" t="n">
         <v>736</v>
       </c>
-      <c r="M12" s="15" t="inlineStr">
-        <is>
-          <t>'The ultimate plane.' 500 seats. Chapter 4's new idea: financed, not bought (£18m down, then £808,000 a week for a year). Only fills on the busiest route with a strong reputation.</t>
-        </is>
-      </c>
-      <c r="N12" s="18" t="n"/>
-      <c r="O12" s="18" t="n"/>
-      <c r="P12" s="18" t="n"/>
-      <c r="Q12" s="18" t="n"/>
-      <c r="R12" s="18" t="n"/>
-      <c r="S12" s="15" t="inlineStr">
-        <is>
-          <t>later</t>
+      <c r="M12" s="12" t="inlineStr">
+        <is>
+          <t>'The ultimate plane.' 500 seats on two decks. Financed, never bought: £20m down, then £1m a month for 40 months. Fills Hong Kong at three stars only at the bottom fare; at four and a half stars it fills at £830 and earns £10,000 a day more than a 747.</t>
+        </is>
+      </c>
+      <c r="N12" s="13" t="n"/>
+      <c r="O12" s="13" t="n"/>
+      <c r="P12" s="13" t="n"/>
+      <c r="Q12" s="13" t="n"/>
+      <c r="R12" s="13" t="n"/>
+      <c r="S12" s="12" t="inlineStr">
+        <is>
+          <t>live</t>
         </is>
       </c>
     </row>
@@ -5351,7 +5800,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5397,12 +5846,12 @@
       </c>
       <c r="E1" s="21" t="inlineStr">
         <is>
-          <t>financeWeeklyPayment</t>
+          <t>monthlyPayment</t>
         </is>
       </c>
       <c r="F1" s="21" t="inlineStr">
         <is>
-          <t>financeWeeks</t>
+          <t>months</t>
         </is>
       </c>
       <c r="G1" s="21" t="inlineStr">
@@ -5841,16 +6290,16 @@
         <v>1500</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>900000</v>
+        <v>1000000</v>
       </c>
       <c r="E10" s="13" t="n">
-        <v>40000</v>
+        <v>50000</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>2980000</v>
+        <v>3000000</v>
       </c>
       <c r="H10" s="13" t="inlineStr">
         <is>
@@ -5891,16 +6340,16 @@
         <v>6000</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>3600000</v>
+        <v>4000000</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>162000</v>
+        <v>200000</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>12024000</v>
+        <v>12000000</v>
       </c>
       <c r="H11" s="13" t="inlineStr">
         <is>
@@ -5941,16 +6390,16 @@
         <v>5000</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>3000000</v>
+        <v>2000000</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>135000</v>
+        <v>200000</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>10020000</v>
+        <v>10000000</v>
       </c>
       <c r="H12" s="13" t="inlineStr">
         <is>
@@ -5987,16 +6436,16 @@
         <v>12000</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>7200000</v>
+        <v>8000000</v>
       </c>
       <c r="E13" s="13" t="n">
-        <v>323000</v>
+        <v>400000</v>
       </c>
       <c r="F13" s="13" t="n">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>23996000</v>
+        <v>24000000</v>
       </c>
       <c r="H13" s="13" t="inlineStr">
         <is>
@@ -6033,16 +6482,16 @@
         <v>15000</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>9000000</v>
+        <v>10000000</v>
       </c>
       <c r="E14" s="13" t="n">
-        <v>404000</v>
+        <v>500000</v>
       </c>
       <c r="F14" s="13" t="n">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="G14" s="13" t="n">
-        <v>30008000</v>
+        <v>30000000</v>
       </c>
       <c r="H14" s="13" t="inlineStr">
         <is>
@@ -6067,98 +6516,102 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>b747</t>
         </is>
       </c>
-      <c r="B15" s="18" t="n">
+      <c r="B15" s="13" t="n">
         <v>40000000</v>
       </c>
-      <c r="C15" s="18" t="n">
+      <c r="C15" s="13" t="n">
         <v>20000</v>
       </c>
-      <c r="D15" s="18" t="n">
-        <v>12000000</v>
-      </c>
-      <c r="E15" s="18" t="n">
-        <v>538000</v>
-      </c>
-      <c r="F15" s="18" t="n">
-        <v>52</v>
-      </c>
-      <c r="G15" s="18" t="n">
-        <v>39976000</v>
-      </c>
-      <c r="H15" s="18" t="inlineStr">
+      <c r="D15" s="13" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="E15" s="13" t="n">
+        <v>600000</v>
+      </c>
+      <c r="F15" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="G15" s="13" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H15" s="13" t="inlineStr">
         <is>
           <t>2032-09-07</t>
         </is>
       </c>
-      <c r="I15" s="18" t="inlineStr">
+      <c r="I15" s="13" t="inlineStr">
         <is>
           <t>2032-09-06</t>
         </is>
       </c>
-      <c r="J15" s="18" t="inlineStr">
+      <c r="J15" s="13" t="inlineStr">
         <is>
           <t>2032-09-06</t>
         </is>
       </c>
-      <c r="K15" s="18" t="inlineStr"/>
-      <c r="L15" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
+      <c r="K15" s="13" t="inlineStr">
+        <is>
+          <t>The real alternative to the A380 (D84): £16m down, £600,000 a month; 400 seats; thirstier per seat. At three stars it earns as much as the A380 after payments; the A380 pulls ahead with stars or growth.</t>
+        </is>
+      </c>
+      <c r="L15" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>a380</t>
         </is>
       </c>
-      <c r="B16" s="18" t="n">
+      <c r="B16" s="13" t="n">
         <v>60000000</v>
       </c>
-      <c r="C16" s="18" t="n">
+      <c r="C16" s="13" t="n">
         <v>30000</v>
       </c>
-      <c r="D16" s="18" t="n">
-        <v>18000000</v>
-      </c>
-      <c r="E16" s="18" t="n">
-        <v>808000</v>
-      </c>
-      <c r="F16" s="18" t="n">
-        <v>52</v>
-      </c>
-      <c r="G16" s="18" t="n">
-        <v>60016000</v>
-      </c>
-      <c r="H16" s="18" t="inlineStr">
+      <c r="D16" s="13" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="E16" s="13" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="G16" s="13" t="n">
+        <v>60000000</v>
+      </c>
+      <c r="H16" s="13" t="inlineStr">
         <is>
           <t>2032-09-07</t>
         </is>
       </c>
-      <c r="I16" s="18" t="inlineStr">
+      <c r="I16" s="13" t="inlineStr">
         <is>
           <t>2032-09-06</t>
         </is>
       </c>
-      <c r="J16" s="18" t="inlineStr">
+      <c r="J16" s="13" t="inlineStr">
         <is>
           <t>2032-09-06</t>
         </is>
       </c>
-      <c r="K16" s="18" t="inlineStr">
-        <is>
-          <t>Chapter 4's worked example: 60,000,000 − 18,000,000 = 42,000,000; ÷ 52 ≈ £808,000 a week; total paid £60.0m.</t>
-        </is>
-      </c>
-      <c r="L16" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
+      <c r="K16" s="13" t="inlineStr">
+        <is>
+          <t>Chapter 4's worked example: 60,000,000 − 20,000,000 = 40,000,000; ÷ 40 = £1,000,000 a month; total paid £60m (no interest: PS4 maths). About a third of a good airline's monthly profit.</t>
+        </is>
+      </c>
+      <c r="L16" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
         </is>
       </c>
     </row>
@@ -6181,7 +6634,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6489,13 +6942,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R43"/>
+  <dimension ref="A1:R50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6652,7 +7105,7 @@
       <c r="J2" s="13" t="inlineStr"/>
       <c r="K2" s="13" t="inlineStr">
         <is>
-          <t>routes: dub, par; planes: dhc6 (launch deal); mechanics: timetable with demand curve, fare, snacks, fuel, modelling tool, workings page</t>
+          <t>routes: dub, par; planes: dhc6 (launch deal); mechanics: timetable with demand curve, fare, snacks, fuel, modelling tool, answer box (working on paper)</t>
         </is>
       </c>
       <c r="L2" s="13" t="inlineStr"/>
@@ -6664,7 +7117,7 @@
       </c>
       <c r="O2" s="13" t="inlineStr">
         <is>
-          <t>ticketRevenue,profit,snackRevenue,fuelCost</t>
+          <t>ticketRevenue,profit,fuelOrder</t>
         </is>
       </c>
       <c r="P2" s="13" t="n"/>
@@ -8016,11 +8469,7 @@
           <t>fuel</t>
         </is>
       </c>
-      <c r="O25" s="13" t="inlineStr">
-        <is>
-          <t>fuelCost</t>
-        </is>
-      </c>
+      <c r="O25" s="13" t="inlineStr"/>
       <c r="P25" s="13" t="n"/>
       <c r="Q25" s="13" t="inlineStr">
         <is>
@@ -9053,12 +9502,398 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="13" t="n">
+        <v>736</v>
+      </c>
+      <c r="B44" s="13" t="inlineStr">
+        <is>
+          <t>2032-09-06</t>
+        </is>
+      </c>
+      <c r="C44" s="13" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="D44" s="13" t="n">
+        <v>106</v>
+      </c>
+      <c r="E44" s="13" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="F44" s="13" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="G44" s="13" t="inlineStr">
+        <is>
+          <t>Chapter 4: the ultimate plane</t>
+        </is>
+      </c>
+      <c r="H44" s="13" t="inlineStr">
+        <is>
+          <t>Airbus offers you an A380 on finance. Hong Kong and Los Angeles open — the only routes big enough for it. Or take the 747.</t>
+        </is>
+      </c>
+      <c r="I44" s="13" t="inlineStr">
+        <is>
+          <t>Fuel £2.35 a litre.</t>
+        </is>
+      </c>
+      <c r="J44" s="13" t="inlineStr">
+        <is>
+          <t>a380_offer</t>
+        </is>
+      </c>
+      <c r="K44" s="13" t="inlineStr">
+        <is>
+          <t>routes: hkg, lax; planes: b747, a380 (finance); mechanics: finance (deposit + monthly), does it fill (demand ÷ seats)</t>
+        </is>
+      </c>
+      <c r="L44" s="13" t="n"/>
+      <c r="M44" s="13" t="n"/>
+      <c r="N44" s="13" t="inlineStr">
+        <is>
+          <t>fleet,assignment,pricing</t>
+        </is>
+      </c>
+      <c r="O44" s="13" t="inlineStr">
+        <is>
+          <t>financeDeposit,doesItFill</t>
+        </is>
+      </c>
+      <c r="P44" s="13" t="n"/>
+      <c r="Q44" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="R44" s="13" t="inlineStr">
+        <is>
+          <t>plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="13" t="n">
+        <v>737</v>
+      </c>
+      <c r="B45" s="13" t="inlineStr">
+        <is>
+          <t>2032-09-07</t>
+        </is>
+      </c>
+      <c r="C45" s="13" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D45" s="13" t="n">
+        <v>106</v>
+      </c>
+      <c r="E45" s="13" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="F45" s="13" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="G45" s="13" t="inlineStr">
+        <is>
+          <t>Tuesday: the first Hong Kong flight</t>
+        </is>
+      </c>
+      <c r="H45" s="13" t="inlineStr"/>
+      <c r="I45" s="13" t="inlineStr"/>
+      <c r="J45" s="13" t="inlineStr"/>
+      <c r="K45" s="13" t="inlineStr"/>
+      <c r="L45" s="13" t="n"/>
+      <c r="M45" s="13" t="n"/>
+      <c r="N45" s="13" t="inlineStr"/>
+      <c r="O45" s="13" t="inlineStr"/>
+      <c r="P45" s="13" t="n"/>
+      <c r="Q45" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="R45" s="13" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="13" t="n">
+        <v>738</v>
+      </c>
+      <c r="B46" s="13" t="inlineStr">
+        <is>
+          <t>2032-09-08</t>
+        </is>
+      </c>
+      <c r="C46" s="13" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="D46" s="13" t="n">
+        <v>106</v>
+      </c>
+      <c r="E46" s="13" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="F46" s="13" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="G46" s="13" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="H46" s="13" t="inlineStr"/>
+      <c r="I46" s="13" t="inlineStr"/>
+      <c r="J46" s="13" t="inlineStr"/>
+      <c r="K46" s="13" t="inlineStr"/>
+      <c r="L46" s="13" t="n"/>
+      <c r="M46" s="13" t="n"/>
+      <c r="N46" s="13" t="inlineStr">
+        <is>
+          <t>fuel</t>
+        </is>
+      </c>
+      <c r="O46" s="13" t="inlineStr"/>
+      <c r="P46" s="13" t="n"/>
+      <c r="Q46" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="R46" s="13" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="13" t="n">
+        <v>739</v>
+      </c>
+      <c r="B47" s="13" t="inlineStr">
+        <is>
+          <t>2032-09-09</t>
+        </is>
+      </c>
+      <c r="C47" s="13" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="D47" s="13" t="n">
+        <v>106</v>
+      </c>
+      <c r="E47" s="13" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="F47" s="13" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="G47" s="13" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="H47" s="13" t="inlineStr"/>
+      <c r="I47" s="13" t="inlineStr"/>
+      <c r="J47" s="13" t="inlineStr"/>
+      <c r="K47" s="13" t="inlineStr"/>
+      <c r="L47" s="13" t="n"/>
+      <c r="M47" s="13" t="n"/>
+      <c r="N47" s="13" t="inlineStr"/>
+      <c r="O47" s="13" t="inlineStr"/>
+      <c r="P47" s="13" t="n"/>
+      <c r="Q47" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="R47" s="13" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="13" t="n">
+        <v>740</v>
+      </c>
+      <c r="B48" s="13" t="inlineStr">
+        <is>
+          <t>2032-09-10</t>
+        </is>
+      </c>
+      <c r="C48" s="13" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="D48" s="13" t="n">
+        <v>106</v>
+      </c>
+      <c r="E48" s="13" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="F48" s="13" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="G48" s="13" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="H48" s="13" t="inlineStr"/>
+      <c r="I48" s="13" t="inlineStr"/>
+      <c r="J48" s="13" t="inlineStr"/>
+      <c r="K48" s="13" t="inlineStr"/>
+      <c r="L48" s="13" t="n"/>
+      <c r="M48" s="13" t="n"/>
+      <c r="N48" s="13" t="inlineStr"/>
+      <c r="O48" s="13" t="inlineStr"/>
+      <c r="P48" s="13" t="n"/>
+      <c r="Q48" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="R48" s="13" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="13" t="n">
+        <v>741</v>
+      </c>
+      <c r="B49" s="13" t="inlineStr">
+        <is>
+          <t>2032-09-11</t>
+        </is>
+      </c>
+      <c r="C49" s="13" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="D49" s="13" t="n">
+        <v>106</v>
+      </c>
+      <c r="E49" s="13" t="inlineStr">
+        <is>
+          <t>weekend</t>
+        </is>
+      </c>
+      <c r="F49" s="13" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="G49" s="13" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="H49" s="13" t="inlineStr"/>
+      <c r="I49" s="13" t="inlineStr"/>
+      <c r="J49" s="13" t="inlineStr"/>
+      <c r="K49" s="13" t="inlineStr"/>
+      <c r="L49" s="13" t="n"/>
+      <c r="M49" s="13" t="n"/>
+      <c r="N49" s="13" t="inlineStr"/>
+      <c r="O49" s="13" t="inlineStr"/>
+      <c r="P49" s="13" t="n"/>
+      <c r="Q49" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="R49" s="13" t="inlineStr">
+        <is>
+          <t>run</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="13" t="n">
+        <v>742</v>
+      </c>
+      <c r="B50" s="13" t="inlineStr">
+        <is>
+          <t>2032-09-12</t>
+        </is>
+      </c>
+      <c r="C50" s="13" t="inlineStr">
+        <is>
+          <t>Sun</t>
+        </is>
+      </c>
+      <c r="D50" s="13" t="n">
+        <v>106</v>
+      </c>
+      <c r="E50" s="13" t="inlineStr">
+        <is>
+          <t>weekend</t>
+        </is>
+      </c>
+      <c r="F50" s="13" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="G50" s="13" t="inlineStr">
+        <is>
+          <t>Sunday: the first week of chapter 4</t>
+        </is>
+      </c>
+      <c r="H50" s="13" t="inlineStr"/>
+      <c r="I50" s="13" t="inlineStr"/>
+      <c r="J50" s="13" t="inlineStr"/>
+      <c r="K50" s="13" t="inlineStr"/>
+      <c r="L50" s="13" t="n"/>
+      <c r="M50" s="13" t="n"/>
+      <c r="N50" s="13" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="O50" s="13" t="inlineStr">
+        <is>
+          <t>weekTotal,projectedVsActual,mean</t>
+        </is>
+      </c>
+      <c r="P50" s="13" t="n"/>
+      <c r="Q50" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="R50" s="13" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15014,2148 +15849,2848 @@
       <c r="P105" s="13" t="n"/>
     </row>
     <row r="106">
-      <c r="A106" s="18" t="n">
+      <c r="A106" s="13" t="n">
         <v>105</v>
       </c>
-      <c r="B106" s="18" t="inlineStr">
+      <c r="B106" s="13" t="inlineStr">
         <is>
           <t>2032-08-30</t>
         </is>
       </c>
-      <c r="C106" s="18" t="inlineStr">
+      <c r="C106" s="13" t="inlineStr">
         <is>
           <t>summer</t>
         </is>
       </c>
-      <c r="D106" s="18" t="n">
+      <c r="D106" s="13" t="n">
         <v>2.31</v>
       </c>
-      <c r="E106" s="18" t="n">
+      <c r="E106" s="13" t="n">
         <v>0.85</v>
       </c>
-      <c r="F106" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G106" s="18" t="n">
+      <c r="F106" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G106" s="13" t="n">
         <v>1.3</v>
       </c>
-      <c r="H106" s="18" t="n">
+      <c r="H106" s="13" t="n">
         <v>0.5</v>
       </c>
-      <c r="I106" s="18" t="inlineStr">
+      <c r="I106" s="13" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="J106" s="18" t="inlineStr">
+      <c r="J106" s="13" t="inlineStr">
         <is>
           <t>Chapter 4 begins: the ultimate plane.</t>
         </is>
       </c>
-      <c r="K106" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="K106" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L106" s="13" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="M106" s="13" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="N106" s="13" t="inlineStr">
+        <is>
+          <t>Year three: the airline is now a big buyer; prices firm.</t>
+        </is>
+      </c>
+      <c r="O106" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P106" s="13" t="n"/>
     </row>
     <row r="107">
-      <c r="A107" s="18" t="n">
+      <c r="A107" s="13" t="n">
         <v>106</v>
       </c>
-      <c r="B107" s="18" t="inlineStr">
+      <c r="B107" s="13" t="inlineStr">
         <is>
           <t>2032-09-06</t>
         </is>
       </c>
-      <c r="C107" s="18" t="inlineStr">
+      <c r="C107" s="13" t="inlineStr">
         <is>
           <t>autumn</t>
         </is>
       </c>
-      <c r="D107" s="18" t="n">
+      <c r="D107" s="13" t="n">
         <v>2.35</v>
       </c>
-      <c r="E107" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F107" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G107" s="18" t="n">
+      <c r="E107" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F107" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" s="13" t="n">
         <v>1.1</v>
       </c>
-      <c r="H107" s="18" t="n">
+      <c r="H107" s="13" t="n">
         <v>0.5</v>
       </c>
-      <c r="I107" s="18" t="inlineStr">
+      <c r="I107" s="13" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="J107" s="18" t="inlineStr"/>
-      <c r="K107" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="J107" s="13" t="inlineStr"/>
+      <c r="K107" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L107" s="13" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="M107" s="13" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="N107" s="13" t="n"/>
+      <c r="O107" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P107" s="13" t="n"/>
     </row>
     <row r="108">
-      <c r="A108" s="18" t="n">
+      <c r="A108" s="13" t="n">
         <v>107</v>
       </c>
-      <c r="B108" s="18" t="inlineStr">
+      <c r="B108" s="13" t="inlineStr">
         <is>
           <t>2032-09-13</t>
         </is>
       </c>
-      <c r="C108" s="18" t="inlineStr">
+      <c r="C108" s="13" t="inlineStr">
         <is>
           <t>autumn</t>
         </is>
       </c>
-      <c r="D108" s="18" t="n">
+      <c r="D108" s="13" t="n">
         <v>2.39</v>
       </c>
-      <c r="E108" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F108" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G108" s="18" t="n">
+      <c r="E108" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F108" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G108" s="13" t="n">
         <v>1.1</v>
       </c>
-      <c r="H108" s="18" t="n">
+      <c r="H108" s="13" t="n">
         <v>0.5</v>
       </c>
-      <c r="I108" s="18" t="inlineStr">
+      <c r="I108" s="13" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="J108" s="18" t="inlineStr"/>
-      <c r="K108" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="J108" s="13" t="inlineStr"/>
+      <c r="K108" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L108" s="13" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="M108" s="13" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="N108" s="13" t="n"/>
+      <c r="O108" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P108" s="13" t="n"/>
     </row>
     <row r="109">
-      <c r="A109" s="18" t="n">
+      <c r="A109" s="13" t="n">
         <v>108</v>
       </c>
-      <c r="B109" s="18" t="inlineStr">
+      <c r="B109" s="13" t="inlineStr">
         <is>
           <t>2032-09-20</t>
         </is>
       </c>
-      <c r="C109" s="18" t="inlineStr">
+      <c r="C109" s="13" t="inlineStr">
         <is>
           <t>autumn</t>
         </is>
       </c>
-      <c r="D109" s="18" t="n">
+      <c r="D109" s="13" t="n">
         <v>2.45</v>
       </c>
-      <c r="E109" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F109" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G109" s="18" t="n">
+      <c r="E109" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F109" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G109" s="13" t="n">
         <v>1.1</v>
       </c>
-      <c r="H109" s="18" t="n">
+      <c r="H109" s="13" t="n">
         <v>0.5</v>
       </c>
-      <c r="I109" s="18" t="inlineStr">
+      <c r="I109" s="13" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="J109" s="18" t="inlineStr"/>
-      <c r="K109" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="J109" s="13" t="inlineStr"/>
+      <c r="K109" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L109" s="13" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="M109" s="13" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="N109" s="13" t="n"/>
+      <c r="O109" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P109" s="13" t="n"/>
     </row>
     <row r="110">
-      <c r="A110" s="18" t="n">
+      <c r="A110" s="13" t="n">
         <v>109</v>
       </c>
-      <c r="B110" s="18" t="inlineStr">
+      <c r="B110" s="13" t="inlineStr">
         <is>
           <t>2032-09-27</t>
         </is>
       </c>
-      <c r="C110" s="18" t="inlineStr">
+      <c r="C110" s="13" t="inlineStr">
         <is>
           <t>autumn</t>
         </is>
       </c>
-      <c r="D110" s="18" t="n">
+      <c r="D110" s="13" t="n">
         <v>2.49</v>
       </c>
-      <c r="E110" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F110" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G110" s="18" t="n">
+      <c r="E110" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F110" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G110" s="13" t="n">
         <v>1.1</v>
       </c>
-      <c r="H110" s="18" t="n">
+      <c r="H110" s="13" t="n">
         <v>0.5</v>
       </c>
-      <c r="I110" s="18" t="inlineStr">
+      <c r="I110" s="13" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="J110" s="18" t="inlineStr"/>
-      <c r="K110" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="J110" s="13" t="inlineStr"/>
+      <c r="K110" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L110" s="13" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M110" s="13" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="N110" s="13" t="n"/>
+      <c r="O110" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P110" s="13" t="n"/>
     </row>
     <row r="111">
-      <c r="A111" s="18" t="n">
+      <c r="A111" s="13" t="n">
         <v>110</v>
       </c>
-      <c r="B111" s="18" t="inlineStr">
+      <c r="B111" s="13" t="inlineStr">
         <is>
           <t>2032-10-04</t>
         </is>
       </c>
-      <c r="C111" s="18" t="inlineStr">
+      <c r="C111" s="13" t="inlineStr">
         <is>
           <t>autumn</t>
         </is>
       </c>
-      <c r="D111" s="18" t="n">
+      <c r="D111" s="13" t="n">
         <v>2.53</v>
       </c>
-      <c r="E111" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F111" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G111" s="18" t="n">
+      <c r="E111" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F111" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G111" s="13" t="n">
         <v>0.9</v>
       </c>
-      <c r="H111" s="18" t="n">
+      <c r="H111" s="13" t="n">
         <v>0.6</v>
       </c>
-      <c r="I111" s="18" t="inlineStr">
+      <c r="I111" s="13" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="J111" s="18" t="inlineStr"/>
-      <c r="K111" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="J111" s="13" t="inlineStr"/>
+      <c r="K111" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L111" s="13" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="M111" s="13" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="N111" s="13" t="n"/>
+      <c r="O111" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P111" s="13" t="n"/>
     </row>
     <row r="112">
-      <c r="A112" s="18" t="n">
+      <c r="A112" s="13" t="n">
         <v>111</v>
       </c>
-      <c r="B112" s="18" t="inlineStr">
+      <c r="B112" s="13" t="inlineStr">
         <is>
           <t>2032-10-11</t>
         </is>
       </c>
-      <c r="C112" s="18" t="inlineStr">
+      <c r="C112" s="13" t="inlineStr">
         <is>
           <t>autumn</t>
         </is>
       </c>
-      <c r="D112" s="18" t="n">
+      <c r="D112" s="13" t="n">
         <v>2.57</v>
       </c>
-      <c r="E112" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F112" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G112" s="18" t="n">
+      <c r="E112" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F112" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G112" s="13" t="n">
         <v>0.9</v>
       </c>
-      <c r="H112" s="18" t="n">
+      <c r="H112" s="13" t="n">
         <v>0.6</v>
       </c>
-      <c r="I112" s="18" t="inlineStr">
+      <c r="I112" s="13" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="J112" s="18" t="inlineStr"/>
-      <c r="K112" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="J112" s="13" t="inlineStr"/>
+      <c r="K112" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L112" s="13" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="M112" s="13" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="N112" s="13" t="n"/>
+      <c r="O112" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P112" s="13" t="n"/>
     </row>
     <row r="113">
-      <c r="A113" s="18" t="n">
+      <c r="A113" s="13" t="n">
         <v>112</v>
       </c>
-      <c r="B113" s="18" t="inlineStr">
+      <c r="B113" s="13" t="inlineStr">
         <is>
           <t>2032-10-18</t>
         </is>
       </c>
-      <c r="C113" s="18" t="inlineStr">
+      <c r="C113" s="13" t="inlineStr">
         <is>
           <t>autumn</t>
         </is>
       </c>
-      <c r="D113" s="18" t="n">
+      <c r="D113" s="13" t="n">
         <v>3.24</v>
       </c>
-      <c r="E113" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F113" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G113" s="18" t="n">
+      <c r="E113" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F113" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G113" s="13" t="n">
         <v>0.9</v>
       </c>
-      <c r="H113" s="18" t="n">
+      <c r="H113" s="13" t="n">
         <v>0.6</v>
       </c>
-      <c r="I113" s="18" t="inlineStr">
+      <c r="I113" s="13" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="J113" s="18" t="inlineStr"/>
-      <c r="K113" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="J113" s="13" t="inlineStr"/>
+      <c r="K113" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L113" s="13" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="M113" s="13" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="N113" s="13" t="inlineStr">
+        <is>
+          <t>Autumn shock expected within a fortnight.</t>
+        </is>
+      </c>
+      <c r="O113" s="13" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="P113" s="13" t="n"/>
     </row>
     <row r="114">
-      <c r="A114" s="18" t="n">
+      <c r="A114" s="13" t="n">
         <v>113</v>
       </c>
-      <c r="B114" s="18" t="inlineStr">
+      <c r="B114" s="13" t="inlineStr">
         <is>
           <t>2032-10-25</t>
         </is>
       </c>
-      <c r="C114" s="18" t="inlineStr">
+      <c r="C114" s="13" t="inlineStr">
         <is>
           <t>autumn</t>
         </is>
       </c>
-      <c r="D114" s="18" t="n">
+      <c r="D114" s="13" t="n">
         <v>3.29</v>
       </c>
-      <c r="E114" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F114" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G114" s="18" t="n">
+      <c r="E114" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F114" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G114" s="13" t="n">
         <v>0.9</v>
       </c>
-      <c r="H114" s="18" t="n">
+      <c r="H114" s="13" t="n">
         <v>0.6</v>
       </c>
-      <c r="I114" s="18" t="inlineStr">
+      <c r="I114" s="13" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="J114" s="18" t="inlineStr"/>
-      <c r="K114" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="J114" s="13" t="inlineStr"/>
+      <c r="K114" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L114" s="13" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="M114" s="13" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="N114" s="13" t="n"/>
+      <c r="O114" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P114" s="13" t="n"/>
     </row>
     <row r="115">
-      <c r="A115" s="18" t="n">
+      <c r="A115" s="13" t="n">
         <v>114</v>
       </c>
-      <c r="B115" s="18" t="inlineStr">
+      <c r="B115" s="13" t="inlineStr">
         <is>
           <t>2032-11-01</t>
         </is>
       </c>
-      <c r="C115" s="18" t="inlineStr">
+      <c r="C115" s="13" t="inlineStr">
         <is>
           <t>autumn</t>
         </is>
       </c>
-      <c r="D115" s="18" t="n">
+      <c r="D115" s="13" t="n">
         <v>2.7</v>
       </c>
-      <c r="E115" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F115" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G115" s="18" t="n">
+      <c r="E115" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F115" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G115" s="13" t="n">
         <v>0.6</v>
       </c>
-      <c r="H115" s="18" t="n">
+      <c r="H115" s="13" t="n">
         <v>0.9</v>
       </c>
-      <c r="I115" s="18" t="inlineStr">
+      <c r="I115" s="13" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="J115" s="18" t="inlineStr"/>
-      <c r="K115" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="J115" s="13" t="inlineStr"/>
+      <c r="K115" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L115" s="13" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="M115" s="13" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="N115" s="13" t="n"/>
+      <c r="O115" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P115" s="13" t="n"/>
     </row>
     <row r="116">
-      <c r="A116" s="18" t="n">
+      <c r="A116" s="13" t="n">
         <v>115</v>
       </c>
-      <c r="B116" s="18" t="inlineStr">
+      <c r="B116" s="13" t="inlineStr">
         <is>
           <t>2032-11-08</t>
         </is>
       </c>
-      <c r="C116" s="18" t="inlineStr">
+      <c r="C116" s="13" t="inlineStr">
         <is>
           <t>autumn</t>
         </is>
       </c>
-      <c r="D116" s="18" t="n">
+      <c r="D116" s="13" t="n">
         <v>2.74</v>
       </c>
-      <c r="E116" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F116" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G116" s="18" t="n">
+      <c r="E116" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F116" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G116" s="13" t="n">
         <v>0.6</v>
       </c>
-      <c r="H116" s="18" t="n">
+      <c r="H116" s="13" t="n">
         <v>0.9</v>
       </c>
-      <c r="I116" s="18" t="inlineStr">
+      <c r="I116" s="13" t="inlineStr">
         <is>
           <t>Fog season</t>
         </is>
       </c>
-      <c r="J116" s="18" t="inlineStr"/>
-      <c r="K116" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="J116" s="13" t="inlineStr"/>
+      <c r="K116" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L116" s="13" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="M116" s="13" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="N116" s="13" t="n"/>
+      <c r="O116" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P116" s="13" t="n"/>
     </row>
     <row r="117">
-      <c r="A117" s="18" t="n">
+      <c r="A117" s="13" t="n">
         <v>116</v>
       </c>
-      <c r="B117" s="18" t="inlineStr">
+      <c r="B117" s="13" t="inlineStr">
         <is>
           <t>2032-11-15</t>
         </is>
       </c>
-      <c r="C117" s="18" t="inlineStr">
+      <c r="C117" s="13" t="inlineStr">
         <is>
           <t>autumn</t>
         </is>
       </c>
-      <c r="D117" s="18" t="n">
+      <c r="D117" s="13" t="n">
         <v>2.77</v>
       </c>
-      <c r="E117" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F117" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G117" s="18" t="n">
+      <c r="E117" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F117" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G117" s="13" t="n">
         <v>0.6</v>
       </c>
-      <c r="H117" s="18" t="n">
+      <c r="H117" s="13" t="n">
         <v>0.9</v>
       </c>
-      <c r="I117" s="18" t="inlineStr">
+      <c r="I117" s="13" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="J117" s="18" t="inlineStr"/>
-      <c r="K117" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="J117" s="13" t="inlineStr"/>
+      <c r="K117" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L117" s="13" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="M117" s="13" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="N117" s="13" t="n"/>
+      <c r="O117" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P117" s="13" t="n"/>
     </row>
     <row r="118">
-      <c r="A118" s="18" t="n">
+      <c r="A118" s="13" t="n">
         <v>117</v>
       </c>
-      <c r="B118" s="18" t="inlineStr">
+      <c r="B118" s="13" t="inlineStr">
         <is>
           <t>2032-11-22</t>
         </is>
       </c>
-      <c r="C118" s="18" t="inlineStr">
+      <c r="C118" s="13" t="inlineStr">
         <is>
           <t>autumn</t>
         </is>
       </c>
-      <c r="D118" s="18" t="n">
+      <c r="D118" s="13" t="n">
         <v>2.8</v>
       </c>
-      <c r="E118" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F118" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G118" s="18" t="n">
+      <c r="E118" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F118" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G118" s="13" t="n">
         <v>0.6</v>
       </c>
-      <c r="H118" s="18" t="n">
+      <c r="H118" s="13" t="n">
         <v>0.9</v>
       </c>
-      <c r="I118" s="18" t="inlineStr">
+      <c r="I118" s="13" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="J118" s="18" t="inlineStr"/>
-      <c r="K118" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="J118" s="13" t="inlineStr"/>
+      <c r="K118" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L118" s="13" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="M118" s="13" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="N118" s="13" t="n"/>
+      <c r="O118" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P118" s="13" t="n"/>
     </row>
     <row r="119">
-      <c r="A119" s="18" t="n">
+      <c r="A119" s="13" t="n">
         <v>118</v>
       </c>
-      <c r="B119" s="18" t="inlineStr">
+      <c r="B119" s="13" t="inlineStr">
         <is>
           <t>2032-11-29</t>
         </is>
       </c>
-      <c r="C119" s="18" t="inlineStr">
+      <c r="C119" s="13" t="inlineStr">
         <is>
           <t>autumn</t>
         </is>
       </c>
-      <c r="D119" s="18" t="n">
+      <c r="D119" s="13" t="n">
         <v>2.84</v>
       </c>
-      <c r="E119" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F119" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G119" s="18" t="n">
+      <c r="E119" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F119" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G119" s="13" t="n">
         <v>0.6</v>
       </c>
-      <c r="H119" s="18" t="n">
+      <c r="H119" s="13" t="n">
         <v>0.9</v>
       </c>
-      <c r="I119" s="18" t="inlineStr">
+      <c r="I119" s="13" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="J119" s="18" t="inlineStr"/>
-      <c r="K119" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="J119" s="13" t="inlineStr"/>
+      <c r="K119" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L119" s="13" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="M119" s="13" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="N119" s="13" t="n"/>
+      <c r="O119" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P119" s="13" t="n"/>
     </row>
     <row r="120">
-      <c r="A120" s="18" t="n">
+      <c r="A120" s="13" t="n">
         <v>119</v>
       </c>
-      <c r="B120" s="18" t="inlineStr">
+      <c r="B120" s="13" t="inlineStr">
         <is>
           <t>2032-12-06</t>
         </is>
       </c>
-      <c r="C120" s="18" t="inlineStr">
+      <c r="C120" s="13" t="inlineStr">
         <is>
           <t>winter</t>
         </is>
       </c>
-      <c r="D120" s="18" t="n">
+      <c r="D120" s="13" t="n">
         <v>2.86</v>
       </c>
-      <c r="E120" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F120" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G120" s="18" t="n">
+      <c r="E120" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F120" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G120" s="13" t="n">
         <v>0.6</v>
       </c>
-      <c r="H120" s="18" t="n">
+      <c r="H120" s="13" t="n">
         <v>1.4</v>
       </c>
-      <c r="I120" s="18" t="inlineStr">
+      <c r="I120" s="13" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="J120" s="18" t="inlineStr"/>
-      <c r="K120" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="J120" s="13" t="inlineStr"/>
+      <c r="K120" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L120" s="13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M120" s="13" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="N120" s="13" t="n"/>
+      <c r="O120" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P120" s="13" t="n"/>
     </row>
     <row r="121">
-      <c r="A121" s="18" t="n">
+      <c r="A121" s="13" t="n">
         <v>120</v>
       </c>
-      <c r="B121" s="18" t="inlineStr">
+      <c r="B121" s="13" t="inlineStr">
         <is>
           <t>2032-12-13</t>
         </is>
       </c>
-      <c r="C121" s="18" t="inlineStr">
+      <c r="C121" s="13" t="inlineStr">
         <is>
           <t>winter</t>
         </is>
       </c>
-      <c r="D121" s="18" t="n">
+      <c r="D121" s="13" t="n">
         <v>2.88</v>
       </c>
-      <c r="E121" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F121" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G121" s="18" t="n">
+      <c r="E121" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F121" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G121" s="13" t="n">
         <v>0.6</v>
       </c>
-      <c r="H121" s="18" t="n">
+      <c r="H121" s="13" t="n">
         <v>1.4</v>
       </c>
-      <c r="I121" s="18" t="inlineStr">
+      <c r="I121" s="13" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="J121" s="18" t="inlineStr">
+      <c r="J121" s="13" t="inlineStr">
         <is>
           <t>Concorde for sale: fast, prestigious, thirsty.</t>
         </is>
       </c>
-      <c r="K121" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="K121" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L121" s="13" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="M121" s="13" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="N121" s="13" t="n"/>
+      <c r="O121" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P121" s="13" t="n"/>
     </row>
     <row r="122">
-      <c r="A122" s="18" t="n">
+      <c r="A122" s="13" t="n">
         <v>121</v>
       </c>
-      <c r="B122" s="18" t="inlineStr">
+      <c r="B122" s="13" t="inlineStr">
         <is>
           <t>2032-12-20</t>
         </is>
       </c>
-      <c r="C122" s="18" t="inlineStr">
+      <c r="C122" s="13" t="inlineStr">
         <is>
           <t>winter</t>
         </is>
       </c>
-      <c r="D122" s="18" t="n">
+      <c r="D122" s="13" t="n">
         <v>2.9</v>
       </c>
-      <c r="E122" s="18" t="n">
+      <c r="E122" s="13" t="n">
         <v>0.7</v>
       </c>
-      <c r="F122" s="18" t="n">
+      <c r="F122" s="13" t="n">
         <v>1.3</v>
       </c>
-      <c r="G122" s="18" t="n">
+      <c r="G122" s="13" t="n">
         <v>0.6</v>
       </c>
-      <c r="H122" s="18" t="n">
+      <c r="H122" s="13" t="n">
         <v>1.4</v>
       </c>
-      <c r="I122" s="18" t="inlineStr">
+      <c r="I122" s="13" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="J122" s="18" t="inlineStr"/>
-      <c r="K122" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="J122" s="13" t="inlineStr"/>
+      <c r="K122" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L122" s="13" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="M122" s="13" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="N122" s="13" t="n"/>
+      <c r="O122" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P122" s="13" t="n"/>
     </row>
     <row r="123">
-      <c r="A123" s="18" t="n">
+      <c r="A123" s="13" t="n">
         <v>122</v>
       </c>
-      <c r="B123" s="18" t="inlineStr">
+      <c r="B123" s="13" t="inlineStr">
         <is>
           <t>2032-12-27</t>
         </is>
       </c>
-      <c r="C123" s="18" t="inlineStr">
+      <c r="C123" s="13" t="inlineStr">
         <is>
           <t>winter</t>
         </is>
       </c>
-      <c r="D123" s="18" t="n">
+      <c r="D123" s="13" t="n">
         <v>2.91</v>
       </c>
-      <c r="E123" s="18" t="n">
+      <c r="E123" s="13" t="n">
         <v>0.7</v>
       </c>
-      <c r="F123" s="18" t="n">
+      <c r="F123" s="13" t="n">
         <v>1.3</v>
       </c>
-      <c r="G123" s="18" t="n">
+      <c r="G123" s="13" t="n">
         <v>0.6</v>
       </c>
-      <c r="H123" s="18" t="n">
+      <c r="H123" s="13" t="n">
         <v>1.4</v>
       </c>
-      <c r="I123" s="18" t="inlineStr">
+      <c r="I123" s="13" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="J123" s="18" t="inlineStr"/>
-      <c r="K123" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="J123" s="13" t="inlineStr"/>
+      <c r="K123" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L123" s="13" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="M123" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="N123" s="13" t="inlineStr">
+        <is>
+          <t>Winter: high and steady.</t>
+        </is>
+      </c>
+      <c r="O123" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P123" s="13" t="n"/>
     </row>
     <row r="124">
-      <c r="A124" s="18" t="n">
+      <c r="A124" s="13" t="n">
         <v>123</v>
       </c>
-      <c r="B124" s="18" t="inlineStr">
+      <c r="B124" s="13" t="inlineStr">
         <is>
           <t>2033-01-03</t>
         </is>
       </c>
-      <c r="C124" s="18" t="inlineStr">
+      <c r="C124" s="13" t="inlineStr">
         <is>
           <t>winter</t>
         </is>
       </c>
-      <c r="D124" s="18" t="n">
+      <c r="D124" s="13" t="n">
         <v>2.92</v>
       </c>
-      <c r="E124" s="18" t="n">
+      <c r="E124" s="13" t="n">
         <v>0.7</v>
       </c>
-      <c r="F124" s="18" t="n">
+      <c r="F124" s="13" t="n">
         <v>1.3</v>
       </c>
-      <c r="G124" s="18" t="n">
+      <c r="G124" s="13" t="n">
         <v>0.6</v>
       </c>
-      <c r="H124" s="18" t="n">
+      <c r="H124" s="13" t="n">
         <v>1.4</v>
       </c>
-      <c r="I124" s="18" t="inlineStr">
+      <c r="I124" s="13" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="J124" s="18" t="inlineStr"/>
-      <c r="K124" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="J124" s="13" t="inlineStr"/>
+      <c r="K124" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L124" s="13" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="M124" s="13" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="N124" s="13" t="n"/>
+      <c r="O124" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P124" s="13" t="n"/>
     </row>
     <row r="125">
-      <c r="A125" s="18" t="n">
+      <c r="A125" s="13" t="n">
         <v>124</v>
       </c>
-      <c r="B125" s="18" t="inlineStr">
+      <c r="B125" s="13" t="inlineStr">
         <is>
           <t>2033-01-10</t>
         </is>
       </c>
-      <c r="C125" s="18" t="inlineStr">
+      <c r="C125" s="13" t="inlineStr">
         <is>
           <t>winter</t>
         </is>
       </c>
-      <c r="D125" s="18" t="n">
+      <c r="D125" s="13" t="n">
         <v>2.93</v>
       </c>
-      <c r="E125" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F125" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G125" s="18" t="n">
+      <c r="E125" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F125" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G125" s="13" t="n">
         <v>0.6</v>
       </c>
-      <c r="H125" s="18" t="n">
+      <c r="H125" s="13" t="n">
         <v>1.4</v>
       </c>
-      <c r="I125" s="18" t="inlineStr">
+      <c r="I125" s="13" t="inlineStr">
         <is>
           <t>Heavy snow</t>
         </is>
       </c>
-      <c r="J125" s="18" t="inlineStr"/>
-      <c r="K125" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="J125" s="13" t="inlineStr"/>
+      <c r="K125" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L125" s="13" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="M125" s="13" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="N125" s="13" t="n"/>
+      <c r="O125" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P125" s="13" t="n"/>
     </row>
     <row r="126">
-      <c r="A126" s="18" t="n">
+      <c r="A126" s="13" t="n">
         <v>125</v>
       </c>
-      <c r="B126" s="18" t="inlineStr">
+      <c r="B126" s="13" t="inlineStr">
         <is>
           <t>2033-01-17</t>
         </is>
       </c>
-      <c r="C126" s="18" t="inlineStr">
+      <c r="C126" s="13" t="inlineStr">
         <is>
           <t>winter</t>
         </is>
       </c>
-      <c r="D126" s="18" t="n">
+      <c r="D126" s="13" t="n">
         <v>2.93</v>
       </c>
-      <c r="E126" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F126" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G126" s="18" t="n">
+      <c r="E126" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F126" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G126" s="13" t="n">
         <v>0.6</v>
       </c>
-      <c r="H126" s="18" t="n">
+      <c r="H126" s="13" t="n">
         <v>1.4</v>
       </c>
-      <c r="I126" s="18" t="inlineStr">
+      <c r="I126" s="13" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="J126" s="18" t="inlineStr"/>
-      <c r="K126" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="J126" s="13" t="inlineStr"/>
+      <c r="K126" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L126" s="13" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="M126" s="13" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="N126" s="13" t="n"/>
+      <c r="O126" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P126" s="13" t="n"/>
     </row>
     <row r="127">
-      <c r="A127" s="18" t="n">
+      <c r="A127" s="13" t="n">
         <v>126</v>
       </c>
-      <c r="B127" s="18" t="inlineStr">
+      <c r="B127" s="13" t="inlineStr">
         <is>
           <t>2033-01-24</t>
         </is>
       </c>
-      <c r="C127" s="18" t="inlineStr">
+      <c r="C127" s="13" t="inlineStr">
         <is>
           <t>winter</t>
         </is>
       </c>
-      <c r="D127" s="18" t="n">
+      <c r="D127" s="13" t="n">
         <v>2.93</v>
       </c>
-      <c r="E127" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F127" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G127" s="18" t="n">
+      <c r="E127" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F127" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G127" s="13" t="n">
         <v>0.6</v>
       </c>
-      <c r="H127" s="18" t="n">
+      <c r="H127" s="13" t="n">
         <v>1.4</v>
       </c>
-      <c r="I127" s="18" t="inlineStr">
+      <c r="I127" s="13" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="J127" s="18" t="inlineStr"/>
-      <c r="K127" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="J127" s="13" t="inlineStr"/>
+      <c r="K127" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L127" s="13" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="M127" s="13" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="N127" s="13" t="n"/>
+      <c r="O127" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P127" s="13" t="n"/>
     </row>
     <row r="128">
-      <c r="A128" s="18" t="n">
+      <c r="A128" s="13" t="n">
         <v>127</v>
       </c>
-      <c r="B128" s="18" t="inlineStr">
+      <c r="B128" s="13" t="inlineStr">
         <is>
           <t>2033-01-31</t>
         </is>
       </c>
-      <c r="C128" s="18" t="inlineStr">
+      <c r="C128" s="13" t="inlineStr">
         <is>
           <t>winter</t>
         </is>
       </c>
-      <c r="D128" s="18" t="n">
+      <c r="D128" s="13" t="n">
         <v>2.93</v>
       </c>
-      <c r="E128" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F128" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G128" s="18" t="n">
+      <c r="E128" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F128" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G128" s="13" t="n">
         <v>0.6</v>
       </c>
-      <c r="H128" s="18" t="n">
+      <c r="H128" s="13" t="n">
         <v>1.4</v>
       </c>
-      <c r="I128" s="18" t="inlineStr">
+      <c r="I128" s="13" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="J128" s="18" t="inlineStr"/>
-      <c r="K128" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="J128" s="13" t="inlineStr"/>
+      <c r="K128" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L128" s="13" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="M128" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="N128" s="13" t="n"/>
+      <c r="O128" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P128" s="13" t="n"/>
     </row>
     <row r="129">
-      <c r="A129" s="18" t="n">
+      <c r="A129" s="13" t="n">
         <v>128</v>
       </c>
-      <c r="B129" s="18" t="inlineStr">
+      <c r="B129" s="13" t="inlineStr">
         <is>
           <t>2033-02-07</t>
         </is>
       </c>
-      <c r="C129" s="18" t="inlineStr">
+      <c r="C129" s="13" t="inlineStr">
         <is>
           <t>winter</t>
         </is>
       </c>
-      <c r="D129" s="18" t="n">
+      <c r="D129" s="13" t="n">
         <v>2.92</v>
       </c>
-      <c r="E129" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F129" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G129" s="18" t="n">
+      <c r="E129" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F129" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G129" s="13" t="n">
         <v>0.6</v>
       </c>
-      <c r="H129" s="18" t="n">
+      <c r="H129" s="13" t="n">
         <v>1.4</v>
       </c>
-      <c r="I129" s="18" t="inlineStr">
+      <c r="I129" s="13" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="J129" s="18" t="inlineStr"/>
-      <c r="K129" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="J129" s="13" t="inlineStr"/>
+      <c r="K129" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L129" s="13" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="M129" s="13" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="N129" s="13" t="inlineStr">
+        <is>
+          <t>A glut again: prices may dip.</t>
+        </is>
+      </c>
+      <c r="O129" s="13" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="P129" s="13" t="n"/>
     </row>
     <row r="130">
-      <c r="A130" s="18" t="n">
+      <c r="A130" s="13" t="n">
         <v>129</v>
       </c>
-      <c r="B130" s="18" t="inlineStr">
+      <c r="B130" s="13" t="inlineStr">
         <is>
           <t>2033-02-14</t>
         </is>
       </c>
-      <c r="C130" s="18" t="inlineStr">
+      <c r="C130" s="13" t="inlineStr">
         <is>
           <t>winter</t>
         </is>
       </c>
-      <c r="D130" s="18" t="n">
+      <c r="D130" s="13" t="n">
         <v>2.38</v>
       </c>
-      <c r="E130" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F130" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G130" s="18" t="n">
+      <c r="E130" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F130" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G130" s="13" t="n">
         <v>0.6</v>
       </c>
-      <c r="H130" s="18" t="n">
+      <c r="H130" s="13" t="n">
         <v>1.4</v>
       </c>
-      <c r="I130" s="18" t="inlineStr">
+      <c r="I130" s="13" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="J130" s="18" t="inlineStr"/>
-      <c r="K130" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="J130" s="13" t="inlineStr"/>
+      <c r="K130" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L130" s="13" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="M130" s="13" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="N130" s="13" t="n"/>
+      <c r="O130" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P130" s="13" t="n"/>
     </row>
     <row r="131">
-      <c r="A131" s="18" t="n">
+      <c r="A131" s="13" t="n">
         <v>130</v>
       </c>
-      <c r="B131" s="18" t="inlineStr">
+      <c r="B131" s="13" t="inlineStr">
         <is>
           <t>2033-02-21</t>
         </is>
       </c>
-      <c r="C131" s="18" t="inlineStr">
+      <c r="C131" s="13" t="inlineStr">
         <is>
           <t>winter</t>
         </is>
       </c>
-      <c r="D131" s="18" t="n">
+      <c r="D131" s="13" t="n">
         <v>2.9</v>
       </c>
-      <c r="E131" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F131" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G131" s="18" t="n">
+      <c r="E131" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F131" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G131" s="13" t="n">
         <v>0.6</v>
       </c>
-      <c r="H131" s="18" t="n">
+      <c r="H131" s="13" t="n">
         <v>1.4</v>
       </c>
-      <c r="I131" s="18" t="inlineStr">
+      <c r="I131" s="13" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="J131" s="18" t="inlineStr"/>
-      <c r="K131" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="J131" s="13" t="inlineStr"/>
+      <c r="K131" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L131" s="13" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="M131" s="13" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="N131" s="13" t="n"/>
+      <c r="O131" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P131" s="13" t="n"/>
     </row>
     <row r="132">
-      <c r="A132" s="18" t="n">
+      <c r="A132" s="13" t="n">
         <v>131</v>
       </c>
-      <c r="B132" s="18" t="inlineStr">
+      <c r="B132" s="13" t="inlineStr">
         <is>
           <t>2033-02-28</t>
         </is>
       </c>
-      <c r="C132" s="18" t="inlineStr">
+      <c r="C132" s="13" t="inlineStr">
         <is>
           <t>winter</t>
         </is>
       </c>
-      <c r="D132" s="18" t="n">
+      <c r="D132" s="13" t="n">
         <v>2.89</v>
       </c>
-      <c r="E132" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F132" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G132" s="18" t="n">
+      <c r="E132" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F132" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G132" s="13" t="n">
         <v>0.6</v>
       </c>
-      <c r="H132" s="18" t="n">
+      <c r="H132" s="13" t="n">
         <v>1.4</v>
       </c>
-      <c r="I132" s="18" t="inlineStr">
+      <c r="I132" s="13" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="J132" s="18" t="inlineStr"/>
-      <c r="K132" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="J132" s="13" t="inlineStr"/>
+      <c r="K132" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L132" s="13" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="M132" s="13" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="N132" s="13" t="n"/>
+      <c r="O132" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P132" s="13" t="n"/>
     </row>
     <row r="133">
-      <c r="A133" s="18" t="n">
+      <c r="A133" s="13" t="n">
         <v>132</v>
       </c>
-      <c r="B133" s="18" t="inlineStr">
+      <c r="B133" s="13" t="inlineStr">
         <is>
           <t>2033-03-07</t>
         </is>
       </c>
-      <c r="C133" s="18" t="inlineStr">
+      <c r="C133" s="13" t="inlineStr">
         <is>
           <t>spring</t>
         </is>
       </c>
-      <c r="D133" s="18" t="n">
+      <c r="D133" s="13" t="n">
         <v>2.87</v>
       </c>
-      <c r="E133" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F133" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G133" s="18" t="n">
+      <c r="E133" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F133" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G133" s="13" t="n">
         <v>0.9</v>
       </c>
-      <c r="H133" s="18" t="n">
+      <c r="H133" s="13" t="n">
         <v>1.2</v>
       </c>
-      <c r="I133" s="18" t="inlineStr">
+      <c r="I133" s="13" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="J133" s="18" t="inlineStr"/>
-      <c r="K133" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="J133" s="13" t="inlineStr"/>
+      <c r="K133" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L133" s="13" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="M133" s="13" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="N133" s="13" t="n"/>
+      <c r="O133" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P133" s="13" t="n"/>
     </row>
     <row r="134">
-      <c r="A134" s="18" t="n">
+      <c r="A134" s="13" t="n">
         <v>133</v>
       </c>
-      <c r="B134" s="18" t="inlineStr">
+      <c r="B134" s="13" t="inlineStr">
         <is>
           <t>2033-03-14</t>
         </is>
       </c>
-      <c r="C134" s="18" t="inlineStr">
+      <c r="C134" s="13" t="inlineStr">
         <is>
           <t>spring</t>
         </is>
       </c>
-      <c r="D134" s="18" t="n">
+      <c r="D134" s="13" t="n">
         <v>2.86</v>
       </c>
-      <c r="E134" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F134" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G134" s="18" t="n">
+      <c r="E134" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F134" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G134" s="13" t="n">
         <v>0.9</v>
       </c>
-      <c r="H134" s="18" t="n">
+      <c r="H134" s="13" t="n">
         <v>1.2</v>
       </c>
-      <c r="I134" s="18" t="inlineStr">
+      <c r="I134" s="13" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="J134" s="18" t="inlineStr"/>
-      <c r="K134" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="J134" s="13" t="inlineStr"/>
+      <c r="K134" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L134" s="13" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="M134" s="13" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="N134" s="13" t="n"/>
+      <c r="O134" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P134" s="13" t="n"/>
     </row>
     <row r="135">
-      <c r="A135" s="18" t="n">
+      <c r="A135" s="13" t="n">
         <v>134</v>
       </c>
-      <c r="B135" s="18" t="inlineStr">
+      <c r="B135" s="13" t="inlineStr">
         <is>
           <t>2033-03-21</t>
         </is>
       </c>
-      <c r="C135" s="18" t="inlineStr">
+      <c r="C135" s="13" t="inlineStr">
         <is>
           <t>spring</t>
         </is>
       </c>
-      <c r="D135" s="18" t="n">
+      <c r="D135" s="13" t="n">
         <v>2.84</v>
       </c>
-      <c r="E135" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F135" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G135" s="18" t="n">
+      <c r="E135" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F135" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G135" s="13" t="n">
         <v>0.9</v>
       </c>
-      <c r="H135" s="18" t="n">
+      <c r="H135" s="13" t="n">
         <v>1.2</v>
       </c>
-      <c r="I135" s="18" t="inlineStr">
+      <c r="I135" s="13" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="J135" s="18" t="inlineStr"/>
-      <c r="K135" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="J135" s="13" t="inlineStr"/>
+      <c r="K135" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L135" s="13" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="M135" s="13" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="N135" s="13" t="n"/>
+      <c r="O135" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P135" s="13" t="n"/>
     </row>
     <row r="136">
-      <c r="A136" s="18" t="n">
+      <c r="A136" s="13" t="n">
         <v>135</v>
       </c>
-      <c r="B136" s="18" t="inlineStr">
+      <c r="B136" s="13" t="inlineStr">
         <is>
           <t>2033-03-28</t>
         </is>
       </c>
-      <c r="C136" s="18" t="inlineStr">
+      <c r="C136" s="13" t="inlineStr">
         <is>
           <t>spring</t>
         </is>
       </c>
-      <c r="D136" s="18" t="n">
+      <c r="D136" s="13" t="n">
         <v>2.81</v>
       </c>
-      <c r="E136" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F136" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G136" s="18" t="n">
+      <c r="E136" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F136" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G136" s="13" t="n">
         <v>0.9</v>
       </c>
-      <c r="H136" s="18" t="n">
+      <c r="H136" s="13" t="n">
         <v>1.2</v>
       </c>
-      <c r="I136" s="18" t="inlineStr">
+      <c r="I136" s="13" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="J136" s="18" t="inlineStr"/>
-      <c r="K136" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="J136" s="13" t="inlineStr"/>
+      <c r="K136" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L136" s="13" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="M136" s="13" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="N136" s="13" t="n"/>
+      <c r="O136" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P136" s="13" t="n"/>
     </row>
     <row r="137">
-      <c r="A137" s="18" t="n">
+      <c r="A137" s="13" t="n">
         <v>136</v>
       </c>
-      <c r="B137" s="18" t="inlineStr">
+      <c r="B137" s="13" t="inlineStr">
         <is>
           <t>2033-04-04</t>
         </is>
       </c>
-      <c r="C137" s="18" t="inlineStr">
+      <c r="C137" s="13" t="inlineStr">
         <is>
           <t>spring</t>
         </is>
       </c>
-      <c r="D137" s="18" t="n">
+      <c r="D137" s="13" t="n">
         <v>2.79</v>
       </c>
-      <c r="E137" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F137" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G137" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="H137" s="18" t="n">
+      <c r="E137" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F137" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G137" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H137" s="13" t="n">
         <v>0.9</v>
       </c>
-      <c r="I137" s="18" t="inlineStr">
+      <c r="I137" s="13" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="J137" s="18" t="inlineStr"/>
-      <c r="K137" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="J137" s="13" t="inlineStr"/>
+      <c r="K137" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L137" s="13" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="M137" s="13" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="N137" s="13" t="inlineStr">
+        <is>
+          <t>Spring drift down.</t>
+        </is>
+      </c>
+      <c r="O137" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P137" s="13" t="n"/>
     </row>
     <row r="138">
-      <c r="A138" s="18" t="n">
+      <c r="A138" s="13" t="n">
         <v>137</v>
       </c>
-      <c r="B138" s="18" t="inlineStr">
+      <c r="B138" s="13" t="inlineStr">
         <is>
           <t>2033-04-11</t>
         </is>
       </c>
-      <c r="C138" s="18" t="inlineStr">
+      <c r="C138" s="13" t="inlineStr">
         <is>
           <t>spring</t>
         </is>
       </c>
-      <c r="D138" s="18" t="n">
+      <c r="D138" s="13" t="n">
         <v>2.77</v>
       </c>
-      <c r="E138" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F138" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G138" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="H138" s="18" t="n">
+      <c r="E138" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F138" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G138" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H138" s="13" t="n">
         <v>0.9</v>
       </c>
-      <c r="I138" s="18" t="inlineStr">
+      <c r="I138" s="13" t="inlineStr">
         <is>
           <t>Ash cloud again</t>
         </is>
       </c>
-      <c r="J138" s="18" t="inlineStr"/>
-      <c r="K138" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="J138" s="13" t="inlineStr"/>
+      <c r="K138" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L138" s="13" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="M138" s="13" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="N138" s="13" t="n"/>
+      <c r="O138" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P138" s="13" t="n"/>
     </row>
     <row r="139">
-      <c r="A139" s="18" t="n">
+      <c r="A139" s="13" t="n">
         <v>138</v>
       </c>
-      <c r="B139" s="18" t="inlineStr">
+      <c r="B139" s="13" t="inlineStr">
         <is>
           <t>2033-04-18</t>
         </is>
       </c>
-      <c r="C139" s="18" t="inlineStr">
+      <c r="C139" s="13" t="inlineStr">
         <is>
           <t>spring</t>
         </is>
       </c>
-      <c r="D139" s="18" t="n">
+      <c r="D139" s="13" t="n">
         <v>2.76</v>
       </c>
-      <c r="E139" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F139" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G139" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="H139" s="18" t="n">
+      <c r="E139" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F139" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G139" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H139" s="13" t="n">
         <v>0.9</v>
       </c>
-      <c r="I139" s="18" t="inlineStr">
+      <c r="I139" s="13" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="J139" s="18" t="inlineStr"/>
-      <c r="K139" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="J139" s="13" t="inlineStr"/>
+      <c r="K139" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L139" s="13" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="M139" s="13" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="N139" s="13" t="n"/>
+      <c r="O139" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P139" s="13" t="n"/>
     </row>
     <row r="140">
-      <c r="A140" s="18" t="n">
+      <c r="A140" s="13" t="n">
         <v>139</v>
       </c>
-      <c r="B140" s="18" t="inlineStr">
+      <c r="B140" s="13" t="inlineStr">
         <is>
           <t>2033-04-25</t>
         </is>
       </c>
-      <c r="C140" s="18" t="inlineStr">
+      <c r="C140" s="13" t="inlineStr">
         <is>
           <t>spring</t>
         </is>
       </c>
-      <c r="D140" s="18" t="n">
+      <c r="D140" s="13" t="n">
         <v>2.74</v>
       </c>
-      <c r="E140" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F140" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G140" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="H140" s="18" t="n">
+      <c r="E140" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F140" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G140" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H140" s="13" t="n">
         <v>0.9</v>
       </c>
-      <c r="I140" s="18" t="inlineStr">
+      <c r="I140" s="13" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="J140" s="18" t="inlineStr"/>
-      <c r="K140" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="J140" s="13" t="inlineStr"/>
+      <c r="K140" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L140" s="13" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="M140" s="13" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="N140" s="13" t="n"/>
+      <c r="O140" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P140" s="13" t="n"/>
     </row>
     <row r="141">
-      <c r="A141" s="18" t="n">
+      <c r="A141" s="13" t="n">
         <v>140</v>
       </c>
-      <c r="B141" s="18" t="inlineStr">
+      <c r="B141" s="13" t="inlineStr">
         <is>
           <t>2033-05-02</t>
         </is>
       </c>
-      <c r="C141" s="18" t="inlineStr">
+      <c r="C141" s="13" t="inlineStr">
         <is>
           <t>spring</t>
         </is>
       </c>
-      <c r="D141" s="18" t="n">
+      <c r="D141" s="13" t="n">
         <v>2.73</v>
       </c>
-      <c r="E141" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F141" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G141" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="H141" s="18" t="n">
+      <c r="E141" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F141" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G141" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H141" s="13" t="n">
         <v>0.5</v>
       </c>
-      <c r="I141" s="18" t="inlineStr">
+      <c r="I141" s="13" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="J141" s="18" t="inlineStr">
+      <c r="J141" s="13" t="inlineStr">
         <is>
           <t>Cherry blossom in Tokyo: demand doubles for a fortnight.</t>
         </is>
       </c>
-      <c r="K141" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="K141" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L141" s="13" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="M141" s="13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N141" s="13" t="n"/>
+      <c r="O141" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P141" s="13" t="n"/>
     </row>
     <row r="142">
-      <c r="A142" s="18" t="n">
+      <c r="A142" s="13" t="n">
         <v>141</v>
       </c>
-      <c r="B142" s="18" t="inlineStr">
+      <c r="B142" s="13" t="inlineStr">
         <is>
           <t>2033-05-09</t>
         </is>
       </c>
-      <c r="C142" s="18" t="inlineStr">
+      <c r="C142" s="13" t="inlineStr">
         <is>
           <t>spring</t>
         </is>
       </c>
-      <c r="D142" s="18" t="n">
+      <c r="D142" s="13" t="n">
         <v>2.72</v>
       </c>
-      <c r="E142" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F142" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G142" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="H142" s="18" t="n">
+      <c r="E142" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F142" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G142" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H142" s="13" t="n">
         <v>0.5</v>
       </c>
-      <c r="I142" s="18" t="inlineStr">
+      <c r="I142" s="13" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="J142" s="18" t="inlineStr"/>
-      <c r="K142" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="J142" s="13" t="inlineStr"/>
+      <c r="K142" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L142" s="13" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="M142" s="13" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="N142" s="13" t="n"/>
+      <c r="O142" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P142" s="13" t="n"/>
     </row>
     <row r="143">
-      <c r="A143" s="18" t="n">
+      <c r="A143" s="13" t="n">
         <v>142</v>
       </c>
-      <c r="B143" s="18" t="inlineStr">
+      <c r="B143" s="13" t="inlineStr">
         <is>
           <t>2033-05-16</t>
         </is>
       </c>
-      <c r="C143" s="18" t="inlineStr">
+      <c r="C143" s="13" t="inlineStr">
         <is>
           <t>spring</t>
         </is>
       </c>
-      <c r="D143" s="18" t="n">
+      <c r="D143" s="13" t="n">
         <v>2.71</v>
       </c>
-      <c r="E143" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F143" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G143" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="H143" s="18" t="n">
+      <c r="E143" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F143" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G143" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H143" s="13" t="n">
         <v>0.5</v>
       </c>
-      <c r="I143" s="18" t="inlineStr">
+      <c r="I143" s="13" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="J143" s="18" t="inlineStr"/>
-      <c r="K143" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="J143" s="13" t="inlineStr"/>
+      <c r="K143" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L143" s="13" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="M143" s="13" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="N143" s="13" t="n"/>
+      <c r="O143" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P143" s="13" t="n"/>
     </row>
     <row r="144">
-      <c r="A144" s="18" t="n">
+      <c r="A144" s="13" t="n">
         <v>143</v>
       </c>
-      <c r="B144" s="18" t="inlineStr">
+      <c r="B144" s="13" t="inlineStr">
         <is>
           <t>2033-05-23</t>
         </is>
       </c>
-      <c r="C144" s="18" t="inlineStr">
+      <c r="C144" s="13" t="inlineStr">
         <is>
           <t>spring</t>
         </is>
       </c>
-      <c r="D144" s="18" t="n">
+      <c r="D144" s="13" t="n">
         <v>2.7</v>
       </c>
-      <c r="E144" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F144" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G144" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="H144" s="18" t="n">
+      <c r="E144" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F144" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G144" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H144" s="13" t="n">
         <v>0.5</v>
       </c>
-      <c r="I144" s="18" t="inlineStr">
+      <c r="I144" s="13" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="J144" s="18" t="inlineStr"/>
-      <c r="K144" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="J144" s="13" t="inlineStr"/>
+      <c r="K144" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L144" s="13" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="M144" s="13" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="N144" s="13" t="n"/>
+      <c r="O144" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P144" s="13" t="n"/>
     </row>
     <row r="145">
-      <c r="A145" s="18" t="n">
+      <c r="A145" s="13" t="n">
         <v>144</v>
       </c>
-      <c r="B145" s="18" t="inlineStr">
+      <c r="B145" s="13" t="inlineStr">
         <is>
           <t>2033-05-30</t>
         </is>
       </c>
-      <c r="C145" s="18" t="inlineStr">
+      <c r="C145" s="13" t="inlineStr">
         <is>
           <t>spring</t>
         </is>
       </c>
-      <c r="D145" s="18" t="n">
+      <c r="D145" s="13" t="n">
         <v>2.7</v>
       </c>
-      <c r="E145" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F145" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G145" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="H145" s="18" t="n">
+      <c r="E145" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F145" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G145" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H145" s="13" t="n">
         <v>0.5</v>
       </c>
-      <c r="I145" s="18" t="inlineStr">
+      <c r="I145" s="13" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="J145" s="18" t="inlineStr"/>
-      <c r="K145" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="J145" s="13" t="inlineStr"/>
+      <c r="K145" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L145" s="13" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="M145" s="13" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="N145" s="13" t="n"/>
+      <c r="O145" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P145" s="13" t="n"/>
     </row>
     <row r="146">
-      <c r="A146" s="18" t="n">
+      <c r="A146" s="13" t="n">
         <v>145</v>
       </c>
-      <c r="B146" s="18" t="inlineStr">
+      <c r="B146" s="13" t="inlineStr">
         <is>
           <t>2033-06-06</t>
         </is>
       </c>
-      <c r="C146" s="18" t="inlineStr">
+      <c r="C146" s="13" t="inlineStr">
         <is>
           <t>summer</t>
         </is>
       </c>
-      <c r="D146" s="18" t="n">
+      <c r="D146" s="13" t="n">
         <v>2.7</v>
       </c>
-      <c r="E146" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F146" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G146" s="18" t="n">
+      <c r="E146" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F146" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G146" s="13" t="n">
         <v>1.3</v>
       </c>
-      <c r="H146" s="18" t="n">
+      <c r="H146" s="13" t="n">
         <v>0.5</v>
       </c>
-      <c r="I146" s="18" t="inlineStr">
+      <c r="I146" s="13" t="inlineStr">
         <is>
           <t>Heatwave: Barcelona demand up</t>
         </is>
       </c>
-      <c r="J146" s="18" t="inlineStr"/>
-      <c r="K146" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="J146" s="13" t="inlineStr"/>
+      <c r="K146" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L146" s="13" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="M146" s="13" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="N146" s="13" t="n"/>
+      <c r="O146" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P146" s="13" t="n"/>
     </row>
     <row r="147">
-      <c r="A147" s="18" t="n">
+      <c r="A147" s="13" t="n">
         <v>146</v>
       </c>
-      <c r="B147" s="18" t="inlineStr">
+      <c r="B147" s="13" t="inlineStr">
         <is>
           <t>2033-06-13</t>
         </is>
       </c>
-      <c r="C147" s="18" t="inlineStr">
+      <c r="C147" s="13" t="inlineStr">
         <is>
           <t>summer</t>
         </is>
       </c>
-      <c r="D147" s="18" t="n">
+      <c r="D147" s="13" t="n">
         <v>2.7</v>
       </c>
-      <c r="E147" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F147" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G147" s="18" t="n">
+      <c r="E147" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F147" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G147" s="13" t="n">
         <v>1.3</v>
       </c>
-      <c r="H147" s="18" t="n">
+      <c r="H147" s="13" t="n">
         <v>0.5</v>
       </c>
-      <c r="I147" s="18" t="inlineStr">
+      <c r="I147" s="13" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="J147" s="18" t="inlineStr"/>
-      <c r="K147" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="J147" s="13" t="inlineStr"/>
+      <c r="K147" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L147" s="13" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="M147" s="13" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="N147" s="13" t="n"/>
+      <c r="O147" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P147" s="13" t="n"/>
     </row>
     <row r="148">
-      <c r="A148" s="18" t="n">
+      <c r="A148" s="13" t="n">
         <v>147</v>
       </c>
-      <c r="B148" s="18" t="inlineStr">
+      <c r="B148" s="13" t="inlineStr">
         <is>
           <t>2033-06-20</t>
         </is>
       </c>
-      <c r="C148" s="18" t="inlineStr">
+      <c r="C148" s="13" t="inlineStr">
         <is>
           <t>summer</t>
         </is>
       </c>
-      <c r="D148" s="18" t="n">
+      <c r="D148" s="13" t="n">
         <v>2.71</v>
       </c>
-      <c r="E148" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F148" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G148" s="18" t="n">
+      <c r="E148" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F148" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G148" s="13" t="n">
         <v>1.3</v>
       </c>
-      <c r="H148" s="18" t="n">
+      <c r="H148" s="13" t="n">
         <v>0.5</v>
       </c>
-      <c r="I148" s="18" t="inlineStr">
+      <c r="I148" s="13" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="J148" s="18" t="inlineStr"/>
-      <c r="K148" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="J148" s="13" t="inlineStr"/>
+      <c r="K148" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L148" s="13" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="M148" s="13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N148" s="13" t="n"/>
+      <c r="O148" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P148" s="13" t="n"/>
     </row>
     <row r="149">
-      <c r="A149" s="18" t="n">
+      <c r="A149" s="13" t="n">
         <v>148</v>
       </c>
-      <c r="B149" s="18" t="inlineStr">
+      <c r="B149" s="13" t="inlineStr">
         <is>
           <t>2033-06-27</t>
         </is>
       </c>
-      <c r="C149" s="18" t="inlineStr">
+      <c r="C149" s="13" t="inlineStr">
         <is>
           <t>summer</t>
         </is>
       </c>
-      <c r="D149" s="18" t="n">
+      <c r="D149" s="13" t="n">
         <v>2.72</v>
       </c>
-      <c r="E149" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F149" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G149" s="18" t="n">
+      <c r="E149" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F149" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G149" s="13" t="n">
         <v>1.3</v>
       </c>
-      <c r="H149" s="18" t="n">
+      <c r="H149" s="13" t="n">
         <v>0.5</v>
       </c>
-      <c r="I149" s="18" t="inlineStr">
+      <c r="I149" s="13" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="J149" s="18" t="inlineStr"/>
-      <c r="K149" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="J149" s="13" t="inlineStr"/>
+      <c r="K149" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L149" s="13" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="M149" s="13" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="N149" s="13" t="inlineStr">
+        <is>
+          <t>Summer drift up.</t>
+        </is>
+      </c>
+      <c r="O149" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P149" s="13" t="n"/>
     </row>
     <row r="150">
-      <c r="A150" s="18" t="n">
+      <c r="A150" s="13" t="n">
         <v>149</v>
       </c>
-      <c r="B150" s="18" t="inlineStr">
+      <c r="B150" s="13" t="inlineStr">
         <is>
           <t>2033-07-04</t>
         </is>
       </c>
-      <c r="C150" s="18" t="inlineStr">
+      <c r="C150" s="13" t="inlineStr">
         <is>
           <t>summer</t>
         </is>
       </c>
-      <c r="D150" s="18" t="n">
+      <c r="D150" s="13" t="n">
         <v>2.73</v>
       </c>
-      <c r="E150" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F150" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G150" s="18" t="n">
+      <c r="E150" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F150" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G150" s="13" t="n">
         <v>1.3</v>
       </c>
-      <c r="H150" s="18" t="n">
+      <c r="H150" s="13" t="n">
         <v>0.5</v>
       </c>
-      <c r="I150" s="18" t="inlineStr">
+      <c r="I150" s="13" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="J150" s="18" t="inlineStr"/>
-      <c r="K150" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="J150" s="13" t="inlineStr"/>
+      <c r="K150" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L150" s="13" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="M150" s="13" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="N150" s="13" t="n"/>
+      <c r="O150" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P150" s="13" t="n"/>
     </row>
     <row r="151">
-      <c r="A151" s="18" t="n">
+      <c r="A151" s="13" t="n">
         <v>150</v>
       </c>
-      <c r="B151" s="18" t="inlineStr">
+      <c r="B151" s="13" t="inlineStr">
         <is>
           <t>2033-07-11</t>
         </is>
       </c>
-      <c r="C151" s="18" t="inlineStr">
+      <c r="C151" s="13" t="inlineStr">
         <is>
           <t>summer</t>
         </is>
       </c>
-      <c r="D151" s="18" t="n">
+      <c r="D151" s="13" t="n">
         <v>2.75</v>
       </c>
-      <c r="E151" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F151" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G151" s="18" t="n">
+      <c r="E151" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F151" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G151" s="13" t="n">
         <v>1.3</v>
       </c>
-      <c r="H151" s="18" t="n">
+      <c r="H151" s="13" t="n">
         <v>0.5</v>
       </c>
-      <c r="I151" s="18" t="inlineStr">
+      <c r="I151" s="13" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="J151" s="18" t="inlineStr"/>
-      <c r="K151" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="J151" s="13" t="inlineStr"/>
+      <c r="K151" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L151" s="13" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="M151" s="13" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="N151" s="13" t="n"/>
+      <c r="O151" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P151" s="13" t="n"/>
     </row>
     <row r="152">
-      <c r="A152" s="18" t="n">
+      <c r="A152" s="13" t="n">
         <v>151</v>
       </c>
-      <c r="B152" s="18" t="inlineStr">
+      <c r="B152" s="13" t="inlineStr">
         <is>
           <t>2033-07-18</t>
         </is>
       </c>
-      <c r="C152" s="18" t="inlineStr">
+      <c r="C152" s="13" t="inlineStr">
         <is>
           <t>summer</t>
         </is>
       </c>
-      <c r="D152" s="18" t="n">
+      <c r="D152" s="13" t="n">
         <v>2.77</v>
       </c>
-      <c r="E152" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F152" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G152" s="18" t="n">
+      <c r="E152" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F152" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G152" s="13" t="n">
         <v>1.3</v>
       </c>
-      <c r="H152" s="18" t="n">
+      <c r="H152" s="13" t="n">
         <v>0.5</v>
       </c>
-      <c r="I152" s="18" t="inlineStr">
+      <c r="I152" s="13" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="J152" s="18" t="inlineStr"/>
-      <c r="K152" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="J152" s="13" t="inlineStr"/>
+      <c r="K152" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L152" s="13" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="M152" s="13" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="N152" s="13" t="n"/>
+      <c r="O152" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P152" s="13" t="n"/>
     </row>
     <row r="153">
-      <c r="A153" s="18" t="n">
+      <c r="A153" s="13" t="n">
         <v>152</v>
       </c>
-      <c r="B153" s="18" t="inlineStr">
+      <c r="B153" s="13" t="inlineStr">
         <is>
           <t>2033-07-25</t>
         </is>
       </c>
-      <c r="C153" s="18" t="inlineStr">
+      <c r="C153" s="13" t="inlineStr">
         <is>
           <t>summer</t>
         </is>
       </c>
-      <c r="D153" s="18" t="n">
+      <c r="D153" s="13" t="n">
         <v>2.79</v>
       </c>
-      <c r="E153" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F153" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G153" s="18" t="n">
+      <c r="E153" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F153" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G153" s="13" t="n">
         <v>1.3</v>
       </c>
-      <c r="H153" s="18" t="n">
+      <c r="H153" s="13" t="n">
         <v>0.5</v>
       </c>
-      <c r="I153" s="18" t="inlineStr">
+      <c r="I153" s="13" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="J153" s="18" t="inlineStr"/>
-      <c r="K153" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="J153" s="13" t="inlineStr"/>
+      <c r="K153" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L153" s="13" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="M153" s="13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N153" s="13" t="n"/>
+      <c r="O153" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P153" s="13" t="n"/>
     </row>
     <row r="154">
-      <c r="A154" s="18" t="n">
+      <c r="A154" s="13" t="n">
         <v>153</v>
       </c>
-      <c r="B154" s="18" t="inlineStr">
+      <c r="B154" s="13" t="inlineStr">
         <is>
           <t>2033-08-01</t>
         </is>
       </c>
-      <c r="C154" s="18" t="inlineStr">
+      <c r="C154" s="13" t="inlineStr">
         <is>
           <t>summer</t>
         </is>
       </c>
-      <c r="D154" s="18" t="n">
+      <c r="D154" s="13" t="n">
         <v>2.82</v>
       </c>
-      <c r="E154" s="18" t="n">
+      <c r="E154" s="13" t="n">
         <v>0.85</v>
       </c>
-      <c r="F154" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G154" s="18" t="n">
+      <c r="F154" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G154" s="13" t="n">
         <v>1.3</v>
       </c>
-      <c r="H154" s="18" t="n">
+      <c r="H154" s="13" t="n">
         <v>0.5</v>
       </c>
-      <c r="I154" s="18" t="inlineStr">
+      <c r="I154" s="13" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="J154" s="18" t="inlineStr"/>
-      <c r="K154" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="J154" s="13" t="inlineStr"/>
+      <c r="K154" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L154" s="13" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="M154" s="13" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="N154" s="13" t="n"/>
+      <c r="O154" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P154" s="13" t="n"/>
     </row>
     <row r="155">
-      <c r="A155" s="18" t="n">
+      <c r="A155" s="13" t="n">
         <v>154</v>
       </c>
-      <c r="B155" s="18" t="inlineStr">
+      <c r="B155" s="13" t="inlineStr">
         <is>
           <t>2033-08-08</t>
         </is>
       </c>
-      <c r="C155" s="18" t="inlineStr">
+      <c r="C155" s="13" t="inlineStr">
         <is>
           <t>summer</t>
         </is>
       </c>
-      <c r="D155" s="18" t="n">
+      <c r="D155" s="13" t="n">
         <v>2.86</v>
       </c>
-      <c r="E155" s="18" t="n">
+      <c r="E155" s="13" t="n">
         <v>0.85</v>
       </c>
-      <c r="F155" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G155" s="18" t="n">
+      <c r="F155" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G155" s="13" t="n">
         <v>1.3</v>
       </c>
-      <c r="H155" s="18" t="n">
+      <c r="H155" s="13" t="n">
         <v>0.5</v>
       </c>
-      <c r="I155" s="18" t="inlineStr">
+      <c r="I155" s="13" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="J155" s="18" t="inlineStr"/>
-      <c r="K155" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="J155" s="13" t="inlineStr"/>
+      <c r="K155" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L155" s="13" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="M155" s="13" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="N155" s="13" t="n"/>
+      <c r="O155" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P155" s="13" t="n"/>
     </row>
     <row r="156">
-      <c r="A156" s="18" t="n">
+      <c r="A156" s="13" t="n">
         <v>155</v>
       </c>
-      <c r="B156" s="18" t="inlineStr">
+      <c r="B156" s="13" t="inlineStr">
         <is>
           <t>2033-08-15</t>
         </is>
       </c>
-      <c r="C156" s="18" t="inlineStr">
+      <c r="C156" s="13" t="inlineStr">
         <is>
           <t>summer</t>
         </is>
       </c>
-      <c r="D156" s="18" t="n">
+      <c r="D156" s="13" t="n">
         <v>2.89</v>
       </c>
-      <c r="E156" s="18" t="n">
+      <c r="E156" s="13" t="n">
         <v>0.85</v>
       </c>
-      <c r="F156" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G156" s="18" t="n">
+      <c r="F156" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G156" s="13" t="n">
         <v>1.3</v>
       </c>
-      <c r="H156" s="18" t="n">
+      <c r="H156" s="13" t="n">
         <v>0.5</v>
       </c>
-      <c r="I156" s="18" t="inlineStr">
+      <c r="I156" s="13" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="J156" s="18" t="inlineStr"/>
-      <c r="K156" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="J156" s="13" t="inlineStr"/>
+      <c r="K156" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L156" s="13" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="M156" s="13" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="N156" s="13" t="n"/>
+      <c r="O156" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P156" s="13" t="n"/>
     </row>
     <row r="157">
-      <c r="A157" s="18" t="n">
+      <c r="A157" s="13" t="n">
         <v>156</v>
       </c>
-      <c r="B157" s="18" t="inlineStr">
+      <c r="B157" s="13" t="inlineStr">
         <is>
           <t>2033-08-22</t>
         </is>
       </c>
-      <c r="C157" s="18" t="inlineStr">
+      <c r="C157" s="13" t="inlineStr">
         <is>
           <t>summer</t>
         </is>
       </c>
-      <c r="D157" s="18" t="n">
+      <c r="D157" s="13" t="n">
         <v>2.93</v>
       </c>
-      <c r="E157" s="18" t="n">
+      <c r="E157" s="13" t="n">
         <v>0.85</v>
       </c>
-      <c r="F157" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G157" s="18" t="n">
+      <c r="F157" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G157" s="13" t="n">
         <v>1.3</v>
       </c>
-      <c r="H157" s="18" t="n">
+      <c r="H157" s="13" t="n">
         <v>0.5</v>
       </c>
-      <c r="I157" s="18" t="inlineStr">
+      <c r="I157" s="13" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="J157" s="18" t="inlineStr"/>
-      <c r="K157" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
+      <c r="J157" s="13" t="inlineStr"/>
+      <c r="K157" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="L157" s="13" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="M157" s="13" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="N157" s="13" t="n"/>
+      <c r="O157" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P157" s="13" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="18" t="n">
@@ -27858,13 +29393,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S39"/>
+  <dimension ref="A1:S42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -29523,49 +31058,49 @@
       <c r="S33" s="13" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="inlineStr">
+      <c r="A34" s="13" t="inlineStr">
         <is>
           <t>a380_offer</t>
         </is>
       </c>
-      <c r="B34" s="18" t="inlineStr">
+      <c r="B34" s="13" t="inlineStr">
         <is>
           <t>2032-09-06</t>
         </is>
       </c>
-      <c r="C34" s="18" t="inlineStr">
+      <c r="C34" s="13" t="inlineStr">
         <is>
           <t>The ultimate plane</t>
         </is>
       </c>
-      <c r="D34" s="18" t="inlineStr">
+      <c r="D34" s="13" t="inlineStr">
         <is>
           <t>Airbus offers you an A380 — on finance: 30% down, the rest over a year. It only fills on the busiest route with a strong reputation.</t>
         </is>
       </c>
-      <c r="E34" s="18" t="n"/>
-      <c r="F34" s="18" t="n"/>
-      <c r="G34" s="18" t="n"/>
-      <c r="H34" s="18" t="n"/>
-      <c r="I34" s="18" t="n"/>
-      <c r="J34" s="18" t="n"/>
-      <c r="K34" s="18" t="inlineStr">
-        <is>
-          <t>Airbus offers you an A380 on finance: £18m down, then £808,000 a week for a year. It only fills on the busiest route with a strong reputation.</t>
-        </is>
-      </c>
-      <c r="L34" s="18" t="n"/>
-      <c r="M34" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
-      <c r="N34" s="18" t="n"/>
-      <c r="O34" s="18" t="n"/>
-      <c r="P34" s="18" t="n"/>
-      <c r="Q34" s="18" t="n"/>
-      <c r="R34" s="18" t="n"/>
-      <c r="S34" s="18" t="n"/>
+      <c r="E34" s="13" t="n"/>
+      <c r="F34" s="13" t="n"/>
+      <c r="G34" s="13" t="n"/>
+      <c r="H34" s="13" t="n"/>
+      <c r="I34" s="13" t="n"/>
+      <c r="J34" s="13" t="n"/>
+      <c r="K34" s="13" t="inlineStr">
+        <is>
+          <t>Airbus offers you an A380: £20m down, then £1m a month for 40 months. 500 seats. Or the 747: £16m down, £600,000 a month, 400 seats. Or neither — fly the big twins.</t>
+        </is>
+      </c>
+      <c r="L34" s="13" t="n"/>
+      <c r="M34" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="N34" s="13" t="n"/>
+      <c r="O34" s="13" t="n"/>
+      <c r="P34" s="13" t="n"/>
+      <c r="Q34" s="13" t="n"/>
+      <c r="R34" s="13" t="n"/>
+      <c r="S34" s="13" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="22" t="inlineStr">
@@ -29767,12 +31302,135 @@
       </c>
       <c r="N39" s="18" t="n"/>
     </row>
+    <row r="40">
+      <c r="A40" s="13" t="inlineStr">
+        <is>
+          <t>storm3</t>
+        </is>
+      </c>
+      <c r="B40" s="13" t="inlineStr">
+        <is>
+          <t>2032-10-18</t>
+        </is>
+      </c>
+      <c r="C40" s="13" t="inlineStr">
+        <is>
+          <t>Autumn storm</t>
+        </is>
+      </c>
+      <c r="D40" s="13" t="n"/>
+      <c r="E40" s="13" t="n"/>
+      <c r="F40" s="13" t="n"/>
+      <c r="G40" s="13" t="n"/>
+      <c r="H40" s="13" t="n"/>
+      <c r="I40" s="13" t="n"/>
+      <c r="J40" s="13" t="n"/>
+      <c r="K40" s="13" t="inlineStr">
+        <is>
+          <t>Storm season again; the storm2 options apply (EventOptions storm2).</t>
+        </is>
+      </c>
+      <c r="L40" s="13" t="n"/>
+      <c r="M40" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="N40" s="13" t="n"/>
+      <c r="O40" s="13" t="n"/>
+      <c r="P40" s="13" t="n"/>
+      <c r="Q40" s="13" t="n"/>
+      <c r="R40" s="13" t="n"/>
+      <c r="S40" s="13" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="13" t="inlineStr">
+        <is>
+          <t>ash_cloud3</t>
+        </is>
+      </c>
+      <c r="B41" s="13" t="inlineStr">
+        <is>
+          <t>2033-04-25</t>
+        </is>
+      </c>
+      <c r="C41" s="13" t="inlineStr">
+        <is>
+          <t>Ash, a third time</t>
+        </is>
+      </c>
+      <c r="D41" s="13" t="n"/>
+      <c r="E41" s="13" t="n"/>
+      <c r="F41" s="13" t="n"/>
+      <c r="G41" s="13" t="n"/>
+      <c r="H41" s="13" t="n"/>
+      <c r="I41" s="13" t="n"/>
+      <c r="J41" s="13" t="n"/>
+      <c r="K41" s="13" t="inlineStr">
+        <is>
+          <t>Two days; the ash_cloud2 options apply.</t>
+        </is>
+      </c>
+      <c r="L41" s="13" t="n"/>
+      <c r="M41" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="N41" s="13" t="n"/>
+      <c r="O41" s="13" t="n"/>
+      <c r="P41" s="13" t="n"/>
+      <c r="Q41" s="13" t="n"/>
+      <c r="R41" s="13" t="n"/>
+      <c r="S41" s="13" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="13" t="inlineStr">
+        <is>
+          <t>fuel_shock3</t>
+        </is>
+      </c>
+      <c r="B42" s="13" t="inlineStr">
+        <is>
+          <t>2032-11-01</t>
+        </is>
+      </c>
+      <c r="C42" s="13" t="inlineStr">
+        <is>
+          <t>Oil shock</t>
+        </is>
+      </c>
+      <c r="D42" s="13" t="n"/>
+      <c r="E42" s="13" t="n"/>
+      <c r="F42" s="13" t="n"/>
+      <c r="G42" s="13" t="n"/>
+      <c r="H42" s="13" t="n"/>
+      <c r="I42" s="13" t="n"/>
+      <c r="J42" s="13" t="n"/>
+      <c r="K42" s="13" t="inlineStr">
+        <is>
+          <t>Fuel +60p for a fortnight (Market). Headline only.</t>
+        </is>
+      </c>
+      <c r="L42" s="13" t="n"/>
+      <c r="M42" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="N42" s="13" t="n"/>
+      <c r="O42" s="13" t="n"/>
+      <c r="P42" s="13" t="n"/>
+      <c r="Q42" s="13" t="n"/>
+      <c r="R42" s="13" t="n"/>
+      <c r="S42" s="13" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -30037,96 +31695,96 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="n">
+      <c r="A6" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>2032-04-19</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>Airport slot auction</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>68 slots a week for 52 weeks. How many slots in a year?</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>68 × 54</t>
         </is>
       </c>
-      <c r="F6" s="11" t="n">
+      <c r="F6" s="12" t="n">
         <v>3672</v>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="12" t="inlineStr">
         <is>
           <t>slots</t>
         </is>
       </c>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="H6" s="12" t="inlineStr">
         <is>
           <t>+½ star</t>
         </is>
       </c>
-      <c r="I6" s="11" t="inlineStr">
-        <is>
-          <t>placeholder</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="J6" s="13" t="inlineStr">
         <is>
           <t>+½★</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="n">
+      <c r="A7" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>2032-09-07</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>Prize money</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>£2,184 shared equally between 7 airlines. How much each?</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>2,184 ÷ 7</t>
         </is>
       </c>
-      <c r="F7" s="11" t="n">
+      <c r="F7" s="12" t="n">
         <v>312</v>
       </c>
-      <c r="G7" s="11" t="inlineStr">
+      <c r="G7" s="12" t="inlineStr">
         <is>
           <t>£</t>
         </is>
       </c>
-      <c r="H7" s="11" t="inlineStr">
+      <c r="H7" s="12" t="inlineStr">
         <is>
           <t>£3,000</t>
         </is>
       </c>
-      <c r="I7" s="11" t="inlineStr">
-        <is>
-          <t>placeholder</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="I7" s="12" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="J7" s="13" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
@@ -30225,424 +31883,6 @@
       <c r="J9" t="inlineStr">
         <is>
           <t>0.5</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>from day</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>mechanic</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="13" t="inlineStr">
-        <is>
-          <t>Launch Day: standing plan on one page; all opening sums in one sitting (tickets ×3, profit, snacks ×2, fuel); both routes; modelling tool; workings page</t>
-        </is>
-      </c>
-      <c r="C2" s="13" t="inlineStr">
-        <is>
-          <t>D52, D54</t>
-        </is>
-      </c>
-      <c r="D2" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>The week runs day by day on the operations board; results equal the projection; pauses for events (day 4 Red Kite with numbers, day 5 storm)</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>D52, D50</t>
-        </is>
-      </c>
-      <c r="D3" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="13" t="n">
-        <v>7</v>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>Weekly review every Sunday: seven-row table, total by hand, projected − actual, missed-profit line</t>
-        </is>
-      </c>
-      <c r="C4" s="13" t="inlineStr">
-        <is>
-          <t>D55</t>
-        </is>
-      </c>
-      <c r="D4" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Week 2: second plane, buy only; buy now or wait (time to afford); Buy greyed until affordable; two timetables; assignment</t>
-        </is>
-      </c>
-      <c r="C5" s="13" t="inlineStr">
-        <is>
-          <t>D53, D55</t>
-        </is>
-      </c>
-      <c r="D5" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="13" t="n">
-        <v>15</v>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Week 3: four routes; £5 fares; season badge; use-it-or-lose-it begins</t>
-        </is>
-      </c>
-      <c r="C6" s="13" t="inlineStr">
-        <is>
-          <t>D28, D55</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="13" t="n">
-        <v>19</v>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>Season forecast card</t>
-        </is>
-      </c>
-      <c r="C7" s="13" t="inlineStr"/>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="13" t="n">
-        <v>22</v>
-      </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>Week 4: medium haul; range check; services per day; E175 and E190; load factor as a percentage</t>
-        </is>
-      </c>
-      <c r="C8" s="13" t="inlineStr">
-        <is>
-          <t>D19, D23</t>
-        </is>
-      </c>
-      <c r="D8" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="13" t="n">
-        <v>29</v>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>Week-at-a-time skips; Marrakech; event costs as a share of a day</t>
-        </is>
-      </c>
-      <c r="C9" s="13" t="inlineStr">
-        <is>
-          <t>D21</t>
-        </is>
-      </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>2030-12-02</t>
-        </is>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>Month-at-a-time play; monthly reports from here on</t>
-        </is>
-      </c>
-      <c r="C10" s="13" t="inlineStr"/>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t>2030-12-29</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>Chapter 1 review: chapter accounts by hand; the long-haul decision</t>
-        </is>
-      </c>
-      <c r="C11" s="13" t="inlineStr"/>
-      <c r="D11" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>2031-01-06</t>
-        </is>
-      </c>
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>CHAPTER 2 set-up (days 127–131, one at a time): long haul same-day to 6,000 km (New York, Dubai); the 757 and 787 to lease; arrival in local time; reputation revealed at the banked level and ×5% a half-star; the airline type chosen (light profiles); Value's bag fee; £500 second crew per long-haul service; Captain's challenge 1. Then weeks, then months from February.</t>
-        </is>
-      </c>
-      <c r="C12" s="13" t="inlineStr"/>
-      <c r="D12" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>2031-08-31</t>
-        </is>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>Chapter 2 review: year-1 accounts (show what to add, the mean), hunt h1, the full airline-type profiles arrive, next investment (buying opens in chapter 3)</t>
-        </is>
-      </c>
-      <c r="C13" s="13" t="inlineStr"/>
-      <c r="D13" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t>2031-09-01</t>
-        </is>
-      </c>
-      <c r="B14" s="13" t="inlineStr">
-        <is>
-          <t>CHAPTER 3 set-up (days 365–369, one at a time): buy big planes outright — (price − cash) ÷ profit a week; the overdraft safety net; Tokyo and Cape Town; the A340, 777 and A350 in the shop; Challenge 3. Then months.</t>
-        </is>
-      </c>
-      <c r="C14" s="13" t="inlineStr"/>
-      <c r="D14" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="13" t="inlineStr">
-        <is>
-          <t>2032-08-31</t>
-        </is>
-      </c>
-      <c r="B15" s="13" t="inlineStr">
-        <is>
-          <t>Chapter 3 review: year-2 accounts, hunt h3, next investment (the A380 offer opens chapter 4)</t>
-        </is>
-      </c>
-      <c r="C15" s="13" t="inlineStr"/>
-      <c r="D15" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="18" t="inlineStr">
-        <is>
-          <t>2032-09-06</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>CHAPTER 4: A380 on finance; reputation that matters</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr"/>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="18" t="inlineStr">
-        <is>
-          <t>2033-08-31</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>Chapter 4 review</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr"/>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="18" t="inlineStr">
-        <is>
-          <t>2033-09-05</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>CHAPTER 5: rival enters the best route; marketing; quarterly comparison task</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr"/>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="18" t="inlineStr">
-        <is>
-          <t>2034-08-31</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>Chapter 5 review</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr"/>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="18" t="inlineStr">
-        <is>
-          <t>2034-09-04</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>CHAPTER 6: no new mechanic; the five-year review</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr"/>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="13" t="inlineStr">
-        <is>
-          <t>rule</t>
-        </is>
-      </c>
-      <c r="B21" s="13" t="inlineStr">
-        <is>
-          <t>No crew mechanic before 2031-01-06; no second hub, sell-back, fleet renewal, investor; Heathrow only; cash reserve block before Sep 2031; HandSumRules govern hand sums</t>
-        </is>
-      </c>
-      <c r="C21" s="13" t="inlineStr">
-        <is>
-          <t>D51 D31 D25 D46 D44 D32 D26 D34</t>
-        </is>
-      </c>
-      <c r="D21" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
         </is>
       </c>
     </row>
@@ -30905,58 +32145,58 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="n">
+      <c r="A5" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>The ultimate plane</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>2032-09-06</t>
         </is>
       </c>
-      <c r="D5" s="18" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t>2033-08-31</t>
         </is>
       </c>
-      <c r="E5" s="18" t="n">
+      <c r="E5" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="F5" s="18" t="inlineStr">
+      <c r="F5" s="13" t="inlineStr">
         <is>
           <t>month</t>
         </is>
       </c>
-      <c r="G5" s="18" t="inlineStr">
+      <c r="G5" s="13" t="inlineStr">
         <is>
           <t>2033-08-31</t>
         </is>
       </c>
-      <c r="H5" s="18" t="inlineStr">
-        <is>
-          <t>The A380: does a 500-seat plane fill? Finance: deposit and repayments</t>
-        </is>
-      </c>
-      <c r="I5" s="18" t="inlineStr">
+      <c r="H5" s="13" t="inlineStr">
+        <is>
+          <t>The ultimate plane: the A380 on finance (£20m down, £1m a month for 40 months) or the 747 as the real alternative; Hong Kong and Los Angeles, the two routes big enough for it; does a 500-seat plane fill? (demand ÷ seats); reputation that decides it; the A380 launch campaign as the one marketing project</t>
+        </is>
+      </c>
+      <c r="I5" s="13" t="inlineStr">
         <is>
           <t>finance; reputation that matters</t>
         </is>
       </c>
-      <c r="J5" s="18" t="n">
+      <c r="J5" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="K5" s="18" t="inlineStr">
-        <is>
-          <t>ratio and scaling (demand ÷ seats, cost per seat); 30% deposit; (price − deposit) ÷ 52</t>
-        </is>
-      </c>
-      <c r="L5" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
+      <c r="K5" s="13" t="inlineStr">
+        <is>
+          <t>deposit and monthly payments with millions (60 − 20 = 40; ÷ 40); does it fill? demand ÷ seats as a percentage; the campaign's funnel fractions and return on spending; year-3 totals and the mean</t>
+        </is>
+      </c>
+      <c r="L5" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
         </is>
       </c>
     </row>
@@ -31072,7 +32312,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="17" t="inlineStr">
         <is>
@@ -31086,6 +32325,424 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>from day</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>mechanic</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>Launch Day: standing plan on one page; all opening sums in one sitting (tickets ×3, profit, snacks ×2, fuel); both routes; modelling tool; workings page</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="inlineStr">
+        <is>
+          <t>D52, D54</t>
+        </is>
+      </c>
+      <c r="D2" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>The week runs day by day on the operations board; results equal the projection; pauses for events (day 4 Red Kite with numbers, day 5 storm)</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>D52, D50</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Weekly review every Sunday: seven-row table, total by hand, projected − actual, missed-profit line</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>D55</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Week 2: second plane, buy only; buy now or wait (time to afford); Buy greyed until affordable; two timetables; assignment</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>D53, D55</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Week 3: four routes; £5 fares; season badge; use-it-or-lose-it begins</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>D28, D55</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Season forecast card</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr"/>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>Week 4: medium haul; range check; services per day; E175 and E190; load factor as a percentage</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>D19, D23</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="n">
+        <v>29</v>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>Week-at-a-time skips; Marrakech; event costs as a share of a day</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>D21</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>2030-12-02</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>Month-at-a-time play; monthly reports from here on</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr"/>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>2030-12-29</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Chapter 1 review: chapter accounts by hand; the long-haul decision</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr"/>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>2031-01-06</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>CHAPTER 2 set-up (days 127–131, one at a time): long haul same-day to 6,000 km (New York, Dubai); the 757 and 787 to lease; arrival in local time; reputation revealed at the banked level and ×5% a half-star; the airline type chosen (light profiles); Value's bag fee; £500 second crew per long-haul service; Captain's challenge 1. Then weeks, then months from February.</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr"/>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>2031-08-31</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>Chapter 2 review: year-1 accounts (show what to add, the mean), hunt h1, the full airline-type profiles arrive, next investment (buying opens in chapter 3)</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr"/>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>2031-09-01</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>CHAPTER 3 set-up (days 365–369, one at a time): buy big planes outright — (price − cash) ÷ profit a week; the overdraft safety net; Tokyo and Cape Town; the A340, 777 and A350 in the shop; Challenge 3. Then months.</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr"/>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>2032-08-31</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>Chapter 3 review: year-2 accounts, hunt h3, next investment (the A380 offer opens chapter 4)</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr"/>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>2032-09-06</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>CHAPTER 4 set-up (days 736–740, one at a time): the A380 offer on finance (monthly), the 747 as the alternative, Hong Kong and Los Angeles, does-it-fill (demand ÷ seats), Challenge 5; the launch campaign project in October; then months.</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr"/>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>2033-08-31</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>Chapter 4 review: year-3 accounts, hunt h5 (the finance line), the A380's fill month by month, next: the rival</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr"/>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="18" t="inlineStr">
+        <is>
+          <t>2033-09-05</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>CHAPTER 5: rival enters the best route; marketing; quarterly comparison task</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="inlineStr"/>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>later</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="18" t="inlineStr">
+        <is>
+          <t>2034-08-31</t>
+        </is>
+      </c>
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t>Chapter 5 review</t>
+        </is>
+      </c>
+      <c r="C19" s="18" t="inlineStr"/>
+      <c r="D19" s="18" t="inlineStr">
+        <is>
+          <t>later</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="18" t="inlineStr">
+        <is>
+          <t>2034-09-04</t>
+        </is>
+      </c>
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>CHAPTER 6: no new mechanic; the five-year review</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="inlineStr"/>
+      <c r="D20" s="18" t="inlineStr">
+        <is>
+          <t>later</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>No crew mechanic before 2031-01-06; no second hub, sell-back, fleet renewal, investor; Heathrow only; cash reserve block before Sep 2031; HandSumRules govern hand sums</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>D51 D31 D25 D46 D44 D32 D26 D34</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -31314,7 +32971,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -31536,42 +33193,42 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>h5</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>2033-08-31</t>
         </is>
       </c>
-      <c r="C6" s="14" t="n">
+      <c r="C6" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>Finance statement</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
-        <is>
-          <t>Weekly repayment × weeks does not reach the balance</t>
-        </is>
-      </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>Year-3 accounts, 31 Aug 2033: the A380's finance line shows 12 payments of £1,000,000 = £13,000,000. Twelve months, twelve payments: £12,000,000.</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>(price − deposit) ÷ 52; compare</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="13" t="inlineStr">
         <is>
           <t>Repayments run a month longer</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
-        <is>
-          <t>placeholder</t>
+      <c r="H6" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
         </is>
       </c>
     </row>
@@ -31667,7 +33324,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -32642,7 +34299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -32726,7 +34383,7 @@
       </c>
       <c r="C3" s="13" t="inlineStr">
         <is>
-          <t>A relationship already shown is asked by hand again only when an input has moved by more than its threshold; otherwise the model does it.</t>
+          <t>Fuel is one sum a week: the order on the fuel desk (blocks × price per 1,000 L). By hand only when the price has moved 50p or more since the last time; the game breaks the bill down by route and plane for the pupil to read.</t>
         </is>
       </c>
       <c r="D3" s="13" t="inlineStr">
@@ -32736,7 +34393,7 @@
       </c>
       <c r="E3" s="13" t="inlineStr">
         <is>
-          <t>fuel by hand about six times in five years: day 3, the Oct 2030 spike, the Dec 2030 crash, the first jet, the first 787, the Oct 2031 shock</t>
+          <t>Launch Day: 3 × £1,470; week 7: 6 × £2,940; week 14: 5 × £1,120</t>
         </is>
       </c>
       <c r="F3" s="13" t="inlineStr">
@@ -32786,7 +34443,7 @@
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
-          <t>Every new route brings one × (passengers × the new fare) and one ÷ (distance ÷ speed); every new plane brings one × (seats × fare) and one ÷ (price ÷ rent, or price − cash ÷ profit a week).</t>
+          <t>One × and one ÷ for every new route or plane, on tickets or flight time — never on fuel (fuel is the weekly order, rule 2).</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
@@ -33019,6 +34676,32 @@
       <c r="A14" s="17" t="inlineStr">
         <is>
           <t>Rough count: chapter 1 about 25 hand sums, chapter 2 about 8, chapter 3 about 6, chapter 4 about 6, chapter 5 about 5, chapter 6 about 4 — roughly 55 over the game, half of them × or ÷, excluding challenges and hunts. The teacher's Calculate / Build / Model setting overrides any rule (D34).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>On paper, two tries</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>All working is done on paper; the game takes the answer. A wrong answer gets a note and one more try; a second wrong answer shows the figure and moves on.</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr"/>
+      <c r="F15" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
         </is>
       </c>
     </row>
@@ -33033,7 +34716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -33122,7 +34805,7 @@
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>litres × price per litre</t>
+          <t>fuel: the weekly order</t>
         </is>
       </c>
       <c r="B3" s="13" t="inlineStr">
@@ -33132,22 +34815,22 @@
       </c>
       <c r="C3" s="13" t="inlineStr">
         <is>
-          <t>Aircraft performance card</t>
+          <t>Fuel desk, Monday</t>
         </is>
       </c>
       <c r="D3" s="13" t="inlineStr">
         <is>
-          <t>partition the price (£1 + 40p + 7p) | scale from 100 L | make it pence | count the decimal places | formal multiplication</t>
+          <t>blocks × price per 1,000 L (reference card: partition the price | make it pence | formal)</t>
         </is>
       </c>
       <c r="E3" s="13" t="inlineStr">
         <is>
-          <t>120 L × £1.47</t>
+          <t>3 × £1,470; Launch Day's one per-service example 120 L × £1.47</t>
         </is>
       </c>
       <c r="F3" s="13" t="inlineStr">
         <is>
-          <t>Scale from 100 L: 100 L costs £147, so 20 L costs £29.40</t>
+          <t>D86: methods shown as reference only; working on paper</t>
         </is>
       </c>
       <c r="G3" s="10" t="inlineStr">
@@ -33469,7 +35152,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
@@ -33952,14 +35634,125 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="17" t="inlineStr">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>finance: deposit and monthly payments</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>operational</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>Shop (chapter 4)</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="inlineStr">
+        <is>
+          <t>subtract the deposit; divide by the months; multiply back to check</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>60m − 20m = 40m; 40m ÷ 40 = £1m a month; 40 × £1m + £20m = £60m</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="G27" s="13" t="inlineStr">
+        <is>
+          <t>NCP-3-02 · NCP-3-05 · NCP-3-06 · MON-3-03 · PFA-MM-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>does it fill? demand ÷ seats</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>Aircraft comparison; monthly review</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="inlineStr">
+        <is>
+          <t>fraction → percentage; filled-aircraft graphic</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>480 ÷ 500 = 96%; 442 of 500</t>
+        </is>
+      </c>
+      <c r="F28" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="G28" s="13" t="inlineStr">
+        <is>
+          <t>FDP-3-02 · FDP-3-03 · STAT-3-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>campaign funnel and return on spending</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>strategic</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>The A380 launch project</t>
+        </is>
+      </c>
+      <c r="D29" s="13" t="inlineStr">
+        <is>
+          <t>a chain of fractions; extra profit ÷ cost</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>20 → 16 → 12 → 9 → 7 → 5; £420,000 ÷ £300,000 = 1.4</t>
+        </is>
+      </c>
+      <c r="F29" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="G29" s="13" t="inlineStr">
+        <is>
+          <t>FDP-3-02 · FDP-3-03 · STAT-3-18 · STAT-3-25 · MON-3-03 · PFA-MM-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="17" t="inlineStr">
         <is>
           <t>D60: the workbench (Work it out) offers the methods listed for the relationship being signed off; the pupil chooses. Levels: operational (what does this one thing cost? — taught and calculated), model (what happens if I change this? — the console calculates), strategic (what should I do when the future is uncertain? — maths supports judgement).</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="17" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="17" t="inlineStr">
         <is>
           <t>Statement codes are from Bettws-Master-Dataset-v1_21 (WPS 3 main curriculum and PFA Managing Money). Drafted by Fable 13 Oct for Bertie to check; the pupil record prints these codes against each entry.</t>
         </is>
@@ -33976,7 +35769,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D132"/>
+  <dimension ref="A1:D139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -34787,12 +36580,12 @@
       </c>
       <c r="B39" s="13" t="inlineStr">
         <is>
-          <t>2032-09-07</t>
+          <t>2032-09-06</t>
         </is>
       </c>
       <c r="C39" s="13" t="inlineStr">
         <is>
-          <t>D43: finance (deposit and weekly payments) with the A380, chapter 4.</t>
+          <t>D43/D83: finance from chapter 4, monthly: a deposit, then a round monthly payment for 40 months (Finance sheet). The first offer is the A380.</t>
         </is>
       </c>
       <c r="D39" s="13" t="inlineStr">
@@ -35257,12 +37050,12 @@
       </c>
       <c r="B62" s="13" t="inlineStr">
         <is>
-          <t>tickets ×3 fares; profit; snacks ×2 prices; fuel after a guided example</t>
+          <t>tickets at 3 fares; profit; the fuel order (blocks × price per 1,000 L); snacks as Build</t>
         </is>
       </c>
       <c r="C62" s="13" t="inlineStr">
         <is>
-          <t>D54: all on Launch Day, in one sitting, on the workings page, in this order.</t>
+          <t>D86: five by hand on Launch Day; snacks become pick-the-figures.</t>
         </is>
       </c>
       <c r="D62" s="13" t="inlineStr">
@@ -35423,12 +37216,12 @@
       </c>
       <c r="B70" s="13" t="inlineStr">
         <is>
-          <t>per service on the aircraft performance card</t>
+          <t>the weekly order: blocks × price per 1,000 L</t>
         </is>
       </c>
       <c r="C70" s="13" t="inlineStr">
         <is>
-          <t>D60: litres × price per litre is asked on the performance card the first time a plane flies a route, and again when the price it is valued at has moved 50p or more. Purchases on the desk are 1,000 L blocks: cost of 1,000 L × number of blocks.</t>
+          <t>D86: the only fuel sum after Launch Day is the Monday order on the fuel desk (3 × £1,470 = £4,410), by hand when the price has moved fuelHandSumPriceStep (50p) since it was last asked, otherwise Build or Model. The game breaks the week's bill down by route and plane on the load sheets automatically for the pupil to read. The per-service decimal multiplication is Launch Day's one example and Model afterwards.</t>
         </is>
       </c>
       <c r="D70" s="13" t="inlineStr">
@@ -35782,7 +37575,7 @@
       </c>
       <c r="C87" s="13" t="inlineStr">
         <is>
-          <t>D63: from week 2, at most this many Calculate sign-offs in a week (teacher dial 1–3). Launch Day's sums and the review's Build steps are outside the cap. When more qualify, the game asks the most instructive first: a relationship never met, then a known relationship with a changed input (a fuel price jump), then the one with the most money in it; the rest are filled by the model with ƒ. A sum that misses the cap is carried to the next week it is relevant.</t>
+          <t>D63/D86 confirmed: three a week from week 2 (teacher dial 1–3).</t>
         </is>
       </c>
       <c r="D87" s="13" t="inlineStr">
@@ -36702,6 +38495,154 @@
         </is>
       </c>
       <c r="D132" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="13" t="inlineStr">
+        <is>
+          <t>financeShape</t>
+        </is>
+      </c>
+      <c r="B133" s="13" t="inlineStr">
+        <is>
+          <t>deposit, then 40 monthly payments</t>
+        </is>
+      </c>
+      <c r="C133" s="13" t="inlineStr">
+        <is>
+          <t>D83: payments on the first of each month from the planning page; shown on the statement as 'Finance: A380 £1,000,000 (month 7 of 40)'. Missing a payment is not possible: it is taken before anything else, into the overdraft if need be.</t>
+        </is>
+      </c>
+      <c r="D133" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="13" t="inlineStr">
+        <is>
+          <t>chapter4SetUpDays</t>
+        </is>
+      </c>
+      <c r="B134" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C134" s="13" t="inlineStr">
+        <is>
+          <t>Chapter 4 opens Monday 6 September 2032 with five days one at a time (Calendar days 736–740): the A380 offer, Hong Kong and Los Angeles, the 747 as the alternative; then months.</t>
+        </is>
+      </c>
+      <c r="D134" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="13" t="inlineStr">
+        <is>
+          <t>a380FillQuestion</t>
+        </is>
+      </c>
+      <c r="B135" s="13" t="inlineStr">
+        <is>
+          <t>demand ÷ seats</t>
+        </is>
+      </c>
+      <c r="C135" s="13" t="inlineStr">
+        <is>
+          <t>D84: the chapter's sum. Does a 500-seat plane fill? Passengers wanting to fly at the fare ÷ 500, as a percentage; the review shows the A380's fill each month.</t>
+        </is>
+      </c>
+      <c r="D135" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="13" t="inlineStr">
+        <is>
+          <t>campaignProjectDate</t>
+        </is>
+      </c>
+      <c r="B136" s="13" t="inlineStr">
+        <is>
+          <t>2032-10-04</t>
+        </is>
+      </c>
+      <c r="C136" s="13" t="inlineStr">
+        <is>
+          <t>D82: the A380 launch campaign is one standalone project, started in the first month of chapter 4 and run over several sessions with the game paused; its result applies from the launch date the pupil chooses (Campaign sheet).</t>
+        </is>
+      </c>
+      <c r="D136" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="13" t="inlineStr">
+        <is>
+          <t>workingOnPaper</t>
+        </is>
+      </c>
+      <c r="B137" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="C137" s="13" t="inlineStr">
+        <is>
+          <t>D86: the pupil works on paper. The workbench is an answer box (question in black, answer typed, tick or error note); no column frames, no cell-by-cell capture. The method picker becomes an optional reference card showing the shape of a method, not an input.</t>
+        </is>
+      </c>
+      <c r="D137" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="13" t="inlineStr">
+        <is>
+          <t>twoTriesRule</t>
+        </is>
+      </c>
+      <c r="B138" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="C138" s="13" t="inlineStr">
+        <is>
+          <t>D86: a wrong answer gets the error note and one more try; a second wrong answer shows the correct figure and the game moves on. The record keeps both attempts.</t>
+        </is>
+      </c>
+      <c r="D138" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="13" t="inlineStr">
+        <is>
+          <t>sumNumbering</t>
+        </is>
+      </c>
+      <c r="B139" s="13" t="inlineStr">
+        <is>
+          <t>running number per pupil, never reset</t>
+        </is>
+      </c>
+      <c r="C139" s="13" t="inlineStr">
+        <is>
+          <t>D86: every sign-off and review Build step shows 'Sum N · Week W · what it is' in the answer box; the pupil writes N beside his working on paper; the record and printout carry the same N. Practice questions use a separate letter series (P1, P2 …) so they don't disturb the count.</t>
+        </is>
+      </c>
+      <c r="D139" s="13" t="inlineStr">
         <is>
           <t>live</t>
         </is>
@@ -37139,7 +39080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L57"/>
+  <dimension ref="A1:L74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -40352,6 +42293,992 @@
         </is>
       </c>
       <c r="L57" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="13" t="inlineStr">
+        <is>
+          <t>hkg_launch</t>
+        </is>
+      </c>
+      <c r="B58" s="13" t="inlineStr">
+        <is>
+          <t>2032-09-06</t>
+        </is>
+      </c>
+      <c r="C58" s="13" t="inlineStr">
+        <is>
+          <t>2032-09-06</t>
+        </is>
+      </c>
+      <c r="D58" s="13" t="inlineStr">
+        <is>
+          <t>2032-09-19</t>
+        </is>
+      </c>
+      <c r="E58" s="13" t="inlineStr">
+        <is>
+          <t>rival</t>
+        </is>
+      </c>
+      <c r="F58" s="13" t="inlineStr">
+        <is>
+          <t>hkg</t>
+        </is>
+      </c>
+      <c r="G58" s="13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H58" s="13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I58" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J58" s="13" t="inlineStr">
+        <is>
+          <t>Hong Kong opens: the biggest route yet.</t>
+        </is>
+      </c>
+      <c r="K58" s="13" t="inlineStr">
+        <is>
+          <t>The 747 fills it on day one; the A380 needs the campaign or the stars.</t>
+        </is>
+      </c>
+      <c r="L58" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="13" t="inlineStr">
+        <is>
+          <t>lax_launch</t>
+        </is>
+      </c>
+      <c r="B59" s="13" t="inlineStr">
+        <is>
+          <t>2032-09-06</t>
+        </is>
+      </c>
+      <c r="C59" s="13" t="inlineStr">
+        <is>
+          <t>2032-09-06</t>
+        </is>
+      </c>
+      <c r="D59" s="13" t="inlineStr">
+        <is>
+          <t>2032-09-19</t>
+        </is>
+      </c>
+      <c r="E59" s="13" t="inlineStr">
+        <is>
+          <t>rival</t>
+        </is>
+      </c>
+      <c r="F59" s="13" t="inlineStr">
+        <is>
+          <t>lax</t>
+        </is>
+      </c>
+      <c r="G59" s="13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H59" s="13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I59" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J59" s="13" t="inlineStr">
+        <is>
+          <t>Los Angeles opens.</t>
+        </is>
+      </c>
+      <c r="K59" s="13" t="inlineStr">
+        <is>
+          <t>Same question as Hong Kong.</t>
+        </is>
+      </c>
+      <c r="L59" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="13" t="inlineStr">
+        <is>
+          <t>a380_delivery</t>
+        </is>
+      </c>
+      <c r="B60" s="13" t="inlineStr">
+        <is>
+          <t>2032-09-27</t>
+        </is>
+      </c>
+      <c r="C60" s="13" t="inlineStr">
+        <is>
+          <t>2032-10-04</t>
+        </is>
+      </c>
+      <c r="D60" s="13" t="inlineStr">
+        <is>
+          <t>2032-10-17</t>
+        </is>
+      </c>
+      <c r="E60" s="13" t="inlineStr">
+        <is>
+          <t>rival</t>
+        </is>
+      </c>
+      <c r="F60" s="13" t="inlineStr">
+        <is>
+          <t>hkg,lax</t>
+        </is>
+      </c>
+      <c r="G60" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H60" s="13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I60" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J60" s="13" t="inlineStr">
+        <is>
+          <t>Your A380 is delivered on 4 October: the newspapers want to see it.</t>
+        </is>
+      </c>
+      <c r="K60" s="13" t="inlineStr">
+        <is>
+          <t>Start the launch campaign (the marketing project).</t>
+        </is>
+      </c>
+      <c r="L60" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="13" t="inlineStr">
+        <is>
+          <t>hkg_rugby_sevens</t>
+        </is>
+      </c>
+      <c r="B61" s="13" t="inlineStr">
+        <is>
+          <t>2032-10-25</t>
+        </is>
+      </c>
+      <c r="C61" s="13" t="inlineStr">
+        <is>
+          <t>2032-11-05</t>
+        </is>
+      </c>
+      <c r="D61" s="13" t="inlineStr">
+        <is>
+          <t>2032-11-07</t>
+        </is>
+      </c>
+      <c r="E61" s="13" t="inlineStr">
+        <is>
+          <t>sport</t>
+        </is>
+      </c>
+      <c r="F61" s="13" t="inlineStr">
+        <is>
+          <t>hkg</t>
+        </is>
+      </c>
+      <c r="G61" s="13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H61" s="13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I61" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J61" s="13" t="inlineStr">
+        <is>
+          <t>The Hong Kong Sevens weekend.</t>
+        </is>
+      </c>
+      <c r="K61" s="13" t="inlineStr">
+        <is>
+          <t>Raise the Hong Kong fare for the weekend.</t>
+        </is>
+      </c>
+      <c r="L61" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="13" t="inlineStr">
+        <is>
+          <t>us_election</t>
+        </is>
+      </c>
+      <c r="B62" s="13" t="inlineStr">
+        <is>
+          <t>2032-10-18</t>
+        </is>
+      </c>
+      <c r="C62" s="13" t="inlineStr">
+        <is>
+          <t>2032-11-01</t>
+        </is>
+      </c>
+      <c r="D62" s="13" t="inlineStr">
+        <is>
+          <t>2032-11-07</t>
+        </is>
+      </c>
+      <c r="E62" s="13" t="inlineStr">
+        <is>
+          <t>political</t>
+        </is>
+      </c>
+      <c r="F62" s="13" t="inlineStr">
+        <is>
+          <t>nyc,lax,yyz</t>
+        </is>
+      </c>
+      <c r="G62" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H62" s="13" t="inlineStr">
+        <is>
+          <t>business</t>
+        </is>
+      </c>
+      <c r="I62" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J62" s="13" t="inlineStr">
+        <is>
+          <t>US election week: business travel pauses.</t>
+        </is>
+      </c>
+      <c r="K62" s="13" t="inlineStr">
+        <is>
+          <t>Lower the long-haul fares a step for the week.</t>
+        </is>
+      </c>
+      <c r="L62" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="13" t="inlineStr">
+        <is>
+          <t>tyo_autumn_leaves</t>
+        </is>
+      </c>
+      <c r="B63" s="13" t="inlineStr">
+        <is>
+          <t>2032-11-08</t>
+        </is>
+      </c>
+      <c r="C63" s="13" t="inlineStr">
+        <is>
+          <t>2032-11-15</t>
+        </is>
+      </c>
+      <c r="D63" s="13" t="inlineStr">
+        <is>
+          <t>2032-12-05</t>
+        </is>
+      </c>
+      <c r="E63" s="13" t="inlineStr">
+        <is>
+          <t>culture</t>
+        </is>
+      </c>
+      <c r="F63" s="13" t="inlineStr">
+        <is>
+          <t>tyo</t>
+        </is>
+      </c>
+      <c r="G63" s="13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H63" s="13" t="inlineStr">
+        <is>
+          <t>leisure</t>
+        </is>
+      </c>
+      <c r="I63" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J63" s="13" t="inlineStr">
+        <is>
+          <t>Autumn colours in Japan.</t>
+        </is>
+      </c>
+      <c r="K63" s="13" t="inlineStr">
+        <is>
+          <t>Tokyo at the top fare.</t>
+        </is>
+      </c>
+      <c r="L63" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="13" t="inlineStr">
+        <is>
+          <t>lax_awards</t>
+        </is>
+      </c>
+      <c r="B64" s="13" t="inlineStr">
+        <is>
+          <t>2033-01-24</t>
+        </is>
+      </c>
+      <c r="C64" s="13" t="inlineStr">
+        <is>
+          <t>2033-02-14</t>
+        </is>
+      </c>
+      <c r="D64" s="13" t="inlineStr">
+        <is>
+          <t>2033-02-20</t>
+        </is>
+      </c>
+      <c r="E64" s="13" t="inlineStr">
+        <is>
+          <t>culture</t>
+        </is>
+      </c>
+      <c r="F64" s="13" t="inlineStr">
+        <is>
+          <t>lax</t>
+        </is>
+      </c>
+      <c r="G64" s="13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H64" s="13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I64" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J64" s="13" t="inlineStr">
+        <is>
+          <t>Awards season in Los Angeles.</t>
+        </is>
+      </c>
+      <c r="K64" s="13" t="inlineStr">
+        <is>
+          <t>The A380 fills on Los Angeles for the week.</t>
+        </is>
+      </c>
+      <c r="L64" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="13" t="inlineStr">
+        <is>
+          <t>hkg_new_year</t>
+        </is>
+      </c>
+      <c r="B65" s="13" t="inlineStr">
+        <is>
+          <t>2033-01-17</t>
+        </is>
+      </c>
+      <c r="C65" s="13" t="inlineStr">
+        <is>
+          <t>2033-01-31</t>
+        </is>
+      </c>
+      <c r="D65" s="13" t="inlineStr">
+        <is>
+          <t>2033-02-13</t>
+        </is>
+      </c>
+      <c r="E65" s="13" t="inlineStr">
+        <is>
+          <t>culture</t>
+        </is>
+      </c>
+      <c r="F65" s="13" t="inlineStr">
+        <is>
+          <t>hkg</t>
+        </is>
+      </c>
+      <c r="G65" s="13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H65" s="13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I65" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J65" s="13" t="inlineStr">
+        <is>
+          <t>Chinese New Year: two weeks of full planes to Hong Kong.</t>
+        </is>
+      </c>
+      <c r="K65" s="13" t="inlineStr">
+        <is>
+          <t>Raise the fare two steps.</t>
+        </is>
+      </c>
+      <c r="L65" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="13" t="inlineStr">
+        <is>
+          <t>atlantic_storms</t>
+        </is>
+      </c>
+      <c r="B66" s="13" t="inlineStr">
+        <is>
+          <t>2033-02-07</t>
+        </is>
+      </c>
+      <c r="C66" s="13" t="inlineStr">
+        <is>
+          <t>2033-02-07</t>
+        </is>
+      </c>
+      <c r="D66" s="13" t="inlineStr">
+        <is>
+          <t>2033-02-09</t>
+        </is>
+      </c>
+      <c r="E66" s="13" t="inlineStr">
+        <is>
+          <t>nature</t>
+        </is>
+      </c>
+      <c r="F66" s="13" t="inlineStr">
+        <is>
+          <t>nyc,yyz,lax</t>
+        </is>
+      </c>
+      <c r="G66" s="13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H66" s="13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I66" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J66" s="13" t="inlineStr">
+        <is>
+          <t>Storms close airports on both US coasts for three days.</t>
+        </is>
+      </c>
+      <c r="K66" s="13" t="inlineStr">
+        <is>
+          <t>None in advance.</t>
+        </is>
+      </c>
+      <c r="L66" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="13" t="inlineStr">
+        <is>
+          <t>red_kite_a380</t>
+        </is>
+      </c>
+      <c r="B67" s="13" t="inlineStr">
+        <is>
+          <t>2033-03-07</t>
+        </is>
+      </c>
+      <c r="C67" s="13" t="inlineStr">
+        <is>
+          <t>2033-03-21</t>
+        </is>
+      </c>
+      <c r="D67" s="13" t="inlineStr">
+        <is>
+          <t>2033-08-31</t>
+        </is>
+      </c>
+      <c r="E67" s="13" t="inlineStr">
+        <is>
+          <t>rival</t>
+        </is>
+      </c>
+      <c r="F67" s="13" t="inlineStr">
+        <is>
+          <t>hkg</t>
+        </is>
+      </c>
+      <c r="G67" s="13" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H67" s="13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I67" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J67" s="13" t="inlineStr">
+        <is>
+          <t>Red Kite orders its own A380 and announces Hong Kong from Luton.</t>
+        </is>
+      </c>
+      <c r="K67" s="13" t="inlineStr">
+        <is>
+          <t>The switching rule applies on Hong Kong from 21 March.</t>
+        </is>
+      </c>
+      <c r="L67" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="13" t="inlineStr">
+        <is>
+          <t>tyo_blossom3</t>
+        </is>
+      </c>
+      <c r="B68" s="13" t="inlineStr">
+        <is>
+          <t>2033-03-21</t>
+        </is>
+      </c>
+      <c r="C68" s="13" t="inlineStr">
+        <is>
+          <t>2033-04-01</t>
+        </is>
+      </c>
+      <c r="D68" s="13" t="inlineStr">
+        <is>
+          <t>2033-04-14</t>
+        </is>
+      </c>
+      <c r="E68" s="13" t="inlineStr">
+        <is>
+          <t>culture</t>
+        </is>
+      </c>
+      <c r="F68" s="13" t="inlineStr">
+        <is>
+          <t>tyo</t>
+        </is>
+      </c>
+      <c r="G68" s="13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H68" s="13" t="inlineStr">
+        <is>
+          <t>leisure</t>
+        </is>
+      </c>
+      <c r="I68" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J68" s="13" t="inlineStr">
+        <is>
+          <t>Cherry blossom.</t>
+        </is>
+      </c>
+      <c r="K68" s="13" t="inlineStr">
+        <is>
+          <t>Tokyo at the top fare.</t>
+        </is>
+      </c>
+      <c r="L68" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="13" t="inlineStr">
+        <is>
+          <t>easter3</t>
+        </is>
+      </c>
+      <c r="B69" s="13" t="inlineStr">
+        <is>
+          <t>2033-04-04</t>
+        </is>
+      </c>
+      <c r="C69" s="13" t="inlineStr">
+        <is>
+          <t>2033-04-15</t>
+        </is>
+      </c>
+      <c r="D69" s="13" t="inlineStr">
+        <is>
+          <t>2033-05-01</t>
+        </is>
+      </c>
+      <c r="E69" s="13" t="inlineStr">
+        <is>
+          <t>culture</t>
+        </is>
+      </c>
+      <c r="F69" s="13" t="inlineStr">
+        <is>
+          <t>bcn,mad,lis,fco,ath,rak,cai</t>
+        </is>
+      </c>
+      <c r="G69" s="13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H69" s="13" t="inlineStr">
+        <is>
+          <t>leisure</t>
+        </is>
+      </c>
+      <c r="I69" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J69" s="13" t="inlineStr">
+        <is>
+          <t>Easter holidays.</t>
+        </is>
+      </c>
+      <c r="K69" s="13" t="inlineStr">
+        <is>
+          <t>Fares up on the sun routes.</t>
+        </is>
+      </c>
+      <c r="L69" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="13" t="inlineStr">
+        <is>
+          <t>sin_grounding</t>
+        </is>
+      </c>
+      <c r="B70" s="13" t="inlineStr">
+        <is>
+          <t>2033-05-09</t>
+        </is>
+      </c>
+      <c r="C70" s="13" t="inlineStr">
+        <is>
+          <t>2033-05-09</t>
+        </is>
+      </c>
+      <c r="D70" s="13" t="inlineStr">
+        <is>
+          <t>2033-05-15</t>
+        </is>
+      </c>
+      <c r="E70" s="13" t="inlineStr">
+        <is>
+          <t>political</t>
+        </is>
+      </c>
+      <c r="F70" s="13" t="inlineStr">
+        <is>
+          <t>sin,syd</t>
+        </is>
+      </c>
+      <c r="G70" s="13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H70" s="13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I70" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J70" s="13" t="inlineStr">
+        <is>
+          <t>A security alert at Singapore delays flights for a week.</t>
+        </is>
+      </c>
+      <c r="K70" s="13" t="inlineStr">
+        <is>
+          <t>None in advance; Sydney suffers too.</t>
+        </is>
+      </c>
+      <c r="L70" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="13" t="inlineStr">
+        <is>
+          <t>lax_summer</t>
+        </is>
+      </c>
+      <c r="B71" s="13" t="inlineStr">
+        <is>
+          <t>2033-06-13</t>
+        </is>
+      </c>
+      <c r="C71" s="13" t="inlineStr">
+        <is>
+          <t>2033-06-20</t>
+        </is>
+      </c>
+      <c r="D71" s="13" t="inlineStr">
+        <is>
+          <t>2033-08-28</t>
+        </is>
+      </c>
+      <c r="E71" s="13" t="inlineStr">
+        <is>
+          <t>culture</t>
+        </is>
+      </c>
+      <c r="F71" s="13" t="inlineStr">
+        <is>
+          <t>lax</t>
+        </is>
+      </c>
+      <c r="G71" s="13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H71" s="13" t="inlineStr">
+        <is>
+          <t>leisure</t>
+        </is>
+      </c>
+      <c r="I71" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J71" s="13" t="inlineStr">
+        <is>
+          <t>Summer in California.</t>
+        </is>
+      </c>
+      <c r="K71" s="13" t="inlineStr">
+        <is>
+          <t>Los Angeles fills the A380 all summer.</t>
+        </is>
+      </c>
+      <c r="L71" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="13" t="inlineStr">
+        <is>
+          <t>hkg_typhoon</t>
+        </is>
+      </c>
+      <c r="B72" s="13" t="inlineStr">
+        <is>
+          <t>2033-07-18</t>
+        </is>
+      </c>
+      <c r="C72" s="13" t="inlineStr">
+        <is>
+          <t>2033-07-18</t>
+        </is>
+      </c>
+      <c r="D72" s="13" t="inlineStr">
+        <is>
+          <t>2033-07-20</t>
+        </is>
+      </c>
+      <c r="E72" s="13" t="inlineStr">
+        <is>
+          <t>nature</t>
+        </is>
+      </c>
+      <c r="F72" s="13" t="inlineStr">
+        <is>
+          <t>hkg</t>
+        </is>
+      </c>
+      <c r="G72" s="13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H72" s="13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I72" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J72" s="13" t="inlineStr">
+        <is>
+          <t>A typhoon closes Hong Kong for three days.</t>
+        </is>
+      </c>
+      <c r="K72" s="13" t="inlineStr">
+        <is>
+          <t>None in advance.</t>
+        </is>
+      </c>
+      <c r="L72" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="13" t="inlineStr">
+        <is>
+          <t>edi_festival3</t>
+        </is>
+      </c>
+      <c r="B73" s="13" t="inlineStr">
+        <is>
+          <t>2033-07-25</t>
+        </is>
+      </c>
+      <c r="C73" s="13" t="inlineStr">
+        <is>
+          <t>2033-08-01</t>
+        </is>
+      </c>
+      <c r="D73" s="13" t="inlineStr">
+        <is>
+          <t>2033-08-21</t>
+        </is>
+      </c>
+      <c r="E73" s="13" t="inlineStr">
+        <is>
+          <t>culture</t>
+        </is>
+      </c>
+      <c r="F73" s="13" t="inlineStr">
+        <is>
+          <t>edi</t>
+        </is>
+      </c>
+      <c r="G73" s="13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H73" s="13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I73" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J73" s="13" t="inlineStr">
+        <is>
+          <t>The Edinburgh festivals.</t>
+        </is>
+      </c>
+      <c r="K73" s="13" t="inlineStr">
+        <is>
+          <t>A bigger plane on Edinburgh.</t>
+        </is>
+      </c>
+      <c r="L73" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="13" t="inlineStr">
+        <is>
+          <t>a380_anniversary</t>
+        </is>
+      </c>
+      <c r="B74" s="13" t="inlineStr">
+        <is>
+          <t>2033-09-26</t>
+        </is>
+      </c>
+      <c r="C74" s="13" t="inlineStr">
+        <is>
+          <t>2033-10-04</t>
+        </is>
+      </c>
+      <c r="D74" s="13" t="inlineStr">
+        <is>
+          <t>2033-10-10</t>
+        </is>
+      </c>
+      <c r="E74" s="13" t="inlineStr">
+        <is>
+          <t>rival</t>
+        </is>
+      </c>
+      <c r="F74" s="13" t="inlineStr">
+        <is>
+          <t>hkg,lax</t>
+        </is>
+      </c>
+      <c r="G74" s="13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H74" s="13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I74" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J74" s="13" t="inlineStr">
+        <is>
+          <t>A year since the A380's first flight.</t>
+        </is>
+      </c>
+      <c r="K74" s="13" t="inlineStr">
+        <is>
+          <t>A fare rise the passengers will pay.</t>
+        </is>
+      </c>
+      <c r="L74" s="13" t="inlineStr">
         <is>
           <t>live</t>
         </is>
@@ -40956,7 +43883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -42315,7 +45242,114 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="17" t="inlineStr">
+      <c r="A40" s="13" t="inlineStr">
+        <is>
+          <t>a380_offer</t>
+        </is>
+      </c>
+      <c r="B40" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" s="13" t="inlineStr">
+        <is>
+          <t>Take the A380</t>
+        </is>
+      </c>
+      <c r="D40" s="13" t="inlineStr">
+        <is>
+          <t>£20m down, then £1m a month for 40 months</t>
+        </is>
+      </c>
+      <c r="E40" s="13" t="n"/>
+      <c r="F40" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="13" t="inlineStr">
+        <is>
+          <t>finance a380</t>
+        </is>
+      </c>
+      <c r="I40" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="13" t="inlineStr">
+        <is>
+          <t>a380_offer</t>
+        </is>
+      </c>
+      <c r="B41" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C41" s="13" t="inlineStr">
+        <is>
+          <t>Take the 747 instead</t>
+        </is>
+      </c>
+      <c r="D41" s="13" t="inlineStr">
+        <is>
+          <t>£16m down, then £600,000 a month</t>
+        </is>
+      </c>
+      <c r="E41" s="13" t="n"/>
+      <c r="F41" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="13" t="inlineStr">
+        <is>
+          <t>finance b747</t>
+        </is>
+      </c>
+      <c r="I41" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="13" t="inlineStr">
+        <is>
+          <t>a380_offer</t>
+        </is>
+      </c>
+      <c r="B42" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C42" s="13" t="inlineStr">
+        <is>
+          <t>Neither, for now</t>
+        </is>
+      </c>
+      <c r="D42" s="13" t="inlineStr">
+        <is>
+          <t>The offer stays open on the Fleet desk</t>
+        </is>
+      </c>
+      <c r="E42" s="13" t="n"/>
+      <c r="F42" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="13" t="inlineStr"/>
+      <c r="I42" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="17" t="inlineStr">
         <is>
           <t>D81: one row per option. Before day 29 'cash £' is the fixed price; from day 29 costShare × yesterday's profit, rounded to £10 and printed on the card. Headline-only events (fuel_shock, football_final, price_war, oil_find, first_snow, christmas, new_year, half_term, easter, summer_holidays, fuel_shock2, xmas2, oil_glut, heatwave, easter2) have no rows: their effects are in Events.otherEffects and change Market or route demand only.</t>
         </is>

--- a/data/Airline-World-Workbook.xlsx
+++ b/data/Airline-World-Workbook.xlsx
@@ -572,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A31"/>
+  <dimension ref="A1:A32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -792,6 +792,13 @@
       <c r="A31" s="17" t="inlineStr">
         <is>
           <t>v5.6 (15 Oct): D86 working on paper — the workbench is an answer box, methods are reference cards; the two-tries rule; fuel is one sum a week (the Monday order, blocks × price per 1,000 L, by hand only on a 50p move) with the bill broken down by route and plane automatically; Launch Day keeps five sums (snacks as Build); cap of three a week confirmed. HandSumRules 2, 4 and 12. Every sum is numbered (Settings sumNumbering) so paper working matches the record.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="17" t="inlineStr">
+        <is>
+          <t>v5.7 (15 Oct): D87 decision support — PlanTips gains action, moneyAtStake and experiment columns plus plane_unused, loss_making_service and plan_loses_money; Settings operationsCheck, blockPreview, missedProfitDisplay (words for the pupil, figures for the teacher), reviewFixLink, planningSupport dial (guided | supported | independent | management), experimentFlow, helpMeInvestigate, planImprovedBanner. Brief: Decision support. D88 'what was it worth?' (Settings whatWasItWorth; WorkingMethods row).</t>
         </is>
       </c>
     </row>
@@ -34716,7 +34723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -35152,6 +35159,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
@@ -35745,14 +35753,51 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="17" t="inlineStr">
-        <is>
-          <t>D60: the workbench (Work it out) offers the methods listed for the relationship being signed off; the pupil chooses. Levels: operational (what does this one thing cost? — taught and calculated), model (what happens if I change this? — the console calculates), strategic (what should I do when the future is uncertain? — maths supports judgement).</t>
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>what a change was worth</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>Plan improved banner; experiment compare; Sunday review</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>change per unit × units; then × 7 for the week</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>£20 × 57 = £1,140 a day; × 7 = £7,980 a week</t>
+        </is>
+      </c>
+      <c r="F30" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="G30" s="13" t="inlineStr">
+        <is>
+          <t>NCP-3-06 · NCP-3-04 · MON-3-02 · PFA-MM-07</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="17" t="inlineStr">
+        <is>
+          <t>D60: the workbench (Work it out) offers the methods listed for the relationship being signed off; the pupil chooses. Levels: operational (what does this one thing cost? — taught and calculated), model (what happens if I change this? — the console calculates), strategic (what should I do when the future is uncertain? — maths supports judgement).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="17" t="inlineStr">
         <is>
           <t>Statement codes are from Bettws-Master-Dataset-v1_21 (WPS 3 main curriculum and PFA Managing Money). Drafted by Fable 13 Oct for Bertie to check; the pupil record prints these codes against each entry.</t>
         </is>
@@ -35769,7 +35814,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D139"/>
+  <dimension ref="A1:D148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -38643,6 +38688,194 @@
         </is>
       </c>
       <c r="D139" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="13" t="inlineStr">
+        <is>
+          <t>operationsCheck</t>
+        </is>
+      </c>
+      <c r="B140" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="C140" s="13" t="inlineStr">
+        <is>
+          <t>D87: before Run week, a check shows the one or two PlanTips with the most money at stake, each with its action and 'Run anyway'. Never blocks; the action is the visually dominant button.</t>
+        </is>
+      </c>
+      <c r="D140" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="13" t="inlineStr">
+        <is>
+          <t>blockPreview</t>
+        </is>
+      </c>
+      <c r="B141" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="C141" s="13" t="inlineStr">
+        <is>
+          <t>D87: a service block shows its expected fill while being moved (Earlier / Later or drag) and a one-line 'this change: seats a → b, profit £x → £y' after the drop; a full service with passengers turned away shows the fare chips with expected fill at each.</t>
+        </is>
+      </c>
+      <c r="D141" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="13" t="inlineStr">
+        <is>
+          <t>missedProfitDisplay</t>
+        </is>
+      </c>
+      <c r="B142" s="13" t="inlineStr">
+        <is>
+          <t>words for the pupil; figures for the teacher</t>
+        </is>
+      </c>
+      <c r="C142" s="13" t="inlineStr">
+        <is>
+          <t>D87: the pupil's review says 'a large improvement is available' (gap &gt; 30% of the best), 'a better plan is available' (10–30%) or 'a good plan' (&lt; 10%); the exact best-plan figure appears on the teacher panel and the printed review only.</t>
+        </is>
+      </c>
+      <c r="D142" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="13" t="inlineStr">
+        <is>
+          <t>reviewFixLink</t>
+        </is>
+      </c>
+      <c r="B143" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="C143" s="13" t="inlineStr">
+        <is>
+          <t>D87: the Sunday review names the biggest missed opportunity (the tip with the most money at stake over the week) and offers 'Fix next week's {route} plan', which opens the carried-over plan with that route selected and its demand curve shown.</t>
+        </is>
+      </c>
+      <c r="D143" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="13" t="inlineStr">
+        <is>
+          <t>planningSupport</t>
+        </is>
+      </c>
+      <c r="B144" s="13" t="inlineStr">
+        <is>
+          <t>guided</t>
+        </is>
+      </c>
+      <c r="C144" s="13" t="inlineStr">
+        <is>
+          <t>D87: teacher dial — guided | supported | independent | management. guided: the check names the issue and offers 2–3 experiments (change the fare / the times / the number of services / the aircraft) with a prediction step; supported: names the issue only, the pupil chooses what to change; independent: shows the data and the modelling controls, no issue named; management: flags only losses and exceptions. Default guided for chapter 1; the dial is per pupil.</t>
+        </is>
+      </c>
+      <c r="D144" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="13" t="inlineStr">
+        <is>
+          <t>experimentFlow</t>
+        </is>
+      </c>
+      <c r="B145" s="13" t="inlineStr">
+        <is>
+          <t>choose variable → predict → change one thing → model → compare → decide</t>
+        </is>
+      </c>
+      <c r="C145" s="13" t="inlineStr">
+        <is>
+          <t>D87: in guided and supported levels every test is one variable at a time; the prediction (more / fewer / about the same seats; higher / lower / about the same profit) is recorded and compared; never a 'recommended' plan.</t>
+        </is>
+      </c>
+      <c r="D145" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="13" t="inlineStr">
+        <is>
+          <t>helpMeInvestigate</t>
+        </is>
+      </c>
+      <c r="B146" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="C146" s="13" t="inlineStr">
+        <is>
+          <t>A small button on the plan and the review that reopens the guided experiment at any support level.</t>
+        </is>
+      </c>
+      <c r="D146" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="13" t="inlineStr">
+        <is>
+          <t>planImprovedBanner</t>
+        </is>
+      </c>
+      <c r="B147" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="C147" s="13" t="inlineStr">
+        <is>
+          <t>D87: when the projected result improves after a change, a small 'Plan improved: seats a → b, result £x → £y' confirmation above Run week.</t>
+        </is>
+      </c>
+      <c r="D147" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="13" t="inlineStr">
+        <is>
+          <t>whatWasItWorth</t>
+        </is>
+      </c>
+      <c r="B148" s="13" t="inlineStr">
+        <is>
+          <t>change per unit × units = a day; × 7 = a week</t>
+        </is>
+      </c>
+      <c r="C148" s="13" t="inlineStr">
+        <is>
+          <t>D88: whenever the pupil changes a fare, a time or a service (in the plan or an experiment), show one line: fare — '£20 more a ticket × 57 passengers = £1,140 more a day'; time — '9 more passengers × £90 = £810 more a day'; service — 'one more flight: 19 × £90 − £615 costs = £1,095 a day'. The first time each kind appears it is a Build (tap the figures and ×), then Model; not counted in the sign-off cap. The Sunday review repeats it for the week ('Your Dublin fare rise was worth £7,980 this week'). Rule: the pupil sees figures for changes he made or tested; words for what is still available (missedProfitDisplay).</t>
+        </is>
+      </c>
+      <c r="D148" s="13" t="inlineStr">
         <is>
           <t>live</t>
         </is>
@@ -38659,7 +38892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -38668,6 +38901,9 @@
     <col width="70" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -38701,6 +38937,21 @@
           <t>status</t>
         </is>
       </c>
+      <c r="G1" s="20" t="inlineStr">
+        <is>
+          <t>action (what the button opens)</t>
+        </is>
+      </c>
+      <c r="H1" s="20" t="inlineStr">
+        <is>
+          <t>moneyAtStake (rule)</t>
+        </is>
+      </c>
+      <c r="I1" s="20" t="inlineStr">
+        <is>
+          <t>experiment (guided)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="13" t="inlineStr">
@@ -38731,6 +38982,21 @@
           <t>live</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Show on timetable: highlight the band and the route's flights</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>profit of the best plan that adds one service in the band − current</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Change the times</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
@@ -38761,6 +39027,21 @@
           <t>live</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Select this flight (Earlier / Later / Remove)</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>profit with this flight at its best time − current</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Change the times</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
@@ -38791,6 +39072,21 @@
           <t>live</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Test fare: show the fare chips with expected fill at each; or Add a service</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>max over fares and +1 service − current</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Change the fare | Change the number of services</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
@@ -38821,6 +39117,21 @@
           <t>live</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Test fare: chips with expected fill</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>profit at the best fare − current</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Change the fare</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
@@ -38851,6 +39162,21 @@
           <t>live</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Test next fare up</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>profit at the next fare − current</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Change the fare</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
@@ -38881,6 +39207,21 @@
           <t>live</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Add a service in the idle time (opens + Service at that time)</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>profit of the best added service</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Change the number of services</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
@@ -38911,6 +39252,21 @@
           <t>live</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Open the route on the comparison (which plane suits it)</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>profit with the best plane − current</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Change the aircraft</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
@@ -38941,6 +39297,21 @@
           <t>live</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Open the aircraft comparison</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Change the aircraft</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
@@ -38971,6 +39342,21 @@
           <t>live</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
@@ -39001,6 +39387,21 @@
           <t>live</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
@@ -39031,6 +39432,21 @@
           <t>live</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Test the lower fare</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>profit at the lower fare − current</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Change the fare</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
@@ -39061,11 +39477,168 @@
           <t>live</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Add a Sat–Sun service on the route</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>profit of the weekend service</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Change the number of services</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>plane_unused</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>A plane in the fleet has no flights in the standing plan</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>{plane} has no flights. It costs £{dayCost} a day parked.</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>Find work for this aircraft (opens the timetable with the plane's row selected and + Service)</t>
+        </is>
+      </c>
+      <c r="H15" s="13" t="inlineStr">
+        <is>
+          <t>its day cost + profit of its best plan</t>
+        </is>
+      </c>
+      <c r="I15" s="13" t="inlineStr">
+        <is>
+          <t>Change the number of services | Change the aircraft</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>loss_making_service</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>A service's revenue is below its own flying, fuel, landing and passenger costs</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>{band} {route} loses £{loss} a trip.</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="G16" s="13" t="inlineStr">
+        <is>
+          <t>Compare: remove / retime / reprice (three previews)</t>
+        </is>
+      </c>
+      <c r="H16" s="13" t="inlineStr">
+        <is>
+          <t>the loss, or the gain from the best of the three</t>
+        </is>
+      </c>
+      <c r="I16" s="13" t="inlineStr">
+        <is>
+          <t>Change the times | Change the fare | Change the number of services</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>plan_loses_money</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>The whole plan projects a loss for the day</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>This plan loses £{loss} a day. The biggest opportunity is {topTip}.</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>Show me (opens the top tip's action)</t>
+        </is>
+      </c>
+      <c r="H17" s="13" t="inlineStr">
+        <is>
+          <t>the loss</t>
+        </is>
+      </c>
+      <c r="I17" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>D66: the Live seat fill panel shows at most two tips, lowest priority number first. Conditions are evaluated on the projected plan every time it changes; the same conditions feed the Sunday review's explanation of missed profit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>D87: the Operations Check shows the one or two tips with the most money at stake (moneyAtStake rule, engine-computed), each with its action button; the pupil sees the words, never the best-plan figure. Priority 0–1 tips always rank first.</t>
         </is>
       </c>
     </row>

--- a/data/Airline-World-Workbook.xlsx
+++ b/data/Airline-World-Workbook.xlsx
@@ -572,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A32"/>
+  <dimension ref="A1:A33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -799,6 +799,13 @@
       <c r="A32" s="17" t="inlineStr">
         <is>
           <t>v5.7 (15 Oct): D87 decision support — PlanTips gains action, moneyAtStake and experiment columns plus plane_unused, loss_making_service and plan_loses_money; Settings operationsCheck, blockPreview, missedProfitDisplay (words for the pupil, figures for the teacher), reviewFixLink, planningSupport dial (guided | supported | independent | management), experimentFlow, helpMeInvestigate, planImprovedBanner. Brief: Decision support. D88 'what was it worth?' (Settings whatWasItWorth; WorkingMethods row).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="17" t="inlineStr">
+        <is>
+          <t>v5.8 (15 Oct): D89 fuel storage — the tank grows with the fleet (three weeks of the standing plan's fuel, recomputed each Monday, never shrinking; tankUpgradeDay withdrawn); block size 1,000 L, then 10,000 from January 2031, then 100,000 from September 2031; a fuel farm to buy from chapter 3 (1,500,000 L for £2m; 3,000,000 L for £3m more in chapter 4) with an is-it-worth-it sum. Answers Claude Code's tank question.</t>
         </is>
       </c>
     </row>
@@ -5813,7 +5820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6633,6 +6640,46 @@
       <c r="A19" s="17" t="inlineStr">
         <is>
           <t>Tutorial prices are 2½× v4.3 (D55): the second plane is rented or financed in week 2 and bought outright around week 4–5. The first Twin Otter is still the £2,500 launch deal. Rent-or-buy ≈ 55 days for every tutorial plane; 1,000 days for jets from the A220 up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>fuelFarm</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="C20" s="13" t="n"/>
+      <c r="D20" s="13" t="n"/>
+      <c r="E20" s="13" t="n"/>
+      <c r="F20" s="13" t="n"/>
+      <c r="G20" s="13" t="n"/>
+      <c r="H20" s="13" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>2031-09-01</t>
+        </is>
+      </c>
+      <c r="J20" s="13" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="inlineStr">
+        <is>
+          <t>D89: fuel storage to buy, 1,500,000 L (chapter 3); a second stage of 3,000,000 L for £3m from 2032-09-06. Not a plane: no rent, no finance. Is it worth it? litres × the next shock's rise against the price.</t>
+        </is>
+      </c>
+      <c r="L20" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
         </is>
       </c>
     </row>
@@ -34723,7 +34770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -35790,14 +35837,51 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="17" t="inlineStr">
-        <is>
-          <t>D60: the workbench (Work it out) offers the methods listed for the relationship being signed off; the pupil chooses. Levels: operational (what does this one thing cost? — taught and calculated), model (what happens if I change this? — the console calculates), strategic (what should I do when the future is uncertain? — maths supports judgement).</t>
+      <c r="A31" s="13" t="inlineStr">
+        <is>
+          <t>is the fuel farm worth it?</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>strategic</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="inlineStr">
+        <is>
+          <t>Fuel desk (chapter 3)</t>
+        </is>
+      </c>
+      <c r="D31" s="13" t="inlineStr">
+        <is>
+          <t>litres × the expected price rise, against the price; weeks to afford</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>1,500,000 × 60p = £900,000 a shock; £2m ÷ £900,000 ≈ 2 shocks to pay back</t>
+        </is>
+      </c>
+      <c r="F31" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="G31" s="13" t="inlineStr">
+        <is>
+          <t>NCP-3-02 · NCP-3-05 · NCP-3-06 · MON-3-03 · PFA-MM-07 · STAT-3-25 (what the forecast cannot tell us)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="17" t="inlineStr">
+        <is>
+          <t>D60: the workbench (Work it out) offers the methods listed for the relationship being signed off; the pupil chooses. Levels: operational (what does this one thing cost? — taught and calculated), model (what happens if I change this? — the console calculates), strategic (what should I do when the future is uncertain? — maths supports judgement).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="17" t="inlineStr">
         <is>
           <t>Statement codes are from Bettws-Master-Dataset-v1_21 (WPS 3 main curriculum and PFA Managing Money). Drafted by Fable 13 Oct for Bertie to check; the pupil record prints these codes against each entry.</t>
         </is>
@@ -35814,7 +35898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D148"/>
+  <dimension ref="A1:D150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -37135,12 +37219,14 @@
           <t>fuelLotSize</t>
         </is>
       </c>
-      <c r="B64" s="13" t="n">
-        <v>1000</v>
+      <c r="B64" s="13" t="inlineStr">
+        <is>
+          <t>1000 | 10000 from 2031-01-06 | 100000 from 2031-09-01</t>
+        </is>
       </c>
       <c r="C64" s="13" t="inlineStr">
         <is>
-          <t>D57: fuel is bought in whole thousands of litres on the fuel desk (replaces the 500-litre lot).</t>
+          <t>D89: the block size grows so the Monday order sum stays blocks × price per block: 6 × £1,470; 25 × £21,700; 8 × £257,000. The desk shows the price per block.</t>
         </is>
       </c>
       <c r="D64" s="13" t="inlineStr">
@@ -37160,7 +37246,7 @@
       </c>
       <c r="C65" s="13" t="inlineStr">
         <is>
-          <t>D60: litres of storage from week 2.</t>
+          <t>D89: starting storage (week 2). From then the tank grows with the fleet (tankWeeksOfFuel); it never shrinks. tankUpgradeDay / tankCapacityUpgraded are withdrawn.</t>
         </is>
       </c>
       <c r="D65" s="13" t="inlineStr">
@@ -37365,12 +37451,14 @@
           <t>tankUpgradeDay</t>
         </is>
       </c>
-      <c r="B75" s="13" t="n">
-        <v>29</v>
+      <c r="B75" s="13" t="inlineStr">
+        <is>
+          <t>withdrawn</t>
+        </is>
       </c>
       <c r="C75" s="13" t="inlineStr">
         <is>
-          <t>D60: storage grows to tankCapacityUpgraded on this day, announced as a storage upgrade.</t>
+          <t>replaced by tankWeeksOfFuel (D89)</t>
         </is>
       </c>
       <c r="D75" s="13" t="inlineStr">
@@ -37385,10 +37473,16 @@
           <t>tankCapacityUpgraded</t>
         </is>
       </c>
-      <c r="B76" s="13" t="n">
-        <v>20000</v>
-      </c>
-      <c r="C76" s="13" t="inlineStr"/>
+      <c r="B76" s="13" t="inlineStr">
+        <is>
+          <t>withdrawn</t>
+        </is>
+      </c>
+      <c r="C76" s="13" t="inlineStr">
+        <is>
+          <t>replaced by tankWeeksOfFuel (D89)</t>
+        </is>
+      </c>
       <c r="D76" s="13" t="inlineStr">
         <is>
           <t>live</t>
@@ -38876,6 +38970,48 @@
         </is>
       </c>
       <c r="D148" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="13" t="inlineStr">
+        <is>
+          <t>tankWeeksOfFuel</t>
+        </is>
+      </c>
+      <c r="B149" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C149" s="13" t="inlineStr">
+        <is>
+          <t>D89: each Monday, capacity = max(current, 3 × the standing plan's weekly litres, rounded UP to the block size × 10). The desk says 'Storage: 60,000 L — about three weeks of flying'. No cost.</t>
+        </is>
+      </c>
+      <c r="D149" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="13" t="inlineStr">
+        <is>
+          <t>fuelFarm</t>
+        </is>
+      </c>
+      <c r="B150" s="13" t="inlineStr">
+        <is>
+          <t>chapter 3: buy storage</t>
+        </is>
+      </c>
+      <c r="C150" s="13" t="inlineStr">
+        <is>
+          <t>D89: from 2031-09-01 the Fuel desk offers a fuel farm to buy (Finance sheet row fuelFarm): capacity 1,500,000 L for £2m, then 3,000,000 L for £3m more in chapter 4. The sum: what a full farm saves in a shock (litres × the price rise, e.g. 1,500,000 × 60p = £900,000) against the price; the same buy-now-or-wait shape as a plane. Below the farm, capacity still grows with the fleet.</t>
+        </is>
+      </c>
+      <c r="D150" s="13" t="inlineStr">
         <is>
           <t>live</t>
         </is>

--- a/data/Airline-World-Workbook.xlsx
+++ b/data/Airline-World-Workbook.xlsx
@@ -14,26 +14,27 @@
     <sheet name="Settings" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="PlanTips" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="DailyColour" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Upgrades" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Briefings" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="RouteNews" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Archetypes" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="EventOptions" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Milestones" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Campaign" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Routes" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="RouteCatalogue" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Aircraft" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Finance" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Airports" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Calendar" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Market" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Events" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Challenges" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Mechanics" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Catering" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="Hunts" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="Livery" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="Roadmap" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Upgrades" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Briefings" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="RouteNews" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Archetypes" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="EventOptions" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Milestones" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Campaign" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Routes" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="RouteCatalogue" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Aircraft" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Finance" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Airports" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Calendar" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Market" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Events" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Challenges" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Mechanics" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="Catering" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="Hunts" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="Livery" sheetId="28" state="visible" r:id="rId28"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -576,7 +577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A34"/>
+  <dimension ref="A1:A35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -820,12 +821,660 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Took from v5.17 (17 Oct 2026, Claude Code): D101 and D102 only (Screens brief 3) — the Roadmap sheet; Settings adaptToOnlyFlight, demandShapeDisplay, flightTimeDecay, timeAnswerFormat, flightTimesTable, weekPlanTutorial, redMeans, opportunityDisplay, resultsFraming, flightInspector, activeRoutesCollapsible, weekGraphDefault, dailyColourLimit, comingUp, aircraftWorthCheck, teacherTestMode, and from D100 the three rows D101 builds on (waitCostLine, aircraftCardMeasure, demandStripMode); the fuel dips: Market weeks 3–5 and Calendar days 22–28. The rest of v5.16–v5.17 (D100, the D92 market from week 6 on) is kept in data/incoming/.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="20" t="inlineStr">
+        <is>
+          <t>briefingId</t>
+        </is>
+      </c>
+      <c r="B1" s="20" t="inlineStr">
+        <is>
+          <t>trigger</t>
+        </is>
+      </c>
+      <c r="C1" s="20" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="D1" s="20" t="inlineStr">
+        <is>
+          <t>beat1 (show)</t>
+        </is>
+      </c>
+      <c r="E1" s="20" t="inlineStr">
+        <is>
+          <t>beat2 (predict: the pupil does…)</t>
+        </is>
+      </c>
+      <c r="F1" s="20" t="inlineStr">
+        <is>
+          <t>beat3 (reveal)</t>
+        </is>
+      </c>
+      <c r="G1" s="20" t="inlineStr">
+        <is>
+          <t>beat4 (use)</t>
+        </is>
+      </c>
+      <c r="H1" s="20" t="inlineStr">
+        <is>
+          <t>leadsInto</t>
+        </is>
+      </c>
+      <c r="I1" s="20" t="inlineStr">
+        <is>
+          <t>seconds</t>
+        </is>
+      </c>
+      <c r="J1" s="20" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="K1" s="20" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>fare_lever</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>Launch Day, the fare chips</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="inlineStr">
+        <is>
+          <t>What a fare does</t>
+        </is>
+      </c>
+      <c r="D2" s="13" t="inlineStr">
+        <is>
+          <t>Nineteen passenger dots and a £ meter. The fare slides from £80 to £90 to £100; the meter per passenger rises as dots fade.</t>
+        </is>
+      </c>
+      <c r="E2" s="13" t="inlineStr">
+        <is>
+          <t>Drag the fare yourself; predict: more or fewer dots at £100?</t>
+        </is>
+      </c>
+      <c r="F2" s="13" t="inlineStr">
+        <is>
+          <t>Revenue = passengers × fare: both move. At £100 Paris wants 44, not 50 — two planes still fill.</t>
+        </is>
+      </c>
+      <c r="G2" s="13" t="inlineStr">
+        <is>
+          <t>Back to the chips with the three revenue figures</t>
+        </is>
+      </c>
+      <c r="H2" s="13" t="inlineStr">
+        <is>
+          <t>Launch Day sum 1</t>
+        </is>
+      </c>
+      <c r="I2" s="13" t="n">
+        <v>35</v>
+      </c>
+      <c r="J2" s="13" t="inlineStr">
+        <is>
+          <t>briefing-fare.html</t>
+        </is>
+      </c>
+      <c r="K2" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>rival_split</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>Thu, week 1 (Red Kite)</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>Customers have a choice</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>62 Dublin dots; a red-kite plane lands beside yours; its price tag reads £50.</t>
+        </is>
+      </c>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>Slide your fare; watch dots cross to Red Kite: 1 in 10 per £10.</t>
+        </is>
+      </c>
+      <c r="F3" s="13" t="inlineStr">
+        <is>
+          <t>The switching rule in one line; advertising halves it.</t>
+        </is>
+      </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>The Red Kite decision with the sum on it</t>
+        </is>
+      </c>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>Red Kite card</t>
+        </is>
+      </c>
+      <c r="I3" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="J3" s="13" t="inlineStr">
+        <is>
+          <t>briefing-rival.html</t>
+        </is>
+      </c>
+      <c r="K3" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>full_route</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Week-1 review</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>More demand than seats</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>Passenger dots arrive at the terminal; 57 board three Twin Otters; the rest stay on the apron.</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>Click the dots left behind; how many?</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>High demand is not profit if you cannot carry people: a bigger plane, another plane, or a higher fare.</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>The capacity observation and Compare aircraft</t>
+        </is>
+      </c>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t>Week-2 decision</t>
+        </is>
+      </c>
+      <c r="I4" s="13" t="n">
+        <v>35</v>
+      </c>
+      <c r="J4" s="13" t="inlineStr">
+        <is>
+          <t>briefing-capacity.html</t>
+        </is>
+      </c>
+      <c r="K4" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>weekend_demand</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Week-2 review</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Weekdays and weekends</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>Mon–Sun bars grow for Dublin; business icons fill weekdays, families the weekend.</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>Click the days that look different.</t>
+        </is>
+      </c>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>Why: business travel builds on weekdays; leisure swells at the weekend. Your timetable appears underneath — the same every day.</t>
+        </is>
+      </c>
+      <c r="G5" s="13" t="inlineStr">
+        <is>
+          <t>Does the planner fit what the passengers do? → the Upgrades question</t>
+        </is>
+      </c>
+      <c r="H5" s="13" t="inlineStr">
+        <is>
+          <t>weekend_schedules upgrade</t>
+        </is>
+      </c>
+      <c r="I5" s="13" t="n">
+        <v>45</v>
+      </c>
+      <c r="J5" s="13" t="inlineStr">
+        <is>
+          <t>briefing-weekend.html</t>
+        </is>
+      </c>
+      <c r="K5" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>fuel_cash_tank_profit</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>First Fuel desk visit (day 8)</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>Cash, tank, profit</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>Three gauges: cash £12,409, tank 0 L, profit today. Press Buy 7,000 L: cash flows into the tank; profit does not move.</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>Press Buy yourself; then: what changed? (tap the gauge)</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>A Twin Otter departs for Paris: 120 L drains, £176 flows into today's costs. Buying fuel and using fuel are different events.</t>
+        </is>
+      </c>
+      <c r="G6" s="13" t="inlineStr">
+        <is>
+          <t>The Fuel desk with the order instrument</t>
+        </is>
+      </c>
+      <c r="H6" s="13" t="inlineStr">
+        <is>
+          <t>Fuel order sum</t>
+        </is>
+      </c>
+      <c r="I6" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="J6" s="13" t="inlineStr">
+        <is>
+          <t>briefing-fuel.html</t>
+        </is>
+      </c>
+      <c r="K6" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>aircraft_efficiency</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Week-2 shop, first comparison</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>Two planes, one route</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>A Twin Otter and a Saab fly Dublin side by side; both gauges drain; a seat-row per plane.</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>Which burned more per seat? Tap it.</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>Litres per seat: the Saab 6.6, the Twin Otter 9.5 — bigger can be cheaper a seat, if it fills.</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="inlineStr">
+        <is>
+          <t>The comparison with the litres-per-seat widget</t>
+        </is>
+      </c>
+      <c r="H7" s="13" t="inlineStr">
+        <is>
+          <t>Second-plane decision</t>
+        </is>
+      </c>
+      <c r="I7" s="13" t="n">
+        <v>35</v>
+      </c>
+      <c r="J7" s="13" t="inlineStr">
+        <is>
+          <t>briefing-efficiency.html</t>
+        </is>
+      </c>
+      <c r="K7" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>event_weekend</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>Announced event (day 22: the All Blacks)</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>One big Saturday</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>A normal Saturday: 62 Dublin dots. An event card slides onto the date; dots stream in to 124. Your two flights stay where they are.</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>What changed? Tap the day.</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>Events change a market for a day; a weekend plan changes every Saturday.</t>
+        </is>
+      </c>
+      <c r="G8" s="13" t="inlineStr">
+        <is>
+          <t>Can the planner respond to one date? → Upgrades question</t>
+        </is>
+      </c>
+      <c r="H8" s="13" t="inlineStr">
+        <is>
+          <t>day_override upgrade</t>
+        </is>
+      </c>
+      <c r="I8" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="J8" s="13" t="inlineStr">
+        <is>
+          <t>briefing-event.html</t>
+        </is>
+      </c>
+      <c r="K8" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>seasons</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>Chapter-1 review</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>A year of demand</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>Twelve months; Geneva's bar grows in winter, Barcelona's in summer; Christmas and half-term markers.</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>Drag a plane icon to the month you'd fly Geneva.</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>Markets change through the year for different reasons; a weekly plan does not.</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>The Upgrades question (seasonal plans)</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="inlineStr">
+        <is>
+          <t>seasonal_plans upgrade</t>
+        </is>
+      </c>
+      <c r="I9" s="13" t="n">
+        <v>45</v>
+      </c>
+      <c r="J9" s="13" t="inlineStr">
+        <is>
+          <t>briefing-seasons.html</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>lease_money</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>6 Jan 2031, the 787 to lease</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Renting a plane</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>A 787; the price £12m against cash £1.5m; a rent meter ticks £6,000 a day.</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>Slide the days: when does rent pass the price?</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>Rent-or-buy: 12,000,000 ÷ 6,000 = 2,000 days. Rent keeps cash; buying keeps the plane.</t>
+        </is>
+      </c>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
+          <t>The shop with Rent and (greyed) Buy</t>
+        </is>
+      </c>
+      <c r="H10" s="13" t="inlineStr">
+        <is>
+          <t>Rent-or-buy sum</t>
+        </is>
+      </c>
+      <c r="I10" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="J10" s="13" t="inlineStr">
+        <is>
+          <t>briefing-lease.html</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>profit_vs_cash</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Chapter 3, first overdrawn month or the 787 purchase</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Profit is not cash</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>The month's profit bar rises while the cash gauge falls: the money went into a plane and a full tank.</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>Tap where the money went.</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>Profit answers 'did we earn?'; cash answers 'can we pay?'. Both matter.</t>
+        </is>
+      </c>
+      <c r="G11" s="13" t="inlineStr">
+        <is>
+          <t>The Finance desk with the overdraft line</t>
+        </is>
+      </c>
+      <c r="H11" s="13" t="inlineStr">
+        <is>
+          <t>Overdraft / buying outright</t>
+        </is>
+      </c>
+      <c r="I11" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="J11" s="13" t="inlineStr">
+        <is>
+          <t>briefing-cash.html</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>D99: Show → Predict → Reveal → Use. Full screen, the interface darkened behind; the pupil advances by the interaction in beat 2, never by Next; a Pause &amp; discuss button at each stop for the teacher; a Replay from the Briefings shelf. Each is built as a separate HTML piece in the game's style (see the flight-time tutorial) and the game loads it at its trigger.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5040,7 +5689,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5628,7 +6277,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7111,7 +7760,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7734,7 +8383,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
     <row r="21">
       <c r="A21" s="17" t="inlineStr">
         <is>
@@ -7747,7 +8395,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8009,7 +8657,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10438,7 +11086,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11704,7 +12352,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12747,7 +13395,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13613,314 +14261,6 @@
       <c r="L20" s="13" t="inlineStr">
         <is>
           <t>live</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>code</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>landingFee</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>demandModifier</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>tendency</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>terminal</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>turnaroundMin</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>passengerCharge</t>
-        </is>
-      </c>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="12" t="inlineStr">
-        <is>
-          <t>LHR</t>
-        </is>
-      </c>
-      <c r="B2" s="12" t="inlineStr">
-        <is>
-          <t>London Heathrow</t>
-        </is>
-      </c>
-      <c r="C2" s="12" t="n">
-        <v>120</v>
-      </c>
-      <c r="D2" s="12" t="inlineStr">
-        <is>
-          <t>+15%</t>
-        </is>
-      </c>
-      <c r="E2" s="12" t="inlineStr">
-        <is>
-          <t>business</t>
-        </is>
-      </c>
-      <c r="F2" s="12" t="inlineStr">
-        <is>
-          <t>T5</t>
-        </is>
-      </c>
-      <c r="G2" s="12" t="n">
-        <v>35</v>
-      </c>
-      <c r="H2" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="I2" s="12" t="inlineStr">
-        <is>
-          <t>The only home airport at setup (D32)</t>
-        </is>
-      </c>
-      <c r="J2" s="12" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="19" t="inlineStr">
-        <is>
-          <t>LHR</t>
-        </is>
-      </c>
-      <c r="B3" s="19" t="inlineStr">
-        <is>
-          <t>London Heathrow</t>
-        </is>
-      </c>
-      <c r="C3" s="19" t="n">
-        <v>120</v>
-      </c>
-      <c r="D3" s="19" t="inlineStr">
-        <is>
-          <t>+15%</t>
-        </is>
-      </c>
-      <c r="E3" s="19" t="inlineStr">
-        <is>
-          <t>business</t>
-        </is>
-      </c>
-      <c r="F3" s="19" t="inlineStr">
-        <is>
-          <t>T4</t>
-        </is>
-      </c>
-      <c r="G3" s="19" t="n">
-        <v>55</v>
-      </c>
-      <c r="H3" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="I3" s="19" t="inlineStr">
-        <is>
-          <t>Removed 6 Oct (D32); row kept for its id</t>
-        </is>
-      </c>
-      <c r="J3" s="19" t="inlineStr">
-        <is>
-          <t>removed</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="19" t="inlineStr">
-        <is>
-          <t>LGW</t>
-        </is>
-      </c>
-      <c r="B4" s="19" t="inlineStr">
-        <is>
-          <t>London Gatwick</t>
-        </is>
-      </c>
-      <c r="C4" s="19" t="n">
-        <v>80</v>
-      </c>
-      <c r="D4" s="19" t="inlineStr">
-        <is>
-          <t>+5%</t>
-        </is>
-      </c>
-      <c r="E4" s="19" t="inlineStr">
-        <is>
-          <t>leisure</t>
-        </is>
-      </c>
-      <c r="F4" s="19" t="inlineStr">
-        <is>
-          <t>North</t>
-        </is>
-      </c>
-      <c r="G4" s="19" t="n">
-        <v>45</v>
-      </c>
-      <c r="H4" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="I4" s="19" t="inlineStr">
-        <is>
-          <t>Removed 6 Oct (D32); row kept for its id</t>
-        </is>
-      </c>
-      <c r="J4" s="19" t="inlineStr">
-        <is>
-          <t>removed</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="15" t="inlineStr">
-        <is>
-          <t>LTN</t>
-        </is>
-      </c>
-      <c r="B5" s="15" t="inlineStr">
-        <is>
-          <t>London Luton</t>
-        </is>
-      </c>
-      <c r="C5" s="15" t="n">
-        <v>40</v>
-      </c>
-      <c r="D5" s="15" t="inlineStr">
-        <is>
-          <t>-5%</t>
-        </is>
-      </c>
-      <c r="E5" s="15" t="inlineStr">
-        <is>
-          <t>leisure</t>
-        </is>
-      </c>
-      <c r="F5" s="15" t="inlineStr">
-        <is>
-          <t>Main</t>
-        </is>
-      </c>
-      <c r="G5" s="15" t="n">
-        <v>40</v>
-      </c>
-      <c r="H5" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="I5" s="15" t="inlineStr">
-        <is>
-          <t>Kept for the one-off April 2031 switch (fees_rise option 4). Needs a balance pass if taken.</t>
-        </is>
-      </c>
-      <c r="J5" s="15" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>MAN</t>
-        </is>
-      </c>
-      <c r="B6" s="19" t="inlineStr">
-        <is>
-          <t>Manchester</t>
-        </is>
-      </c>
-      <c r="C6" s="19" t="n">
-        <v>60</v>
-      </c>
-      <c r="D6" s="19" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="E6" s="19" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="F6" s="19" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="G6" s="19" t="n">
-        <v>45</v>
-      </c>
-      <c r="H6" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="I6" s="19" t="inlineStr">
-        <is>
-          <t>Removed 6 Oct (D32); row kept for its id</t>
-        </is>
-      </c>
-      <c r="J6" s="19" t="inlineStr">
-        <is>
-          <t>removed</t>
         </is>
       </c>
     </row>
@@ -14368,6 +14708,314 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>landingFee</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>demandModifier</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>tendency</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>terminal</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>turnaroundMin</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>passengerCharge</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>LHR</t>
+        </is>
+      </c>
+      <c r="B2" s="12" t="inlineStr">
+        <is>
+          <t>London Heathrow</t>
+        </is>
+      </c>
+      <c r="C2" s="12" t="n">
+        <v>120</v>
+      </c>
+      <c r="D2" s="12" t="inlineStr">
+        <is>
+          <t>+15%</t>
+        </is>
+      </c>
+      <c r="E2" s="12" t="inlineStr">
+        <is>
+          <t>business</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="G2" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="H2" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I2" s="12" t="inlineStr">
+        <is>
+          <t>The only home airport at setup (D32)</t>
+        </is>
+      </c>
+      <c r="J2" s="12" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="19" t="inlineStr">
+        <is>
+          <t>LHR</t>
+        </is>
+      </c>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>London Heathrow</t>
+        </is>
+      </c>
+      <c r="C3" s="19" t="n">
+        <v>120</v>
+      </c>
+      <c r="D3" s="19" t="inlineStr">
+        <is>
+          <t>+15%</t>
+        </is>
+      </c>
+      <c r="E3" s="19" t="inlineStr">
+        <is>
+          <t>business</t>
+        </is>
+      </c>
+      <c r="F3" s="19" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="G3" s="19" t="n">
+        <v>55</v>
+      </c>
+      <c r="H3" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I3" s="19" t="inlineStr">
+        <is>
+          <t>Removed 6 Oct (D32); row kept for its id</t>
+        </is>
+      </c>
+      <c r="J3" s="19" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>LGW</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>London Gatwick</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="n">
+        <v>80</v>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>+5%</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>leisure</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="n">
+        <v>45</v>
+      </c>
+      <c r="H4" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>Removed 6 Oct (D32); row kept for its id</t>
+        </is>
+      </c>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>LTN</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>London Luton</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>-5%</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>leisure</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="G5" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="H5" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" s="15" t="inlineStr">
+        <is>
+          <t>Kept for the one-off April 2031 switch (fees_rise option 4). Needs a balance pass if taken.</t>
+        </is>
+      </c>
+      <c r="J5" s="15" t="inlineStr">
+        <is>
+          <t>later</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>MAN</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="C6" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="D6" s="19" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E6" s="19" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="F6" s="19" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="G6" s="19" t="n">
+        <v>45</v>
+      </c>
+      <c r="H6" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I6" s="19" t="inlineStr">
+        <is>
+          <t>Removed 6 Oct (D32); row kept for its id</t>
+        </is>
+      </c>
+      <c r="J6" s="19" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:R50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -15747,7 +16395,7 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>1.79</v>
+        <v>1.62</v>
       </c>
       <c r="G23" s="13" t="inlineStr">
         <is>
@@ -15761,16 +16409,16 @@
       </c>
       <c r="I23" s="13" t="inlineStr">
         <is>
-          <t>Fuel £1.79 a litre.</t>
-        </is>
-      </c>
-      <c r="J23" s="13" t="inlineStr"/>
+          <t>Fuel £1.62 a litre.</t>
+        </is>
+      </c>
+      <c r="J23" s="13" t="n"/>
       <c r="K23" s="13" t="inlineStr">
         <is>
           <t>routes: mad; planes: e175, e190; mechanics: range check, services per day on a long leg, load factor as a percentage</t>
         </is>
       </c>
-      <c r="L23" s="13" t="inlineStr"/>
+      <c r="L23" s="13" t="n"/>
       <c r="M23" s="13" t="n"/>
       <c r="N23" s="13" t="inlineStr">
         <is>
@@ -15817,21 +16465,21 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>1.79</v>
+        <v>1.62</v>
       </c>
       <c r="G24" s="13" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="H24" s="13" t="inlineStr"/>
-      <c r="I24" s="13" t="inlineStr"/>
-      <c r="J24" s="13" t="inlineStr"/>
-      <c r="K24" s="13" t="inlineStr"/>
-      <c r="L24" s="13" t="inlineStr"/>
+      <c r="H24" s="13" t="n"/>
+      <c r="I24" s="13" t="n"/>
+      <c r="J24" s="13" t="n"/>
+      <c r="K24" s="13" t="n"/>
+      <c r="L24" s="13" t="n"/>
       <c r="M24" s="13" t="n"/>
-      <c r="N24" s="13" t="inlineStr"/>
-      <c r="O24" s="13" t="inlineStr"/>
+      <c r="N24" s="13" t="n"/>
+      <c r="O24" s="13" t="n"/>
       <c r="P24" s="13" t="n"/>
       <c r="Q24" s="13" t="inlineStr">
         <is>
@@ -15867,7 +16515,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>1.79</v>
+        <v>1.62</v>
       </c>
       <c r="G25" s="13" t="inlineStr">
         <is>
@@ -15879,17 +16527,17 @@
           <t>A jet burns in one trip what a Twin Otter burns in a week.</t>
         </is>
       </c>
-      <c r="I25" s="13" t="inlineStr"/>
-      <c r="J25" s="13" t="inlineStr"/>
-      <c r="K25" s="13" t="inlineStr"/>
-      <c r="L25" s="13" t="inlineStr"/>
+      <c r="I25" s="13" t="n"/>
+      <c r="J25" s="13" t="n"/>
+      <c r="K25" s="13" t="n"/>
+      <c r="L25" s="13" t="n"/>
       <c r="M25" s="13" t="n"/>
       <c r="N25" s="13" t="inlineStr">
         <is>
           <t>fuel</t>
         </is>
       </c>
-      <c r="O25" s="13" t="inlineStr"/>
+      <c r="O25" s="13" t="n"/>
       <c r="P25" s="13" t="n"/>
       <c r="Q25" s="13" t="inlineStr">
         <is>
@@ -15925,7 +16573,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>1.79</v>
+        <v>1.62</v>
       </c>
       <c r="G26" s="13" t="inlineStr">
         <is>
@@ -15937,13 +16585,13 @@
           <t>Red Kite announces Madrid flights from Luton.</t>
         </is>
       </c>
-      <c r="I26" s="13" t="inlineStr"/>
-      <c r="J26" s="13" t="inlineStr"/>
-      <c r="K26" s="13" t="inlineStr"/>
-      <c r="L26" s="13" t="inlineStr"/>
+      <c r="I26" s="13" t="n"/>
+      <c r="J26" s="13" t="n"/>
+      <c r="K26" s="13" t="n"/>
+      <c r="L26" s="13" t="n"/>
       <c r="M26" s="13" t="n"/>
-      <c r="N26" s="13" t="inlineStr"/>
-      <c r="O26" s="13" t="inlineStr"/>
+      <c r="N26" s="13" t="n"/>
+      <c r="O26" s="13" t="n"/>
       <c r="P26" s="13" t="n"/>
       <c r="Q26" s="13" t="inlineStr">
         <is>
@@ -15979,21 +16627,21 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>1.79</v>
+        <v>1.62</v>
       </c>
       <c r="G27" s="13" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="H27" s="13" t="inlineStr"/>
-      <c r="I27" s="13" t="inlineStr"/>
-      <c r="J27" s="13" t="inlineStr"/>
-      <c r="K27" s="13" t="inlineStr"/>
-      <c r="L27" s="13" t="inlineStr"/>
+      <c r="H27" s="13" t="n"/>
+      <c r="I27" s="13" t="n"/>
+      <c r="J27" s="13" t="n"/>
+      <c r="K27" s="13" t="n"/>
+      <c r="L27" s="13" t="n"/>
       <c r="M27" s="13" t="n"/>
-      <c r="N27" s="13" t="inlineStr"/>
-      <c r="O27" s="13" t="inlineStr"/>
+      <c r="N27" s="13" t="n"/>
+      <c r="O27" s="13" t="n"/>
       <c r="P27" s="13" t="n"/>
       <c r="Q27" s="13" t="inlineStr">
         <is>
@@ -16029,25 +16677,25 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>1.79</v>
+        <v>1.62</v>
       </c>
       <c r="G28" s="13" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="H28" s="13" t="inlineStr"/>
-      <c r="I28" s="13" t="inlineStr"/>
-      <c r="J28" s="13" t="inlineStr"/>
-      <c r="K28" s="13" t="inlineStr"/>
+      <c r="H28" s="13" t="n"/>
+      <c r="I28" s="13" t="n"/>
+      <c r="J28" s="13" t="n"/>
+      <c r="K28" s="13" t="n"/>
       <c r="L28" s="13" t="inlineStr">
         <is>
           <t>weekend multipliers (Settings)</t>
         </is>
       </c>
       <c r="M28" s="13" t="n"/>
-      <c r="N28" s="13" t="inlineStr"/>
-      <c r="O28" s="13" t="inlineStr"/>
+      <c r="N28" s="13" t="n"/>
+      <c r="O28" s="13" t="n"/>
       <c r="P28" s="13" t="n"/>
       <c r="Q28" s="13" t="inlineStr">
         <is>
@@ -16083,7 +16731,7 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>1.79</v>
+        <v>1.62</v>
       </c>
       <c r="G29" s="13" t="inlineStr">
         <is>
@@ -16095,8 +16743,8 @@
           <t>From next week the game runs a week at a time.</t>
         </is>
       </c>
-      <c r="I29" s="13" t="inlineStr"/>
-      <c r="J29" s="13" t="inlineStr"/>
+      <c r="I29" s="13" t="n"/>
+      <c r="J29" s="13" t="n"/>
       <c r="K29" s="13" t="inlineStr">
         <is>
           <t>mechanics: weekly skips begin day 29</t>
@@ -17313,7 +17961,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17588,22 +18236,23 @@
           <t>live</t>
         </is>
       </c>
-      <c r="L4" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Analysts expect another small rise next week.</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
+      <c r="L4" s="13" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="M4" s="13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="N4" s="13" t="inlineStr">
+        <is>
+          <t>Tankers arriving early: prices expected to ease a little next week.</t>
+        </is>
+      </c>
+      <c r="O4" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P4" s="13" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="12" t="n">
@@ -17620,7 +18269,7 @@
         </is>
       </c>
       <c r="D5" s="12" t="n">
-        <v>1.79</v>
+        <v>1.62</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>1</v>
@@ -17639,28 +18288,29 @@
           <t>Clear</t>
         </is>
       </c>
-      <c r="J5" s="12" t="inlineStr"/>
+      <c r="J5" s="12" t="n"/>
       <c r="K5" s="12" t="inlineStr">
         <is>
           <t>live</t>
         </is>
       </c>
-      <c r="L5" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Steady rises continue.</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
+      <c r="L5" s="13" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="M5" s="13" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="N5" s="13" t="inlineStr">
+        <is>
+          <t>A quiet week; tankers arrived early. Prices expected to rise again as winter approaches.</t>
+        </is>
+      </c>
+      <c r="O5" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="P5" s="13" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="12" t="n">
@@ -17677,7 +18327,7 @@
         </is>
       </c>
       <c r="D6" s="12" t="n">
-        <v>1.86</v>
+        <v>1.74</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>1</v>
@@ -17696,28 +18346,29 @@
           <t>Storm over the Irish Sea</t>
         </is>
       </c>
-      <c r="J6" s="12" t="inlineStr"/>
+      <c r="J6" s="12" t="n"/>
       <c r="K6" s="12" t="inlineStr">
         <is>
           <t>live</t>
         </is>
       </c>
-      <c r="L6" t="n">
+      <c r="L6" s="13" t="n">
         <v>1.89</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6" s="13" t="n">
         <v>2.05</v>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N6" s="13" t="inlineStr">
         <is>
           <t>Little change expected.</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="O6" s="13" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="P6" s="13" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="12" t="n">
@@ -36813,7 +37464,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -38850,7 +39501,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -39311,7 +39962,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -39729,7 +40380,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -39958,7 +40609,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -40311,7 +40962,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -42830,7 +43481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D162"/>
+  <dimension ref="A1:D180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -44797,12 +45448,12 @@
       </c>
       <c r="B95" s="13" t="inlineStr">
         <is>
-          <t>selected route, else all routes</t>
+          <t>follows the selected flight's route; otherwise route tabs (each route · All)</t>
         </is>
       </c>
       <c r="C95" s="13" t="inlineStr">
         <is>
-          <t>D66: the demand-through-the-day strip shows the selected or hovered route's own five bands (Archetypes shares); with nothing selected, the sum across open routes.</t>
+          <t>D100: the strip header always names what it shows ('Madrid · people who want to fly at £170'); 'All' is a tab, never the silent default.</t>
         </is>
       </c>
       <c r="D95" s="13" t="inlineStr">
@@ -46200,6 +46851,398 @@
         </is>
       </c>
       <c r="D162" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="13" t="inlineStr">
+        <is>
+          <t>adaptToOnlyFlight</t>
+        </is>
+      </c>
+      <c r="B163" s="13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C163" s="13" t="inlineStr">
+        <is>
+          <t>D101: when time-locked passengers want a band with no service on their route, this share of them take the nearest service on that route instead. Fixes one-flight routes that could never fill (Marrakech: 76 → about 87 wanting the 06:00); timing still matters wherever a route has more than one service.</t>
+        </is>
+      </c>
+      <c r="D163" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="13" t="inlineStr">
+        <is>
+          <t>demandShapeDisplay</t>
+        </is>
+      </c>
+      <c r="B164" s="13" t="inlineStr">
+        <is>
+          <t>route demand by band, flexible shown separately; the selected flight's catchable slice highlighted</t>
+        </is>
+      </c>
+      <c r="C164" s="13" t="inlineStr">
+        <is>
+          <t>D101: the route card and the strip show demand as a shape across the day plus the 'any time' passengers, and when a flight is selected the part it can catch lights up (its band's locked passengers + the flexible ones not taken by earlier flights + the adapters).</t>
+        </is>
+      </c>
+      <c r="D164" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="13" t="inlineStr">
+        <is>
+          <t>flightTimeDecay</t>
+        </is>
+      </c>
+      <c r="B165" s="13" t="inlineStr">
+        <is>
+          <t>per kind of sum, whole game: Calculate twice, then Build, then Model</t>
+        </is>
+      </c>
+      <c r="C165" s="13" t="inlineStr">
+        <is>
+          <t>D101: flight-time sums count once for the whole game, not per aircraft and route; a plane already flying a route is never asked about it.</t>
+        </is>
+      </c>
+      <c r="D165" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="13" t="inlineStr">
+        <is>
+          <t>timeAnswerFormat</t>
+        </is>
+      </c>
+      <c r="B166" s="13" t="inlineStr">
+        <is>
+          <t>hours + minutes (selector 0, 15, 30, 45)</t>
+        </is>
+      </c>
+      <c r="C166" s="13" t="inlineStr">
+        <is>
+          <t>D101: no decimal hours in answers or questions; '225 km ÷ 900 km/h = ? h ? min'.</t>
+        </is>
+      </c>
+      <c r="D166" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="13" t="inlineStr">
+        <is>
+          <t>flightTimesTable</t>
+        </is>
+      </c>
+      <c r="B167" s="13" t="inlineStr">
+        <is>
+          <t>fixed-width columns; the active sum in the instrument below with its cell highlighted; a 'time saved' column between aircraft</t>
+        </is>
+      </c>
+      <c r="C167" s="13" t="inlineStr">
+        <is>
+          <t>D101: e.g. 'Twin Otter 1 h 30 → Saab 1 h: 30 min faster'.</t>
+        </is>
+      </c>
+      <c r="D167" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="13" t="inlineStr">
+        <is>
+          <t>weekPlanTutorial</t>
+        </is>
+      </c>
+      <c r="B168" s="13" t="inlineStr">
+        <is>
+          <t>removed</t>
+        </is>
+      </c>
+      <c r="C168" s="13" t="inlineStr">
+        <is>
+          <t>D101: the week-5 'Planning a whole week' tutorial goes; a one-line notice says the game now runs a week at a time.</t>
+        </is>
+      </c>
+      <c r="D168" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="13" t="inlineStr">
+        <is>
+          <t>redMeans</t>
+        </is>
+      </c>
+      <c r="B169" s="13" t="inlineStr">
+        <is>
+          <t>only genuinely bad or urgent: an invalid timetable, a plane that can't reach a route, a real loss, a disruption</t>
+        </is>
+      </c>
+      <c r="C169" s="13" t="inlineStr">
+        <is>
+          <t>D101 amends D95: unserved demand and forecast variance are information, never red.</t>
+        </is>
+      </c>
+      <c r="D169" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="13" t="inlineStr">
+        <is>
+          <t>opportunityDisplay</t>
+        </is>
+      </c>
+      <c r="B170" s="13" t="inlineStr">
+        <is>
+          <t>quiet type with an 'opportunity' label; gold only on the single biggest opportunity on a screen</t>
+        </is>
+      </c>
+      <c r="C170" s="13" t="inlineStr">
+        <is>
+          <t>D101: keeps gold rare (D95).</t>
+        </is>
+      </c>
+      <c r="D170" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="13" t="inlineStr">
+        <is>
+          <t>resultsFraming</t>
+        </is>
+      </c>
+      <c r="B171" s="13" t="inlineStr">
+        <is>
+          <t>lead with the result and the comparison with last week; variance with its reasons; 'passengers we couldn't carry' totalled once; cash change as profit − fuel bought</t>
+        </is>
+      </c>
+      <c r="C171" s="13" t="inlineStr">
+        <is>
+          <t>D101.</t>
+        </is>
+      </c>
+      <c r="D171" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="13" t="inlineStr">
+        <is>
+          <t>flightInspector</t>
+        </is>
+      </c>
+      <c r="B172" s="13" t="inlineStr">
+        <is>
+          <t>fixed bar under the timetable</t>
+        </is>
+      </c>
+      <c r="C172" s="13" t="inlineStr">
+        <is>
+          <t>D101: Earlier · Later · Route · Fare · Days · Aircraft · Remove; never moves; the focus rail marks the selected block.</t>
+        </is>
+      </c>
+      <c r="D172" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="13" t="inlineStr">
+        <is>
+          <t>activeRoutesCollapsible</t>
+        </is>
+      </c>
+      <c r="B173" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="C173" s="13" t="inlineStr">
+        <is>
+          <t>D101: collapses to one line ('7 routes · 9 flights a day · 98% filled · 2 need attention') with route chips; opens with a tap.</t>
+        </is>
+      </c>
+      <c r="D173" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="13" t="inlineStr">
+        <is>
+          <t>weekGraphDefault</t>
+        </is>
+      </c>
+      <c r="B174" s="13" t="inlineStr">
+        <is>
+          <t>weekly history (profit per week so far, projection as a faint marker); 'this week by day' as a tab</t>
+        </is>
+      </c>
+      <c r="C174" s="13" t="inlineStr">
+        <is>
+          <t>D101.</t>
+        </is>
+      </c>
+      <c r="D174" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="13" t="inlineStr">
+        <is>
+          <t>dailyColourLimit</t>
+        </is>
+      </c>
+      <c r="B175" s="13" t="inlineStr">
+        <is>
+          <t>at most two a week; never the same item twice in a row; no duplicate lines</t>
+        </is>
+      </c>
+      <c r="C175" s="13" t="inlineStr">
+        <is>
+          <t>D101: tightens the DailyColour rule after a week showed four and a repeat.</t>
+        </is>
+      </c>
+      <c r="D175" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="13" t="inlineStr">
+        <is>
+          <t>comingUp</t>
+        </is>
+      </c>
+      <c r="B176" s="13" t="inlineStr">
+        <is>
+          <t>Roadmap sheet</t>
+        </is>
+      </c>
+      <c r="C176" s="13" t="inlineStr">
+        <is>
+          <t>D101: a 'Coming up' strip on Home (NOW · NEXT · LATER) and one line at the end of each review about next week. Planner upgrades are never named in advance.</t>
+        </is>
+      </c>
+      <c r="D176" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="13" t="inlineStr">
+        <is>
+          <t>aircraftWorthCheck</t>
+        </is>
+      </c>
+      <c r="B177" s="13" t="inlineStr">
+        <is>
+          <t>inside the comparison, not a separate page</t>
+        </is>
+      </c>
+      <c r="C177" s="13" t="inlineStr">
+        <is>
+          <t>D101: choosing a plane on 'Which aircraft should we add?' opens its worth check in place: WHY (the routes leaving people behind, with numbers) · WORK IT OUT (one full flight at the route's current fare) · WHAT IT MEANS (full-flight money → extra profit a day → payback, revealed one by one after the answer, payback as a coin bar). No numbered steps, no 'recommended routes', no sum counter; Give me a hint.</t>
+        </is>
+      </c>
+      <c r="D177" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="13" t="inlineStr">
+        <is>
+          <t>teacherTestMode</t>
+        </is>
+      </c>
+      <c r="B178" s="13" t="inlineStr">
+        <is>
+          <t>teacher panel, behind the PIN; amber TEST MODE bar; Answer · Answer all · Auto-plan · Run week/month · Skip briefing · Jump to… · Show the answer · Event now</t>
+        </is>
+      </c>
+      <c r="C178" s="13" t="inlineStr">
+        <is>
+          <t>D102: for testing screens without playing every sum. Nothing in test mode reaches the record, milestones or sum numbering; test airlines saved separately and labelled TEST. Jump-to points along the Steady path: Launch Day, weeks 2, 3, 4, 5, 7, 9, December, January 2031, June 2031, chapter 3, chapter 4. Shortcuts Ctrl+Shift+T (tools), Ctrl+Shift+A (answer), Ctrl+Shift+R (run).</t>
+        </is>
+      </c>
+      <c r="D178" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="13" t="inlineStr">
+        <is>
+          <t>waitCostLine</t>
+        </is>
+      </c>
+      <c r="B179" s="13" t="inlineStr">
+        <is>
+          <t>idle days × day cost</t>
+        </is>
+      </c>
+      <c r="C179" s="13" t="inlineStr">
+        <is>
+          <t>D100: on Buy now or wait, per plane: 'Its best work starts {date} ({route}). Bought today, it costs £{dayCost} a day for {days} days first: £{total}', against its earnings meanwhile. A Build the first time.</t>
+        </is>
+      </c>
+      <c r="D179" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="13" t="inlineStr">
+        <is>
+          <t>aircraftCardMeasure</t>
+        </is>
+      </c>
+      <c r="B180" s="13" t="inlineStr">
+        <is>
+          <t>extra profit for the airline (incremental), one measure on the whole screen</t>
+        </is>
+      </c>
+      <c r="C180" s="13" t="inlineStr">
+        <is>
+          <t>D100: the cards, the waterfall, 'What the extra money buys' and 'Where could it fly?' all use the airline's extra profit against today's plan; the waterfall must add up line by line (show snacks if included); the route's current fare unless a card says otherwise; 'What you give up' written per plane from its own figures.</t>
+        </is>
+      </c>
+      <c r="D180" s="13" t="inlineStr">
         <is>
           <t>live</t>
         </is>
@@ -46817,7 +47860,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
         <is>
@@ -47393,7 +48435,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="17" t="inlineStr">
         <is>
@@ -47407,6 +48448,342 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="20" t="inlineStr">
+        <is>
+          <t>when</t>
+        </is>
+      </c>
+      <c r="B1" s="20" t="inlineStr">
+        <is>
+          <t>now / next / later line</t>
+        </is>
+      </c>
+      <c r="C1" s="20" t="inlineStr">
+        <is>
+          <t>shown from</t>
+        </is>
+      </c>
+      <c r="D1" s="20" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>Week 3</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>New routes: Amsterdam, Frankfurt, Geneva, Barcelona</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="inlineStr">
+        <is>
+          <t>day 8</t>
+        </is>
+      </c>
+      <c r="D2" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>Week 4</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>Medium haul: Madrid, and your first jets</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>day 15</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>Week 5</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Marrakech — and the game runs a week at a time</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>day 22</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Week 6</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Brussels, Berlin and Milan</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>day 29</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>Week 7</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Rome and Lisbon</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>day 36</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Week 9</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Bigger jets in the shop: the A220, A320 and 737</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>day 50</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>Week 9</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>Athens and Istanbul</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>day 50</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>December</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>A month at a time — and the chapter review</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>day 78</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>January 2031</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>Long haul: New York, Dubai, and the 787</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>day 85</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>January 2031</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Your star rating goes public; what sort of airline are you?</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>day 106</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>June 2031</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>Delhi: the first flight too far for one day</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>day 240</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>September 2031</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>Buying big planes outright; Tokyo and Cape Town</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>day 330</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>September 2032</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>The ultimate plane</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>day 700</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>D101: Home shows the current stage (NOW), the next item (NEXT) and one or two after it (LATER), each with a greyed silhouette until it arrives. Planner upgrades (Upgrades sheet) are never listed: the pupil discovers the need.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -47739,653 +49116,10 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="17" t="inlineStr">
         <is>
           <t>D98: the review shows dataShown, then asks the question with the three options as cards (the right one first in the sheet, shuffled on screen); from freeTextFrom the pupil writes the requirement in a sentence and picks the card it matches. Granting: a result plate 'Operations request · Planner upgrade approved: …'. Fallback: the systems team proposes it with the same card. The data never waits: the feature exists in the engine from day one and is simply switched on for the pupil.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
-    <col width="44" customWidth="1" min="6" max="6"/>
-    <col width="36" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="20" t="inlineStr">
-        <is>
-          <t>briefingId</t>
-        </is>
-      </c>
-      <c r="B1" s="20" t="inlineStr">
-        <is>
-          <t>trigger</t>
-        </is>
-      </c>
-      <c r="C1" s="20" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="D1" s="20" t="inlineStr">
-        <is>
-          <t>beat1 (show)</t>
-        </is>
-      </c>
-      <c r="E1" s="20" t="inlineStr">
-        <is>
-          <t>beat2 (predict: the pupil does…)</t>
-        </is>
-      </c>
-      <c r="F1" s="20" t="inlineStr">
-        <is>
-          <t>beat3 (reveal)</t>
-        </is>
-      </c>
-      <c r="G1" s="20" t="inlineStr">
-        <is>
-          <t>beat4 (use)</t>
-        </is>
-      </c>
-      <c r="H1" s="20" t="inlineStr">
-        <is>
-          <t>leadsInto</t>
-        </is>
-      </c>
-      <c r="I1" s="20" t="inlineStr">
-        <is>
-          <t>seconds</t>
-        </is>
-      </c>
-      <c r="J1" s="20" t="inlineStr">
-        <is>
-          <t>html</t>
-        </is>
-      </c>
-      <c r="K1" s="20" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="13" t="inlineStr">
-        <is>
-          <t>fare_lever</t>
-        </is>
-      </c>
-      <c r="B2" s="13" t="inlineStr">
-        <is>
-          <t>Launch Day, the fare chips</t>
-        </is>
-      </c>
-      <c r="C2" s="13" t="inlineStr">
-        <is>
-          <t>What a fare does</t>
-        </is>
-      </c>
-      <c r="D2" s="13" t="inlineStr">
-        <is>
-          <t>Nineteen passenger dots and a £ meter. The fare slides from £80 to £90 to £100; the meter per passenger rises as dots fade.</t>
-        </is>
-      </c>
-      <c r="E2" s="13" t="inlineStr">
-        <is>
-          <t>Drag the fare yourself; predict: more or fewer dots at £100?</t>
-        </is>
-      </c>
-      <c r="F2" s="13" t="inlineStr">
-        <is>
-          <t>Revenue = passengers × fare: both move. At £100 Paris wants 44, not 50 — two planes still fill.</t>
-        </is>
-      </c>
-      <c r="G2" s="13" t="inlineStr">
-        <is>
-          <t>Back to the chips with the three revenue figures</t>
-        </is>
-      </c>
-      <c r="H2" s="13" t="inlineStr">
-        <is>
-          <t>Launch Day sum 1</t>
-        </is>
-      </c>
-      <c r="I2" s="13" t="n">
-        <v>35</v>
-      </c>
-      <c r="J2" s="13" t="inlineStr">
-        <is>
-          <t>briefing-fare.html</t>
-        </is>
-      </c>
-      <c r="K2" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="13" t="inlineStr">
-        <is>
-          <t>rival_split</t>
-        </is>
-      </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>Thu, week 1 (Red Kite)</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>Customers have a choice</t>
-        </is>
-      </c>
-      <c r="D3" s="13" t="inlineStr">
-        <is>
-          <t>62 Dublin dots; a red-kite plane lands beside yours; its price tag reads £50.</t>
-        </is>
-      </c>
-      <c r="E3" s="13" t="inlineStr">
-        <is>
-          <t>Slide your fare; watch dots cross to Red Kite: 1 in 10 per £10.</t>
-        </is>
-      </c>
-      <c r="F3" s="13" t="inlineStr">
-        <is>
-          <t>The switching rule in one line; advertising halves it.</t>
-        </is>
-      </c>
-      <c r="G3" s="13" t="inlineStr">
-        <is>
-          <t>The Red Kite decision with the sum on it</t>
-        </is>
-      </c>
-      <c r="H3" s="13" t="inlineStr">
-        <is>
-          <t>Red Kite card</t>
-        </is>
-      </c>
-      <c r="I3" s="13" t="n">
-        <v>40</v>
-      </c>
-      <c r="J3" s="13" t="inlineStr">
-        <is>
-          <t>briefing-rival.html</t>
-        </is>
-      </c>
-      <c r="K3" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>full_route</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>Week-1 review</t>
-        </is>
-      </c>
-      <c r="C4" s="13" t="inlineStr">
-        <is>
-          <t>More demand than seats</t>
-        </is>
-      </c>
-      <c r="D4" s="13" t="inlineStr">
-        <is>
-          <t>Passenger dots arrive at the terminal; 57 board three Twin Otters; the rest stay on the apron.</t>
-        </is>
-      </c>
-      <c r="E4" s="13" t="inlineStr">
-        <is>
-          <t>Click the dots left behind; how many?</t>
-        </is>
-      </c>
-      <c r="F4" s="13" t="inlineStr">
-        <is>
-          <t>High demand is not profit if you cannot carry people: a bigger plane, another plane, or a higher fare.</t>
-        </is>
-      </c>
-      <c r="G4" s="13" t="inlineStr">
-        <is>
-          <t>The capacity observation and Compare aircraft</t>
-        </is>
-      </c>
-      <c r="H4" s="13" t="inlineStr">
-        <is>
-          <t>Week-2 decision</t>
-        </is>
-      </c>
-      <c r="I4" s="13" t="n">
-        <v>35</v>
-      </c>
-      <c r="J4" s="13" t="inlineStr">
-        <is>
-          <t>briefing-capacity.html</t>
-        </is>
-      </c>
-      <c r="K4" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>weekend_demand</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Week-2 review</t>
-        </is>
-      </c>
-      <c r="C5" s="13" t="inlineStr">
-        <is>
-          <t>Weekdays and weekends</t>
-        </is>
-      </c>
-      <c r="D5" s="13" t="inlineStr">
-        <is>
-          <t>Mon–Sun bars grow for Dublin; business icons fill weekdays, families the weekend.</t>
-        </is>
-      </c>
-      <c r="E5" s="13" t="inlineStr">
-        <is>
-          <t>Click the days that look different.</t>
-        </is>
-      </c>
-      <c r="F5" s="13" t="inlineStr">
-        <is>
-          <t>Why: business travel builds on weekdays; leisure swells at the weekend. Your timetable appears underneath — the same every day.</t>
-        </is>
-      </c>
-      <c r="G5" s="13" t="inlineStr">
-        <is>
-          <t>Does the planner fit what the passengers do? → the Upgrades question</t>
-        </is>
-      </c>
-      <c r="H5" s="13" t="inlineStr">
-        <is>
-          <t>weekend_schedules upgrade</t>
-        </is>
-      </c>
-      <c r="I5" s="13" t="n">
-        <v>45</v>
-      </c>
-      <c r="J5" s="13" t="inlineStr">
-        <is>
-          <t>briefing-weekend.html</t>
-        </is>
-      </c>
-      <c r="K5" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>fuel_cash_tank_profit</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>First Fuel desk visit (day 8)</t>
-        </is>
-      </c>
-      <c r="C6" s="13" t="inlineStr">
-        <is>
-          <t>Cash, tank, profit</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>Three gauges: cash £12,409, tank 0 L, profit today. Press Buy 7,000 L: cash flows into the tank; profit does not move.</t>
-        </is>
-      </c>
-      <c r="E6" s="13" t="inlineStr">
-        <is>
-          <t>Press Buy yourself; then: what changed? (tap the gauge)</t>
-        </is>
-      </c>
-      <c r="F6" s="13" t="inlineStr">
-        <is>
-          <t>A Twin Otter departs for Paris: 120 L drains, £176 flows into today's costs. Buying fuel and using fuel are different events.</t>
-        </is>
-      </c>
-      <c r="G6" s="13" t="inlineStr">
-        <is>
-          <t>The Fuel desk with the order instrument</t>
-        </is>
-      </c>
-      <c r="H6" s="13" t="inlineStr">
-        <is>
-          <t>Fuel order sum</t>
-        </is>
-      </c>
-      <c r="I6" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="J6" s="13" t="inlineStr">
-        <is>
-          <t>briefing-fuel.html</t>
-        </is>
-      </c>
-      <c r="K6" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>aircraft_efficiency</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>Week-2 shop, first comparison</t>
-        </is>
-      </c>
-      <c r="C7" s="13" t="inlineStr">
-        <is>
-          <t>Two planes, one route</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>A Twin Otter and a Saab fly Dublin side by side; both gauges drain; a seat-row per plane.</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
-        <is>
-          <t>Which burned more per seat? Tap it.</t>
-        </is>
-      </c>
-      <c r="F7" s="13" t="inlineStr">
-        <is>
-          <t>Litres per seat: the Saab 6.6, the Twin Otter 9.5 — bigger can be cheaper a seat, if it fills.</t>
-        </is>
-      </c>
-      <c r="G7" s="13" t="inlineStr">
-        <is>
-          <t>The comparison with the litres-per-seat widget</t>
-        </is>
-      </c>
-      <c r="H7" s="13" t="inlineStr">
-        <is>
-          <t>Second-plane decision</t>
-        </is>
-      </c>
-      <c r="I7" s="13" t="n">
-        <v>35</v>
-      </c>
-      <c r="J7" s="13" t="inlineStr">
-        <is>
-          <t>briefing-efficiency.html</t>
-        </is>
-      </c>
-      <c r="K7" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>event_weekend</t>
-        </is>
-      </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>Announced event (day 22: the All Blacks)</t>
-        </is>
-      </c>
-      <c r="C8" s="13" t="inlineStr">
-        <is>
-          <t>One big Saturday</t>
-        </is>
-      </c>
-      <c r="D8" s="13" t="inlineStr">
-        <is>
-          <t>A normal Saturday: 62 Dublin dots. An event card slides onto the date; dots stream in to 124. Your two flights stay where they are.</t>
-        </is>
-      </c>
-      <c r="E8" s="13" t="inlineStr">
-        <is>
-          <t>What changed? Tap the day.</t>
-        </is>
-      </c>
-      <c r="F8" s="13" t="inlineStr">
-        <is>
-          <t>Events change a market for a day; a weekend plan changes every Saturday.</t>
-        </is>
-      </c>
-      <c r="G8" s="13" t="inlineStr">
-        <is>
-          <t>Can the planner respond to one date? → Upgrades question</t>
-        </is>
-      </c>
-      <c r="H8" s="13" t="inlineStr">
-        <is>
-          <t>day_override upgrade</t>
-        </is>
-      </c>
-      <c r="I8" s="13" t="n">
-        <v>40</v>
-      </c>
-      <c r="J8" s="13" t="inlineStr">
-        <is>
-          <t>briefing-event.html</t>
-        </is>
-      </c>
-      <c r="K8" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>seasons</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>Chapter-1 review</t>
-        </is>
-      </c>
-      <c r="C9" s="13" t="inlineStr">
-        <is>
-          <t>A year of demand</t>
-        </is>
-      </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>Twelve months; Geneva's bar grows in winter, Barcelona's in summer; Christmas and half-term markers.</t>
-        </is>
-      </c>
-      <c r="E9" s="13" t="inlineStr">
-        <is>
-          <t>Drag a plane icon to the month you'd fly Geneva.</t>
-        </is>
-      </c>
-      <c r="F9" s="13" t="inlineStr">
-        <is>
-          <t>Markets change through the year for different reasons; a weekly plan does not.</t>
-        </is>
-      </c>
-      <c r="G9" s="13" t="inlineStr">
-        <is>
-          <t>The Upgrades question (seasonal plans)</t>
-        </is>
-      </c>
-      <c r="H9" s="13" t="inlineStr">
-        <is>
-          <t>seasonal_plans upgrade</t>
-        </is>
-      </c>
-      <c r="I9" s="13" t="n">
-        <v>45</v>
-      </c>
-      <c r="J9" s="13" t="inlineStr">
-        <is>
-          <t>briefing-seasons.html</t>
-        </is>
-      </c>
-      <c r="K9" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>lease_money</t>
-        </is>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>6 Jan 2031, the 787 to lease</t>
-        </is>
-      </c>
-      <c r="C10" s="13" t="inlineStr">
-        <is>
-          <t>Renting a plane</t>
-        </is>
-      </c>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>A 787; the price £12m against cash £1.5m; a rent meter ticks £6,000 a day.</t>
-        </is>
-      </c>
-      <c r="E10" s="13" t="inlineStr">
-        <is>
-          <t>Slide the days: when does rent pass the price?</t>
-        </is>
-      </c>
-      <c r="F10" s="13" t="inlineStr">
-        <is>
-          <t>Rent-or-buy: 12,000,000 ÷ 6,000 = 2,000 days. Rent keeps cash; buying keeps the plane.</t>
-        </is>
-      </c>
-      <c r="G10" s="13" t="inlineStr">
-        <is>
-          <t>The shop with Rent and (greyed) Buy</t>
-        </is>
-      </c>
-      <c r="H10" s="13" t="inlineStr">
-        <is>
-          <t>Rent-or-buy sum</t>
-        </is>
-      </c>
-      <c r="I10" s="13" t="n">
-        <v>40</v>
-      </c>
-      <c r="J10" s="13" t="inlineStr">
-        <is>
-          <t>briefing-lease.html</t>
-        </is>
-      </c>
-      <c r="K10" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t>profit_vs_cash</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>Chapter 3, first overdrawn month or the 787 purchase</t>
-        </is>
-      </c>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>Profit is not cash</t>
-        </is>
-      </c>
-      <c r="D11" s="13" t="inlineStr">
-        <is>
-          <t>The month's profit bar rises while the cash gauge falls: the money went into a plane and a full tank.</t>
-        </is>
-      </c>
-      <c r="E11" s="13" t="inlineStr">
-        <is>
-          <t>Tap where the money went.</t>
-        </is>
-      </c>
-      <c r="F11" s="13" t="inlineStr">
-        <is>
-          <t>Profit answers 'did we earn?'; cash answers 'can we pay?'. Both matter.</t>
-        </is>
-      </c>
-      <c r="G11" s="13" t="inlineStr">
-        <is>
-          <t>The Finance desk with the overdraft line</t>
-        </is>
-      </c>
-      <c r="H11" s="13" t="inlineStr">
-        <is>
-          <t>Overdraft / buying outright</t>
-        </is>
-      </c>
-      <c r="I11" s="13" t="n">
-        <v>40</v>
-      </c>
-      <c r="J11" s="13" t="inlineStr">
-        <is>
-          <t>briefing-cash.html</t>
-        </is>
-      </c>
-      <c r="K11" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="17" t="inlineStr">
-        <is>
-          <t>D99: Show → Predict → Reveal → Use. Full screen, the interface darkened behind; the pupil advances by the interaction in beat 2, never by Next; a Pause &amp; discuss button at each stop for the teacher; a Replay from the Briefings shelf. Each is built as a separate HTML piece in the game's style (see the flight-time tutorial) and the game loads it at its trigger.</t>
         </is>
       </c>
     </row>

--- a/data/Airline-World-Workbook.xlsx
+++ b/data/Airline-World-Workbook.xlsx
@@ -577,7 +577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A35"/>
+  <dimension ref="A1:A36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -825,6 +825,13 @@
       <c r="A35" t="inlineStr">
         <is>
           <t>Took from v5.17 (17 Oct 2026, Claude Code): D101 and D102 only (Screens brief 3) — the Roadmap sheet; Settings adaptToOnlyFlight, demandShapeDisplay, flightTimeDecay, timeAnswerFormat, flightTimesTable, weekPlanTutorial, redMeans, opportunityDisplay, resultsFraming, flightInspector, activeRoutesCollapsible, weekGraphDefault, dailyColourLimit, comingUp, aircraftWorthCheck, teacherTestMode, and from D100 the three rows D101 builds on (waitCostLine, aircraftCardMeasure, demandStripMode); the fuel dips: Market weeks 3–5 and Calendar days 22–28. The rest of v5.16–v5.17 (D100, the D92 market from week 6 on) is kept in data/incoming/.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>D103 (18 Oct 2026, Claude Code, from Claude Design's handover and Fable's Briefing 13 brief; rules confirmed by Bertie): Settings pupilReserve, bustRule and standingAim (cashReserve's note says what replaces it in year one); Briefings row cash_to_fly. The workbook has no Design Register sheet: the D103 entry itself is in Fable's register.</t>
         </is>
       </c>
     </row>
@@ -839,7 +846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1462,8 +1469,66 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>cash_to_fly</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>Week 2: the Fuel desk, after Cash, tank, profit and before the first order (or the shop, if he gets there first)</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>Can you afford to run it?</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>Seven stands, the fuel each day needs as drums; the planes at Monday; cash in a tall glass gauge.</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>Drag the red reserve line up the gauge: how much will you keep back? Buy says what fits above it.</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>Buy what you can, fly a day at a time, buy the rest with the tickets; run dry and the day costs 10p a litre more.</t>
+        </is>
+      </c>
+      <c r="G12" s="13" t="inlineStr">
+        <is>
+          <t>The twist (the shop's plane: a plane you can't fuel still costs you every day), then the rules card; back to the Fuel desk with the line kept</t>
+        </is>
+      </c>
+      <c r="H12" s="13" t="inlineStr">
+        <is>
+          <t>Fuel desk (pupilReserve)</t>
+        </is>
+      </c>
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J12" s="13" t="inlineStr">
+        <is>
+          <t>briefing-cash-to-fly.html</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>D99: Show → Predict → Reveal → Use. Full screen, the interface darkened behind; the pupil advances by the interaction in beat 2, never by Next; a Pause &amp; discuss button at each stop for the teacher; a Replay from the Briefings shelf. Each is built as a separate HTML piece in the game's style (see the flight-time tutorial) and the game loads it at its trigger.</t>
         </is>
@@ -43481,7 +43546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D180"/>
+  <dimension ref="A1:D183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -43911,7 +43976,7 @@
       </c>
       <c r="C21" s="13" t="inlineStr">
         <is>
-          <t>Before overdraftFromDate: block any plan or purchase whose projected cash falls below £1,000. From overdraftFromDate the overdraft limit replaces the reserve: the block applies at −overdraftLimit instead.</t>
+          <t>Before overdraftFromDate: block any plan or purchase whose projected cash falls below £1,000. From overdraftFromDate the overdraft limit replaces the reserve: the block applies at −overdraftLimit instead. Year one (D103): the pupil's own reserve (pupilReserve) replaces it.</t>
         </is>
       </c>
       <c r="D21" s="13" t="inlineStr">
@@ -47243,6 +47308,70 @@
         </is>
       </c>
       <c r="D180" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="13" t="inlineStr">
+        <is>
+          <t>pupilReserve</t>
+        </is>
+      </c>
+      <c r="B181" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C181" s="13" t="inlineStr">
+        <is>
+          <t>D103 (Bertie, 18 Oct 2026; Briefing 13, Can you afford to run it?): the reserve is the pupil's. In year one the fixed cashReserve (£1,000) goes: the pupil sets their own reserve line, starting at £0, first in Briefing 13, then on the Fuel desk and the Finance desk (± £500). The shop and the Fuel desk show 'above your reserve' figures from it; the Fuel desk buys with the cash above it. It never stops a plan on the Ready screen; the board nudges (once a week) only if nothing is kept back and the tank runs dry. Chapter 3's overdraft is unchanged.</t>
+        </is>
+      </c>
+      <c r="D181" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="13" t="inlineStr">
+        <is>
+          <t>bustRule</t>
+        </is>
+      </c>
+      <c r="B182" s="13" t="inlineStr">
+        <is>
+          <t>3 grounded days in a week</t>
+        </is>
+      </c>
+      <c r="C182" s="13" t="inlineStr">
+        <is>
+          <t>D103: going bust. If a day's fuel can't be paid (the tank is dry, cash can't buy it and the day's takings won't cover the emergency fuel), the planes are grounded for that day and the day's costs still run. Three grounded days in one week and the airline closes: a short closing screen, then the pupil starts again from Launch Day (not the start of the chapter), with the same name, code and colours. No loans, no rescue: in year one the bank's free top-up is gone. The overdraft in chapter 3 stays a safety net, not a loan.</t>
+        </is>
+      </c>
+      <c r="D182" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="13" t="inlineStr">
+        <is>
+          <t>standingAim</t>
+        </is>
+      </c>
+      <c r="B183" s="13" t="inlineStr">
+        <is>
+          <t>Make as much money as you can. | In January you'll choose what kind of airline you are. | Keep cash for emergencies: you decide how much. | Run out of cash and the airline closes. | You start again from Launch Day. No loans.</t>
+        </is>
+      </c>
+      <c r="C183" s="13" t="inlineStr">
+        <is>
+          <t>D103: the rules-of-the-game card (lines separated by |). It ends Briefing 13 and then stays on Home, under Coming up, until the airline-type choice in January, when it changes to that chapter's aim.</t>
+        </is>
+      </c>
+      <c r="D183" s="13" t="inlineStr">
         <is>
           <t>live</t>
         </is>
@@ -48770,7 +48899,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
         <is>

--- a/data/Airline-World-Workbook.xlsx
+++ b/data/Airline-World-Workbook.xlsx
@@ -17,24 +17,25 @@
     <sheet name="Roadmap" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Upgrades" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Briefings" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="RouteNews" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Archetypes" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="EventOptions" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Milestones" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Campaign" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Routes" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="RouteCatalogue" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Aircraft" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Finance" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Airports" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Calendar" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Market" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Events" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Challenges" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Mechanics" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="Catering" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="Hunts" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="Livery" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="BriefingData" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="RouteNews" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Archetypes" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="EventOptions" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Milestones" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Campaign" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Routes" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="RouteCatalogue" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Aircraft" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Finance" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Airports" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Calendar" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Market" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Events" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Challenges" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="Mechanics" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="Catering" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="Hunts" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="Livery" sheetId="29" state="visible" r:id="rId29"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -44,7 +45,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -78,6 +79,9 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="8">
@@ -144,7 +148,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -212,6 +216,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -577,7 +582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A36"/>
+  <dimension ref="A1:A37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -832,6 +837,13 @@
       <c r="A36" t="inlineStr">
         <is>
           <t>D103 (18 Oct 2026, Claude Code, from Claude Design's handover and Fable's Briefing 13 brief; rules confirmed by Bertie): Settings pupilReserve, bustRule and standingAim (cashReserve's note says what replaces it in year one); Briefings row cash_to_fly. The workbook has no Design Register sheet: the D103 entry itself is in Fable's register.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>D104 (19 Oct 2026, Claude Code, from Claude Design's handover of 19 Oct; chosen by Bertie): What a fare does is rebuilt in seven beats (tickets make money, the fare slider, seats run out, the challenge, £100 full or £110 with one empty seat, the sheet works it out, back to his fares). Its numbers are a fixed teaching example on the new BriefingData sheet, not live route data. Briefings fare_lever beats updated.</t>
         </is>
       </c>
     </row>
@@ -937,22 +949,22 @@
       </c>
       <c r="D2" s="13" t="inlineStr">
         <is>
-          <t>Nineteen passenger dots and a £ meter. The fare slides from £80 to £90 to £100; the meter per passenger rises as dots fade.</t>
+          <t>Rebuilt 19 Oct (D104), seven beats. Show: tickets make money (Sell a ticket, the coin into Ticket money · revenue); the fare slider against the crowd in rows of ten; seats run out (two seat plans, 38 fly, 42 can't); the challenge (fill the seats and make the most money).</t>
         </is>
       </c>
       <c r="E2" s="13" t="inlineStr">
         <is>
-          <t>Drag the fare yourself; predict: more or fewer dots at £100?</t>
+          <t>Notice: which plane makes more ticket money, £100 with 19 of 19 seats or £110 with 18 of 19? His guess, never marked.</t>
         </is>
       </c>
       <c r="F2" s="13" t="inlineStr">
         <is>
-          <t>Revenue = passengers × fare: both move. At £100 Paris wants 44, not 50 — two planes still fill.</t>
+          <t>Reveal: the figures sheet (Work it out page rules) works it out row by row: 19 × £100 = £1,900; 18 × £110 = £1,980; £80 more. He types nothing.</t>
         </is>
       </c>
       <c r="G2" s="13" t="inlineStr">
         <is>
-          <t>Back to the chips with the three revenue figures</t>
+          <t>Use: four recap tiles; "Now set your fares." Set my fares ▶ returns to the fare stepper in his plan.</t>
         </is>
       </c>
       <c r="H2" s="13" t="inlineStr">
@@ -961,7 +973,7 @@
         </is>
       </c>
       <c r="I2" s="13" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="J2" s="13" t="inlineStr">
         <is>
@@ -1540,6 +1552,250 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="90" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="25" t="inlineStr">
+        <is>
+          <t>briefingId</t>
+        </is>
+      </c>
+      <c r="B1" s="25" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="C1" s="25" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="D1" s="25" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>fare_lever</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>route</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>The route named on the gate sign and the fare slider. A fixed teaching example, not live route data (D104).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>fare_lever</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>plane</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Twin Otter</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>fare_lever</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>seatsPerPlane</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>19</v>
+      </c>
+      <c r="D4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>fare_lever</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>planes</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Two planes: 38 seats.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>fare_lever</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>fares</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>60|70|80|90|100|110|120|130|140</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>£60 to £140 in £10 steps.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>fare_lever</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>wantToFly</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>100|80|64|50|40|36|30|24|18</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>People wanting to fly at each fare, in the order of fares.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>fare_lever</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>sellFare</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>100</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Beat 1: the fare on the gate sign.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>fare_lever</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>startFare</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>100</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Beat 2: where the slider starts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>fare_lever</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>seatsRunOutFare</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>70</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Beat 3: 80 want, 38 fly, 42 can't. Also beat 4's low fare; the high fare is the last fare.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>fare_lever</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>compareFares</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>100|110</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Beats 5 and 6: £100 with 19 of 19 against £110 with 18 of 19 (£1,900 against £1,980, £80 more).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5754,7 +6010,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6342,7 +6598,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7825,7 +8081,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8460,7 +8716,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8722,7 +8978,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11151,7 +11407,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12417,7 +12673,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13452,880 +13708,6 @@
       <c r="A20" s="17" t="inlineStr">
         <is>
           <t>Prices from the A220 up are tuned to the cash curve (F5, replacing D16's three-tenths rule): on the Steady path each plane is a few lessons of saving away when it is meant to arrive. Tutorial planes (Twin Otter to E190, E175) keep launch-deal prices. Real prices are on the plane card for interest only.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="60" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="21" t="inlineStr">
-        <is>
-          <t>aircraftId</t>
-        </is>
-      </c>
-      <c r="B1" s="21" t="inlineStr">
-        <is>
-          <t>cashPrice</t>
-        </is>
-      </c>
-      <c r="C1" s="21" t="inlineStr">
-        <is>
-          <t>leaseDaily</t>
-        </is>
-      </c>
-      <c r="D1" s="21" t="inlineStr">
-        <is>
-          <t>financeDeposit</t>
-        </is>
-      </c>
-      <c r="E1" s="21" t="inlineStr">
-        <is>
-          <t>monthlyPayment</t>
-        </is>
-      </c>
-      <c r="F1" s="21" t="inlineStr">
-        <is>
-          <t>months</t>
-        </is>
-      </c>
-      <c r="G1" s="21" t="inlineStr">
-        <is>
-          <t>financeTotalPaid</t>
-        </is>
-      </c>
-      <c r="H1" s="21" t="inlineStr">
-        <is>
-          <t>leaseFrom</t>
-        </is>
-      </c>
-      <c r="I1" s="21" t="inlineStr">
-        <is>
-          <t>buyFrom</t>
-        </is>
-      </c>
-      <c r="J1" s="21" t="inlineStr">
-        <is>
-          <t>financeFrom</t>
-        </is>
-      </c>
-      <c r="K1" s="21" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="L1" s="21" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="13" t="inlineStr">
-        <is>
-          <t>dhc6</t>
-        </is>
-      </c>
-      <c r="B2" s="13" t="n">
-        <v>10000</v>
-      </c>
-      <c r="C2" s="13" t="n">
-        <v>250</v>
-      </c>
-      <c r="D2" s="13" t="n">
-        <v>4000</v>
-      </c>
-      <c r="E2" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="F2" s="13" t="n">
-        <v>30</v>
-      </c>
-      <c r="G2" s="13" t="n">
-        <v>13000</v>
-      </c>
-      <c r="H2" s="13" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="I2" s="13" t="inlineStr">
-        <is>
-          <t>day 8</t>
-        </is>
-      </c>
-      <c r="J2" s="13" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="K2" s="13" t="inlineStr">
-        <is>
-          <t>Chapter 1 is buy only (D76). Week-2 sum: (price − cash) ÷ profit a day = days to wait.</t>
-        </is>
-      </c>
-      <c r="L2" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="13" t="inlineStr">
-        <is>
-          <t>saab340</t>
-        </is>
-      </c>
-      <c r="B3" s="13" t="n">
-        <v>22000</v>
-      </c>
-      <c r="C3" s="13" t="n">
-        <v>400</v>
-      </c>
-      <c r="D3" s="13" t="n">
-        <v>7000</v>
-      </c>
-      <c r="E3" s="13" t="n">
-        <v>500</v>
-      </c>
-      <c r="F3" s="13" t="n">
-        <v>32</v>
-      </c>
-      <c r="G3" s="13" t="n">
-        <v>23000</v>
-      </c>
-      <c r="H3" s="13" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="I3" s="13" t="inlineStr">
-        <is>
-          <t>day 8</t>
-        </is>
-      </c>
-      <c r="J3" s="13" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="K3" s="13" t="inlineStr">
-        <is>
-          <t>Chapter 1 is buy only (D76). Week-2 sum: (price − cash) ÷ profit a day = days to wait.</t>
-        </is>
-      </c>
-      <c r="L3" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>atr72</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="n">
-        <v>36000</v>
-      </c>
-      <c r="C4" s="13" t="n">
-        <v>650</v>
-      </c>
-      <c r="D4" s="13" t="n">
-        <v>11000</v>
-      </c>
-      <c r="E4" s="13" t="n">
-        <v>800</v>
-      </c>
-      <c r="F4" s="13" t="n">
-        <v>35</v>
-      </c>
-      <c r="G4" s="13" t="n">
-        <v>39000</v>
-      </c>
-      <c r="H4" s="13" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="I4" s="13" t="inlineStr">
-        <is>
-          <t>day 8</t>
-        </is>
-      </c>
-      <c r="J4" s="13" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="K4" s="13" t="inlineStr">
-        <is>
-          <t>Chapter 1 is buy only (D76). Week-2 sum: (price − cash) ÷ profit a day = days to wait.</t>
-        </is>
-      </c>
-      <c r="L4" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>e175</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="n">
-        <v>50000</v>
-      </c>
-      <c r="C5" s="13" t="n">
-        <v>900</v>
-      </c>
-      <c r="D5" s="13" t="n">
-        <v>15000</v>
-      </c>
-      <c r="E5" s="13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F5" s="13" t="n">
-        <v>38</v>
-      </c>
-      <c r="G5" s="13" t="n">
-        <v>53000</v>
-      </c>
-      <c r="H5" s="13" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="I5" s="13" t="inlineStr">
-        <is>
-          <t>day 22</t>
-        </is>
-      </c>
-      <c r="J5" s="13" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="K5" s="13" t="inlineStr">
-        <is>
-          <t>Chapter 1 is buy only (D76). Week-2 sum: (price − cash) ÷ profit a day = days to wait.</t>
-        </is>
-      </c>
-      <c r="L5" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>e190</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="n">
-        <v>70000</v>
-      </c>
-      <c r="C6" s="13" t="n">
-        <v>1200</v>
-      </c>
-      <c r="D6" s="13" t="n">
-        <v>21000</v>
-      </c>
-      <c r="E6" s="13" t="n">
-        <v>1500</v>
-      </c>
-      <c r="F6" s="13" t="n">
-        <v>36</v>
-      </c>
-      <c r="G6" s="13" t="n">
-        <v>75000</v>
-      </c>
-      <c r="H6" s="13" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="I6" s="13" t="inlineStr">
-        <is>
-          <t>day 22</t>
-        </is>
-      </c>
-      <c r="J6" s="13" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="K6" s="13" t="inlineStr">
-        <is>
-          <t>Chapter 1 is buy only (D76). Week-2 sum: (price − cash) ÷ profit a day = days to wait.</t>
-        </is>
-      </c>
-      <c r="L6" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>a220</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="n">
-        <v>300000</v>
-      </c>
-      <c r="C7" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="D7" s="13" t="n">
-        <v>90000</v>
-      </c>
-      <c r="E7" s="13" t="n">
-        <v>4000</v>
-      </c>
-      <c r="F7" s="13" t="n">
-        <v>52</v>
-      </c>
-      <c r="G7" s="13" t="n">
-        <v>298000</v>
-      </c>
-      <c r="H7" s="13" t="inlineStr">
-        <is>
-          <t>2031-01-06</t>
-        </is>
-      </c>
-      <c r="I7" s="13" t="inlineStr">
-        <is>
-          <t>2031-09-02</t>
-        </is>
-      </c>
-      <c r="J7" s="13" t="inlineStr">
-        <is>
-          <t>2032-09-07</t>
-        </is>
-      </c>
-      <c r="K7" s="13" t="inlineStr">
-        <is>
-          <t>Rent = price ÷ 1,000. Finance = 30% deposit, balance over 52 weeks, rounded to £1,000.</t>
-        </is>
-      </c>
-      <c r="L7" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>a320</t>
-        </is>
-      </c>
-      <c r="B8" s="13" t="n">
-        <v>400000</v>
-      </c>
-      <c r="C8" s="13" t="n">
-        <v>400</v>
-      </c>
-      <c r="D8" s="13" t="n">
-        <v>120000</v>
-      </c>
-      <c r="E8" s="13" t="n">
-        <v>5000</v>
-      </c>
-      <c r="F8" s="13" t="n">
-        <v>52</v>
-      </c>
-      <c r="G8" s="13" t="n">
-        <v>380000</v>
-      </c>
-      <c r="H8" s="13" t="inlineStr">
-        <is>
-          <t>2031-01-06</t>
-        </is>
-      </c>
-      <c r="I8" s="13" t="inlineStr">
-        <is>
-          <t>2031-09-02</t>
-        </is>
-      </c>
-      <c r="J8" s="13" t="inlineStr">
-        <is>
-          <t>2032-09-07</t>
-        </is>
-      </c>
-      <c r="K8" s="13" t="inlineStr"/>
-      <c r="L8" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>b737</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="n">
-        <v>400000</v>
-      </c>
-      <c r="C9" s="13" t="n">
-        <v>400</v>
-      </c>
-      <c r="D9" s="13" t="n">
-        <v>120000</v>
-      </c>
-      <c r="E9" s="13" t="n">
-        <v>5000</v>
-      </c>
-      <c r="F9" s="13" t="n">
-        <v>52</v>
-      </c>
-      <c r="G9" s="13" t="n">
-        <v>380000</v>
-      </c>
-      <c r="H9" s="13" t="inlineStr">
-        <is>
-          <t>2031-01-06</t>
-        </is>
-      </c>
-      <c r="I9" s="13" t="inlineStr">
-        <is>
-          <t>2031-09-02</t>
-        </is>
-      </c>
-      <c r="J9" s="13" t="inlineStr">
-        <is>
-          <t>2032-09-07</t>
-        </is>
-      </c>
-      <c r="K9" s="13" t="inlineStr"/>
-      <c r="L9" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>b757</t>
-        </is>
-      </c>
-      <c r="B10" s="13" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="C10" s="13" t="n">
-        <v>1500</v>
-      </c>
-      <c r="D10" s="13" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="E10" s="13" t="n">
-        <v>50000</v>
-      </c>
-      <c r="F10" s="13" t="n">
-        <v>40</v>
-      </c>
-      <c r="G10" s="13" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="H10" s="13" t="inlineStr">
-        <is>
-          <t>2031-01-06</t>
-        </is>
-      </c>
-      <c r="I10" s="13" t="inlineStr">
-        <is>
-          <t>2031-09-01</t>
-        </is>
-      </c>
-      <c r="J10" s="13" t="inlineStr">
-        <is>
-          <t>2032-09-06</t>
-        </is>
-      </c>
-      <c r="K10" s="13" t="inlineStr">
-        <is>
-          <t>Leased in January 2031 at £1,500 a day (price ÷ 1,000). Buy from chapter 3.</t>
-        </is>
-      </c>
-      <c r="L10" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t>b787</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="n">
-        <v>12000000</v>
-      </c>
-      <c r="C11" s="13" t="n">
-        <v>6000</v>
-      </c>
-      <c r="D11" s="13" t="n">
-        <v>4000000</v>
-      </c>
-      <c r="E11" s="13" t="n">
-        <v>200000</v>
-      </c>
-      <c r="F11" s="13" t="n">
-        <v>40</v>
-      </c>
-      <c r="G11" s="13" t="n">
-        <v>12000000</v>
-      </c>
-      <c r="H11" s="13" t="inlineStr">
-        <is>
-          <t>2031-01-06</t>
-        </is>
-      </c>
-      <c r="I11" s="13" t="inlineStr">
-        <is>
-          <t>2031-09-01</t>
-        </is>
-      </c>
-      <c r="J11" s="13" t="inlineStr">
-        <is>
-          <t>2032-09-06</t>
-        </is>
-      </c>
-      <c r="K11" s="13" t="inlineStr">
-        <is>
-          <t>Leased from January 2031 at £6,000 a day; bought outright from chapter 3. 12,000,000 ÷ 6,000 = 2,000 days.</t>
-        </is>
-      </c>
-      <c r="L11" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>a340</t>
-        </is>
-      </c>
-      <c r="B12" s="13" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="C12" s="13" t="n">
-        <v>5000</v>
-      </c>
-      <c r="D12" s="13" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="E12" s="13" t="n">
-        <v>200000</v>
-      </c>
-      <c r="F12" s="13" t="n">
-        <v>40</v>
-      </c>
-      <c r="G12" s="13" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="H12" s="13" t="inlineStr">
-        <is>
-          <t>2031-09-02</t>
-        </is>
-      </c>
-      <c r="I12" s="13" t="inlineStr">
-        <is>
-          <t>2031-09-01</t>
-        </is>
-      </c>
-      <c r="J12" s="13" t="inlineStr">
-        <is>
-          <t>2032-09-06</t>
-        </is>
-      </c>
-      <c r="K12" s="13" t="inlineStr"/>
-      <c r="L12" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>b777</t>
-        </is>
-      </c>
-      <c r="B13" s="13" t="n">
-        <v>24000000</v>
-      </c>
-      <c r="C13" s="13" t="n">
-        <v>12000</v>
-      </c>
-      <c r="D13" s="13" t="n">
-        <v>8000000</v>
-      </c>
-      <c r="E13" s="13" t="n">
-        <v>400000</v>
-      </c>
-      <c r="F13" s="13" t="n">
-        <v>40</v>
-      </c>
-      <c r="G13" s="13" t="n">
-        <v>24000000</v>
-      </c>
-      <c r="H13" s="13" t="inlineStr">
-        <is>
-          <t>2031-09-02</t>
-        </is>
-      </c>
-      <c r="I13" s="13" t="inlineStr">
-        <is>
-          <t>2031-09-01</t>
-        </is>
-      </c>
-      <c r="J13" s="13" t="inlineStr">
-        <is>
-          <t>2032-09-06</t>
-        </is>
-      </c>
-      <c r="K13" s="13" t="inlineStr"/>
-      <c r="L13" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t>a350</t>
-        </is>
-      </c>
-      <c r="B14" s="13" t="n">
-        <v>30000000</v>
-      </c>
-      <c r="C14" s="13" t="n">
-        <v>15000</v>
-      </c>
-      <c r="D14" s="13" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="E14" s="13" t="n">
-        <v>500000</v>
-      </c>
-      <c r="F14" s="13" t="n">
-        <v>40</v>
-      </c>
-      <c r="G14" s="13" t="n">
-        <v>30000000</v>
-      </c>
-      <c r="H14" s="13" t="inlineStr">
-        <is>
-          <t>2031-09-02</t>
-        </is>
-      </c>
-      <c r="I14" s="13" t="inlineStr">
-        <is>
-          <t>2031-09-01</t>
-        </is>
-      </c>
-      <c r="J14" s="13" t="inlineStr">
-        <is>
-          <t>2032-09-06</t>
-        </is>
-      </c>
-      <c r="K14" s="13" t="inlineStr"/>
-      <c r="L14" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="13" t="inlineStr">
-        <is>
-          <t>b747</t>
-        </is>
-      </c>
-      <c r="B15" s="13" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="C15" s="13" t="n">
-        <v>20000</v>
-      </c>
-      <c r="D15" s="13" t="n">
-        <v>16000000</v>
-      </c>
-      <c r="E15" s="13" t="n">
-        <v>600000</v>
-      </c>
-      <c r="F15" s="13" t="n">
-        <v>40</v>
-      </c>
-      <c r="G15" s="13" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="H15" s="13" t="inlineStr">
-        <is>
-          <t>2032-09-07</t>
-        </is>
-      </c>
-      <c r="I15" s="13" t="inlineStr">
-        <is>
-          <t>2032-09-06</t>
-        </is>
-      </c>
-      <c r="J15" s="13" t="inlineStr">
-        <is>
-          <t>2032-09-06</t>
-        </is>
-      </c>
-      <c r="K15" s="13" t="inlineStr">
-        <is>
-          <t>The real alternative to the A380 (D84): £16m down, £600,000 a month; 400 seats; thirstier per seat. At three stars it earns as much as the A380 after payments; the A380 pulls ahead with stars or growth.</t>
-        </is>
-      </c>
-      <c r="L15" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t>a380</t>
-        </is>
-      </c>
-      <c r="B16" s="13" t="n">
-        <v>60000000</v>
-      </c>
-      <c r="C16" s="13" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D16" s="13" t="n">
-        <v>20000000</v>
-      </c>
-      <c r="E16" s="13" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="F16" s="13" t="n">
-        <v>40</v>
-      </c>
-      <c r="G16" s="13" t="n">
-        <v>60000000</v>
-      </c>
-      <c r="H16" s="13" t="inlineStr">
-        <is>
-          <t>2032-09-07</t>
-        </is>
-      </c>
-      <c r="I16" s="13" t="inlineStr">
-        <is>
-          <t>2032-09-06</t>
-        </is>
-      </c>
-      <c r="J16" s="13" t="inlineStr">
-        <is>
-          <t>2032-09-06</t>
-        </is>
-      </c>
-      <c r="K16" s="13" t="inlineStr">
-        <is>
-          <t>Chapter 4's worked example: 60,000,000 − 20,000,000 = 40,000,000; ÷ 40 = £1,000,000 a month; total paid £60m (no interest: PS4 maths). About a third of a good airline's monthly profit.</t>
-        </is>
-      </c>
-      <c r="L16" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="17" t="inlineStr">
-        <is>
-          <t>Note on the launch-deal rows: tutorial finance is in daily payments (as in the game today), because the opening is played by the day; from the A220 the payments are weekly, because chapter 4 is played by the month. 'When does renting cost more than buying?' = price ÷ leaseDaily: about 20–25 days for tutorial planes (launch deals), 1,000 days for every jet from the A220 up (F4).</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="17" t="inlineStr">
-        <is>
-          <t>Tutorial prices are 2½× v4.3 (D55): the second plane is rented or financed in week 2 and bought outright around week 4–5. The first Twin Otter is still the £2,500 launch deal. Rent-or-buy ≈ 55 days for every tutorial plane; 1,000 days for jets from the A220 up.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="13" t="inlineStr">
-        <is>
-          <t>fuelFarm</t>
-        </is>
-      </c>
-      <c r="B20" s="13" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="C20" s="13" t="n"/>
-      <c r="D20" s="13" t="n"/>
-      <c r="E20" s="13" t="n"/>
-      <c r="F20" s="13" t="n"/>
-      <c r="G20" s="13" t="n"/>
-      <c r="H20" s="13" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="I20" s="13" t="inlineStr">
-        <is>
-          <t>2031-09-01</t>
-        </is>
-      </c>
-      <c r="J20" s="13" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="K20" s="13" t="inlineStr">
-        <is>
-          <t>D89: fuel storage to buy, 1,500,000 L (chapter 3); a second stage of 3,000,000 L for £3m from 2032-09-06. Not a plane: no rent, no finance. Is it worth it? litres × the next shock's rise against the price.</t>
-        </is>
-      </c>
-      <c r="L20" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
         </is>
       </c>
     </row>
@@ -14773,6 +14155,880 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:L20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="21" t="inlineStr">
+        <is>
+          <t>aircraftId</t>
+        </is>
+      </c>
+      <c r="B1" s="21" t="inlineStr">
+        <is>
+          <t>cashPrice</t>
+        </is>
+      </c>
+      <c r="C1" s="21" t="inlineStr">
+        <is>
+          <t>leaseDaily</t>
+        </is>
+      </c>
+      <c r="D1" s="21" t="inlineStr">
+        <is>
+          <t>financeDeposit</t>
+        </is>
+      </c>
+      <c r="E1" s="21" t="inlineStr">
+        <is>
+          <t>monthlyPayment</t>
+        </is>
+      </c>
+      <c r="F1" s="21" t="inlineStr">
+        <is>
+          <t>months</t>
+        </is>
+      </c>
+      <c r="G1" s="21" t="inlineStr">
+        <is>
+          <t>financeTotalPaid</t>
+        </is>
+      </c>
+      <c r="H1" s="21" t="inlineStr">
+        <is>
+          <t>leaseFrom</t>
+        </is>
+      </c>
+      <c r="I1" s="21" t="inlineStr">
+        <is>
+          <t>buyFrom</t>
+        </is>
+      </c>
+      <c r="J1" s="21" t="inlineStr">
+        <is>
+          <t>financeFrom</t>
+        </is>
+      </c>
+      <c r="K1" s="21" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="L1" s="21" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>dhc6</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C2" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="D2" s="13" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E2" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="F2" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="G2" s="13" t="n">
+        <v>13000</v>
+      </c>
+      <c r="H2" s="13" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I2" s="13" t="inlineStr">
+        <is>
+          <t>day 8</t>
+        </is>
+      </c>
+      <c r="J2" s="13" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K2" s="13" t="inlineStr">
+        <is>
+          <t>Chapter 1 is buy only (D76). Week-2 sum: (price − cash) ÷ profit a day = days to wait.</t>
+        </is>
+      </c>
+      <c r="L2" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>saab340</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="n">
+        <v>22000</v>
+      </c>
+      <c r="C3" s="13" t="n">
+        <v>400</v>
+      </c>
+      <c r="D3" s="13" t="n">
+        <v>7000</v>
+      </c>
+      <c r="E3" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="F3" s="13" t="n">
+        <v>32</v>
+      </c>
+      <c r="G3" s="13" t="n">
+        <v>23000</v>
+      </c>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I3" s="13" t="inlineStr">
+        <is>
+          <t>day 8</t>
+        </is>
+      </c>
+      <c r="J3" s="13" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K3" s="13" t="inlineStr">
+        <is>
+          <t>Chapter 1 is buy only (D76). Week-2 sum: (price − cash) ÷ profit a day = days to wait.</t>
+        </is>
+      </c>
+      <c r="L3" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>atr72</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="n">
+        <v>36000</v>
+      </c>
+      <c r="C4" s="13" t="n">
+        <v>650</v>
+      </c>
+      <c r="D4" s="13" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E4" s="13" t="n">
+        <v>800</v>
+      </c>
+      <c r="F4" s="13" t="n">
+        <v>35</v>
+      </c>
+      <c r="G4" s="13" t="n">
+        <v>39000</v>
+      </c>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>day 8</t>
+        </is>
+      </c>
+      <c r="J4" s="13" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K4" s="13" t="inlineStr">
+        <is>
+          <t>Chapter 1 is buy only (D76). Week-2 sum: (price − cash) ÷ profit a day = days to wait.</t>
+        </is>
+      </c>
+      <c r="L4" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>e175</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="n">
+        <v>50000</v>
+      </c>
+      <c r="C5" s="13" t="n">
+        <v>900</v>
+      </c>
+      <c r="D5" s="13" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E5" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F5" s="13" t="n">
+        <v>38</v>
+      </c>
+      <c r="G5" s="13" t="n">
+        <v>53000</v>
+      </c>
+      <c r="H5" s="13" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I5" s="13" t="inlineStr">
+        <is>
+          <t>day 22</t>
+        </is>
+      </c>
+      <c r="J5" s="13" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K5" s="13" t="inlineStr">
+        <is>
+          <t>Chapter 1 is buy only (D76). Week-2 sum: (price − cash) ÷ profit a day = days to wait.</t>
+        </is>
+      </c>
+      <c r="L5" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>e190</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="n">
+        <v>70000</v>
+      </c>
+      <c r="C6" s="13" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D6" s="13" t="n">
+        <v>21000</v>
+      </c>
+      <c r="E6" s="13" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F6" s="13" t="n">
+        <v>36</v>
+      </c>
+      <c r="G6" s="13" t="n">
+        <v>75000</v>
+      </c>
+      <c r="H6" s="13" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>day 22</t>
+        </is>
+      </c>
+      <c r="J6" s="13" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K6" s="13" t="inlineStr">
+        <is>
+          <t>Chapter 1 is buy only (D76). Week-2 sum: (price − cash) ÷ profit a day = days to wait.</t>
+        </is>
+      </c>
+      <c r="L6" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>a220</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="n">
+        <v>300000</v>
+      </c>
+      <c r="C7" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="D7" s="13" t="n">
+        <v>90000</v>
+      </c>
+      <c r="E7" s="13" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F7" s="13" t="n">
+        <v>52</v>
+      </c>
+      <c r="G7" s="13" t="n">
+        <v>298000</v>
+      </c>
+      <c r="H7" s="13" t="inlineStr">
+        <is>
+          <t>2031-01-06</t>
+        </is>
+      </c>
+      <c r="I7" s="13" t="inlineStr">
+        <is>
+          <t>2031-09-02</t>
+        </is>
+      </c>
+      <c r="J7" s="13" t="inlineStr">
+        <is>
+          <t>2032-09-07</t>
+        </is>
+      </c>
+      <c r="K7" s="13" t="inlineStr">
+        <is>
+          <t>Rent = price ÷ 1,000. Finance = 30% deposit, balance over 52 weeks, rounded to £1,000.</t>
+        </is>
+      </c>
+      <c r="L7" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>a320</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="n">
+        <v>400000</v>
+      </c>
+      <c r="C8" s="13" t="n">
+        <v>400</v>
+      </c>
+      <c r="D8" s="13" t="n">
+        <v>120000</v>
+      </c>
+      <c r="E8" s="13" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F8" s="13" t="n">
+        <v>52</v>
+      </c>
+      <c r="G8" s="13" t="n">
+        <v>380000</v>
+      </c>
+      <c r="H8" s="13" t="inlineStr">
+        <is>
+          <t>2031-01-06</t>
+        </is>
+      </c>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>2031-09-02</t>
+        </is>
+      </c>
+      <c r="J8" s="13" t="inlineStr">
+        <is>
+          <t>2032-09-07</t>
+        </is>
+      </c>
+      <c r="K8" s="13" t="inlineStr"/>
+      <c r="L8" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>b737</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="n">
+        <v>400000</v>
+      </c>
+      <c r="C9" s="13" t="n">
+        <v>400</v>
+      </c>
+      <c r="D9" s="13" t="n">
+        <v>120000</v>
+      </c>
+      <c r="E9" s="13" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F9" s="13" t="n">
+        <v>52</v>
+      </c>
+      <c r="G9" s="13" t="n">
+        <v>380000</v>
+      </c>
+      <c r="H9" s="13" t="inlineStr">
+        <is>
+          <t>2031-01-06</t>
+        </is>
+      </c>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>2031-09-02</t>
+        </is>
+      </c>
+      <c r="J9" s="13" t="inlineStr">
+        <is>
+          <t>2032-09-07</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="inlineStr"/>
+      <c r="L9" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>b757</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="C10" s="13" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D10" s="13" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="E10" s="13" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F10" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="G10" s="13" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="H10" s="13" t="inlineStr">
+        <is>
+          <t>2031-01-06</t>
+        </is>
+      </c>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>2031-09-01</t>
+        </is>
+      </c>
+      <c r="J10" s="13" t="inlineStr">
+        <is>
+          <t>2032-09-06</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="inlineStr">
+        <is>
+          <t>Leased in January 2031 at £1,500 a day (price ÷ 1,000). Buy from chapter 3.</t>
+        </is>
+      </c>
+      <c r="L10" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>b787</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="C11" s="13" t="n">
+        <v>6000</v>
+      </c>
+      <c r="D11" s="13" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="E11" s="13" t="n">
+        <v>200000</v>
+      </c>
+      <c r="F11" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="G11" s="13" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="H11" s="13" t="inlineStr">
+        <is>
+          <t>2031-01-06</t>
+        </is>
+      </c>
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>2031-09-01</t>
+        </is>
+      </c>
+      <c r="J11" s="13" t="inlineStr">
+        <is>
+          <t>2032-09-06</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="inlineStr">
+        <is>
+          <t>Leased from January 2031 at £6,000 a day; bought outright from chapter 3. 12,000,000 ÷ 6,000 = 2,000 days.</t>
+        </is>
+      </c>
+      <c r="L11" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>a340</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="C12" s="13" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D12" s="13" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="E12" s="13" t="n">
+        <v>200000</v>
+      </c>
+      <c r="F12" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="G12" s="13" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="H12" s="13" t="inlineStr">
+        <is>
+          <t>2031-09-02</t>
+        </is>
+      </c>
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>2031-09-01</t>
+        </is>
+      </c>
+      <c r="J12" s="13" t="inlineStr">
+        <is>
+          <t>2032-09-06</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="inlineStr"/>
+      <c r="L12" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>b777</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="n">
+        <v>24000000</v>
+      </c>
+      <c r="C13" s="13" t="n">
+        <v>12000</v>
+      </c>
+      <c r="D13" s="13" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="E13" s="13" t="n">
+        <v>400000</v>
+      </c>
+      <c r="F13" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="G13" s="13" t="n">
+        <v>24000000</v>
+      </c>
+      <c r="H13" s="13" t="inlineStr">
+        <is>
+          <t>2031-09-02</t>
+        </is>
+      </c>
+      <c r="I13" s="13" t="inlineStr">
+        <is>
+          <t>2031-09-01</t>
+        </is>
+      </c>
+      <c r="J13" s="13" t="inlineStr">
+        <is>
+          <t>2032-09-06</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="inlineStr"/>
+      <c r="L13" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>a350</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="C14" s="13" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D14" s="13" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="E14" s="13" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F14" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="G14" s="13" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="H14" s="13" t="inlineStr">
+        <is>
+          <t>2031-09-02</t>
+        </is>
+      </c>
+      <c r="I14" s="13" t="inlineStr">
+        <is>
+          <t>2031-09-01</t>
+        </is>
+      </c>
+      <c r="J14" s="13" t="inlineStr">
+        <is>
+          <t>2032-09-06</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="inlineStr"/>
+      <c r="L14" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>b747</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="C15" s="13" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D15" s="13" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="E15" s="13" t="n">
+        <v>600000</v>
+      </c>
+      <c r="F15" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="G15" s="13" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H15" s="13" t="inlineStr">
+        <is>
+          <t>2032-09-07</t>
+        </is>
+      </c>
+      <c r="I15" s="13" t="inlineStr">
+        <is>
+          <t>2032-09-06</t>
+        </is>
+      </c>
+      <c r="J15" s="13" t="inlineStr">
+        <is>
+          <t>2032-09-06</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="inlineStr">
+        <is>
+          <t>The real alternative to the A380 (D84): £16m down, £600,000 a month; 400 seats; thirstier per seat. At three stars it earns as much as the A380 after payments; the A380 pulls ahead with stars or growth.</t>
+        </is>
+      </c>
+      <c r="L15" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>a380</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="n">
+        <v>60000000</v>
+      </c>
+      <c r="C16" s="13" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D16" s="13" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="E16" s="13" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="G16" s="13" t="n">
+        <v>60000000</v>
+      </c>
+      <c r="H16" s="13" t="inlineStr">
+        <is>
+          <t>2032-09-07</t>
+        </is>
+      </c>
+      <c r="I16" s="13" t="inlineStr">
+        <is>
+          <t>2032-09-06</t>
+        </is>
+      </c>
+      <c r="J16" s="13" t="inlineStr">
+        <is>
+          <t>2032-09-06</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="inlineStr">
+        <is>
+          <t>Chapter 4's worked example: 60,000,000 − 20,000,000 = 40,000,000; ÷ 40 = £1,000,000 a month; total paid £60m (no interest: PS4 maths). About a third of a good airline's monthly profit.</t>
+        </is>
+      </c>
+      <c r="L16" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>Note on the launch-deal rows: tutorial finance is in daily payments (as in the game today), because the opening is played by the day; from the A220 the payments are weekly, because chapter 4 is played by the month. 'When does renting cost more than buying?' = price ÷ leaseDaily: about 20–25 days for tutorial planes (launch deals), 1,000 days for every jet from the A220 up (F4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>Tutorial prices are 2½× v4.3 (D55): the second plane is rented or financed in week 2 and bought outright around week 4–5. The first Twin Otter is still the £2,500 launch deal. Rent-or-buy ≈ 55 days for every tutorial plane; 1,000 days for jets from the A220 up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>fuelFarm</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="C20" s="13" t="n"/>
+      <c r="D20" s="13" t="n"/>
+      <c r="E20" s="13" t="n"/>
+      <c r="F20" s="13" t="n"/>
+      <c r="G20" s="13" t="n"/>
+      <c r="H20" s="13" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>2031-09-01</t>
+        </is>
+      </c>
+      <c r="J20" s="13" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="inlineStr">
+        <is>
+          <t>D89: fuel storage to buy, 1,500,000 L (chapter 3); a second stage of 3,000,000 L for £3m from 2032-09-06. Not a plane: no rent, no finance. Is it worth it? litres × the next shock's rise against the price.</t>
+        </is>
+      </c>
+      <c r="L20" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -15075,7 +15331,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -18026,7 +18282,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -37529,7 +37785,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -39566,7 +39822,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -40027,7 +40283,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -40445,7 +40701,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -40674,7 +40930,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -41027,7 +41283,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/data/Airline-World-Workbook.xlsx
+++ b/data/Airline-World-Workbook.xlsx
@@ -20,24 +20,25 @@
     <sheet name="Upgrades" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="Briefings" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="BriefingData" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="RouteNews" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Archetypes" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="EventOptions" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Milestones" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Campaign" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Routes" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="RouteCatalogue" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Aircraft" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Finance" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Airports" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Calendar" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Market" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="Events" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="Challenges" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="Mechanics" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="Catering" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="Hunts" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="Livery" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="SheetSums" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="RouteNews" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Archetypes" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="EventOptions" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Milestones" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Campaign" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Routes" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="RouteCatalogue" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Aircraft" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Finance" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Airports" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Calendar" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="Market" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="Events" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="Challenges" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="Mechanics" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="Catering" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="Hunts" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="Livery" sheetId="32" state="visible" r:id="rId32"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -584,7 +585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A45"/>
+  <dimension ref="A1:A46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -902,6 +903,13 @@
       <c r="A45" t="inlineStr">
         <is>
           <t>D104 (19 Oct 2026, Claude Code, from Claude Design's handover of 19 Oct; chosen by Bertie): What a fare does is rebuilt in seven beats (tickets make money, the fare slider, seats run out, the challenge, £100 full or £110 with one empty seat, the sheet works it out, back to his fares). Its numbers are a fixed teaching example on the new BriefingData sheet, not live route data. Briefings fare_lever beats updated. Numbering: Fable's v6.0 also uses D104 (a richer first eight weeks), so this one needs a new number in Fable's register.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>D105 (Claude Code, 19 Oct 2026, evening handover 7.10): every sum on the Sheet. Settings fuelDeskOpensDay = 1 (the Fuel desk from Launch Day, the order paid when it arrives on Wednesday); the SheetSums sheet lists every year-one sheet's sums (cells, formula, words, pupil or ƒ, book or build, the sum numbers of a week-1 run); BriefingData holds Cash, tank, profit's example (version A); the Briefings rows say what plays now that no briefing asks for a guess. Notes on launchDaySums, fuelHandSum and fuelDeskFromDay say what changed.</t>
         </is>
       </c>
     </row>
@@ -1635,7 +1643,7 @@
       </c>
       <c r="E1" s="20" t="inlineStr">
         <is>
-          <t>beat2 (predict: the pupil does…)</t>
+          <t>beat2 (no guesses since 19 Oct: what plays instead)</t>
         </is>
       </c>
       <c r="F1" s="20" t="inlineStr">
@@ -1692,7 +1700,7 @@
       </c>
       <c r="E2" s="13" t="inlineStr">
         <is>
-          <t>Notice: which plane makes more ticket money, £100 with 19 of 19 seats or £110 with 18 of 19? His guess, never marked.</t>
+          <t>Beat 5 asks its question as the caption (£100 full or £110 with one empty seat: which makes more ticket money? Let's work it out); beat 6 (design B) answers it. No choice buttons, no 'Your guess'.</t>
         </is>
       </c>
       <c r="F2" s="13" t="inlineStr">
@@ -1747,7 +1755,7 @@
       </c>
       <c r="E3" s="13" t="inlineStr">
         <is>
-          <t>Slide your fare; watch dots cross to Red Kite: 1 in 10 per £10.</t>
+          <t>Nothing to drag: the context (Red Kite at £50, you £110: £60 dearer) leads straight to the reveal, where the rule builds while 18 of the 30 walk across.</t>
         </is>
       </c>
       <c r="F3" s="13" t="inlineStr">
@@ -1802,7 +1810,7 @@
       </c>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>Click the dots left behind; how many?</t>
+          <t>After Next the crowd still at the gate counts itself (no tap).</t>
         </is>
       </c>
       <c r="F4" s="13" t="inlineStr">
@@ -1857,7 +1865,7 @@
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>Click the days that look different.</t>
+          <t>The crowds rise over the seats line on their own and the weekend lights by itself (no taps). The Operations Request stays.</t>
         </is>
       </c>
       <c r="F5" s="13" t="inlineStr">
@@ -1897,7 +1905,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>First Fuel desk visit (day 8)</t>
+          <t>First Fuel desk visit, before the first order: Launch Day in year one (the desk opens on day 1, fuelDeskOpensDay)</t>
         </is>
       </c>
       <c r="C6" s="13" t="inlineStr">
@@ -1907,22 +1915,22 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Three gauges: cash £12,409, tank 0 L, profit today. Press Buy 7,000 L: cash flows into the tank; profit does not move.</t>
+          <t>What fuel is: a price board drops in over the airport (£1.30 today; ten weeks from £1.22 to £1.47); cash £8,600, an empty tank, profit this week £0.</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>Press Buy yourself; then: what changed? (tap the gauge)</t>
+          <t>Buying: 3,000 L at £1.30 moves £3,900 from cash into the tank and profit stays £0 (no question, no buttons). Then the week flies (Wed–Sun, 600 L a day).</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>A Twin Otter departs for Paris: 120 L drains, £176 flows into today's costs. Buying fuel and using fuel are different events.</t>
+          <t>The rule: the Fuel burned column framed; 5 × £780 = £3,900, the whole bill, a day at a time. Each day pays for the fuel it burns.</t>
         </is>
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t>The Fuel desk with the order instrument</t>
+          <t>Go on: the desk's tour, then the week's fuel order (its small sheet).</t>
         </is>
       </c>
       <c r="H6" s="13" t="inlineStr">
@@ -1967,7 +1975,7 @@
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>Which burned more per seat? Tap it.</t>
+          <t>The caption asks which used less fuel for each passenger; after Next the fuel shares out across the seats (no tap).</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
@@ -2022,7 +2030,7 @@
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>What changed? Tap the day.</t>
+          <t>After Next the match weekend lights by itself (no tap). The Operations Request stays.</t>
         </is>
       </c>
       <c r="F8" s="13" t="inlineStr">
@@ -2077,7 +2085,7 @@
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>Drag a plane icon to the month you'd fly Geneva.</t>
+          <t>The caption asks when to send a plane to Geneva; after Next its busiest months light (no drag). The Operations Request stays.</t>
         </is>
       </c>
       <c r="F9" s="13" t="inlineStr">
@@ -2132,7 +2140,7 @@
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>Slide the days: when does rent pass the price?</t>
+          <t>The caption asks how many days of rent make the price; after Next the stack grows until it does (no drag).</t>
         </is>
       </c>
       <c r="F10" s="13" t="inlineStr">
@@ -2219,10 +2227,11 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="17" t="inlineStr">
         <is>
-          <t>D99: Show → Predict → Reveal → Use. Full screen, the interface darkened behind; the pupil advances by the interaction in beat 2, never by Next; a Pause &amp; discuss button at each stop for the teacher; a Replay from the Briefings shelf. Each is built as a separate HTML piece in the game's style (see the flight-time tutorial) and the game loads it at its trigger.</t>
+          <t>D99: Show → Predict → Reveal → Use. Full screen, the interface darkened behind; the pupil advances by the interaction in beat 2, never by Next; a Pause &amp; discuss button at each stop for the teacher; a Replay from the Briefings shelf. Each is built as a separate HTML piece in the game's style (see the flight-time tutorial) and the game loads it at its trigger. D105 (19 Oct, evening): no guesses: Show → Reveal → Use; Next and Back are always allowed (an Operations Request or the reserve line waits for its decision); profit_vs_cash (chapter 3) keeps its tap; cabin_sales is not built yet.</t>
         </is>
       </c>
     </row>
@@ -2249,7 +2258,7 @@
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>Press Fly one hour; count the chunks; a quarter-hour for the last bit.</t>
+          <t>The plane flies there an hour at a time on its own, the last bit a quarter hour at a time; then the T lights on the triangle (no buttons, no tap).</t>
         </is>
       </c>
       <c r="F14" s="13" t="inlineStr">
@@ -2402,7 +2411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2633,12 +2642,1119 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>fuel_cash_tank_profit</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>8600</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Beat 1: the cash vault before buying.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>fuel_cash_tank_profit</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Beat 1: today's price a litre (gold on the board); beat 2 buys at it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>fuel_cash_tank_profit</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>history</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1.22|1.25|1.3|1.37|1.47|1.41|1.36|1.3|1.35|1.3</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Beat 1: the last ten weeks, oldest first (£1.22 to £1.47; today's point cyan).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>fuel_cash_tank_profit</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>buyL</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Beat 2: 3,000 L for £3,900; cash £8,600 → £4,700; profit still £0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>fuel_cash_tank_profit</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>tank</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>The tank drawn in the scene (3,000 L fills it about 60%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>fuel_cash_tank_profit</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>perDay</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>600</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Beat 3: litres burned each day, Wed to Sun (−£780 a day).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>fuel_cash_tank_profit</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>days</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Beat 3: Wed to Sun (Monday and Tuesday of week 1 are free).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>fuel_cash_tank_profit</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>tickets</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>6660</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Beat 3: ticket money each day (gold).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>fuel_cash_tank_profit</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>otherCosts</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>3610</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Beat 3: other costs each day (plain). Profit this week £11,350; cash £19,950 on Sunday; beat 4: 5 × £780 = £3,900, the whole bill, a day at a time.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="90" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="25" t="inlineStr">
+        <is>
+          <t>sheet</t>
+        </is>
+      </c>
+      <c r="B1" s="25" t="inlineStr">
+        <is>
+          <t>cell</t>
+        </is>
+      </c>
+      <c r="C1" s="25" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="D1" s="25" t="inlineStr">
+        <is>
+          <t>formula</t>
+        </is>
+      </c>
+      <c r="E1" s="25" t="inlineStr">
+        <is>
+          <t>words</t>
+        </is>
+      </c>
+      <c r="F1" s="25" t="inlineStr">
+        <is>
+          <t>whose</t>
+        </is>
+      </c>
+      <c r="G1" s="25" t="inlineStr">
+        <is>
+          <t>how</t>
+        </is>
+      </c>
+      <c r="H1" s="25" t="inlineStr">
+        <is>
+          <t>sumNo (week 1, Steady)</t>
+        </is>
+      </c>
+      <c r="I1" s="25" t="inlineStr">
+        <is>
+          <t>sumId</t>
+        </is>
+      </c>
+      <c r="J1" s="25" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Launch Day</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>B4 · C4 · D4</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Ticket revenue</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>= B2 × B3 (and C, D)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Passengers × Fare</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>pupil</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>book</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>1–3</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>launch.tickets</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>The first market at three fares around the pupil's own (one column each); worked out in the book, typed in the cell.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Launch Day</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ticket revenue</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>= E2 × E3</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Passengers × Fare</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>pupil</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>book</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>launch.otherTickets</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Each other route in the plan, a column each.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Launch Day</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>F5</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Total revenue</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>= the plan's ticket revenue</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Ticket revenue (the plan)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ƒ</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>airline</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Filled once the ticket sums are done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Launch Day</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>F6</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Other costs</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>given</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>What's in this?</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ƒ</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>airline</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Flying, landing and passenger charges; the link lists them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Launch Day</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>F7</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Fuel burned</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>£0</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>free on Launch Day</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>ƒ</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>airline</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>The fuel burned that day (7.6): £0 on Launch Day. The week's order is on the Fuel desk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Launch Day</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>F8</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Total costs</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>= F6 + F7</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Other costs + Fuel burned</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>ƒ</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>airline</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Launch Day</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>F9</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Profit</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>= F5 − F8</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Total revenue − Total costs</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>pupil</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>book</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>launch.profit</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>A loss gets a minus sign.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Launch Day</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>B13 · C13</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Cabin sales</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>= B11 × B12</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Passengers buying snacks × Snack price</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>pupil</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>6–7</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>launch.cabin</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Built by clicking the cells the first time (a Build-level sum), then answered in the cell.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Changes (week 2 on)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>B2…C7</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Passengers a day, Empty seats, Fare, Ticket revenue a day, Over a week</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>given and ƒ</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Now · With your change</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ƒ</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>airline</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>A fare change on its own route; Over a week is × 7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Changes (week 2 on)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Difference (a fare change: ticket revenue a day)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>= C5 − B5</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>With your change − Now</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>pupil</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>build once</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>next</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>changes.difference</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Built the first time, then from the book. "Worth keeping?": green "✓ Yes, +£60 a day", or plain "Not worth keeping: −£40 a day".</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Changes (week 2 on)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>D7</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Difference (a plan change: profit a day)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>= C7 − B7</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>With your change − Now</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>pupil</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>build once</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>next</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>changes.difference</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Flights, passengers, empty seats, revenue, costs and profit a day for the plan; the same sum.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Event sums</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Stay with you</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>= B2 × B3</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Your passengers × Stay with you, in every 10</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>pupil</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>book</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>event.stay</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Under the rows of ten (3.4). People, so no £. Whole people: the answer rounds (62 × 0.6 = 37.2 → 37).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Event sums</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Business travellers today</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>= B2 × B3</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Business travellers on a weekday × Fly on a Saturday, in every 10</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>pupil</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>book</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>event.business</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Whole people (3.4): 34 × 0.7 = 23.8 → 24 in the game (the handover's 17 × 0.7 = 11.9 is the picture's example). 23.8 is accepted and the line says "People come whole: 23.8 rounds to 24."</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Sunday review</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>B9</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Profit this week</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>= B2 + B3 + … + B8</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Mon + Tue + … + Sun</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>pupil</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>week.total</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>The seven day cells are outlined without A / B tags.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Sunday review</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>B11</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Difference from the plan</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>= B10 − B9 (the larger first)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Projected on Monday − Profit this week</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>pupil</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>week.difference</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Taken larger first so it never goes below zero; the cell says more or less than planned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Sunday review</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>B13</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Average a day</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>= B9 ÷ B12</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Profit this week ÷ Days flown</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>pupil</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>week.average</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Days flown (B12) holds 7: every figure the sum uses is on the sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Fuel desk</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Cost of this order</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>= B2 × B3</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Litres to buy × Price a litre</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>pupil</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>book</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>fuel.order</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>From Launch Day (fuelDeskOpensDay). The level follows the toolkit (Calculate: book; Build: built; Model: ƒ). Two tries, then Finance fills it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Sum numbers come from the game at run time (a running number per pupil, sumNumbering); the column above is a week-1 Steady run with the day-1 jump, for reading the sheets against. whose: pupil (worked out by the pupil) or ƒ (worked out by the airline). how: book (the formula is on the bar; worked out in the book and typed in the cell), build (built by clicking the cells, then typed), build once (built the first time, then book).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9277,7 +10393,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9951,7 +11067,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12705,7 +13821,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13340,7 +14456,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13602,7 +14718,440 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="44" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="21" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B1" s="21" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="21" t="inlineStr">
+        <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="D1" s="21" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+      <c r="E1" s="21" t="inlineStr">
+        <is>
+          <t>setUpDays</t>
+        </is>
+      </c>
+      <c r="F1" s="21" t="inlineStr">
+        <is>
+          <t>runCadence</t>
+        </is>
+      </c>
+      <c r="G1" s="21" t="inlineStr">
+        <is>
+          <t>reviewDate</t>
+        </is>
+      </c>
+      <c r="H1" s="21" t="inlineStr">
+        <is>
+          <t>newIdea</t>
+        </is>
+      </c>
+      <c r="I1" s="21" t="inlineStr">
+        <is>
+          <t>mechanicsArriving</t>
+        </is>
+      </c>
+      <c r="J1" s="21" t="inlineStr">
+        <is>
+          <t>handSumsPlanned</t>
+        </is>
+      </c>
+      <c r="K1" s="21" t="inlineStr">
+        <is>
+          <t>mathsFront</t>
+        </is>
+      </c>
+      <c r="L1" s="21" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>Starting out</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="inlineStr">
+        <is>
+          <t>2030-09-02</t>
+        </is>
+      </c>
+      <c r="D2" s="13" t="inlineStr">
+        <is>
+          <t>2030-12-28</t>
+        </is>
+      </c>
+      <c r="E2" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="13" t="inlineStr">
+        <is>
+          <t>week (plan → run → review) to day 28; week-skips from day 29; months from 2030-12-02</t>
+        </is>
+      </c>
+      <c r="G2" s="13" t="inlineStr">
+        <is>
+          <t>2030-12-28</t>
+        </is>
+      </c>
+      <c r="H2" s="13" t="inlineStr">
+        <is>
+          <t>Running an airline a week at a time: the standing plan on one page (timetable with demand curve, fare, snacks, fuel), the week on the operations board, the weekly review</t>
+        </is>
+      </c>
+      <c r="I2" s="13" t="inlineStr">
+        <is>
+          <t>Launch Day: timetable, fare, snacks, fuel, both routes, modelling tool, workings page; week 2: second plane bought outright or wait for a bigger one; time-to-afford sum; week 3: four routes, £5 fares, seasons, use-it-or-lose-it; week 4: medium haul, range, E175/E190, load factor %; from week 5: weekly skips, Marrakech, the autumn pairs, scaled event costs</t>
+        </is>
+      </c>
+      <c r="J2" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="K2" s="13" t="inlineStr">
+        <is>
+          <t>column + and −; short ×; long × (fuel, £5 fares, jet fares); ÷ (flight time, rent-or-buy); time</t>
+        </is>
+      </c>
+      <c r="L2" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>Going long</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>2031-01-06</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>2031-08-31</t>
+        </is>
+      </c>
+      <c r="E3" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" s="13" t="inlineStr">
+        <is>
+          <t>week → month</t>
+        </is>
+      </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>2031-08-31</t>
+        </is>
+      </c>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>Long haul: overnight rotations, time zones; the 787 by lease; reputation revealed; airline type chosen</t>
+        </is>
+      </c>
+      <c r="I3" s="13" t="inlineStr">
+        <is>
+          <t>leasing (standing); reputation as demand multiplier; airline type; extras (Value only); Captain's challenge one a term; hunts</t>
+        </is>
+      </c>
+      <c r="J3" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="K3" s="13" t="inlineStr">
+        <is>
+          <t>big numbers (£k, £m) and estimating; revenue ÷ 2 for overnight rotations; time across zones; rent against earnings</t>
+        </is>
+      </c>
+      <c r="L3" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Owning</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>2031-09-01</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>2032-08-31</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>2032-08-31</t>
+        </is>
+      </c>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t>Owning: buying big planes outright (price − cash, ÷ profit a week); the overdraft safety net; Tokyo and Cape Town from the start, Singapore in October, Sydney via Singapore in March; the A340, 777 and A350 in the shop</t>
+        </is>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>buy outright; overdraft (no charge)</t>
+        </is>
+      </c>
+      <c r="J4" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K4" s="13" t="inlineStr">
+        <is>
+          <t>subtraction and division with millions (time to afford, weekly); percentage change on the monthly report; rent-or-buy at jet prices; the two-leg rotation; negative cash; year-2 totals and the mean at the review</t>
+        </is>
+      </c>
+      <c r="L4" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>The ultimate plane</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>2032-09-06</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>2033-08-31</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="G5" s="13" t="inlineStr">
+        <is>
+          <t>2033-08-31</t>
+        </is>
+      </c>
+      <c r="H5" s="13" t="inlineStr">
+        <is>
+          <t>The ultimate plane: the A380 on finance (£20m down, £1m a month for 40 months) or the 747 as the real alternative; Hong Kong and Los Angeles, the two routes big enough for it; does a 500-seat plane fill? (demand ÷ seats); reputation that decides it; the A380 launch campaign as the one marketing project</t>
+        </is>
+      </c>
+      <c r="I5" s="13" t="inlineStr">
+        <is>
+          <t>finance; reputation that matters</t>
+        </is>
+      </c>
+      <c r="J5" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K5" s="13" t="inlineStr">
+        <is>
+          <t>deposit and monthly payments with millions (60 − 20 = 40; ÷ 40); does it fill? demand ÷ seats as a percentage; the campaign's funnel fractions and return on spending; year-3 totals and the mean</t>
+        </is>
+      </c>
+      <c r="L5" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>The rival</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="inlineStr">
+        <is>
+          <t>2033-09-05</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="inlineStr">
+        <is>
+          <t>2034-08-31</t>
+        </is>
+      </c>
+      <c r="E6" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" s="18" t="inlineStr">
+        <is>
+          <t>month + quarterly task</t>
+        </is>
+      </c>
+      <c r="G6" s="18" t="inlineStr">
+        <is>
+          <t>2034-08-31</t>
+        </is>
+      </c>
+      <c r="H6" s="18" t="inlineStr">
+        <is>
+          <t>Red Kite enters the best route; marketing; the quarterly comparison</t>
+        </is>
+      </c>
+      <c r="I6" s="18" t="inlineStr">
+        <is>
+          <t>rival on routes; marketing; quarterly data task</t>
+        </is>
+      </c>
+      <c r="J6" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="K6" s="18" t="inlineStr">
+        <is>
+          <t>several variables at once; percentages (+10% for £X); averages over quarters; same quarter year on year</t>
+        </is>
+      </c>
+      <c r="L6" s="18" t="inlineStr">
+        <is>
+          <t>later</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>Review year</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>2034-09-04</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="inlineStr">
+        <is>
+          <t>2035-08-31</t>
+        </is>
+      </c>
+      <c r="E7" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" s="18" t="inlineStr">
+        <is>
+          <t>month + quarterly task</t>
+        </is>
+      </c>
+      <c r="G7" s="18" t="inlineStr">
+        <is>
+          <t>2035-08-31</t>
+        </is>
+      </c>
+      <c r="H7" s="18" t="inlineStr">
+        <is>
+          <t>No new mechanic: the five-year review with graphs and averages</t>
+        </is>
+      </c>
+      <c r="I7" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J7" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="K7" s="18" t="inlineStr">
+        <is>
+          <t>statistics: interpret graphs and tables; averages; trends year on year</t>
+        </is>
+      </c>
+      <c r="L7" s="18" t="inlineStr">
+        <is>
+          <t>later</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>Each chapter: Set up (day by day, the new idea and its hand sums) → Run (the standing plan at the run cadence; the market, events, 'what changed?') → Review (chapter accounts by hand, one hunt, the next investment). Reviews are dated on the last day of the chapter (D35, D40).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16182,440 +17731,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="44" customWidth="1" min="8" max="8"/>
-    <col width="50" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="44" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="21" t="inlineStr">
-        <is>
-          <t>chapter</t>
-        </is>
-      </c>
-      <c r="B1" s="21" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C1" s="21" t="inlineStr">
-        <is>
-          <t>start</t>
-        </is>
-      </c>
-      <c r="D1" s="21" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
-      <c r="E1" s="21" t="inlineStr">
-        <is>
-          <t>setUpDays</t>
-        </is>
-      </c>
-      <c r="F1" s="21" t="inlineStr">
-        <is>
-          <t>runCadence</t>
-        </is>
-      </c>
-      <c r="G1" s="21" t="inlineStr">
-        <is>
-          <t>reviewDate</t>
-        </is>
-      </c>
-      <c r="H1" s="21" t="inlineStr">
-        <is>
-          <t>newIdea</t>
-        </is>
-      </c>
-      <c r="I1" s="21" t="inlineStr">
-        <is>
-          <t>mechanicsArriving</t>
-        </is>
-      </c>
-      <c r="J1" s="21" t="inlineStr">
-        <is>
-          <t>handSumsPlanned</t>
-        </is>
-      </c>
-      <c r="K1" s="21" t="inlineStr">
-        <is>
-          <t>mathsFront</t>
-        </is>
-      </c>
-      <c r="L1" s="21" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="13" t="inlineStr">
-        <is>
-          <t>Starting out</t>
-        </is>
-      </c>
-      <c r="C2" s="13" t="inlineStr">
-        <is>
-          <t>2030-09-02</t>
-        </is>
-      </c>
-      <c r="D2" s="13" t="inlineStr">
-        <is>
-          <t>2030-12-28</t>
-        </is>
-      </c>
-      <c r="E2" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" s="13" t="inlineStr">
-        <is>
-          <t>week (plan → run → review) to day 28; week-skips from day 29; months from 2030-12-02</t>
-        </is>
-      </c>
-      <c r="G2" s="13" t="inlineStr">
-        <is>
-          <t>2030-12-28</t>
-        </is>
-      </c>
-      <c r="H2" s="13" t="inlineStr">
-        <is>
-          <t>Running an airline a week at a time: the standing plan on one page (timetable with demand curve, fare, snacks, fuel), the week on the operations board, the weekly review</t>
-        </is>
-      </c>
-      <c r="I2" s="13" t="inlineStr">
-        <is>
-          <t>Launch Day: timetable, fare, snacks, fuel, both routes, modelling tool, workings page; week 2: second plane bought outright or wait for a bigger one; time-to-afford sum; week 3: four routes, £5 fares, seasons, use-it-or-lose-it; week 4: medium haul, range, E175/E190, load factor %; from week 5: weekly skips, Marrakech, the autumn pairs, scaled event costs</t>
-        </is>
-      </c>
-      <c r="J2" s="13" t="n">
-        <v>25</v>
-      </c>
-      <c r="K2" s="13" t="inlineStr">
-        <is>
-          <t>column + and −; short ×; long × (fuel, £5 fares, jet fares); ÷ (flight time, rent-or-buy); time</t>
-        </is>
-      </c>
-      <c r="L2" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>Going long</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>2031-01-06</t>
-        </is>
-      </c>
-      <c r="D3" s="13" t="inlineStr">
-        <is>
-          <t>2031-08-31</t>
-        </is>
-      </c>
-      <c r="E3" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="F3" s="13" t="inlineStr">
-        <is>
-          <t>week → month</t>
-        </is>
-      </c>
-      <c r="G3" s="13" t="inlineStr">
-        <is>
-          <t>2031-08-31</t>
-        </is>
-      </c>
-      <c r="H3" s="13" t="inlineStr">
-        <is>
-          <t>Long haul: overnight rotations, time zones; the 787 by lease; reputation revealed; airline type chosen</t>
-        </is>
-      </c>
-      <c r="I3" s="13" t="inlineStr">
-        <is>
-          <t>leasing (standing); reputation as demand multiplier; airline type; extras (Value only); Captain's challenge one a term; hunts</t>
-        </is>
-      </c>
-      <c r="J3" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="K3" s="13" t="inlineStr">
-        <is>
-          <t>big numbers (£k, £m) and estimating; revenue ÷ 2 for overnight rotations; time across zones; rent against earnings</t>
-        </is>
-      </c>
-      <c r="L3" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>Owning</t>
-        </is>
-      </c>
-      <c r="C4" s="13" t="inlineStr">
-        <is>
-          <t>2031-09-01</t>
-        </is>
-      </c>
-      <c r="D4" s="13" t="inlineStr">
-        <is>
-          <t>2032-08-31</t>
-        </is>
-      </c>
-      <c r="E4" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="F4" s="13" t="inlineStr">
-        <is>
-          <t>month</t>
-        </is>
-      </c>
-      <c r="G4" s="13" t="inlineStr">
-        <is>
-          <t>2032-08-31</t>
-        </is>
-      </c>
-      <c r="H4" s="13" t="inlineStr">
-        <is>
-          <t>Owning: buying big planes outright (price − cash, ÷ profit a week); the overdraft safety net; Tokyo and Cape Town from the start, Singapore in October, Sydney via Singapore in March; the A340, 777 and A350 in the shop</t>
-        </is>
-      </c>
-      <c r="I4" s="13" t="inlineStr">
-        <is>
-          <t>buy outright; overdraft (no charge)</t>
-        </is>
-      </c>
-      <c r="J4" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="K4" s="13" t="inlineStr">
-        <is>
-          <t>subtraction and division with millions (time to afford, weekly); percentage change on the monthly report; rent-or-buy at jet prices; the two-leg rotation; negative cash; year-2 totals and the mean at the review</t>
-        </is>
-      </c>
-      <c r="L4" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>The ultimate plane</t>
-        </is>
-      </c>
-      <c r="C5" s="13" t="inlineStr">
-        <is>
-          <t>2032-09-06</t>
-        </is>
-      </c>
-      <c r="D5" s="13" t="inlineStr">
-        <is>
-          <t>2033-08-31</t>
-        </is>
-      </c>
-      <c r="E5" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="F5" s="13" t="inlineStr">
-        <is>
-          <t>month</t>
-        </is>
-      </c>
-      <c r="G5" s="13" t="inlineStr">
-        <is>
-          <t>2033-08-31</t>
-        </is>
-      </c>
-      <c r="H5" s="13" t="inlineStr">
-        <is>
-          <t>The ultimate plane: the A380 on finance (£20m down, £1m a month for 40 months) or the 747 as the real alternative; Hong Kong and Los Angeles, the two routes big enough for it; does a 500-seat plane fill? (demand ÷ seats); reputation that decides it; the A380 launch campaign as the one marketing project</t>
-        </is>
-      </c>
-      <c r="I5" s="13" t="inlineStr">
-        <is>
-          <t>finance; reputation that matters</t>
-        </is>
-      </c>
-      <c r="J5" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="K5" s="13" t="inlineStr">
-        <is>
-          <t>deposit and monthly payments with millions (60 − 20 = 40; ÷ 40); does it fill? demand ÷ seats as a percentage; the campaign's funnel fractions and return on spending; year-3 totals and the mean</t>
-        </is>
-      </c>
-      <c r="L5" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t>The rival</t>
-        </is>
-      </c>
-      <c r="C6" s="18" t="inlineStr">
-        <is>
-          <t>2033-09-05</t>
-        </is>
-      </c>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t>2034-08-31</t>
-        </is>
-      </c>
-      <c r="E6" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="F6" s="18" t="inlineStr">
-        <is>
-          <t>month + quarterly task</t>
-        </is>
-      </c>
-      <c r="G6" s="18" t="inlineStr">
-        <is>
-          <t>2034-08-31</t>
-        </is>
-      </c>
-      <c r="H6" s="18" t="inlineStr">
-        <is>
-          <t>Red Kite enters the best route; marketing; the quarterly comparison</t>
-        </is>
-      </c>
-      <c r="I6" s="18" t="inlineStr">
-        <is>
-          <t>rival on routes; marketing; quarterly data task</t>
-        </is>
-      </c>
-      <c r="J6" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="K6" s="18" t="inlineStr">
-        <is>
-          <t>several variables at once; percentages (+10% for £X); averages over quarters; same quarter year on year</t>
-        </is>
-      </c>
-      <c r="L6" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="18" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>Review year</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>2034-09-04</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>2035-08-31</t>
-        </is>
-      </c>
-      <c r="E7" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="F7" s="18" t="inlineStr">
-        <is>
-          <t>month + quarterly task</t>
-        </is>
-      </c>
-      <c r="G7" s="18" t="inlineStr">
-        <is>
-          <t>2035-08-31</t>
-        </is>
-      </c>
-      <c r="H7" s="18" t="inlineStr">
-        <is>
-          <t>No new mechanic: the five-year review with graphs and averages</t>
-        </is>
-      </c>
-      <c r="I7" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J7" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="K7" s="18" t="inlineStr">
-        <is>
-          <t>statistics: interpret graphs and tables; averages; trends year on year</t>
-        </is>
-      </c>
-      <c r="L7" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="17" t="inlineStr">
-        <is>
-          <t>Each chapter: Set up (day by day, the new idea and its hand sums) → Run (the standing plan at the run cadence; the market, events, 'what changed?') → Review (chapter accounts by hand, one hunt, the next investment). Reviews are dated on the last day of the chapter (D35, D40).</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17881,7 +18997,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -18924,7 +20040,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -19806,7 +20922,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -20114,7 +21230,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -23065,7 +24181,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -47467,7 +48583,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -50388,7 +51504,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -50849,7 +51965,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -51259,235 +52375,6 @@
       <c r="D21" s="13" t="inlineStr">
         <is>
           <t>live</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="21" t="inlineStr">
-        <is>
-          <t>optionId</t>
-        </is>
-      </c>
-      <c r="B1" s="21" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C1" s="21" t="inlineStr">
-        <is>
-          <t>sellingPrice</t>
-        </is>
-      </c>
-      <c r="D1" s="21" t="inlineStr">
-        <is>
-          <t>takeUp</t>
-        </is>
-      </c>
-      <c r="E1" s="21" t="inlineStr">
-        <is>
-          <t>unitStockCost</t>
-        </is>
-      </c>
-      <c r="F1" s="21" t="inlineStr">
-        <is>
-          <t>freeCostPerPassenger</t>
-        </is>
-      </c>
-      <c r="G1" s="21" t="inlineStr">
-        <is>
-          <t>reputationEffect</t>
-        </is>
-      </c>
-      <c r="H1" s="21" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="I1" s="21" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="13" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="B2" s="13" t="inlineStr">
-        <is>
-          <t>No snacks</t>
-        </is>
-      </c>
-      <c r="C2" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="13" t="inlineStr">
-        <is>
-          <t>Nothing sold, nothing spent.</t>
-        </is>
-      </c>
-      <c r="I2" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="13" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>Snacks at £3</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="D3" s="13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E3" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="13" t="inlineStr">
-        <is>
-          <t>Half of passengers buy. Day 2's hand sum: 10 × £3 = £30; £30 − £10 stock = £20.</t>
-        </is>
-      </c>
-      <c r="I3" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>Snacks at £5</t>
-        </is>
-      </c>
-      <c r="C4" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="D4" s="13" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E4" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="13" t="inlineStr">
-        <is>
-          <t>Three in ten buy.</t>
-        </is>
-      </c>
-      <c r="I4" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>free</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Free snacks</t>
-        </is>
-      </c>
-      <c r="C5" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="G5" s="13" t="inlineStr">
-        <is>
-          <t>later: +reputation</t>
-        </is>
-      </c>
-      <c r="H5" s="13" t="inlineStr">
-        <is>
-          <t>Costs £2 a passenger; reputation effect once reputation is live (Jan 2031).</t>
-        </is>
-      </c>
-      <c r="I5" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="17" t="inlineStr">
-        <is>
-          <t>Today's game values, moved into the workbook (F3). Extras for the Value airline (bag fee, seat fee, take-up) to be added here when chapter 2 is designed (D37).</t>
         </is>
       </c>
     </row>
@@ -51919,6 +52806,235 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="21" t="inlineStr">
+        <is>
+          <t>optionId</t>
+        </is>
+      </c>
+      <c r="B1" s="21" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="21" t="inlineStr">
+        <is>
+          <t>sellingPrice</t>
+        </is>
+      </c>
+      <c r="D1" s="21" t="inlineStr">
+        <is>
+          <t>takeUp</t>
+        </is>
+      </c>
+      <c r="E1" s="21" t="inlineStr">
+        <is>
+          <t>unitStockCost</t>
+        </is>
+      </c>
+      <c r="F1" s="21" t="inlineStr">
+        <is>
+          <t>freeCostPerPassenger</t>
+        </is>
+      </c>
+      <c r="G1" s="21" t="inlineStr">
+        <is>
+          <t>reputationEffect</t>
+        </is>
+      </c>
+      <c r="H1" s="21" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="I1" s="21" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>No snacks</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="13" t="inlineStr">
+        <is>
+          <t>Nothing sold, nothing spent.</t>
+        </is>
+      </c>
+      <c r="I2" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>Snacks at £3</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" s="13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E3" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>Half of passengers buy. Day 2's hand sum: 10 × £3 = £30; £30 − £10 stock = £20.</t>
+        </is>
+      </c>
+      <c r="I3" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Snacks at £5</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" s="13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E4" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t>Three in ten buy.</t>
+        </is>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>free</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Free snacks</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" s="13" t="inlineStr">
+        <is>
+          <t>later: +reputation</t>
+        </is>
+      </c>
+      <c r="H5" s="13" t="inlineStr">
+        <is>
+          <t>Costs £2 a passenger; reputation effect once reputation is live (Jan 2031).</t>
+        </is>
+      </c>
+      <c r="I5" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>Today's game values, moved into the workbook (F3). Extras for the Value airline (bag fee, seat fee, take-up) to be added here when chapter 2 is designed (D37).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -52266,7 +53382,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -54503,7 +55619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D220"/>
+  <dimension ref="A1:D221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -55789,7 +56905,7 @@
       </c>
       <c r="C62" s="13" t="inlineStr">
         <is>
-          <t>D94: four hand sums on Launch Day.</t>
+          <t>D94: four hand sums on Launch Day. D105: on the Launch Day sheet (SheetSums): ticket revenue at the market's three fares and the other route's, the profit, and the cabin sales (built the first time). No fuel sum: the sheet's Fuel line is the fuel burned, £0 on Launch Day.</t>
         </is>
       </c>
       <c r="D62" s="13" t="inlineStr">
@@ -55957,7 +57073,7 @@
       </c>
       <c r="C70" s="13" t="inlineStr">
         <is>
-          <t>D86: the only fuel sum after Launch Day is the Monday order on the fuel desk (3 × £1,470 = £4,410), by hand when the price has moved fuelHandSumPriceStep (50p) since it was last asked, otherwise Build or Model. The game breaks the week's bill down by route and plane on the load sheets automatically for the pupil to read. The per-service decimal multiplication is Launch Day's one example and Model afterwards.</t>
+          <t>D86: the only fuel sum after Launch Day is the Monday order on the fuel desk (3 × £1,470 = £4,410), by hand when the price has moved fuelHandSumPriceStep (50p) since it was last asked, otherwise Build or Model. The game breaks the week's bill down by route and plane on the load sheets automatically for the pupil to read. The per-service decimal multiplication is Launch Day's one example and Model afterwards. D105: the weekly order's sum is a small sheet on the Fuel desk (Litres to buy × Price a litre = Cost of this order), from Launch Day.</t>
         </is>
       </c>
       <c r="D70" s="13" t="inlineStr">
@@ -56041,7 +57157,7 @@
       </c>
       <c r="C74" s="13" t="inlineStr">
         <is>
-          <t>D94: the Fuel desk opens in week 2 with its visual introduction (gauges on the apron, litres becoming pounds), then the first per-flight fuel sum with Show me how, then the week's order; blocks as a later beat.</t>
+          <t>D94: the Fuel desk opens in week 2 with its visual introduction (gauges on the apron, litres becoming pounds), then the first per-flight fuel sum with Show me how, then the week's order; blocks as a later beat. D105: in year one the desk itself opens on day 1 (fuelDeskOpensDay); this day still dates the week-2 features.</t>
         </is>
       </c>
       <c r="D74" s="13" t="inlineStr">
@@ -56051,22 +57167,20 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="13" t="inlineStr">
-        <is>
-          <t>tankUpgradeDay</t>
-        </is>
-      </c>
-      <c r="B75" s="13" t="inlineStr">
-        <is>
-          <t>withdrawn</t>
-        </is>
-      </c>
-      <c r="C75" s="13" t="inlineStr">
-        <is>
-          <t>replaced by tankWeeksOfFuel (D89)</t>
-        </is>
-      </c>
-      <c r="D75" s="13" t="inlineStr">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>fuelDeskOpensDay</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>1</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>D105 (Claude Code, 19 Oct 2026, evening handover 7.10): year one: the Fuel desk is open from Launch Day (no padlock) and the week's fuel order is placed there. On the first visit: the Cash, tank, profit briefing, then the desk's tour, then the order. Monday and Tuesday of week 1 stay free (fuelWeek1): an order placed on a free day arrives for the first paid day (Wednesday 4 Sep) at that day's price and is paid from cash when it arrives. No forced worked example: the order's sum is a small sheet (SheetSums: fuel.order). fuelDeskFromDay (8) still dates the week-2 desk features.</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
         <is>
           <t>live</t>
         </is>
@@ -56075,7 +57189,7 @@
     <row r="76">
       <c r="A76" s="13" t="inlineStr">
         <is>
-          <t>tankCapacityUpgraded</t>
+          <t>tankUpgradeDay</t>
         </is>
       </c>
       <c r="B76" s="13" t="inlineStr">
@@ -56097,17 +57211,17 @@
     <row r="77">
       <c r="A77" s="13" t="inlineStr">
         <is>
-          <t>fuelAdvantageWording</t>
+          <t>tankCapacityUpgraded</t>
         </is>
       </c>
       <c r="B77" s="13" t="inlineStr">
         <is>
-          <t>saved compared with buying later</t>
+          <t>withdrawn</t>
         </is>
       </c>
       <c r="C77" s="13" t="inlineStr">
         <is>
-          <t>D60: buying ahead is reported as 'Fuel purchasing advantage: +£X (saved compared with buying next week)' or '−£X', never as profit.</t>
+          <t>replaced by tankWeeksOfFuel (D89)</t>
         </is>
       </c>
       <c r="D77" s="13" t="inlineStr">
@@ -56119,15 +57233,17 @@
     <row r="78">
       <c r="A78" s="13" t="inlineStr">
         <is>
-          <t>fuelCoverage</t>
-        </is>
-      </c>
-      <c r="B78" s="13" t="b">
-        <v>1</v>
+          <t>fuelAdvantageWording</t>
+        </is>
+      </c>
+      <c r="B78" s="13" t="inlineStr">
+        <is>
+          <t>saved compared with buying later</t>
+        </is>
       </c>
       <c r="C78" s="13" t="inlineStr">
         <is>
-          <t>D60: the desk shows this week's requirement (litres the standing plan burns), litres in storage, % covered, and litres still exposed to the market price.</t>
+          <t>D60: buying ahead is reported as 'Fuel purchasing advantage: +£X (saved compared with buying next week)' or '−£X', never as profit.</t>
         </is>
       </c>
       <c r="D78" s="13" t="inlineStr">
@@ -56139,17 +57255,15 @@
     <row r="79">
       <c r="A79" s="13" t="inlineStr">
         <is>
-          <t>forecastConfidenceLevels</t>
-        </is>
-      </c>
-      <c r="B79" s="13" t="inlineStr">
-        <is>
-          <t>high | medium | low</t>
-        </is>
+          <t>fuelCoverage</t>
+        </is>
+      </c>
+      <c r="B79" s="13" t="b">
+        <v>1</v>
       </c>
       <c r="C79" s="13" t="inlineStr">
         <is>
-          <t>D60: Market forecastConfidence; low-confidence weeks have a wider range and may carry a second, conflicting signal (fuelHeadline2). The actual price always lies inside the range (no randomness).</t>
+          <t>D60: the desk shows this week's requirement (litres the standing plan burns), litres in storage, % covered, and litres still exposed to the market price.</t>
         </is>
       </c>
       <c r="D79" s="13" t="inlineStr">
@@ -56161,17 +57275,17 @@
     <row r="80">
       <c r="A80" s="13" t="inlineStr">
         <is>
-          <t>reviewTotalsMode</t>
+          <t>forecastConfidenceLevels</t>
         </is>
       </c>
       <c r="B80" s="13" t="inlineStr">
         <is>
-          <t>build</t>
+          <t>high | medium | low</t>
         </is>
       </c>
       <c r="C80" s="13" t="inlineStr">
         <is>
-          <t>D61: totals, differences and means at reviews are Build steps (pupil selects figures, operation, order or divisor; the game calculates). Teacher can set Calculate per pupil.</t>
+          <t>D60: Market forecastConfidence; low-confidence weeks have a wider range and may carry a second, conflicting signal (fuelHeadline2). The actual price always lies inside the range (no randomness).</t>
         </is>
       </c>
       <c r="D80" s="13" t="inlineStr">
@@ -56183,15 +57297,17 @@
     <row r="81">
       <c r="A81" s="13" t="inlineStr">
         <is>
-          <t>meanFromDay</t>
-        </is>
-      </c>
-      <c r="B81" s="13" t="n">
-        <v>7</v>
+          <t>reviewTotalsMode</t>
+        </is>
+      </c>
+      <c r="B81" s="13" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
       </c>
       <c r="C81" s="13" t="inlineStr">
         <is>
-          <t>D61: from the first weekly review, the review asks for the average profit a day (total ÷ number of days flown). Monthly reports from December ask for the average week (month total ÷ number of weeks).</t>
+          <t>D61: totals, differences and means at reviews are Build steps (pupil selects figures, operation, order or divisor; the game calculates). Teacher can set Calculate per pupil.</t>
         </is>
       </c>
       <c r="D81" s="13" t="inlineStr">
@@ -56203,17 +57319,15 @@
     <row r="82">
       <c r="A82" s="13" t="inlineStr">
         <is>
-          <t>secondAircraftCompare</t>
-        </is>
-      </c>
-      <c r="B82" s="13" t="inlineStr">
-        <is>
-          <t>choose plane, or wait</t>
-        </is>
+          <t>meanFromDay</t>
+        </is>
+      </c>
+      <c r="B82" s="13" t="n">
+        <v>7</v>
       </c>
       <c r="C82" s="13" t="inlineStr">
         <is>
-          <t>D62/D76: the week-2 comparison's second screen is 'Buy now or wait?': for each plane, cash now, price, still to save, days to wait at the current rate, and what waiting costs (the smaller plane's extra profit × days). Buy is greyed with the shortfall when unaffordable.</t>
+          <t>D61: from the first weekly review, the review asks for the average profit a day (total ÷ number of days flown). Monthly reports from December ask for the average week (month total ÷ number of weeks).</t>
         </is>
       </c>
       <c r="D82" s="13" t="inlineStr">
@@ -56225,42 +57339,42 @@
     <row r="83">
       <c r="A83" s="13" t="inlineStr">
         <is>
+          <t>secondAircraftCompare</t>
+        </is>
+      </c>
+      <c r="B83" s="13" t="inlineStr">
+        <is>
+          <t>choose plane, or wait</t>
+        </is>
+      </c>
+      <c r="C83" s="13" t="inlineStr">
+        <is>
+          <t>D62/D76: the week-2 comparison's second screen is 'Buy now or wait?': for each plane, cash now, price, still to save, days to wait at the current rate, and what waiting costs (the smaller plane's extra profit × days). Buy is greyed with the shortfall when unaffordable.</t>
+        </is>
+      </c>
+      <c r="D83" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="13" t="inlineStr">
+        <is>
           <t>whereCouldItFly</t>
         </is>
       </c>
-      <c r="B83" s="13" t="inlineStr">
+      <c r="B84" s="13" t="inlineStr">
         <is>
           <t>today, week 3, week 4</t>
         </is>
       </c>
-      <c r="C83" s="13" t="inlineStr">
+      <c r="C84" s="13" t="inlineStr">
         <is>
           <t>D62: the comparison's what-if preview shows each plane's extra profit a day on today's routes, on the routes opening in week 3 (Amsterdam, Barcelona) and in week 4 (Madrid), plus a Dublin-demand tab.</t>
         </is>
       </c>
-      <c r="D83" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="23" t="inlineStr">
-        <is>
-          <t>blockedFlightCodes</t>
-        </is>
-      </c>
-      <c r="B84" s="23" t="inlineStr">
-        <is>
-          <t>BA, EZ, FR, VS, LH, AF, KL, U2</t>
-        </is>
-      </c>
-      <c r="C84" s="23" t="inlineStr">
-        <is>
-          <t>CR5. Real airline codes the pupil cannot pick; refused calmly ("That code belongs to a real airline, try another").</t>
-        </is>
-      </c>
-      <c r="D84" s="23" t="inlineStr">
+      <c r="D84" s="13" t="inlineStr">
         <is>
           <t>live</t>
         </is>
@@ -56269,17 +57383,17 @@
     <row r="85">
       <c r="A85" s="23" t="inlineStr">
         <is>
-          <t>soundDefault</t>
+          <t>blockedFlightCodes</t>
         </is>
       </c>
       <c r="B85" s="23" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>BA, EZ, FR, VS, LH, AF, KL, U2</t>
         </is>
       </c>
       <c r="C85" s="23" t="inlineStr">
         <is>
-          <t>CR5. Sound (take-off, airport chimes, announcements) is off until the teacher turns it on; a mute control sits in the top bar.</t>
+          <t>CR5. Real airline codes the pupil cannot pick; refused calmly ("That code belongs to a real airline, try another").</t>
         </is>
       </c>
       <c r="D85" s="23" t="inlineStr">
@@ -56291,38 +57405,40 @@
     <row r="86">
       <c r="A86" s="23" t="inlineStr">
         <is>
+          <t>soundDefault</t>
+        </is>
+      </c>
+      <c r="B86" s="23" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="C86" s="23" t="inlineStr">
+        <is>
+          <t>CR5. Sound (take-off, airport chimes, announcements) is off until the teacher turns it on; a mute control sits in the top bar.</t>
+        </is>
+      </c>
+      <c r="D86" s="23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="23" t="inlineStr">
+        <is>
           <t>revealSeconds</t>
         </is>
       </c>
-      <c r="B86" s="23" t="n">
+      <c r="B87" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="C86" s="23" t="inlineStr">
+      <c r="C87" s="23" t="inlineStr">
         <is>
           <t>CR5. The hangar reveal on launch day: doors close, open, the plane rolls in. Later planes get about half.</t>
         </is>
       </c>
-      <c r="D86" s="23" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="13" t="inlineStr">
-        <is>
-          <t>signOffCapPerWeek</t>
-        </is>
-      </c>
-      <c r="B87" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="C87" s="13" t="inlineStr">
-        <is>
-          <t>D63/D86 confirmed: three a week from week 2 (teacher dial 1–3).</t>
-        </is>
-      </c>
-      <c r="D87" s="13" t="inlineStr">
+      <c r="D87" s="23" t="inlineStr">
         <is>
           <t>live</t>
         </is>
@@ -56331,15 +57447,15 @@
     <row r="88">
       <c r="A88" s="13" t="inlineStr">
         <is>
-          <t>signOffDecayAfter</t>
+          <t>signOffCapPerWeek</t>
         </is>
       </c>
       <c r="B88" s="13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C88" s="13" t="inlineStr">
         <is>
-          <t>D63: a relationship is Calculate the first two times it appears; a new instance from the third time (tickets on a new route, fuel for a new plane) is Build; once nothing is new it is Model. The teacher can hold any relationship at Calculate.</t>
+          <t>D63/D86 confirmed: three a week from week 2 (teacher dial 1–3).</t>
         </is>
       </c>
       <c r="D88" s="13" t="inlineStr">
@@ -56351,17 +57467,15 @@
     <row r="89">
       <c r="A89" s="13" t="inlineStr">
         <is>
-          <t>auditFloor</t>
-        </is>
-      </c>
-      <c r="B89" s="13" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
+          <t>signOffDecayAfter</t>
+        </is>
+      </c>
+      <c r="B89" s="13" t="n">
+        <v>2</v>
       </c>
       <c r="C89" s="13" t="inlineStr">
         <is>
-          <t>D64: at each month end Finance sends an audit — re-check one existing figure from the pupil's own airline, chosen as the route with the most missed profit. Falls on the last day of each month; from December it comes with the monthly report.</t>
+          <t>D63: a relationship is Calculate the first two times it appears; a new instance from the third time (tickets on a new route, fuel for a new plane) is Build; once nothing is new it is Model. The teacher can hold any relationship at Calculate.</t>
         </is>
       </c>
       <c r="D89" s="13" t="inlineStr">
@@ -56373,15 +57487,17 @@
     <row r="90">
       <c r="A90" s="13" t="inlineStr">
         <is>
-          <t>boardNudgeIdleWeeks</t>
-        </is>
-      </c>
-      <c r="B90" s="13" t="n">
-        <v>4</v>
+          <t>auditFloor</t>
+        </is>
+      </c>
+      <c r="B90" s="13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="C90" s="13" t="inlineStr">
         <is>
-          <t>D64: if the standing plan has not changed for a month, the month-end audit becomes a board review: three sign-offs (re-check two lines and the month's average day) and the board asks for a plan that tests a different fare or route before the next month runs.</t>
+          <t>D64: at each month end Finance sends an audit — re-check one existing figure from the pupil's own airline, chosen as the route with the most missed profit. Falls on the last day of each month; from December it comes with the monthly report.</t>
         </is>
       </c>
       <c r="D90" s="13" t="inlineStr">
@@ -56393,15 +57509,15 @@
     <row r="91">
       <c r="A91" s="13" t="inlineStr">
         <is>
-          <t>boardNudgeMissedShare</t>
+          <t>boardNudgeIdleWeeks</t>
         </is>
       </c>
       <c r="B91" s="13" t="n">
-        <v>0.2</v>
+        <v>4</v>
       </c>
       <c r="C91" s="13" t="inlineStr">
         <is>
-          <t>Missed profit as a share of the best plan available, over the month.</t>
+          <t>D64: if the standing plan has not changed for a month, the month-end audit becomes a board review: three sign-offs (re-check two lines and the month's average day) and the board asks for a plan that tests a different fare or route before the next month runs.</t>
         </is>
       </c>
       <c r="D91" s="13" t="inlineStr">
@@ -56413,13 +57529,17 @@
     <row r="92">
       <c r="A92" s="13" t="inlineStr">
         <is>
-          <t>boardReviewSignOffs</t>
+          <t>boardNudgeMissedShare</t>
         </is>
       </c>
       <c r="B92" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="C92" s="13" t="inlineStr"/>
+        <v>0.2</v>
+      </c>
+      <c r="C92" s="13" t="inlineStr">
+        <is>
+          <t>Missed profit as a share of the best plan available, over the month.</t>
+        </is>
+      </c>
       <c r="D92" s="13" t="inlineStr">
         <is>
           <t>live</t>
@@ -56429,17 +57549,13 @@
     <row r="93">
       <c r="A93" s="13" t="inlineStr">
         <is>
-          <t>seatFillGood</t>
+          <t>boardReviewSignOffs</t>
         </is>
       </c>
       <c r="B93" s="13" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="C93" s="13" t="inlineStr">
-        <is>
-          <t>D66: a service block is green at 80% of seats filled or more, amber from 50% to 79%, red under 50% (the neglect rule's line). Blocks show filled seats / seats on that plane.</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="C93" s="13" t="inlineStr"/>
       <c r="D93" s="13" t="inlineStr">
         <is>
           <t>live</t>
@@ -56449,13 +57565,17 @@
     <row r="94">
       <c r="A94" s="13" t="inlineStr">
         <is>
-          <t>seatFillMedium</t>
+          <t>seatFillGood</t>
         </is>
       </c>
       <c r="B94" s="13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C94" s="13" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="C94" s="13" t="inlineStr">
+        <is>
+          <t>D66: a service block is green at 80% of seats filled or more, amber from 50% to 79%, red under 50% (the neglect rule's line). Blocks show filled seats / seats on that plane.</t>
+        </is>
+      </c>
       <c r="D94" s="13" t="inlineStr">
         <is>
           <t>live</t>
@@ -56465,19 +57585,13 @@
     <row r="95">
       <c r="A95" s="13" t="inlineStr">
         <is>
-          <t>demandStripMode</t>
-        </is>
-      </c>
-      <c r="B95" s="13" t="inlineStr">
-        <is>
-          <t>follows the selected flight's route; otherwise route tabs (each route · All)</t>
-        </is>
-      </c>
-      <c r="C95" s="13" t="inlineStr">
-        <is>
-          <t>D100: the strip header always names what it shows ('Madrid · people who want to fly at £170'); 'All' is a tab, never the silent default.</t>
-        </is>
-      </c>
+          <t>seatFillMedium</t>
+        </is>
+      </c>
+      <c r="B95" s="13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C95" s="13" t="inlineStr"/>
       <c r="D95" s="13" t="inlineStr">
         <is>
           <t>live</t>
@@ -56487,17 +57601,17 @@
     <row r="96">
       <c r="A96" s="13" t="inlineStr">
         <is>
-          <t>planStudioSteps</t>
+          <t>demandStripMode</t>
         </is>
       </c>
       <c r="B96" s="13" t="inlineStr">
         <is>
-          <t>Choose routes | Set fares | Place services | Review seat fill</t>
+          <t>follows the selected flight's route; otherwise route tabs (each route · All)</t>
         </is>
       </c>
       <c r="C96" s="13" t="inlineStr">
         <is>
-          <t>D66: the four-step bar on the Operating Plan Studio. Step 4's three figures (seats likely filled, empty seats, turned away) are the same three the Sunday review reports as actuals.</t>
+          <t>D100: the strip header always names what it shows ('Madrid · people who want to fly at £170'); 'All' is a tab, never the silent default.</t>
         </is>
       </c>
       <c r="D96" s="13" t="inlineStr">
@@ -56509,17 +57623,17 @@
     <row r="97">
       <c r="A97" s="13" t="inlineStr">
         <is>
-          <t>flightDays</t>
+          <t>planStudioSteps</t>
         </is>
       </c>
       <c r="B97" s="13" t="inlineStr">
         <is>
-          <t>All week | Mon–Fri | Sat–Sun</t>
+          <t>Choose routes | Set fares | Place services | Review seat fill</t>
         </is>
       </c>
       <c r="C97" s="13" t="inlineStr">
         <is>
-          <t>D67: every flight in a standing plan has a Days setting, default All week, set in the flight editor. Weekend-only services exist for news such as the Dublin rugby; weekday-only services suit business routes that are quiet on Saturdays.</t>
+          <t>D66: the four-step bar on the Operating Plan Studio. Step 4's three figures (seats likely filled, empty seats, turned away) are the same three the Sunday review reports as actuals.</t>
         </is>
       </c>
       <c r="D97" s="13" t="inlineStr">
@@ -56531,17 +57645,17 @@
     <row r="98">
       <c r="A98" s="13" t="inlineStr">
         <is>
-          <t>flightDaysFromDay</t>
+          <t>flightDays</t>
         </is>
       </c>
       <c r="B98" s="13" t="inlineStr">
         <is>
-          <t>earned: week-2 review (day 14); fallback day 21</t>
+          <t>All week | Mon–Fri | Sat–Sun</t>
         </is>
       </c>
       <c r="C98" s="13" t="inlineStr">
         <is>
-          <t>D98: replaces the fixed day 8 in D67.</t>
+          <t>D67: every flight in a standing plan has a Days setting, default All week, set in the flight editor. Weekend-only services exist for news such as the Dublin rugby; weekday-only services suit business routes that are quiet on Saturdays.</t>
         </is>
       </c>
       <c r="D98" s="13" t="inlineStr">
@@ -56553,15 +57667,17 @@
     <row r="99">
       <c r="A99" s="13" t="inlineStr">
         <is>
-          <t>summaryWeekdayWeekend</t>
-        </is>
-      </c>
-      <c r="B99" s="13" t="b">
-        <v>1</v>
+          <t>flightDaysFromDay</t>
+        </is>
+      </c>
+      <c r="B99" s="13" t="inlineStr">
+        <is>
+          <t>earned: week-2 review (day 14); fallback day 21</t>
+        </is>
       </c>
       <c r="C99" s="13" t="inlineStr">
         <is>
-          <t>D67: the summary bar and the Sunday review show seat fill for weekdays and the weekend separately when any flight is not All week.</t>
+          <t>D98: replaces the fixed day 8 in D67.</t>
         </is>
       </c>
       <c r="D99" s="13" t="inlineStr">
@@ -56573,7 +57689,7 @@
     <row r="100">
       <c r="A100" s="13" t="inlineStr">
         <is>
-          <t>patternPlusExtras</t>
+          <t>summaryWeekdayWeekend</t>
         </is>
       </c>
       <c r="B100" s="13" t="b">
@@ -56581,7 +57697,7 @@
       </c>
       <c r="C100" s="13" t="inlineStr">
         <is>
-          <t>D67: a regular operating pattern is a whole day, and an aircraft may fly a pattern plus extra flights (for example Pattern A all week plus a Saturday Dublin service).</t>
+          <t>D67: the summary bar and the Sunday review show seat fill for weekdays and the weekend separately when any flight is not All week.</t>
         </is>
       </c>
       <c r="D100" s="13" t="inlineStr">
@@ -56593,15 +57709,15 @@
     <row r="101">
       <c r="A101" s="13" t="inlineStr">
         <is>
-          <t>shortHaulMaxKm</t>
-        </is>
-      </c>
-      <c r="B101" s="13" t="n">
-        <v>1000</v>
+          <t>patternPlusExtras</t>
+        </is>
+      </c>
+      <c r="B101" s="13" t="b">
+        <v>1</v>
       </c>
       <c r="C101" s="13" t="inlineStr">
         <is>
-          <t>D100: short haul up to 1,000 km; medium 1,000–4,000 km; long beyond (= longHaulFromKm). Madrid and Barcelona are medium haul.</t>
+          <t>D67: a regular operating pattern is a whole day, and an aircraft may fly a pattern plus extra flights (for example Pattern A all week plus a Saturday Dublin service).</t>
         </is>
       </c>
       <c r="D101" s="13" t="inlineStr">
@@ -56613,13 +57729,17 @@
     <row r="102">
       <c r="A102" s="13" t="inlineStr">
         <is>
-          <t>mediumHaulMaxKm</t>
+          <t>shortHaulMaxKm</t>
         </is>
       </c>
       <c r="B102" s="13" t="n">
-        <v>4000</v>
-      </c>
-      <c r="C102" s="13" t="inlineStr"/>
+        <v>1000</v>
+      </c>
+      <c r="C102" s="13" t="inlineStr">
+        <is>
+          <t>D100: short haul up to 1,000 km; medium 1,000–4,000 km; long beyond (= longHaulFromKm). Madrid and Barcelona are medium haul.</t>
+        </is>
+      </c>
       <c r="D102" s="13" t="inlineStr">
         <is>
           <t>live</t>
@@ -56629,17 +57749,13 @@
     <row r="103">
       <c r="A103" s="13" t="inlineStr">
         <is>
-          <t>longHaulFromKm</t>
+          <t>mediumHaulMaxKm</t>
         </is>
       </c>
       <c r="B103" s="13" t="n">
         <v>4000</v>
       </c>
-      <c r="C103" s="13" t="inlineStr">
-        <is>
-          <t>D68: a route over this distance is long haul: turnaround away longHaulTurnaroundMin, a flat second-crew charge longHaulCrewCost per service, arrival shown in local time.</t>
-        </is>
-      </c>
+      <c r="C103" s="13" t="inlineStr"/>
       <c r="D103" s="13" t="inlineStr">
         <is>
           <t>live</t>
@@ -56649,13 +57765,17 @@
     <row r="104">
       <c r="A104" s="13" t="inlineStr">
         <is>
-          <t>longHaulTurnaroundMin</t>
+          <t>longHaulFromKm</t>
         </is>
       </c>
       <c r="B104" s="13" t="n">
-        <v>120</v>
-      </c>
-      <c r="C104" s="13" t="inlineStr"/>
+        <v>4000</v>
+      </c>
+      <c r="C104" s="13" t="inlineStr">
+        <is>
+          <t>D68: a route over this distance is long haul: turnaround away longHaulTurnaroundMin, a flat second-crew charge longHaulCrewCost per service, arrival shown in local time.</t>
+        </is>
+      </c>
       <c r="D104" s="13" t="inlineStr">
         <is>
           <t>live</t>
@@ -56665,17 +57785,13 @@
     <row r="105">
       <c r="A105" s="13" t="inlineStr">
         <is>
-          <t>longHaulCrewCost</t>
+          <t>longHaulTurnaroundMin</t>
         </is>
       </c>
       <c r="B105" s="13" t="n">
-        <v>500</v>
-      </c>
-      <c r="C105" s="13" t="inlineStr">
-        <is>
-          <t>D73: flat second crew per long-haul service from 2031-01-06.</t>
-        </is>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="C105" s="13" t="inlineStr"/>
       <c r="D105" s="13" t="inlineStr">
         <is>
           <t>live</t>
@@ -56685,15 +57801,15 @@
     <row r="106">
       <c r="A106" s="13" t="inlineStr">
         <is>
-          <t>longHaulSameDayMaxKm</t>
+          <t>longHaulCrewCost</t>
         </is>
       </c>
       <c r="B106" s="13" t="n">
-        <v>6000</v>
+        <v>500</v>
       </c>
       <c r="C106" s="13" t="inlineStr">
         <is>
-          <t>D68: up to this distance a long-haul service goes out and back in one day (06:30 to about 21:30). Beyond it the route is an overnight rotation (Routes.rotation = overnight): out on day 1, back on day 2; the plane earns every second day and the day cost is paid both days. First overnight route: Delhi (June 2031).</t>
+          <t>D73: flat second crew per long-haul service from 2031-01-06.</t>
         </is>
       </c>
       <c r="D106" s="13" t="inlineStr">
@@ -56705,15 +57821,15 @@
     <row r="107">
       <c r="A107" s="13" t="inlineStr">
         <is>
-          <t>reputationPerHalfStar</t>
+          <t>longHaulSameDayMaxKm</t>
         </is>
       </c>
       <c r="B107" s="13" t="n">
-        <v>0.05</v>
+        <v>6000</v>
       </c>
       <c r="C107" s="13" t="inlineStr">
         <is>
-          <t>D69: from 2031-01-06, demand on every route × (1 + 0.05 × half-stars above or below 3). Five stars +20%, one star −20%.</t>
+          <t>D68: up to this distance a long-haul service goes out and back in one day (06:30 to about 21:30). Beyond it the route is an overnight rotation (Routes.rotation = overnight): out on day 1, back on day 2; the plane earns every second day and the day cost is paid both days. First overnight route: Delhi (June 2031).</t>
         </is>
       </c>
       <c r="D107" s="13" t="inlineStr">
@@ -56725,15 +57841,15 @@
     <row r="108">
       <c r="A108" s="13" t="inlineStr">
         <is>
-          <t>reputationBankedFromAutumn</t>
-        </is>
-      </c>
-      <c r="B108" s="13" t="b">
-        <v>1</v>
+          <t>reputationPerHalfStar</t>
+        </is>
+      </c>
+      <c r="B108" s="13" t="n">
+        <v>0.05</v>
       </c>
       <c r="C108" s="13" t="inlineStr">
         <is>
-          <t>D30: the autumn's star changes are applied silently and revealed on 2031-01-06.</t>
+          <t>D69: from 2031-01-06, demand on every route × (1 + 0.05 × half-stars above or below 3). Five stars +20%, one star −20%.</t>
         </is>
       </c>
       <c r="D108" s="13" t="inlineStr">
@@ -56745,17 +57861,15 @@
     <row r="109">
       <c r="A109" s="13" t="inlineStr">
         <is>
-          <t>airlineTypeMode</t>
-        </is>
-      </c>
-      <c r="B109" s="13" t="inlineStr">
-        <is>
-          <t>light</t>
-        </is>
+          <t>reputationBankedFromAutumn</t>
+        </is>
+      </c>
+      <c r="B109" s="13" t="b">
+        <v>1</v>
       </c>
       <c r="C109" s="13" t="inlineStr">
         <is>
-          <t>D77: the light profiles (Premium two higher fare options and 1.5× stars; Value one lower fare option, the bag fee, 0.75× stars; Full Service unchanged) are permanent. No full profiles.</t>
+          <t>D30: the autumn's star changes are applied silently and revealed on 2031-01-06.</t>
         </is>
       </c>
       <c r="D109" s="13" t="inlineStr">
@@ -56767,15 +57881,17 @@
     <row r="110">
       <c r="A110" s="13" t="inlineStr">
         <is>
-          <t>premiumExtraFareSteps</t>
-        </is>
-      </c>
-      <c r="B110" s="13" t="n">
-        <v>2</v>
+          <t>airlineTypeMode</t>
+        </is>
+      </c>
+      <c r="B110" s="13" t="inlineStr">
+        <is>
+          <t>light</t>
+        </is>
       </c>
       <c r="C110" s="13" t="inlineStr">
         <is>
-          <t>Premium: the Routes demand table's two steps above today's top fare option become available.</t>
+          <t>D77: the light profiles (Premium two higher fare options and 1.5× stars; Value one lower fare option, the bag fee, 0.75× stars; Full Service unchanged) are permanent. No full profiles.</t>
         </is>
       </c>
       <c r="D110" s="13" t="inlineStr">
@@ -56787,15 +57903,15 @@
     <row r="111">
       <c r="A111" s="13" t="inlineStr">
         <is>
-          <t>valueLowerFareSteps</t>
+          <t>premiumExtraFareSteps</t>
         </is>
       </c>
       <c r="B111" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C111" s="13" t="inlineStr">
         <is>
-          <t>Value: one step below today's lowest fare option becomes available (demand table extended downwards).</t>
+          <t>Premium: the Routes demand table's two steps above today's top fare option become available.</t>
         </is>
       </c>
       <c r="D111" s="13" t="inlineStr">
@@ -56807,15 +57923,15 @@
     <row r="112">
       <c r="A112" s="13" t="inlineStr">
         <is>
-          <t>premiumStarRate</t>
+          <t>valueLowerFareSteps</t>
         </is>
       </c>
       <c r="B112" s="13" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="C112" s="13" t="inlineStr">
         <is>
-          <t>Premium gains and loses stars 1.5× as fast; Value 0.75×; Full Service 1×.</t>
+          <t>Value: one step below today's lowest fare option becomes available (demand table extended downwards).</t>
         </is>
       </c>
       <c r="D112" s="13" t="inlineStr">
@@ -56827,13 +57943,17 @@
     <row r="113">
       <c r="A113" s="13" t="inlineStr">
         <is>
-          <t>valueStarRate</t>
+          <t>premiumStarRate</t>
         </is>
       </c>
       <c r="B113" s="13" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="C113" s="13" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="C113" s="13" t="inlineStr">
+        <is>
+          <t>Premium gains and loses stars 1.5× as fast; Value 0.75×; Full Service 1×.</t>
+        </is>
+      </c>
       <c r="D113" s="13" t="inlineStr">
         <is>
           <t>live</t>
@@ -56843,17 +57963,13 @@
     <row r="114">
       <c r="A114" s="13" t="inlineStr">
         <is>
-          <t>extrasBagFee</t>
+          <t>valueStarRate</t>
         </is>
       </c>
       <c r="B114" s="13" t="n">
-        <v>20</v>
-      </c>
-      <c r="C114" s="13" t="inlineStr">
-        <is>
-          <t>D71: Value airline only, from 2031-01-06. Bag fee £20.</t>
-        </is>
-      </c>
+        <v>0.75</v>
+      </c>
+      <c r="C114" s="13" t="inlineStr"/>
       <c r="D114" s="13" t="inlineStr">
         <is>
           <t>live</t>
@@ -56863,15 +57979,15 @@
     <row r="115">
       <c r="A115" s="13" t="inlineStr">
         <is>
-          <t>extrasBagTakeUp</t>
+          <t>extrasBagFee</t>
         </is>
       </c>
       <c r="B115" s="13" t="n">
-        <v>0.4</v>
+        <v>20</v>
       </c>
       <c r="C115" s="13" t="inlineStr">
         <is>
-          <t>Four in ten passengers pay it. Revenue = passengers × 0.4 × £20, a modelling line after the first time (one hand sum on the first long-haul week).</t>
+          <t>D71: Value airline only, from 2031-01-06. Bag fee £20.</t>
         </is>
       </c>
       <c r="D115" s="13" t="inlineStr">
@@ -56883,17 +57999,15 @@
     <row r="116">
       <c r="A116" s="13" t="inlineStr">
         <is>
-          <t>timeZonesFromDate</t>
-        </is>
-      </c>
-      <c r="B116" s="13" t="inlineStr">
-        <is>
-          <t>2031-01-06</t>
-        </is>
+          <t>extrasBagTakeUp</t>
+        </is>
+      </c>
+      <c r="B116" s="13" t="n">
+        <v>0.4</v>
       </c>
       <c r="C116" s="13" t="inlineStr">
         <is>
-          <t>D24: arrival cards show local time from long haul: London time ± the route's utc offset.</t>
+          <t>Four in ten passengers pay it. Revenue = passengers × 0.4 × £20, a modelling line after the first time (one hand sum on the first long-haul week).</t>
         </is>
       </c>
       <c r="D116" s="13" t="inlineStr">
@@ -56905,15 +58019,17 @@
     <row r="117">
       <c r="A117" s="13" t="inlineStr">
         <is>
-          <t>chapter2SetUpDays</t>
-        </is>
-      </c>
-      <c r="B117" s="13" t="n">
-        <v>7</v>
+          <t>timeZonesFromDate</t>
+        </is>
+      </c>
+      <c r="B117" s="13" t="inlineStr">
+        <is>
+          <t>2031-01-06</t>
+        </is>
       </c>
       <c r="C117" s="13" t="inlineStr">
         <is>
-          <t>Days 127–133: plan, run, review of the first week, one day at a time (the Calendar's rows). Then weeks, then months from February.</t>
+          <t>D24: arrival cards show local time from long haul: London time ± the route's utc offset.</t>
         </is>
       </c>
       <c r="D117" s="13" t="inlineStr">
@@ -56925,17 +58041,15 @@
     <row r="118">
       <c r="A118" s="13" t="inlineStr">
         <is>
-          <t>captainsChallengeFirst</t>
-        </is>
-      </c>
-      <c r="B118" s="13" t="inlineStr">
-        <is>
-          <t>2031-01-06</t>
-        </is>
+          <t>chapter2SetUpDays</t>
+        </is>
+      </c>
+      <c r="B118" s="13" t="n">
+        <v>7</v>
       </c>
       <c r="C118" s="13" t="inlineStr">
         <is>
-          <t>D36: one a term, optional, with a reward. Challenges 1 and 2 live.</t>
+          <t>Days 127–133: plan, run, review of the first week, one day at a time (the Calendar's rows). Then weeks, then months from February.</t>
         </is>
       </c>
       <c r="D118" s="13" t="inlineStr">
@@ -56947,17 +58061,17 @@
     <row r="119">
       <c r="A119" s="13" t="inlineStr">
         <is>
-          <t>hunt1</t>
+          <t>captainsChallengeFirst</t>
         </is>
       </c>
       <c r="B119" s="13" t="inlineStr">
         <is>
-          <t>2031-04-21</t>
+          <t>2031-01-06</t>
         </is>
       </c>
       <c r="C119" s="13" t="inlineStr">
         <is>
-          <t>D39: first hunts live — h2 (fuel invoice) in the spring run, h1 (year-1 accounts) at the August review.</t>
+          <t>D36: one a term, optional, with a reward. Challenges 1 and 2 live.</t>
         </is>
       </c>
       <c r="D119" s="13" t="inlineStr">
@@ -56969,15 +58083,17 @@
     <row r="120">
       <c r="A120" s="13" t="inlineStr">
         <is>
-          <t>chapter1BuyOnly</t>
-        </is>
-      </c>
-      <c r="B120" s="13" t="b">
-        <v>1</v>
+          <t>hunt1</t>
+        </is>
+      </c>
+      <c r="B120" s="13" t="inlineStr">
+        <is>
+          <t>2031-04-21</t>
+        </is>
       </c>
       <c r="C120" s="13" t="inlineStr">
         <is>
-          <t>D76: in chapter 1 planes are bought outright only. No rent, no launch-deal finance. The week-2 decision is buy a smaller plane now or wait for a bigger one; the week-2 hand sum is time to afford: (price − cash) ÷ profit a day.</t>
+          <t>D39: first hunts live — h2 (fuel invoice) in the spring run, h1 (year-1 accounts) at the August review.</t>
         </is>
       </c>
       <c r="D120" s="13" t="inlineStr">
@@ -56989,17 +58105,15 @@
     <row r="121">
       <c r="A121" s="13" t="inlineStr">
         <is>
-          <t>timeToAffordSum</t>
-        </is>
-      </c>
-      <c r="B121" s="13" t="inlineStr">
-        <is>
-          <t>(price − cash) ÷ profit a day = days to wait</t>
-        </is>
+          <t>chapter1BuyOnly</t>
+        </is>
+      </c>
+      <c r="B121" s="13" t="b">
+        <v>1</v>
       </c>
       <c r="C121" s="13" t="inlineStr">
         <is>
-          <t>D76: Calculate the first time (week 2), Build after.</t>
+          <t>D76: in chapter 1 planes are bought outright only. No rent, no launch-deal finance. The week-2 decision is buy a smaller plane now or wait for a bigger one; the week-2 hand sum is time to afford: (price − cash) ÷ profit a day.</t>
         </is>
       </c>
       <c r="D121" s="13" t="inlineStr">
@@ -57011,17 +58125,17 @@
     <row r="122">
       <c r="A122" s="13" t="inlineStr">
         <is>
-          <t>bigPlanePriceRule</t>
+          <t>timeToAffordSum</t>
         </is>
       </c>
       <c r="B122" s="13" t="inlineStr">
         <is>
-          <t>doubled from v5.2</t>
+          <t>(price − cash) ÷ profit a day = days to wait</t>
         </is>
       </c>
       <c r="C122" s="13" t="inlineStr">
         <is>
-          <t>D78: from the 757 up, buy prices are doubled so the A380 needs finance in chapter 4 (757 £3m, 787 £12m, A340 £10m, 777 £24m, A350 £30m, 747 £40m, A380 £60m). Leases unchanged.</t>
+          <t>D76: Calculate the first time (week 2), Build after.</t>
         </is>
       </c>
       <c r="D122" s="13" t="inlineStr">
@@ -57033,17 +58147,17 @@
     <row r="123">
       <c r="A123" s="13" t="inlineStr">
         <is>
-          <t>twoLegRotation</t>
+          <t>bigPlanePriceRule</t>
         </is>
       </c>
       <c r="B123" s="13" t="inlineStr">
         <is>
-          <t>Sydney via Singapore</t>
+          <t>doubled from v5.2</t>
         </is>
       </c>
       <c r="C123" s="13" t="inlineStr">
         <is>
-          <t>D79: a two-leg route lists its legs (Routes.legs) and takes rotationDays (4): London–Singapore on day 1, Singapore–Sydney on day 2, back the same way. Revenue is the through fare × passengers once per rotation; each leg is costed separately (flying, fuel, landing at the stop both ways); the day cost is paid every day; the £500 crew charge applies per leg.</t>
+          <t>D78: from the 757 up, buy prices are doubled so the A380 needs finance in chapter 4 (757 £3m, 787 £12m, A340 £10m, 777 £24m, A350 £30m, 747 £40m, A380 £60m). Leases unchanged.</t>
         </is>
       </c>
       <c r="D123" s="13" t="inlineStr">
@@ -57055,15 +58169,17 @@
     <row r="124">
       <c r="A124" s="13" t="inlineStr">
         <is>
-          <t>chapter3SetUpDays</t>
-        </is>
-      </c>
-      <c r="B124" s="13" t="n">
-        <v>7</v>
+          <t>twoLegRotation</t>
+        </is>
+      </c>
+      <c r="B124" s="13" t="inlineStr">
+        <is>
+          <t>Sydney via Singapore</t>
+        </is>
       </c>
       <c r="C124" s="13" t="inlineStr">
         <is>
-          <t>Days 365–371, as the Calendar's rows: plan, run, review. Then months.</t>
+          <t>D79: a two-leg route lists its legs (Routes.legs) and takes rotationDays (4): London–Singapore on day 1, Singapore–Sydney on day 2, back the same way. Revenue is the through fare × passengers once per rotation; each leg is costed separately (flying, fuel, landing at the stop both ways); the day cost is paid every day; the £500 crew charge applies per leg.</t>
         </is>
       </c>
       <c r="D124" s="13" t="inlineStr">
@@ -57075,103 +58191,101 @@
     <row r="125">
       <c r="A125" s="13" t="inlineStr">
         <is>
+          <t>chapter3SetUpDays</t>
+        </is>
+      </c>
+      <c r="B125" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="C125" s="13" t="inlineStr">
+        <is>
+          <t>Days 365–371, as the Calendar's rows: plan, run, review. Then months.</t>
+        </is>
+      </c>
+      <c r="D125" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="13" t="inlineStr">
+        <is>
           <t>timeToAffordWeekly</t>
         </is>
       </c>
-      <c r="B125" s="13" t="inlineStr">
+      <c r="B126" s="13" t="inlineStr">
         <is>
           <t>(price − cash) ÷ profit a week = weeks to wait</t>
         </is>
       </c>
-      <c r="C125" s="13" t="inlineStr">
+      <c r="C126" s="13" t="inlineStr">
         <is>
           <t>Chapter 3's version of the time-to-afford sum (chapter 1 used days). Calculate the first time, Build after.</t>
         </is>
       </c>
-      <c r="D125" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="14" t="inlineStr">
-        <is>
-          <t>marketingCostShare</t>
-        </is>
-      </c>
-      <c r="B126" s="14" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C126" s="14" t="inlineStr">
-        <is>
-          <t>Chapter 5 placeholder: spend a tenth of a day's profit on a route each week for +10% demand on it while it runs (D38). Values confirmed when chapter 5 is designed.</t>
-        </is>
-      </c>
-      <c r="D126" s="14" t="inlineStr">
-        <is>
-          <t>placeholder</t>
+      <c r="D126" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="14" t="inlineStr">
         <is>
+          <t>marketingCostShare</t>
+        </is>
+      </c>
+      <c r="B127" s="14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C127" s="14" t="inlineStr">
+        <is>
+          <t>Chapter 5 placeholder: spend a tenth of a day's profit on a route each week for +10% demand on it while it runs (D38). Values confirmed when chapter 5 is designed.</t>
+        </is>
+      </c>
+      <c r="D127" s="14" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="14" t="inlineStr">
+        <is>
           <t>rivalEntryRule</t>
         </is>
       </c>
-      <c r="B127" s="14" t="inlineStr">
+      <c r="B128" s="14" t="inlineStr">
         <is>
           <t>most profitable route, fare × 0.9, from 2033-09-05</t>
         </is>
       </c>
-      <c r="C127" s="14" t="inlineStr">
+      <c r="C128" s="14" t="inlineStr">
         <is>
           <t>Chapter 5 placeholder: Red Kite enters the pupil's most profitable route at nine-tenths of his fare; the switching rule (1 in 10 per £10 dearer) applies on that route from then on (D38).</t>
         </is>
       </c>
-      <c r="D127" s="14" t="inlineStr">
+      <c r="D128" s="14" t="inlineStr">
         <is>
           <t>placeholder</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="13" t="inlineStr">
-        <is>
-          <t>overdraftAtLimit</t>
-        </is>
-      </c>
-      <c r="B128" s="13" t="inlineStr">
-        <is>
-          <t>purchases and fuel orders blocked; flights continue</t>
-        </is>
-      </c>
-      <c r="C128" s="13" t="inlineStr">
-        <is>
-          <t>At the overdraft limit: no purchase, lease or fuel order that would go further; the standing plan keeps flying (fuel bought as emergency fuel if the tank is empty); the statement shows 'Overdrawn £X of £Y'; two months overdrawn triggers the board review (D64).</t>
-        </is>
-      </c>
-      <c r="D128" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="13" t="inlineStr">
         <is>
-          <t>buyLeasedPlane</t>
+          <t>overdraftAtLimit</t>
         </is>
       </c>
       <c r="B129" s="13" t="inlineStr">
         <is>
-          <t>yes, at list price; the lease stops that day</t>
+          <t>purchases and fuel orders blocked; flights continue</t>
         </is>
       </c>
       <c r="C129" s="13" t="inlineStr">
         <is>
-          <t>D81: a plane the pupil is renting can be bought from buyFromDate at the Aircraft list price; the rent stops on the day of purchase.</t>
+          <t>At the overdraft limit: no purchase, lease or fuel order that would go further; the standing plan keeps flying (fuel bought as emergency fuel if the tank is empty); the statement shows 'Overdrawn £X of £Y'; two months overdrawn triggers the board review (D64).</t>
         </is>
       </c>
       <c r="D129" s="13" t="inlineStr">
@@ -57183,17 +58297,17 @@
     <row r="130">
       <c r="A130" s="13" t="inlineStr">
         <is>
-          <t>leaseReturn</t>
+          <t>buyLeasedPlane</t>
         </is>
       </c>
       <c r="B130" s="13" t="inlineStr">
         <is>
-          <t>at a month end, no charge</t>
+          <t>yes, at list price; the lease stops that day</t>
         </is>
       </c>
       <c r="C130" s="13" t="inlineStr">
         <is>
-          <t>D81: a rented plane can be handed back on the last day of any month from the Fleet desk; the rent stops; it leaves the timetable. Owned planes cannot be sold (D25).</t>
+          <t>D81: a plane the pupil is renting can be bought from buyFromDate at the Aircraft list price; the rent stops on the day of purchase.</t>
         </is>
       </c>
       <c r="D130" s="13" t="inlineStr">
@@ -57205,17 +58319,17 @@
     <row r="131">
       <c r="A131" s="13" t="inlineStr">
         <is>
-          <t>challengeRewardRule</t>
+          <t>leaseReturn</t>
         </is>
       </c>
       <c r="B131" s="13" t="inlineStr">
         <is>
-          <t>a share of a day's profit, or stars</t>
+          <t>at a month end, no charge</t>
         </is>
       </c>
       <c r="C131" s="13" t="inlineStr">
         <is>
-          <t>D81: from chapter 2 a Captain's challenge rewards a share of a day's profit (Challenges.rewardShare) or half a star, never a fixed pound sum, so rewards keep pace with the airline.</t>
+          <t>D81: a rented plane can be handed back on the last day of any month from the Fleet desk; the rent stops; it leaves the timetable. Owned planes cannot be sold (D25).</t>
         </is>
       </c>
       <c r="D131" s="13" t="inlineStr">
@@ -57227,17 +58341,17 @@
     <row r="132">
       <c r="A132" s="13" t="inlineStr">
         <is>
-          <t>missedHuntH1Effect</t>
+          <t>challengeRewardRule</t>
         </is>
       </c>
       <c r="B132" s="13" t="inlineStr">
         <is>
-          <t>chapter-3 opening cash shown £2,000 high until the first audit</t>
+          <t>a share of a day's profit, or stars</t>
         </is>
       </c>
       <c r="C132" s="13" t="inlineStr">
         <is>
-          <t>D81: if h1 was missed, Finance's cash figure on chapter 3's opening plan page reads £2,000 above the true balance; the first month-end audit corrects it and says why.</t>
+          <t>D81: from chapter 2 a Captain's challenge rewards a share of a day's profit (Challenges.rewardShare) or half a star, never a fixed pound sum, so rewards keep pace with the airline.</t>
         </is>
       </c>
       <c r="D132" s="13" t="inlineStr">
@@ -57249,17 +58363,17 @@
     <row r="133">
       <c r="A133" s="13" t="inlineStr">
         <is>
-          <t>financeShape</t>
+          <t>missedHuntH1Effect</t>
         </is>
       </c>
       <c r="B133" s="13" t="inlineStr">
         <is>
-          <t>deposit, then 40 monthly payments</t>
+          <t>chapter-3 opening cash shown £2,000 high until the first audit</t>
         </is>
       </c>
       <c r="C133" s="13" t="inlineStr">
         <is>
-          <t>D83: payments on the first of each month from the planning page; shown on the statement as 'Finance: A380 £1,000,000 (month 7 of 40)'. Missing a payment is not possible: it is taken before anything else, into the overdraft if need be.</t>
+          <t>D81: if h1 was missed, Finance's cash figure on chapter 3's opening plan page reads £2,000 above the true balance; the first month-end audit corrects it and says why.</t>
         </is>
       </c>
       <c r="D133" s="13" t="inlineStr">
@@ -57271,15 +58385,17 @@
     <row r="134">
       <c r="A134" s="13" t="inlineStr">
         <is>
-          <t>chapter4SetUpDays</t>
-        </is>
-      </c>
-      <c r="B134" s="13" t="n">
-        <v>7</v>
+          <t>financeShape</t>
+        </is>
+      </c>
+      <c r="B134" s="13" t="inlineStr">
+        <is>
+          <t>deposit, then 40 monthly payments</t>
+        </is>
       </c>
       <c r="C134" s="13" t="inlineStr">
         <is>
-          <t>Days 736–742, as the Calendar's rows. The gap 1–5 September 2032 after chapter 3's review flies as one short run ('the end of the summer'); chapter 4 opens Monday 6 September.</t>
+          <t>D83: payments on the first of each month from the planning page; shown on the statement as 'Finance: A380 £1,000,000 (month 7 of 40)'. Missing a payment is not possible: it is taken before anything else, into the overdraft if need be.</t>
         </is>
       </c>
       <c r="D134" s="13" t="inlineStr">
@@ -57291,17 +58407,15 @@
     <row r="135">
       <c r="A135" s="13" t="inlineStr">
         <is>
-          <t>a380FillQuestion</t>
-        </is>
-      </c>
-      <c r="B135" s="13" t="inlineStr">
-        <is>
-          <t>demand ÷ seats</t>
-        </is>
+          <t>chapter4SetUpDays</t>
+        </is>
+      </c>
+      <c r="B135" s="13" t="n">
+        <v>7</v>
       </c>
       <c r="C135" s="13" t="inlineStr">
         <is>
-          <t>D84: the chapter's sum. Does a 500-seat plane fill? Passengers wanting to fly at the fare ÷ 500, as a percentage; the review shows the A380's fill each month.</t>
+          <t>Days 736–742, as the Calendar's rows. The gap 1–5 September 2032 after chapter 3's review flies as one short run ('the end of the summer'); chapter 4 opens Monday 6 September.</t>
         </is>
       </c>
       <c r="D135" s="13" t="inlineStr">
@@ -57313,17 +58427,17 @@
     <row r="136">
       <c r="A136" s="13" t="inlineStr">
         <is>
-          <t>campaignProjectDate</t>
+          <t>a380FillQuestion</t>
         </is>
       </c>
       <c r="B136" s="13" t="inlineStr">
         <is>
-          <t>2032-10-04</t>
+          <t>demand ÷ seats</t>
         </is>
       </c>
       <c r="C136" s="13" t="inlineStr">
         <is>
-          <t>D82: the A380 launch campaign is one standalone project, started in the first month of chapter 4 and run over several sessions with the game paused; its result applies from the launch date the pupil chooses (Campaign sheet).</t>
+          <t>D84: the chapter's sum. Does a 500-seat plane fill? Passengers wanting to fly at the fare ÷ 500, as a percentage; the review shows the A380's fill each month.</t>
         </is>
       </c>
       <c r="D136" s="13" t="inlineStr">
@@ -57335,15 +58449,17 @@
     <row r="137">
       <c r="A137" s="13" t="inlineStr">
         <is>
-          <t>workingOnPaper</t>
-        </is>
-      </c>
-      <c r="B137" s="13" t="b">
-        <v>1</v>
+          <t>campaignProjectDate</t>
+        </is>
+      </c>
+      <c r="B137" s="13" t="inlineStr">
+        <is>
+          <t>2032-10-04</t>
+        </is>
       </c>
       <c r="C137" s="13" t="inlineStr">
         <is>
-          <t>D86: the pupil works on paper. The workbench is an answer box (question in black, answer typed, tick or error note); no column frames, no cell-by-cell capture. The method picker becomes an optional reference card showing the shape of a method, not an input.</t>
+          <t>D82: the A380 launch campaign is one standalone project, started in the first month of chapter 4 and run over several sessions with the game paused; its result applies from the launch date the pupil chooses (Campaign sheet).</t>
         </is>
       </c>
       <c r="D137" s="13" t="inlineStr">
@@ -57355,7 +58471,7 @@
     <row r="138">
       <c r="A138" s="13" t="inlineStr">
         <is>
-          <t>twoTriesRule</t>
+          <t>workingOnPaper</t>
         </is>
       </c>
       <c r="B138" s="13" t="b">
@@ -57363,7 +58479,7 @@
       </c>
       <c r="C138" s="13" t="inlineStr">
         <is>
-          <t>D86: a wrong answer gets the error note and one more try; a second wrong answer shows the correct figure and the game moves on. The record keeps both attempts.</t>
+          <t>D86: the pupil works on paper. The workbench is an answer box (question in black, answer typed, tick or error note); no column frames, no cell-by-cell capture. The method picker becomes an optional reference card showing the shape of a method, not an input.</t>
         </is>
       </c>
       <c r="D138" s="13" t="inlineStr">
@@ -57375,17 +58491,15 @@
     <row r="139">
       <c r="A139" s="13" t="inlineStr">
         <is>
-          <t>sumNumbering</t>
-        </is>
-      </c>
-      <c r="B139" s="13" t="inlineStr">
-        <is>
-          <t>running number per pupil, never reset</t>
-        </is>
+          <t>twoTriesRule</t>
+        </is>
+      </c>
+      <c r="B139" s="13" t="b">
+        <v>1</v>
       </c>
       <c r="C139" s="13" t="inlineStr">
         <is>
-          <t>D86: every sign-off and review Build step shows 'Sum N · Week W · what it is' in the answer box; the pupil writes N beside his working on paper; the record and printout carry the same N. Practice questions use a separate letter series (P1, P2 …) so they don't disturb the count.</t>
+          <t>D86: a wrong answer gets the error note and one more try; a second wrong answer shows the correct figure and the game moves on. The record keeps both attempts.</t>
         </is>
       </c>
       <c r="D139" s="13" t="inlineStr">
@@ -57397,15 +58511,17 @@
     <row r="140">
       <c r="A140" s="13" t="inlineStr">
         <is>
-          <t>operationsCheck</t>
-        </is>
-      </c>
-      <c r="B140" s="13" t="b">
-        <v>1</v>
+          <t>sumNumbering</t>
+        </is>
+      </c>
+      <c r="B140" s="13" t="inlineStr">
+        <is>
+          <t>running number per pupil, never reset</t>
+        </is>
       </c>
       <c r="C140" s="13" t="inlineStr">
         <is>
-          <t>D87: before Run week, a check shows the one or two PlanTips with the most money at stake, each with its action and 'Run anyway'. Never blocks; the action is the visually dominant button.</t>
+          <t>D86: every sign-off and review Build step shows 'Sum N · Week W · what it is' in the answer box; the pupil writes N beside his working on paper; the record and printout carry the same N. Practice questions use a separate letter series (P1, P2 …) so they don't disturb the count.</t>
         </is>
       </c>
       <c r="D140" s="13" t="inlineStr">
@@ -57417,7 +58533,7 @@
     <row r="141">
       <c r="A141" s="13" t="inlineStr">
         <is>
-          <t>blockPreview</t>
+          <t>operationsCheck</t>
         </is>
       </c>
       <c r="B141" s="13" t="b">
@@ -57425,7 +58541,7 @@
       </c>
       <c r="C141" s="13" t="inlineStr">
         <is>
-          <t>D87: a service block shows its expected fill while being moved (Earlier / Later or drag) and a one-line 'this change: seats a → b, profit £x → £y' after the drop; a full service with passengers turned away shows the fare chips with expected fill at each.</t>
+          <t>D87: before Run week, a check shows the one or two PlanTips with the most money at stake, each with its action and 'Run anyway'. Never blocks; the action is the visually dominant button.</t>
         </is>
       </c>
       <c r="D141" s="13" t="inlineStr">
@@ -57437,17 +58553,15 @@
     <row r="142">
       <c r="A142" s="13" t="inlineStr">
         <is>
-          <t>missedProfitDisplay</t>
-        </is>
-      </c>
-      <c r="B142" s="13" t="inlineStr">
-        <is>
-          <t>words for the pupil; figures for the teacher</t>
-        </is>
+          <t>blockPreview</t>
+        </is>
+      </c>
+      <c r="B142" s="13" t="b">
+        <v>1</v>
       </c>
       <c r="C142" s="13" t="inlineStr">
         <is>
-          <t>D87: the pupil's review says 'a large improvement is available' (gap &gt; 30% of the best), 'a better plan is available' (10–30%) or 'a good plan' (&lt; 10%); the exact best-plan figure appears on the teacher panel and the printed review only.</t>
+          <t>D87: a service block shows its expected fill while being moved (Earlier / Later or drag) and a one-line 'this change: seats a → b, profit £x → £y' after the drop; a full service with passengers turned away shows the fare chips with expected fill at each.</t>
         </is>
       </c>
       <c r="D142" s="13" t="inlineStr">
@@ -57459,15 +58573,17 @@
     <row r="143">
       <c r="A143" s="13" t="inlineStr">
         <is>
-          <t>reviewFixLink</t>
-        </is>
-      </c>
-      <c r="B143" s="13" t="b">
-        <v>1</v>
+          <t>missedProfitDisplay</t>
+        </is>
+      </c>
+      <c r="B143" s="13" t="inlineStr">
+        <is>
+          <t>words for the pupil; figures for the teacher</t>
+        </is>
       </c>
       <c r="C143" s="13" t="inlineStr">
         <is>
-          <t>D87: the Sunday review names the biggest missed opportunity (the tip with the most money at stake over the week) and offers 'Fix next week's {route} plan', which opens the carried-over plan with that route selected and its demand curve shown.</t>
+          <t>D87: the pupil's review says 'a large improvement is available' (gap &gt; 30% of the best), 'a better plan is available' (10–30%) or 'a good plan' (&lt; 10%); the exact best-plan figure appears on the teacher panel and the printed review only.</t>
         </is>
       </c>
       <c r="D143" s="13" t="inlineStr">
@@ -57479,17 +58595,15 @@
     <row r="144">
       <c r="A144" s="13" t="inlineStr">
         <is>
-          <t>planningSupport</t>
-        </is>
-      </c>
-      <c r="B144" s="13" t="inlineStr">
-        <is>
-          <t>guided</t>
-        </is>
+          <t>reviewFixLink</t>
+        </is>
+      </c>
+      <c r="B144" s="13" t="b">
+        <v>1</v>
       </c>
       <c r="C144" s="13" t="inlineStr">
         <is>
-          <t>D87: teacher dial — guided | supported | independent | management. guided: the check names the issue and offers 2–3 experiments (change the fare / the times / the number of services / the aircraft) with a prediction step; supported: names the issue only, the pupil chooses what to change; independent: shows the data and the modelling controls, no issue named; management: flags only losses and exceptions. Default guided for chapter 1; the dial is per pupil.</t>
+          <t>D87: the Sunday review names the biggest missed opportunity (the tip with the most money at stake over the week) and offers 'Fix next week's {route} plan', which opens the carried-over plan with that route selected and its demand curve shown.</t>
         </is>
       </c>
       <c r="D144" s="13" t="inlineStr">
@@ -57501,17 +58615,17 @@
     <row r="145">
       <c r="A145" s="13" t="inlineStr">
         <is>
-          <t>experimentFlow</t>
+          <t>planningSupport</t>
         </is>
       </c>
       <c r="B145" s="13" t="inlineStr">
         <is>
-          <t>choose variable → predict → change one thing → model → compare → decide</t>
+          <t>guided</t>
         </is>
       </c>
       <c r="C145" s="13" t="inlineStr">
         <is>
-          <t>D87: in guided and supported levels every test is one variable at a time; the prediction (more / fewer / about the same seats; higher / lower / about the same profit) is recorded and compared; never a 'recommended' plan.</t>
+          <t>D87: teacher dial — guided | supported | independent | management. guided: the check names the issue and offers 2–3 experiments (change the fare / the times / the number of services / the aircraft) with a prediction step; supported: names the issue only, the pupil chooses what to change; independent: shows the data and the modelling controls, no issue named; management: flags only losses and exceptions. Default guided for chapter 1; the dial is per pupil.</t>
         </is>
       </c>
       <c r="D145" s="13" t="inlineStr">
@@ -57523,15 +58637,17 @@
     <row r="146">
       <c r="A146" s="13" t="inlineStr">
         <is>
-          <t>helpMeInvestigate</t>
-        </is>
-      </c>
-      <c r="B146" s="13" t="b">
-        <v>1</v>
+          <t>experimentFlow</t>
+        </is>
+      </c>
+      <c r="B146" s="13" t="inlineStr">
+        <is>
+          <t>choose variable → predict → change one thing → model → compare → decide</t>
+        </is>
       </c>
       <c r="C146" s="13" t="inlineStr">
         <is>
-          <t>A small button on the plan and the review that reopens the guided experiment at any support level.</t>
+          <t>D87: in guided and supported levels every test is one variable at a time; the prediction (more / fewer / about the same seats; higher / lower / about the same profit) is recorded and compared; never a 'recommended' plan.</t>
         </is>
       </c>
       <c r="D146" s="13" t="inlineStr">
@@ -57543,7 +58659,7 @@
     <row r="147">
       <c r="A147" s="13" t="inlineStr">
         <is>
-          <t>planImprovedBanner</t>
+          <t>helpMeInvestigate</t>
         </is>
       </c>
       <c r="B147" s="13" t="b">
@@ -57551,7 +58667,7 @@
       </c>
       <c r="C147" s="13" t="inlineStr">
         <is>
-          <t>D87: when the projected result improves after a change, a small 'Plan improved: seats a → b, result £x → £y' confirmation above Run week.</t>
+          <t>A small button on the plan and the review that reopens the guided experiment at any support level.</t>
         </is>
       </c>
       <c r="D147" s="13" t="inlineStr">
@@ -57563,17 +58679,15 @@
     <row r="148">
       <c r="A148" s="13" t="inlineStr">
         <is>
-          <t>whatWasItWorth</t>
-        </is>
-      </c>
-      <c r="B148" s="13" t="inlineStr">
-        <is>
-          <t>change per unit × units = a day; × 7 = a week</t>
-        </is>
+          <t>planImprovedBanner</t>
+        </is>
+      </c>
+      <c r="B148" s="13" t="b">
+        <v>1</v>
       </c>
       <c r="C148" s="13" t="inlineStr">
         <is>
-          <t>D88: whenever the pupil changes a fare, a time or a service (in the plan or an experiment), show one line: fare — '£20 more a ticket × 57 passengers = £1,140 more a day'; time — '9 more passengers × £90 = £810 more a day'; service — 'one more flight: 19 × £90 − £615 costs = £1,095 a day'. The first time each kind appears it is a Build (tap the figures and ×), then Model; not counted in the sign-off cap. The Sunday review repeats it for the week ('Your Dublin fare rise was worth £7,980 this week'). Rule: the pupil sees figures for changes he made or tested; words for what is still available (missedProfitDisplay).</t>
+          <t>D87: when the projected result improves after a change, a small 'Plan improved: seats a → b, result £x → £y' confirmation above Run week.</t>
         </is>
       </c>
       <c r="D148" s="13" t="inlineStr">
@@ -57585,15 +58699,17 @@
     <row r="149">
       <c r="A149" s="13" t="inlineStr">
         <is>
-          <t>tankWeeksOfFuel</t>
-        </is>
-      </c>
-      <c r="B149" s="13" t="n">
-        <v>3</v>
+          <t>whatWasItWorth</t>
+        </is>
+      </c>
+      <c r="B149" s="13" t="inlineStr">
+        <is>
+          <t>change per unit × units = a day; × 7 = a week</t>
+        </is>
       </c>
       <c r="C149" s="13" t="inlineStr">
         <is>
-          <t>D89: each Monday, capacity = max(current, 3 × the standing plan's weekly litres, rounded UP to the block size × 10). The desk says 'Storage: 60,000 L — about three weeks of flying'. No cost.</t>
+          <t>D88: whenever the pupil changes a fare, a time or a service (in the plan or an experiment), show one line: fare — '£20 more a ticket × 57 passengers = £1,140 more a day'; time — '9 more passengers × £90 = £810 more a day'; service — 'one more flight: 19 × £90 − £615 costs = £1,095 a day'. The first time each kind appears it is a Build (tap the figures and ×), then Model; not counted in the sign-off cap. The Sunday review repeats it for the week ('Your Dublin fare rise was worth £7,980 this week'). Rule: the pupil sees figures for changes he made or tested; words for what is still available (missedProfitDisplay).</t>
         </is>
       </c>
       <c r="D149" s="13" t="inlineStr">
@@ -57605,17 +58721,15 @@
     <row r="150">
       <c r="A150" s="13" t="inlineStr">
         <is>
-          <t>fuelFarm</t>
-        </is>
-      </c>
-      <c r="B150" s="13" t="inlineStr">
-        <is>
-          <t>chapter 3: buy storage</t>
-        </is>
+          <t>tankWeeksOfFuel</t>
+        </is>
+      </c>
+      <c r="B150" s="13" t="n">
+        <v>3</v>
       </c>
       <c r="C150" s="13" t="inlineStr">
         <is>
-          <t>D89: from 2031-09-01 the Fuel desk offers a fuel farm to buy (Finance sheet row fuelFarm): capacity 1,500,000 L for £2m, then 3,000,000 L for £3m more in chapter 4. The sum: what a full farm saves in a shock (litres × the price rise, e.g. 1,500,000 × 60p = £900,000) against the price; the same buy-now-or-wait shape as a plane. Below the farm, capacity still grows with the fleet.</t>
+          <t>D89: each Monday, capacity = max(current, 3 × the standing plan's weekly litres, rounded UP to the block size × 10). The desk says 'Storage: 60,000 L — about three weeks of flying'. No cost.</t>
         </is>
       </c>
       <c r="D150" s="13" t="inlineStr">
@@ -57627,15 +58741,17 @@
     <row r="151">
       <c r="A151" s="13" t="inlineStr">
         <is>
-          <t>clashingWeeks</t>
-        </is>
-      </c>
-      <c r="B151" s="13" t="b">
-        <v>1</v>
+          <t>fuelFarm</t>
+        </is>
+      </c>
+      <c r="B151" s="13" t="inlineStr">
+        <is>
+          <t>chapter 3: buy storage</t>
+        </is>
       </c>
       <c r="C151" s="13" t="inlineStr">
         <is>
-          <t>D90: from the autumn of chapter 1 some weeks carry two or three pieces of good news at once, so the pupil chooses which to serve with the planes he has. RouteNews.clashGroup marks them; the World report shows a clash as one card ('Two things this week — which do you serve?') with each item's extra passengers at the chosen fare.</t>
+          <t>D89: from 2031-09-01 the Fuel desk offers a fuel farm to buy (Finance sheet row fuelFarm): capacity 1,500,000 L for £2m, then 3,000,000 L for £3m more in chapter 4. The sum: what a full farm saves in a shock (litres × the price rise, e.g. 1,500,000 × 60p = £900,000) against the price; the same buy-now-or-wait shape as a plane. Below the farm, capacity still grows with the fleet.</t>
         </is>
       </c>
       <c r="D151" s="13" t="inlineStr">
@@ -57647,17 +58763,15 @@
     <row r="152">
       <c r="A152" s="13" t="inlineStr">
         <is>
-          <t>charterDeskFromDate</t>
-        </is>
-      </c>
-      <c r="B152" s="13" t="inlineStr">
-        <is>
-          <t>2031-01-06</t>
-        </is>
+          <t>clashingWeeks</t>
+        </is>
+      </c>
+      <c r="B152" s="13" t="b">
+        <v>1</v>
       </c>
       <c r="C152" s="13" t="inlineStr">
         <is>
-          <t>D90: the Charter desk opens with chapter 2. Offers (CharterOffers sheet) arrive about one a month: a fee, dates, a plane size and a destination, often off the network. Accepting takes that plane off the timetable for those days; the card shows fee against what the plane would have earned (opportunity cost). Offers can be declined; some clash with the pupil's own busy weeks.</t>
+          <t>D90: from the autumn of chapter 1 some weeks carry two or three pieces of good news at once, so the pupil chooses which to serve with the planes he has. RouteNews.clashGroup marks them; the World report shows a clash as one card ('Two things this week — which do you serve?') with each item's extra passengers at the chosen fare.</t>
         </is>
       </c>
       <c r="D152" s="13" t="inlineStr">
@@ -57669,17 +58783,17 @@
     <row r="153">
       <c r="A153" s="13" t="inlineStr">
         <is>
-          <t>charterFeeRule</t>
+          <t>charterDeskFromDate</t>
         </is>
       </c>
       <c r="B153" s="13" t="inlineStr">
         <is>
-          <t>1.2 × the plane's best network day × days, rounded to £1,000</t>
+          <t>2031-01-06</t>
         </is>
       </c>
       <c r="C153" s="13" t="inlineStr">
         <is>
-          <t>D90: so a charter beats the network only when the plane is not at its best use — the choice is real.</t>
+          <t>D90: the Charter desk opens with chapter 2. Offers (CharterOffers sheet) arrive about one a month: a fee, dates, a plane size and a destination, often off the network. Accepting takes that plane off the timetable for those days; the card shows fee against what the plane would have earned (opportunity cost). Offers can be declined; some clash with the pupil's own busy weeks.</t>
         </is>
       </c>
       <c r="D153" s="13" t="inlineStr">
@@ -57691,17 +58805,17 @@
     <row r="154">
       <c r="A154" s="13" t="inlineStr">
         <is>
-          <t>knownForRule</t>
+          <t>charterFeeRule</t>
         </is>
       </c>
       <c r="B154" s="13" t="inlineStr">
         <is>
-          <t>3 in a year → level 1 (+10% on that tag's news; first refusal on its offers); 6 → level 2 (+15%, fees +10%); fades after a year without</t>
+          <t>1.2 × the plane's best network day × days, rounded to £1,000</t>
         </is>
       </c>
       <c r="C154" s="13" t="inlineStr">
         <is>
-          <t>D90: tags sport | pilgrimage | music | winter sun | business, earned by charters taken and news served (a service added or a fare raised on a tagged item). Shown on the reputation card: 'Known for: sport ★'. From chapter 3 (2031-09-01).</t>
+          <t>D90: so a charter beats the network only when the plane is not at its best use — the choice is real.</t>
         </is>
       </c>
       <c r="D154" s="13" t="inlineStr">
@@ -57713,15 +58827,19 @@
     <row r="155">
       <c r="A155" s="13" t="inlineStr">
         <is>
-          <t>knownForFromDate</t>
+          <t>knownForRule</t>
         </is>
       </c>
       <c r="B155" s="13" t="inlineStr">
         <is>
-          <t>2031-09-01</t>
-        </is>
-      </c>
-      <c r="C155" s="13" t="inlineStr"/>
+          <t>3 in a year → level 1 (+10% on that tag's news; first refusal on its offers); 6 → level 2 (+15%, fees +10%); fades after a year without</t>
+        </is>
+      </c>
+      <c r="C155" s="13" t="inlineStr">
+        <is>
+          <t>D90: tags sport | pilgrimage | music | winter sun | business, earned by charters taken and news served (a service added or a fare raised on a tagged item). Shown on the reputation card: 'Known for: sport ★'. From chapter 3 (2031-09-01).</t>
+        </is>
+      </c>
       <c r="D155" s="13" t="inlineStr">
         <is>
           <t>live</t>
@@ -57731,79 +58849,77 @@
     <row r="156">
       <c r="A156" s="13" t="inlineStr">
         <is>
+          <t>knownForFromDate</t>
+        </is>
+      </c>
+      <c r="B156" s="13" t="inlineStr">
+        <is>
+          <t>2031-09-01</t>
+        </is>
+      </c>
+      <c r="C156" s="13" t="inlineStr"/>
+      <c r="D156" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="13" t="inlineStr">
+        <is>
           <t>festivalsCalendar</t>
         </is>
       </c>
-      <c r="B156" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="C156" s="13" t="inlineStr">
+      <c r="B157" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="C157" s="13" t="inlineStr">
         <is>
           <t>D90: religious and cultural festivals across the network are news items with kind = festival and an 'about' line (RouteNews.about) explaining what is being celebrated — a humanities thread. Dates for moving festivals (Chinese New Year, Ramadan, Eid, Hajj, Diwali, Orthodox Easter) follow their calendars for 2030–2033 and are approximate to a day or two.</t>
         </is>
       </c>
-      <c r="D156" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="14" t="inlineStr">
+      <c r="D157" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="14" t="inlineStr">
         <is>
           <t>planningLevel</t>
         </is>
       </c>
-      <c r="B157" s="14" t="inlineStr">
+      <c r="B158" s="14" t="inlineStr">
         <is>
           <t>flights (chapters 1–2) | assignment (from chapter 3)</t>
         </is>
       </c>
-      <c r="C157" s="14" t="inlineStr">
+      <c r="C158" s="14" t="inlineStr">
         <is>
           <t>D91 direction, to be designed: as the fleet grows, planning moves up a level — the pupil assigns planes to routes and sets fares, the engine builds each plane's timetable from the demand bands (auto-schedule), and the pupil opens a plane's day only when he wants to adjust it. The decisions become which plane where, which fare, which offer; not where each flight sits.</t>
         </is>
       </c>
-      <c r="D157" s="14" t="inlineStr">
+      <c r="D158" s="14" t="inlineStr">
         <is>
           <t>placeholder</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="13" t="inlineStr">
-        <is>
-          <t>fuelGraph</t>
-        </is>
-      </c>
-      <c r="B158" s="13" t="inlineStr">
-        <is>
-          <t>price line · forecast band · purchases as dots</t>
-        </is>
-      </c>
-      <c r="C158" s="13" t="inlineStr">
-        <is>
-          <t>D92: the fuel desk's graph shows the weekly price line, next week's band, and the pupil's purchases as dots on the line sized by litres bought.</t>
-        </is>
-      </c>
-      <c r="D158" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="13" t="inlineStr">
         <is>
-          <t>averagePaidVsMarket</t>
-        </is>
-      </c>
-      <c r="B159" s="13" t="b">
-        <v>1</v>
+          <t>fuelGraph</t>
+        </is>
+      </c>
+      <c r="B159" s="13" t="inlineStr">
+        <is>
+          <t>price line · forecast band · purchases as dots</t>
+        </is>
       </c>
       <c r="C159" s="13" t="inlineStr">
         <is>
-          <t>D92: the desk and the monthly review show the average price the pupil paid per litre against the market's average for the same period, and what buying ahead saved or cost: 'You paid £1.62 on average; the market averaged £1.75; saved £4,200.' A Build step the first time (the divisor), then Model.</t>
+          <t>D92: the fuel desk's graph shows the weekly price line, next week's band, and the pupil's purchases as dots on the line sized by litres bought.</t>
         </is>
       </c>
       <c r="D159" s="13" t="inlineStr">
@@ -57815,17 +58931,15 @@
     <row r="160">
       <c r="A160" s="13" t="inlineStr">
         <is>
-          <t>whyPricesMove</t>
-        </is>
-      </c>
-      <c r="B160" s="13" t="inlineStr">
-        <is>
-          <t>Fuel costs more when more people want it: cold winters (heating), summer travel, and shocks when supply is cut; it costs less when there is plenty.</t>
-        </is>
+          <t>averagePaidVsMarket</t>
+        </is>
+      </c>
+      <c r="B160" s="13" t="b">
+        <v>1</v>
       </c>
       <c r="C160" s="13" t="inlineStr">
         <is>
-          <t>D92: the one-line explanation on the fuel desk; the yearly pattern (winter up, spring down), small weekly moves with a reason, shocks that come back down, and the occasional false alarm are in the Market sheet. No randomness.</t>
+          <t>D92: the desk and the monthly review show the average price the pupil paid per litre against the market's average for the same period, and what buying ahead saved or cost: 'You paid £1.62 on average; the market averaged £1.75; saved £4,200.' A Build step the first time (the divisor), then Model.</t>
         </is>
       </c>
       <c r="D160" s="13" t="inlineStr">
@@ -57837,17 +58951,17 @@
     <row r="161">
       <c r="A161" s="13" t="inlineStr">
         <is>
-          <t>chapterReviewDay</t>
+          <t>whyPricesMove</t>
         </is>
       </c>
       <c r="B161" s="13" t="inlineStr">
         <is>
-          <t>last day of the chapter, whatever the weekday</t>
+          <t>Fuel costs more when more people want it: cold winters (heating), summer travel, and shocks when supply is cut; it costs less when there is plenty.</t>
         </is>
       </c>
       <c r="C161" s="13" t="inlineStr">
         <is>
-          <t>Chapter reviews fall on 28 Dec 2030, 31 Aug 2031, 31 Aug 2032, 31 Aug 2033, 31 Aug 2034, 31 Aug 2035. Chapters open on the next Monday; any days between fly as one short run.</t>
+          <t>D92: the one-line explanation on the fuel desk; the yearly pattern (winter up, spring down), small weekly moves with a reason, shocks that come back down, and the occasional false alarm are in the Market sheet. No randomness.</t>
         </is>
       </c>
       <c r="D161" s="13" t="inlineStr">
@@ -57859,17 +58973,17 @@
     <row r="162">
       <c r="A162" s="13" t="inlineStr">
         <is>
-          <t>overdraftDeclined</t>
+          <t>chapterReviewDay</t>
         </is>
       </c>
       <c r="B162" s="13" t="inlineStr">
         <is>
-          <t>no overdraft until accepted on the Finance desk</t>
+          <t>last day of the chapter, whatever the weekday</t>
         </is>
       </c>
       <c r="C162" s="13" t="inlineStr">
         <is>
-          <t>Confirmed: declined means spending is blocked at £0.</t>
+          <t>Chapter reviews fall on 28 Dec 2030, 31 Aug 2031, 31 Aug 2032, 31 Aug 2033, 31 Aug 2034, 31 Aug 2035. Chapters open on the next Monday; any days between fly as one short run.</t>
         </is>
       </c>
       <c r="D162" s="13" t="inlineStr">
@@ -57881,17 +58995,17 @@
     <row r="163">
       <c r="A163" s="13" t="inlineStr">
         <is>
-          <t>overdraftLimitRecalc</t>
+          <t>overdraftDeclined</t>
         </is>
       </c>
       <c r="B163" s="13" t="inlineStr">
         <is>
-          <t>each beat from the last four weeks; if overdrawn beyond a lower new limit, the plan flies and nothing new is bought</t>
+          <t>no overdraft until accepted on the Finance desk</t>
         </is>
       </c>
       <c r="C163" s="13" t="inlineStr">
         <is>
-          <t>Confirmed.</t>
+          <t>Confirmed: declined means spending is blocked at £0.</t>
         </is>
       </c>
       <c r="D163" s="13" t="inlineStr">
@@ -57903,17 +59017,17 @@
     <row r="164">
       <c r="A164" s="13" t="inlineStr">
         <is>
-          <t>twoLegCrew</t>
+          <t>overdraftLimitRecalc</t>
         </is>
       </c>
       <c r="B164" s="13" t="inlineStr">
         <is>
-          <t>£500 per leg flown: four per Sydney rotation</t>
+          <t>each beat from the last four weeks; if overdrawn beyond a lower new limit, the plan flies and nothing new is bought</t>
         </is>
       </c>
       <c r="C164" s="13" t="inlineStr">
         <is>
-          <t>D79 clarified.</t>
+          <t>Confirmed.</t>
         </is>
       </c>
       <c r="D164" s="13" t="inlineStr">
@@ -57925,17 +59039,17 @@
     <row r="165">
       <c r="A165" s="13" t="inlineStr">
         <is>
-          <t>rotationTypicalDay</t>
+          <t>twoLegCrew</t>
         </is>
       </c>
       <c r="B165" s="13" t="inlineStr">
         <is>
-          <t>the average day: the rotation's profit ÷ rotationDays</t>
+          <t>£500 per leg flown: four per Sydney rotation</t>
         </is>
       </c>
       <c r="C165" s="13" t="inlineStr">
         <is>
-          <t>Confirmed: the plan page and cost breakdown show a rotation's average day (÷ 2, ÷ 4 for Sydney), so profit a day is honest.</t>
+          <t>D79 clarified.</t>
         </is>
       </c>
       <c r="D165" s="13" t="inlineStr">
@@ -57947,17 +59061,17 @@
     <row r="166">
       <c r="A166" s="13" t="inlineStr">
         <is>
-          <t>tankRoundingBlocks</t>
+          <t>rotationTypicalDay</t>
         </is>
       </c>
       <c r="B166" s="13" t="inlineStr">
         <is>
-          <t>10 blocks in chapters 1–2; 1 block (100,000 L) from 2031-09-01</t>
+          <t>the average day: the rotation's profit ÷ rotationDays</t>
         </is>
       </c>
       <c r="C166" s="13" t="inlineStr">
         <is>
-          <t>D89 clarified: capacity rounds up to a multiple of ten blocks while blocks are 1,000 or 10,000 L, and to a single block once blocks are 100,000 L, so storage stays near three weeks and the farm still adds something.</t>
+          <t>Confirmed: the plan page and cost breakdown show a rotation's average day (÷ 2, ÷ 4 for Sydney), so profit a day is honest.</t>
         </is>
       </c>
       <c r="D166" s="13" t="inlineStr">
@@ -57969,15 +59083,17 @@
     <row r="167">
       <c r="A167" s="13" t="inlineStr">
         <is>
-          <t>fuelShockRise</t>
-        </is>
-      </c>
-      <c r="B167" s="13" t="n">
-        <v>0.6</v>
+          <t>tankRoundingBlocks</t>
+        </is>
+      </c>
+      <c r="B167" s="13" t="inlineStr">
+        <is>
+          <t>10 blocks in chapters 1–2; 1 block (100,000 L) from 2031-09-01</t>
+        </is>
       </c>
       <c r="C167" s="13" t="inlineStr">
         <is>
-          <t>D89: the rise used in the fuel farm's worth line when the forecast's expected rise is under 20p.</t>
+          <t>D89 clarified: capacity rounds up to a multiple of ten blocks while blocks are 1,000 or 10,000 L, and to a single block once blocks are 100,000 L, so storage stays near three weeks and the farm still adds something.</t>
         </is>
       </c>
       <c r="D167" s="13" t="inlineStr">
@@ -57989,15 +59105,15 @@
     <row r="168">
       <c r="A168" s="13" t="inlineStr">
         <is>
-          <t>flightTimesPerPage</t>
+          <t>fuelShockRise</t>
         </is>
       </c>
       <c r="B168" s="13" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="C168" s="13" t="inlineStr">
         <is>
-          <t>Flight-times page: at most two Calculate sums the first two times an aircraft meets a route; Builds after (the decay rule applies to flight times too). The rest filled by the model.</t>
+          <t>D89: the rise used in the fuel farm's worth line when the forecast's expected rise is under 20p.</t>
         </is>
       </c>
       <c r="D168" s="13" t="inlineStr">
@@ -58009,17 +59125,15 @@
     <row r="169">
       <c r="A169" s="13" t="inlineStr">
         <is>
-          <t>weekendAddPrompt</t>
-        </is>
-      </c>
-      <c r="B169" s="13" t="inlineStr">
-        <is>
-          <t>ask: Sat–Sun only, or all week?</t>
-        </is>
+          <t>flightTimesPerPage</t>
+        </is>
+      </c>
+      <c r="B169" s="13" t="n">
+        <v>2</v>
       </c>
       <c r="C169" s="13" t="inlineStr">
         <is>
-          <t>Adding a flight in the Sat–Sun view asks which; default all week.</t>
+          <t>Flight-times page: at most two Calculate sums the first two times an aircraft meets a route; Builds after (the decay rule applies to flight times too). The rest filled by the model.</t>
         </is>
       </c>
       <c r="D169" s="13" t="inlineStr">
@@ -58031,15 +59145,17 @@
     <row r="170">
       <c r="A170" s="13" t="inlineStr">
         <is>
-          <t>huntsTwoTries</t>
-        </is>
-      </c>
-      <c r="B170" s="13" t="b">
-        <v>1</v>
+          <t>weekendAddPrompt</t>
+        </is>
+      </c>
+      <c r="B170" s="13" t="inlineStr">
+        <is>
+          <t>ask: Sat–Sun only, or all week?</t>
+        </is>
       </c>
       <c r="C170" s="13" t="inlineStr">
         <is>
-          <t>Hunts follow the two-tries rule like other sums.</t>
+          <t>Adding a flight in the Sat–Sun view asks which; default all week.</t>
         </is>
       </c>
       <c r="D170" s="13" t="inlineStr">
@@ -58051,7 +59167,7 @@
     <row r="171">
       <c r="A171" s="13" t="inlineStr">
         <is>
-          <t>workingOnPaperTeacherSwitch</t>
+          <t>huntsTwoTries</t>
         </is>
       </c>
       <c r="B171" s="13" t="b">
@@ -58059,7 +59175,7 @@
       </c>
       <c r="C171" s="13" t="inlineStr">
         <is>
-          <t>Add a teacher-panel switch for workingOnPaper (on by default).</t>
+          <t>Hunts follow the two-tries rule like other sums.</t>
         </is>
       </c>
       <c r="D171" s="13" t="inlineStr">
@@ -58071,17 +59187,15 @@
     <row r="172">
       <c r="A172" s="13" t="inlineStr">
         <is>
-          <t>operationsCheckByLevel</t>
-        </is>
-      </c>
-      <c r="B172" s="13" t="inlineStr">
-        <is>
-          <t>guided/supported: all tips; independent: priority 0–1 only; management: losses and exceptions</t>
-        </is>
+          <t>workingOnPaperTeacherSwitch</t>
+        </is>
+      </c>
+      <c r="B172" s="13" t="b">
+        <v>1</v>
       </c>
       <c r="C172" s="13" t="inlineStr">
         <is>
-          <t>D87 clarified: the check stays on at independent for the serious cases.</t>
+          <t>Add a teacher-panel switch for workingOnPaper (on by default).</t>
         </is>
       </c>
       <c r="D172" s="13" t="inlineStr">
@@ -58093,17 +59207,17 @@
     <row r="173">
       <c r="A173" s="13" t="inlineStr">
         <is>
-          <t>milestonesSheet</t>
+          <t>operationsCheckByLevel</t>
         </is>
       </c>
       <c r="B173" s="13" t="inlineStr">
         <is>
-          <t>Milestones</t>
+          <t>guided/supported: all tips; independent: priority 0–1 only; management: losses and exceptions</t>
         </is>
       </c>
       <c r="C173" s="13" t="inlineStr">
         <is>
-          <t>D93: teacher-only milestones, measured by the game, rewarded by the teacher outside it. No money or stars change.</t>
+          <t>D87 clarified: the check stays on at independent for the serious cases.</t>
         </is>
       </c>
       <c r="D173" s="13" t="inlineStr">
@@ -58115,17 +59229,17 @@
     <row r="174">
       <c r="A174" s="13" t="inlineStr">
         <is>
-          <t>hkgLaxPools</t>
+          <t>milestonesSheet</t>
         </is>
       </c>
       <c r="B174" s="13" t="inlineStr">
         <is>
-          <t>reduced 8% from v5.5</t>
+          <t>Milestones</t>
         </is>
       </c>
       <c r="C174" s="13" t="inlineStr">
         <is>
-          <t>So the A380 is about 50 short at £830 at three stars in its first weeks; growth (5% a week) fills it within a month regardless, which is fine: the fill question is for the first weeks and the fare choice.</t>
+          <t>D93: teacher-only milestones, measured by the game, rewarded by the teacher outside it. No money or stars change.</t>
         </is>
       </c>
       <c r="D174" s="13" t="inlineStr">
@@ -58137,17 +59251,17 @@
     <row r="175">
       <c r="A175" s="13" t="inlineStr">
         <is>
-          <t>litresPerSeat</t>
+          <t>hkgLaxPools</t>
         </is>
       </c>
       <c r="B175" s="13" t="inlineStr">
         <is>
-          <t>aircraft comparison only</t>
+          <t>reduced 8% from v5.5</t>
         </is>
       </c>
       <c r="C175" s="13" t="inlineStr">
         <is>
-          <t>D94: an infographic beside each plane on the comparison (seats with a fuel bar); total litres everywhere else.</t>
+          <t>So the A380 is about 50 short at £830 at three stars in its first weeks; growth (5% a week) fills it within a month regardless, which is fine: the fill question is for the first weeks and the fare choice.</t>
         </is>
       </c>
       <c r="D175" s="13" t="inlineStr">
@@ -58159,17 +59273,17 @@
     <row r="176">
       <c r="A176" s="13" t="inlineStr">
         <is>
-          <t>attentionGrammar</t>
+          <t>litresPerSeat</t>
         </is>
       </c>
       <c r="B176" s="13" t="inlineStr">
         <is>
-          <t>see the brief 'Attention grammar' (16 Oct)</t>
+          <t>aircraft comparison only</t>
         </is>
       </c>
       <c r="C176" s="13" t="inlineStr">
         <is>
-          <t>D95: replaces all earlier visual-hierarchy rules — colour roles (cyan current, gold unknown/result, green success, red problem, pale mono figures), type roles, focus rail, spotlight, active datum, change pulse, cause→effect line, result plate, eyebrows, progressive reveal; one calculation instrument with three states; sums on the decision screen; hints from WorkingMethods.hintTemplate. Claude Code, 19 Oct 2026: superseded by DESIGN.md (BertieV4, 18–19 Oct): magenta for the unknown, gold for money.</t>
+          <t>D94: an infographic beside each plane on the comparison (seats with a fuel bar); total litres everywhere else.</t>
         </is>
       </c>
       <c r="D176" s="13" t="inlineStr">
@@ -58181,15 +59295,17 @@
     <row r="177">
       <c r="A177" s="13" t="inlineStr">
         <is>
-          <t>reviewAsSpreadsheet</t>
-        </is>
-      </c>
-      <c r="B177" s="13" t="b">
-        <v>1</v>
+          <t>attentionGrammar</t>
+        </is>
+      </c>
+      <c r="B177" s="13" t="inlineStr">
+        <is>
+          <t>see the brief 'Attention grammar' (16 Oct)</t>
+        </is>
       </c>
       <c r="C177" s="13" t="inlineStr">
         <is>
-          <t>D96: the Sunday review's Build steps are cells in the week table — the pupil taps the ? cell (Profit this week, Difference, Average a day) and builds its formula from the figures above it, as in the analytics console; the active cell carries the focus rail and a soft gold edge, not a step number.</t>
+          <t>D95: replaces all earlier visual-hierarchy rules — colour roles (cyan current, gold unknown/result, green success, red problem, pale mono figures), type roles, focus rail, spotlight, active datum, change pulse, cause→effect line, result plate, eyebrows, progressive reveal; one calculation instrument with three states; sums on the decision screen; hints from WorkingMethods.hintTemplate. Claude Code, 19 Oct 2026: superseded by DESIGN.md (BertieV4, 18–19 Oct): magenta for the unknown, gold for money.</t>
         </is>
       </c>
       <c r="D177" s="13" t="inlineStr">
@@ -58201,17 +59317,15 @@
     <row r="178">
       <c r="A178" s="13" t="inlineStr">
         <is>
-          <t>fuelAccounting</t>
-        </is>
-      </c>
-      <c r="B178" s="13" t="inlineStr">
-        <is>
-          <t>cash buys fuel into the tank; profit counts only the fuel burned, at the price paid</t>
-        </is>
+          <t>reviewAsSpreadsheet</t>
+        </is>
+      </c>
+      <c r="B178" s="13" t="b">
+        <v>1</v>
       </c>
       <c r="C178" s="13" t="inlineStr">
         <is>
-          <t>D96: shown on the Fuel desk when an order is placed ('Buying fuel moves £10,290 from cash into the tank. Each day's profit counts only the fuel your flights burn, at the price you paid for it') and on the statement's fuel line (ƒ: litres burned × price paid).</t>
+          <t>D96: the Sunday review's Build steps are cells in the week table — the pupil taps the ? cell (Profit this week, Difference, Average a day) and builds its formula from the figures above it, as in the analytics console; the active cell carries the focus rail and a soft gold edge, not a step number.</t>
         </is>
       </c>
       <c r="D178" s="13" t="inlineStr">
@@ -58223,17 +59337,17 @@
     <row r="179">
       <c r="A179" s="13" t="inlineStr">
         <is>
-          <t>fuelFillLabel</t>
+          <t>fuelAccounting</t>
         </is>
       </c>
       <c r="B179" s="13" t="inlineStr">
         <is>
-          <t>Most I can afford: N blocks</t>
+          <t>cash buys fuel into the tank; profit counts only the fuel burned, at the price paid</t>
         </is>
       </c>
       <c r="C179" s="13" t="inlineStr">
         <is>
-          <t>D96: replaces 'Fill' when cash, not the tank, is the limit; 'Fill the tank' when the tank is.</t>
+          <t>D96: shown on the Fuel desk when an order is placed ('Buying fuel moves £10,290 from cash into the tank. Each day's profit counts only the fuel your flights burn, at the price you paid for it') and on the statement's fuel line (ƒ: litres burned × price paid).</t>
         </is>
       </c>
       <c r="D179" s="13" t="inlineStr">
@@ -58245,15 +59359,17 @@
     <row r="180">
       <c r="A180" s="13" t="inlineStr">
         <is>
-          <t>compareLastWeek</t>
-        </is>
-      </c>
-      <c r="B180" s="13" t="b">
-        <v>1</v>
+          <t>fuelFillLabel</t>
+        </is>
+      </c>
+      <c r="B180" s="13" t="inlineStr">
+        <is>
+          <t>Most I can afford: N blocks</t>
+        </is>
       </c>
       <c r="C180" s="13" t="inlineStr">
         <is>
-          <t>D96: the plan page can show last week's plan as faint ghost blocks behind this week's, with a change line (seats, projected profit, fares) and a list of what changed.</t>
+          <t>D96: replaces 'Fill' when cash, not the tank, is the limit; 'Fill the tank' when the tank is.</t>
         </is>
       </c>
       <c r="D180" s="13" t="inlineStr">
@@ -58265,17 +59381,15 @@
     <row r="181">
       <c r="A181" s="13" t="inlineStr">
         <is>
-          <t>keyboardShortcuts</t>
-        </is>
-      </c>
-      <c r="B181" s="13" t="inlineStr">
-        <is>
-          <t>Ctrl+→ / Ctrl+← between Home, Plan and the Operations Wall; Esc closes a panel; Enter checks a sum</t>
-        </is>
+          <t>compareLastWeek</t>
+        </is>
+      </c>
+      <c r="B181" s="13" t="b">
+        <v>1</v>
       </c>
       <c r="C181" s="13" t="inlineStr">
         <is>
-          <t>D96: shown as small key hints on the desk bar; teaches real shortcuts.</t>
+          <t>D96: the plan page can show last week's plan as faint ghost blocks behind this week's, with a change line (seats, projected profit, fares) and a list of what changed.</t>
         </is>
       </c>
       <c r="D181" s="13" t="inlineStr">
@@ -58287,17 +59401,17 @@
     <row r="182">
       <c r="A182" s="13" t="inlineStr">
         <is>
-          <t>soundSet</t>
+          <t>keyboardShortcuts</t>
         </is>
       </c>
       <c r="B182" s="13" t="inlineStr">
         <is>
-          <t>tap · slot · check-tick · query · result-plate · cash · fuel-pour · plane-move · day-tick</t>
+          <t>Ctrl+→ / Ctrl+← between Home, Plan and the Operations Wall; Esc closes a panel; Enter checks a sum</t>
         </is>
       </c>
       <c r="C182" s="13" t="inlineStr">
         <is>
-          <t>D96: short, soft, consistent UI sounds; one volume with mute; the voice and operations sounds as now. No sound on error louder than on success.</t>
+          <t>D96: shown as small key hints on the desk bar; teaches real shortcuts.</t>
         </is>
       </c>
       <c r="D182" s="13" t="inlineStr">
@@ -58309,15 +59423,17 @@
     <row r="183">
       <c r="A183" s="13" t="inlineStr">
         <is>
-          <t>dailyColour</t>
-        </is>
-      </c>
-      <c r="B183" s="13" t="b">
-        <v>1</v>
+          <t>soundSet</t>
+        </is>
+      </c>
+      <c r="B183" s="13" t="inlineStr">
+        <is>
+          <t>tap · slot · check-tick · query · result-plate · cash · fuel-pour · plane-move · day-tick</t>
+        </is>
       </c>
       <c r="C183" s="13" t="inlineStr">
         <is>
-          <t>D96: small, explained, deterministic daily effects from the DailyColour sheet (mostly good: a group booking, a snack rush, a tailwind saving fuel), within ±5% of a day's profit, so results move up as well as down and every move has a one-line reason on the day's row. Not random: fixed by date.</t>
+          <t>D96: short, soft, consistent UI sounds; one volume with mute; the voice and operations sounds as now. No sound on error louder than on success.</t>
         </is>
       </c>
       <c r="D183" s="13" t="inlineStr">
@@ -58329,15 +59445,15 @@
     <row r="184">
       <c r="A184" s="13" t="inlineStr">
         <is>
-          <t>tipGainGate</t>
-        </is>
-      </c>
-      <c r="B184" s="13" t="n">
-        <v>50</v>
+          <t>dailyColour</t>
+        </is>
+      </c>
+      <c r="B184" s="13" t="b">
+        <v>1</v>
       </c>
       <c r="C184" s="13" t="inlineStr">
         <is>
-          <t>D97: a PlanTip shows only if the best plan that answers it gains at least this much a day over the current plan (moneyAtStake ≥ £50/day). A tip that cannot be acted on with the planes in the fleet is silent, however large the demand gap.</t>
+          <t>D96: small, explained, deterministic daily effects from the DailyColour sheet (mostly good: a group booking, a snack rush, a tailwind saving fuel), within ±5% of a day's profit, so results move up as well as down and every move has a one-line reason on the day's row. Not random: fixed by date.</t>
         </is>
       </c>
       <c r="D184" s="13" t="inlineStr">
@@ -58349,15 +59465,15 @@
     <row r="185">
       <c r="A185" s="13" t="inlineStr">
         <is>
-          <t>allFullCapacityTip</t>
-        </is>
-      </c>
-      <c r="B185" s="13" t="b">
-        <v>1</v>
+          <t>tipGainGate</t>
+        </is>
+      </c>
+      <c r="B185" s="13" t="n">
+        <v>50</v>
       </c>
       <c r="C185" s="13" t="inlineStr">
         <is>
-          <t>D97: when every service is at or above seatFillGood and passengers are turned away, the operations check leads with the capacity observation (PlanTips all_full_capacity) and the timing tips stay silent.</t>
+          <t>D97: a PlanTip shows only if the best plan that answers it gains at least this much a day over the current plan (moneyAtStake ≥ £50/day). A tip that cannot be acted on with the planes in the fleet is silent, however large the demand gap.</t>
         </is>
       </c>
       <c r="D185" s="13" t="inlineStr">
@@ -58369,17 +59485,15 @@
     <row r="186">
       <c r="A186" s="13" t="inlineStr">
         <is>
-          <t>plannerUpgrades</t>
-        </is>
-      </c>
-      <c r="B186" s="13" t="inlineStr">
-        <is>
-          <t>earned at a review; fallback a week later</t>
-        </is>
+          <t>allFullCapacityTip</t>
+        </is>
+      </c>
+      <c r="B186" s="13" t="b">
+        <v>1</v>
       </c>
       <c r="C186" s="13" t="inlineStr">
         <is>
-          <t>D98: planner features arrive as upgrades the pupil asks for (Upgrades sheet): the review shows the data, asks what the planner cannot handle, offers three statements (later free text), and grants the matching upgrade; if he does not name it, the systems team proposes it a week later. Never blocks play.</t>
+          <t>D97: when every service is at or above seatFillGood and passengers are turned away, the operations check leads with the capacity observation (PlanTips all_full_capacity) and the timing tips stay silent.</t>
         </is>
       </c>
       <c r="D186" s="13" t="inlineStr">
@@ -58391,17 +59505,17 @@
     <row r="187">
       <c r="A187" s="13" t="inlineStr">
         <is>
-          <t>operationsBriefings</t>
+          <t>plannerUpgrades</t>
         </is>
       </c>
       <c r="B187" s="13" t="inlineStr">
         <is>
-          <t>full screen; 30–60 s; advance by doing, never by Next; a Pause &amp; discuss state at each stop</t>
+          <t>earned at a review; fallback a week later</t>
         </is>
       </c>
       <c r="C187" s="13" t="inlineStr">
         <is>
-          <t>D99: ten briefings (Briefings sheet), each shown once at its trigger and replayable from a Briefings shelf; built as separate HTML pieces in the game's style and dropped in.</t>
+          <t>D98: planner features arrive as upgrades the pupil asks for (Upgrades sheet): the review shows the data, asks what the planner cannot handle, offers three statements (later free text), and grants the matching upgrade; if he does not name it, the systems team proposes it a week later. Never blocks play.</t>
         </is>
       </c>
       <c r="D187" s="13" t="inlineStr">
@@ -58413,17 +59527,17 @@
     <row r="188">
       <c r="A188" s="13" t="inlineStr">
         <is>
-          <t>flightTimeIntroAt</t>
+          <t>operationsBriefings</t>
         </is>
       </c>
       <c r="B188" s="13" t="inlineStr">
         <is>
-          <t>first opening of the Flight times page</t>
+          <t>full screen; 30–60 s; advance by doing, never by Next; a Pause &amp; discuss state at each stop</t>
         </is>
       </c>
       <c r="C188" s="13" t="inlineStr">
         <is>
-          <t>D100: the flight-time concept (the slideshow: fly it an hour at a time, the triangle, the sum) plays the first time the Flight times page opens — when a second aircraft type or a new route first needs a flight time — not on day 22. The day-22 Madrid screen teaches range only and refers back to flight time.</t>
+          <t>D99: ten briefings (Briefings sheet), each shown once at its trigger and replayable from a Briefings shelf; built as separate HTML pieces in the game's style and dropped in.</t>
         </is>
       </c>
       <c r="D188" s="13" t="inlineStr">
@@ -58435,17 +59549,17 @@
     <row r="189">
       <c r="A189" s="13" t="inlineStr">
         <is>
-          <t>formulaMarks</t>
+          <t>flightTimeIntroAt</t>
         </is>
       </c>
       <c r="B189" s="13" t="inlineStr">
         <is>
-          <t>ƒ on the cells the airline works out (the Sheet)</t>
+          <t>first opening of the Flight times page</t>
         </is>
       </c>
       <c r="C189" s="13" t="inlineStr">
         <is>
-          <t>Claude Code, 19 Oct 2026: DESIGN.md (19 Oct, Sheet) shows a small ƒ on every figure the airline works out with a sum the pupil has mastered; which sums are ƒ is set per sum in the workbook's sum list. (v6.0 had: on tap only)</t>
+          <t>D100: the flight-time concept (the slideshow: fly it an hour at a time, the triangle, the sum) plays the first time the Flight times page opens — when a second aircraft type or a new route first needs a flight time — not on day 22. The day-22 Madrid screen teaches range only and refers back to flight time.</t>
         </is>
       </c>
       <c r="D189" s="13" t="inlineStr">
@@ -58457,17 +59571,17 @@
     <row r="190">
       <c r="A190" s="13" t="inlineStr">
         <is>
-          <t>emergencyFuelPayment</t>
+          <t>formulaMarks</t>
         </is>
       </c>
       <c r="B190" s="13" t="inlineStr">
         <is>
-          <t>from the same day's takings</t>
+          <t>ƒ on the cells the airline works out (the Sheet)</t>
         </is>
       </c>
       <c r="C190" s="13" t="inlineStr">
         <is>
-          <t>D100: when the tank runs dry, the day's fuel is bought at the day's price + emergencyFuelPremium and paid from that day's ticket revenue before cash, so a profitable plan always flies. The desk says so in one line.</t>
+          <t>Claude Code, 19 Oct 2026: DESIGN.md (19 Oct, Sheet) shows a small ƒ on every figure the airline works out with a sum the pupil has mastered; which sums are ƒ is set per sum in the workbook's sum list. (v6.0 had: on tap only)</t>
         </is>
       </c>
       <c r="D190" s="13" t="inlineStr">
@@ -58479,17 +59593,17 @@
     <row r="191">
       <c r="A191" s="13" t="inlineStr">
         <is>
-          <t>perFlightFares</t>
+          <t>emergencyFuelPayment</t>
         </is>
       </c>
       <c r="B191" s="13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>from the same day's takings</t>
         </is>
       </c>
       <c r="C191" s="13" t="inlineStr">
         <is>
-          <t>D100: fares stay per route for the whole game (no per-flight or peak/off-peak fares).</t>
+          <t>D100: when the tank runs dry, the day's fuel is bought at the day's price + emergencyFuelPremium and paid from that day's ticket revenue before cash, so a profitable plan always flies. The desk says so in one line.</t>
         </is>
       </c>
       <c r="D191" s="13" t="inlineStr">
@@ -58501,15 +59615,17 @@
     <row r="192">
       <c r="A192" s="13" t="inlineStr">
         <is>
-          <t>marketSheetFromDay</t>
-        </is>
-      </c>
-      <c r="B192" s="13" t="n">
-        <v>15</v>
+          <t>perFlightFares</t>
+        </is>
+      </c>
+      <c r="B192" s="13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
       </c>
       <c r="C192" s="13" t="inlineStr">
         <is>
-          <t>D100: the Change network screen gains a market sheet from week 3 (MarketSheet columns in this sheet's note): destination · fare · people who want to fly · possible revenue (fare × people, Build the first time) · what your plane can carry (seats × services, the smaller of the two) · revenue you could take. Editing a fare updates the row. Revenue only until profit columns arrive in chapter 2.</t>
+          <t>D100: fares stay per route for the whole game (no per-flight or peak/off-peak fares).</t>
         </is>
       </c>
       <c r="D192" s="13" t="inlineStr">
@@ -58521,17 +59637,15 @@
     <row r="193">
       <c r="A193" s="13" t="inlineStr">
         <is>
-          <t>aircraftCardMeasure</t>
-        </is>
-      </c>
-      <c r="B193" s="13" t="inlineStr">
-        <is>
-          <t>extra profit for the airline (incremental), one measure on the whole screen</t>
-        </is>
+          <t>marketSheetFromDay</t>
+        </is>
+      </c>
+      <c r="B193" s="13" t="n">
+        <v>15</v>
       </c>
       <c r="C193" s="13" t="inlineStr">
         <is>
-          <t>D100: the cards, the waterfall, 'What the extra money buys' and 'Where could it fly?' all use the airline's extra profit against today's plan; the waterfall must add up line by line (show snacks if included); the route's current fare unless a card says otherwise; 'What you give up' written per plane from its own figures.</t>
+          <t>D100: the Change network screen gains a market sheet from week 3 (MarketSheet columns in this sheet's note): destination · fare · people who want to fly · possible revenue (fare × people, Build the first time) · what your plane can carry (seats × services, the smaller of the two) · revenue you could take. Editing a fare updates the row. Revenue only until profit columns arrive in chapter 2.</t>
         </is>
       </c>
       <c r="D193" s="13" t="inlineStr">
@@ -58543,17 +59657,17 @@
     <row r="194">
       <c r="A194" s="13" t="inlineStr">
         <is>
-          <t>waitCostLine</t>
+          <t>aircraftCardMeasure</t>
         </is>
       </c>
       <c r="B194" s="13" t="inlineStr">
         <is>
-          <t>idle days × day cost</t>
+          <t>extra profit for the airline (incremental), one measure on the whole screen</t>
         </is>
       </c>
       <c r="C194" s="13" t="inlineStr">
         <is>
-          <t>D100: on Buy now or wait, per plane: 'Its best work starts {date} ({route}). Bought today, it costs £{dayCost} a day for {days} days first: £{total}', against its earnings meanwhile. A Build the first time.</t>
+          <t>D100: the cards, the waterfall, 'What the extra money buys' and 'Where could it fly?' all use the airline's extra profit against today's plan; the waterfall must add up line by line (show snacks if included); the route's current fare unless a card says otherwise; 'What you give up' written per plane from its own figures.</t>
         </is>
       </c>
       <c r="D194" s="13" t="inlineStr">
@@ -58565,15 +59679,17 @@
     <row r="195">
       <c r="A195" s="13" t="inlineStr">
         <is>
-          <t>reviewQuestionsPerWeek</t>
-        </is>
-      </c>
-      <c r="B195" s="13" t="n">
-        <v>2</v>
+          <t>waitCostLine</t>
+        </is>
+      </c>
+      <c r="B195" s="13" t="inlineStr">
+        <is>
+          <t>idle days × day cost</t>
+        </is>
       </c>
       <c r="C195" s="13" t="inlineStr">
         <is>
-          <t>D100: from week 2 the review asks two questions from ReviewQuestions, chosen to point at the plan's biggest weakness (the engine's top tip); week 1 keeps total, projected − actual and the mean.</t>
+          <t>D100: on Buy now or wait, per plane: 'Its best work starts {date} ({route}). Bought today, it costs £{dayCost} a day for {days} days first: £{total}', against its earnings meanwhile. A Build the first time.</t>
         </is>
       </c>
       <c r="D195" s="13" t="inlineStr">
@@ -58585,17 +59701,15 @@
     <row r="196">
       <c r="A196" s="13" t="inlineStr">
         <is>
-          <t>spreadsheetFunctionsFromDate</t>
-        </is>
-      </c>
-      <c r="B196" s="13" t="inlineStr">
-        <is>
-          <t>2031-01-06</t>
-        </is>
+          <t>reviewQuestionsPerWeek</t>
+        </is>
+      </c>
+      <c r="B196" s="13" t="n">
+        <v>2</v>
       </c>
       <c r="C196" s="13" t="inlineStr">
         <is>
-          <t>D100: from chapter 2 the spreadsheet names SUM, AVERAGE, MAX and MIN; the review's Build steps can be written with them.</t>
+          <t>D100: from week 2 the review asks two questions from ReviewQuestions, chosen to point at the plan's biggest weakness (the engine's top tip); week 1 keeps total, projected − actual and the mean.</t>
         </is>
       </c>
       <c r="D196" s="13" t="inlineStr">
@@ -58607,17 +59721,17 @@
     <row r="197">
       <c r="A197" s="13" t="inlineStr">
         <is>
-          <t>amountFormat</t>
+          <t>spreadsheetFunctionsFromDate</t>
         </is>
       </c>
       <c r="B197" s="13" t="inlineStr">
         <is>
-          <t>whole pounds without pence when the pence are zero</t>
+          <t>2031-01-06</t>
         </is>
       </c>
       <c r="C197" s="13" t="inlineStr">
         <is>
-          <t>£19,690, not £19,690.00.</t>
+          <t>D100: from chapter 2 the spreadsheet names SUM, AVERAGE, MAX and MIN; the review's Build steps can be written with them.</t>
         </is>
       </c>
       <c r="D197" s="13" t="inlineStr">
@@ -58629,15 +59743,17 @@
     <row r="198">
       <c r="A198" s="13" t="inlineStr">
         <is>
-          <t>adaptToOnlyFlight</t>
-        </is>
-      </c>
-      <c r="B198" s="13" t="n">
-        <v>0.5</v>
+          <t>amountFormat</t>
+        </is>
+      </c>
+      <c r="B198" s="13" t="inlineStr">
+        <is>
+          <t>whole pounds without pence when the pence are zero</t>
+        </is>
       </c>
       <c r="C198" s="13" t="inlineStr">
         <is>
-          <t>D101: when time-locked passengers want a band with no service on their route, this share of them take the nearest service on that route instead. Fixes one-flight routes that could never fill (Marrakech: 76 → about 87 wanting the 06:00); timing still matters wherever a route has more than one service.</t>
+          <t>£19,690, not £19,690.00.</t>
         </is>
       </c>
       <c r="D198" s="13" t="inlineStr">
@@ -58649,17 +59765,15 @@
     <row r="199">
       <c r="A199" s="13" t="inlineStr">
         <is>
-          <t>demandShapeDisplay</t>
-        </is>
-      </c>
-      <c r="B199" s="13" t="inlineStr">
-        <is>
-          <t>route demand by band, flexible shown separately; the selected flight's catchable slice highlighted</t>
-        </is>
+          <t>adaptToOnlyFlight</t>
+        </is>
+      </c>
+      <c r="B199" s="13" t="n">
+        <v>0.5</v>
       </c>
       <c r="C199" s="13" t="inlineStr">
         <is>
-          <t>D101: the route card and the strip show demand as a shape across the day plus the 'any time' passengers, and when a flight is selected the part it can catch lights up (its band's locked passengers + the flexible ones not taken by earlier flights + the adapters).</t>
+          <t>D101: when time-locked passengers want a band with no service on their route, this share of them take the nearest service on that route instead. Fixes one-flight routes that could never fill (Marrakech: 76 → about 87 wanting the 06:00); timing still matters wherever a route has more than one service.</t>
         </is>
       </c>
       <c r="D199" s="13" t="inlineStr">
@@ -58671,17 +59785,17 @@
     <row r="200">
       <c r="A200" s="13" t="inlineStr">
         <is>
-          <t>flightTimeDecay</t>
+          <t>demandShapeDisplay</t>
         </is>
       </c>
       <c r="B200" s="13" t="inlineStr">
         <is>
-          <t>per kind of sum, whole game: Calculate twice, then Build, then Model</t>
+          <t>route demand by band, flexible shown separately; the selected flight's catchable slice highlighted</t>
         </is>
       </c>
       <c r="C200" s="13" t="inlineStr">
         <is>
-          <t>D101: flight-time sums count once for the whole game, not per aircraft and route; a plane already flying a route is never asked about it.</t>
+          <t>D101: the route card and the strip show demand as a shape across the day plus the 'any time' passengers, and when a flight is selected the part it can catch lights up (its band's locked passengers + the flexible ones not taken by earlier flights + the adapters).</t>
         </is>
       </c>
       <c r="D200" s="13" t="inlineStr">
@@ -58693,17 +59807,17 @@
     <row r="201">
       <c r="A201" s="13" t="inlineStr">
         <is>
-          <t>timeAnswerFormat</t>
+          <t>flightTimeDecay</t>
         </is>
       </c>
       <c r="B201" s="13" t="inlineStr">
         <is>
-          <t>hours + minutes (selector 0, 15, 30, 45)</t>
+          <t>per kind of sum, whole game: Calculate twice, then Build, then Model</t>
         </is>
       </c>
       <c r="C201" s="13" t="inlineStr">
         <is>
-          <t>D101: no decimal hours in answers or questions; '225 km ÷ 900 km/h = ? h ? min'.</t>
+          <t>D101: flight-time sums count once for the whole game, not per aircraft and route; a plane already flying a route is never asked about it.</t>
         </is>
       </c>
       <c r="D201" s="13" t="inlineStr">
@@ -58715,17 +59829,17 @@
     <row r="202">
       <c r="A202" s="13" t="inlineStr">
         <is>
-          <t>flightTimesTable</t>
+          <t>timeAnswerFormat</t>
         </is>
       </c>
       <c r="B202" s="13" t="inlineStr">
         <is>
-          <t>fixed-width columns; the active sum in the instrument below with its cell highlighted; a 'time saved' column between aircraft</t>
+          <t>hours + minutes (selector 0, 15, 30, 45)</t>
         </is>
       </c>
       <c r="C202" s="13" t="inlineStr">
         <is>
-          <t>D101: e.g. 'Twin Otter 1 h 30 → Saab 1 h: 30 min faster'.</t>
+          <t>D101: no decimal hours in answers or questions; '225 km ÷ 900 km/h = ? h ? min'.</t>
         </is>
       </c>
       <c r="D202" s="13" t="inlineStr">
@@ -58737,17 +59851,17 @@
     <row r="203">
       <c r="A203" s="13" t="inlineStr">
         <is>
-          <t>weekPlanTutorial</t>
+          <t>flightTimesTable</t>
         </is>
       </c>
       <c r="B203" s="13" t="inlineStr">
         <is>
-          <t>removed</t>
+          <t>fixed-width columns; the active sum in the instrument below with its cell highlighted; a 'time saved' column between aircraft</t>
         </is>
       </c>
       <c r="C203" s="13" t="inlineStr">
         <is>
-          <t>D101: the week-5 'Planning a whole week' tutorial goes; a one-line notice says the game now runs a week at a time.</t>
+          <t>D101: e.g. 'Twin Otter 1 h 30 → Saab 1 h: 30 min faster'.</t>
         </is>
       </c>
       <c r="D203" s="13" t="inlineStr">
@@ -58759,17 +59873,17 @@
     <row r="204">
       <c r="A204" s="13" t="inlineStr">
         <is>
-          <t>redMeans</t>
+          <t>weekPlanTutorial</t>
         </is>
       </c>
       <c r="B204" s="13" t="inlineStr">
         <is>
-          <t>only genuinely bad or urgent: an invalid timetable, a plane that can't reach a route, a real loss, a disruption</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="C204" s="13" t="inlineStr">
         <is>
-          <t>D101 amends D95: unserved demand and forecast variance are information, never red.</t>
+          <t>D101: the week-5 'Planning a whole week' tutorial goes; a one-line notice says the game now runs a week at a time.</t>
         </is>
       </c>
       <c r="D204" s="13" t="inlineStr">
@@ -58781,17 +59895,17 @@
     <row r="205">
       <c r="A205" s="13" t="inlineStr">
         <is>
-          <t>opportunityDisplay</t>
+          <t>redMeans</t>
         </is>
       </c>
       <c r="B205" s="13" t="inlineStr">
         <is>
-          <t>quiet type with an 'opportunity' label; gold only on the single biggest opportunity on a screen</t>
+          <t>only genuinely bad or urgent: an invalid timetable, a plane that can't reach a route, a real loss, a disruption</t>
         </is>
       </c>
       <c r="C205" s="13" t="inlineStr">
         <is>
-          <t>D101: keeps gold rare (D95).</t>
+          <t>D101 amends D95: unserved demand and forecast variance are information, never red.</t>
         </is>
       </c>
       <c r="D205" s="13" t="inlineStr">
@@ -58803,17 +59917,17 @@
     <row r="206">
       <c r="A206" s="13" t="inlineStr">
         <is>
-          <t>resultsFraming</t>
+          <t>opportunityDisplay</t>
         </is>
       </c>
       <c r="B206" s="13" t="inlineStr">
         <is>
-          <t>lead with the result and the comparison with last week; variance with its reasons; 'passengers we couldn't carry' totalled once; cash change as profit − fuel bought</t>
+          <t>quiet type with an 'opportunity' label; gold only on the single biggest opportunity on a screen</t>
         </is>
       </c>
       <c r="C206" s="13" t="inlineStr">
         <is>
-          <t>D101.</t>
+          <t>D101: keeps gold rare (D95).</t>
         </is>
       </c>
       <c r="D206" s="13" t="inlineStr">
@@ -58825,17 +59939,17 @@
     <row r="207">
       <c r="A207" s="13" t="inlineStr">
         <is>
-          <t>flightInspector</t>
+          <t>resultsFraming</t>
         </is>
       </c>
       <c r="B207" s="13" t="inlineStr">
         <is>
-          <t>fixed bar under the timetable</t>
+          <t>lead with the result and the comparison with last week; variance with its reasons; 'passengers we couldn't carry' totalled once; cash change as profit − fuel bought</t>
         </is>
       </c>
       <c r="C207" s="13" t="inlineStr">
         <is>
-          <t>D101: Earlier · Later · Route · Fare · Days · Aircraft · Remove; never moves; the focus rail marks the selected block.</t>
+          <t>D101.</t>
         </is>
       </c>
       <c r="D207" s="13" t="inlineStr">
@@ -58847,15 +59961,17 @@
     <row r="208">
       <c r="A208" s="13" t="inlineStr">
         <is>
-          <t>activeRoutesCollapsible</t>
-        </is>
-      </c>
-      <c r="B208" s="13" t="b">
-        <v>1</v>
+          <t>flightInspector</t>
+        </is>
+      </c>
+      <c r="B208" s="13" t="inlineStr">
+        <is>
+          <t>fixed bar under the timetable</t>
+        </is>
       </c>
       <c r="C208" s="13" t="inlineStr">
         <is>
-          <t>D101: collapses to one line ('7 routes · 9 flights a day · 98% filled · 2 need attention') with route chips; opens with a tap.</t>
+          <t>D101: Earlier · Later · Route · Fare · Days · Aircraft · Remove; never moves; the focus rail marks the selected block.</t>
         </is>
       </c>
       <c r="D208" s="13" t="inlineStr">
@@ -58867,17 +59983,15 @@
     <row r="209">
       <c r="A209" s="13" t="inlineStr">
         <is>
-          <t>weekGraphDefault</t>
-        </is>
-      </c>
-      <c r="B209" s="13" t="inlineStr">
-        <is>
-          <t>weekly history (profit per week so far, projection as a faint marker); 'this week by day' as a tab</t>
-        </is>
+          <t>activeRoutesCollapsible</t>
+        </is>
+      </c>
+      <c r="B209" s="13" t="b">
+        <v>1</v>
       </c>
       <c r="C209" s="13" t="inlineStr">
         <is>
-          <t>D101.</t>
+          <t>D101: collapses to one line ('7 routes · 9 flights a day · 98% filled · 2 need attention') with route chips; opens with a tap.</t>
         </is>
       </c>
       <c r="D209" s="13" t="inlineStr">
@@ -58889,17 +60003,17 @@
     <row r="210">
       <c r="A210" s="13" t="inlineStr">
         <is>
-          <t>dailyColourLimit</t>
+          <t>weekGraphDefault</t>
         </is>
       </c>
       <c r="B210" s="13" t="inlineStr">
         <is>
-          <t>at most two a week; never the same item twice in a row; no duplicate lines</t>
+          <t>weekly history (profit per week so far, projection as a faint marker); 'this week by day' as a tab</t>
         </is>
       </c>
       <c r="C210" s="13" t="inlineStr">
         <is>
-          <t>D101: tightens the DailyColour rule after a week showed four and a repeat.</t>
+          <t>D101.</t>
         </is>
       </c>
       <c r="D210" s="13" t="inlineStr">
@@ -58911,17 +60025,17 @@
     <row r="211">
       <c r="A211" s="13" t="inlineStr">
         <is>
-          <t>comingUp</t>
+          <t>dailyColourLimit</t>
         </is>
       </c>
       <c r="B211" s="13" t="inlineStr">
         <is>
-          <t>Roadmap sheet</t>
+          <t>at most two a week; never the same item twice in a row; no duplicate lines</t>
         </is>
       </c>
       <c r="C211" s="13" t="inlineStr">
         <is>
-          <t>D101: a 'Coming up' strip on Home (NOW · NEXT · LATER) and one line at the end of each review about next week. Planner upgrades are never named in advance.</t>
+          <t>D101: tightens the DailyColour rule after a week showed four and a repeat.</t>
         </is>
       </c>
       <c r="D211" s="13" t="inlineStr">
@@ -58933,17 +60047,17 @@
     <row r="212">
       <c r="A212" s="13" t="inlineStr">
         <is>
-          <t>aircraftWorthCheck</t>
+          <t>comingUp</t>
         </is>
       </c>
       <c r="B212" s="13" t="inlineStr">
         <is>
-          <t>inside the comparison, not a separate page</t>
+          <t>Roadmap sheet</t>
         </is>
       </c>
       <c r="C212" s="13" t="inlineStr">
         <is>
-          <t>D101: choosing a plane on 'Which aircraft should we add?' opens its worth check in place: WHY (the routes leaving people behind, with numbers) · WORK IT OUT (one full flight at the route's current fare) · WHAT IT MEANS (full-flight money → extra profit a day → payback, revealed one by one after the answer, payback as a coin bar). No numbered steps, no 'recommended routes', no sum counter; Give me a hint.</t>
+          <t>D101: a 'Coming up' strip on Home (NOW · NEXT · LATER) and one line at the end of each review about next week. Planner upgrades are never named in advance.</t>
         </is>
       </c>
       <c r="D212" s="13" t="inlineStr">
@@ -58955,17 +60069,17 @@
     <row r="213">
       <c r="A213" s="13" t="inlineStr">
         <is>
-          <t>teacherTestMode</t>
+          <t>aircraftWorthCheck</t>
         </is>
       </c>
       <c r="B213" s="13" t="inlineStr">
         <is>
-          <t>teacher panel, behind the PIN; amber TEST MODE bar; Answer · Answer all · Auto-plan · Run week/month · Skip briefing · Jump to… · Show the answer · Event now</t>
+          <t>inside the comparison, not a separate page</t>
         </is>
       </c>
       <c r="C213" s="13" t="inlineStr">
         <is>
-          <t>D102: for testing screens without playing every sum. Nothing in test mode reaches the record, milestones or sum numbering; test airlines saved separately and labelled TEST. Jump-to points along the Steady path: Launch Day, weeks 2, 3, 4, 5, 7, 9, December, January 2031, June 2031, chapter 3, chapter 4. Shortcuts Ctrl+Shift+T (tools), Ctrl+Shift+A (answer), Ctrl+Shift+R (run).</t>
+          <t>D101: choosing a plane on 'Which aircraft should we add?' opens its worth check in place: WHY (the routes leaving people behind, with numbers) · WORK IT OUT (one full flight at the route's current fare) · WHAT IT MEANS (full-flight money → extra profit a day → payback, revealed one by one after the answer, payback as a coin bar). No numbered steps, no 'recommended routes', no sum counter; Give me a hint.</t>
         </is>
       </c>
       <c r="D213" s="13" t="inlineStr">
@@ -58977,15 +60091,17 @@
     <row r="214">
       <c r="A214" s="13" t="inlineStr">
         <is>
-          <t>growthResponds</t>
-        </is>
-      </c>
-      <c r="B214" s="13" t="b">
-        <v>1</v>
+          <t>teacherTestMode</t>
+        </is>
+      </c>
+      <c r="B214" s="13" t="inlineStr">
+        <is>
+          <t>teacher panel, behind the PIN; amber TEST MODE bar; Answer · Answer all · Auto-plan · Run week/month · Skip briefing · Jump to… · Show the answer · Event now</t>
+        </is>
       </c>
       <c r="C214" s="13" t="inlineStr">
         <is>
-          <t>D104: a route's weekly growth depends on how it is served (Archetypes columns): base growthPerWeek; + growthFillBonus when the week's seat fill was ≥ 80% AND passengers were turned away; × growthFareDrag when the fare sits at the top option of its table (half when second from top); − growthDropDecay for each week the route is not flown, back towards its opening demand. Growth never passes growthCeiling.</t>
+          <t>D102: for testing screens without playing every sum. Nothing in test mode reaches the record, milestones or sum numbering; test airlines saved separately and labelled TEST. Jump-to points along the Steady path: Launch Day, weeks 2, 3, 4, 5, 7, 9, December, January 2031, June 2031, chapter 3, chapter 4. Shortcuts Ctrl+Shift+T (tools), Ctrl+Shift+A (answer), Ctrl+Shift+R (run).</t>
         </is>
       </c>
       <c r="D214" s="13" t="inlineStr">
@@ -58997,15 +60113,15 @@
     <row r="215">
       <c r="A215" s="13" t="inlineStr">
         <is>
-          <t>reputationFromDay</t>
-        </is>
-      </c>
-      <c r="B215" s="13" t="n">
-        <v>15</v>
+          <t>growthResponds</t>
+        </is>
+      </c>
+      <c r="B215" s="13" t="b">
+        <v>1</v>
       </c>
       <c r="C215" s="13" t="inlineStr">
         <is>
-          <t>D104: stars move from week 3 (not January): reputationDemandPerHalfStar applies from day 15. Drivers in chapter 1: a route with ≥ 20% of its demand turned away for two weeks running −½★ once; a cancelled or grounded flight −½★; free snacks for two weeks +½★; an on-time week with no event choice costing stars +½★ at the month review. Stars start at 3 and stay within 1–5.</t>
+          <t>D104: a route's weekly growth depends on how it is served (Archetypes columns): base growthPerWeek; + growthFillBonus when the week's seat fill was ≥ 80% AND passengers were turned away; × growthFareDrag when the fare sits at the top option of its table (half when second from top); − growthDropDecay for each week the route is not flown, back towards its opening demand. Growth never passes growthCeiling.</t>
         </is>
       </c>
       <c r="D215" s="13" t="inlineStr">
@@ -59017,15 +60133,15 @@
     <row r="216">
       <c r="A216" s="13" t="inlineStr">
         <is>
-          <t>newRouteUncertainty</t>
+          <t>reputationFromDay</t>
         </is>
       </c>
       <c r="B216" s="13" t="n">
-        <v>0.15</v>
+        <v>15</v>
       </c>
       <c r="C216" s="13" t="inlineStr">
         <is>
-          <t>D104: until a route has been flown for a week, the market sheet and route cards show its demand as a range (the table × (1 ± 0.15), e.g. 'about 50–70 at £90'); the true table is fixed and revealed after the first week. Paris and Dublin are known from the start.</t>
+          <t>D104: stars move from week 3 (not January): reputationDemandPerHalfStar applies from day 15. Drivers in chapter 1: a route with ≥ 20% of its demand turned away for two weeks running −½★ once; a cancelled or grounded flight −½★; free snacks for two weeks +½★; an on-time week with no event choice costing stars +½★ at the month review. Stars start at 3 and stay within 1–5.</t>
         </is>
       </c>
       <c r="D216" s="13" t="inlineStr">
@@ -59037,17 +60153,15 @@
     <row r="217">
       <c r="A217" s="13" t="inlineStr">
         <is>
-          <t>autumnTrack</t>
-        </is>
-      </c>
-      <c r="B217" s="13" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
+          <t>newRouteUncertainty</t>
+        </is>
+      </c>
+      <c r="B217" s="13" t="n">
+        <v>0.15</v>
       </c>
       <c r="C217" s="13" t="inlineStr">
         <is>
-          <t>D104: teacher setting. Track B is a second autumn for pupils who have played before: the same rules, a different order of events and different offers (Events/EventOptions/RouteNews rows with track = B). Items with track = both play on either.</t>
+          <t>D104: until a route has been flown for a week, the market sheet and route cards show its demand as a range (the table × (1 ± 0.15), e.g. 'about 50–70 at £90'); the true table is fixed and revealed after the first week. Paris and Dublin are known from the start.</t>
         </is>
       </c>
       <c r="D217" s="13" t="inlineStr">
@@ -59059,17 +60173,17 @@
     <row r="218">
       <c r="A218" s="13" t="inlineStr">
         <is>
-          <t>pupilReserve</t>
+          <t>autumnTrack</t>
         </is>
       </c>
       <c r="B218" s="13" t="inlineStr">
         <is>
-          <t>set by the pupil; default £0</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C218" s="13" t="inlineStr">
         <is>
-          <t>D103: replaces the fixed £1,000 emergency reserve. First set in Briefing 13; changeable on the Fuel desk and the Finance desk. The shop and the fuel desk show 'above your reserve' from it. The board nudges only if it is £0 and the airline runs short.</t>
+          <t>D104: teacher setting. Track B is a second autumn for pupils who have played before: the same rules, a different order of events and different offers (Events/EventOptions/RouteNews rows with track = B). Items with track = both play on either.</t>
         </is>
       </c>
       <c r="D218" s="13" t="inlineStr">
@@ -59081,17 +60195,17 @@
     <row r="219">
       <c r="A219" s="13" t="inlineStr">
         <is>
-          <t>bustRule</t>
+          <t>pupilReserve</t>
         </is>
       </c>
       <c r="B219" s="13" t="inlineStr">
         <is>
-          <t>3 grounded days in a week; the airline closes and starts again from Launch Day</t>
+          <t>set by the pupil; default £0</t>
         </is>
       </c>
       <c r="C219" s="13" t="inlineStr">
         <is>
-          <t>Claude Code, 19 Oct 2026: Bertie's rule of 18 Oct, repeated in the handover of 19 Oct (section 5: "he starts again from Launch Day (not the start of the chapter)"). (v6.0 had: three grounded days in a week → the airline closes; restart from the beginning of the current chapter)</t>
+          <t>D103: replaces the fixed £1,000 emergency reserve. First set in Briefing 13; changeable on the Fuel desk and the Finance desk. The shop and the fuel desk show 'above your reserve' from it. The board nudges only if it is £0 and the airline runs short.</t>
         </is>
       </c>
       <c r="D219" s="13" t="inlineStr">
@@ -59103,20 +60217,42 @@
     <row r="220">
       <c r="A220" s="13" t="inlineStr">
         <is>
+          <t>bustRule</t>
+        </is>
+      </c>
+      <c r="B220" s="13" t="inlineStr">
+        <is>
+          <t>3 grounded days in a week; the airline closes and starts again from Launch Day</t>
+        </is>
+      </c>
+      <c r="C220" s="13" t="inlineStr">
+        <is>
+          <t>Claude Code, 19 Oct 2026: Bertie's rule of 18 Oct, repeated in the handover of 19 Oct (section 5: "he starts again from Launch Day (not the start of the chapter)"). (v6.0 had: three grounded days in a week → the airline closes; restart from the beginning of the current chapter)</t>
+        </is>
+      </c>
+      <c r="D220" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="13" t="inlineStr">
+        <is>
           <t>standingAim</t>
         </is>
       </c>
-      <c r="B220" s="13" t="inlineStr">
+      <c r="B221" s="13" t="inlineStr">
         <is>
           <t>Make as much money as you can. | In January you'll choose what kind of airline you are. | Keep cash for emergencies: you decide how much. | Run out of cash and the airline closes. | You start again from Launch Day. No loans.</t>
         </is>
       </c>
-      <c r="C220" s="13" t="inlineStr">
+      <c r="C221" s="13" t="inlineStr">
         <is>
           <t>Claude Code, 19 Oct 2026: the card's lines as the handover gives them (lines separated by |; the last one "You start again from Launch Day."). (v6.0 had: year one: make as much money as you can; many good plans, some bad; run out of cash and the airline closes)</t>
         </is>
       </c>
-      <c r="D220" s="13" t="inlineStr">
+      <c r="D221" s="13" t="inlineStr">
         <is>
           <t>live</t>
         </is>

--- a/data/Airline-World-Workbook.xlsx
+++ b/data/Airline-World-Workbook.xlsx
@@ -585,7 +585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A46"/>
+  <dimension ref="A1:A47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -910,6 +910,13 @@
       <c r="A46" t="inlineStr">
         <is>
           <t>D105 (Claude Code, 19 Oct 2026, evening handover 7.10): every sum on the Sheet. Settings fuelDeskOpensDay = 1 (the Fuel desk from Launch Day, the order paid when it arrives on Wednesday); the SheetSums sheet lists every year-one sheet's sums (cells, formula, words, pupil or ƒ, book or build, the sum numbers of a week-1 run); BriefingData holds Cash, tank, profit's example (version A); the Briefings rows say what plays now that no briefing asks for a guess. Notes on launchDaySums, fuelHandSum and fuelDeskFromDay say what changed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>v6.1 (20 Oct) — release. Backlog 9–15 from Claude Code's D104 report: growth responds to service for the whole game (old rule withdrawn); the week-1 Red Kite undercut on both tracks; unflown routes project from the range midpoint ('about'); RouteNews rows for track B's Dublin concert and Amsterdam fair; the fault's £800 in its EventOptions rows; the turned-away star rule softened to 1 in 3, two weeks running, from week 5.</t>
         </is>
       </c>
     </row>
@@ -2227,7 +2234,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="17" t="inlineStr">
         <is>
@@ -3042,8 +3048,6 @@
           <t>airline</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>Filled once the ticket sums are done.</t>
@@ -3086,8 +3090,6 @@
           <t>airline</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>Flying, landing and passenger charges; the link lists them.</t>
@@ -3130,8 +3132,6 @@
           <t>airline</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>The fuel burned that day (7.6): £0 on Launch Day. The week's order is on the Fuel desk.</t>
@@ -3174,9 +3174,6 @@
           <t>airline</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3318,8 +3315,6 @@
           <t>airline</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>A fare change on its own route; Over a week is × 7.</t>
@@ -3760,7 +3755,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O104"/>
+  <dimension ref="A1:O106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4686,6 +4681,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
         <is>
@@ -10376,6 +10372,7 @@
         </is>
       </c>
     </row>
+    <row r="103"/>
     <row r="104">
       <c r="A104" s="17" t="inlineStr">
         <is>
@@ -10385,6 +10382,132 @@
       <c r="O104" t="inlineStr">
         <is>
           <t>both</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="17" t="inlineStr">
+        <is>
+          <t>dub_concert_b</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2030-09-23</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2030-10-05</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2030-10-05</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>culture</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>dub</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I105" t="b">
+        <v>1</v>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>A stadium concert in Dublin on Saturday 5 October: the city will be full.</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>A bigger plane, more flights or the top fare on Saturday only.</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="17" t="inlineStr">
+        <is>
+          <t>ams_fair_b</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2030-10-07</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>2030-10-14</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2030-10-20</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>economic</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>ams</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>business</t>
+        </is>
+      </c>
+      <c r="I106" t="b">
+        <v>1</v>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>A week-long trade fair in Amsterdam, 14–20 October: business travellers fill the morning flights.</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Raise the fare or add a morning service on Amsterdam for the week.</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -12092,6 +12215,7 @@
         </is>
       </c>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
         <is>
@@ -12252,7 +12376,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>both</t>
         </is>
       </c>
     </row>
@@ -12294,7 +12418,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>both</t>
         </is>
       </c>
     </row>
@@ -12336,7 +12460,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>both</t>
         </is>
       </c>
     </row>
@@ -12596,17 +12720,23 @@
       </c>
       <c r="D39" s="13" t="inlineStr">
         <is>
-          <t>Engineers in overnight</t>
-        </is>
-      </c>
-      <c r="E39" s="13" t="n"/>
+          <t>Engineers in overnight: £800 (before day 29); half a day's profit after</t>
+        </is>
+      </c>
+      <c r="E39" s="13" t="n">
+        <v>800</v>
+      </c>
       <c r="F39" s="13" t="n">
         <v>0.5</v>
       </c>
       <c r="G39" s="13" t="n">
         <v>0.5</v>
       </c>
-      <c r="H39" s="13" t="inlineStr"/>
+      <c r="H39" s="13" t="inlineStr">
+        <is>
+          <t>cost £800 up to day 28, then 0.5 × the day's profit</t>
+        </is>
+      </c>
       <c r="I39" s="13" t="inlineStr">
         <is>
           <t>live</t>
@@ -13590,17 +13720,23 @@
       </c>
       <c r="D63" s="13" t="inlineStr">
         <is>
-          <t>Engineers in overnight</t>
-        </is>
-      </c>
-      <c r="E63" s="13" t="n"/>
+          <t>Engineers in overnight: £800 (before day 29); half a day's profit after</t>
+        </is>
+      </c>
+      <c r="E63" s="13" t="n">
+        <v>800</v>
+      </c>
       <c r="F63" s="13" t="n">
         <v>0.5</v>
       </c>
       <c r="G63" s="13" t="n">
         <v>0.5</v>
       </c>
-      <c r="H63" s="13" t="inlineStr"/>
+      <c r="H63" s="13" t="inlineStr">
+        <is>
+          <t>cost £800 up to day 28, then 0.5 × the day's profit</t>
+        </is>
+      </c>
       <c r="I63" s="13" t="inlineStr">
         <is>
           <t>live</t>
@@ -48744,9 +48880,9 @@
           <t>Dublin fare becomes £50 next round</t>
         </is>
       </c>
-      <c r="H2" s="12" t="inlineStr"/>
-      <c r="I2" s="12" t="inlineStr"/>
-      <c r="J2" s="12" t="inlineStr"/>
+      <c r="H2" s="12" t="n"/>
+      <c r="I2" s="12" t="n"/>
+      <c r="J2" s="12" t="n"/>
       <c r="K2" s="12" t="inlineStr">
         <is>
           <t>switch share = min(0.6, 0.1 × (yourFare − 50) ÷ 10); options: match (your fare → £50), hold, advertise (£300, switch share halved, −½★ as before); the pupil may also move the plane to Paris</t>
@@ -48783,7 +48919,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>both</t>
         </is>
       </c>
     </row>
@@ -51492,6 +51628,7 @@
         </is>
       </c>
     </row>
+    <row r="56"/>
     <row r="57">
       <c r="A57" s="17" t="inlineStr">
         <is>
@@ -55619,7 +55756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D221"/>
+  <dimension ref="A1:D223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -60121,7 +60258,7 @@
       </c>
       <c r="C215" s="13" t="inlineStr">
         <is>
-          <t>D104: a route's weekly growth depends on how it is served (Archetypes columns): base growthPerWeek; + growthFillBonus when the week's seat fill was ≥ 80% AND passengers were turned away; × growthFareDrag when the fare sits at the top option of its table (half when second from top); − growthDropDecay for each week the route is not flown, back towards its opening demand. Growth never passes growthCeiling.</t>
+          <t>D104/v6.1: a route's weekly growth depends on how it is served for the WHOLE GAME (not year one only): base growthPerWeek; + growthFillBonus when the week's seat fill was ≥ 80% AND passengers were turned away; × growthFareDrag at the top fare (half the drag at the second from top); − growthDropDecay for each week not flown, back towards opening demand; never past growthCeiling. The old 'growthPerWeek × weeks since week 3' rule is withdrawn everywhere. Check at the chapter-2 re-run that long-haul routes do not fill too easily; if they do, long_haul_mixed's ceiling goes to 1.4.</t>
         </is>
       </c>
       <c r="D215" s="13" t="inlineStr">
@@ -60141,7 +60278,7 @@
       </c>
       <c r="C216" s="13" t="inlineStr">
         <is>
-          <t>D104: stars move from week 3 (not January): reputationDemandPerHalfStar applies from day 15. Drivers in chapter 1: a route with ≥ 20% of its demand turned away for two weeks running −½★ once; a cancelled or grounded flight −½★; free snacks for two weeks +½★; an on-time week with no event choice costing stars +½★ at the month review. Stars start at 3 and stay within 1–5.</t>
+          <t>D104: stars go public on day 15 (Mon 16 Sep) and reputationDemandPerHalfStar applies from then; the turned-away driver is judged from day 29 (starsTurnedAwayRule).</t>
         </is>
       </c>
       <c r="D216" s="13" t="inlineStr">
@@ -60253,6 +60390,50 @@
         </is>
       </c>
       <c r="D221" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="13" t="inlineStr">
+        <is>
+          <t>unflownProjection</t>
+        </is>
+      </c>
+      <c r="B222" s="13" t="inlineStr">
+        <is>
+          <t>the range midpoint, shown as 'about'</t>
+        </is>
+      </c>
+      <c r="C222" s="13" t="inlineStr">
+        <is>
+          <t>v6.1: for a route not yet flown a week, the plan's projection (seats filled at each fare, profit) and Change network's sort use the middle of the shown range and say 'about' ('about 14 of 19', 'about £1,200'); the true table is used only once the route has flown a week.</t>
+        </is>
+      </c>
+      <c r="D222" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="13" t="inlineStr">
+        <is>
+          <t>starsTurnedAwayRule</t>
+        </is>
+      </c>
+      <c r="B223" s="13" t="inlineStr">
+        <is>
+          <t>−½★ once per route when 1 in 3 of a route's demand is turned away two weeks running, judged from week 5 (day 29)</t>
+        </is>
+      </c>
+      <c r="C223" s="13" t="inlineStr">
+        <is>
+          <t>v6.1: softened from 1 in 5 and week 3, so stars move because of choices, not because the first planes were small. The other drivers unchanged: grounded day −½★; free snacks two weeks +½★ once; an on-time week +½★ once at each month's review.</t>
+        </is>
+      </c>
+      <c r="D223" s="13" t="inlineStr">
         <is>
           <t>live</t>
         </is>

--- a/data/Airline-World-Workbook.xlsx
+++ b/data/Airline-World-Workbook.xlsx
@@ -2234,6 +2234,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="17" t="inlineStr">
         <is>
@@ -2359,7 +2360,7 @@
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>Launch Day, before the cabin-sales Builds</t>
+          <t>Launch Day, before the cabin-sales Builds · Bertie, 20 Oct 2026: not needed (dropped)</t>
         </is>
       </c>
       <c r="C16" s="13" t="inlineStr">
@@ -2402,7 +2403,7 @@
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>dropped</t>
         </is>
       </c>
     </row>
@@ -4681,7 +4682,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
         <is>
@@ -10372,7 +10372,6 @@
         </is>
       </c>
     </row>
-    <row r="103"/>
     <row r="104">
       <c r="A104" s="17" t="inlineStr">
         <is>
@@ -12215,7 +12214,6 @@
         </is>
       </c>
     </row>
-    <row r="26"/>
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
         <is>
@@ -51628,7 +51626,6 @@
         </is>
       </c>
     </row>
-    <row r="56"/>
     <row r="57">
       <c r="A57" s="17" t="inlineStr">
         <is>

--- a/data/Airline-World-Workbook.xlsx
+++ b/data/Airline-World-Workbook.xlsx
@@ -585,7 +585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A47"/>
+  <dimension ref="A1:A48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -917,6 +917,13 @@
       <c r="A47" t="inlineStr">
         <is>
           <t>v6.1 (20 Oct) — release. Backlog 9–15 from Claude Code's D104 report: growth responds to service for the whole game (old rule withdrawn); the week-1 Red Kite undercut on both tracks; unflown routes project from the range midpoint ('about'); RouteNews rows for track B's Dublin concert and Amsterdam fair; the fault's £800 in its EventOptions rows; the turned-away star rule softened to 1 in 3, two weeks running, from week 5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>20 Oct 2026 (Claude Code, Bertie's DESIGN.md of 20 Oct, briefings review): snacks on board dropped from the game in year one (Settings snacksInYearOne off; Calendar day 1 headline and Chapters 1 text without snacks; the snack supplier event removed; the mystery shopper's option 1 now "Seats, service, signs"); the briefings More demand than seats (full_route) and Snacks on board (cabin_sales) removed.</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1809,7 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>Week-1 review</t>
+          <t>Week-1 review · Bertie, 20 Oct 2026 (DESIGN.md): retired as a briefing; its ideas move into How an airline makes money, What a fare does, Two planes and Can I afford the plane (scene-by-scene doc)</t>
         </is>
       </c>
       <c r="C4" s="13" t="inlineStr">
@@ -1845,7 +1852,7 @@
       </c>
       <c r="K4" s="13" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>removed</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2367,7 @@
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>Launch Day, before the cabin-sales Builds · Bertie, 20 Oct 2026: not needed (dropped)</t>
+          <t>Launch Day, before the cabin-sales Builds · Bertie, 20 Oct 2026: not needed (removed)</t>
         </is>
       </c>
       <c r="C16" s="13" t="inlineStr">
@@ -2403,7 +2410,7 @@
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>dropped</t>
+          <t>removed</t>
         </is>
       </c>
     </row>
@@ -3276,7 +3283,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Built by clicking the cells the first time (a Build-level sum), then answered in the cell.</t>
+          <t>Built by clicking the cells the first time (a Build-level sum), then answered in the cell. · Not on the sheet: Bertie, 20 Oct 2026 (DESIGN.md): snacks on board are dropped from the game, so the Launch Day sheet has no Cabin sales rows (year one; Settings snacksInYearOne).</t>
         </is>
       </c>
     </row>
@@ -3738,6 +3745,7 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
@@ -11808,7 +11816,7 @@
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>Seats, snacks, signs</t>
+          <t>Seats, service, signs</t>
         </is>
       </c>
       <c r="E15" s="13" t="n"/>
@@ -12214,6 +12222,7 @@
         </is>
       </c>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
         <is>
@@ -13175,7 +13184,7 @@
       </c>
       <c r="I50" s="13" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="J50" s="13" t="inlineStr">
@@ -13219,7 +13228,7 @@
       </c>
       <c r="I51" s="13" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="J51" s="13" t="inlineStr">
@@ -14971,12 +14980,12 @@
       </c>
       <c r="H2" s="13" t="inlineStr">
         <is>
-          <t>Running an airline a week at a time: the standing plan on one page (timetable with demand curve, fare, snacks, fuel), the week on the operations board, the weekly review</t>
+          <t>Running an airline a week at a time: the standing plan on one page (timetable with demand curve, fare, fuel), the week on the operations board, the weekly review</t>
         </is>
       </c>
       <c r="I2" s="13" t="inlineStr">
         <is>
-          <t>Launch Day: timetable, fare, snacks, fuel, both routes, modelling tool, workings page; week 2: second plane bought outright or wait for a bigger one; time-to-afford sum; week 3: four routes, £5 fares, seasons, use-it-or-lose-it; week 4: medium haul, range, E175/E190, load factor %; from week 5: weekly skips, Marrakech, the autumn pairs, scaled event costs</t>
+          <t>Launch Day: timetable, fare, fuel, both routes, modelling tool, workings page; week 2: second plane bought outright or wait for a bigger one; time-to-afford sum; week 3: four routes, £5 fares, seasons, use-it-or-lose-it; week 4: medium haul, range, E175/E190, load factor %; from week 5: weekly skips, Marrakech, the autumn pairs, scaled event costs</t>
         </is>
       </c>
       <c r="J2" s="13" t="n">
@@ -15273,6 +15282,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="17" t="inlineStr">
         <is>
@@ -21516,7 +21526,7 @@
       </c>
       <c r="H2" s="13" t="inlineStr">
         <is>
-          <t>Your airline is cleared for take-off. Build the week's plan: timetable, fare, snacks, fuel.</t>
+          <t>Your airline is cleared for take-off. Build the week's plan: timetable, fare, fuel.</t>
         </is>
       </c>
       <c r="I2" s="13" t="inlineStr">
@@ -51143,13 +51153,13 @@
       <c r="J46" s="13" t="n"/>
       <c r="K46" s="13" t="inlineStr">
         <is>
-          <t>from the day chosen</t>
+          <t>from the day chosen · removed: Bertie, 20 Oct 2026 (DESIGN.md): snacks on board are dropped from the game (no snack stock to buy)</t>
         </is>
       </c>
       <c r="L46" s="13" t="n"/>
       <c r="M46" s="13" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>removed</t>
         </is>
       </c>
       <c r="N46" s="13" t="n"/>
@@ -51626,6 +51636,7 @@
         </is>
       </c>
     </row>
+    <row r="56"/>
     <row r="57">
       <c r="A57" s="17" t="inlineStr">
         <is>
@@ -55753,7 +55764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D223"/>
+  <dimension ref="A1:D224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -60431,6 +60442,28 @@
         </is>
       </c>
       <c r="D223" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>snacksInYearOne</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>off</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Bertie, 20 Oct 2026 (DESIGN.md): snacks on board are dropped from the game, so the Launch Day sheet has no Cabin sales rows. off: no snack choice, no snack money, no Cabin sales sums, and the snack-only daily colours (hen party, birthday cake) give way to another, from Launch Day to the year-1 accounts. Chapters 3 and 4 keep snacks until Bertie says "extend". on: snacks as before.</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
         <is>
           <t>live</t>
         </is>

--- a/data/Airline-World-Workbook.xlsx
+++ b/data/Airline-World-Workbook.xlsx
@@ -21,24 +21,25 @@
     <sheet name="Briefings" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="BriefingData" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="SheetSums" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="RouteNews" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Archetypes" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="EventOptions" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Milestones" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Campaign" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Routes" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="RouteCatalogue" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Aircraft" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Finance" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Airports" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Calendar" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="Market" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="Events" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="Challenges" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="Mechanics" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="Catering" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="Hunts" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet name="Livery" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="ScreenText" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="RouteNews" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Archetypes" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="EventOptions" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Milestones" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Campaign" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Routes" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="RouteCatalogue" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Aircraft" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Finance" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Airports" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="Calendar" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="Market" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="Events" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="Challenges" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="Mechanics" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="Catering" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="Hunts" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="Livery" sheetId="33" state="visible" r:id="rId33"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -151,7 +152,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -220,6 +221,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -585,7 +589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A48"/>
+  <dimension ref="A1:A49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -924,6 +928,13 @@
       <c r="A48" t="inlineStr">
         <is>
           <t>20 Oct 2026 (Claude Code, Bertie's DESIGN.md of 20 Oct, briefings review): snacks on board dropped from the game in year one (Settings snacksInYearOne off; Calendar day 1 headline and Chapters 1 text without snacks; the snack supplier event removed; the mystery shopper's option 1 now "Seats, service, signs"); the briefings More demand than seats (full_route) and Snacks on board (cabin_sales) removed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="26" t="inlineStr">
+        <is>
+          <t>21 Oct 2026 (Claude Code, Bertie's play-test of 21 Oct, approved on mock-ups): SheetSums gains how = formula (he builds the formula and the sheet shows the answer; no book, no Sum number): the Sunday review's Profit this week and Average a day, all weeks; the difference from the plan stays a book sum, and the later Sum numbers close up. Σ SUM (drag down a column) unlocks at the week 3 review (Calendar day 21, skills: sumDrag; Settings spreadsheetFunctionsFromDate's note). Launch Day's first ticket column (B4) is a Build; C4 and D4 stay Calculate. Week 3's flight times are a small sheet: Amsterdam and Barcelona are the pupil's, Frankfurt and Geneva ƒ (both 675 km). The new ScreenText sheet holds the round's tour, callout and line texts (the Fuel desk tour, the week 3 plan opener and Studio, the Changes sheet, the review and flight times). The Briefings row flight_time is rebuilt in six scenes (Bertie's order).</t>
         </is>
       </c>
     </row>
@@ -1255,6 +1266,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
         <is>
@@ -1600,6 +1612,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="17" t="inlineStr">
         <is>
@@ -2267,22 +2280,22 @@
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>A route bar; the plane flies it an hour at a time, each hour the same chunk.</t>
+          <t>Why it matters: a Saab 340 (450 km/h) and his Twin Otter (300 km/h) leave London for Amsterdam (450 km) side by side; the Saab lands, turns round and sets off again while the Twin Otter is still flying. "A faster plane fits more flights into a day, but it can cost more in fuel."</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>The plane flies there an hour at a time on its own, the last bit a quarter hour at a time; then the T lights on the triangle (no buttons, no tap).</t>
+          <t>Predict (21 Oct 2026): "How long will the Twin Otter take?" 1 hour · 1 h 30 · 2 hours · Not sure. It is two-thirds of the way there when the Saab lands.</t>
         </is>
       </c>
       <c r="F14" s="13" t="inlineStr">
         <is>
-          <t>Time = distance ÷ speed, with the triangle (tap the one you want).</t>
+          <t>The sum on screen, step by step: the whole hours (450 km ÷ 300 km/h: 300 goes into 450 once, 1 hour, 150 km left over; "You predicted: …" beside it); the part left over (150 km is half of 300 km, so 30 minutes: 1 hour + 30 minutes = 1 h 30 min); then the ruler checks it (one hour to the 300 km mark, then the last 150 km in quarter hours: it lands at 1 h 30, the same as the sum).</t>
         </is>
       </c>
       <c r="G14" s="13" t="inlineStr">
         <is>
-          <t>The Flight times page, first sum</t>
+          <t>His routes: the Flight times sheet (week 3).</t>
         </is>
       </c>
       <c r="H14" s="13" t="inlineStr">
@@ -2291,11 +2304,11 @@
         </is>
       </c>
       <c r="I14" s="13" t="n">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="J14" s="13" t="inlineStr">
         <is>
-          <t>flight-time-tutorial.html</t>
+          <t>briefing-time.html</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
@@ -2849,7 +2862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2924,7 +2937,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>B4 · C4 · D4</t>
+          <t>B4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2934,7 +2947,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>= B2 × B3 (and C, D)</t>
+          <t>= B2 × B3</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -2949,12 +2962,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>book</t>
+          <t>build</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1–3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -2964,7 +2977,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>The first market at three fares around the pupil's own (one column each); worked out in the book, typed in the cell.</t>
+          <t>The first market's first column (the lowest of the three fares around the pupil's own): a Build. He clicks B2 then B3 (the formula bar shows = B2 × B3), works it out in his book and types the answer. 21 Oct 2026: Bertie said yes on 20 Oct to Launch Day having one Build.</t>
         </is>
       </c>
     </row>
@@ -2976,7 +2989,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>E4</t>
+          <t>C4 · D4</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2986,7 +2999,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>= E2 × E3</t>
+          <t>= C2 × C3 (and D)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -3006,17 +3019,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2–3</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>launch.otherTickets</t>
+          <t>launch.tickets</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Each other route in the plan, a column each.</t>
+          <t>The first market's other two fares: the formula is on the bar; worked out in the book, typed in the cell (Calculate). The game reads how for each cell (B4 build, C4 and D4 book).</t>
         </is>
       </c>
     </row>
@@ -3028,37 +3041,47 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>F5</t>
+          <t>E4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Total revenue</t>
+          <t>Ticket revenue</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>= the plan's ticket revenue</t>
+          <t>= E2 × E3</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ticket revenue (the plan)</t>
+          <t>Passengers × Fare</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ƒ</t>
+          <t>pupil</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>airline</t>
+          <t>book</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>launch.otherTickets</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Filled once the ticket sums are done.</t>
+          <t>Each other route in the plan, a column each.</t>
         </is>
       </c>
     </row>
@@ -3070,22 +3093,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>F6</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Other costs</t>
+          <t>Total revenue</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>given</t>
+          <t>= the plan's ticket revenue</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>What's in this?</t>
+          <t>Ticket revenue (the plan)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -3100,7 +3123,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Flying, landing and passenger charges; the link lists them.</t>
+          <t>Filled once the ticket sums are done.</t>
         </is>
       </c>
     </row>
@@ -3112,22 +3135,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>F7</t>
+          <t>F6</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fuel burned</t>
+          <t>Other costs</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>£0</t>
+          <t>given</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>free on Launch Day</t>
+          <t>What's in this?</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -3142,7 +3165,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>The fuel burned that day (7.6): £0 on Launch Day. The week's order is on the Fuel desk.</t>
+          <t>Flying, landing and passenger charges; the link lists them.</t>
         </is>
       </c>
     </row>
@@ -3154,22 +3177,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>F8</t>
+          <t>F7</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Total costs</t>
+          <t>Fuel burned</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>= F6 + F7</t>
+          <t>£0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Other costs + Fuel burned</t>
+          <t>free on Launch Day</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -3180,6 +3203,11 @@
       <c r="G7" t="inlineStr">
         <is>
           <t>airline</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>The fuel burned that day (7.6): £0 on Launch Day. The week's order is on the Fuel desk.</t>
         </is>
       </c>
     </row>
@@ -3191,47 +3219,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>F9</t>
+          <t>F8</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Profit</t>
+          <t>Total costs</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>= F5 − F8</t>
+          <t>= F6 + F7</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Total revenue − Total costs</t>
+          <t>Other costs + Fuel burned</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>pupil</t>
+          <t>ƒ</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>book</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>launch.profit</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>A loss gets a minus sign.</t>
+          <t>airline</t>
         </is>
       </c>
     </row>
@@ -3243,22 +3256,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>B13 · C13</t>
+          <t>F9</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cabin sales</t>
+          <t>Profit</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>= B11 × B12</t>
+          <t>= F5 − F8</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Passengers buying snacks × Snack price</t>
+          <t>Total revenue − Total costs</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -3268,64 +3281,74 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>build</t>
+          <t>book</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6–7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>launch.cabin</t>
+          <t>launch.profit</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Built by clicking the cells the first time (a Build-level sum), then answered in the cell. · Not on the sheet: Bertie, 20 Oct 2026 (DESIGN.md): snacks on board are dropped from the game, so the Launch Day sheet has no Cabin sales rows (year one; Settings snacksInYearOne).</t>
+          <t>A loss gets a minus sign.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Changes (week 2 on)</t>
+          <t>Launch Day</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>B2…C7</t>
+          <t>B13 · C13</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Passengers a day, Empty seats, Fare, Ticket revenue a day, Over a week</t>
+          <t>Cabin sales</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>given and ƒ</t>
+          <t>= B11 × B12</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Now · With your change</t>
+          <t>Passengers buying snacks × Snack price</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ƒ</t>
+          <t>pupil</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>airline</t>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>launch.cabin</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>A fare change on its own route; Over a week is × 7.</t>
+          <t>Built by clicking the cells the first time (a Build-level sum), then answered in the cell. · Not on the sheet: Bertie, 20 Oct 2026 (DESIGN.md): snacks on board are dropped from the game, so the Launch Day sheet has no Cabin sales rows (year one; Settings snacksInYearOne).</t>
         </is>
       </c>
     </row>
@@ -3337,47 +3360,37 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>B2…C7</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Difference (a fare change: ticket revenue a day)</t>
+          <t>Passengers a day, Empty seats, Fare, Ticket revenue a day, Over a week</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>= C5 − B5</t>
+          <t>given and ƒ</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>With your change − Now</t>
+          <t>Now · With your change</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>pupil</t>
+          <t>ƒ</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>build once</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>next</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>changes.difference</t>
+          <t>airline</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Built the first time, then from the book. "Worth keeping?": green "✓ Yes, +£60 a day", or plain "Not worth keeping: −£40 a day".</t>
+          <t>A fare change on its own route; Over a week is × 7.</t>
         </is>
       </c>
     </row>
@@ -3389,17 +3402,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Difference (a plan change: profit a day)</t>
+          <t>Difference (a fare change: ticket revenue a day)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>= C7 − B7</t>
+          <t>= C5 − B5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -3429,34 +3442,34 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Flights, passengers, empty seats, revenue, costs and profit a day for the plan; the same sum.</t>
+          <t>Built the first time, then from the book. "Worth keeping?": green "✓ Yes, +£60 a day", or plain "Not worth keeping: −£40 a day".</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Event sums</t>
+          <t>Changes (week 2 on)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>B4</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Stay with you</t>
+          <t>Difference (a plan change: profit a day)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>= B2 × B3</t>
+          <t>= C7 − B7</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Your passengers × Stay with you, in every 10</t>
+          <t>With your change − Now</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -3466,22 +3479,22 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>book</t>
+          <t>build once</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>next</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>event.stay</t>
+          <t>changes.difference</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Under the rows of ten (3.4). People, so no £. Whole people: the answer rounds (62 × 0.6 = 37.2 → 37).</t>
+          <t>Flights, passengers, empty seats, revenue, costs and profit a day for the plan; the same sum.</t>
         </is>
       </c>
     </row>
@@ -3498,7 +3511,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Business travellers today</t>
+          <t>Stay with you</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3508,7 +3521,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Business travellers on a weekday × Fly on a Saturday, in every 10</t>
+          <t>Your passengers × Stay with you, in every 10</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3523,44 +3536,44 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>event.business</t>
+          <t>event.stay</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Whole people (3.4): 34 × 0.7 = 23.8 → 24 in the game (the handover's 17 × 0.7 = 11.9 is the picture's example). 23.8 is accepted and the line says "People come whole: 23.8 rounds to 24."</t>
+          <t>Under the rows of ten (3.4). People, so no £. Whole people: the answer rounds (62 × 0.6 = 37.2 → 37).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sunday review</t>
+          <t>Event sums</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>B9</t>
+          <t>B4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Profit this week</t>
+          <t>Business travellers today</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>= B2 + B3 + … + B8</t>
+          <t>= B2 × B3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mon + Tue + … + Sun</t>
+          <t>Business travellers on a weekday × Fly on a Saturday, in every 10</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3570,22 +3583,22 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>build</t>
+          <t>book</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>week.total</t>
+          <t>event.business</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>The seven day cells are outlined without A / B tags.</t>
+          <t>Whole people (3.4): 34 × 0.7 = 23.8 → 24 in the game (the handover's 17 × 0.7 = 11.9 is the picture's example). 23.8 is accepted and the line says "People come whole: 23.8 rounds to 24."</t>
         </is>
       </c>
     </row>
@@ -3597,22 +3610,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>B11</t>
+          <t>B9</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Difference from the plan</t>
+          <t>Profit this week</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>= B10 − B9 (the larger first)</t>
+          <t>= B2 + B3 + … + B8 (weeks 1–2) · =SUM(B2:B8) with Σ SUM (from week 3)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Projected on Monday − Profit this week</t>
+          <t>Mon + Tue + … + Sun</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3622,22 +3635,22 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>build</t>
+          <t>formula</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>— (no Sum number)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>week.difference</t>
+          <t>week.total</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Taken larger first so it never goes below zero; the cell says more or less than planned.</t>
+          <t>21 Oct 2026 (Bertie, play-test of 21 Oct): the sheet does the adding. He builds the formula and the sheet shows the total at once (gold); nothing in his book, no Sum number. Weeks 1 and 2: he clicks Mon to Sun into the formula one cell at a time (outlined, no A / B tags). From the week 3 review (Calendar day 21, skills: sumDrag) he presses Σ SUM and drags down the Profit column from Monday's profit to Sunday's.</t>
         </is>
       </c>
     </row>
@@ -3649,22 +3662,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>B13</t>
+          <t>B11</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Average a day</t>
+          <t>Difference from the plan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>= B9 ÷ B12</t>
+          <t>= B10 − B9 (the larger first)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Profit this week ÷ Days flown</t>
+          <t>Projected on Monday − Profit this week</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3679,77 +3692,317 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>week.average</t>
+          <t>week.difference</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Days flown (B12) holds 7: every figure the sum uses is on the sheet.</t>
+          <t>Taken larger first so it never goes below zero; the cell says how far above or below the plan. 21 Oct 2026: stays a book sum (Sum n): he clicks the two cells, works it out in his book and types it in the cell.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Sunday review</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>B13</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Average a day</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>= B9 ÷ B12</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Profit this week ÷ Days flown</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>pupil</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>formula</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>— (no Sum number)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>week.average</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Days flown (B12) holds 7: every figure the sum uses is on the sheet. 21 Oct 2026: formula-only. He clicks Profit this week and Days flown (= B9 ÷ B12) and the sheet works out the average, rounded to the nearest pound.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>Fuel desk</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>B4</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Cost of this order</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>= B2 × B3</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Litres to buy × Price a litre</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>pupil</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>book</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
         <is>
           <t>fuel.order</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>From Launch Day (fuelDeskOpensDay). The level follows the toolkit (Calculate: book; Build: built; Model: ƒ). Two tries, then Finance fills it.</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sum numbers come from the game at run time (a running number per pupil, sumNumbering); the column above is a week-1 Steady run with the day-1 jump, for reading the sheets against. whose: pupil (worked out by the pupil) or ƒ (worked out by the airline). how: book (the formula is on the bar; worked out in the book and typed in the cell), build (built by clicking the cells, then typed), build once (built the first time, then book).</t>
+          <t>Flight times (week 3)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>= B2 ÷ C2</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Distance ÷ Speed</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>pupil</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>next</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>flight.time</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>The first flight-time sum: a Build. He clicks B2 (Distance) then C2 (Speed); the formula bar shows = B2 ÷ C2 and "Distance ÷ Speed". The answer cell takes hours and minutes (an h box and a minutes list: 0, 15, 30, 45), never a decimal. 450 km ÷ 300 km/h = 1 h 30 min.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Flight times (week 3)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Frankfurt</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>= B3 ÷ C3</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Distance ÷ Speed</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>ƒ</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>airline</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Worked out by the game: grey figures with ƒ ("ƒ worked out for you" under the sheet). 675 km, 2 h 15 min. Frankfurt and Geneva are both 675 km, so asking one and showing the other would give the answer away (21 Oct 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Flight times (week 3)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Geneva</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>= B4 ÷ C4</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Distance ÷ Speed</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>ƒ</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>airline</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Worked out by the game, as Frankfurt (675 km, 2 h 15 min).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Flight times (week 3)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>= B5 ÷ C5</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Distance ÷ Speed</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>pupil</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>book</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>next</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>flight.time</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>The second: the formula is on the bar (= B5 ÷ C5); worked out in his book, typed as hours and minutes. 1,125 km ÷ 300 km/h = 3 h 45 min. The cell stays blank until its turn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Sum numbers come from the game at run time (a running number per pupil, sumNumbering); the column above is a week-1 Steady run with the day-1 jump, for reading the sheets against. whose: pupil (worked out by the pupil) or ƒ (worked out by the airline). how: book (the formula is on the bar; worked out in the book and typed in the cell), build (built by clicking the cells, then typed), build once (built the first time, then book), formula (21 Oct 2026: he builds the formula by clicking the cells and the sheet shows the answer at once; no book, no Sum number). A row's cells may be listed with · (B4 · C4); where one sum differs by cell, each cell has its own row (Launch Day B4, then C4 · D4). Flight times: the row is the route; the pupil's routes are worked in the order listed.</t>
         </is>
       </c>
     </row>
@@ -3759,6 +4012,865 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="90" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="25" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="25" t="inlineStr">
+        <is>
+          <t>screen</t>
+        </is>
+      </c>
+      <c r="C1" s="25" t="inlineStr">
+        <is>
+          <t>eyebrow</t>
+        </is>
+      </c>
+      <c r="D1" s="25" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="E1" s="25" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1" s="25" t="inlineStr">
+        <is>
+          <t>button</t>
+        </is>
+      </c>
+      <c r="G1" s="25" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="26" t="inlineStr">
+        <is>
+          <t>fuel.tour.1</t>
+        </is>
+      </c>
+      <c r="B2" s="26" t="inlineStr">
+        <is>
+          <t>Fuel desk, first-visit tour, step 1: Your position (the tank gauge ringed)</t>
+        </is>
+      </c>
+      <c r="C2" s="26" t="inlineStr"/>
+      <c r="D2" s="26" t="inlineStr">
+        <is>
+          <t>Your tank</t>
+        </is>
+      </c>
+      <c r="E2" s="26" t="inlineStr">
+        <is>
+          <t>holds {capacity}, {weeks}. The dashed line shows the {need} this week needs.</t>
+        </is>
+      </c>
+      <c r="F2" s="26" t="inlineStr">
+        <is>
+          <t>Next ▶</t>
+        </is>
+      </c>
+      <c r="G2" s="26" t="inlineStr">
+        <is>
+          <t>21 Oct 2026, section 1. In the box at the foot of Your position. {capacity}: the tank (8,000 L); {weeks}: the storage in weeks of flying; {need}: this week's need (4,200 L). The title is bold before the text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="26" t="inlineStr">
+        <is>
+          <t>fuel.tour.2</t>
+        </is>
+      </c>
+      <c r="B3" s="26" t="inlineStr">
+        <is>
+          <t>Fuel desk tour, step 2: Market</t>
+        </is>
+      </c>
+      <c r="C3" s="26" t="inlineStr"/>
+      <c r="D3" s="26" t="inlineStr">
+        <is>
+          <t>Market:</t>
+        </is>
+      </c>
+      <c r="E3" s="26" t="inlineStr">
+        <is>
+          <t>today's price for a litre, and what it might cost next week. The news underneath says why.</t>
+        </is>
+      </c>
+      <c r="F3" s="26" t="inlineStr">
+        <is>
+          <t>Next ▶</t>
+        </is>
+      </c>
+      <c r="G3" s="26" t="inlineStr">
+        <is>
+          <t>In the empty space under the Market panel (its width), pointer up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="26" t="inlineStr">
+        <is>
+          <t>fuel.tour.3</t>
+        </is>
+      </c>
+      <c r="B4" s="26" t="inlineStr">
+        <is>
+          <t>Fuel desk tour, step 3: Place a purchase order</t>
+        </is>
+      </c>
+      <c r="C4" s="26" t="inlineStr"/>
+      <c r="D4" s="26" t="inlineStr">
+        <is>
+          <t>Place a purchase order:</t>
+        </is>
+      </c>
+      <c r="E4" s="26" t="inlineStr">
+        <is>
+          <t>choose how many litres to buy. Then build the cost on the sheet and work it out in your book.</t>
+        </is>
+      </c>
+      <c r="F4" s="26" t="inlineStr">
+        <is>
+          <t>Got it</t>
+        </is>
+      </c>
+      <c r="G4" s="26" t="inlineStr">
+        <is>
+          <t>In the same place under Market, pointer left at the order panel. The order sheet stays idle until this step.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="26" t="inlineStr">
+        <is>
+          <t>opener.newRoutes</t>
+        </is>
+      </c>
+      <c r="B5" s="26" t="inlineStr">
+        <is>
+          <t>Week plan opener: This week, the first row in the week routes open</t>
+        </is>
+      </c>
+      <c r="C5" s="26" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D5" s="26" t="inlineStr"/>
+      <c r="E5" s="26" t="inlineStr">
+        <is>
+          <t>{Count} new routes open: {routes}.</t>
+        </is>
+      </c>
+      <c r="F5" s="26" t="inlineStr">
+        <is>
+          <t>Add a route ›</t>
+        </is>
+      </c>
+      <c r="G5" s="26" t="inlineStr">
+        <is>
+          <t>21 Oct 2026, section 4. {Count}: how many, in words; {routes}: the routes that open that week (Routes sheet, unlockDay). "Add a route ›" opens the Studio's Add / change routes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="26" t="inlineStr">
+        <is>
+          <t>opener.newRoute</t>
+        </is>
+      </c>
+      <c r="B6" s="26" t="inlineStr">
+        <is>
+          <t>Week plan opener: the same row when one route opens</t>
+        </is>
+      </c>
+      <c r="C6" s="26" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="D6" s="26" t="inlineStr"/>
+      <c r="E6" s="26" t="inlineStr">
+        <is>
+          <t>A new route opens: {routes}.</t>
+        </is>
+      </c>
+      <c r="F6" s="26" t="inlineStr">
+        <is>
+          <t>Add a route ›</t>
+        </is>
+      </c>
+      <c r="G6" s="26" t="inlineStr">
+        <is>
+          <t>One route (week 4: Madrid).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="26" t="inlineStr">
+        <is>
+          <t>opener.weekends</t>
+        </is>
+      </c>
+      <c r="B7" s="26" t="inlineStr">
+        <is>
+          <t>Week plan opener: first-time callout on the Mon–Fri / Sat–Sun switch (the first week Days exist)</t>
+        </is>
+      </c>
+      <c r="C7" s="26" t="inlineStr">
+        <is>
+          <t>NEW · WEEKENDS</t>
+        </is>
+      </c>
+      <c r="D7" s="26" t="inlineStr">
+        <is>
+          <t>Plan Saturday and Sunday on their own</t>
+        </is>
+      </c>
+      <c r="E7" s="26" t="inlineStr">
+        <is>
+          <t>Different numbers of people want to fly at the weekend. Switch to **Sat–Sun** to see the weekend's flights, then edit the plan to fit.</t>
+        </is>
+      </c>
+      <c r="F7" s="26" t="inlineStr">
+        <is>
+          <t>Got it</t>
+        </is>
+      </c>
+      <c r="G7" s="26" t="inlineStr">
+        <is>
+          <t>In the empty part of the timetable panel, joined to the switch by a cyan leader line. Shows once.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="26" t="inlineStr">
+        <is>
+          <t>studio.routes</t>
+        </is>
+      </c>
+      <c r="B8" s="26" t="inlineStr">
+        <is>
+          <t>Studio: first-time callout under Add / change routes (the week routes open)</t>
+        </is>
+      </c>
+      <c r="C8" s="26" t="inlineStr">
+        <is>
+          <t>NEW · ROUTES</t>
+        </is>
+      </c>
+      <c r="D8" s="26" t="inlineStr">
+        <is>
+          <t>{Count} new routes open this week</t>
+        </is>
+      </c>
+      <c r="E8" s="26" t="inlineStr">
+        <is>
+          <t>{routes}. Add one here, then give it flights on the timetable.</t>
+        </is>
+      </c>
+      <c r="F8" s="26" t="inlineStr">
+        <is>
+          <t>Got it</t>
+        </is>
+      </c>
+      <c r="G8" s="26" t="inlineStr">
+        <is>
+          <t>21 Oct 2026, section 5. Under the button, pointer up, right-aligned to it. One callout at a time; each shows once.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="26" t="inlineStr">
+        <is>
+          <t>studio.route</t>
+        </is>
+      </c>
+      <c r="B9" s="26" t="inlineStr">
+        <is>
+          <t>Studio: the same callout when one route opens</t>
+        </is>
+      </c>
+      <c r="C9" s="26" t="inlineStr">
+        <is>
+          <t>NEW · ROUTES</t>
+        </is>
+      </c>
+      <c r="D9" s="26" t="inlineStr">
+        <is>
+          <t>A new route opens this week</t>
+        </is>
+      </c>
+      <c r="E9" s="26" t="inlineStr">
+        <is>
+          <t>{routes}. Add it here, then give it flights on the timetable.</t>
+        </is>
+      </c>
+      <c r="F9" s="26" t="inlineStr">
+        <is>
+          <t>Got it</t>
+        </is>
+      </c>
+      <c r="G9" s="26" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="26" t="inlineStr">
+        <is>
+          <t>studio.weekends</t>
+        </is>
+      </c>
+      <c r="B10" s="26" t="inlineStr">
+        <is>
+          <t>Studio: first-time callout on the Sat–Sun switch, in the empty "Select a flight to change it." box</t>
+        </is>
+      </c>
+      <c r="C10" s="26" t="inlineStr">
+        <is>
+          <t>NEW · WEEKENDS</t>
+        </is>
+      </c>
+      <c r="D10" s="26" t="inlineStr">
+        <is>
+          <t>Plan Saturday and Sunday on their own</t>
+        </is>
+      </c>
+      <c r="E10" s="26" t="inlineStr">
+        <is>
+          <t>Different numbers of people want to fly at the weekend. Switch to **Sat–Sun** to see them, and give those days their own flights.</t>
+        </is>
+      </c>
+      <c r="F10" s="26" t="inlineStr">
+        <is>
+          <t>Got it</t>
+        </is>
+      </c>
+      <c r="G10" s="26" t="inlineStr">
+        <is>
+          <t>After the routes callout. The leader line runs left from the switch and down the gap left of the chart. Shows once, even if the opener's was dismissed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t>changes.difference</t>
+        </is>
+      </c>
+      <c r="B11" s="26" t="inlineStr">
+        <is>
+          <t>"Is the change worth it?": first-time callout to the right of the Difference column (D1 to the row above the sum ringed)</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="inlineStr">
+        <is>
+          <t>NEW · YOUR CHANGE</t>
+        </is>
+      </c>
+      <c r="D11" s="26" t="inlineStr">
+        <is>
+          <t>What the Difference column means</t>
+        </is>
+      </c>
+      <c r="E11" s="26" t="inlineStr">
+        <is>
+          <t>**Difference = [A] With your change − [B] Now** | {signs} | First, work out **{cell}**: the difference in {row}.</t>
+        </is>
+      </c>
+      <c r="F11" s="26" t="inlineStr">
+        <is>
+          <t>Got it</t>
+        </is>
+      </c>
+      <c r="G11" s="26" t="inlineStr">
+        <is>
+          <t>21 Oct 2026, section 6. {signs}: one sentence for each sign the change shows, from the plan change on screen ("+10 means 10 more passengers a day. −10 means 10 fewer empty seats. −£10 means the fare is £10 lower."); {cell}: D5 (a fare change) or D7 (a timetable change); {row}: ticket revenue a day, or profit a day. [A] and [B] are the tags.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="26" t="inlineStr">
+        <is>
+          <t>changes.line</t>
+        </is>
+      </c>
+      <c r="B12" s="26" t="inlineStr">
+        <is>
+          <t>"Is the change worth it?": the line under the grid while the callout is open</t>
+        </is>
+      </c>
+      <c r="C12" s="26" t="inlineStr"/>
+      <c r="D12" s="26" t="inlineStr"/>
+      <c r="E12" s="26" t="inlineStr">
+        <is>
+          <t>Read the note beside the sheet, then press **Got it**.</t>
+        </is>
+      </c>
+      <c r="F12" s="26" t="inlineStr"/>
+      <c r="G12" s="26" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="26" t="inlineStr">
+        <is>
+          <t>review.sumSkill</t>
+        </is>
+      </c>
+      <c r="B13" s="26" t="inlineStr">
+        <is>
+          <t>Sunday review from week 3: first-time callout for Σ SUM, right of the sheet, pointer left at the Profit column</t>
+        </is>
+      </c>
+      <c r="C13" s="26" t="inlineStr">
+        <is>
+          <t>NEW SKILL · SUM</t>
+        </is>
+      </c>
+      <c r="D13" s="26" t="inlineStr">
+        <is>
+          <t>Add a whole column at once</t>
+        </is>
+      </c>
+      <c r="E13" s="26" t="inlineStr">
+        <is>
+          <t>Press **Σ SUM**, then drag down the **Profit** column, from Monday's profit to Sunday's. | The sheet adds every cell you drag over: **=SUM({range})**.</t>
+        </is>
+      </c>
+      <c r="F13" s="26" t="inlineStr">
+        <is>
+          <t>Got it</t>
+        </is>
+      </c>
+      <c r="G13" s="26" t="inlineStr">
+        <is>
+          <t>21 Oct 2026, section 8. {range}: B2:B8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="26" t="inlineStr">
+        <is>
+          <t>review.sum.wait</t>
+        </is>
+      </c>
+      <c r="B14" s="26" t="inlineStr">
+        <is>
+          <t>Sunday review (Σ SUM): the line under the grid, waiting</t>
+        </is>
+      </c>
+      <c r="C14" s="26" t="inlineStr"/>
+      <c r="D14" s="26" t="inlineStr"/>
+      <c r="E14" s="26" t="inlineStr">
+        <is>
+          <t>Press **Σ SUM**, then drag down the Profit column from {first} to {last}. The sheet adds them up.</t>
+        </is>
+      </c>
+      <c r="F14" s="26" t="inlineStr"/>
+      <c r="G14" s="26" t="inlineStr">
+        <is>
+          <t>{first}, {last}: Mon, Sun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="26" t="inlineStr">
+        <is>
+          <t>review.sum.drag</t>
+        </is>
+      </c>
+      <c r="B15" s="26" t="inlineStr">
+        <is>
+          <t>Sunday review (Σ SUM): the line while dragging</t>
+        </is>
+      </c>
+      <c r="C15" s="26" t="inlineStr"/>
+      <c r="D15" s="26" t="inlineStr"/>
+      <c r="E15" s="26" t="inlineStr">
+        <is>
+          <t>Let go on {lastDay}'s profit ({cell}), then press Enter.</t>
+        </is>
+      </c>
+      <c r="F15" s="26" t="inlineStr"/>
+      <c r="G15" s="26" t="inlineStr">
+        <is>
+          <t>{lastDay}: Sunday; {cell}: B8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="26" t="inlineStr">
+        <is>
+          <t>review.total.done</t>
+        </is>
+      </c>
+      <c r="B16" s="26" t="inlineStr">
+        <is>
+          <t>Sunday review: the line when the sheet has added the week</t>
+        </is>
+      </c>
+      <c r="C16" s="26" t="inlineStr"/>
+      <c r="D16" s="26" t="inlineStr"/>
+      <c r="E16" s="26" t="inlineStr">
+        <is>
+          <t>✓ The sheet added the {days} days: **{total}**. Next: the difference from the plan, in your book.</t>
+        </is>
+      </c>
+      <c r="F16" s="26" t="inlineStr"/>
+      <c r="G16" s="26" t="inlineStr">
+        <is>
+          <t>{days}: seven, in words.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="26" t="inlineStr">
+        <is>
+          <t>review.total.card</t>
+        </is>
+      </c>
+      <c r="B17" s="26" t="inlineStr">
+        <is>
+          <t>Sunday review: the card beside the sheet, Profit this week (weeks 1–2)</t>
+        </is>
+      </c>
+      <c r="C17" s="26" t="inlineStr">
+        <is>
+          <t>FORMULA</t>
+        </is>
+      </c>
+      <c r="D17" s="26" t="inlineStr">
+        <is>
+          <t>Profit this week = add the {days} days</t>
+        </is>
+      </c>
+      <c r="E17" s="26" t="inlineStr">
+        <is>
+          <t>Click each day into the formula. The sheet adds them up.</t>
+        </is>
+      </c>
+      <c r="F17" s="26" t="inlineStr"/>
+      <c r="G17" s="26" t="inlineStr">
+        <is>
+          <t>The cyan FORMULA tag: no Sum number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="26" t="inlineStr">
+        <is>
+          <t>review.total.cardSum</t>
+        </is>
+      </c>
+      <c r="B18" s="26" t="inlineStr">
+        <is>
+          <t>Sunday review: the same card from week 3 (Σ SUM), once the sheet has added them</t>
+        </is>
+      </c>
+      <c r="C18" s="26" t="inlineStr">
+        <is>
+          <t>FORMULA</t>
+        </is>
+      </c>
+      <c r="D18" s="26" t="inlineStr">
+        <is>
+          <t>Profit this week = add the {days} days</t>
+        </is>
+      </c>
+      <c r="E18" s="26" t="inlineStr">
+        <is>
+          <t>=SUM({range}) added {first} to {last}.</t>
+        </is>
+      </c>
+      <c r="F18" s="26" t="inlineStr"/>
+      <c r="G18" s="26" t="inlineStr">
+        <is>
+          <t>While he presses Σ SUM and drags, the card shows the title only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="26" t="inlineStr">
+        <is>
+          <t>review.average.card</t>
+        </is>
+      </c>
+      <c r="B19" s="26" t="inlineStr">
+        <is>
+          <t>Sunday review: the card for Average a day</t>
+        </is>
+      </c>
+      <c r="C19" s="26" t="inlineStr">
+        <is>
+          <t>FORMULA</t>
+        </is>
+      </c>
+      <c r="D19" s="26" t="inlineStr">
+        <is>
+          <t>Average a day = profit this week ÷ days flown</t>
+        </is>
+      </c>
+      <c r="E19" s="26" t="inlineStr">
+        <is>
+          <t>Click the two cells. The sheet works it out.</t>
+        </is>
+      </c>
+      <c r="F19" s="26" t="inlineStr"/>
+      <c r="G19" s="26" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="26" t="inlineStr">
+        <is>
+          <t>review.average.done</t>
+        </is>
+      </c>
+      <c r="B20" s="26" t="inlineStr">
+        <is>
+          <t>Sunday review: the line when the sheet has worked out the average</t>
+        </is>
+      </c>
+      <c r="C20" s="26" t="inlineStr"/>
+      <c r="D20" s="26" t="inlineStr"/>
+      <c r="E20" s="26" t="inlineStr">
+        <is>
+          <t>✓ The sheet worked out the average: **{mean}** a day.</t>
+        </is>
+      </c>
+      <c r="F20" s="26" t="inlineStr"/>
+      <c r="G20" s="26" t="inlineStr">
+        <is>
+          <t>Rounded to the nearest pound.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="26" t="inlineStr">
+        <is>
+          <t>review.footer</t>
+        </is>
+      </c>
+      <c r="B21" s="26" t="inlineStr">
+        <is>
+          <t>Sunday review: the footer while the sums are open</t>
+        </is>
+      </c>
+      <c r="C21" s="26" t="inlineStr"/>
+      <c r="D21" s="26" t="inlineStr"/>
+      <c r="E21" s="26" t="inlineStr">
+        <is>
+          <t>Build each formula by clicking the cells. The sheet adds up; work out the difference from the plan in your book.</t>
+        </is>
+      </c>
+      <c r="F21" s="26" t="inlineStr"/>
+      <c r="G21" s="26" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="26" t="inlineStr">
+        <is>
+          <t>review.unflown</t>
+        </is>
+      </c>
+      <c r="B22" s="26" t="inlineStr">
+        <is>
+          <t>Sunday review, What happened: routes not flown yet (only once a plan screen has shown them)</t>
+        </is>
+      </c>
+      <c r="C22" s="26" t="inlineStr"/>
+      <c r="D22" s="26" t="inlineStr">
+        <is>
+          <t>You could fly these new routes.</t>
+        </is>
+      </c>
+      <c r="E22" s="26" t="inlineStr">
+        <is>
+          <t>Red Kite flies them for now, so fewer people are left wanting to fly with you each day: {list}</t>
+        </is>
+      </c>
+      <c r="F22" s="26" t="inlineStr"/>
+      <c r="G22" s="26" t="inlineStr">
+        <is>
+          <t>21 Oct 2026, section 9. A panel with a cyan left rail (a chance, not a loss). {list}: "Amsterdam 73 → 68 · Frankfurt 50 → 45 · …", figures from the game.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="26" t="inlineStr">
+        <is>
+          <t>flightTimes.line</t>
+        </is>
+      </c>
+      <c r="B23" s="26" t="inlineStr">
+        <is>
+          <t>Flight times sheet: the line under the grid (typing)</t>
+        </is>
+      </c>
+      <c r="C23" s="26" t="inlineStr"/>
+      <c r="D23" s="26" t="inlineStr"/>
+      <c r="E23" s="26" t="inlineStr">
+        <is>
+          <t>Work it out in your book. Write **Sum {n}** beside it, then type the time in **{cell}**.</t>
+        </is>
+      </c>
+      <c r="F23" s="26" t="inlineStr">
+        <is>
+          <t>Give me a hint</t>
+        </is>
+      </c>
+      <c r="G23" s="26" t="inlineStr">
+        <is>
+          <t>21 Oct 2026, section 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="26" t="inlineStr">
+        <is>
+          <t>flightTimes.build</t>
+        </is>
+      </c>
+      <c r="B24" s="26" t="inlineStr">
+        <is>
+          <t>Flight times sheet: the line while building the first sum</t>
+        </is>
+      </c>
+      <c r="C24" s="26" t="inlineStr"/>
+      <c r="D24" s="26" t="inlineStr"/>
+      <c r="E24" s="26" t="inlineStr">
+        <is>
+          <t>Click the cells to build the formula. Then work it out in your book and type the time in **{cell}**.</t>
+        </is>
+      </c>
+      <c r="F24" s="26" t="inlineStr"/>
+      <c r="G24" s="26" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="26" t="inlineStr">
+        <is>
+          <t>flightTimes.formula</t>
+        </is>
+      </c>
+      <c r="B25" s="26" t="inlineStr">
+        <is>
+          <t>Flight times sheet: the line for a formula-only flight time (the third, when the decay makes it a Build)</t>
+        </is>
+      </c>
+      <c r="C25" s="26" t="inlineStr"/>
+      <c r="D25" s="26" t="inlineStr"/>
+      <c r="E25" s="26" t="inlineStr">
+        <is>
+          <t>Click the cells to build the formula. The sheet works out the time in **{cell}**.</t>
+        </is>
+      </c>
+      <c r="F25" s="26" t="inlineStr"/>
+      <c r="G25" s="26" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="26" t="inlineStr">
+        <is>
+          <t>flightTimes.f</t>
+        </is>
+      </c>
+      <c r="B26" s="26" t="inlineStr">
+        <is>
+          <t>Flight times sheet: under the grid, when the game has worked out rows</t>
+        </is>
+      </c>
+      <c r="C26" s="26" t="inlineStr"/>
+      <c r="D26" s="26" t="inlineStr"/>
+      <c r="E26" s="26" t="inlineStr">
+        <is>
+          <t>ƒ worked out for you</t>
+        </is>
+      </c>
+      <c r="F26" s="26" t="inlineStr"/>
+      <c r="G26" s="26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="26" t="inlineStr">
+        <is>
+          <t>flightTimes.footer</t>
+        </is>
+      </c>
+      <c r="B27" s="26" t="inlineStr">
+        <is>
+          <t>Flight times: the footer</t>
+        </is>
+      </c>
+      <c r="C27" s="26" t="inlineStr"/>
+      <c r="D27" s="26" t="inlineStr"/>
+      <c r="E27" s="26" t="inlineStr">
+        <is>
+          <t>Work out the flight times on the sheet, then go on to the timetable.</t>
+        </is>
+      </c>
+      <c r="F27" s="26" t="inlineStr"/>
+      <c r="G27" s="26" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="26" t="inlineStr">
+        <is>
+          <t>flightTimes.card</t>
+        </is>
+      </c>
+      <c r="B28" s="26" t="inlineStr">
+        <is>
+          <t>Flight times: the SUM card under the sheet, one row</t>
+        </is>
+      </c>
+      <c r="C28" s="26" t="inlineStr"/>
+      <c r="D28" s="26" t="inlineStr">
+        <is>
+          <t>Flight time = distance ÷ speed</t>
+        </is>
+      </c>
+      <c r="E28" s="26" t="inlineStr">
+        <is>
+          <t>{plane} to {route}</t>
+        </is>
+      </c>
+      <c r="F28" s="26" t="inlineStr"/>
+      <c r="G28" s="26" t="inlineStr">
+        <is>
+          <t>Gold SUM n tag · the rule · on the right in text-soft, the sum being worked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Screen text the game reads by id (21 Oct 2026). {name} is filled by the game; **…** is bold; [A] and [B] are the A / B tags; | starts a new line. A row missing here falls back to the game's own copy of the same words.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4690,6 +5802,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
         <is>
@@ -10380,6 +11493,7 @@
         </is>
       </c>
     </row>
+    <row r="103"/>
     <row r="104">
       <c r="A104" s="17" t="inlineStr">
         <is>
@@ -10523,7 +11637,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11178,6 +12292,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="17" t="inlineStr">
         <is>
@@ -11197,7 +12312,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13964,7 +15079,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14587,272 +15702,11 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="17" t="inlineStr">
         <is>
           <t>D93: teacher-only; nothing on the pupil's screen; no money or stars change. The teacher panel's Milestones table per chapter (reached, count, evidence, Awarded tick) and the record printout show them. Chapter 4 is added to each range once chapter 4's milestones are reviewed.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="20" t="inlineStr">
-        <is>
-          <t>field</t>
-        </is>
-      </c>
-      <c r="B1" s="20" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="C1" s="20" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="D1" s="20" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="13" t="inlineStr">
-        <is>
-          <t>project</t>
-        </is>
-      </c>
-      <c r="B2" s="13" t="inlineStr">
-        <is>
-          <t>The A380 launch</t>
-        </is>
-      </c>
-      <c r="C2" s="13" t="inlineStr">
-        <is>
-          <t>One standalone creative project (D82). The game pauses while the pupil works on it over several sessions; the result applies from the launch date he chooses.</t>
-        </is>
-      </c>
-      <c r="D2" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="13" t="inlineStr">
-        <is>
-          <t>brief</t>
-        </is>
-      </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>Fill the A380's first month on Hong Kong (or Los Angeles). Tell people what flying on it is like, and give them a reason to book now.</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>Shown as a letter from the board.</t>
-        </is>
-      </c>
-      <c r="D3" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>choices</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>route (hkg | lax); audience (business | families | holidaymakers); channel (stations | online | sponsorship); budget (share of a month's profit: 0.05 | 0.1 | 0.2); launch date; length (2 | 4 | 8 weeks)</t>
-        </is>
-      </c>
-      <c r="C4" s="13" t="inlineStr">
-        <is>
-          <t>The structured part the engine reads.</t>
-        </is>
-      </c>
-      <c r="D4" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>portfolio</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>livery and cabin concept; a poster or a 30–90 second advert (script and storyboard); an offer; optionally a snack or activity idea</t>
-        </is>
-      </c>
-      <c r="C5" s="13" t="inlineStr">
-        <is>
-          <t>Hand-drawn work counts; photographed or scanned in.</t>
-        </is>
-      </c>
-      <c r="D5" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>aiSignals</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>audience_fit, message_clarity, offer_visibility, brand_consistency, distinctiveness, trust, experience_fit — each 0–4; plus strongest_feature and missed_opportunity</t>
-        </is>
-      </c>
-      <c r="C6" s="13" t="inlineStr">
-        <is>
-          <t>The AI (or the teacher from a rubric) returns these. The pupil sees three in plain words: speaks to the people you chose? offer clear? honest?</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>focusGroup</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>20 people from the chosen audience: count who would book, with short comments</t>
-        </is>
-      </c>
-      <c r="C7" s="13" t="inlineStr">
-        <is>
-          <t>Count = round(20 × average of audience_fit, message_clarity, offer_visibility, trust ÷ 4). The pupil's appeal figure, as a fraction and a percentage.</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="14" t="inlineStr">
-        <is>
-          <t>reach</t>
-        </is>
-      </c>
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t>stations: business 0.6, families 0.2, holidaymakers 0.3 · online: 0.3, 0.4, 0.6 · sponsorship: 0.2, 0.6, 0.4 — share of the route's pool reached per 0.1 of a month's profit spent, capped at 0.9</t>
-        </is>
-      </c>
-      <c r="C8" s="14" t="inlineStr">
-        <is>
-          <t>Placeholder values; deterministic.</t>
-        </is>
-      </c>
-      <c r="D8" s="14" t="inlineStr">
-        <is>
-          <t>placeholder</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="14" t="inlineStr">
-        <is>
-          <t>funnel</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>reached → remember (0.8) → understand the offer (offer_visibility ÷ 4) → consider us (brand_consistency ÷ 4 × stars factor) → can use the fare and times (engine) → get a seat (capacity)</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="inlineStr">
-        <is>
-          <t>Shown as six bars; the last two are the engine's usual demand and capacity. Decays 20% a week after the campaign ends.</t>
-        </is>
-      </c>
-      <c r="D9" s="14" t="inlineStr">
-        <is>
-          <t>placeholder</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>honesty</t>
-        </is>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>a claim the AI flags as untrue (cheapest, fastest, biggest) → trust 0 and −½★</t>
-        </is>
-      </c>
-      <c r="C10" s="13" t="inlineStr">
-        <is>
-          <t>Shown by the focus group calling it out.</t>
-        </is>
-      </c>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t>teacherOverride</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>always</t>
-        </is>
-      </c>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>The teacher sees the AI's signals first and can change them or score from the rubric with no AI.</t>
-        </is>
-      </c>
-      <c r="D11" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
         </is>
       </c>
     </row>
@@ -15296,6 +16150,268 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="20" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="B1" s="20" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="C1" s="20" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="D1" s="20" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>project</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>The A380 launch</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="inlineStr">
+        <is>
+          <t>One standalone creative project (D82). The game pauses while the pupil works on it over several sessions; the result applies from the launch date he chooses.</t>
+        </is>
+      </c>
+      <c r="D2" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>brief</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>Fill the A380's first month on Hong Kong (or Los Angeles). Tell people what flying on it is like, and give them a reason to book now.</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>Shown as a letter from the board.</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>choices</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>route (hkg | lax); audience (business | families | holidaymakers); channel (stations | online | sponsorship); budget (share of a month's profit: 0.05 | 0.1 | 0.2); launch date; length (2 | 4 | 8 weeks)</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>The structured part the engine reads.</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>portfolio</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>livery and cabin concept; a poster or a 30–90 second advert (script and storyboard); an offer; optionally a snack or activity idea</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Hand-drawn work counts; photographed or scanned in.</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>aiSignals</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>audience_fit, message_clarity, offer_visibility, brand_consistency, distinctiveness, trust, experience_fit — each 0–4; plus strongest_feature and missed_opportunity</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>The AI (or the teacher from a rubric) returns these. The pupil sees three in plain words: speaks to the people you chose? offer clear? honest?</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>focusGroup</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>20 people from the chosen audience: count who would book, with short comments</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>Count = round(20 × average of audience_fit, message_clarity, offer_visibility, trust ÷ 4). The pupil's appeal figure, as a fraction and a percentage.</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>reach</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>stations: business 0.6, families 0.2, holidaymakers 0.3 · online: 0.3, 0.4, 0.6 · sponsorship: 0.2, 0.6, 0.4 — share of the route's pool reached per 0.1 of a month's profit spent, capped at 0.9</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>Placeholder values; deterministic.</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>funnel</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>reached → remember (0.8) → understand the offer (offer_visibility ÷ 4) → consider us (brand_consistency ÷ 4 × stars factor) → can use the fare and times (engine) → get a seat (capacity)</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>Shown as six bars; the last two are the engine's usual demand and capacity. Decays 20% a week after the campaign ends.</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>honesty</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>a claim the AI flags as untrue (cheapest, fastest, biggest) → trust 0 and −½★</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Shown by the focus group calling it out.</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>teacherOverride</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>The teacher sees the AI's signals first and can change them or score from the rubric with no AI.</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17875,7 +18991,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -19141,7 +20257,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -19944,6 +21060,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
         <is>
@@ -20172,6 +21289,7 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="17" t="inlineStr">
         <is>
@@ -20184,7 +21302,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -21007,6 +22125,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="17" t="inlineStr">
         <is>
@@ -21066,7 +22185,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -21374,7 +22493,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -22707,7 +23826,11 @@
       <c r="H22" s="13" t="inlineStr"/>
       <c r="I22" s="13" t="inlineStr"/>
       <c r="J22" s="13" t="inlineStr"/>
-      <c r="K22" s="13" t="inlineStr"/>
+      <c r="K22" s="13" t="inlineStr">
+        <is>
+          <t>skills: sumDrag (Σ SUM, drag down a column to add it up: 21 Oct 2026)</t>
+        </is>
+      </c>
       <c r="L22" s="13" t="inlineStr">
         <is>
           <t>weekend multipliers (Settings)</t>
@@ -24325,7 +25448,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -48727,7 +49850,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -51649,7 +52772,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -52102,424 +53225,6 @@
       <c r="J9" t="inlineStr">
         <is>
           <t>0.5</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>from day</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>mechanic</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="13" t="inlineStr">
-        <is>
-          <t>Launch Day: standing plan on one page; all opening sums in one sitting (tickets ×3, profit, snacks ×2, fuel); both routes; modelling tool; workings page</t>
-        </is>
-      </c>
-      <c r="C2" s="13" t="inlineStr">
-        <is>
-          <t>D52, D54</t>
-        </is>
-      </c>
-      <c r="D2" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>The week runs day by day on the operations board; results equal the projection; pauses for events (day 4 Red Kite with numbers, day 5 storm)</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>D52, D50</t>
-        </is>
-      </c>
-      <c r="D3" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="13" t="n">
-        <v>7</v>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>Weekly review every Sunday: seven-row table, total by hand, projected − actual, missed-profit line</t>
-        </is>
-      </c>
-      <c r="C4" s="13" t="inlineStr">
-        <is>
-          <t>D55</t>
-        </is>
-      </c>
-      <c r="D4" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Week 2: second plane, buy only; buy now or wait (time to afford); Buy greyed until affordable; two timetables; assignment</t>
-        </is>
-      </c>
-      <c r="C5" s="13" t="inlineStr">
-        <is>
-          <t>D53, D55</t>
-        </is>
-      </c>
-      <c r="D5" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="13" t="n">
-        <v>15</v>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Week 3: four routes; £5 fares; season badge; use-it-or-lose-it begins</t>
-        </is>
-      </c>
-      <c r="C6" s="13" t="inlineStr">
-        <is>
-          <t>D28, D55</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="13" t="n">
-        <v>19</v>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>Season forecast card</t>
-        </is>
-      </c>
-      <c r="C7" s="13" t="inlineStr"/>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="13" t="n">
-        <v>22</v>
-      </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>Week 4: medium haul; range check; services per day; E175 and E190; load factor as a percentage</t>
-        </is>
-      </c>
-      <c r="C8" s="13" t="inlineStr">
-        <is>
-          <t>D19, D23</t>
-        </is>
-      </c>
-      <c r="D8" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="13" t="n">
-        <v>29</v>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>Week-at-a-time skips; Marrakech; event costs as a share of a day Clashing news weeks from November (D90).</t>
-        </is>
-      </c>
-      <c r="C9" s="13" t="inlineStr">
-        <is>
-          <t>D21</t>
-        </is>
-      </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>2030-12-02</t>
-        </is>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>Month-at-a-time play; monthly reports from here on</t>
-        </is>
-      </c>
-      <c r="C10" s="13" t="inlineStr"/>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t>2030-12-29</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>Chapter 1 review: chapter accounts by hand; the long-haul decision</t>
-        </is>
-      </c>
-      <c r="C11" s="13" t="inlineStr"/>
-      <c r="D11" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>2031-01-06</t>
-        </is>
-      </c>
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>CHAPTER 2 set-up (days 127–131, one at a time): long haul same-day to 6,000 km (New York, Dubai); the 757 and 787 to lease; arrival in local time; reputation revealed at the banked level and ×5% a half-star; the airline type chosen (light profiles); Value's bag fee; £500 second crew per long-haul service; Captain's challenge 1. Then weeks, then months from February. The Charter desk opens (D90).</t>
-        </is>
-      </c>
-      <c r="C12" s="13" t="inlineStr"/>
-      <c r="D12" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>2031-08-31</t>
-        </is>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>Chapter 2 review: year-1 accounts (show what to add, the mean), hunt h1, next investment (buying opens in chapter 3)</t>
-        </is>
-      </c>
-      <c r="C13" s="13" t="inlineStr"/>
-      <c r="D13" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t>2031-09-01</t>
-        </is>
-      </c>
-      <c r="B14" s="13" t="inlineStr">
-        <is>
-          <t>CHAPTER 3 set-up (days 365–369, one at a time): buy big planes outright — (price − cash) ÷ profit a week; the overdraft safety net; Tokyo and Cape Town; the A340, 777 and A350 in the shop; Challenge 3. Then months. 'Known for' tags begin (D90).</t>
-        </is>
-      </c>
-      <c r="C14" s="13" t="inlineStr"/>
-      <c r="D14" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="13" t="inlineStr">
-        <is>
-          <t>2032-08-31</t>
-        </is>
-      </c>
-      <c r="B15" s="13" t="inlineStr">
-        <is>
-          <t>Chapter 3 review: year-2 accounts, hunt h3, next investment (the A380 offer opens chapter 4)</t>
-        </is>
-      </c>
-      <c r="C15" s="13" t="inlineStr"/>
-      <c r="D15" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t>2032-09-06</t>
-        </is>
-      </c>
-      <c r="B16" s="13" t="inlineStr">
-        <is>
-          <t>CHAPTER 4 set-up (days 736–740, one at a time): the A380 offer on finance (monthly), the 747 as the alternative, Hong Kong and Los Angeles, does-it-fill (demand ÷ seats), Challenge 5; the launch campaign project in October; then months.</t>
-        </is>
-      </c>
-      <c r="C16" s="13" t="inlineStr"/>
-      <c r="D16" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="13" t="inlineStr">
-        <is>
-          <t>2033-08-31</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="inlineStr">
-        <is>
-          <t>Chapter 4 review: year-3 accounts, hunt h5 (the finance line), the A380's fill month by month, next: the rival</t>
-        </is>
-      </c>
-      <c r="C17" s="13" t="inlineStr"/>
-      <c r="D17" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="18" t="inlineStr">
-        <is>
-          <t>2033-09-05</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>CHAPTER 5: rival enters the best route; marketing; quarterly comparison task</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr"/>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="18" t="inlineStr">
-        <is>
-          <t>2034-08-31</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>Chapter 5 review</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr"/>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="18" t="inlineStr">
-        <is>
-          <t>2034-09-04</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>CHAPTER 6: no new mechanic; the five-year review</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr"/>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>later</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="13" t="inlineStr">
-        <is>
-          <t>rule</t>
-        </is>
-      </c>
-      <c r="B21" s="13" t="inlineStr">
-        <is>
-          <t>No crew mechanic before 2031-01-06; no second hub, sell-back, fleet renewal, investor; Heathrow only; cash reserve block before Sep 2031; HandSumRules govern hand sums</t>
-        </is>
-      </c>
-      <c r="C21" s="13" t="inlineStr">
-        <is>
-          <t>D51 D31 D25 D46 D44 D32 D26 D34</t>
-        </is>
-      </c>
-      <c r="D21" s="13" t="inlineStr">
-        <is>
-          <t>live</t>
         </is>
       </c>
     </row>
@@ -52907,6 +53612,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="17" t="inlineStr">
         <is>
@@ -52946,6 +53652,424 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>from day</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>mechanic</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>Launch Day: standing plan on one page; all opening sums in one sitting (tickets ×3, profit, snacks ×2, fuel); both routes; modelling tool; workings page</t>
+        </is>
+      </c>
+      <c r="C2" s="13" t="inlineStr">
+        <is>
+          <t>D52, D54</t>
+        </is>
+      </c>
+      <c r="D2" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>The week runs day by day on the operations board; results equal the projection; pauses for events (day 4 Red Kite with numbers, day 5 storm)</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>D52, D50</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Weekly review every Sunday: seven-row table, total by hand, projected − actual, missed-profit line</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>D55</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Week 2: second plane, buy only; buy now or wait (time to afford); Buy greyed until affordable; two timetables; assignment</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>D53, D55</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Week 3: four routes; £5 fares; season badge; use-it-or-lose-it begins</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>D28, D55</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Season forecast card</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr"/>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>Week 4: medium haul; range check; services per day; E175 and E190; load factor as a percentage</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>D19, D23</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="n">
+        <v>29</v>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>Week-at-a-time skips; Marrakech; event costs as a share of a day Clashing news weeks from November (D90).</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>D21</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>2030-12-02</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>Month-at-a-time play; monthly reports from here on</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr"/>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>2030-12-29</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Chapter 1 review: chapter accounts by hand; the long-haul decision</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr"/>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>2031-01-06</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>CHAPTER 2 set-up (days 127–131, one at a time): long haul same-day to 6,000 km (New York, Dubai); the 757 and 787 to lease; arrival in local time; reputation revealed at the banked level and ×5% a half-star; the airline type chosen (light profiles); Value's bag fee; £500 second crew per long-haul service; Captain's challenge 1. Then weeks, then months from February. The Charter desk opens (D90).</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr"/>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>2031-08-31</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>Chapter 2 review: year-1 accounts (show what to add, the mean), hunt h1, next investment (buying opens in chapter 3)</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr"/>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>2031-09-01</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>CHAPTER 3 set-up (days 365–369, one at a time): buy big planes outright — (price − cash) ÷ profit a week; the overdraft safety net; Tokyo and Cape Town; the A340, 777 and A350 in the shop; Challenge 3. Then months. 'Known for' tags begin (D90).</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr"/>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>2032-08-31</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>Chapter 3 review: year-2 accounts, hunt h3, next investment (the A380 offer opens chapter 4)</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr"/>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>2032-09-06</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>CHAPTER 4 set-up (days 736–740, one at a time): the A380 offer on finance (monthly), the 747 as the alternative, Hong Kong and Los Angeles, does-it-fill (demand ÷ seats), Challenge 5; the launch campaign project in October; then months.</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr"/>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>2033-08-31</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>Chapter 4 review: year-3 accounts, hunt h5 (the finance line), the A380's fill month by month, next: the rival</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr"/>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="18" t="inlineStr">
+        <is>
+          <t>2033-09-05</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>CHAPTER 5: rival enters the best route; marketing; quarterly comparison task</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="inlineStr"/>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>later</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="18" t="inlineStr">
+        <is>
+          <t>2034-08-31</t>
+        </is>
+      </c>
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t>Chapter 5 review</t>
+        </is>
+      </c>
+      <c r="C19" s="18" t="inlineStr"/>
+      <c r="D19" s="18" t="inlineStr">
+        <is>
+          <t>later</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="18" t="inlineStr">
+        <is>
+          <t>2034-09-04</t>
+        </is>
+      </c>
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>CHAPTER 6: no new mechanic; the five-year review</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="inlineStr"/>
+      <c r="D20" s="18" t="inlineStr">
+        <is>
+          <t>later</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>No crew mechanic before 2031-01-06; no second hub, sell-back, fleet renewal, investor; Heathrow only; cash reserve block before Sep 2031; HandSumRules govern hand sums</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>D51 D31 D25 D46 D44 D32 D26 D34</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -53162,6 +54286,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="17" t="inlineStr">
         <is>
@@ -53174,7 +54299,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -53515,6 +54640,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="17" t="inlineStr">
         <is>
@@ -53527,7 +54653,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -54484,6 +55610,7 @@
         </is>
       </c>
     </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
@@ -54979,6 +56106,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
@@ -59876,7 +61004,7 @@
       </c>
       <c r="C197" s="13" t="inlineStr">
         <is>
-          <t>D100: from chapter 2 the spreadsheet names SUM, AVERAGE, MAX and MIN; the review's Build steps can be written with them.</t>
+          <t>D100: from chapter 2 the spreadsheet names SUM, AVERAGE, MAX and MIN; the review's Build steps can be written with them. 21 Oct 2026 (Bertie): SUM comes earlier, as the Σ SUM key on the Sunday review from week 3 (Calendar day 21, skills: sumDrag); AVERAGE, MAX and MIN stay from chapter 2.</t>
         </is>
       </c>
       <c r="D197" s="13" t="inlineStr">
@@ -61081,6 +62209,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
         <is>
@@ -62110,6 +63239,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="17" t="inlineStr">
         <is>
@@ -62491,6 +63621,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="17" t="inlineStr">
         <is>
@@ -62891,6 +64022,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="17" t="inlineStr">
         <is>

--- a/data/Airline-World-Workbook.xlsx
+++ b/data/Airline-World-Workbook.xlsx
@@ -1266,7 +1266,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
         <is>
@@ -1612,7 +1611,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="17" t="inlineStr">
         <is>
@@ -2254,7 +2252,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="17" t="inlineStr">
         <is>
@@ -3998,7 +3995,6 @@
         </is>
       </c>
     </row>
-    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
@@ -4017,7 +4013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4498,95 +4494,87 @@
     <row r="15">
       <c r="A15" s="26" t="inlineStr">
         <is>
-          <t>review.sum.drag</t>
+          <t>review.sum.go</t>
         </is>
       </c>
       <c r="B15" s="26" t="inlineStr">
         <is>
-          <t>Sunday review (Σ SUM): the line while dragging</t>
+          <t>Sunday review (Σ SUM): the line once Σ SUM is pressed, before the drag</t>
         </is>
       </c>
       <c r="C15" s="26" t="inlineStr"/>
       <c r="D15" s="26" t="inlineStr"/>
       <c r="E15" s="26" t="inlineStr">
         <is>
-          <t>Let go on {lastDay}'s profit ({cell}), then press Enter.</t>
+          <t>Now drag down the Profit column, from {first} to {last}.</t>
         </is>
       </c>
       <c r="F15" s="26" t="inlineStr"/>
       <c r="G15" s="26" t="inlineStr">
         <is>
-          <t>{lastDay}: Sunday; {cell}: B8.</t>
+          <t>Added by Claude Code (21 Oct 2026): the step between pressing Σ SUM and dragging.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t>review.total.done</t>
+          <t>review.sum.drag</t>
         </is>
       </c>
       <c r="B16" s="26" t="inlineStr">
         <is>
-          <t>Sunday review: the line when the sheet has added the week</t>
+          <t>Sunday review (Σ SUM): the line while dragging</t>
         </is>
       </c>
       <c r="C16" s="26" t="inlineStr"/>
       <c r="D16" s="26" t="inlineStr"/>
       <c r="E16" s="26" t="inlineStr">
         <is>
-          <t>✓ The sheet added the {days} days: **{total}**. Next: the difference from the plan, in your book.</t>
+          <t>Let go on {lastDay}'s profit ({cell}), then press Enter.</t>
         </is>
       </c>
       <c r="F16" s="26" t="inlineStr"/>
       <c r="G16" s="26" t="inlineStr">
         <is>
-          <t>{days}: seven, in words.</t>
+          <t>{lastDay}: Sunday; {cell}: B8.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t>review.total.card</t>
+          <t>review.total.done</t>
         </is>
       </c>
       <c r="B17" s="26" t="inlineStr">
         <is>
-          <t>Sunday review: the card beside the sheet, Profit this week (weeks 1–2)</t>
-        </is>
-      </c>
-      <c r="C17" s="26" t="inlineStr">
-        <is>
-          <t>FORMULA</t>
-        </is>
-      </c>
-      <c r="D17" s="26" t="inlineStr">
-        <is>
-          <t>Profit this week = add the {days} days</t>
-        </is>
-      </c>
+          <t>Sunday review: the line when the sheet has added the week</t>
+        </is>
+      </c>
+      <c r="C17" s="26" t="inlineStr"/>
+      <c r="D17" s="26" t="inlineStr"/>
       <c r="E17" s="26" t="inlineStr">
         <is>
-          <t>Click each day into the formula. The sheet adds them up.</t>
+          <t>✓ The sheet added the {days} days: **{total}**. Next: the difference from the plan, in your book.</t>
         </is>
       </c>
       <c r="F17" s="26" t="inlineStr"/>
       <c r="G17" s="26" t="inlineStr">
         <is>
-          <t>The cyan FORMULA tag: no Sum number.</t>
+          <t>{days}: seven, in words.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t>review.total.cardSum</t>
+          <t>review.total.card</t>
         </is>
       </c>
       <c r="B18" s="26" t="inlineStr">
         <is>
-          <t>Sunday review: the same card from week 3 (Σ SUM), once the sheet has added them</t>
+          <t>Sunday review: the card beside the sheet, Profit this week (weeks 1–2)</t>
         </is>
       </c>
       <c r="C18" s="26" t="inlineStr">
@@ -4601,25 +4589,25 @@
       </c>
       <c r="E18" s="26" t="inlineStr">
         <is>
-          <t>=SUM({range}) added {first} to {last}.</t>
+          <t>Click each day into the formula. The sheet adds them up.</t>
         </is>
       </c>
       <c r="F18" s="26" t="inlineStr"/>
       <c r="G18" s="26" t="inlineStr">
         <is>
-          <t>While he presses Σ SUM and drags, the card shows the title only.</t>
+          <t>The cyan FORMULA tag: no Sum number.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t>review.average.card</t>
+          <t>review.total.cardSum</t>
         </is>
       </c>
       <c r="B19" s="26" t="inlineStr">
         <is>
-          <t>Sunday review: the card for Average a day</t>
+          <t>Sunday review: the same card from week 3 (Σ SUM), once the sheet has added them</t>
         </is>
       </c>
       <c r="C19" s="26" t="inlineStr">
@@ -4629,158 +4617,170 @@
       </c>
       <c r="D19" s="26" t="inlineStr">
         <is>
-          <t>Average a day = profit this week ÷ days flown</t>
+          <t>Profit this week = add the {days} days</t>
         </is>
       </c>
       <c r="E19" s="26" t="inlineStr">
         <is>
-          <t>Click the two cells. The sheet works it out.</t>
+          <t>=SUM({range}) added {first} to {last}.</t>
         </is>
       </c>
       <c r="F19" s="26" t="inlineStr"/>
-      <c r="G19" s="26" t="inlineStr"/>
+      <c r="G19" s="26" t="inlineStr">
+        <is>
+          <t>While he presses Σ SUM and drags, the card shows the title only.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="26" t="inlineStr">
         <is>
-          <t>review.average.done</t>
+          <t>review.average.card</t>
         </is>
       </c>
       <c r="B20" s="26" t="inlineStr">
         <is>
-          <t>Sunday review: the line when the sheet has worked out the average</t>
-        </is>
-      </c>
-      <c r="C20" s="26" t="inlineStr"/>
-      <c r="D20" s="26" t="inlineStr"/>
+          <t>Sunday review: the card for Average a day</t>
+        </is>
+      </c>
+      <c r="C20" s="26" t="inlineStr">
+        <is>
+          <t>FORMULA</t>
+        </is>
+      </c>
+      <c r="D20" s="26" t="inlineStr">
+        <is>
+          <t>Average a day = profit this week ÷ days flown</t>
+        </is>
+      </c>
       <c r="E20" s="26" t="inlineStr">
         <is>
-          <t>✓ The sheet worked out the average: **{mean}** a day.</t>
+          <t>Click the two cells. The sheet works it out.</t>
         </is>
       </c>
       <c r="F20" s="26" t="inlineStr"/>
-      <c r="G20" s="26" t="inlineStr">
-        <is>
-          <t>Rounded to the nearest pound.</t>
-        </is>
-      </c>
+      <c r="G20" s="26" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="26" t="inlineStr">
         <is>
-          <t>review.footer</t>
+          <t>review.average.done</t>
         </is>
       </c>
       <c r="B21" s="26" t="inlineStr">
         <is>
-          <t>Sunday review: the footer while the sums are open</t>
+          <t>Sunday review: the line when the sheet has worked out the average</t>
         </is>
       </c>
       <c r="C21" s="26" t="inlineStr"/>
       <c r="D21" s="26" t="inlineStr"/>
       <c r="E21" s="26" t="inlineStr">
         <is>
-          <t>Build each formula by clicking the cells. The sheet adds up; work out the difference from the plan in your book.</t>
+          <t>✓ The sheet worked out the average: **{mean}** a day.</t>
         </is>
       </c>
       <c r="F21" s="26" t="inlineStr"/>
-      <c r="G21" s="26" t="inlineStr"/>
+      <c r="G21" s="26" t="inlineStr">
+        <is>
+          <t>Rounded to the nearest pound.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="26" t="inlineStr">
         <is>
-          <t>review.unflown</t>
+          <t>review.footer</t>
         </is>
       </c>
       <c r="B22" s="26" t="inlineStr">
         <is>
-          <t>Sunday review, What happened: routes not flown yet (only once a plan screen has shown them)</t>
+          <t>Sunday review: the footer while the sums are open</t>
         </is>
       </c>
       <c r="C22" s="26" t="inlineStr"/>
-      <c r="D22" s="26" t="inlineStr">
-        <is>
-          <t>You could fly these new routes.</t>
-        </is>
-      </c>
+      <c r="D22" s="26" t="inlineStr"/>
       <c r="E22" s="26" t="inlineStr">
         <is>
-          <t>Red Kite flies them for now, so fewer people are left wanting to fly with you each day: {list}</t>
+          <t>Build each formula by clicking the cells. The sheet adds up; work out the difference from the plan in your book.</t>
         </is>
       </c>
       <c r="F22" s="26" t="inlineStr"/>
-      <c r="G22" s="26" t="inlineStr">
-        <is>
-          <t>21 Oct 2026, section 9. A panel with a cyan left rail (a chance, not a loss). {list}: "Amsterdam 73 → 68 · Frankfurt 50 → 45 · …", figures from the game.</t>
-        </is>
-      </c>
+      <c r="G22" s="26" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="26" t="inlineStr">
         <is>
-          <t>flightTimes.line</t>
+          <t>review.unflown</t>
         </is>
       </c>
       <c r="B23" s="26" t="inlineStr">
         <is>
-          <t>Flight times sheet: the line under the grid (typing)</t>
+          <t>Sunday review, What happened: routes not flown yet (only once a plan screen has shown them)</t>
         </is>
       </c>
       <c r="C23" s="26" t="inlineStr"/>
-      <c r="D23" s="26" t="inlineStr"/>
+      <c r="D23" s="26" t="inlineStr">
+        <is>
+          <t>You could fly these new routes.</t>
+        </is>
+      </c>
       <c r="E23" s="26" t="inlineStr">
         <is>
-          <t>Work it out in your book. Write **Sum {n}** beside it, then type the time in **{cell}**.</t>
-        </is>
-      </c>
-      <c r="F23" s="26" t="inlineStr">
-        <is>
-          <t>Give me a hint</t>
-        </is>
-      </c>
+          <t>Red Kite flies them for now, so fewer people are left wanting to fly with you each day: {list}</t>
+        </is>
+      </c>
+      <c r="F23" s="26" t="inlineStr"/>
       <c r="G23" s="26" t="inlineStr">
         <is>
-          <t>21 Oct 2026, section 3.</t>
+          <t>21 Oct 2026, section 9. A panel with a cyan left rail (a chance, not a loss). {list}: "Amsterdam 73 → 68 · Frankfurt 50 → 45 · …", figures from the game.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="26" t="inlineStr">
         <is>
-          <t>flightTimes.build</t>
+          <t>flightTimes.line</t>
         </is>
       </c>
       <c r="B24" s="26" t="inlineStr">
         <is>
-          <t>Flight times sheet: the line while building the first sum</t>
+          <t>Flight times sheet: the line under the grid (typing)</t>
         </is>
       </c>
       <c r="C24" s="26" t="inlineStr"/>
       <c r="D24" s="26" t="inlineStr"/>
       <c r="E24" s="26" t="inlineStr">
         <is>
-          <t>Click the cells to build the formula. Then work it out in your book and type the time in **{cell}**.</t>
-        </is>
-      </c>
-      <c r="F24" s="26" t="inlineStr"/>
-      <c r="G24" s="26" t="inlineStr"/>
+          <t>Work it out in your book. Write **Sum {n}** beside it, then type the time in **{cell}**.</t>
+        </is>
+      </c>
+      <c r="F24" s="26" t="inlineStr">
+        <is>
+          <t>Give me a hint</t>
+        </is>
+      </c>
+      <c r="G24" s="26" t="inlineStr">
+        <is>
+          <t>21 Oct 2026, section 3.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="26" t="inlineStr">
         <is>
-          <t>flightTimes.formula</t>
+          <t>flightTimes.build</t>
         </is>
       </c>
       <c r="B25" s="26" t="inlineStr">
         <is>
-          <t>Flight times sheet: the line for a formula-only flight time (the third, when the decay makes it a Build)</t>
+          <t>Flight times sheet: the line while building the first sum</t>
         </is>
       </c>
       <c r="C25" s="26" t="inlineStr"/>
       <c r="D25" s="26" t="inlineStr"/>
       <c r="E25" s="26" t="inlineStr">
         <is>
-          <t>Click the cells to build the formula. The sheet works out the time in **{cell}**.</t>
+          <t>Click the cells to build the formula. Then work it out in your book and type the time in **{cell}**.</t>
         </is>
       </c>
       <c r="F25" s="26" t="inlineStr"/>
@@ -4789,19 +4789,19 @@
     <row r="26">
       <c r="A26" s="26" t="inlineStr">
         <is>
-          <t>flightTimes.f</t>
+          <t>flightTimes.formula</t>
         </is>
       </c>
       <c r="B26" s="26" t="inlineStr">
         <is>
-          <t>Flight times sheet: under the grid, when the game has worked out rows</t>
+          <t>Flight times sheet: the line for a formula-only flight time (the third, when the decay makes it a Build)</t>
         </is>
       </c>
       <c r="C26" s="26" t="inlineStr"/>
       <c r="D26" s="26" t="inlineStr"/>
       <c r="E26" s="26" t="inlineStr">
         <is>
-          <t>ƒ worked out for you</t>
+          <t>Click the cells to build the formula. The sheet works out the time in **{cell}**.</t>
         </is>
       </c>
       <c r="F26" s="26" t="inlineStr"/>
@@ -4810,19 +4810,19 @@
     <row r="27">
       <c r="A27" s="26" t="inlineStr">
         <is>
-          <t>flightTimes.footer</t>
+          <t>flightTimes.f</t>
         </is>
       </c>
       <c r="B27" s="26" t="inlineStr">
         <is>
-          <t>Flight times: the footer</t>
+          <t>Flight times sheet: under the grid, when the game has worked out rows</t>
         </is>
       </c>
       <c r="C27" s="26" t="inlineStr"/>
       <c r="D27" s="26" t="inlineStr"/>
       <c r="E27" s="26" t="inlineStr">
         <is>
-          <t>Work out the flight times on the sheet, then go on to the timetable.</t>
+          <t>ƒ worked out for you</t>
         </is>
       </c>
       <c r="F27" s="26" t="inlineStr"/>
@@ -4831,35 +4831,56 @@
     <row r="28">
       <c r="A28" s="26" t="inlineStr">
         <is>
+          <t>flightTimes.footer</t>
+        </is>
+      </c>
+      <c r="B28" s="26" t="inlineStr">
+        <is>
+          <t>Flight times: the footer</t>
+        </is>
+      </c>
+      <c r="C28" s="26" t="inlineStr"/>
+      <c r="D28" s="26" t="inlineStr"/>
+      <c r="E28" s="26" t="inlineStr">
+        <is>
+          <t>Work out the flight times on the sheet, then go on to the timetable.</t>
+        </is>
+      </c>
+      <c r="F28" s="26" t="inlineStr"/>
+      <c r="G28" s="26" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="26" t="inlineStr">
+        <is>
           <t>flightTimes.card</t>
         </is>
       </c>
-      <c r="B28" s="26" t="inlineStr">
+      <c r="B29" s="26" t="inlineStr">
         <is>
           <t>Flight times: the SUM card under the sheet, one row</t>
         </is>
       </c>
-      <c r="C28" s="26" t="inlineStr"/>
-      <c r="D28" s="26" t="inlineStr">
+      <c r="C29" s="26" t="inlineStr"/>
+      <c r="D29" s="26" t="inlineStr">
         <is>
           <t>Flight time = distance ÷ speed</t>
         </is>
       </c>
-      <c r="E28" s="26" t="inlineStr">
+      <c r="E29" s="26" t="inlineStr">
         <is>
           <t>{plane} to {route}</t>
         </is>
       </c>
-      <c r="F28" s="26" t="inlineStr"/>
-      <c r="G28" s="26" t="inlineStr">
+      <c r="F29" s="26" t="inlineStr"/>
+      <c r="G29" s="26" t="inlineStr">
         <is>
           <t>Gold SUM n tag · the rule · on the right in text-soft, the sum being worked.</t>
         </is>
       </c>
     </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Screen text the game reads by id (21 Oct 2026). {name} is filled by the game; **…** is bold; [A] and [B] are the A / B tags; | starts a new line. A row missing here falls back to the game's own copy of the same words.</t>
         </is>
@@ -5802,7 +5823,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
         <is>
@@ -11493,7 +11513,6 @@
         </is>
       </c>
     </row>
-    <row r="103"/>
     <row r="104">
       <c r="A104" s="17" t="inlineStr">
         <is>
@@ -12292,7 +12311,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="17" t="inlineStr">
         <is>
@@ -13337,7 +13355,6 @@
         </is>
       </c>
     </row>
-    <row r="26"/>
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
         <is>
@@ -15702,7 +15719,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
     <row r="21">
       <c r="A21" s="17" t="inlineStr">
         <is>
@@ -16136,7 +16152,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="17" t="inlineStr">
         <is>
@@ -21060,7 +21075,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
         <is>
@@ -21289,7 +21303,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="A20" s="17" t="inlineStr">
         <is>
@@ -22125,7 +22138,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
       <c r="A18" s="17" t="inlineStr">
         <is>
@@ -52759,7 +52771,6 @@
         </is>
       </c>
     </row>
-    <row r="56"/>
     <row r="57">
       <c r="A57" s="17" t="inlineStr">
         <is>
@@ -53612,7 +53623,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="17" t="inlineStr">
         <is>
@@ -54286,7 +54296,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="17" t="inlineStr">
         <is>
@@ -54640,7 +54649,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="17" t="inlineStr">
         <is>
@@ -55610,7 +55618,6 @@
         </is>
       </c>
     </row>
-    <row r="37"/>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
@@ -56106,7 +56113,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
@@ -62209,7 +62215,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
         <is>
@@ -63239,7 +63244,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="17" t="inlineStr">
         <is>
@@ -63621,7 +63625,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="17" t="inlineStr">
         <is>
@@ -64022,7 +64025,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="17" t="inlineStr">
         <is>

--- a/data/Airline-World-Workbook.xlsx
+++ b/data/Airline-World-Workbook.xlsx
@@ -2435,7 +2435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2845,6 +2845,72 @@
       <c r="D20" t="inlineStr">
         <is>
           <t>Beat 3: other costs each day (plain). Profit this week £11,350; cash £19,950 on Sunday; beat 4: 5 × £780 = £3,900, the whole bill, a day at a time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>flight_time</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>route</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>How long will it take? (21 Oct 2026, Bertie's order): the example route. Its distance comes from the Routes sheet (450 km).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>flight_time</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>plane</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Twin Otter</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>His plane in the example, drawn in his colours. Its speed comes from the Aircraft sheet (300 km/h): 1 h 30 to Amsterdam.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>flight_time</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>fasterPlane</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Saab 340</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>The faster plane beside it. Its speed comes from the Aircraft sheet (450 km/h): it lands at 1 hour, when the Twin Otter is two-thirds of the way.</t>
         </is>
       </c>
     </row>
@@ -4878,7 +4944,6 @@
         </is>
       </c>
     </row>
-    <row r="30"/>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
